--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1309"/>
+  <dimension ref="A1:F1310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606625476003</v>
+        <v>13.76606525790047</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404556981654</v>
+        <v>13.00404462813815</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647056839647</v>
+        <v>13.42646959612849</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -512,16 +512,16 @@
         <v>44321</v>
       </c>
       <c r="B5" t="n">
-        <v>12.93778419494629</v>
+        <v>12.93778324127197</v>
       </c>
       <c r="C5" t="n">
-        <v>13.33535974162644</v>
+        <v>13.3353587586459</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92949993209467</v>
+        <v>12.92949897903101</v>
       </c>
       <c r="E5" t="n">
-        <v>13.32707631094588</v>
+        <v>13.32707532857593</v>
       </c>
       <c r="F5" t="n">
         <v>876510</v>
@@ -532,16 +532,16 @@
         <v>44322</v>
       </c>
       <c r="B6" t="n">
-        <v>12.64788436889648</v>
+        <v>12.64788341522217</v>
       </c>
       <c r="C6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="D6" t="n">
-        <v>12.59818794458523</v>
+        <v>12.59818699465811</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="F6" t="n">
         <v>671078</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C9" t="n">
-        <v>12.54848908114925</v>
+        <v>12.5484900443603</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717518992304</v>
+        <v>12.21717612770272</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83233070373535</v>
+        <v>13.83232975006104</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677421586986</v>
+        <v>14.19677323706887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101675563449</v>
+        <v>13.50101582480272</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56728004455733</v>
+        <v>13.56727910915701</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889316558838</v>
+        <v>13.84889602661133</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24646865971732</v>
+        <v>14.24647160287482</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323705643921</v>
+        <v>13.68323988323951</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222720198366</v>
+        <v>14.12223011947429</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -712,16 +712,16 @@
         <v>44335</v>
       </c>
       <c r="B15" t="n">
-        <v>13.48444938659668</v>
+        <v>13.484450340271</v>
       </c>
       <c r="C15" t="n">
-        <v>13.94828817352505</v>
+        <v>13.9482891600039</v>
       </c>
       <c r="D15" t="n">
-        <v>13.36020625997589</v>
+        <v>13.36020720486323</v>
       </c>
       <c r="E15" t="n">
-        <v>13.77434862842691</v>
+        <v>13.77434960260406</v>
       </c>
       <c r="F15" t="n">
         <v>804661</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="D16" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21939945220947</v>
+        <v>13.21940040588379</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48445008239211</v>
+        <v>13.48445105518772</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -772,16 +772,16 @@
         <v>44340</v>
       </c>
       <c r="B18" t="n">
-        <v>13.42646980285645</v>
+        <v>13.42647075653076</v>
       </c>
       <c r="C18" t="n">
-        <v>14.02283349370625</v>
+        <v>14.02283448973993</v>
       </c>
       <c r="D18" t="n">
-        <v>13.32707529960082</v>
+        <v>13.3270762462152</v>
       </c>
       <c r="E18" t="n">
-        <v>13.40162117704254</v>
+        <v>13.40162212895187</v>
       </c>
       <c r="F18" t="n">
         <v>1040223</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.26909637451172</v>
+        <v>13.2690954208374</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182412334521</v>
+        <v>13.64182314288226</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253117759573</v>
+        <v>13.25253022511198</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162211069491</v>
+        <v>13.40162114749573</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -812,16 +812,16 @@
         <v>44342</v>
       </c>
       <c r="B20" t="n">
-        <v>13.27737808227539</v>
+        <v>13.27737903594971</v>
       </c>
       <c r="C20" t="n">
-        <v>13.51758091098307</v>
+        <v>13.51758188191043</v>
       </c>
       <c r="D20" t="n">
-        <v>13.26081288647065</v>
+        <v>13.26081383895514</v>
       </c>
       <c r="E20" t="n">
-        <v>13.36848915571444</v>
+        <v>13.36849011593299</v>
       </c>
       <c r="F20" t="n">
         <v>382946</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131836345614</v>
+        <v>13.45131738938882</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313733320078</v>
+        <v>13.15313638072602</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707605947365</v>
+        <v>13.32707509440325</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889347076416</v>
+        <v>13.02889442443848</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879186799003</v>
+        <v>13.31879284288401</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263019535136</v>
+        <v>12.96263114417541</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111560576475</v>
+        <v>13.21111657277715</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95434856414795</v>
+        <v>12.95435047149658</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879286133005</v>
+        <v>13.31879482233806</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808528379311</v>
+        <v>12.88808718138539</v>
       </c>
       <c r="E25" t="n">
-        <v>13.25253041314621</v>
+        <v>13.252532364398</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -952,16 +952,16 @@
         <v>44354</v>
       </c>
       <c r="B27" t="n">
-        <v>12.76384353637695</v>
+        <v>12.76384449005127</v>
       </c>
       <c r="C27" t="n">
-        <v>13.07859057440149</v>
+        <v>13.07859155159272</v>
       </c>
       <c r="D27" t="n">
-        <v>12.69758025748196</v>
+        <v>12.69758120620529</v>
       </c>
       <c r="E27" t="n">
-        <v>12.86323720646297</v>
+        <v>12.86323816756367</v>
       </c>
       <c r="F27" t="n">
         <v>662018</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95434856414795</v>
+        <v>12.95435047149658</v>
       </c>
       <c r="C30" t="n">
-        <v>13.00404498420033</v>
+        <v>13.00404689886607</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72242916333352</v>
+        <v>12.72243103653523</v>
       </c>
       <c r="E30" t="n">
-        <v>12.82182283560928</v>
+        <v>12.82182472344533</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667205810547</v>
+        <v>12.84667110443115</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555932114021</v>
+        <v>12.75555837422966</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1132,16 +1132,16 @@
         <v>44365</v>
       </c>
       <c r="B36" t="n">
-        <v>12.65616607666016</v>
+        <v>12.65616703033447</v>
       </c>
       <c r="C36" t="n">
-        <v>12.74727715234998</v>
+        <v>12.74727811288975</v>
       </c>
       <c r="D36" t="n">
-        <v>12.54848980475637</v>
+        <v>12.548490750317</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6396008804462</v>
+        <v>12.63960183287228</v>
       </c>
       <c r="F36" t="n">
         <v>365879</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949802398682</v>
       </c>
       <c r="C39" t="n">
-        <v>12.49051027219619</v>
+        <v>12.49050830483521</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949802398682</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424782130851</v>
+        <v>12.42424586438442</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.33313655853271</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C40" t="n">
-        <v>12.5153587118295</v>
+        <v>12.51535967959436</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717602295992</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717602295992</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657123565674</v>
+        <v>12.31657028198242</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424750758757</v>
+        <v>12.42424654557586</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293359717298</v>
+        <v>12.09293266081497</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596490947851</v>
+        <v>12.41596394810812</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1252,16 +1252,16 @@
         <v>44375</v>
       </c>
       <c r="B42" t="n">
-        <v>12.1757640838623</v>
+        <v>12.17576217651367</v>
       </c>
       <c r="C42" t="n">
-        <v>12.42424955767507</v>
+        <v>12.42424761140088</v>
       </c>
       <c r="D42" t="n">
-        <v>12.13435025431242</v>
+        <v>12.13434835345131</v>
       </c>
       <c r="E42" t="n">
-        <v>12.34142106640415</v>
+        <v>12.34141913310514</v>
       </c>
       <c r="F42" t="n">
         <v>425086</v>
@@ -1332,16 +1332,16 @@
         <v>44379</v>
       </c>
       <c r="B46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="C46" t="n">
-        <v>12.74727718624468</v>
+        <v>12.7472762129657</v>
       </c>
       <c r="D46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51535861343547</v>
+        <v>12.51535765786391</v>
       </c>
       <c r="F46" t="n">
         <v>443206</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.3414192199707</v>
+        <v>12.34141731262207</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54849000108201</v>
+        <v>12.54848806173089</v>
       </c>
       <c r="D49" t="n">
-        <v>12.3414192199707</v>
+        <v>12.34141731262207</v>
       </c>
       <c r="E49" t="n">
-        <v>12.4076825023763</v>
+        <v>12.40768058478677</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.3414192199707</v>
+        <v>12.34141731262207</v>
       </c>
       <c r="C50" t="n">
-        <v>12.65616627467043</v>
+        <v>12.65616431867809</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576226221325</v>
+        <v>12.17576038046666</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25859074109198</v>
+        <v>12.25858884654436</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717739105225</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020776395842</v>
+        <v>12.5402087428486</v>
       </c>
       <c r="D51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717739105225</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424805662318</v>
+        <v>12.42424902646154</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1452,16 +1452,16 @@
         <v>44390</v>
       </c>
       <c r="B52" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C52" t="n">
-        <v>12.30828606118626</v>
+        <v>12.3082870318438</v>
       </c>
       <c r="D52" t="n">
-        <v>12.05151888146321</v>
+        <v>12.05151983187154</v>
       </c>
       <c r="E52" t="n">
-        <v>12.2171749922247</v>
+        <v>12.21717595569702</v>
       </c>
       <c r="F52" t="n">
         <v>433935</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949802398682</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16747978390493</v>
+        <v>12.16747786742398</v>
       </c>
       <c r="D55" t="n">
-        <v>11.89414654986496</v>
+        <v>11.8941446764363</v>
       </c>
       <c r="E55" t="n">
-        <v>12.06808610757341</v>
+        <v>12.0680842067478</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303508758545</v>
       </c>
       <c r="C58" t="n">
-        <v>11.67050888395185</v>
+        <v>11.6705098973207</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303508758545</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970139416144</v>
+        <v>11.52970239530374</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879135131836</v>
+        <v>10.85879230499268</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525663025563</v>
+        <v>11.16525761084529</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798385706797</v>
+        <v>10.71798479837585</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76768027708593</v>
+        <v>10.76768122275841</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1692,16 +1692,16 @@
         <v>44406</v>
       </c>
       <c r="B64" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C64" t="n">
-        <v>11.45515649173092</v>
+        <v>11.45515552548068</v>
       </c>
       <c r="D64" t="n">
-        <v>11.01616629311581</v>
+        <v>11.01616536389469</v>
       </c>
       <c r="E64" t="n">
-        <v>11.33919678522236</v>
+        <v>11.3391958287534</v>
       </c>
       <c r="F64" t="n">
         <v>449738</v>
@@ -1712,16 +1712,16 @@
         <v>44407</v>
       </c>
       <c r="B65" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626846313477</v>
       </c>
       <c r="C65" t="n">
-        <v>11.92727785279649</v>
+        <v>11.9272788379407</v>
       </c>
       <c r="D65" t="n">
-        <v>11.09899471480624</v>
+        <v>11.09899563153766</v>
       </c>
       <c r="E65" t="n">
-        <v>11.2066709901555</v>
+        <v>11.20667191578054</v>
       </c>
       <c r="F65" t="n">
         <v>977013</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727827162325</v>
+        <v>11.92727731662251</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61253120072406</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61253120072406</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273265838623</v>
+        <v>11.85273170471191</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556114342346</v>
+        <v>11.93556018308474</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030846651876</v>
+        <v>11.43030754683281</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727854457107</v>
+        <v>11.92727758489877</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515632629395</v>
+        <v>11.45515537261963</v>
       </c>
       <c r="C68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.85273087597138</v>
       </c>
       <c r="D68" t="n">
-        <v>11.44687372799754</v>
+        <v>11.44687277501277</v>
       </c>
       <c r="E68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.85273087597138</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283187866211</v>
+        <v>11.56283378601074</v>
       </c>
       <c r="C70" t="n">
-        <v>11.595963934121</v>
+        <v>11.59596584693494</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495278588257</v>
+        <v>11.21495463584676</v>
       </c>
       <c r="E70" t="n">
-        <v>11.28121606462938</v>
+        <v>11.28121792552403</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1832,16 +1832,16 @@
         <v>44417</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C71" t="n">
-        <v>12.03495292569004</v>
+        <v>12.0349548369848</v>
       </c>
       <c r="D71" t="n">
-        <v>11.59596360543989</v>
+        <v>11.59596544701789</v>
       </c>
       <c r="E71" t="n">
-        <v>11.62909482778872</v>
+        <v>11.62909667462835</v>
       </c>
       <c r="F71" t="n">
         <v>438360</v>
@@ -1872,16 +1872,16 @@
         <v>44419</v>
       </c>
       <c r="B73" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.01838819869508</v>
       </c>
       <c r="D73" t="n">
-        <v>11.71192469562211</v>
+        <v>11.71192375590401</v>
       </c>
       <c r="E73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.01838819869508</v>
       </c>
       <c r="F73" t="n">
         <v>262426</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859195709229</v>
+        <v>11.43859100341797</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727860666524</v>
+        <v>11.92727761224746</v>
       </c>
       <c r="D77" t="n">
-        <v>11.32263141169959</v>
+        <v>11.3226304676933</v>
       </c>
       <c r="E77" t="n">
-        <v>11.8444501211968</v>
+        <v>11.84444913368471</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -1992,16 +1992,16 @@
         <v>44427</v>
       </c>
       <c r="B79" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C79" t="n">
-        <v>12.19232719973869</v>
+        <v>12.19232816125147</v>
       </c>
       <c r="D79" t="n">
-        <v>11.54626628734149</v>
+        <v>11.54626719790453</v>
       </c>
       <c r="E79" t="n">
-        <v>11.59596353665541</v>
+        <v>11.59596445113769</v>
       </c>
       <c r="F79" t="n">
         <v>301405</v>
@@ -2012,16 +2012,16 @@
         <v>44428</v>
       </c>
       <c r="B80" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>12.12606392326314</v>
+        <v>12.12606487955025</v>
       </c>
       <c r="D80" t="n">
-        <v>11.87758017320638</v>
+        <v>11.87758110989754</v>
       </c>
       <c r="E80" t="n">
-        <v>12.05980231112949</v>
+        <v>12.05980326219108</v>
       </c>
       <c r="F80" t="n">
         <v>324055</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C82" t="n">
-        <v>12.32485465783526</v>
+        <v>12.32485367100113</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990390400258</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E82" t="n">
-        <v>12.010106754765</v>
+        <v>12.0101057931323</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010696614738</v>
+        <v>12.01010503212249</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071245175947</v>
+        <v>11.91071053374038</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848987579346</v>
+        <v>11.72848892211914</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697532092373</v>
+        <v>11.97697434704441</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081359852429</v>
+        <v>11.62081265360541</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444958375337</v>
+        <v>11.84444862065007</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C86" t="n">
-        <v>11.96869289533168</v>
+        <v>11.9686919095953</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55455048079756</v>
+        <v>11.55454952916977</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101495216464</v>
+        <v>11.86101397529656</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="D87" t="n">
-        <v>11.38889235890981</v>
+        <v>11.388893311891</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737827423737</v>
+        <v>11.63737923751014</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576244764404</v>
+        <v>11.35576338760633</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313597332352</v>
+        <v>11.51313692631225</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465129852295</v>
+        <v>11.26465034484863</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596437620398</v>
+        <v>11.59596339448043</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838801724993</v>
+        <v>11.19838706918552</v>
       </c>
       <c r="E90" t="n">
-        <v>11.35576237408096</v>
+        <v>11.3557614126931</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566040039062</v>
+        <v>11.64566135406494</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67050902600049</v>
+        <v>11.67050998170969</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010503811302</v>
+        <v>11.19010595448147</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313550669932</v>
+        <v>11.51313644952104</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909565647244</v>
+        <v>11.62909661287153</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38061022289286</v>
+        <v>11.38061115885603</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485335576816</v>
+        <v>11.50485430194932</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444975488591</v>
+        <v>11.84444877938214</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545954443371</v>
+        <v>11.40545860508498</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596513833651</v>
+        <v>11.59596418329782</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364284515381</v>
+        <v>11.70364189147949</v>
       </c>
       <c r="C96" t="n">
-        <v>11.83616775881459</v>
+        <v>11.83616679434145</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172258190522</v>
+        <v>11.47172164712899</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313724155255</v>
+        <v>11.51313630340163</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444903317125</v>
+        <v>11.84445000728142</v>
       </c>
       <c r="D97" t="n">
-        <v>11.587681001457</v>
+        <v>11.58768195445007</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364153619761</v>
+        <v>11.7036424987275</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192413433229</v>
+        <v>11.71192509754336</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313595390284</v>
+        <v>11.51313690076518</v>
       </c>
       <c r="E98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C100" t="n">
-        <v>11.6456602402011</v>
+        <v>11.64566120833546</v>
       </c>
       <c r="D100" t="n">
-        <v>11.0575799923214</v>
+        <v>11.05758091156711</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26465075999399</v>
+        <v>11.26465169645404</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81960010528564</v>
+        <v>11.81959915161133</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05151950451265</v>
+        <v>12.05151853212572</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58768070605864</v>
+        <v>11.58767977109694</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535780774861</v>
+        <v>11.69535686409888</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.3414192199707</v>
+        <v>12.34141731262207</v>
       </c>
       <c r="C103" t="n">
-        <v>12.3414192199707</v>
+        <v>12.34141731262207</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677207310991</v>
+        <v>11.73677025920863</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76162069999063</v>
+        <v>11.76161888224903</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.05152034759521</v>
+        <v>12.0515193939209</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424809845207</v>
+        <v>12.42424711528264</v>
       </c>
       <c r="D104" t="n">
-        <v>11.99354049373239</v>
+        <v>11.9935395446462</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34141961690932</v>
+        <v>12.34141864029437</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2512,16 +2512,16 @@
         <v>44466</v>
       </c>
       <c r="B105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C105" t="n">
-        <v>12.16748009742714</v>
+        <v>12.16747912115709</v>
       </c>
       <c r="D105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="E105" t="n">
-        <v>12.05152038930021</v>
+        <v>12.05151942233431</v>
       </c>
       <c r="F105" t="n">
         <v>207539</v>
@@ -2532,16 +2532,16 @@
         <v>44467</v>
       </c>
       <c r="B106" t="n">
-        <v>11.9438419342041</v>
+        <v>11.94384288787842</v>
       </c>
       <c r="C106" t="n">
-        <v>12.09293285183314</v>
+        <v>12.09293381741185</v>
       </c>
       <c r="D106" t="n">
-        <v>11.74505459881269</v>
+        <v>11.74505553661453</v>
       </c>
       <c r="E106" t="n">
-        <v>11.86101346170553</v>
+        <v>11.86101440876628</v>
       </c>
       <c r="F106" t="n">
         <v>282337</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.76162152260959</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889282102754</v>
+        <v>11.38889375767189</v>
       </c>
       <c r="E109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.76162152260959</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545977752449</v>
+        <v>11.40545794086782</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596350798623</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010550156678</v>
+        <v>12.01010650652883</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444855256879</v>
+        <v>11.84444954366927</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2652,16 +2652,16 @@
         <v>44475</v>
       </c>
       <c r="B112" t="n">
-        <v>11.38061046600342</v>
+        <v>11.3806095123291</v>
       </c>
       <c r="C112" t="n">
-        <v>11.62909590489109</v>
+        <v>11.62909493039415</v>
       </c>
       <c r="D112" t="n">
-        <v>11.18182311349852</v>
+        <v>11.18182217648222</v>
       </c>
       <c r="E112" t="n">
-        <v>11.40545909310929</v>
+        <v>11.4054581373527</v>
       </c>
       <c r="F112" t="n">
         <v>433409</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677192873634</v>
+        <v>11.73677289399093</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687444589615</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687444589615</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667045593262</v>
+        <v>12.02667236328125</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495305356509</v>
+        <v>12.03495496222729</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768213657487</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768213657487</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2772,16 +2772,16 @@
         <v>44484</v>
       </c>
       <c r="B118" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C118" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="D118" t="n">
-        <v>11.84444811888313</v>
+        <v>11.84444905296142</v>
       </c>
       <c r="E118" t="n">
-        <v>11.92727659034935</v>
+        <v>11.92727753095967</v>
       </c>
       <c r="F118" t="n">
         <v>256632</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22545936636416</v>
+        <v>12.22546032458287</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727751178659</v>
+        <v>11.92727844663413</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465103721058</v>
+        <v>12.08465198439289</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2832,16 +2832,16 @@
         <v>44489</v>
       </c>
       <c r="B121" t="n">
-        <v>11.8030366897583</v>
+        <v>11.80303478240967</v>
       </c>
       <c r="C121" t="n">
-        <v>12.20061226827963</v>
+        <v>12.20061029668353</v>
       </c>
       <c r="D121" t="n">
-        <v>11.7284908006893</v>
+        <v>11.72848890538714</v>
       </c>
       <c r="E121" t="n">
-        <v>12.01839009345022</v>
+        <v>12.01838815130088</v>
       </c>
       <c r="F121" t="n">
         <v>129580</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D122" t="n">
-        <v>11.41374237633313</v>
+        <v>11.41374053834268</v>
       </c>
       <c r="E122" t="n">
-        <v>11.6787930277491</v>
+        <v>11.67879114707672</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81959932971621</v>
+        <v>11.81960031587073</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212460723993</v>
+        <v>11.13212553603579</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76161948371394</v>
+        <v>11.76162046503097</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172059900599</v>
+        <v>11.47172147956523</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141784912412</v>
+        <v>11.52141873349808</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.05152034759521</v>
+        <v>12.0515193939209</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030853686361</v>
+        <v>12.25030756745856</v>
       </c>
       <c r="D126" t="n">
-        <v>11.84444955982386</v>
+        <v>11.8444486225357</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717647850966</v>
+        <v>12.21717551172646</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980324204109</v>
+        <v>12.0598042338624</v>
       </c>
       <c r="D127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010598889097</v>
+        <v>12.01010697662508</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72848826202277</v>
+        <v>11.72848924057554</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596337525811</v>
+        <v>11.59596434275382</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -3012,16 +3012,16 @@
         <v>44503</v>
       </c>
       <c r="B130" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C130" t="n">
-        <v>12.01838773060111</v>
+        <v>12.01838963926511</v>
       </c>
       <c r="D130" t="n">
-        <v>11.43859009124023</v>
+        <v>11.43859190782543</v>
       </c>
       <c r="E130" t="n">
-        <v>11.50485253593789</v>
+        <v>11.50485436304635</v>
       </c>
       <c r="F130" t="n">
         <v>128737</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727688367788</v>
+        <v>11.92727787522379</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899381298753</v>
+        <v>11.09899473567608</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81959978490659</v>
+        <v>11.81960076750101</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.05152034759521</v>
+        <v>12.0515193939209</v>
       </c>
       <c r="C134" t="n">
-        <v>12.05152034759521</v>
+        <v>12.0515193939209</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283288901272</v>
+        <v>11.56283197400976</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707602741238</v>
+        <v>11.68707510257767</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929850548507</v>
+        <v>11.86929758022087</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05152067045827</v>
+        <v>12.05151973098904</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232940673828</v>
+        <v>12.19232845306396</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374406605356</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465229112388</v>
+        <v>12.08465134587198</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374406605356</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3152,16 +3152,16 @@
         <v>44512</v>
       </c>
       <c r="B137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C137" t="n">
-        <v>12.23374338219328</v>
+        <v>12.23374240060653</v>
       </c>
       <c r="D137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="E137" t="n">
-        <v>12.14263230183227</v>
+        <v>12.14263132755591</v>
       </c>
       <c r="F137" t="n">
         <v>236720</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576211321089</v>
+        <v>12.17576306753439</v>
       </c>
       <c r="D138" t="n">
-        <v>11.6870755084975</v>
+        <v>11.68707642451825</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242888520996</v>
+        <v>11.90242981810988</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.05152034759521</v>
+        <v>12.0515193939209</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364177700074</v>
+        <v>12.52364078596598</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131833364097</v>
+        <v>11.81131739897459</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424809845207</v>
+        <v>12.42424711528264</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.33313655853271</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566145832273</v>
+        <v>12.46566242224469</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010607508077</v>
+        <v>12.01010700377637</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05151989822239</v>
+        <v>12.05152083012037</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.9874792098999</v>
+        <v>12.98748016357422</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374165513303</v>
+        <v>13.05374261367302</v>
       </c>
       <c r="D142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="E142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3272,16 +3272,16 @@
         <v>44523</v>
       </c>
       <c r="B143" t="n">
-        <v>12.79697513580322</v>
+        <v>12.79697418212891</v>
       </c>
       <c r="C143" t="n">
-        <v>13.33535985473798</v>
+        <v>13.33535886094139</v>
       </c>
       <c r="D143" t="n">
-        <v>12.65616679909195</v>
+        <v>12.65616585591115</v>
       </c>
       <c r="E143" t="n">
-        <v>13.0371779841559</v>
+        <v>13.03717701258084</v>
       </c>
       <c r="F143" t="n">
         <v>747456</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.44081401824951</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89637027711621</v>
+        <v>12.89636928852036</v>
       </c>
       <c r="D144" t="n">
-        <v>12.44081401824951</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010698872958</v>
+        <v>12.83010600521327</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010578155518</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010578155518</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283299592728</v>
+        <v>12.38283207549919</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131843161235</v>
+        <v>12.63131749271409</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808597564697</v>
+        <v>11.24808406829834</v>
       </c>
       <c r="C150" t="n">
-        <v>11.8196010912967</v>
+        <v>11.81959908703571</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182352238896</v>
+        <v>11.18182162627651</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333863803869</v>
+        <v>11.75333664501388</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.76990413665771</v>
+        <v>11.76990222930908</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212630386892</v>
+        <v>11.95212436699063</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485431683857</v>
+        <v>11.50485245244207</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970294548939</v>
+        <v>11.52970107706609</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3472,16 +3472,16 @@
         <v>44537</v>
       </c>
       <c r="B153" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C153" t="n">
-        <v>12.09293277284322</v>
+        <v>12.09293469334588</v>
       </c>
       <c r="D153" t="n">
-        <v>11.78646834198837</v>
+        <v>11.78647021382081</v>
       </c>
       <c r="E153" t="n">
-        <v>11.89414543875028</v>
+        <v>11.89414732768312</v>
       </c>
       <c r="F153" t="n">
         <v>308042</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626857588447</v>
+        <v>12.36626761187925</v>
       </c>
       <c r="D154" t="n">
-        <v>11.8941471338307</v>
+        <v>11.89414620662944</v>
       </c>
       <c r="E154" t="n">
-        <v>12.01010684466293</v>
+        <v>12.0101059084221</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000495910645</v>
+        <v>12.30000591278076</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626824363818</v>
+        <v>12.36626920245019</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778279902904</v>
+        <v>12.11778373857486</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668737329261</v>
+        <v>12.26687468403161</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485485076904</v>
+        <v>12.32485389709473</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303589683919</v>
+        <v>12.62303492009218</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374376753817</v>
+        <v>12.23374282091386</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000539004934</v>
+        <v>12.30000443829783</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3592,16 +3592,16 @@
         <v>44545</v>
       </c>
       <c r="B159" t="n">
-        <v>12.54849052429199</v>
+        <v>12.54848957061768</v>
       </c>
       <c r="C159" t="n">
-        <v>12.54849052429199</v>
+        <v>12.54848957061768</v>
       </c>
       <c r="D159" t="n">
-        <v>12.05152046246946</v>
+        <v>12.05151954656443</v>
       </c>
       <c r="E159" t="n">
-        <v>12.32485453738304</v>
+        <v>12.32485360070486</v>
       </c>
       <c r="F159" t="n">
         <v>233455</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606685638428</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606685638428</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25858939858541</v>
+        <v>12.25859120464801</v>
       </c>
       <c r="E161" t="n">
-        <v>12.42424633820085</v>
+        <v>12.42424816866975</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202507019043</v>
+        <v>13.06202411651611</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16141957643138</v>
+        <v>13.16141861550016</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273204678879</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273204678879</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.7224292755127</v>
+        <v>12.72243022918701</v>
       </c>
       <c r="C163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.0620259287079</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737864826929</v>
+        <v>12.45737958207539</v>
       </c>
       <c r="E163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.0620259287079</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.8218240737915</v>
       </c>
       <c r="C164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.8218240737915</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43252926346614</v>
+        <v>12.43253111290434</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72242849935444</v>
+        <v>12.72243039191747</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.83838939666748</v>
+        <v>12.8383903503418</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495625873149</v>
+        <v>12.85495721363644</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020834813482</v>
+        <v>12.54020927965935</v>
       </c>
       <c r="E165" t="n">
-        <v>12.81354160008474</v>
+        <v>12.81354255191329</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828866415499</v>
+        <v>13.12828770746268</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384435172153</v>
+        <v>12.76384342158722</v>
       </c>
       <c r="E166" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="D167" t="n">
-        <v>12.92121704861566</v>
+        <v>12.9212161070132</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C168" t="n">
-        <v>13.37677327132853</v>
+        <v>13.3767722965285</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04546018437347</v>
+        <v>13.04545923371708</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3812,16 +3812,16 @@
         <v>44564</v>
       </c>
       <c r="B170" t="n">
-        <v>12.92949867248535</v>
+        <v>12.92949962615967</v>
       </c>
       <c r="C170" t="n">
-        <v>13.6004090584999</v>
+        <v>13.60041006166028</v>
       </c>
       <c r="D170" t="n">
-        <v>12.78869118285713</v>
+        <v>12.78869212614555</v>
       </c>
       <c r="E170" t="n">
-        <v>13.16970149539972</v>
+        <v>13.1697024667913</v>
       </c>
       <c r="F170" t="n">
         <v>289922</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98747925372556</v>
+        <v>12.98748125957582</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92949857373721</v>
+        <v>12.92950057063265</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.69535827636719</v>
+        <v>11.69535732269287</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78646935368979</v>
+        <v>11.78646839258601</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657009304013</v>
+        <v>11.49656915557559</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333812849712</v>
+        <v>11.75333717009495</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586465533357</v>
+        <v>11.88586274131581</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202580731284</v>
+        <v>11.42202396798849</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55455071693529</v>
+        <v>11.55454885627004</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818730142888</v>
+        <v>11.77818633138246</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798528351884</v>
+        <v>11.53798433325535</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333867333973</v>
+        <v>11.75333770533982</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4032,16 +4032,16 @@
         <v>44579</v>
       </c>
       <c r="B181" t="n">
-        <v>11.49656963348389</v>
+        <v>11.4965705871582</v>
       </c>
       <c r="C181" t="n">
-        <v>11.72020643480869</v>
+        <v>11.72020740703434</v>
       </c>
       <c r="D181" t="n">
-        <v>11.46343840961558</v>
+        <v>11.46343936054156</v>
       </c>
       <c r="E181" t="n">
-        <v>11.57939810924015</v>
+        <v>11.57939906978533</v>
       </c>
       <c r="F181" t="n">
         <v>311203</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111549377441</v>
+        <v>11.5711145401001</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101391022536</v>
+        <v>11.86101293265804</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828701814372</v>
+        <v>11.488286071296</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707519322319</v>
+        <v>11.68707422999165</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616828918457</v>
+        <v>11.83616638183594</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84445088861673</v>
+        <v>11.84444897993339</v>
       </c>
       <c r="D186" t="n">
-        <v>11.46344049651252</v>
+        <v>11.4634386492274</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172309594468</v>
+        <v>11.47172124732486</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4212,16 +4212,16 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C190" t="n">
-        <v>11.78646910353603</v>
+        <v>11.78647006600311</v>
       </c>
       <c r="D190" t="n">
-        <v>11.45515602647001</v>
+        <v>11.45515696188252</v>
       </c>
       <c r="E190" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="F190" t="n">
         <v>318367</v>
@@ -4292,16 +4292,16 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C194" t="n">
-        <v>11.62909605149376</v>
+        <v>11.6290950705716</v>
       </c>
       <c r="D194" t="n">
-        <v>11.19838845129467</v>
+        <v>11.19838750670299</v>
       </c>
       <c r="E194" t="n">
-        <v>11.48828771756607</v>
+        <v>11.48828674852119</v>
       </c>
       <c r="F194" t="n">
         <v>381155</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596538543701</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697476418123</v>
+        <v>11.97697574919057</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970198234322</v>
+        <v>11.52970293056798</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364153619761</v>
+        <v>11.7036424987275</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313689072104</v>
+        <v>11.51313503672479</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596350798623</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788276672363</v>
+        <v>11.82788467407227</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84445070485071</v>
       </c>
       <c r="D198" t="n">
-        <v>11.6290954224653</v>
+        <v>11.62909729775775</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84445070485071</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4392,16 +4392,16 @@
         <v>44603</v>
       </c>
       <c r="B199" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626846313477</v>
       </c>
       <c r="C199" t="n">
-        <v>11.81960074527618</v>
+        <v>11.8196017215267</v>
       </c>
       <c r="D199" t="n">
-        <v>11.52141888217337</v>
+        <v>11.5214198337953</v>
       </c>
       <c r="E199" t="n">
-        <v>11.71192446992692</v>
+        <v>11.71192543728382</v>
       </c>
       <c r="F199" t="n">
         <v>419186</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424613952637</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444812437002</v>
+        <v>11.84444909778491</v>
       </c>
       <c r="D200" t="n">
-        <v>11.5131350705226</v>
+        <v>11.51313601670912</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61252956919649</v>
+        <v>11.61253052355157</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.69535827636719</v>
+        <v>11.69535732269287</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81959961507706</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394362074808</v>
+        <v>11.65394267045083</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81959961507706</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4512,16 +4512,16 @@
         <v>44613</v>
       </c>
       <c r="B205" t="n">
-        <v>11.49656963348389</v>
+        <v>11.4965705871582</v>
       </c>
       <c r="C205" t="n">
-        <v>11.92727720811385</v>
+        <v>11.92727819751663</v>
       </c>
       <c r="D205" t="n">
-        <v>11.49656963348389</v>
+        <v>11.4965705871582</v>
       </c>
       <c r="E205" t="n">
-        <v>11.92727720811385</v>
+        <v>11.92727819751663</v>
       </c>
       <c r="F205" t="n">
         <v>449843</v>
@@ -4532,16 +4532,16 @@
         <v>44614</v>
       </c>
       <c r="B206" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626846313477</v>
       </c>
       <c r="C206" t="n">
-        <v>11.72848966667094</v>
+        <v>11.72849063539606</v>
       </c>
       <c r="D206" t="n">
-        <v>11.51313628380136</v>
+        <v>11.51313723473918</v>
       </c>
       <c r="E206" t="n">
-        <v>11.51313628380136</v>
+        <v>11.51313723473918</v>
       </c>
       <c r="F206" t="n">
         <v>213649</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="D210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="E210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4632,16 +4632,16 @@
         <v>44623</v>
       </c>
       <c r="B211" t="n">
-        <v>12.70586395263672</v>
+        <v>12.7058629989624</v>
       </c>
       <c r="C211" t="n">
-        <v>13.12828895937023</v>
+        <v>13.12828797398962</v>
       </c>
       <c r="D211" t="n">
-        <v>12.59818767545336</v>
+        <v>12.59818672986099</v>
       </c>
       <c r="E211" t="n">
-        <v>13.12828895937023</v>
+        <v>13.12828797398962</v>
       </c>
       <c r="F211" t="n">
         <v>452688</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.8383903503418</v>
       </c>
       <c r="C212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.8383903503418</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000549162855</v>
+        <v>12.30000640531008</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586448620852</v>
+        <v>12.70586543003849</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.73899555206299</v>
+        <v>12.73899459838867</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202605741871</v>
+        <v>13.06202507956149</v>
       </c>
       <c r="D213" t="n">
-        <v>12.1095005710341</v>
+        <v>12.10949966448541</v>
       </c>
       <c r="E213" t="n">
-        <v>12.846673496743</v>
+        <v>12.84667253500764</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.15919780731201</v>
+        <v>12.1591968536377</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697538601619</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="D214" t="n">
-        <v>12.1426326098286</v>
+        <v>12.14263165745353</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697538601619</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081198328363</v>
+        <v>12.44081293822948</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293289679869</v>
+        <v>12.09293382504164</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576136960524</v>
+        <v>12.17576230420604</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919617434651</v>
+        <v>12.15919710767578</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111473316551</v>
+        <v>12.39111568429664</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45737956512522</v>
+        <v>12.45737856768</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990390400258</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081353562843</v>
+        <v>12.44081253950964</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242825840982</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242825840982</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303523023652</v>
+        <v>11.80303620722139</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515612194091</v>
+        <v>11.45515707013042</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626719808914</v>
+        <v>11.54626815382028</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.79475212097168</v>
+        <v>11.794753074646</v>
       </c>
       <c r="C220" t="n">
-        <v>11.80303471876141</v>
+        <v>11.80303567310543</v>
       </c>
       <c r="D220" t="n">
-        <v>11.4634382233306</v>
+        <v>11.46343915021626</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596394882123</v>
+        <v>11.59596488642237</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222858428955</v>
+        <v>11.6622257232666</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84445076288966</v>
+        <v>11.84444785716326</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404668618553</v>
+        <v>11.36404389831371</v>
       </c>
       <c r="E222" t="n">
-        <v>11.5379862654414</v>
+        <v>11.53798343489805</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4872,16 +4872,16 @@
         <v>44641</v>
       </c>
       <c r="B223" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C223" t="n">
-        <v>11.75333787904653</v>
+        <v>11.75333883880816</v>
       </c>
       <c r="D223" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="E223" t="n">
-        <v>11.69535802814715</v>
+        <v>11.69535898317423</v>
       </c>
       <c r="F223" t="n">
         <v>273488</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.96869277954102</v>
+        <v>11.9686918258667</v>
       </c>
       <c r="C225" t="n">
-        <v>12.20889396295617</v>
+        <v>12.20889299014245</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798517189504</v>
+        <v>11.53798425253982</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677253034297</v>
+        <v>11.73677159514823</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424613952637</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C227" t="n">
-        <v>11.7864682775339</v>
+        <v>11.78646924618382</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030659901801</v>
+        <v>11.43030753839741</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535720853013</v>
+        <v>11.69535816969225</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C230" t="n">
-        <v>11.89414566071079</v>
+        <v>11.8941466495024</v>
       </c>
       <c r="D230" t="n">
-        <v>11.35576183119625</v>
+        <v>11.3557627752306</v>
       </c>
       <c r="E230" t="n">
-        <v>11.84444841017465</v>
+        <v>11.84444939483481</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374111175537</v>
+        <v>11.413743019104</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283396691093</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23151896512815</v>
+        <v>11.23152084202566</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283396691093</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374111175537</v>
+        <v>11.413743019104</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909531428845</v>
+        <v>11.62909725762489</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636759097204</v>
+        <v>11.256369472022</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313561513094</v>
+        <v>11.51313753908938</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283176669787</v>
+        <v>11.56283272794649</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919580362721</v>
+        <v>11.33919674628439</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41374084726044</v>
+        <v>11.41374179611474</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5092,16 +5092,16 @@
         <v>44656</v>
       </c>
       <c r="B234" t="n">
-        <v>11.19010639190674</v>
+        <v>11.19010448455811</v>
       </c>
       <c r="C234" t="n">
-        <v>11.57939935443586</v>
+        <v>11.57939738073242</v>
       </c>
       <c r="D234" t="n">
-        <v>11.19010639190674</v>
+        <v>11.19010448455811</v>
       </c>
       <c r="E234" t="n">
-        <v>11.52141949838869</v>
+        <v>11.52141753456788</v>
       </c>
       <c r="F234" t="n">
         <v>602179</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444839477539</v>
+        <v>11.02444934844971</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495314278623</v>
+        <v>11.21495411294023</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192349740629</v>
+        <v>10.89192443961648</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495314278623</v>
+        <v>11.21495411294023</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364219665527</v>
+        <v>10.88364028930664</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394493813262</v>
+        <v>10.83394303949338</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192295074463</v>
+        <v>10.89192390441895</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303402115581</v>
+        <v>10.98303498280762</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313478249707</v>
+        <v>10.69313571876591</v>
       </c>
       <c r="E237" t="n">
-        <v>10.93333677105118</v>
+        <v>10.9333377283516</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5172,16 +5172,16 @@
         <v>44662</v>
       </c>
       <c r="B238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="C238" t="n">
-        <v>11.07414542638119</v>
+        <v>11.07414640045497</v>
       </c>
       <c r="D238" t="n">
-        <v>10.80909480476127</v>
+        <v>10.80909575552138</v>
       </c>
       <c r="E238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="F238" t="n">
         <v>406860</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798515319824</v>
+        <v>10.71798419952393</v>
       </c>
       <c r="C239" t="n">
-        <v>11.00788443907316</v>
+        <v>11.00788345960393</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798515319824</v>
+        <v>10.71798419952393</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333855177485</v>
+        <v>10.93333757893863</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000556945801</v>
+        <v>10.66000366210938</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566254625604</v>
+        <v>10.82566060926712</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000556945801</v>
+        <v>10.66000366210938</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566254625604</v>
+        <v>10.82566060926712</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5292,16 +5292,16 @@
         <v>44671</v>
       </c>
       <c r="B244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="C244" t="n">
-        <v>10.90848818540733</v>
+        <v>10.90848916207064</v>
       </c>
       <c r="D244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="E244" t="n">
-        <v>10.76767986438283</v>
+        <v>10.76768082843923</v>
       </c>
       <c r="F244" t="n">
         <v>446683</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434757232666</v>
+        <v>10.49434661865234</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919703181856</v>
+        <v>10.51919607588605</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707477706429</v>
+        <v>10.04707386403591</v>
       </c>
       <c r="E246" t="n">
-        <v>10.15475105255997</v>
+        <v>10.1547501297465</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5352,16 +5352,16 @@
         <v>44677</v>
       </c>
       <c r="B247" t="n">
-        <v>10.35354137420654</v>
+        <v>10.35354042053223</v>
       </c>
       <c r="C247" t="n">
-        <v>10.66828847409488</v>
+        <v>10.66828749142892</v>
       </c>
       <c r="D247" t="n">
-        <v>10.35354137420654</v>
+        <v>10.35354042053223</v>
       </c>
       <c r="E247" t="n">
-        <v>10.48606629370245</v>
+        <v>10.48606532782114</v>
       </c>
       <c r="F247" t="n">
         <v>670551</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525585174561</v>
+        <v>10.34525680541992</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56060920116428</v>
+        <v>10.56061017469088</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32868899323284</v>
+        <v>10.32868994537994</v>
       </c>
       <c r="E248" t="n">
-        <v>10.4115174606003</v>
+        <v>10.41151842038292</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838840484619</v>
+        <v>10.37838745117188</v>
       </c>
       <c r="C249" t="n">
-        <v>10.55232797294748</v>
+        <v>10.55232700328979</v>
       </c>
       <c r="D249" t="n">
-        <v>10.23758006416832</v>
+        <v>10.23757912343294</v>
       </c>
       <c r="E249" t="n">
-        <v>10.34525800959385</v>
+        <v>10.3452570589639</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394432067871</v>
+        <v>10.83394336700439</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525741688146</v>
+        <v>11.16525643404281</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576245087913</v>
+        <v>10.53576152345272</v>
       </c>
       <c r="E250" t="n">
-        <v>10.5688936772823</v>
+        <v>10.56889274693946</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5452,16 +5452,16 @@
         <v>44684</v>
       </c>
       <c r="B252" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C252" t="n">
-        <v>10.72603654719261</v>
+        <v>10.72603559055428</v>
       </c>
       <c r="D252" t="n">
-        <v>10.51002056175287</v>
+        <v>10.51001962438067</v>
       </c>
       <c r="E252" t="n">
-        <v>10.71772763006424</v>
+        <v>10.71772667416696</v>
       </c>
       <c r="F252" t="n">
         <v>311097</v>
@@ -5472,16 +5472,16 @@
         <v>44685</v>
       </c>
       <c r="B253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90051078796387</v>
       </c>
       <c r="C253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90051078796387</v>
       </c>
       <c r="D253" t="n">
-        <v>10.48509591818506</v>
+        <v>10.48509500085503</v>
       </c>
       <c r="E253" t="n">
-        <v>10.69280382991162</v>
+        <v>10.69280289440945</v>
       </c>
       <c r="F253" t="n">
         <v>328902</v>
@@ -5532,16 +5532,16 @@
         <v>44690</v>
       </c>
       <c r="B256" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036047311521</v>
       </c>
       <c r="D256" t="n">
-        <v>10.618028137107</v>
+        <v>10.61802719010177</v>
       </c>
       <c r="E256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036047311521</v>
       </c>
       <c r="F256" t="n">
         <v>340595</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340438842773</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C257" t="n">
-        <v>10.8838951433366</v>
+        <v>10.88389316500986</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340438842773</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727897723452</v>
+        <v>10.86727700192804</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340446133011</v>
+        <v>10.49340354046572</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802904688768</v>
+        <v>10.61802811508668</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5672,16 +5672,16 @@
         <v>44699</v>
       </c>
       <c r="B263" t="n">
-        <v>11.11652565002441</v>
+        <v>11.11652660369873</v>
       </c>
       <c r="C263" t="n">
-        <v>11.24945828791266</v>
+        <v>11.24945925299112</v>
       </c>
       <c r="D263" t="n">
-        <v>10.80911746412798</v>
+        <v>10.80911839143009</v>
       </c>
       <c r="E263" t="n">
-        <v>11.01682617160823</v>
+        <v>11.01682711672944</v>
       </c>
       <c r="F263" t="n">
         <v>416658</v>
@@ -5692,16 +5692,16 @@
         <v>44700</v>
       </c>
       <c r="B264" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C264" t="n">
-        <v>11.4073194012873</v>
+        <v>11.40731747287078</v>
       </c>
       <c r="D264" t="n">
-        <v>11.05006181329636</v>
+        <v>11.05005994527452</v>
       </c>
       <c r="E264" t="n">
-        <v>11.12483706495406</v>
+        <v>11.1248351842914</v>
       </c>
       <c r="F264" t="n">
         <v>530225</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190330505371</v>
+        <v>10.99190235137939</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="D268" t="n">
-        <v>10.892202971845</v>
+        <v>10.89220202682084</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329391479492</v>
+        <v>11.08329296112061</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776865049238</v>
+        <v>11.25776768180519</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667691555787</v>
+        <v>11.06667596331338</v>
       </c>
       <c r="E270" t="n">
-        <v>11.1996104052599</v>
+        <v>11.199609441577</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776767730713</v>
+        <v>11.25776958465576</v>
       </c>
       <c r="C271" t="n">
-        <v>11.27438467510771</v>
+        <v>11.27438658527168</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160187295824</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160187295824</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085273742676</v>
+        <v>11.34085083007812</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085273742676</v>
+        <v>11.34085083007812</v>
       </c>
       <c r="D272" t="n">
-        <v>11.13314482406336</v>
+        <v>11.13314295164785</v>
       </c>
       <c r="E272" t="n">
-        <v>11.24946048759386</v>
+        <v>11.24945859561594</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34915924072266</v>
+        <v>11.34916019439697</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19960959730377</v>
+        <v>11.19961053841137</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622848510742</v>
       </c>
       <c r="C274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.34916115288518</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622848510742</v>
       </c>
       <c r="E274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.34916115288518</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712856292725</v>
+        <v>10.91712760925293</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24946021456504</v>
+        <v>11.24945923185963</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051156297961</v>
+        <v>10.90051061075688</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622788413276</v>
+        <v>11.21622690433039</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344331983751</v>
+        <v>11.03344429480254</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="E276" t="n">
-        <v>11.00851824120922</v>
+        <v>11.00851921397176</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D277" t="n">
-        <v>10.6429532860445</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250209732709</v>
+        <v>10.79250303440952</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5992,16 +5992,16 @@
         <v>44721</v>
       </c>
       <c r="B279" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C279" t="n">
-        <v>10.82573687488132</v>
+        <v>10.82573590935088</v>
       </c>
       <c r="D279" t="n">
-        <v>10.6263362195039</v>
+        <v>10.62633527175769</v>
       </c>
       <c r="E279" t="n">
-        <v>10.79250287583077</v>
+        <v>10.79250191326441</v>
       </c>
       <c r="F279" t="n">
         <v>205537</v>
@@ -6012,16 +6012,16 @@
         <v>44722</v>
       </c>
       <c r="B280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370536804199</v>
       </c>
       <c r="C280" t="n">
-        <v>10.65126248980645</v>
+        <v>10.65126346711301</v>
       </c>
       <c r="D280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370536804199</v>
       </c>
       <c r="E280" t="n">
-        <v>10.63464548972945</v>
+        <v>10.63464646551131</v>
       </c>
       <c r="F280" t="n">
         <v>218179</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768669128418</v>
+        <v>10.1776876449585</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216142044539</v>
+        <v>10.35216239046842</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798720379124</v>
+        <v>10.07798814812347</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599477322573</v>
+        <v>10.18599572767854</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6112,16 +6112,16 @@
         <v>44732</v>
       </c>
       <c r="B285" t="n">
-        <v>10.07798862457275</v>
+        <v>10.07798671722412</v>
       </c>
       <c r="C285" t="n">
-        <v>10.260771461444</v>
+        <v>10.2607695195021</v>
       </c>
       <c r="D285" t="n">
-        <v>9.945055955841498</v>
+        <v>9.945054073651551</v>
       </c>
       <c r="E285" t="n">
-        <v>10.1776881261212</v>
+        <v>10.17768619990355</v>
       </c>
       <c r="F285" t="n">
         <v>293715</v>
@@ -6152,16 +6152,16 @@
         <v>44734</v>
       </c>
       <c r="B287" t="n">
-        <v>9.837045669555664</v>
+        <v>9.83704662322998</v>
       </c>
       <c r="C287" t="n">
-        <v>10.13614495216891</v>
+        <v>10.13614593484008</v>
       </c>
       <c r="D287" t="n">
-        <v>9.820428671752088</v>
+        <v>9.820429623815432</v>
       </c>
       <c r="E287" t="n">
-        <v>9.920128154379375</v>
+        <v>9.920129116108306</v>
       </c>
       <c r="F287" t="n">
         <v>227344</v>
@@ -6172,16 +6172,16 @@
         <v>44735</v>
       </c>
       <c r="B288" t="n">
-        <v>9.637646675109863</v>
+        <v>9.637645721435547</v>
       </c>
       <c r="C288" t="n">
-        <v>9.945054899684594</v>
+        <v>9.945053915591304</v>
       </c>
       <c r="D288" t="n">
-        <v>9.629338592879359</v>
+        <v>9.629337640027153</v>
       </c>
       <c r="E288" t="n">
-        <v>9.93674681745409</v>
+        <v>9.93674583418291</v>
       </c>
       <c r="F288" t="n">
         <v>565728</v>
@@ -6192,16 +6192,16 @@
         <v>44736</v>
       </c>
       <c r="B289" t="n">
-        <v>9.388398170471191</v>
+        <v>9.388399124145508</v>
       </c>
       <c r="C289" t="n">
-        <v>9.795505913764142</v>
+        <v>9.795506908792499</v>
       </c>
       <c r="D289" t="n">
-        <v>9.388398170471191</v>
+        <v>9.388399124145508</v>
       </c>
       <c r="E289" t="n">
-        <v>9.695805581274389</v>
+        <v>9.695806566175177</v>
       </c>
       <c r="F289" t="n">
         <v>325741</v>
@@ -6212,16 +6212,16 @@
         <v>44739</v>
       </c>
       <c r="B290" t="n">
-        <v>9.355164527893066</v>
+        <v>9.35516357421875</v>
       </c>
       <c r="C290" t="n">
-        <v>9.55456351324988</v>
+        <v>9.554562539248643</v>
       </c>
       <c r="D290" t="n">
-        <v>9.26377228285685</v>
+        <v>9.263771338499145</v>
       </c>
       <c r="E290" t="n">
-        <v>9.49640610190275</v>
+        <v>9.496405133830134</v>
       </c>
       <c r="F290" t="n">
         <v>312467</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072681427001953</v>
+        <v>9.072680473327637</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974876940689</v>
+        <v>8.93974782970578</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6272,16 +6272,16 @@
         <v>44742</v>
       </c>
       <c r="B293" t="n">
-        <v>8.732040405273438</v>
+        <v>8.732039451599121</v>
       </c>
       <c r="C293" t="n">
-        <v>9.056065650190641</v>
+        <v>9.05606466112774</v>
       </c>
       <c r="D293" t="n">
-        <v>8.698808074182256</v>
+        <v>8.698807124137426</v>
       </c>
       <c r="E293" t="n">
-        <v>9.056065650190641</v>
+        <v>9.05606466112774</v>
       </c>
       <c r="F293" t="n">
         <v>345757</v>
@@ -6332,16 +6332,16 @@
         <v>44747</v>
       </c>
       <c r="B296" t="n">
-        <v>9.031139373779297</v>
+        <v>9.031140327453613</v>
       </c>
       <c r="C296" t="n">
-        <v>9.213922179017237</v>
+        <v>9.213923151993134</v>
       </c>
       <c r="D296" t="n">
-        <v>9.022830457372914</v>
+        <v>9.022831410169822</v>
       </c>
       <c r="E296" t="n">
-        <v>9.213922179017237</v>
+        <v>9.213923151993134</v>
       </c>
       <c r="F296" t="n">
         <v>222182</v>
@@ -6352,16 +6352,16 @@
         <v>44748</v>
       </c>
       <c r="B297" t="n">
-        <v>9.080989837646484</v>
+        <v>9.080988883972168</v>
       </c>
       <c r="C297" t="n">
-        <v>9.247156500377804</v>
+        <v>9.24715552925287</v>
       </c>
       <c r="D297" t="n">
-        <v>8.923132092363788</v>
+        <v>8.923131155267498</v>
       </c>
       <c r="E297" t="n">
-        <v>9.031140506612298</v>
+        <v>9.031139558173097</v>
       </c>
       <c r="F297" t="n">
         <v>199743</v>
@@ -6372,16 +6372,16 @@
         <v>44749</v>
       </c>
       <c r="B298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="C298" t="n">
-        <v>9.355164883523981</v>
+        <v>9.355163898352176</v>
       </c>
       <c r="D298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="E298" t="n">
-        <v>9.230540304255577</v>
+        <v>9.230539332207711</v>
       </c>
       <c r="F298" t="n">
         <v>150966</v>
@@ -6412,16 +6412,16 @@
         <v>44753</v>
       </c>
       <c r="B300" t="n">
-        <v>8.840047836303711</v>
+        <v>8.840048789978027</v>
       </c>
       <c r="C300" t="n">
-        <v>8.964673237681779</v>
+        <v>8.964674204800824</v>
       </c>
       <c r="D300" t="n">
-        <v>8.79850659233197</v>
+        <v>8.798507541524769</v>
       </c>
       <c r="E300" t="n">
-        <v>8.889897996854938</v>
+        <v>8.889898955907146</v>
       </c>
       <c r="F300" t="n">
         <v>130423</v>
@@ -6452,16 +6452,16 @@
         <v>44755</v>
       </c>
       <c r="B302" t="n">
-        <v>8.59910774230957</v>
+        <v>8.599106788635254</v>
       </c>
       <c r="C302" t="n">
-        <v>8.823431820304181</v>
+        <v>8.823430841751456</v>
       </c>
       <c r="D302" t="n">
-        <v>8.549257576207872</v>
+        <v>8.549256628062132</v>
       </c>
       <c r="E302" t="n">
-        <v>8.56587457648561</v>
+        <v>8.56587362649698</v>
       </c>
       <c r="F302" t="n">
         <v>184467</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864974975585938</v>
+        <v>8.864973068237305</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873283894095279</v>
+        <v>8.873281984958936</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615725784401254</v>
+        <v>8.615723930679971</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632341951956706</v>
+        <v>8.632340094660361</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039446830749512</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039446830749512</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815121963176683</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815121963176683</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6652,16 +6652,16 @@
         <v>44769</v>
       </c>
       <c r="B312" t="n">
-        <v>9.047756195068359</v>
+        <v>9.047757148742676</v>
       </c>
       <c r="C312" t="n">
-        <v>9.072680439606275</v>
+        <v>9.072681395907718</v>
       </c>
       <c r="D312" t="n">
-        <v>8.756964994812122</v>
+        <v>8.756965917835734</v>
       </c>
       <c r="E312" t="n">
-        <v>8.76527307632476</v>
+        <v>8.765274000224082</v>
       </c>
       <c r="F312" t="n">
         <v>161185</v>
@@ -6672,16 +6672,16 @@
         <v>44770</v>
       </c>
       <c r="B313" t="n">
-        <v>9.047756195068359</v>
+        <v>9.047757148742676</v>
       </c>
       <c r="C313" t="n">
-        <v>9.172379921952103</v>
+        <v>9.172380888762323</v>
       </c>
       <c r="D313" t="n">
-        <v>8.914822717209198</v>
+        <v>8.914823656871727</v>
       </c>
       <c r="E313" t="n">
-        <v>8.914822717209198</v>
+        <v>8.914823656871727</v>
       </c>
       <c r="F313" t="n">
         <v>129685</v>
@@ -6732,16 +6732,16 @@
         <v>44775</v>
       </c>
       <c r="B316" t="n">
-        <v>9.114222526550293</v>
+        <v>9.114224433898926</v>
       </c>
       <c r="C316" t="n">
-        <v>9.205614770584537</v>
+        <v>9.205616697058979</v>
       </c>
       <c r="D316" t="n">
-        <v>8.906514626365531</v>
+        <v>8.906516490246783</v>
       </c>
       <c r="E316" t="n">
-        <v>9.006214952682356</v>
+        <v>9.006216837428061</v>
       </c>
       <c r="F316" t="n">
         <v>198584</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.939748764038086</v>
+        <v>8.93974781036377</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172380914689739</v>
+        <v>9.172379936198697</v>
       </c>
       <c r="D317" t="n">
-        <v>8.939748764038086</v>
+        <v>8.93974781036377</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114222668343956</v>
+        <v>9.114221696057117</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6772,16 +6772,16 @@
         <v>44777</v>
       </c>
       <c r="B318" t="n">
-        <v>9.263772010803223</v>
+        <v>9.26377010345459</v>
       </c>
       <c r="C318" t="n">
-        <v>9.297006008784836</v>
+        <v>9.297004094593545</v>
       </c>
       <c r="D318" t="n">
-        <v>8.948056542560964</v>
+        <v>8.948054700216032</v>
       </c>
       <c r="E318" t="n">
-        <v>8.972981623681449</v>
+        <v>8.972979776204609</v>
       </c>
       <c r="F318" t="n">
         <v>175407</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.380087852478027</v>
+        <v>9.380088806152344</v>
       </c>
       <c r="C319" t="n">
-        <v>9.529637494153098</v>
+        <v>9.529638463032139</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197305049845319</v>
+        <v>9.197305984936092</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305313449006189</v>
+        <v>9.305314395078184</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6812,16 +6812,16 @@
         <v>44781</v>
       </c>
       <c r="B320" t="n">
-        <v>9.637646675109863</v>
+        <v>9.637645721435547</v>
       </c>
       <c r="C320" t="n">
-        <v>9.670880673494802</v>
+        <v>9.670879716531882</v>
       </c>
       <c r="D320" t="n">
-        <v>9.371780531150575</v>
+        <v>9.371779603784519</v>
       </c>
       <c r="E320" t="n">
-        <v>9.371780531150575</v>
+        <v>9.371779603784519</v>
       </c>
       <c r="F320" t="n">
         <v>274752</v>
@@ -6832,16 +6832,16 @@
         <v>44782</v>
       </c>
       <c r="B321" t="n">
-        <v>9.263772010803223</v>
+        <v>9.26377010345459</v>
       </c>
       <c r="C321" t="n">
-        <v>9.920128863139675</v>
+        <v>9.920126820651559</v>
       </c>
       <c r="D321" t="n">
-        <v>9.105914276682094</v>
+        <v>9.105912401835312</v>
       </c>
       <c r="E321" t="n">
-        <v>9.687496720388545</v>
+        <v>9.68749472579783</v>
       </c>
       <c r="F321" t="n">
         <v>480605</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513021469116211</v>
+        <v>9.513022422790527</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596104790081913</v>
+        <v>9.596105752085279</v>
       </c>
       <c r="D322" t="n">
-        <v>9.205614099747661</v>
+        <v>9.205615022604585</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288696585981958</v>
+        <v>9.288697517167847</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6872,16 +6872,16 @@
         <v>44784</v>
       </c>
       <c r="B323" t="n">
-        <v>9.762271881103516</v>
+        <v>9.762272834777832</v>
       </c>
       <c r="C323" t="n">
-        <v>9.770579963162858</v>
+        <v>9.77058091764879</v>
       </c>
       <c r="D323" t="n">
-        <v>9.446555580802631</v>
+        <v>9.446556503634687</v>
       </c>
       <c r="E323" t="n">
-        <v>9.446555580802631</v>
+        <v>9.446556503634687</v>
       </c>
       <c r="F323" t="n">
         <v>1309919</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953362464904785</v>
+        <v>9.953364372253418</v>
       </c>
       <c r="C325" t="n">
-        <v>10.1195291092724</v>
+        <v>10.11953104846331</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704112498353368</v>
+        <v>9.704114357938586</v>
       </c>
       <c r="E325" t="n">
-        <v>9.72903757848165</v>
+        <v>9.729039442843225</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494548797607</v>
+        <v>10.53494453430176</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75927040500311</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="D328" t="n">
-        <v>10.3521626550741</v>
+        <v>10.35216171794617</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75927040500311</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340438842773</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494563841447</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092205210854</v>
+        <v>10.21092019610571</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494563841447</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7012,16 +7012,16 @@
         <v>44795</v>
       </c>
       <c r="B330" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370536804199</v>
       </c>
       <c r="C330" t="n">
-        <v>10.54325324140318</v>
+        <v>10.54325420879935</v>
       </c>
       <c r="D330" t="n">
-        <v>10.21922966985091</v>
+        <v>10.2192306075163</v>
       </c>
       <c r="E330" t="n">
-        <v>10.47678774528968</v>
+        <v>10.47678870658731</v>
       </c>
       <c r="F330" t="n">
         <v>111565</v>
@@ -7032,16 +7032,16 @@
         <v>44796</v>
       </c>
       <c r="B331" t="n">
-        <v>10.4850959777832</v>
+        <v>10.48509502410889</v>
       </c>
       <c r="C331" t="n">
-        <v>10.4850959777832</v>
+        <v>10.48509502410889</v>
       </c>
       <c r="D331" t="n">
-        <v>10.29400506519045</v>
+        <v>10.29400412889686</v>
       </c>
       <c r="E331" t="n">
-        <v>10.3853964800911</v>
+        <v>10.38539553548497</v>
       </c>
       <c r="F331" t="n">
         <v>120309</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389284806778</v>
+        <v>10.88389380981785</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633481521728</v>
+        <v>10.62633575420836</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573544424359</v>
+        <v>10.82573640085461</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096225738525</v>
+        <v>10.75096130371094</v>
       </c>
       <c r="C334" t="n">
-        <v>10.77588734076402</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="D334" t="n">
-        <v>10.32723834414087</v>
+        <v>10.32723742805339</v>
       </c>
       <c r="E334" t="n">
-        <v>10.77588734076402</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7132,16 +7132,16 @@
         <v>44803</v>
       </c>
       <c r="B336" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370536804199</v>
       </c>
       <c r="C336" t="n">
-        <v>10.79250323416921</v>
+        <v>10.79250422443531</v>
       </c>
       <c r="D336" t="n">
-        <v>10.31892916611842</v>
+        <v>10.31893011293173</v>
       </c>
       <c r="E336" t="n">
-        <v>10.70111182057445</v>
+        <v>10.70111280245493</v>
       </c>
       <c r="F336" t="n">
         <v>123575</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539600372314</v>
+        <v>10.38539505004883</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648690755074</v>
+        <v>10.57648593632885</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907867632044</v>
+        <v>10.26907773332736</v>
       </c>
       <c r="E337" t="n">
-        <v>10.4020121685439</v>
+        <v>10.40201121334375</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753715515137</v>
+        <v>10.22753810882568</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370380728989</v>
+        <v>10.39370477645853</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937891037603</v>
+        <v>10.16937985862734</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385364470204</v>
+        <v>10.34385460922237</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618656158447</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618656158447</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="D340" t="n">
-        <v>10.25246266602793</v>
+        <v>10.2524617502037</v>
       </c>
       <c r="E340" t="n">
-        <v>10.35216216064962</v>
+        <v>10.35216123591951</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7272,16 +7272,16 @@
         <v>44813</v>
       </c>
       <c r="B343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.0500602722168</v>
       </c>
       <c r="C343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.0500602722168</v>
       </c>
       <c r="D343" t="n">
-        <v>10.68449557428166</v>
+        <v>10.68449465215745</v>
       </c>
       <c r="E343" t="n">
-        <v>10.76757890457422</v>
+        <v>10.76757797527951</v>
       </c>
       <c r="F343" t="n">
         <v>298877</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314533233643</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913035841226</v>
+        <v>11.1913016668102</v>
       </c>
       <c r="D344" t="n">
-        <v>10.94205357586834</v>
+        <v>10.94205170125786</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006199625167</v>
+        <v>11.05006010313701</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314533233643</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C346" t="n">
-        <v>11.14976149871444</v>
+        <v>11.1497595885191</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389532408217</v>
+        <v>10.88389345943545</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145341552543</v>
+        <v>11.14145150675345</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7352,16 +7352,16 @@
         <v>44819</v>
       </c>
       <c r="B347" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C347" t="n">
-        <v>11.29100289964081</v>
+        <v>11.29100099088769</v>
       </c>
       <c r="D347" t="n">
-        <v>10.73434631002577</v>
+        <v>10.73434449537589</v>
       </c>
       <c r="E347" t="n">
-        <v>11.05006181329636</v>
+        <v>11.05005994527452</v>
       </c>
       <c r="F347" t="n">
         <v>361349</v>
@@ -7392,16 +7392,16 @@
         <v>44823</v>
       </c>
       <c r="B349" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C349" t="n">
-        <v>11.38239431740141</v>
+        <v>11.38239239319849</v>
       </c>
       <c r="D349" t="n">
-        <v>11.17468639799431</v>
+        <v>11.17468450890459</v>
       </c>
       <c r="E349" t="n">
-        <v>11.35746923351551</v>
+        <v>11.3574673135262</v>
       </c>
       <c r="F349" t="n">
         <v>125366</v>
@@ -7652,16 +7652,16 @@
         <v>44840</v>
       </c>
       <c r="B362" t="n">
-        <v>10.8838939666748</v>
+        <v>10.88389492034912</v>
       </c>
       <c r="C362" t="n">
-        <v>10.8838939666748</v>
+        <v>10.88389492034912</v>
       </c>
       <c r="D362" t="n">
-        <v>10.51832833517203</v>
+        <v>10.51832925681457</v>
       </c>
       <c r="E362" t="n">
-        <v>10.53494449947773</v>
+        <v>10.53494542257621</v>
       </c>
       <c r="F362" t="n">
         <v>536757</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156188207657</v>
+        <v>10.55156279823885</v>
       </c>
       <c r="E364" t="n">
-        <v>10.6429532860445</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7712,16 +7712,16 @@
         <v>44845</v>
       </c>
       <c r="B365" t="n">
-        <v>11.06667709350586</v>
+        <v>11.06667613983154</v>
       </c>
       <c r="C365" t="n">
-        <v>11.17468550345477</v>
+        <v>11.1746845404728</v>
       </c>
       <c r="D365" t="n">
-        <v>10.80081094455824</v>
+        <v>10.80081001379502</v>
       </c>
       <c r="E365" t="n">
-        <v>10.81742794406249</v>
+        <v>10.8174270118673</v>
       </c>
       <c r="F365" t="n">
         <v>221655</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558460235596</v>
+        <v>10.87558555603027</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160139071456</v>
+        <v>11.09160236333128</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85065952410448</v>
+        <v>10.85066047559313</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344315303822</v>
+        <v>11.03344412055507</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7812,16 +7812,16 @@
         <v>44853</v>
       </c>
       <c r="B370" t="n">
-        <v>10.80912017822266</v>
+        <v>10.80911827087402</v>
       </c>
       <c r="C370" t="n">
-        <v>10.9171294344071</v>
+        <v>10.91712750799944</v>
       </c>
       <c r="D370" t="n">
-        <v>10.7177287580439</v>
+        <v>10.71772686682196</v>
       </c>
       <c r="E370" t="n">
-        <v>10.75927084386342</v>
+        <v>10.75926894531107</v>
       </c>
       <c r="F370" t="n">
         <v>116727</v>
@@ -7852,16 +7852,16 @@
         <v>44855</v>
       </c>
       <c r="B372" t="n">
-        <v>10.684494972229</v>
+        <v>10.68449592590332</v>
       </c>
       <c r="C372" t="n">
-        <v>10.88389395201756</v>
+        <v>10.88389492348978</v>
       </c>
       <c r="D372" t="n">
-        <v>10.684494972229</v>
+        <v>10.68449592590332</v>
       </c>
       <c r="E372" t="n">
-        <v>10.76757829783996</v>
+        <v>10.76757925893011</v>
       </c>
       <c r="F372" t="n">
         <v>132319</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.6512622833252</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866870237426</v>
+        <v>10.95866968357269</v>
       </c>
       <c r="D374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.6512622833252</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772681852483</v>
+        <v>10.71772777815022</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -7932,16 +7932,16 @@
         <v>44861</v>
       </c>
       <c r="B376" t="n">
-        <v>10.85897064208984</v>
+        <v>10.85896968841553</v>
       </c>
       <c r="C376" t="n">
-        <v>10.87558680780617</v>
+        <v>10.87558585267256</v>
       </c>
       <c r="D376" t="n">
-        <v>10.64295464465691</v>
+        <v>10.6429537099539</v>
       </c>
       <c r="E376" t="n">
-        <v>10.78419539217179</v>
+        <v>10.78419444506451</v>
       </c>
       <c r="F376" t="n">
         <v>130423</v>
@@ -7992,16 +7992,16 @@
         <v>44866</v>
       </c>
       <c r="B379" t="n">
-        <v>10.72603511810303</v>
+        <v>10.72603607177734</v>
       </c>
       <c r="C379" t="n">
-        <v>10.7925014378855</v>
+        <v>10.79250239746948</v>
       </c>
       <c r="D379" t="n">
-        <v>10.51832724273427</v>
+        <v>10.51832817794084</v>
       </c>
       <c r="E379" t="n">
-        <v>10.64295263574062</v>
+        <v>10.64295358202789</v>
       </c>
       <c r="F379" t="n">
         <v>132424</v>
@@ -8012,16 +8012,16 @@
         <v>44868</v>
       </c>
       <c r="B380" t="n">
-        <v>11.00852012634277</v>
+        <v>11.00851917266846</v>
       </c>
       <c r="C380" t="n">
-        <v>11.01682820906445</v>
+        <v>11.0168272546704</v>
       </c>
       <c r="D380" t="n">
-        <v>10.59310430401782</v>
+        <v>10.59310338633121</v>
       </c>
       <c r="E380" t="n">
-        <v>10.80081138044879</v>
+        <v>10.80081044476839</v>
       </c>
       <c r="F380" t="n">
         <v>251575</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19961071014404</v>
+        <v>11.19960975646973</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577736811222</v>
+        <v>11.36577640028841</v>
       </c>
       <c r="D381" t="n">
-        <v>10.8838943938971</v>
+        <v>10.8838934671068</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344488690735</v>
+        <v>11.03344394738246</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8052,16 +8052,16 @@
         <v>44872</v>
       </c>
       <c r="B382" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="C382" t="n">
-        <v>11.24115280940709</v>
+        <v>11.24115182292292</v>
       </c>
       <c r="D382" t="n">
-        <v>10.72603746622774</v>
+        <v>10.72603652494829</v>
       </c>
       <c r="E382" t="n">
-        <v>11.11652822384952</v>
+        <v>11.11652724830197</v>
       </c>
       <c r="F382" t="n">
         <v>110617</v>
@@ -8092,16 +8092,16 @@
         <v>44874</v>
       </c>
       <c r="B384" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C384" t="n">
-        <v>10.84235303967512</v>
+        <v>10.84235207266271</v>
       </c>
       <c r="D384" t="n">
-        <v>10.49340356222759</v>
+        <v>10.49340262633743</v>
       </c>
       <c r="E384" t="n">
-        <v>10.79250287583077</v>
+        <v>10.79250191326441</v>
       </c>
       <c r="F384" t="n">
         <v>162870</v>
@@ -8132,16 +8132,16 @@
         <v>44876</v>
       </c>
       <c r="B386" t="n">
-        <v>10.21922969818115</v>
+        <v>10.21922874450684</v>
       </c>
       <c r="C386" t="n">
-        <v>10.6512625193344</v>
+        <v>10.65126152534211</v>
       </c>
       <c r="D386" t="n">
-        <v>10.21922969818115</v>
+        <v>10.21922874450684</v>
       </c>
       <c r="E386" t="n">
-        <v>10.6512625193344</v>
+        <v>10.65126152534211</v>
       </c>
       <c r="F386" t="n">
         <v>372832</v>
@@ -8152,16 +8152,16 @@
         <v>44879</v>
       </c>
       <c r="B387" t="n">
-        <v>10.08629512786865</v>
+        <v>10.08629703521729</v>
       </c>
       <c r="C387" t="n">
-        <v>10.50171173941597</v>
+        <v>10.50171372532113</v>
       </c>
       <c r="D387" t="n">
-        <v>9.953362479958644</v>
+        <v>9.953364362169316</v>
       </c>
       <c r="E387" t="n">
-        <v>10.25246177248758</v>
+        <v>10.25246371125882</v>
       </c>
       <c r="F387" t="n">
         <v>430564</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.707114219665527</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629405073862</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="D388" t="n">
-        <v>8.707114219665527</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629405073862</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562846183776855</v>
+        <v>8.562845230102539</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039489009439741</v>
+        <v>9.039488002680034</v>
       </c>
       <c r="D392" t="n">
-        <v>8.529397667607249</v>
+        <v>8.52939671765821</v>
       </c>
       <c r="E392" t="n">
-        <v>8.94750537993818</v>
+        <v>8.947504383423015</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.780261993408203</v>
+        <v>8.78026294708252</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880607542310836</v>
+        <v>8.880608506884256</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462500668479581</v>
+        <v>8.462501587640029</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537759620121415</v>
+        <v>8.537760547456168</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8332,16 +8332,16 @@
         <v>44893</v>
       </c>
       <c r="B396" t="n">
-        <v>8.537758827209473</v>
+        <v>8.537759780883789</v>
       </c>
       <c r="C396" t="n">
-        <v>8.888969475962179</v>
+        <v>8.888970468867001</v>
       </c>
       <c r="D396" t="n">
-        <v>8.537758827209473</v>
+        <v>8.537759780883789</v>
       </c>
       <c r="E396" t="n">
-        <v>8.888969475962179</v>
+        <v>8.888970468867001</v>
       </c>
       <c r="F396" t="n">
         <v>122943</v>
@@ -8352,16 +8352,16 @@
         <v>44894</v>
       </c>
       <c r="B397" t="n">
-        <v>8.705002784729004</v>
+        <v>8.705001831054688</v>
       </c>
       <c r="C397" t="n">
-        <v>8.87224536129513</v>
+        <v>8.872244389298597</v>
       </c>
       <c r="D397" t="n">
-        <v>8.470862337395888</v>
+        <v>8.470861409372766</v>
       </c>
       <c r="E397" t="n">
-        <v>8.604656398648789</v>
+        <v>8.604655455967894</v>
       </c>
       <c r="F397" t="n">
         <v>205221</v>
@@ -8372,16 +8372,16 @@
         <v>44895</v>
       </c>
       <c r="B398" t="n">
-        <v>8.671554565429688</v>
+        <v>8.671553611755371</v>
       </c>
       <c r="C398" t="n">
-        <v>8.905695020755468</v>
+        <v>8.905694041331014</v>
       </c>
       <c r="D398" t="n">
-        <v>8.604656692379058</v>
+        <v>8.60465574606199</v>
       </c>
       <c r="E398" t="n">
-        <v>8.705003081884717</v>
+        <v>8.705002124531823</v>
       </c>
       <c r="F398" t="n">
         <v>181728</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198371098419715</v>
+        <v>9.198369137593913</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822073797252052</v>
+        <v>8.822071916641914</v>
       </c>
       <c r="E400" t="n">
-        <v>9.1398351412117</v>
+        <v>9.139833192864064</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905694705334085</v>
+        <v>8.905695681933357</v>
       </c>
       <c r="D403" t="n">
-        <v>8.67991617708353</v>
+        <v>8.679917128923909</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437412261962891</v>
+        <v>8.437414169311523</v>
       </c>
       <c r="C404" t="n">
-        <v>8.73845055437487</v>
+        <v>8.738452529775763</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412326507723987</v>
+        <v>8.412328409401773</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705002041915865</v>
+        <v>8.705004009755438</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935684680938721</v>
       </c>
       <c r="C405" t="n">
-        <v>8.479224033940735</v>
+        <v>8.47922454343796</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935684680938721</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462500196792739</v>
+        <v>8.462500705285068</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952408790588379</v>
+        <v>7.952410221099854</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027667737176076</v>
+        <v>8.027669181225434</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818614734370023</v>
+        <v>7.818616140814081</v>
       </c>
       <c r="E406" t="n">
-        <v>7.93568411349083</v>
+        <v>7.935685540993802</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8572,16 +8572,16 @@
         <v>44909</v>
       </c>
       <c r="B408" t="n">
-        <v>8.136377334594727</v>
+        <v>8.13637638092041</v>
       </c>
       <c r="C408" t="n">
-        <v>8.161463094028024</v>
+        <v>8.161462137413377</v>
       </c>
       <c r="D408" t="n">
-        <v>7.634647023397222</v>
+        <v>7.634646128531304</v>
       </c>
       <c r="E408" t="n">
-        <v>8.002583257054573</v>
+        <v>8.002582319062418</v>
       </c>
       <c r="F408" t="n">
         <v>518426</v>
@@ -8632,16 +8632,16 @@
         <v>44914</v>
       </c>
       <c r="B411" t="n">
-        <v>8.161462783813477</v>
+        <v>8.161463737487793</v>
       </c>
       <c r="C411" t="n">
-        <v>8.161462783813477</v>
+        <v>8.161463737487793</v>
       </c>
       <c r="D411" t="n">
-        <v>7.952409755638184</v>
+        <v>7.952410684884464</v>
       </c>
       <c r="E411" t="n">
-        <v>8.128015105840415</v>
+        <v>8.12801605560634</v>
       </c>
       <c r="F411" t="n">
         <v>108510</v>
@@ -8652,16 +8652,16 @@
         <v>44915</v>
       </c>
       <c r="B412" t="n">
-        <v>8.429051399230957</v>
+        <v>8.429050445556641</v>
       </c>
       <c r="C412" t="n">
-        <v>8.579570984352777</v>
+        <v>8.579570013648471</v>
       </c>
       <c r="D412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="E412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="F412" t="n">
         <v>166979</v>
@@ -8692,16 +8692,16 @@
         <v>44917</v>
       </c>
       <c r="B414" t="n">
-        <v>8.487587928771973</v>
+        <v>8.487586975097656</v>
       </c>
       <c r="C414" t="n">
-        <v>8.571209646126793</v>
+        <v>8.571208683056653</v>
       </c>
       <c r="D414" t="n">
-        <v>8.403966211417153</v>
+        <v>8.403965267138661</v>
       </c>
       <c r="E414" t="n">
-        <v>8.462501329551463</v>
+        <v>8.462500378695903</v>
       </c>
       <c r="F414" t="n">
         <v>90284</v>
@@ -8712,16 +8712,16 @@
         <v>44918</v>
       </c>
       <c r="B415" t="n">
-        <v>8.688277244567871</v>
+        <v>8.688278198242188</v>
       </c>
       <c r="C415" t="n">
-        <v>8.763537026657437</v>
+        <v>8.763537988592692</v>
       </c>
       <c r="D415" t="n">
-        <v>8.50431000853621</v>
+        <v>8.504310942017245</v>
       </c>
       <c r="E415" t="n">
-        <v>8.529396602566065</v>
+        <v>8.529397538800746</v>
       </c>
       <c r="F415" t="n">
         <v>92391</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613018306402285</v>
+        <v>8.613019250906639</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730089370059329</v>
+        <v>8.730090327401705</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.738451957702637</v>
+        <v>8.73845100402832</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788624314378202</v>
+        <v>8.788623355228307</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284660898665</v>
+        <v>8.56284567447709</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713365359294553</v>
+        <v>8.713364408358071</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914056624116538</v>
+        <v>8.914057601632781</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830434915870388</v>
+        <v>8.830435884216666</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529397964477539</v>
+        <v>8.529397010803223</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771900345253039</v>
+        <v>8.771899364464465</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529397964477539</v>
+        <v>8.529397010803223</v>
       </c>
       <c r="E420" t="n">
-        <v>8.705003310585438</v>
+        <v>8.705002337276639</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8832,16 +8832,16 @@
         <v>44929</v>
       </c>
       <c r="B421" t="n">
-        <v>8.102927207946777</v>
+        <v>8.102926254272461</v>
       </c>
       <c r="C421" t="n">
-        <v>8.504310201091222</v>
+        <v>8.50430920017612</v>
       </c>
       <c r="D421" t="n">
-        <v>8.086202531501375</v>
+        <v>8.086201579795469</v>
       </c>
       <c r="E421" t="n">
-        <v>8.479223606493356</v>
+        <v>8.47922260853082</v>
       </c>
       <c r="F421" t="n">
         <v>326162</v>
@@ -8852,16 +8852,16 @@
         <v>44930</v>
       </c>
       <c r="B422" t="n">
-        <v>8.328705787658691</v>
+        <v>8.328704833984375</v>
       </c>
       <c r="C422" t="n">
-        <v>8.345429625788091</v>
+        <v>8.345428670198819</v>
       </c>
       <c r="D422" t="n">
-        <v>8.061116816323212</v>
+        <v>8.061115893289037</v>
       </c>
       <c r="E422" t="n">
-        <v>8.345429625788091</v>
+        <v>8.345428670198819</v>
       </c>
       <c r="F422" t="n">
         <v>248204</v>
@@ -8872,16 +8872,16 @@
         <v>44931</v>
       </c>
       <c r="B423" t="n">
-        <v>8.395604133605957</v>
+        <v>8.395602226257324</v>
       </c>
       <c r="C423" t="n">
-        <v>8.454139250637853</v>
+        <v>8.454137329990965</v>
       </c>
       <c r="D423" t="n">
-        <v>8.270171980006358</v>
+        <v>8.270170101153928</v>
       </c>
       <c r="E423" t="n">
-        <v>8.362155615322106</v>
+        <v>8.362153715572447</v>
       </c>
       <c r="F423" t="n">
         <v>69636</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387241379016988</v>
+        <v>8.387239591100503</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395604138698484</v>
+        <v>8.395602348999303</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8932,16 +8932,16 @@
         <v>44936</v>
       </c>
       <c r="B426" t="n">
-        <v>8.930782318115234</v>
+        <v>8.930781364440918</v>
       </c>
       <c r="C426" t="n">
-        <v>8.972592756925931</v>
+        <v>8.972591798786882</v>
       </c>
       <c r="D426" t="n">
-        <v>8.755176962857174</v>
+        <v>8.75517602793489</v>
       </c>
       <c r="E426" t="n">
-        <v>8.830435920744552</v>
+        <v>8.830434977785734</v>
       </c>
       <c r="F426" t="n">
         <v>133478</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964229583740234</v>
+        <v>8.964228630065918</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072937895832748</v>
+        <v>9.072936930593318</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847160192439846</v>
+        <v>8.847159251220148</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922419146857282</v>
+        <v>8.922418197631035</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -8972,16 +8972,16 @@
         <v>44938</v>
       </c>
       <c r="B428" t="n">
-        <v>9.131472587585449</v>
+        <v>9.131471633911133</v>
       </c>
       <c r="C428" t="n">
-        <v>9.323801764514162</v>
+        <v>9.323800790753337</v>
       </c>
       <c r="D428" t="n">
-        <v>8.788623828529191</v>
+        <v>8.788622910661372</v>
       </c>
       <c r="E428" t="n">
-        <v>8.964229167537438</v>
+        <v>8.964228231329717</v>
       </c>
       <c r="F428" t="n">
         <v>167506</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139833970240518</v>
+        <v>9.139834941690628</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006039914165292</v>
+        <v>9.006040871394767</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847159262540833</v>
+        <v>8.847160202883281</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C431" t="n">
-        <v>9.06457502373333</v>
+        <v>9.064575987184355</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905694372108872</v>
+        <v>8.905695318672869</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964228641536403</v>
+        <v>8.964229594321862</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9072,16 +9072,16 @@
         <v>44945</v>
       </c>
       <c r="B433" t="n">
-        <v>9.131472587585449</v>
+        <v>9.131471633911133</v>
       </c>
       <c r="C433" t="n">
-        <v>9.281992169712995</v>
+        <v>9.281991200318688</v>
       </c>
       <c r="D433" t="n">
-        <v>8.989315764558695</v>
+        <v>8.989314825730977</v>
       </c>
       <c r="E433" t="n">
-        <v>9.056212796521677</v>
+        <v>9.056211850707355</v>
       </c>
       <c r="F433" t="n">
         <v>125260</v>
@@ -9092,16 +9092,16 @@
         <v>44946</v>
       </c>
       <c r="B434" t="n">
-        <v>9.365612030029297</v>
+        <v>9.365612983703613</v>
       </c>
       <c r="C434" t="n">
-        <v>9.365612030029297</v>
+        <v>9.365612983703613</v>
       </c>
       <c r="D434" t="n">
-        <v>9.039487984188639</v>
+        <v>9.039488904654647</v>
       </c>
       <c r="E434" t="n">
-        <v>9.131471603257495</v>
+        <v>9.131472533089941</v>
       </c>
       <c r="F434" t="n">
         <v>97975</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566305160522461</v>
+        <v>9.566304206848145</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616477515394145</v>
+        <v>9.616476556718098</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407423656363838</v>
+        <v>9.407422718528574</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424148334748114</v>
+        <v>9.424147395245551</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9132,16 +9132,16 @@
         <v>44950</v>
       </c>
       <c r="B436" t="n">
-        <v>9.474321365356445</v>
+        <v>9.474320411682129</v>
       </c>
       <c r="C436" t="n">
-        <v>9.616477348523446</v>
+        <v>9.616476380539872</v>
       </c>
       <c r="D436" t="n">
-        <v>9.348888380002389</v>
+        <v>9.348887438954012</v>
       </c>
       <c r="E436" t="n">
-        <v>9.616477348523446</v>
+        <v>9.616476380539872</v>
       </c>
       <c r="F436" t="n">
         <v>142116</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C438" t="n">
-        <v>9.959326039139317</v>
+        <v>9.95932505997885</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741910266268745</v>
+        <v>9.741909308483715</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="D439" t="n">
-        <v>9.649926637741174</v>
+        <v>9.6499256889996</v>
       </c>
       <c r="E439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9212,16 +9212,16 @@
         <v>44956</v>
       </c>
       <c r="B440" t="n">
-        <v>9.616477966308594</v>
+        <v>9.616477012634277</v>
       </c>
       <c r="C440" t="n">
-        <v>9.867343112992316</v>
+        <v>9.867342134439488</v>
       </c>
       <c r="D440" t="n">
-        <v>9.57466752859828</v>
+        <v>9.574666579070339</v>
       </c>
       <c r="E440" t="n">
-        <v>9.725186280552268</v>
+        <v>9.725185316097255</v>
       </c>
       <c r="F440" t="n">
         <v>176882</v>
@@ -9232,16 +9232,16 @@
         <v>44957</v>
       </c>
       <c r="B441" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449235916137695</v>
       </c>
       <c r="C441" t="n">
-        <v>9.68337541974836</v>
+        <v>9.683376397053557</v>
       </c>
       <c r="D441" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449235916137695</v>
       </c>
       <c r="E441" t="n">
-        <v>9.616477546137954</v>
+        <v>9.61647851669141</v>
       </c>
       <c r="F441" t="n">
         <v>134742</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.666650772094727</v>
+        <v>9.66664981842041</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725185886602381</v>
+        <v>9.725184927153217</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457596911730329</v>
+        <v>9.457595978680457</v>
       </c>
       <c r="E443" t="n">
-        <v>9.70009928893616</v>
+        <v>9.700098331961943</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312152862549</v>
+        <v>10.09312057495117</v>
       </c>
       <c r="C447" t="n">
-        <v>10.1600177240003</v>
+        <v>10.16001676400513</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649927198089818</v>
+        <v>9.649926286291848</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741910831958663</v>
+        <v>9.741909911469383</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9372,16 +9372,16 @@
         <v>44966</v>
       </c>
       <c r="B448" t="n">
-        <v>10.00949954986572</v>
+        <v>10.00949859619141</v>
       </c>
       <c r="C448" t="n">
-        <v>10.14329361736379</v>
+        <v>10.14329265094199</v>
       </c>
       <c r="D448" t="n">
-        <v>9.884066561410558</v>
+        <v>9.88406561968711</v>
       </c>
       <c r="E448" t="n">
-        <v>10.09312126212231</v>
+        <v>10.09312030048077</v>
       </c>
       <c r="F448" t="n">
         <v>166136</v>
@@ -9392,16 +9392,16 @@
         <v>44967</v>
       </c>
       <c r="B449" t="n">
-        <v>9.37397575378418</v>
+        <v>9.373974800109863</v>
       </c>
       <c r="C449" t="n">
-        <v>10.1432932979536</v>
+        <v>10.1432922660117</v>
       </c>
       <c r="D449" t="n">
-        <v>9.298715963080996</v>
+        <v>9.298715017063337</v>
       </c>
       <c r="E449" t="n">
-        <v>9.950964121946381</v>
+        <v>9.95096310957136</v>
       </c>
       <c r="F449" t="n">
         <v>543394</v>
@@ -9432,16 +9432,16 @@
         <v>44971</v>
       </c>
       <c r="B451" t="n">
-        <v>9.909152984619141</v>
+        <v>9.909153938293457</v>
       </c>
       <c r="C451" t="n">
-        <v>9.909152984619141</v>
+        <v>9.909153938293457</v>
       </c>
       <c r="D451" t="n">
-        <v>9.532854897924329</v>
+        <v>9.532855815383055</v>
       </c>
       <c r="E451" t="n">
-        <v>9.566304251514461</v>
+        <v>9.566305172192413</v>
       </c>
       <c r="F451" t="n">
         <v>266324</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088144470998</v>
+        <v>10.41088241395452</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458513532366</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820590414945</v>
+        <v>10.11820684614614</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C455" t="n">
-        <v>10.61993612237364</v>
+        <v>10.619937111081</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992774609804133</v>
+        <v>9.992775540123269</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889782341103</v>
+        <v>10.31889878409197</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9532,16 +9532,16 @@
         <v>44980</v>
       </c>
       <c r="B456" t="n">
-        <v>10.10148334503174</v>
+        <v>10.10148429870605</v>
       </c>
       <c r="C456" t="n">
-        <v>10.43596935933888</v>
+        <v>10.4359703445918</v>
       </c>
       <c r="D456" t="n">
-        <v>10.03458547005784</v>
+        <v>10.03458641741637</v>
       </c>
       <c r="E456" t="n">
-        <v>10.43596935933888</v>
+        <v>10.4359703445918</v>
       </c>
       <c r="F456" t="n">
         <v>107772</v>
@@ -9552,16 +9552,16 @@
         <v>44981</v>
       </c>
       <c r="B457" t="n">
-        <v>10.00113677978516</v>
+        <v>10.00113773345947</v>
       </c>
       <c r="C457" t="n">
-        <v>10.21018978242951</v>
+        <v>10.21019075603841</v>
       </c>
       <c r="D457" t="n">
-        <v>10.00113677978516</v>
+        <v>10.00113773345947</v>
       </c>
       <c r="E457" t="n">
-        <v>10.10148232187131</v>
+        <v>10.10148328511423</v>
       </c>
       <c r="F457" t="n">
         <v>69320</v>
@@ -9572,16 +9572,16 @@
         <v>44984</v>
       </c>
       <c r="B458" t="n">
-        <v>9.950965881347656</v>
+        <v>9.950963973999023</v>
       </c>
       <c r="C458" t="n">
-        <v>10.04294952615454</v>
+        <v>10.04294760117497</v>
       </c>
       <c r="D458" t="n">
-        <v>9.81717179440699</v>
+        <v>9.817169912703301</v>
       </c>
       <c r="E458" t="n">
-        <v>10.00113908402076</v>
+        <v>10.00113716705519</v>
       </c>
       <c r="F458" t="n">
         <v>122627</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053590514944</v>
+        <v>10.31053686505189</v>
       </c>
       <c r="D460" t="n">
-        <v>9.850616958514175</v>
+        <v>9.85061787559855</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458513532366</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9652,16 +9652,16 @@
         <v>44988</v>
       </c>
       <c r="B462" t="n">
-        <v>10.32726001739502</v>
+        <v>10.32726097106934</v>
       </c>
       <c r="C462" t="n">
-        <v>10.64502216136458</v>
+        <v>10.64502314438275</v>
       </c>
       <c r="D462" t="n">
-        <v>10.32726001739502</v>
+        <v>10.32726097106934</v>
       </c>
       <c r="E462" t="n">
-        <v>10.6115728071442</v>
+        <v>10.61157378707348</v>
       </c>
       <c r="F462" t="n">
         <v>104401</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.74536895751953</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="C465" t="n">
-        <v>10.74536895751953</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="D465" t="n">
-        <v>10.5028665720366</v>
+        <v>10.50286563988488</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502340357023</v>
+        <v>10.64502245880179</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9752,16 +9752,16 @@
         <v>44995</v>
       </c>
       <c r="B467" t="n">
-        <v>10.82062911987305</v>
+        <v>10.82062816619873</v>
       </c>
       <c r="C467" t="n">
-        <v>10.82062911987305</v>
+        <v>10.82062816619873</v>
       </c>
       <c r="D467" t="n">
-        <v>10.23527793497566</v>
+        <v>10.23527703289118</v>
       </c>
       <c r="E467" t="n">
-        <v>10.81226720012898</v>
+        <v>10.81226624719164</v>
       </c>
       <c r="F467" t="n">
         <v>153705</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758634567260742</v>
+        <v>9.758633613586426</v>
       </c>
       <c r="C470" t="n">
-        <v>9.9676884311345</v>
+        <v>9.967687457030143</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675012853683121</v>
+        <v>9.675011908180837</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892428636872463</v>
+        <v>9.892427670122959</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165519714355</v>
+        <v>10.15165615081787</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837903495139</v>
+        <v>10.16837999019679</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683375136415892</v>
+        <v>9.683376046098697</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833893877389167</v>
+        <v>9.833894801212116</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440871238708496</v>
+        <v>9.440872192382812</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583028050414784</v>
+        <v>9.583029018449141</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415785483825466</v>
+        <v>9.415786434965732</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532854860367744</v>
+        <v>9.532855823333831</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9912,16 +9912,16 @@
         <v>45007</v>
       </c>
       <c r="B475" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449235916137695</v>
       </c>
       <c r="C475" t="n">
-        <v>9.507770076784624</v>
+        <v>9.507771036366661</v>
       </c>
       <c r="D475" t="n">
-        <v>9.206732586029814</v>
+        <v>9.206733515229313</v>
       </c>
       <c r="E475" t="n">
-        <v>9.482683479198295</v>
+        <v>9.482684436248439</v>
       </c>
       <c r="F475" t="n">
         <v>116622</v>
@@ -9932,16 +9932,16 @@
         <v>45008</v>
       </c>
       <c r="B476" t="n">
-        <v>9.33216381072998</v>
+        <v>9.332164764404297</v>
       </c>
       <c r="C476" t="n">
-        <v>9.407422755904157</v>
+        <v>9.407423717269351</v>
       </c>
       <c r="D476" t="n">
-        <v>9.131471890031355</v>
+        <v>9.131472823196523</v>
       </c>
       <c r="E476" t="n">
-        <v>9.399060837582692</v>
+        <v>9.399061798093364</v>
       </c>
       <c r="F476" t="n">
         <v>179094</v>
@@ -9972,16 +9972,16 @@
         <v>45012</v>
       </c>
       <c r="B478" t="n">
-        <v>10.46941661834717</v>
+        <v>10.46941757202148</v>
       </c>
       <c r="C478" t="n">
-        <v>10.54467640359397</v>
+        <v>10.54467736412381</v>
       </c>
       <c r="D478" t="n">
-        <v>9.875703615248632</v>
+        <v>9.87570451484077</v>
       </c>
       <c r="E478" t="n">
-        <v>10.31889788799405</v>
+        <v>10.3188988279574</v>
       </c>
       <c r="F478" t="n">
         <v>649270</v>
@@ -10012,16 +10012,16 @@
         <v>45014</v>
       </c>
       <c r="B480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028255462646</v>
       </c>
       <c r="C480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028255462646</v>
       </c>
       <c r="D480" t="n">
-        <v>10.45269265683905</v>
+        <v>10.4526935867087</v>
       </c>
       <c r="E480" t="n">
-        <v>10.70355692438362</v>
+        <v>10.70355787657011</v>
       </c>
       <c r="F480" t="n">
         <v>215756</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820669929775</v>
+        <v>10.11820570451678</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201959763182</v>
+        <v>9.633201012665911</v>
       </c>
       <c r="E483" t="n">
-        <v>10.0345849896889</v>
+        <v>10.03458400312928</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10112,16 +10112,16 @@
         <v>45021</v>
       </c>
       <c r="B485" t="n">
-        <v>9.616477966308594</v>
+        <v>9.616477012634277</v>
       </c>
       <c r="C485" t="n">
-        <v>9.708461601383775</v>
+        <v>9.708460638587363</v>
       </c>
       <c r="D485" t="n">
-        <v>9.022765718147193</v>
+        <v>9.022764823351826</v>
       </c>
       <c r="E485" t="n">
-        <v>9.633202645477088</v>
+        <v>9.633201690144169</v>
       </c>
       <c r="F485" t="n">
         <v>566992</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758634104106184</v>
+        <v>9.758633144676933</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="C489" t="n">
-        <v>9.783719859219421</v>
+        <v>9.78372083371632</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700098156805314</v>
+        <v>9.700099122973164</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683375358581543</v>
+        <v>9.683374404907227</v>
       </c>
       <c r="C490" t="n">
-        <v>9.775358989056672</v>
+        <v>9.77535802632328</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566305130678549</v>
+        <v>9.566304188533978</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608115566297945</v>
+        <v>9.608114620035645</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10252,16 +10252,16 @@
         <v>45033</v>
       </c>
       <c r="B492" t="n">
-        <v>9.64992618560791</v>
+        <v>9.649925231933594</v>
       </c>
       <c r="C492" t="n">
-        <v>9.725185132631342</v>
+        <v>9.7251841715194</v>
       </c>
       <c r="D492" t="n">
-        <v>9.566304479917033</v>
+        <v>9.566303534506806</v>
       </c>
       <c r="E492" t="n">
-        <v>9.616476831219149</v>
+        <v>9.616475880850535</v>
       </c>
       <c r="F492" t="n">
         <v>328796</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766996023024904</v>
+        <v>9.766995062773542</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549581090294884</v>
+        <v>9.549580151418876</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691737072475323</v>
+        <v>9.691736119623117</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.65828800201416</v>
+        <v>9.658288955688477</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716822271224306</v>
+        <v>9.716823230678386</v>
       </c>
       <c r="D494" t="n">
-        <v>9.59975289266351</v>
+        <v>9.59975384055798</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616476729540551</v>
+        <v>9.616477679086358</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10332,16 +10332,16 @@
         <v>45040</v>
       </c>
       <c r="B496" t="n">
-        <v>9.516130447387695</v>
+        <v>9.516132354736328</v>
       </c>
       <c r="C496" t="n">
-        <v>9.700097679563306</v>
+        <v>9.700099623785084</v>
       </c>
       <c r="D496" t="n">
-        <v>9.516130447387695</v>
+        <v>9.516132354736328</v>
       </c>
       <c r="E496" t="n">
-        <v>9.633200656979527</v>
+        <v>9.633202587792919</v>
       </c>
       <c r="F496" t="n">
         <v>136322</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.28199291229248</v>
+        <v>9.281991958618164</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382338468264816</v>
+        <v>9.382337504280539</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215095034836967</v>
+        <v>9.215094088036043</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248543553494413</v>
+        <v>9.248542603256835</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10452,16 +10452,16 @@
         <v>45049</v>
       </c>
       <c r="B502" t="n">
-        <v>9.151030540466309</v>
+        <v>9.151029586791992</v>
       </c>
       <c r="C502" t="n">
-        <v>9.259872012055444</v>
+        <v>9.259871047038219</v>
       </c>
       <c r="D502" t="n">
-        <v>8.941721441697471</v>
+        <v>8.941720509836294</v>
       </c>
       <c r="E502" t="n">
-        <v>9.100796726876458</v>
+        <v>9.100795778437256</v>
       </c>
       <c r="F502" t="n">
         <v>158340</v>
@@ -10472,16 +10472,16 @@
         <v>45050</v>
       </c>
       <c r="B503" t="n">
-        <v>9.209637641906738</v>
+        <v>9.209639549255371</v>
       </c>
       <c r="C503" t="n">
-        <v>9.469181379750328</v>
+        <v>9.469183340851389</v>
       </c>
       <c r="D503" t="n">
-        <v>9.067305848299521</v>
+        <v>9.067307726170736</v>
       </c>
       <c r="E503" t="n">
-        <v>9.159402990182974</v>
+        <v>9.159404887127831</v>
       </c>
       <c r="F503" t="n">
         <v>221234</v>
@@ -10492,16 +10492,16 @@
         <v>45051</v>
       </c>
       <c r="B504" t="n">
-        <v>9.418946266174316</v>
+        <v>9.418947219848633</v>
       </c>
       <c r="C504" t="n">
-        <v>9.477553917758021</v>
+        <v>9.4775548773664</v>
       </c>
       <c r="D504" t="n">
-        <v>9.125913055273472</v>
+        <v>9.125913979277989</v>
       </c>
       <c r="E504" t="n">
-        <v>9.125913055273472</v>
+        <v>9.125913979277989</v>
       </c>
       <c r="F504" t="n">
         <v>204589</v>
@@ -10592,16 +10592,16 @@
         <v>45058</v>
       </c>
       <c r="B509" t="n">
-        <v>10.08036708831787</v>
+        <v>10.08036613464355</v>
       </c>
       <c r="C509" t="n">
-        <v>10.29805004190088</v>
+        <v>10.29804906763221</v>
       </c>
       <c r="D509" t="n">
-        <v>9.762216502753041</v>
+        <v>9.762215579178029</v>
       </c>
       <c r="E509" t="n">
-        <v>9.795705993803564</v>
+        <v>9.795705067060208</v>
       </c>
       <c r="F509" t="n">
         <v>501359</v>
@@ -10612,16 +10612,16 @@
         <v>45061</v>
       </c>
       <c r="B510" t="n">
-        <v>10.18083572387695</v>
+        <v>10.18083381652832</v>
       </c>
       <c r="C510" t="n">
-        <v>10.32316753515924</v>
+        <v>10.32316560114518</v>
       </c>
       <c r="D510" t="n">
-        <v>10.00501694451918</v>
+        <v>10.00501507010967</v>
       </c>
       <c r="E510" t="n">
-        <v>10.07199508651894</v>
+        <v>10.07199319956127</v>
       </c>
       <c r="F510" t="n">
         <v>215124</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845939636230469</v>
+        <v>9.845940589904785</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293249575018</v>
+        <v>10.27293349078287</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745471173433298</v>
+        <v>9.745472117376274</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548421658523</v>
+        <v>10.10548519539895</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10652,16 +10652,16 @@
         <v>45063</v>
       </c>
       <c r="B512" t="n">
-        <v>9.787332534790039</v>
+        <v>9.787333488464355</v>
       </c>
       <c r="C512" t="n">
-        <v>9.904545317354632</v>
+        <v>9.904546282450122</v>
       </c>
       <c r="D512" t="n">
-        <v>9.594766935296825</v>
+        <v>9.594767870207617</v>
       </c>
       <c r="E512" t="n">
-        <v>9.812449018873401</v>
+        <v>9.81244997499506</v>
       </c>
       <c r="F512" t="n">
         <v>227976</v>
@@ -10672,16 +10672,16 @@
         <v>45064</v>
       </c>
       <c r="B513" t="n">
-        <v>9.87105655670166</v>
+        <v>9.871057510375977</v>
       </c>
       <c r="C513" t="n">
-        <v>10.10548380143403</v>
+        <v>10.10548477775711</v>
       </c>
       <c r="D513" t="n">
-        <v>9.670118798192538</v>
+        <v>9.670119732453616</v>
       </c>
       <c r="E513" t="n">
-        <v>9.728724768206007</v>
+        <v>9.728725708129195</v>
       </c>
       <c r="F513" t="n">
         <v>659595</v>
@@ -10772,16 +10772,16 @@
         <v>45071</v>
       </c>
       <c r="B518" t="n">
-        <v>9.301733016967773</v>
+        <v>9.301734924316406</v>
       </c>
       <c r="C518" t="n">
-        <v>9.561277570152697</v>
+        <v>9.56127953072173</v>
       </c>
       <c r="D518" t="n">
-        <v>9.293360856236845</v>
+        <v>9.293362761868741</v>
       </c>
       <c r="E518" t="n">
-        <v>9.435690953340915</v>
+        <v>9.43569288815803</v>
       </c>
       <c r="F518" t="n">
         <v>216177</v>
@@ -10832,16 +10832,16 @@
         <v>45076</v>
       </c>
       <c r="B521" t="n">
-        <v>9.209637641906738</v>
+        <v>9.209639549255371</v>
       </c>
       <c r="C521" t="n">
-        <v>9.544532516166321</v>
+        <v>9.54453449287287</v>
       </c>
       <c r="D521" t="n">
-        <v>9.151029987449244</v>
+        <v>9.151031882660023</v>
       </c>
       <c r="E521" t="n">
-        <v>9.544532516166321</v>
+        <v>9.54453449287287</v>
       </c>
       <c r="F521" t="n">
         <v>214913</v>
@@ -10892,16 +10892,16 @@
         <v>45079</v>
       </c>
       <c r="B524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="C524" t="n">
-        <v>9.234754909248267</v>
+        <v>9.234753923397504</v>
       </c>
       <c r="D524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="E524" t="n">
-        <v>9.084051782474475</v>
+        <v>9.084050812711935</v>
       </c>
       <c r="F524" t="n">
         <v>446577</v>
@@ -10912,16 +10912,16 @@
         <v>45082</v>
       </c>
       <c r="B525" t="n">
-        <v>8.87474250793457</v>
+        <v>8.874741554260254</v>
       </c>
       <c r="C525" t="n">
-        <v>9.142659291459116</v>
+        <v>9.142658308994628</v>
       </c>
       <c r="D525" t="n">
-        <v>8.849626019216153</v>
+        <v>8.849625068240838</v>
       </c>
       <c r="E525" t="n">
-        <v>8.933349330617121</v>
+        <v>8.933348370644952</v>
       </c>
       <c r="F525" t="n">
         <v>464803</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958466529846191</v>
       </c>
       <c r="C526" t="n">
-        <v>9.058934042394197</v>
+        <v>9.058935006763894</v>
       </c>
       <c r="D526" t="n">
-        <v>8.83287978310155</v>
+        <v>8.832880723406619</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933348249323872</v>
+        <v>8.933349200324322</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -11032,16 +11032,16 @@
         <v>45091</v>
       </c>
       <c r="B531" t="n">
-        <v>9.100796699523926</v>
+        <v>9.100795745849609</v>
       </c>
       <c r="C531" t="n">
-        <v>9.218010332830801</v>
+        <v>9.218009366873643</v>
       </c>
       <c r="D531" t="n">
-        <v>9.04218988287049</v>
+        <v>9.042188935337592</v>
       </c>
       <c r="E531" t="n">
-        <v>9.142658350917937</v>
+        <v>9.142657392856929</v>
       </c>
       <c r="F531" t="n">
         <v>269590</v>
@@ -11052,16 +11052,16 @@
         <v>45092</v>
       </c>
       <c r="B532" t="n">
-        <v>9.201265335083008</v>
+        <v>9.201264381408691</v>
       </c>
       <c r="C532" t="n">
-        <v>9.251499990606119</v>
+        <v>9.251499031725182</v>
       </c>
       <c r="D532" t="n">
-        <v>9.092423861839507</v>
+        <v>9.092422919446173</v>
       </c>
       <c r="E532" t="n">
-        <v>9.125914192968059</v>
+        <v>9.125913247103586</v>
       </c>
       <c r="F532" t="n">
         <v>477550</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.99195384979248</v>
       </c>
       <c r="C535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.99195384979248</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899858501814995</v>
+        <v>8.899857557908286</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983582641817451</v>
+        <v>8.983581689031073</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950093269348145</v>
+        <v>8.950092315673828</v>
       </c>
       <c r="C537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="D537" t="n">
-        <v>8.83287964006866</v>
+        <v>8.832878698884004</v>
       </c>
       <c r="E537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11172,16 +11172,16 @@
         <v>45100</v>
       </c>
       <c r="B538" t="n">
-        <v>8.983582496643066</v>
+        <v>8.983583450317383</v>
       </c>
       <c r="C538" t="n">
-        <v>9.008699822354874</v>
+        <v>9.008700778695582</v>
       </c>
       <c r="D538" t="n">
-        <v>8.874741032281783</v>
+        <v>8.874741974401767</v>
       </c>
       <c r="E538" t="n">
-        <v>8.89985835799359</v>
+        <v>8.899859302779966</v>
       </c>
       <c r="F538" t="n">
         <v>372938</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958466529846191</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000328184936123</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841251944994323</v>
+        <v>8.841252886190651</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000328184936123</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695237159729004</v>
+        <v>9.695236206054688</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843977178107</v>
+        <v>9.753843017738918</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511043704053456</v>
+        <v>9.511042768497374</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611513014634612</v>
+        <v>9.611512069195841</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11352,16 +11352,16 @@
         <v>45113</v>
       </c>
       <c r="B547" t="n">
-        <v>9.418946266174316</v>
+        <v>9.418947219848633</v>
       </c>
       <c r="C547" t="n">
-        <v>9.703608157091221</v>
+        <v>9.703609139587735</v>
       </c>
       <c r="D547" t="n">
-        <v>9.410574105020764</v>
+        <v>9.410575057847394</v>
       </c>
       <c r="E547" t="n">
-        <v>9.695235995937669</v>
+        <v>9.695236977586497</v>
       </c>
       <c r="F547" t="n">
         <v>248414</v>
@@ -11372,16 +11372,16 @@
         <v>45114</v>
       </c>
       <c r="B548" t="n">
-        <v>9.628256797790527</v>
+        <v>9.628257751464844</v>
       </c>
       <c r="C548" t="n">
-        <v>9.695236614803234</v>
+        <v>9.69523757511187</v>
       </c>
       <c r="D548" t="n">
-        <v>9.444064193637333</v>
+        <v>9.444065129067459</v>
       </c>
       <c r="E548" t="n">
-        <v>9.444064193637333</v>
+        <v>9.444065129067459</v>
       </c>
       <c r="F548" t="n">
         <v>257790</v>
@@ -11392,16 +11392,16 @@
         <v>45117</v>
       </c>
       <c r="B549" t="n">
-        <v>9.619885444641113</v>
+        <v>9.619884490966797</v>
       </c>
       <c r="C549" t="n">
-        <v>9.745472086364286</v>
+        <v>9.745471120239847</v>
       </c>
       <c r="D549" t="n">
-        <v>9.527789134823944</v>
+        <v>9.527788190279663</v>
       </c>
       <c r="E549" t="n">
-        <v>9.628257607032745</v>
+        <v>9.628256652528449</v>
       </c>
       <c r="F549" t="n">
         <v>614083</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="D550" t="n">
-        <v>9.385457965682171</v>
+        <v>9.385458888088531</v>
       </c>
       <c r="E550" t="n">
-        <v>9.619884374764274</v>
+        <v>9.61988532021015</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11432,16 +11432,16 @@
         <v>45119</v>
       </c>
       <c r="B551" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C551" t="n">
-        <v>9.912918058384282</v>
+        <v>9.912919025122674</v>
       </c>
       <c r="D551" t="n">
-        <v>9.594766682188503</v>
+        <v>9.594767617899787</v>
       </c>
       <c r="E551" t="n">
-        <v>9.753842790871198</v>
+        <v>9.753843742096077</v>
       </c>
       <c r="F551" t="n">
         <v>281073</v>
@@ -11552,16 +11552,16 @@
         <v>45127</v>
       </c>
       <c r="B557" t="n">
-        <v>9.519416809082031</v>
+        <v>9.519415855407715</v>
       </c>
       <c r="C557" t="n">
-        <v>9.628257441814794</v>
+        <v>9.628256477236604</v>
       </c>
       <c r="D557" t="n">
-        <v>9.494299481168403</v>
+        <v>9.49429853001039</v>
       </c>
       <c r="E557" t="n">
-        <v>9.628257441814794</v>
+        <v>9.628256477236604</v>
       </c>
       <c r="F557" t="n">
         <v>109247</v>
@@ -11612,16 +11612,16 @@
         <v>45132</v>
       </c>
       <c r="B560" t="n">
-        <v>9.770587921142578</v>
+        <v>9.770586967468262</v>
       </c>
       <c r="C560" t="n">
-        <v>10.04687683214587</v>
+        <v>10.04687585150392</v>
       </c>
       <c r="D560" t="n">
-        <v>9.661747293809594</v>
+        <v>9.661746350758847</v>
       </c>
       <c r="E560" t="n">
-        <v>9.92129188114766</v>
+        <v>9.921290912763636</v>
       </c>
       <c r="F560" t="n">
         <v>194370</v>
@@ -11652,16 +11652,16 @@
         <v>45134</v>
       </c>
       <c r="B562" t="n">
-        <v>9.720352172851562</v>
+        <v>9.720353126525879</v>
       </c>
       <c r="C562" t="n">
-        <v>9.720352172851562</v>
+        <v>9.720353126525879</v>
       </c>
       <c r="D562" t="n">
-        <v>9.502670101536864</v>
+        <v>9.502671033854156</v>
       </c>
       <c r="E562" t="n">
-        <v>9.686862688123885</v>
+        <v>9.686863638512511</v>
       </c>
       <c r="F562" t="n">
         <v>987127</v>
@@ -11672,16 +11672,16 @@
         <v>45135</v>
       </c>
       <c r="B563" t="n">
-        <v>9.527788162231445</v>
+        <v>9.527789115905762</v>
       </c>
       <c r="C563" t="n">
-        <v>9.795704901942495</v>
+        <v>9.795705882433666</v>
       </c>
       <c r="D563" t="n">
-        <v>9.511042997987781</v>
+        <v>9.511043949986009</v>
       </c>
       <c r="E563" t="n">
-        <v>9.795704901942495</v>
+        <v>9.795705882433666</v>
       </c>
       <c r="F563" t="n">
         <v>123785</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728724479675293</v>
+        <v>9.728725433349609</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795704291304954</v>
+        <v>9.795705251545078</v>
       </c>
       <c r="D564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="E564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11712,16 +11712,16 @@
         <v>45139</v>
       </c>
       <c r="B565" t="n">
-        <v>9.896173477172852</v>
+        <v>9.896174430847168</v>
       </c>
       <c r="C565" t="n">
-        <v>9.896173477172852</v>
+        <v>9.896174430847168</v>
       </c>
       <c r="D565" t="n">
-        <v>9.628256734395071</v>
+        <v>9.628257662250791</v>
       </c>
       <c r="E565" t="n">
-        <v>9.753843364735953</v>
+        <v>9.753844304694203</v>
       </c>
       <c r="F565" t="n">
         <v>228819</v>
@@ -11772,16 +11772,16 @@
         <v>45142</v>
       </c>
       <c r="B568" t="n">
-        <v>9.99664306640625</v>
+        <v>9.996641159057617</v>
       </c>
       <c r="C568" t="n">
-        <v>10.0133890738977</v>
+        <v>10.01338716335395</v>
       </c>
       <c r="D568" t="n">
-        <v>9.770588788666778</v>
+        <v>9.770586924449054</v>
       </c>
       <c r="E568" t="n">
-        <v>9.862685100511712</v>
+        <v>9.862683218722113</v>
       </c>
       <c r="F568" t="n">
         <v>196582</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578022956848145</v>
+        <v>9.578023910522461</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695236584795509</v>
+        <v>9.695237550140671</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469181490562828</v>
+        <v>9.469182433399908</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686863581963795</v>
+        <v>9.686864546475267</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11852,16 +11852,16 @@
         <v>45148</v>
       </c>
       <c r="B572" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C572" t="n">
-        <v>9.837566925782678</v>
+        <v>9.837567885172595</v>
       </c>
       <c r="D572" t="n">
-        <v>9.544532033007691</v>
+        <v>9.54453296381994</v>
       </c>
       <c r="E572" t="n">
-        <v>9.578022359907973</v>
+        <v>9.5780232939863</v>
       </c>
       <c r="F572" t="n">
         <v>202060</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294612667715</v>
+        <v>10.63294521258928</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109669703995</v>
+        <v>10.95109575560148</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527669072958</v>
+        <v>10.77527578824517</v>
       </c>
       <c r="E578" t="n">
-        <v>11.09342811537701</v>
+        <v>11.0934271862458</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -11992,16 +11992,16 @@
         <v>45159</v>
       </c>
       <c r="B579" t="n">
-        <v>11.16877841949463</v>
+        <v>11.16877937316895</v>
       </c>
       <c r="C579" t="n">
-        <v>11.436695167162</v>
+        <v>11.43669614371307</v>
       </c>
       <c r="D579" t="n">
-        <v>11.04319262803141</v>
+        <v>11.04319357098227</v>
       </c>
       <c r="E579" t="n">
-        <v>11.37808835232321</v>
+        <v>11.37808932386998</v>
       </c>
       <c r="F579" t="n">
         <v>524641</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716468811035</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716468811035</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10179954134582</v>
+        <v>11.10180045903246</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877851856436</v>
+        <v>11.16877944178756</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12032,16 +12032,16 @@
         <v>45161</v>
       </c>
       <c r="B581" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="C581" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="D581" t="n">
-        <v>11.31948165818213</v>
+        <v>11.3194807332412</v>
       </c>
       <c r="E581" t="n">
-        <v>11.47018477777884</v>
+        <v>11.47018384052361</v>
       </c>
       <c r="F581" t="n">
         <v>383262</v>
@@ -12052,16 +12052,16 @@
         <v>45162</v>
       </c>
       <c r="B582" t="n">
-        <v>11.75484752655029</v>
+        <v>11.75484561920166</v>
       </c>
       <c r="C582" t="n">
-        <v>11.75484752655029</v>
+        <v>11.75484561920166</v>
       </c>
       <c r="D582" t="n">
-        <v>11.51204724443822</v>
+        <v>11.51204537648651</v>
       </c>
       <c r="E582" t="n">
-        <v>11.62088872120674</v>
+        <v>11.62088683559435</v>
       </c>
       <c r="F582" t="n">
         <v>205326</v>
@@ -12072,16 +12072,16 @@
         <v>45163</v>
       </c>
       <c r="B583" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="C583" t="n">
-        <v>11.74647453134756</v>
+        <v>11.74647357151606</v>
       </c>
       <c r="D583" t="n">
-        <v>11.55390892003695</v>
+        <v>11.55390797594043</v>
       </c>
       <c r="E583" t="n">
-        <v>11.74647453134756</v>
+        <v>11.74647357151606</v>
       </c>
       <c r="F583" t="n">
         <v>173405</v>
@@ -12112,16 +12112,16 @@
         <v>45167</v>
       </c>
       <c r="B585" t="n">
-        <v>12.49161624908447</v>
+        <v>12.49161720275879</v>
       </c>
       <c r="C585" t="n">
-        <v>12.71767217435969</v>
+        <v>12.71767314529228</v>
       </c>
       <c r="D585" t="n">
-        <v>11.90554897677267</v>
+        <v>11.90554988570359</v>
       </c>
       <c r="E585" t="n">
-        <v>11.92229414051626</v>
+        <v>11.9222950507256</v>
       </c>
       <c r="F585" t="n">
         <v>842903</v>
@@ -12152,16 +12152,16 @@
         <v>45169</v>
       </c>
       <c r="B587" t="n">
-        <v>12.26556205749512</v>
+        <v>12.26556301116943</v>
       </c>
       <c r="C587" t="n">
-        <v>12.39114784200412</v>
+        <v>12.39114880544301</v>
       </c>
       <c r="D587" t="n">
-        <v>12.081368620223</v>
+        <v>12.08136955957587</v>
       </c>
       <c r="E587" t="n">
-        <v>12.37440351936005</v>
+        <v>12.37440448149703</v>
       </c>
       <c r="F587" t="n">
         <v>308253</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625325429223</v>
+        <v>12.05625227825024</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66275070046011</v>
+        <v>11.66274975627503</v>
       </c>
       <c r="E589" t="n">
-        <v>11.99764643726385</v>
+        <v>11.9976454659665</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461273193359</v>
+        <v>11.70461177825928</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80508120388398</v>
+        <v>11.80508024202364</v>
       </c>
       <c r="D590" t="n">
-        <v>11.59577125644338</v>
+        <v>11.5957703116373</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996387560395</v>
+        <v>11.77996291579013</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12232,16 +12232,16 @@
         <v>45175</v>
       </c>
       <c r="B591" t="n">
-        <v>11.74647426605225</v>
+        <v>11.74647521972656</v>
       </c>
       <c r="C591" t="n">
-        <v>11.90554954393114</v>
+        <v>11.90555051052048</v>
       </c>
       <c r="D591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="E591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="F591" t="n">
         <v>295506</v>
@@ -12252,16 +12252,16 @@
         <v>45177</v>
       </c>
       <c r="B592" t="n">
-        <v>11.7715892791748</v>
+        <v>11.77159023284912</v>
       </c>
       <c r="C592" t="n">
-        <v>11.82182392534764</v>
+        <v>11.82182488309172</v>
       </c>
       <c r="D592" t="n">
-        <v>11.59576885873943</v>
+        <v>11.59576979816967</v>
       </c>
       <c r="E592" t="n">
-        <v>11.74647279725795</v>
+        <v>11.74647374889745</v>
       </c>
       <c r="F592" t="n">
         <v>200375</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879190103679</v>
+        <v>11.52879096769665</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298458432168</v>
+        <v>11.71298367423283</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135758763992</v>
+        <v>11.72135667690049</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461273193359</v>
+        <v>11.70461177825928</v>
       </c>
       <c r="C599" t="n">
-        <v>11.86368802281414</v>
+        <v>11.8636870561786</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414341881347</v>
+        <v>11.60414247332525</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786756602366</v>
+        <v>11.68786661371372</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12452,16 +12452,16 @@
         <v>45191</v>
       </c>
       <c r="B602" t="n">
-        <v>11.54553508758545</v>
+        <v>11.54553699493408</v>
       </c>
       <c r="C602" t="n">
-        <v>11.73810067103286</v>
+        <v>11.73810261019376</v>
       </c>
       <c r="D602" t="n">
-        <v>11.47855611993833</v>
+        <v>11.47855801622189</v>
       </c>
       <c r="E602" t="n">
-        <v>11.52878992508889</v>
+        <v>11.52879182967118</v>
       </c>
       <c r="F602" t="n">
         <v>228714</v>
@@ -12472,16 +12472,16 @@
         <v>45194</v>
       </c>
       <c r="B603" t="n">
-        <v>11.11854362487793</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C603" t="n">
-        <v>11.54553561458025</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="D603" t="n">
-        <v>11.10179846161704</v>
+        <v>11.10179941385507</v>
       </c>
       <c r="E603" t="n">
-        <v>11.54553561458025</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="F603" t="n">
         <v>266745</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27762027064262</v>
+        <v>11.27761930113372</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760720758964</v>
+        <v>10.91760626903017</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901345381215</v>
+        <v>11.21901248934153</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12552,16 +12552,16 @@
         <v>45198</v>
       </c>
       <c r="B607" t="n">
-        <v>11.11854362487793</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C607" t="n">
-        <v>11.41994899304756</v>
+        <v>11.41994997257442</v>
       </c>
       <c r="D607" t="n">
-        <v>11.06830813509526</v>
+        <v>11.06830908446071</v>
       </c>
       <c r="E607" t="n">
-        <v>11.12691578592358</v>
+        <v>11.126916740316</v>
       </c>
       <c r="F607" t="n">
         <v>376204</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876541137695</v>
+        <v>10.80876636505127</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854465153565</v>
+        <v>11.11854563254228</v>
       </c>
       <c r="D608" t="n">
-        <v>10.71666910786212</v>
+        <v>10.71667005341063</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854465153565</v>
+        <v>11.11854563254228</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12652,16 +12652,16 @@
         <v>45205</v>
       </c>
       <c r="B612" t="n">
-        <v>10.48224067687988</v>
+        <v>10.4822416305542</v>
       </c>
       <c r="C612" t="n">
-        <v>10.59945429392961</v>
+        <v>10.59945525826802</v>
       </c>
       <c r="D612" t="n">
-        <v>10.23944128189676</v>
+        <v>10.23944221348118</v>
       </c>
       <c r="E612" t="n">
-        <v>10.53247448335149</v>
+        <v>10.53247544159608</v>
       </c>
       <c r="F612" t="n">
         <v>125682</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691593170166</v>
+        <v>11.12691783905029</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226706443887</v>
+        <v>11.20226898470401</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690290798703</v>
+        <v>10.76690475362312</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970231084856</v>
+        <v>11.00970419810472</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12772,16 +12772,16 @@
         <v>45216</v>
       </c>
       <c r="B618" t="n">
-        <v>10.57433891296387</v>
+        <v>10.57433795928955</v>
       </c>
       <c r="C618" t="n">
-        <v>11.02644830129326</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="D618" t="n">
-        <v>10.41526362109882</v>
+        <v>10.41526268177113</v>
       </c>
       <c r="E618" t="n">
-        <v>11.02644830129326</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="F618" t="n">
         <v>572365</v>
@@ -12792,16 +12792,16 @@
         <v>45217</v>
       </c>
       <c r="B619" t="n">
-        <v>10.2478141784668</v>
+        <v>10.24781513214111</v>
       </c>
       <c r="C619" t="n">
-        <v>10.60782721634484</v>
+        <v>10.60782820352242</v>
       </c>
       <c r="D619" t="n">
-        <v>10.23106985549739</v>
+        <v>10.23107080761346</v>
       </c>
       <c r="E619" t="n">
-        <v>10.57433772923638</v>
+        <v>10.57433871329738</v>
       </c>
       <c r="F619" t="n">
         <v>234192</v>
@@ -12872,16 +12872,16 @@
         <v>45223</v>
       </c>
       <c r="B623" t="n">
-        <v>11.30273628234863</v>
+        <v>11.30273723602295</v>
       </c>
       <c r="C623" t="n">
-        <v>11.51204535675642</v>
+        <v>11.51204632809129</v>
       </c>
       <c r="D623" t="n">
-        <v>11.051563878954</v>
+        <v>11.05156481143551</v>
       </c>
       <c r="E623" t="n">
-        <v>11.14366017451449</v>
+        <v>11.14366111476667</v>
       </c>
       <c r="F623" t="n">
         <v>358083</v>
@@ -12892,16 +12892,16 @@
         <v>45224</v>
       </c>
       <c r="B624" t="n">
-        <v>11.25250339508057</v>
+        <v>11.25250244140625</v>
       </c>
       <c r="C624" t="n">
-        <v>11.37808919585427</v>
+        <v>11.37808823153628</v>
       </c>
       <c r="D624" t="n">
-        <v>11.06830993395344</v>
+        <v>11.06830899588992</v>
       </c>
       <c r="E624" t="n">
-        <v>11.26087555748688</v>
+        <v>11.26087460310301</v>
       </c>
       <c r="F624" t="n">
         <v>356609</v>
@@ -12932,16 +12932,16 @@
         <v>45226</v>
       </c>
       <c r="B626" t="n">
-        <v>10.98458480834961</v>
+        <v>10.98458576202393</v>
       </c>
       <c r="C626" t="n">
-        <v>11.53716257670716</v>
+        <v>11.53716357835591</v>
       </c>
       <c r="D626" t="n">
-        <v>10.96783964514047</v>
+        <v>10.96784059736098</v>
       </c>
       <c r="E626" t="n">
-        <v>11.33622482404551</v>
+        <v>11.33622580824897</v>
       </c>
       <c r="F626" t="n">
         <v>172878</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200588226318</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668177956321</v>
+        <v>11.07668076695393</v>
       </c>
       <c r="D627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200588226318</v>
       </c>
       <c r="E627" t="n">
-        <v>10.99295764074342</v>
+        <v>10.99295663578805</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -13012,16 +13012,16 @@
         <v>45233</v>
       </c>
       <c r="B630" t="n">
-        <v>11.21249866485596</v>
+        <v>11.21249961853027</v>
       </c>
       <c r="C630" t="n">
-        <v>11.21249866485596</v>
+        <v>11.21249961853027</v>
       </c>
       <c r="D630" t="n">
-        <v>10.68783784562804</v>
+        <v>10.68783875467755</v>
       </c>
       <c r="E630" t="n">
-        <v>10.78938553977454</v>
+        <v>10.78938645746115</v>
       </c>
       <c r="F630" t="n">
         <v>226607</v>
@@ -13092,16 +13092,16 @@
         <v>45239</v>
       </c>
       <c r="B634" t="n">
-        <v>11.33097171783447</v>
+        <v>11.33097076416016</v>
       </c>
       <c r="C634" t="n">
-        <v>11.63561228489743</v>
+        <v>11.63561130558296</v>
       </c>
       <c r="D634" t="n">
-        <v>11.25481093841988</v>
+        <v>11.25480999115565</v>
       </c>
       <c r="E634" t="n">
-        <v>11.33943374325882</v>
+        <v>11.3394327888723</v>
       </c>
       <c r="F634" t="n">
         <v>143591</v>
@@ -13192,16 +13192,16 @@
         <v>45247</v>
       </c>
       <c r="B639" t="n">
-        <v>12.85417938232422</v>
+        <v>12.85418033599854</v>
       </c>
       <c r="C639" t="n">
-        <v>12.85417938232422</v>
+        <v>12.85418033599854</v>
       </c>
       <c r="D639" t="n">
-        <v>12.48183836875342</v>
+        <v>12.4818392948031</v>
       </c>
       <c r="E639" t="n">
-        <v>12.7018578267184</v>
+        <v>12.70185876909171</v>
       </c>
       <c r="F639" t="n">
         <v>197425</v>
@@ -13212,16 +13212,16 @@
         <v>45250</v>
       </c>
       <c r="B640" t="n">
-        <v>12.99803829193115</v>
+        <v>12.99803733825684</v>
       </c>
       <c r="C640" t="n">
-        <v>13.12497293214611</v>
+        <v>13.12497196915852</v>
       </c>
       <c r="D640" t="n">
-        <v>12.59184999383886</v>
+        <v>12.59184906996684</v>
       </c>
       <c r="E640" t="n">
-        <v>12.7357078357516</v>
+        <v>12.73570690132464</v>
       </c>
       <c r="F640" t="n">
         <v>416026</v>
@@ -13272,16 +13272,16 @@
         <v>45253</v>
       </c>
       <c r="B643" t="n">
-        <v>12.48183917999268</v>
+        <v>12.48183822631836</v>
       </c>
       <c r="C643" t="n">
-        <v>12.66800884867945</v>
+        <v>12.66800788078085</v>
       </c>
       <c r="D643" t="n">
-        <v>12.42260414922735</v>
+        <v>12.42260320007888</v>
       </c>
       <c r="E643" t="n">
-        <v>12.42260414922735</v>
+        <v>12.42260320007888</v>
       </c>
       <c r="F643" t="n">
         <v>180148</v>
@@ -13332,16 +13332,16 @@
         <v>45258</v>
       </c>
       <c r="B646" t="n">
-        <v>13.21805667877197</v>
+        <v>13.21805763244629</v>
       </c>
       <c r="C646" t="n">
-        <v>13.37037653407904</v>
+        <v>13.37037749874314</v>
       </c>
       <c r="D646" t="n">
-        <v>12.99803722066519</v>
+        <v>12.99803815846524</v>
       </c>
       <c r="E646" t="n">
-        <v>13.20113092787359</v>
+        <v>13.20113188032672</v>
       </c>
       <c r="F646" t="n">
         <v>249995</v>
@@ -13392,16 +13392,16 @@
         <v>45261</v>
       </c>
       <c r="B649" t="n">
-        <v>13.22651863098145</v>
+        <v>13.22651958465576</v>
       </c>
       <c r="C649" t="n">
-        <v>13.35345240983534</v>
+        <v>13.35345337266199</v>
       </c>
       <c r="D649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="E649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="F649" t="n">
         <v>156128</v>
@@ -13412,16 +13412,16 @@
         <v>45264</v>
       </c>
       <c r="B650" t="n">
-        <v>12.76109313964844</v>
+        <v>12.76109409332275</v>
       </c>
       <c r="C650" t="n">
-        <v>13.22651811073723</v>
+        <v>13.22651909919413</v>
       </c>
       <c r="D650" t="n">
-        <v>12.76109313964844</v>
+        <v>12.76109409332275</v>
       </c>
       <c r="E650" t="n">
-        <v>13.22651811073723</v>
+        <v>13.22651909919413</v>
       </c>
       <c r="F650" t="n">
         <v>177619</v>
@@ -13432,16 +13432,16 @@
         <v>45265</v>
       </c>
       <c r="B651" t="n">
-        <v>12.83725452423096</v>
+        <v>12.83725357055664</v>
       </c>
       <c r="C651" t="n">
-        <v>12.94726511106283</v>
+        <v>12.94726414921587</v>
       </c>
       <c r="D651" t="n">
-        <v>12.73570766362991</v>
+        <v>12.73570671749947</v>
       </c>
       <c r="E651" t="n">
-        <v>12.7610945913298</v>
+        <v>12.76109364331337</v>
       </c>
       <c r="F651" t="n">
         <v>155706</v>
@@ -13452,16 +13452,16 @@
         <v>45266</v>
       </c>
       <c r="B652" t="n">
-        <v>11.9741039276123</v>
+        <v>11.97410297393799</v>
       </c>
       <c r="C652" t="n">
-        <v>12.82879233124775</v>
+        <v>12.82879130950201</v>
       </c>
       <c r="D652" t="n">
-        <v>11.9741039276123</v>
+        <v>11.97410297393799</v>
       </c>
       <c r="E652" t="n">
-        <v>12.82879233124775</v>
+        <v>12.82879130950201</v>
       </c>
       <c r="F652" t="n">
         <v>140431</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413126845579</v>
+        <v>12.30413217772953</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568784548951</v>
+        <v>12.51568877039725</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13512,16 +13512,16 @@
         <v>45271</v>
       </c>
       <c r="B655" t="n">
-        <v>12.73570728302002</v>
+        <v>12.7357063293457</v>
       </c>
       <c r="C655" t="n">
-        <v>13.05727360727768</v>
+        <v>13.05727262952386</v>
       </c>
       <c r="D655" t="n">
-        <v>12.57492369579195</v>
+        <v>12.57492275415741</v>
       </c>
       <c r="E655" t="n">
-        <v>12.82033008942451</v>
+        <v>12.82032912941347</v>
       </c>
       <c r="F655" t="n">
         <v>302669</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109408341076</v>
+        <v>12.76109316972536</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033884434287</v>
+        <v>12.93033791853966</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13552,16 +13552,16 @@
         <v>45273</v>
       </c>
       <c r="B657" t="n">
-        <v>13.27729225158691</v>
+        <v>13.27729320526123</v>
       </c>
       <c r="C657" t="n">
-        <v>13.29421630278417</v>
+        <v>13.2942172576741</v>
       </c>
       <c r="D657" t="n">
-        <v>12.92187697406255</v>
+        <v>12.92187790220829</v>
       </c>
       <c r="E657" t="n">
-        <v>13.23498127339527</v>
+        <v>13.2349822240305</v>
       </c>
       <c r="F657" t="n">
         <v>131160</v>
@@ -13592,16 +13592,16 @@
         <v>45275</v>
       </c>
       <c r="B659" t="n">
-        <v>12.76955604553223</v>
+        <v>12.76955699920654</v>
       </c>
       <c r="C659" t="n">
-        <v>13.2434421924373</v>
+        <v>13.24344318150306</v>
       </c>
       <c r="D659" t="n">
-        <v>12.76955604553223</v>
+        <v>12.76955699920654</v>
       </c>
       <c r="E659" t="n">
-        <v>13.22651814265413</v>
+        <v>13.22651913045595</v>
       </c>
       <c r="F659" t="n">
         <v>134531</v>
@@ -13612,16 +13612,16 @@
         <v>45278</v>
       </c>
       <c r="B660" t="n">
-        <v>13.16728115081787</v>
+        <v>13.1672830581665</v>
       </c>
       <c r="C660" t="n">
-        <v>13.6665550626705</v>
+        <v>13.66655704234154</v>
       </c>
       <c r="D660" t="n">
-        <v>13.15881912609787</v>
+        <v>13.15882103222074</v>
       </c>
       <c r="E660" t="n">
-        <v>13.26882884825144</v>
+        <v>13.26883077030978</v>
       </c>
       <c r="F660" t="n">
         <v>541076</v>
@@ -13692,16 +13692,16 @@
         <v>45282</v>
       </c>
       <c r="B664" t="n">
-        <v>13.88704872131348</v>
+        <v>13.88704776763916</v>
       </c>
       <c r="C664" t="n">
-        <v>14.31516630333975</v>
+        <v>14.31516532026503</v>
       </c>
       <c r="D664" t="n">
-        <v>13.74434345803615</v>
+        <v>13.74434251416193</v>
       </c>
       <c r="E664" t="n">
-        <v>13.89596757624402</v>
+        <v>13.89596662195722</v>
       </c>
       <c r="F664" t="n">
         <v>242936</v>
@@ -13732,16 +13732,16 @@
         <v>45287</v>
       </c>
       <c r="B666" t="n">
-        <v>14.54706287384033</v>
+        <v>14.54706192016602</v>
       </c>
       <c r="C666" t="n">
-        <v>14.54706287384033</v>
+        <v>14.54706192016602</v>
       </c>
       <c r="D666" t="n">
-        <v>13.89596764275405</v>
+        <v>13.89596673176415</v>
       </c>
       <c r="E666" t="n">
-        <v>14.18137906677191</v>
+        <v>14.18137813707104</v>
       </c>
       <c r="F666" t="n">
         <v>258949</v>
@@ -13772,16 +13772,16 @@
         <v>45293</v>
       </c>
       <c r="B668" t="n">
-        <v>14.0832691192627</v>
+        <v>14.08326816558838</v>
       </c>
       <c r="C668" t="n">
-        <v>14.5738195893155</v>
+        <v>14.57381860242266</v>
       </c>
       <c r="D668" t="n">
-        <v>13.94056385382812</v>
+        <v>13.94056290981735</v>
       </c>
       <c r="E668" t="n">
-        <v>14.27057045221845</v>
+        <v>14.27056948586068</v>
       </c>
       <c r="F668" t="n">
         <v>272434</v>
@@ -13792,16 +13792,16 @@
         <v>45294</v>
       </c>
       <c r="B669" t="n">
-        <v>14.23489379882812</v>
+        <v>14.23489284515381</v>
       </c>
       <c r="C669" t="n">
-        <v>14.35976135117554</v>
+        <v>14.35976038913565</v>
       </c>
       <c r="D669" t="n">
-        <v>13.64623324870215</v>
+        <v>13.64623233446546</v>
       </c>
       <c r="E669" t="n">
-        <v>13.92272402186245</v>
+        <v>13.92272308910211</v>
       </c>
       <c r="F669" t="n">
         <v>120520</v>
@@ -13832,16 +13832,16 @@
         <v>45296</v>
       </c>
       <c r="B671" t="n">
-        <v>13.96731853485107</v>
+        <v>13.96731948852539</v>
       </c>
       <c r="C671" t="n">
-        <v>14.27056852713726</v>
+        <v>14.27056950151718</v>
       </c>
       <c r="D671" t="n">
-        <v>13.86920845407544</v>
+        <v>13.8692094010509</v>
       </c>
       <c r="E671" t="n">
-        <v>13.97623828481034</v>
+        <v>13.97623923909369</v>
       </c>
       <c r="F671" t="n">
         <v>90074</v>
@@ -13852,16 +13852,16 @@
         <v>45299</v>
       </c>
       <c r="B672" t="n">
-        <v>13.7978572845459</v>
+        <v>13.79785633087158</v>
       </c>
       <c r="C672" t="n">
-        <v>13.97623975716477</v>
+        <v>13.97623879116109</v>
       </c>
       <c r="D672" t="n">
-        <v>13.66407087813031</v>
+        <v>13.66406993370299</v>
       </c>
       <c r="E672" t="n">
-        <v>13.96732000626583</v>
+        <v>13.96731904087866</v>
       </c>
       <c r="F672" t="n">
         <v>138218</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623825073242</v>
+        <v>13.97623920440674</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461235886199</v>
+        <v>13.82461330219005</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13912,16 +13912,16 @@
         <v>45302</v>
       </c>
       <c r="B675" t="n">
-        <v>14.20813465118408</v>
+        <v>14.2081356048584</v>
       </c>
       <c r="C675" t="n">
-        <v>14.20813465118408</v>
+        <v>14.2081356048584</v>
       </c>
       <c r="D675" t="n">
-        <v>13.64623248909294</v>
+        <v>13.64623340505142</v>
       </c>
       <c r="E675" t="n">
-        <v>14.13678292022506</v>
+        <v>14.13678386911013</v>
       </c>
       <c r="F675" t="n">
         <v>191209</v>
@@ -13992,16 +13992,16 @@
         <v>45308</v>
       </c>
       <c r="B679" t="n">
-        <v>14.37759780883789</v>
+        <v>14.37759876251221</v>
       </c>
       <c r="C679" t="n">
-        <v>14.52922280864108</v>
+        <v>14.52922377237277</v>
       </c>
       <c r="D679" t="n">
-        <v>14.24381141328681</v>
+        <v>14.243812358087</v>
       </c>
       <c r="E679" t="n">
-        <v>14.3240837882757</v>
+        <v>14.3240847384004</v>
       </c>
       <c r="F679" t="n">
         <v>153283</v>
@@ -14112,16 +14112,16 @@
         <v>45316</v>
       </c>
       <c r="B685" t="n">
-        <v>14.57381820678711</v>
+        <v>14.57381916046143</v>
       </c>
       <c r="C685" t="n">
-        <v>14.77003837619403</v>
+        <v>14.77003934270851</v>
       </c>
       <c r="D685" t="n">
-        <v>14.46678926786436</v>
+        <v>14.46679021453496</v>
       </c>
       <c r="E685" t="n">
-        <v>14.60949541585844</v>
+        <v>14.60949637186738</v>
       </c>
       <c r="F685" t="n">
         <v>152967</v>
@@ -14252,16 +14252,16 @@
         <v>45327</v>
       </c>
       <c r="B692" t="n">
-        <v>13.21811485290527</v>
+        <v>13.21811580657959</v>
       </c>
       <c r="C692" t="n">
-        <v>13.76218019901698</v>
+        <v>13.76218119194509</v>
       </c>
       <c r="D692" t="n">
-        <v>13.21811485290527</v>
+        <v>13.21811580657959</v>
       </c>
       <c r="E692" t="n">
-        <v>13.76218019901698</v>
+        <v>13.76218119194509</v>
       </c>
       <c r="F692" t="n">
         <v>142538</v>
@@ -14272,16 +14272,16 @@
         <v>45328</v>
       </c>
       <c r="B693" t="n">
-        <v>13.41433429718018</v>
+        <v>13.41433525085449</v>
       </c>
       <c r="C693" t="n">
-        <v>13.47676806610936</v>
+        <v>13.47676902422233</v>
       </c>
       <c r="D693" t="n">
-        <v>13.08432774489562</v>
+        <v>13.08432867510856</v>
       </c>
       <c r="E693" t="n">
-        <v>13.20027553283766</v>
+        <v>13.20027647129375</v>
       </c>
       <c r="F693" t="n">
         <v>1178021</v>
@@ -14352,16 +14352,16 @@
         <v>45336</v>
       </c>
       <c r="B697" t="n">
-        <v>13.5392017364502</v>
+        <v>13.53920078277588</v>
       </c>
       <c r="C697" t="n">
-        <v>13.86920920427044</v>
+        <v>13.86920822735105</v>
       </c>
       <c r="D697" t="n">
-        <v>13.43217279602306</v>
+        <v>13.43217184988765</v>
       </c>
       <c r="E697" t="n">
-        <v>13.86920920427044</v>
+        <v>13.86920822735105</v>
       </c>
       <c r="F697" t="n">
         <v>116200</v>
@@ -14372,16 +14372,16 @@
         <v>45337</v>
       </c>
       <c r="B698" t="n">
-        <v>13.5124454498291</v>
+        <v>13.51244449615479</v>
       </c>
       <c r="C698" t="n">
-        <v>13.65515160274826</v>
+        <v>13.6551506390021</v>
       </c>
       <c r="D698" t="n">
-        <v>13.33406298270443</v>
+        <v>13.3340620416199</v>
       </c>
       <c r="E698" t="n">
-        <v>13.5124454498291</v>
+        <v>13.51244449615479</v>
       </c>
       <c r="F698" t="n">
         <v>118097</v>
@@ -14392,16 +14392,16 @@
         <v>45338</v>
       </c>
       <c r="B699" t="n">
-        <v>13.88704872131348</v>
+        <v>13.88704776763916</v>
       </c>
       <c r="C699" t="n">
-        <v>14.1278649732154</v>
+        <v>14.12786400300335</v>
       </c>
       <c r="D699" t="n">
-        <v>13.29838727005164</v>
+        <v>13.29838635680286</v>
       </c>
       <c r="E699" t="n">
-        <v>13.51244606106478</v>
+        <v>13.51244513311579</v>
       </c>
       <c r="F699" t="n">
         <v>253260</v>
@@ -14452,16 +14452,16 @@
         <v>45343</v>
       </c>
       <c r="B702" t="n">
-        <v>13.75326156616211</v>
+        <v>13.75326061248779</v>
       </c>
       <c r="C702" t="n">
-        <v>14.09218699609062</v>
+        <v>14.09218601891464</v>
       </c>
       <c r="D702" t="n">
-        <v>13.5213641817828</v>
+        <v>13.52136324418864</v>
       </c>
       <c r="E702" t="n">
-        <v>13.85137165336216</v>
+        <v>13.85137069288472</v>
       </c>
       <c r="F702" t="n">
         <v>146120</v>
@@ -14472,16 +14472,16 @@
         <v>45344</v>
       </c>
       <c r="B703" t="n">
-        <v>13.71758460998535</v>
+        <v>13.71758556365967</v>
       </c>
       <c r="C703" t="n">
-        <v>13.8335342004174</v>
+        <v>13.83353516215277</v>
       </c>
       <c r="D703" t="n">
-        <v>13.37865917378605</v>
+        <v>13.37866010389759</v>
       </c>
       <c r="E703" t="n">
-        <v>13.77109952984718</v>
+        <v>13.77110048724197</v>
       </c>
       <c r="F703" t="n">
         <v>122205</v>
@@ -14512,16 +14512,16 @@
         <v>45348</v>
       </c>
       <c r="B705" t="n">
-        <v>13.5392017364502</v>
+        <v>13.53920078277588</v>
       </c>
       <c r="C705" t="n">
-        <v>13.73542190861516</v>
+        <v>13.73542094111948</v>
       </c>
       <c r="D705" t="n">
-        <v>13.30730525080952</v>
+        <v>13.30730431346953</v>
       </c>
       <c r="E705" t="n">
-        <v>13.52136402776089</v>
+        <v>13.52136307534302</v>
       </c>
       <c r="F705" t="n">
         <v>310571</v>
@@ -14692,16 +14692,16 @@
         <v>45359</v>
       </c>
       <c r="B714" t="n">
-        <v>13.41433429718018</v>
+        <v>13.41433525085449</v>
       </c>
       <c r="C714" t="n">
-        <v>13.42325315099948</v>
+        <v>13.42325410530787</v>
       </c>
       <c r="D714" t="n">
-        <v>12.96837906085655</v>
+        <v>12.96837998282627</v>
       </c>
       <c r="E714" t="n">
-        <v>13.15567947154708</v>
+        <v>13.15568040683267</v>
       </c>
       <c r="F714" t="n">
         <v>200691</v>
@@ -14732,16 +14732,16 @@
         <v>45363</v>
       </c>
       <c r="B716" t="n">
-        <v>15.42113304138184</v>
+        <v>15.42113399505615</v>
       </c>
       <c r="C716" t="n">
-        <v>15.98303607223336</v>
+        <v>15.98303706065691</v>
       </c>
       <c r="D716" t="n">
-        <v>13.85137084203124</v>
+        <v>13.85137169862826</v>
       </c>
       <c r="E716" t="n">
-        <v>14.09218617065416</v>
+        <v>14.09218704214369</v>
       </c>
       <c r="F716" t="n">
         <v>1351743</v>
@@ -14752,16 +14752,16 @@
         <v>45364</v>
       </c>
       <c r="B717" t="n">
-        <v>15.79573631286621</v>
+        <v>15.79573535919189</v>
       </c>
       <c r="C717" t="n">
-        <v>15.99195648389114</v>
+        <v>15.99195551836995</v>
       </c>
       <c r="D717" t="n">
-        <v>15.33194334427948</v>
+        <v>15.33194241860686</v>
       </c>
       <c r="E717" t="n">
-        <v>15.33194334427948</v>
+        <v>15.33194241860686</v>
       </c>
       <c r="F717" t="n">
         <v>474916</v>
@@ -14792,16 +14792,16 @@
         <v>45366</v>
       </c>
       <c r="B719" t="n">
-        <v>15.77789878845215</v>
+        <v>15.77789974212646</v>
       </c>
       <c r="C719" t="n">
-        <v>15.86708912461579</v>
+        <v>15.8670900836811</v>
       </c>
       <c r="D719" t="n">
-        <v>15.37653869132738</v>
+        <v>15.37653962074202</v>
       </c>
       <c r="E719" t="n">
-        <v>15.67978870179447</v>
+        <v>15.67978964953865</v>
       </c>
       <c r="F719" t="n">
         <v>999032</v>
@@ -14832,16 +14832,16 @@
         <v>45370</v>
       </c>
       <c r="B721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="C721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="D721" t="n">
-        <v>15.61735280122237</v>
+        <v>15.61735464537877</v>
       </c>
       <c r="E721" t="n">
-        <v>15.8314124586462</v>
+        <v>15.83141432807958</v>
       </c>
       <c r="F721" t="n">
         <v>227239</v>
@@ -14852,16 +14852,16 @@
         <v>45371</v>
       </c>
       <c r="B722" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="C722" t="n">
-        <v>16.2952069476677</v>
+        <v>16.29520886762698</v>
       </c>
       <c r="D722" t="n">
-        <v>16.08114726986159</v>
+        <v>16.08114916459959</v>
       </c>
       <c r="E722" t="n">
-        <v>16.15250169059311</v>
+        <v>16.15250359373834</v>
       </c>
       <c r="F722" t="n">
         <v>449422</v>
@@ -14872,16 +14872,16 @@
         <v>45372</v>
       </c>
       <c r="B723" t="n">
-        <v>16.58061790466309</v>
+        <v>16.58061981201172</v>
       </c>
       <c r="C723" t="n">
-        <v>16.58061790466309</v>
+        <v>16.58061981201172</v>
       </c>
       <c r="D723" t="n">
-        <v>16.11682316862342</v>
+        <v>16.1168250226195</v>
       </c>
       <c r="E723" t="n">
-        <v>16.25061045636449</v>
+        <v>16.25061232575078</v>
       </c>
       <c r="F723" t="n">
         <v>298350</v>
@@ -14892,16 +14892,16 @@
         <v>45373</v>
       </c>
       <c r="B724" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="C724" t="n">
-        <v>16.65197009035419</v>
+        <v>16.65197205234856</v>
       </c>
       <c r="D724" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="E724" t="n">
-        <v>16.42007449565653</v>
+        <v>16.42007643032814</v>
       </c>
       <c r="F724" t="n">
         <v>404437</v>
@@ -14952,16 +14952,16 @@
         <v>45378</v>
       </c>
       <c r="B727" t="n">
-        <v>15.43005466461182</v>
+        <v>15.4300537109375</v>
       </c>
       <c r="C727" t="n">
-        <v>15.75114240582048</v>
+        <v>15.75114143230092</v>
       </c>
       <c r="D727" t="n">
-        <v>14.90382698557158</v>
+        <v>14.90382606442144</v>
       </c>
       <c r="E727" t="n">
-        <v>15.23383447788399</v>
+        <v>15.23383353633731</v>
       </c>
       <c r="F727" t="n">
         <v>340806</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196235656738</v>
+        <v>16.32196426391602</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55385792212777</v>
+        <v>16.55385985657521</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26058922811916</v>
+        <v>15.26059101143806</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005192362683</v>
+        <v>15.43005372674877</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -14992,16 +14992,16 @@
         <v>45383</v>
       </c>
       <c r="B729" t="n">
-        <v>16.41115379333496</v>
+        <v>16.41115570068359</v>
       </c>
       <c r="C729" t="n">
-        <v>16.52710158395999</v>
+        <v>16.52710350478439</v>
       </c>
       <c r="D729" t="n">
-        <v>16.06330862926576</v>
+        <v>16.06331049618689</v>
       </c>
       <c r="E729" t="n">
-        <v>16.25061083648447</v>
+        <v>16.25061272517437</v>
       </c>
       <c r="F729" t="n">
         <v>424348</v>
@@ -15052,16 +15052,16 @@
         <v>45386</v>
       </c>
       <c r="B732" t="n">
-        <v>15.83141326904297</v>
+        <v>15.83141231536865</v>
       </c>
       <c r="C732" t="n">
-        <v>16.42007377270343</v>
+        <v>16.42007278356858</v>
       </c>
       <c r="D732" t="n">
-        <v>15.83141326904297</v>
+        <v>15.83141231536865</v>
       </c>
       <c r="E732" t="n">
-        <v>16.1079058125728</v>
+        <v>16.10790484224275</v>
       </c>
       <c r="F732" t="n">
         <v>700260</v>
@@ -15092,16 +15092,16 @@
         <v>45390</v>
       </c>
       <c r="B734" t="n">
-        <v>15.22491455078125</v>
+        <v>15.22491359710693</v>
       </c>
       <c r="C734" t="n">
-        <v>15.84033256496746</v>
+        <v>15.84033157274394</v>
       </c>
       <c r="D734" t="n">
-        <v>15.20707684097428</v>
+        <v>15.2070758884173</v>
       </c>
       <c r="E734" t="n">
-        <v>15.7422224727377</v>
+        <v>15.7422214866597</v>
       </c>
       <c r="F734" t="n">
         <v>693201</v>
@@ -15112,16 +15112,16 @@
         <v>45391</v>
       </c>
       <c r="B735" t="n">
-        <v>15.51924228668213</v>
+        <v>15.51924419403076</v>
       </c>
       <c r="C735" t="n">
-        <v>15.59059490642255</v>
+        <v>15.59059682254057</v>
       </c>
       <c r="D735" t="n">
-        <v>15.21599230863985</v>
+        <v>15.2159941787184</v>
       </c>
       <c r="E735" t="n">
-        <v>15.26950722149366</v>
+        <v>15.26950909814931</v>
       </c>
       <c r="F735" t="n">
         <v>380734</v>
@@ -15132,16 +15132,16 @@
         <v>45392</v>
       </c>
       <c r="B736" t="n">
-        <v>15.14328002929688</v>
+        <v>15.14327907562256</v>
       </c>
       <c r="C736" t="n">
-        <v>15.53754305795394</v>
+        <v>15.53754207945022</v>
       </c>
       <c r="D736" t="n">
-        <v>15.05367389941404</v>
+        <v>15.05367295138282</v>
       </c>
       <c r="E736" t="n">
-        <v>15.53754305795394</v>
+        <v>15.53754207945022</v>
       </c>
       <c r="F736" t="n">
         <v>317419</v>
@@ -15152,16 +15152,16 @@
         <v>45393</v>
       </c>
       <c r="B737" t="n">
-        <v>14.95510768890381</v>
+        <v>14.95510864257812</v>
       </c>
       <c r="C737" t="n">
-        <v>15.2060023283815</v>
+        <v>15.20600329805515</v>
       </c>
       <c r="D737" t="n">
-        <v>14.75797708255414</v>
+        <v>14.75797802365761</v>
       </c>
       <c r="E737" t="n">
-        <v>15.02679276770881</v>
+        <v>15.02679372595442</v>
       </c>
       <c r="F737" t="n">
         <v>214129</v>
@@ -15172,16 +15172,16 @@
         <v>45394</v>
       </c>
       <c r="B738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="C738" t="n">
-        <v>15.1432798316879</v>
+        <v>15.14327886659233</v>
       </c>
       <c r="D738" t="n">
-        <v>14.76693785469897</v>
+        <v>14.76693691358803</v>
       </c>
       <c r="E738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="F738" t="n">
         <v>376247</v>
@@ -15252,16 +15252,16 @@
         <v>45400</v>
       </c>
       <c r="B742" t="n">
-        <v>14.8834228515625</v>
+        <v>14.88342380523682</v>
       </c>
       <c r="C742" t="n">
-        <v>15.29560598790641</v>
+        <v>15.29560696799188</v>
       </c>
       <c r="D742" t="n">
-        <v>14.83862068738918</v>
+        <v>14.83862163819274</v>
       </c>
       <c r="E742" t="n">
-        <v>14.87446277716666</v>
+        <v>14.87446373026684</v>
       </c>
       <c r="F742" t="n">
         <v>502607</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051448822021</v>
+        <v>15.77051544189453</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804076002569</v>
+        <v>15.87804172020233</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847573748455</v>
+        <v>15.09847665051934</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808006789204</v>
+        <v>15.18808098634539</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15372,16 +15372,16 @@
         <v>45408</v>
       </c>
       <c r="B748" t="n">
-        <v>16.41567420959473</v>
+        <v>16.41567230224609</v>
       </c>
       <c r="C748" t="n">
-        <v>16.74721403793184</v>
+        <v>16.74721209206137</v>
       </c>
       <c r="D748" t="n">
-        <v>16.14685939194446</v>
+        <v>16.14685751582961</v>
       </c>
       <c r="E748" t="n">
-        <v>16.48735839992738</v>
+        <v>16.48735648424971</v>
       </c>
       <c r="F748" t="n">
         <v>618795</v>
@@ -15392,16 +15392,16 @@
         <v>45411</v>
       </c>
       <c r="B749" t="n">
-        <v>16.50527954101562</v>
+        <v>16.50527763366699</v>
       </c>
       <c r="C749" t="n">
-        <v>16.50527954101562</v>
+        <v>16.50527763366699</v>
       </c>
       <c r="D749" t="n">
-        <v>16.23646294424257</v>
+        <v>16.23646106795836</v>
       </c>
       <c r="E749" t="n">
-        <v>16.40671243995541</v>
+        <v>16.40671054399719</v>
       </c>
       <c r="F749" t="n">
         <v>222938</v>
@@ -15492,16 +15492,16 @@
         <v>45419</v>
       </c>
       <c r="B754" t="n">
-        <v>16.57696151733398</v>
+        <v>16.57696342468262</v>
       </c>
       <c r="C754" t="n">
-        <v>16.6665658428468</v>
+        <v>16.66656776050532</v>
       </c>
       <c r="D754" t="n">
-        <v>16.29022480818252</v>
+        <v>16.29022668253917</v>
       </c>
       <c r="E754" t="n">
-        <v>16.41567122233926</v>
+        <v>16.4156731111298</v>
       </c>
       <c r="F754" t="n">
         <v>374150</v>
@@ -15552,16 +15552,16 @@
         <v>45422</v>
       </c>
       <c r="B757" t="n">
-        <v>16.10205459594727</v>
+        <v>16.1020565032959</v>
       </c>
       <c r="C757" t="n">
-        <v>16.83681657186323</v>
+        <v>16.83681856624717</v>
       </c>
       <c r="D757" t="n">
-        <v>16.07517168331335</v>
+        <v>16.0751735874776</v>
       </c>
       <c r="E757" t="n">
-        <v>16.82785739317944</v>
+        <v>16.82785938650213</v>
       </c>
       <c r="F757" t="n">
         <v>188543</v>
@@ -15572,16 +15572,16 @@
         <v>45425</v>
       </c>
       <c r="B758" t="n">
-        <v>15.76155471801758</v>
+        <v>15.76155376434326</v>
       </c>
       <c r="C758" t="n">
-        <v>15.94076518467647</v>
+        <v>15.94076422015877</v>
       </c>
       <c r="D758" t="n">
-        <v>15.68091135216679</v>
+        <v>15.68091040337191</v>
       </c>
       <c r="E758" t="n">
-        <v>15.90492309134469</v>
+        <v>15.90492212899567</v>
       </c>
       <c r="F758" t="n">
         <v>299278</v>
@@ -15592,16 +15592,16 @@
         <v>45426</v>
       </c>
       <c r="B759" t="n">
-        <v>15.61818790435791</v>
+        <v>15.61818695068359</v>
       </c>
       <c r="C759" t="n">
-        <v>15.74363433305432</v>
+        <v>15.74363337172002</v>
       </c>
       <c r="D759" t="n">
-        <v>15.38521340507279</v>
+        <v>15.38521246562432</v>
       </c>
       <c r="E759" t="n">
-        <v>15.67195014745801</v>
+        <v>15.67194919050088</v>
       </c>
       <c r="F759" t="n">
         <v>391243</v>
@@ -15612,16 +15612,16 @@
         <v>45427</v>
       </c>
       <c r="B760" t="n">
-        <v>15.76155471801758</v>
+        <v>15.76155376434326</v>
       </c>
       <c r="C760" t="n">
-        <v>15.88700294077594</v>
+        <v>15.8870019795112</v>
       </c>
       <c r="D760" t="n">
-        <v>15.09847688747684</v>
+        <v>15.09847597392295</v>
       </c>
       <c r="E760" t="n">
-        <v>15.59130522274021</v>
+        <v>15.59130427936707</v>
       </c>
       <c r="F760" t="n">
         <v>279879</v>
@@ -15632,16 +15632,16 @@
         <v>45428</v>
       </c>
       <c r="B761" t="n">
-        <v>15.81531810760498</v>
+        <v>15.8153190612793</v>
       </c>
       <c r="C761" t="n">
-        <v>16.12893596338921</v>
+        <v>16.1289369359749</v>
       </c>
       <c r="D761" t="n">
-        <v>15.63610764827196</v>
+        <v>15.63610859113976</v>
       </c>
       <c r="E761" t="n">
-        <v>15.80635713658978</v>
+        <v>15.80635808972374</v>
       </c>
       <c r="F761" t="n">
         <v>286904</v>
@@ -15652,16 +15652,16 @@
         <v>45429</v>
       </c>
       <c r="B762" t="n">
-        <v>15.41209411621094</v>
+        <v>15.41209316253662</v>
       </c>
       <c r="C762" t="n">
-        <v>15.87804131017911</v>
+        <v>15.87804032767277</v>
       </c>
       <c r="D762" t="n">
-        <v>15.27768671984559</v>
+        <v>15.27768577448818</v>
       </c>
       <c r="E762" t="n">
-        <v>15.83323824732593</v>
+        <v>15.83323726759193</v>
       </c>
       <c r="F762" t="n">
         <v>361357</v>
@@ -15712,16 +15712,16 @@
         <v>45434</v>
       </c>
       <c r="B765" t="n">
-        <v>14.92822647094727</v>
+        <v>14.92822742462158</v>
       </c>
       <c r="C765" t="n">
-        <v>15.1074369265467</v>
+        <v>15.10743789166969</v>
       </c>
       <c r="D765" t="n">
-        <v>14.82966027231904</v>
+        <v>14.82966121969655</v>
       </c>
       <c r="E765" t="n">
-        <v>15.0626338645983</v>
+        <v>15.06263482685909</v>
       </c>
       <c r="F765" t="n">
         <v>235522</v>
@@ -15732,16 +15732,16 @@
         <v>45435</v>
       </c>
       <c r="B766" t="n">
-        <v>14.87446403503418</v>
+        <v>14.87446308135986</v>
       </c>
       <c r="C766" t="n">
-        <v>14.94614822065114</v>
+        <v>14.9461472623808</v>
       </c>
       <c r="D766" t="n">
-        <v>14.73109566380025</v>
+        <v>14.73109471931798</v>
       </c>
       <c r="E766" t="n">
-        <v>14.93718724940046</v>
+        <v>14.93718629170465</v>
       </c>
       <c r="F766" t="n">
         <v>226398</v>
@@ -15852,16 +15852,16 @@
         <v>45446</v>
       </c>
       <c r="B772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="C772" t="n">
-        <v>15.36729159771533</v>
+        <v>15.36729261993504</v>
       </c>
       <c r="D772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="E772" t="n">
-        <v>14.69525198216746</v>
+        <v>14.69525295968364</v>
       </c>
       <c r="F772" t="n">
         <v>2218059</v>
@@ -15872,16 +15872,16 @@
         <v>45447</v>
       </c>
       <c r="B773" t="n">
-        <v>14.18450450897217</v>
+        <v>14.18450355529785</v>
       </c>
       <c r="C773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="D773" t="n">
-        <v>14.01425411633309</v>
+        <v>14.0142531741053</v>
       </c>
       <c r="E773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="F773" t="n">
         <v>553151</v>
@@ -15952,16 +15952,16 @@
         <v>45453</v>
       </c>
       <c r="B777" t="n">
-        <v>13.27949047088623</v>
+        <v>13.27949142456055</v>
       </c>
       <c r="C777" t="n">
-        <v>13.53038600843974</v>
+        <v>13.53038698013227</v>
       </c>
       <c r="D777" t="n">
-        <v>13.27949047088623</v>
+        <v>13.27949142456055</v>
       </c>
       <c r="E777" t="n">
-        <v>13.43181980839046</v>
+        <v>13.43182077300439</v>
       </c>
       <c r="F777" t="n">
         <v>375304</v>
@@ -16052,16 +16052,16 @@
         <v>45460</v>
       </c>
       <c r="B782" t="n">
-        <v>13.16300392150879</v>
+        <v>13.16300487518311</v>
       </c>
       <c r="C782" t="n">
-        <v>13.45870072497843</v>
+        <v>13.45870170007631</v>
       </c>
       <c r="D782" t="n">
-        <v>12.93899040412829</v>
+        <v>12.93899134157258</v>
       </c>
       <c r="E782" t="n">
-        <v>13.04651667740763</v>
+        <v>13.04651762264232</v>
       </c>
       <c r="F782" t="n">
         <v>743268</v>
@@ -16072,16 +16072,16 @@
         <v>45461</v>
       </c>
       <c r="B783" t="n">
-        <v>13.47662162780762</v>
+        <v>13.47662258148193</v>
       </c>
       <c r="C783" t="n">
-        <v>13.55726588386456</v>
+        <v>13.55726684324567</v>
       </c>
       <c r="D783" t="n">
-        <v>13.06443758460185</v>
+        <v>13.06443850910792</v>
       </c>
       <c r="E783" t="n">
-        <v>13.08235862995862</v>
+        <v>13.08235955573288</v>
       </c>
       <c r="F783" t="n">
         <v>385685</v>
@@ -16172,16 +16172,16 @@
         <v>45468</v>
       </c>
       <c r="B788" t="n">
-        <v>12.72393989562988</v>
+        <v>12.72393894195557</v>
       </c>
       <c r="C788" t="n">
-        <v>13.24364936702643</v>
+        <v>13.24364837439928</v>
       </c>
       <c r="D788" t="n">
-        <v>12.71497892400382</v>
+        <v>12.71497797100114</v>
       </c>
       <c r="E788" t="n">
-        <v>13.20780727271652</v>
+        <v>13.20780628277578</v>
       </c>
       <c r="F788" t="n">
         <v>394179</v>
@@ -16192,16 +16192,16 @@
         <v>45469</v>
       </c>
       <c r="B789" t="n">
-        <v>12.84042549133301</v>
+        <v>12.84042453765869</v>
       </c>
       <c r="C789" t="n">
-        <v>12.8941886296042</v>
+        <v>12.89418767193683</v>
       </c>
       <c r="D789" t="n">
-        <v>12.67017510542567</v>
+        <v>12.67017416439606</v>
       </c>
       <c r="E789" t="n">
-        <v>12.78666235306181</v>
+        <v>12.78666140338055</v>
       </c>
       <c r="F789" t="n">
         <v>397115</v>
@@ -16212,16 +16212,16 @@
         <v>45470</v>
       </c>
       <c r="B790" t="n">
-        <v>13.1809253692627</v>
+        <v>13.18092441558838</v>
       </c>
       <c r="C790" t="n">
-        <v>13.26157052473157</v>
+        <v>13.26156956522237</v>
       </c>
       <c r="D790" t="n">
-        <v>12.83146452239273</v>
+        <v>12.83146359400282</v>
       </c>
       <c r="E790" t="n">
-        <v>12.90314870676636</v>
+        <v>12.90314777318991</v>
       </c>
       <c r="F790" t="n">
         <v>447659</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61102962493896</v>
+        <v>13.61103057861328</v>
       </c>
       <c r="C795" t="n">
-        <v>13.70063484980648</v>
+        <v>13.7006358097591</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766126515094</v>
+        <v>13.46766220877997</v>
       </c>
       <c r="E795" t="n">
-        <v>13.59310768386841</v>
+        <v>13.593108636287</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16332,16 +16332,16 @@
         <v>45478</v>
       </c>
       <c r="B796" t="n">
-        <v>13.54830551147461</v>
+        <v>13.54830646514893</v>
       </c>
       <c r="C796" t="n">
-        <v>13.8888053657699</v>
+        <v>13.88880634341223</v>
       </c>
       <c r="D796" t="n">
-        <v>13.27948983703096</v>
+        <v>13.27949077178316</v>
       </c>
       <c r="E796" t="n">
-        <v>13.87088521690404</v>
+        <v>13.87088619328496</v>
       </c>
       <c r="F796" t="n">
         <v>907063</v>
@@ -16532,16 +16532,16 @@
         <v>45492</v>
       </c>
       <c r="B806" t="n">
-        <v>13.79024028778076</v>
+        <v>13.79023933410645</v>
       </c>
       <c r="C806" t="n">
-        <v>13.89776656627055</v>
+        <v>13.89776560516017</v>
       </c>
       <c r="D806" t="n">
-        <v>13.65583288771709</v>
+        <v>13.65583194333782</v>
       </c>
       <c r="E806" t="n">
-        <v>13.89776656627055</v>
+        <v>13.89776560516017</v>
       </c>
       <c r="F806" t="n">
         <v>491387</v>
@@ -16552,16 +16552,16 @@
         <v>45495</v>
       </c>
       <c r="B807" t="n">
-        <v>13.98737335205078</v>
+        <v>13.98737239837646</v>
       </c>
       <c r="C807" t="n">
-        <v>14.11282068285336</v>
+        <v>14.11281972062591</v>
       </c>
       <c r="D807" t="n">
-        <v>13.79024093612098</v>
+        <v>13.79023999588737</v>
       </c>
       <c r="E807" t="n">
-        <v>13.79920190779832</v>
+        <v>13.79920096695374</v>
       </c>
       <c r="F807" t="n">
         <v>314378</v>
@@ -16592,16 +16592,16 @@
         <v>45497</v>
       </c>
       <c r="B809" t="n">
-        <v>13.58414840698242</v>
+        <v>13.58414745330811</v>
       </c>
       <c r="C809" t="n">
-        <v>13.77231983830065</v>
+        <v>13.77231887141577</v>
       </c>
       <c r="D809" t="n">
-        <v>13.52142429784398</v>
+        <v>13.5214233485732</v>
       </c>
       <c r="E809" t="n">
-        <v>13.72751677518789</v>
+        <v>13.7275158114484</v>
       </c>
       <c r="F809" t="n">
         <v>613342</v>
@@ -16692,16 +16692,16 @@
         <v>45504</v>
       </c>
       <c r="B814" t="n">
-        <v>13.43181896209717</v>
+        <v>13.43181991577148</v>
       </c>
       <c r="C814" t="n">
-        <v>13.61102940898888</v>
+        <v>13.61103037538734</v>
       </c>
       <c r="D814" t="n">
-        <v>13.40493694701489</v>
+        <v>13.40493789878055</v>
       </c>
       <c r="E814" t="n">
-        <v>13.46766105147551</v>
+        <v>13.46766200769466</v>
       </c>
       <c r="F814" t="n">
         <v>351395</v>
@@ -16712,16 +16712,16 @@
         <v>45505</v>
       </c>
       <c r="B815" t="n">
-        <v>13.36013603210449</v>
+        <v>13.36013507843018</v>
       </c>
       <c r="C815" t="n">
-        <v>13.64687277393235</v>
+        <v>13.64687179979016</v>
       </c>
       <c r="D815" t="n">
-        <v>13.29741281787821</v>
+        <v>13.29741186868121</v>
       </c>
       <c r="E815" t="n">
-        <v>13.44078029269502</v>
+        <v>13.44077933326414</v>
       </c>
       <c r="F815" t="n">
         <v>623514</v>
@@ -16792,16 +16792,16 @@
         <v>45511</v>
       </c>
       <c r="B819" t="n">
-        <v>12.93899059295654</v>
+        <v>12.93899154663086</v>
       </c>
       <c r="C819" t="n">
-        <v>13.00171470133341</v>
+        <v>13.00171565963084</v>
       </c>
       <c r="D819" t="n">
-        <v>12.75082006002013</v>
+        <v>12.75082099982525</v>
       </c>
       <c r="E819" t="n">
-        <v>13.00171470133341</v>
+        <v>13.00171565963084</v>
       </c>
       <c r="F819" t="n">
         <v>296971</v>
@@ -16812,16 +16812,16 @@
         <v>45512</v>
       </c>
       <c r="B820" t="n">
-        <v>12.8045825958252</v>
+        <v>12.80458354949951</v>
       </c>
       <c r="C820" t="n">
-        <v>13.10027938971694</v>
+        <v>13.1002803654145</v>
       </c>
       <c r="D820" t="n">
-        <v>12.8045825958252</v>
+        <v>12.80458354949951</v>
       </c>
       <c r="E820" t="n">
-        <v>13.00171409045204</v>
+        <v>13.00171505880854</v>
       </c>
       <c r="F820" t="n">
         <v>258486</v>
@@ -17112,16 +17112,16 @@
         <v>45533</v>
       </c>
       <c r="B835" t="n">
-        <v>11.42466354370117</v>
+        <v>11.42466449737549</v>
       </c>
       <c r="C835" t="n">
-        <v>12.123583432736</v>
+        <v>12.12358444475269</v>
       </c>
       <c r="D835" t="n">
-        <v>11.29921532719579</v>
+        <v>11.29921627039831</v>
       </c>
       <c r="E835" t="n">
-        <v>11.93541290017211</v>
+        <v>11.93541389648125</v>
       </c>
       <c r="F835" t="n">
         <v>1428127</v>
@@ -17152,16 +17152,16 @@
         <v>45537</v>
       </c>
       <c r="B837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="C837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="D837" t="n">
-        <v>11.42466408609577</v>
+        <v>11.42466315363044</v>
       </c>
       <c r="E837" t="n">
-        <v>11.56803156298606</v>
+        <v>11.56803061881927</v>
       </c>
       <c r="F837" t="n">
         <v>1157790</v>
@@ -17192,16 +17192,16 @@
         <v>45539</v>
       </c>
       <c r="B839" t="n">
-        <v>11.6486759185791</v>
+        <v>11.64867687225342</v>
       </c>
       <c r="C839" t="n">
-        <v>11.85476749250614</v>
+        <v>11.85476846305313</v>
       </c>
       <c r="D839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="E839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="F839" t="n">
         <v>552941</v>
@@ -17252,16 +17252,16 @@
         <v>45544</v>
       </c>
       <c r="B842" t="n">
-        <v>11.23649215698242</v>
+        <v>11.23649120330811</v>
       </c>
       <c r="C842" t="n">
-        <v>11.41570171928039</v>
+        <v>11.41570075039603</v>
       </c>
       <c r="D842" t="n">
-        <v>11.20961014017461</v>
+        <v>11.20960918878185</v>
       </c>
       <c r="E842" t="n">
-        <v>11.35297850689067</v>
+        <v>11.35297754332981</v>
       </c>
       <c r="F842" t="n">
         <v>579052</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37985992431641</v>
+        <v>11.37986087799072</v>
       </c>
       <c r="C844" t="n">
-        <v>11.52322828348119</v>
+        <v>11.5232292491703</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089895382008</v>
+        <v>11.37089990674344</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882089481273</v>
+        <v>11.38882184923801</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17312,16 +17312,16 @@
         <v>45547</v>
       </c>
       <c r="B845" t="n">
-        <v>11.34401893615723</v>
+        <v>11.34401798248291</v>
       </c>
       <c r="C845" t="n">
-        <v>11.47842633787816</v>
+        <v>11.47842537290442</v>
       </c>
       <c r="D845" t="n">
-        <v>11.29025579624943</v>
+        <v>11.2902548470949</v>
       </c>
       <c r="E845" t="n">
-        <v>11.39778207606503</v>
+        <v>11.39778111787093</v>
       </c>
       <c r="F845" t="n">
         <v>413998</v>
@@ -17372,16 +17372,16 @@
         <v>45552</v>
       </c>
       <c r="B848" t="n">
-        <v>11.53218936920166</v>
+        <v>11.53219032287598</v>
       </c>
       <c r="C848" t="n">
-        <v>11.63075466906374</v>
+        <v>11.63075563088909</v>
       </c>
       <c r="D848" t="n">
-        <v>11.39778108309321</v>
+        <v>11.3977820256524</v>
       </c>
       <c r="E848" t="n">
-        <v>11.5232283986158</v>
+        <v>11.52322935154908</v>
       </c>
       <c r="F848" t="n">
         <v>1190193</v>
@@ -17392,16 +17392,16 @@
         <v>45553</v>
       </c>
       <c r="B849" t="n">
-        <v>11.42466354370117</v>
+        <v>11.42466449737549</v>
       </c>
       <c r="C849" t="n">
-        <v>11.71139937996589</v>
+        <v>11.7114003575755</v>
       </c>
       <c r="D849" t="n">
-        <v>11.39778152699371</v>
+        <v>11.39778247842404</v>
       </c>
       <c r="E849" t="n">
-        <v>11.63075512203768</v>
+        <v>11.6307560929155</v>
       </c>
       <c r="F849" t="n">
         <v>662418</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276828765869</v>
+        <v>10.49276733398438</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029456250169</v>
+        <v>10.60029359905444</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212402957499</v>
+        <v>10.41212308323033</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900604633429</v>
+        <v>10.43900509754635</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -26592,19 +26592,39 @@
         <v>46230</v>
       </c>
       <c r="B1309" t="n">
-        <v>5.92</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="C1309" t="n">
-        <v>5.96</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="D1309" t="n">
-        <v>5.59</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="E1309" t="n">
-        <v>5.59</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="F1309" t="n">
         <v>1031800</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1310" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>192600</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2856616973877</v>
+        <v>13.28566360473633</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647174220278</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83010549167658</v>
+        <v>12.83010733362354</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647174220278</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970157623291</v>
+        <v>13.16970443725586</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606525790047</v>
+        <v>13.76606824847914</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404462813815</v>
+        <v>13.00404745317332</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42646959612849</v>
+        <v>13.42647251293245</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -532,16 +532,16 @@
         <v>44322</v>
       </c>
       <c r="B6" t="n">
-        <v>12.64788341522217</v>
+        <v>12.64788246154785</v>
       </c>
       <c r="C6" t="n">
-        <v>13.12828824992877</v>
+        <v>13.12828726003102</v>
       </c>
       <c r="D6" t="n">
-        <v>12.59818699465811</v>
+        <v>12.598186044731</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12828824992877</v>
+        <v>13.12828726003102</v>
       </c>
       <c r="F6" t="n">
         <v>671078</v>
@@ -552,16 +552,16 @@
         <v>44323</v>
       </c>
       <c r="B7" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C7" t="n">
-        <v>12.85495546357991</v>
+        <v>12.85495449619264</v>
       </c>
       <c r="D7" t="n">
-        <v>12.26687350523842</v>
+        <v>12.26687258210669</v>
       </c>
       <c r="E7" t="n">
-        <v>12.71414713079874</v>
+        <v>12.71414617400787</v>
       </c>
       <c r="F7" t="n">
         <v>847960</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566104888916</v>
+        <v>12.46566200256348</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75555946570089</v>
+        <v>12.75556044155362</v>
       </c>
       <c r="D10" t="n">
-        <v>12.3000040974216</v>
+        <v>12.30000503842248</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141875137399</v>
+        <v>12.34141969554326</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162181854248</v>
+        <v>13.40162372589111</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172308737706</v>
+        <v>13.93172507017088</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566158371901</v>
+        <v>12.4656633578597</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273319802321</v>
+        <v>12.67273500163479</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98142051696777</v>
+        <v>13.98142147064209</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778424385328</v>
+        <v>14.57778523820564</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495522297252</v>
+        <v>13.67495615574281</v>
       </c>
       <c r="E13" t="n">
-        <v>13.98970394752027</v>
+        <v>13.9897049017596</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889602661133</v>
+        <v>13.84889507293701</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24647160287482</v>
+        <v>14.24647062182232</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323988323951</v>
+        <v>13.68323894097274</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12223011947429</v>
+        <v>14.12222914697741</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -712,16 +712,16 @@
         <v>44335</v>
       </c>
       <c r="B15" t="n">
-        <v>13.484450340271</v>
+        <v>13.48444938659668</v>
       </c>
       <c r="C15" t="n">
-        <v>13.9482891600039</v>
+        <v>13.94828817352505</v>
       </c>
       <c r="D15" t="n">
-        <v>13.36020720486323</v>
+        <v>13.36020625997589</v>
       </c>
       <c r="E15" t="n">
-        <v>13.77434960260406</v>
+        <v>13.77434862842691</v>
       </c>
       <c r="F15" t="n">
         <v>804661</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253096774176</v>
       </c>
       <c r="D16" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838856883414</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253096774176</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.2690954208374</v>
+        <v>13.26909637451172</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182314288226</v>
+        <v>13.64182412334521</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253022511198</v>
+        <v>13.25253117759573</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162114749573</v>
+        <v>13.40162211069491</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -812,16 +812,16 @@
         <v>44342</v>
       </c>
       <c r="B20" t="n">
-        <v>13.27737903594971</v>
+        <v>13.27737808227539</v>
       </c>
       <c r="C20" t="n">
-        <v>13.51758188191043</v>
+        <v>13.51758091098307</v>
       </c>
       <c r="D20" t="n">
-        <v>13.26081383895514</v>
+        <v>13.26081288647065</v>
       </c>
       <c r="E20" t="n">
-        <v>13.36849011593299</v>
+        <v>13.36848915571444</v>
       </c>
       <c r="F20" t="n">
         <v>382946</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970157623291</v>
+        <v>13.16970443725586</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131738938882</v>
+        <v>13.45132031159078</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313638072602</v>
+        <v>13.1531392381503</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707509440325</v>
+        <v>13.32707798961446</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889442443848</v>
+        <v>13.02889537811279</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879284288401</v>
+        <v>13.31879381777798</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263114417541</v>
+        <v>12.96263209299946</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111657277715</v>
+        <v>13.21111753978956</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253105163574</v>
+        <v>13.25253009796143</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707610139129</v>
+        <v>13.32707514235259</v>
       </c>
       <c r="D24" t="n">
-        <v>12.84667291282778</v>
+        <v>12.8466719883597</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061163964774</v>
+        <v>13.02061070266274</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -932,16 +932,16 @@
         <v>44351</v>
       </c>
       <c r="B26" t="n">
-        <v>12.97919750213623</v>
+        <v>12.97919654846191</v>
       </c>
       <c r="C26" t="n">
-        <v>13.23596470306119</v>
+        <v>13.23596373052036</v>
       </c>
       <c r="D26" t="n">
-        <v>12.85495520076337</v>
+        <v>12.85495425621803</v>
       </c>
       <c r="E26" t="n">
-        <v>12.98748010031548</v>
+        <v>12.98747914603258</v>
       </c>
       <c r="F26" t="n">
         <v>460799</v>
@@ -952,16 +952,16 @@
         <v>44354</v>
       </c>
       <c r="B27" t="n">
-        <v>12.76384449005127</v>
+        <v>12.76384353637695</v>
       </c>
       <c r="C27" t="n">
-        <v>13.07859155159272</v>
+        <v>13.07859057440149</v>
       </c>
       <c r="D27" t="n">
-        <v>12.69758120620529</v>
+        <v>12.69758025748196</v>
       </c>
       <c r="E27" t="n">
-        <v>12.86323816756367</v>
+        <v>12.86323720646297</v>
       </c>
       <c r="F27" t="n">
         <v>662018</v>
@@ -972,16 +972,16 @@
         <v>44355</v>
       </c>
       <c r="B28" t="n">
-        <v>12.44909763336182</v>
+        <v>12.44909572601318</v>
       </c>
       <c r="C28" t="n">
-        <v>12.73899609163126</v>
+        <v>12.73899413986676</v>
       </c>
       <c r="D28" t="n">
-        <v>12.42424900387104</v>
+        <v>12.42424710032951</v>
       </c>
       <c r="E28" t="n">
-        <v>12.69758226392737</v>
+        <v>12.69758031850796</v>
       </c>
       <c r="F28" t="n">
         <v>727440</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667110443115</v>
+        <v>12.84667205810547</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576214769721</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555837422966</v>
+        <v>12.75555932114021</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576214769721</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1052,16 +1052,16 @@
         <v>44361</v>
       </c>
       <c r="B32" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C32" t="n">
-        <v>13.00404556253863</v>
+        <v>13.00404458393173</v>
       </c>
       <c r="D32" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="E32" t="n">
-        <v>12.9377839435789</v>
+        <v>12.93778296995845</v>
       </c>
       <c r="F32" t="n">
         <v>396641</v>
@@ -1072,16 +1072,16 @@
         <v>44362</v>
       </c>
       <c r="B33" t="n">
-        <v>12.74727725982666</v>
+        <v>12.74727821350098</v>
       </c>
       <c r="C33" t="n">
-        <v>12.93778367526155</v>
+        <v>12.9377846431884</v>
       </c>
       <c r="D33" t="n">
-        <v>12.70586343677157</v>
+        <v>12.70586438734755</v>
       </c>
       <c r="E33" t="n">
-        <v>12.82182313993105</v>
+        <v>12.82182409918244</v>
       </c>
       <c r="F33" t="n">
         <v>320579</v>
@@ -1092,16 +1092,16 @@
         <v>44363</v>
       </c>
       <c r="B34" t="n">
-        <v>12.77212715148926</v>
+        <v>12.77212524414062</v>
       </c>
       <c r="C34" t="n">
-        <v>12.88808602640704</v>
+        <v>12.88808410174148</v>
       </c>
       <c r="D34" t="n">
-        <v>12.67273347348642</v>
+        <v>12.67273158098092</v>
       </c>
       <c r="E34" t="n">
-        <v>12.83010617286263</v>
+        <v>12.83010425685559</v>
       </c>
       <c r="F34" t="n">
         <v>265902</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414756774902</v>
+        <v>12.71414852142334</v>
       </c>
       <c r="C35" t="n">
-        <v>12.86323850400263</v>
+        <v>12.86323946886009</v>
       </c>
       <c r="D35" t="n">
-        <v>12.5899052595662</v>
+        <v>12.58990620392123</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384482389058</v>
+        <v>12.76384578129263</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1132,16 +1132,16 @@
         <v>44365</v>
       </c>
       <c r="B36" t="n">
-        <v>12.65616703033447</v>
+        <v>12.65616607666016</v>
       </c>
       <c r="C36" t="n">
-        <v>12.74727811288975</v>
+        <v>12.74727715234998</v>
       </c>
       <c r="D36" t="n">
-        <v>12.548490750317</v>
+        <v>12.54848980475637</v>
       </c>
       <c r="E36" t="n">
-        <v>12.63960183287228</v>
+        <v>12.6396008804462</v>
       </c>
       <c r="F36" t="n">
         <v>365879</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10949802398682</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C39" t="n">
-        <v>12.49050830483521</v>
+        <v>12.4905092885157</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10949802398682</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424586438442</v>
+        <v>12.42424684284646</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.33313751220703</v>
+        <v>12.3331356048584</v>
       </c>
       <c r="C40" t="n">
-        <v>12.51535967959436</v>
+        <v>12.51535774406464</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717696766745</v>
+        <v>12.21717507825239</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717696766745</v>
+        <v>12.21717507825239</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1252,16 +1252,16 @@
         <v>44375</v>
       </c>
       <c r="B42" t="n">
-        <v>12.17576217651367</v>
+        <v>12.17576122283936</v>
       </c>
       <c r="C42" t="n">
-        <v>12.42424761140088</v>
+        <v>12.42424663826379</v>
       </c>
       <c r="D42" t="n">
-        <v>12.13434835345131</v>
+        <v>12.13434740302076</v>
       </c>
       <c r="E42" t="n">
-        <v>12.34141913310514</v>
+        <v>12.34141816645564</v>
       </c>
       <c r="F42" t="n">
         <v>425086</v>
@@ -1272,16 +1272,16 @@
         <v>44376</v>
       </c>
       <c r="B43" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C43" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="D43" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="E43" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="F43" t="n">
         <v>538653</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525779724121</v>
+        <v>12.80525684356689</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525779724121</v>
+        <v>12.80525684356689</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43253006532078</v>
+        <v>12.43252913940544</v>
       </c>
       <c r="E44" t="n">
-        <v>12.58990442190792</v>
+        <v>12.5899034842721</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1332,16 +1332,16 @@
         <v>44379</v>
       </c>
       <c r="B46" t="n">
-        <v>12.49050903320312</v>
+        <v>12.49050998687744</v>
       </c>
       <c r="C46" t="n">
-        <v>12.7472762129657</v>
+        <v>12.74727718624468</v>
       </c>
       <c r="D46" t="n">
-        <v>12.49050903320312</v>
+        <v>12.49050998687744</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51535765786391</v>
+        <v>12.51535861343547</v>
       </c>
       <c r="F46" t="n">
         <v>443206</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798263549805</v>
       </c>
       <c r="C48" t="n">
-        <v>12.49879274279404</v>
+        <v>12.49879177825338</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25858992047414</v>
+        <v>12.25858897447011</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394328540577</v>
+        <v>12.47394232278276</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34141731262207</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54848806173089</v>
+        <v>12.54849097075757</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34141731262207</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768058478677</v>
+        <v>12.40768346117107</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34141731262207</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C50" t="n">
-        <v>12.65616431867809</v>
+        <v>12.6561672526666</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576038046666</v>
+        <v>12.17576320308654</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25858884654436</v>
+        <v>12.25859168836578</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.21717739105225</v>
+        <v>12.2171745300293</v>
       </c>
       <c r="C51" t="n">
-        <v>12.5402087428486</v>
+        <v>12.54020580617806</v>
       </c>
       <c r="D51" t="n">
-        <v>12.21717739105225</v>
+        <v>12.2171745300293</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424902646154</v>
+        <v>12.42424611694648</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121822357178</v>
+        <v>12.10121631622314</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030916512651</v>
+        <v>12.25030723427872</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293288642992</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293288642992</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495597839355</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172210889838</v>
+        <v>12.29172405694066</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010627604678</v>
+        <v>12.01010817945743</v>
       </c>
       <c r="E54" t="n">
-        <v>12.10121735421974</v>
+        <v>12.10121927207005</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10949802398682</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16747786742398</v>
+        <v>12.16747882566446</v>
       </c>
       <c r="D55" t="n">
-        <v>11.8941446764363</v>
+        <v>11.89414561315063</v>
       </c>
       <c r="E55" t="n">
-        <v>12.0680842067478</v>
+        <v>12.0680851571606</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76768016815186</v>
       </c>
       <c r="C59" t="n">
-        <v>11.34747966894678</v>
+        <v>11.34747866392074</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172224457312</v>
+        <v>10.65172130116907</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414642480609</v>
+        <v>11.07414544398869</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879230499268</v>
+        <v>10.85879039764404</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525761084529</v>
+        <v>11.16525564966597</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798479837585</v>
+        <v>10.71798291576008</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76768122275841</v>
+        <v>10.76767933141345</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697383880615</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697383880615</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707459301606</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707459301606</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1712,16 +1712,16 @@
         <v>44407</v>
       </c>
       <c r="B65" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C65" t="n">
-        <v>11.9272788379407</v>
+        <v>11.92727785279649</v>
       </c>
       <c r="D65" t="n">
-        <v>11.09899563153766</v>
+        <v>11.09899471480624</v>
       </c>
       <c r="E65" t="n">
-        <v>11.20667191578054</v>
+        <v>11.2066709901555</v>
       </c>
       <c r="F65" t="n">
         <v>977013</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071319580078</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727731662251</v>
+        <v>11.92727922662398</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61253027092469</v>
+        <v>11.61253213052343</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61253027092469</v>
+        <v>11.61253213052343</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515537261963</v>
+        <v>11.45515727996826</v>
       </c>
       <c r="C68" t="n">
-        <v>11.85273087597138</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="D68" t="n">
-        <v>11.44687277501277</v>
+        <v>11.4468746809823</v>
       </c>
       <c r="E68" t="n">
-        <v>11.85273087597138</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20667171478271</v>
+        <v>11.2066707611084</v>
       </c>
       <c r="C69" t="n">
-        <v>11.6622279694364</v>
+        <v>11.66222697699479</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20667171478271</v>
+        <v>11.2066707611084</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768208275502</v>
+        <v>11.58768109665717</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283378601074</v>
+        <v>11.56283283233643</v>
       </c>
       <c r="C70" t="n">
-        <v>11.59596584693494</v>
+        <v>11.59596489052797</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495463584676</v>
+        <v>11.21495371086467</v>
       </c>
       <c r="E70" t="n">
-        <v>11.28121792552403</v>
+        <v>11.2812169950767</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1832,16 +1832,16 @@
         <v>44417</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010513305664</v>
       </c>
       <c r="C71" t="n">
-        <v>12.0349548369848</v>
+        <v>12.03495292569004</v>
       </c>
       <c r="D71" t="n">
-        <v>11.59596544701789</v>
+        <v>11.59596360543989</v>
       </c>
       <c r="E71" t="n">
-        <v>11.62909667462835</v>
+        <v>11.62909482778872</v>
       </c>
       <c r="F71" t="n">
         <v>438360</v>
@@ -1852,16 +1852,16 @@
         <v>44418</v>
       </c>
       <c r="B72" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2503080475979</v>
+        <v>12.2503090271009</v>
       </c>
       <c r="D72" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="E72" t="n">
-        <v>12.05151986626892</v>
+        <v>12.05152082987733</v>
       </c>
       <c r="F72" t="n">
         <v>351025</v>
@@ -1892,16 +1892,16 @@
         <v>44420</v>
       </c>
       <c r="B74" t="n">
-        <v>12.07636737823486</v>
+        <v>12.07636833190918</v>
       </c>
       <c r="C74" t="n">
-        <v>12.24202431941305</v>
+        <v>12.24202528616934</v>
       </c>
       <c r="D74" t="n">
-        <v>11.81131677165233</v>
+        <v>11.81131770439553</v>
       </c>
       <c r="E74" t="n">
-        <v>11.95212425626575</v>
+        <v>11.95212520012855</v>
       </c>
       <c r="F74" t="n">
         <v>242515</v>
@@ -1932,16 +1932,16 @@
         <v>44424</v>
       </c>
       <c r="B76" t="n">
-        <v>11.74505615234375</v>
+        <v>11.74505519866943</v>
       </c>
       <c r="C76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="D76" t="n">
-        <v>11.40545961983211</v>
+        <v>11.40545869373233</v>
       </c>
       <c r="E76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="F76" t="n">
         <v>788964</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859100341797</v>
+        <v>11.43859004974365</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727761224746</v>
+        <v>11.92727661782967</v>
       </c>
       <c r="D77" t="n">
-        <v>11.3226304676933</v>
+        <v>11.32262952368701</v>
       </c>
       <c r="E77" t="n">
-        <v>11.84444913368471</v>
+        <v>11.84444814617262</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495597839355</v>
       </c>
       <c r="C78" t="n">
-        <v>12.33313676490402</v>
+        <v>12.33313871950986</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313622917634</v>
+        <v>11.51313805382515</v>
       </c>
       <c r="E78" t="n">
-        <v>11.57939868018012</v>
+        <v>11.57940051533047</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071319580078</v>
       </c>
       <c r="C82" t="n">
-        <v>12.32485367100113</v>
+        <v>12.32485564466939</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990296160259</v>
+        <v>11.76990484640257</v>
       </c>
       <c r="E82" t="n">
-        <v>12.0101057931323</v>
+        <v>12.0101077163977</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C86" t="n">
-        <v>11.9686919095953</v>
+        <v>11.96869289533168</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55454952916977</v>
+        <v>11.55455048079756</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101397529656</v>
+        <v>11.86101495216464</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="D87" t="n">
-        <v>11.388893311891</v>
+        <v>11.38889235890981</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141952514648</v>
+        <v>11.52141761779785</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737923751014</v>
+        <v>11.6373773109646</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576338760633</v>
+        <v>11.35576150768174</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313692631225</v>
+        <v>11.51313502033478</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C89" t="n">
-        <v>11.62909547100532</v>
+        <v>11.6290964280881</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010529430325</v>
+        <v>11.19010621525682</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55454959246905</v>
+        <v>11.55455054341664</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465034484863</v>
+        <v>11.26465129852295</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596339448043</v>
+        <v>11.59596437620398</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838706918552</v>
+        <v>11.19838801724993</v>
       </c>
       <c r="E90" t="n">
-        <v>11.3557614126931</v>
+        <v>11.35576237408096</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444877938214</v>
+        <v>11.84444975488591</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545860508498</v>
+        <v>11.40545954443371</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596418329782</v>
+        <v>11.59596513833651</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364189147949</v>
+        <v>11.70364284515381</v>
       </c>
       <c r="C96" t="n">
-        <v>11.83616679434145</v>
+        <v>11.83616775881459</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172164712899</v>
+        <v>11.47172258190522</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313630340163</v>
+        <v>11.51313724155255</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81959915161133</v>
+        <v>11.81960105895996</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05151853212572</v>
+        <v>12.05152047689957</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58767977109694</v>
+        <v>11.58768164102035</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535686409888</v>
+        <v>11.69535875139833</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34141731262207</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34141731262207</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677025920863</v>
+        <v>11.73677298006055</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76161888224903</v>
+        <v>11.76162160886144</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152130126953</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424908162149</v>
       </c>
       <c r="D104" t="n">
-        <v>11.9935395446462</v>
+        <v>11.99354144281858</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34141864029437</v>
+        <v>12.34142059352426</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2532,16 +2532,16 @@
         <v>44467</v>
       </c>
       <c r="B106" t="n">
-        <v>11.94384288787842</v>
+        <v>11.9438419342041</v>
       </c>
       <c r="C106" t="n">
-        <v>12.09293381741185</v>
+        <v>12.09293285183314</v>
       </c>
       <c r="D106" t="n">
-        <v>11.74505553661453</v>
+        <v>11.74505459881269</v>
       </c>
       <c r="E106" t="n">
-        <v>11.86101440876628</v>
+        <v>11.86101346170553</v>
       </c>
       <c r="F106" t="n">
         <v>282337</v>
@@ -2552,16 +2552,16 @@
         <v>44468</v>
       </c>
       <c r="B107" t="n">
-        <v>11.90242862701416</v>
+        <v>11.90242958068848</v>
       </c>
       <c r="C107" t="n">
-        <v>12.03495352298669</v>
+        <v>12.03495448727948</v>
       </c>
       <c r="D107" t="n">
-        <v>11.6125302090315</v>
+        <v>11.61253113947789</v>
       </c>
       <c r="E107" t="n">
-        <v>12.00182229899356</v>
+        <v>12.00182326063173</v>
       </c>
       <c r="F107" t="n">
         <v>186890</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010650652883</v>
+        <v>12.01010550156678</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444954366927</v>
+        <v>11.84444855256879</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2652,16 +2652,16 @@
         <v>44475</v>
       </c>
       <c r="B112" t="n">
-        <v>11.3806095123291</v>
+        <v>11.38061046600342</v>
       </c>
       <c r="C112" t="n">
-        <v>11.62909493039415</v>
+        <v>11.62909590489109</v>
       </c>
       <c r="D112" t="n">
-        <v>11.18182217648222</v>
+        <v>11.18182311349852</v>
       </c>
       <c r="E112" t="n">
-        <v>11.4054581373527</v>
+        <v>11.40545909310929</v>
       </c>
       <c r="F112" t="n">
         <v>433409</v>
@@ -2672,16 +2672,16 @@
         <v>44476</v>
       </c>
       <c r="B113" t="n">
-        <v>11.33091354370117</v>
+        <v>11.3309154510498</v>
       </c>
       <c r="C113" t="n">
-        <v>11.52970171960058</v>
+        <v>11.5297036604115</v>
       </c>
       <c r="D113" t="n">
-        <v>11.28121629168357</v>
+        <v>11.28121819066659</v>
       </c>
       <c r="E113" t="n">
-        <v>11.45515584157418</v>
+        <v>11.45515776983669</v>
       </c>
       <c r="F113" t="n">
         <v>136744</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.40545845031738</v>
+        <v>11.4054594039917</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939799808451</v>
+        <v>11.57939896630289</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38060982461194</v>
+        <v>11.38061077620852</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43859050603864</v>
+        <v>11.43859146248331</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2812,16 +2812,16 @@
         <v>44488</v>
       </c>
       <c r="B120" t="n">
-        <v>12.07636737823486</v>
+        <v>12.07636833190918</v>
       </c>
       <c r="C120" t="n">
-        <v>12.29172073602975</v>
+        <v>12.29172170671058</v>
       </c>
       <c r="D120" t="n">
-        <v>11.9355590614505</v>
+        <v>11.93556000400514</v>
       </c>
       <c r="E120" t="n">
-        <v>12.10949860003631</v>
+        <v>12.10949955632701</v>
       </c>
       <c r="F120" t="n">
         <v>251785</v>
@@ -2832,16 +2832,16 @@
         <v>44489</v>
       </c>
       <c r="B121" t="n">
-        <v>11.80303478240967</v>
+        <v>11.80303573608398</v>
       </c>
       <c r="C121" t="n">
-        <v>12.20061029668353</v>
+        <v>12.20061128248158</v>
       </c>
       <c r="D121" t="n">
-        <v>11.72848890538714</v>
+        <v>11.72848985303822</v>
       </c>
       <c r="E121" t="n">
-        <v>12.01838815130088</v>
+        <v>12.01838912237555</v>
       </c>
       <c r="F121" t="n">
         <v>129580</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.2585916519165</v>
       </c>
       <c r="C125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.2585916519165</v>
       </c>
       <c r="D125" t="n">
-        <v>11.8444491374672</v>
+        <v>11.84445005892279</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030810003457</v>
+        <v>12.25030905306453</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152130126953</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030756745856</v>
+        <v>12.25030950626865</v>
       </c>
       <c r="D126" t="n">
-        <v>11.8444486225357</v>
+        <v>11.84445049711202</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717551172646</v>
+        <v>12.21717744529286</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -3012,16 +3012,16 @@
         <v>44503</v>
       </c>
       <c r="B130" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010513305664</v>
       </c>
       <c r="C130" t="n">
-        <v>12.01838963926511</v>
+        <v>12.01838773060111</v>
       </c>
       <c r="D130" t="n">
-        <v>11.43859190782543</v>
+        <v>11.43859009124023</v>
       </c>
       <c r="E130" t="n">
-        <v>11.50485436304635</v>
+        <v>11.50485253593789</v>
       </c>
       <c r="F130" t="n">
         <v>128737</v>
@@ -3032,16 +3032,16 @@
         <v>44504</v>
       </c>
       <c r="B131" t="n">
-        <v>11.7781867980957</v>
+        <v>11.77818584442139</v>
       </c>
       <c r="C131" t="n">
-        <v>12.08465125636622</v>
+        <v>12.08465027787762</v>
       </c>
       <c r="D131" t="n">
-        <v>11.73677214232659</v>
+        <v>11.73677119200559</v>
       </c>
       <c r="E131" t="n">
-        <v>12.01010620745546</v>
+        <v>12.01010523500273</v>
       </c>
       <c r="F131" t="n">
         <v>218179</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020683994276</v>
+        <v>11.72020588356491</v>
       </c>
       <c r="D133" t="n">
-        <v>11.3806103272545</v>
+        <v>11.38060939858799</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859101124201</v>
+        <v>11.43859007784422</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152130126953</v>
       </c>
       <c r="C134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152130126953</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283197400976</v>
+        <v>11.56283380401568</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707510257767</v>
+        <v>11.68707695224708</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374080657959</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374080657959</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929758022087</v>
+        <v>11.86929572969245</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05151973098904</v>
+        <v>12.05151785205058</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152130126953</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364078596598</v>
+        <v>12.52364276803549</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131739897459</v>
+        <v>11.81131926830736</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424908162149</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.33313751220703</v>
+        <v>12.3331356048584</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566242224469</v>
+        <v>12.46566049440077</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010700377637</v>
+        <v>12.01010514638517</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05152083012037</v>
+        <v>12.05151896632442</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798263549805</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49050931294096</v>
+        <v>12.49050834903954</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293297380614</v>
+        <v>12.09293204058597</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485319844393</v>
+        <v>12.32485224732631</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.98748016357422</v>
+        <v>12.98748111724854</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374261367302</v>
+        <v>13.05374357221301</v>
       </c>
       <c r="D142" t="n">
-        <v>12.35798439112253</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="E142" t="n">
-        <v>12.35798439112253</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.4408130645752</v>
+        <v>12.44081211090088</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89636928852036</v>
+        <v>12.89636829992451</v>
       </c>
       <c r="D144" t="n">
-        <v>12.4408130645752</v>
+        <v>12.44081211090088</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010600521327</v>
+        <v>12.83010502169696</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010482788086</v>
+        <v>12.83010673522949</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010482788086</v>
+        <v>12.83010673522949</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283207549919</v>
+        <v>12.38283391635538</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131749271409</v>
+        <v>12.63131937051061</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3332,16 +3332,16 @@
         <v>44526</v>
       </c>
       <c r="B146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="D146" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="E146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="F146" t="n">
         <v>386739</v>
@@ -3352,16 +3352,16 @@
         <v>44529</v>
       </c>
       <c r="B147" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C147" t="n">
-        <v>12.98748036584146</v>
+        <v>12.98747938848116</v>
       </c>
       <c r="D147" t="n">
-        <v>12.357984583586</v>
+        <v>12.35798365359779</v>
       </c>
       <c r="E147" t="n">
-        <v>12.75556012254167</v>
+        <v>12.75555916263431</v>
       </c>
       <c r="F147" t="n">
         <v>340279</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455081939697</v>
+        <v>12.37454986572266</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90242939089549</v>
+        <v>11.90242847360634</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808406829834</v>
+        <v>11.24808597564697</v>
       </c>
       <c r="C150" t="n">
-        <v>11.81959908703571</v>
+        <v>11.8196010912967</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182162627651</v>
+        <v>11.18182352238896</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333664501388</v>
+        <v>11.75333863803869</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67050929318926</v>
+        <v>11.67051025368041</v>
       </c>
       <c r="D151" t="n">
-        <v>11.24808514466335</v>
+        <v>11.2480860703887</v>
       </c>
       <c r="E151" t="n">
-        <v>11.3391962192048</v>
+        <v>11.33919715242866</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.76990222930908</v>
+        <v>11.7699031829834</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212436699063</v>
+        <v>11.95212533542978</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485245244207</v>
+        <v>11.50485338464032</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970107706609</v>
+        <v>11.52970201127774</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3472,16 +3472,16 @@
         <v>44537</v>
       </c>
       <c r="B153" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010513305664</v>
       </c>
       <c r="C153" t="n">
-        <v>12.09293469334588</v>
+        <v>12.09293277284322</v>
       </c>
       <c r="D153" t="n">
-        <v>11.78647021382081</v>
+        <v>11.78646834198837</v>
       </c>
       <c r="E153" t="n">
-        <v>11.89414732768312</v>
+        <v>11.89414543875028</v>
       </c>
       <c r="F153" t="n">
         <v>308042</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374080657959</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626761187925</v>
+        <v>12.36626568386882</v>
       </c>
       <c r="D154" t="n">
-        <v>11.89414620662944</v>
+        <v>11.8941443522269</v>
       </c>
       <c r="E154" t="n">
-        <v>12.0101059084221</v>
+        <v>12.01010403594042</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.2585916519165</v>
       </c>
       <c r="C155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.2585916519165</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99354006605936</v>
+        <v>11.99354099911369</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22545947324071</v>
+        <v>12.22546042433754</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000591278076</v>
+        <v>12.30000495910645</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626920245019</v>
+        <v>12.36626824363818</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778373857486</v>
+        <v>12.11778279902904</v>
       </c>
       <c r="E156" t="n">
-        <v>12.26687468403161</v>
+        <v>12.2668737329261</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485389709473</v>
+        <v>12.32485485076904</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303492009218</v>
+        <v>12.62303589683919</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374282091386</v>
+        <v>12.23374376753817</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000443829783</v>
+        <v>12.30000539004934</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.25859069824219</v>
+        <v>12.2585916519165</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192392863263</v>
+        <v>12.53192490357129</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606496606526</v>
+        <v>12.12606590942955</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909628221446</v>
+        <v>12.44909725070942</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202411651611</v>
+        <v>13.06202507019043</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16141861550016</v>
+        <v>13.16141957643138</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273204678879</v>
+        <v>12.67273297204042</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273204678879</v>
+        <v>12.67273297204042</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.72243022918701</v>
+        <v>12.7224292755127</v>
       </c>
       <c r="C163" t="n">
-        <v>13.0620259287079</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737958207539</v>
+        <v>12.45737864826929</v>
       </c>
       <c r="E163" t="n">
-        <v>13.0620259287079</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182312011719</v>
       </c>
       <c r="C164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182312011719</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43253111290434</v>
+        <v>12.43253018818525</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72243039191747</v>
+        <v>12.72242944563595</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.8383903503418</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495721363644</v>
+        <v>12.85495625873149</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020927965935</v>
+        <v>12.54020834813482</v>
       </c>
       <c r="E165" t="n">
-        <v>12.81354255191329</v>
+        <v>12.81354160008474</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828770746268</v>
+        <v>13.12828866415499</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384342158722</v>
+        <v>12.76384435172153</v>
       </c>
       <c r="E166" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838856883414</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970248796023</v>
       </c>
       <c r="D167" t="n">
-        <v>12.9212161070132</v>
+        <v>12.92121704861566</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C168" t="n">
-        <v>13.3767722965285</v>
+        <v>13.37677327132853</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04545923371708</v>
+        <v>13.04546018437347</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970248796023</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3812,16 +3812,16 @@
         <v>44564</v>
       </c>
       <c r="B170" t="n">
-        <v>12.92949962615967</v>
+        <v>12.92949867248535</v>
       </c>
       <c r="C170" t="n">
-        <v>13.60041006166028</v>
+        <v>13.6004090584999</v>
       </c>
       <c r="D170" t="n">
-        <v>12.78869212614555</v>
+        <v>12.78869118285713</v>
       </c>
       <c r="E170" t="n">
-        <v>13.1697024667913</v>
+        <v>13.16970149539972</v>
       </c>
       <c r="F170" t="n">
         <v>289922</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970092773438</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98748125957582</v>
+        <v>12.98747925372556</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970092773438</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92950057063265</v>
+        <v>12.92949857373721</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616537688813</v>
+        <v>11.83616633728321</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47172027332021</v>
+        <v>11.47172120414394</v>
       </c>
       <c r="E173" t="n">
-        <v>11.63737721423026</v>
+        <v>11.63737815849552</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.69535732269287</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78646839258601</v>
+        <v>11.78646935368979</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49656915557559</v>
+        <v>11.49657009304013</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333717009495</v>
+        <v>11.75333812849712</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727644473738</v>
+        <v>11.92727741252527</v>
       </c>
       <c r="D176" t="n">
-        <v>11.6125294220476</v>
+        <v>11.61253036429669</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444797428235</v>
+        <v>11.84444893534948</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838751258662</v>
+        <v>12.01838848776734</v>
       </c>
       <c r="D177" t="n">
-        <v>11.64565981162448</v>
+        <v>11.6456607565618</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818553078671</v>
+        <v>11.77818648647726</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071205965744</v>
+        <v>11.91071108497109</v>
       </c>
       <c r="D178" t="n">
-        <v>11.5959649935801</v>
+        <v>11.59596404465037</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273220556355</v>
+        <v>11.85273123562185</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131675253453</v>
+        <v>11.81131771091337</v>
       </c>
       <c r="D179" t="n">
-        <v>11.52970095159257</v>
+        <v>11.5297018871209</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67050843597808</v>
+        <v>11.67050938293163</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818633138246</v>
+        <v>11.77818730142888</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798433325535</v>
+        <v>11.53798528351884</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333770533982</v>
+        <v>11.75333867333973</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010609902517</v>
+        <v>12.01010511899131</v>
       </c>
       <c r="D182" t="n">
-        <v>11.56283248091458</v>
+        <v>11.5628315373786</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596453809916</v>
+        <v>11.59596359185958</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434840086876</v>
+        <v>12.13434741069664</v>
       </c>
       <c r="D184" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84444914178635</v>
+        <v>11.84444817527024</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616638183594</v>
+        <v>11.83616733551025</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444897993339</v>
+        <v>11.84444993427506</v>
       </c>
       <c r="D186" t="n">
-        <v>11.4634386492274</v>
+        <v>11.46343957286996</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172124732486</v>
+        <v>11.47172217163477</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4152,16 +4152,16 @@
         <v>44587</v>
       </c>
       <c r="B187" t="n">
-        <v>11.0161657333374</v>
+        <v>11.01616668701172</v>
       </c>
       <c r="C187" t="n">
-        <v>12.08465083286823</v>
+        <v>12.08465187904177</v>
       </c>
       <c r="D187" t="n">
-        <v>10.90020603272125</v>
+        <v>10.90020697635688</v>
       </c>
       <c r="E187" t="n">
-        <v>11.88586348795854</v>
+        <v>11.88586451692297</v>
       </c>
       <c r="F187" t="n">
         <v>1763028</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586379718157</v>
+        <v>11.88586282728598</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626728449331</v>
+        <v>11.54626634230906</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788311319406</v>
+        <v>11.82788214802975</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.4882869720459</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84444866687487</v>
+        <v>11.84444965011515</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4882869720459</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67050911839965</v>
+        <v>11.67051008720073</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788467407227</v>
+        <v>11.82788276672363</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84445070485071</v>
+        <v>11.84444879483066</v>
       </c>
       <c r="D198" t="n">
-        <v>11.62909729775775</v>
+        <v>11.6290954224653</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84445070485071</v>
+        <v>11.84444879483066</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4392,16 +4392,16 @@
         <v>44603</v>
       </c>
       <c r="B199" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C199" t="n">
-        <v>11.8196017215267</v>
+        <v>11.81960074527618</v>
       </c>
       <c r="D199" t="n">
-        <v>11.5214198337953</v>
+        <v>11.52141888217337</v>
       </c>
       <c r="E199" t="n">
-        <v>11.71192543728382</v>
+        <v>11.71192446992692</v>
       </c>
       <c r="F199" t="n">
         <v>419186</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444909778491</v>
+        <v>11.8444500711998</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313601670912</v>
+        <v>11.51313696289563</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253052355157</v>
+        <v>11.61253147790664</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84444914178635</v>
+        <v>11.84444817527024</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081316490208</v>
+        <v>11.62081221663484</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081316490208</v>
+        <v>11.62081221663484</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.69535732269287</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81959961507706</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394267045083</v>
+        <v>11.65394362074808</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81959961507706</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4492,16 +4492,16 @@
         <v>44610</v>
       </c>
       <c r="B204" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="C204" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="D204" t="n">
-        <v>11.48000394896948</v>
+        <v>11.48000486688096</v>
       </c>
       <c r="E204" t="n">
-        <v>11.76162060853312</v>
+        <v>11.76162154896194</v>
       </c>
       <c r="F204" t="n">
         <v>336065</v>
@@ -4532,16 +4532,16 @@
         <v>44614</v>
       </c>
       <c r="B206" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C206" t="n">
-        <v>11.72849063539606</v>
+        <v>11.72848966667094</v>
       </c>
       <c r="D206" t="n">
-        <v>11.51313723473918</v>
+        <v>11.51313628380136</v>
       </c>
       <c r="E206" t="n">
-        <v>11.51313723473918</v>
+        <v>11.51313628380136</v>
       </c>
       <c r="F206" t="n">
         <v>213649</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899301517222</v>
+        <v>11.91899398228799</v>
       </c>
       <c r="D207" t="n">
-        <v>11.54626614638101</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="E207" t="n">
-        <v>11.54626614638101</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.14263248443604</v>
+        <v>12.14263153076172</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576287906074</v>
+        <v>12.17576192278439</v>
       </c>
       <c r="D208" t="n">
-        <v>11.4220255970719</v>
+        <v>11.42202469999357</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596516187804</v>
+        <v>11.59596425113861</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="D210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.010106267532</v>
       </c>
       <c r="E210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.010106267532</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.8383903503418</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="C212" t="n">
-        <v>12.8383903503418</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000640531008</v>
+        <v>12.30000549162855</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586543003849</v>
+        <v>12.70586448620852</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.73899459838867</v>
+        <v>12.7389965057373</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202507956149</v>
+        <v>13.06202703527593</v>
       </c>
       <c r="D213" t="n">
-        <v>12.10949966448541</v>
+        <v>12.10950147758278</v>
       </c>
       <c r="E213" t="n">
-        <v>12.84667253500764</v>
+        <v>12.84667445847837</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.1591968536377</v>
+        <v>12.15919780731201</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="D214" t="n">
-        <v>12.14263165745353</v>
+        <v>12.1426326098286</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071319580078</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45737856768</v>
+        <v>12.45738056257043</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990296160259</v>
+        <v>11.76990484640257</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081253950964</v>
+        <v>12.44081453174723</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141952514648</v>
+        <v>11.52141761779785</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303620722139</v>
+        <v>11.80303425325166</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515707013042</v>
+        <v>11.45515517375141</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626815382028</v>
+        <v>11.546266242358</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.794753074646</v>
+        <v>11.79475212097168</v>
       </c>
       <c r="C220" t="n">
-        <v>11.80303567310543</v>
+        <v>11.80303471876141</v>
       </c>
       <c r="D220" t="n">
-        <v>11.46343915021626</v>
+        <v>11.4634382233306</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596488642237</v>
+        <v>11.59596394882123</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.6622257232666</v>
+        <v>11.66222667694092</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444785716326</v>
+        <v>11.84444882573873</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404389831371</v>
+        <v>11.36404482760432</v>
       </c>
       <c r="E222" t="n">
-        <v>11.53798343489805</v>
+        <v>11.5379843784125</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333690643311</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475155774609</v>
+        <v>11.79475251478082</v>
       </c>
       <c r="D224" t="n">
-        <v>11.57939736812883</v>
+        <v>11.57939830768957</v>
       </c>
       <c r="E224" t="n">
-        <v>11.6787910333723</v>
+        <v>11.67879198099791</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.9686918258667</v>
+        <v>11.96869087219238</v>
       </c>
       <c r="C225" t="n">
-        <v>12.20889299014245</v>
+        <v>12.20889201732872</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798425253982</v>
+        <v>11.53798333318461</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677159514823</v>
+        <v>11.73677065995349</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10950024971806</v>
+        <v>12.10949925876433</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495436638118</v>
+        <v>12.03495338152774</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78646924618382</v>
+        <v>11.78647021483374</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030753839741</v>
+        <v>11.43030847777682</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535816969225</v>
+        <v>11.69535913085437</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.413743019104</v>
+        <v>11.41374111175537</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283396691093</v>
+        <v>11.56283203464774</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23152084202566</v>
+        <v>11.23151896512815</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283396691093</v>
+        <v>11.56283203464774</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.413743019104</v>
+        <v>11.41374111175537</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909725762489</v>
+        <v>11.62909531428845</v>
       </c>
       <c r="D232" t="n">
-        <v>11.256369472022</v>
+        <v>11.25636759097204</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313753908938</v>
+        <v>11.51313561513094</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5092,16 +5092,16 @@
         <v>44656</v>
       </c>
       <c r="B234" t="n">
-        <v>11.19010448455811</v>
+        <v>11.19010639190674</v>
       </c>
       <c r="C234" t="n">
-        <v>11.57939738073242</v>
+        <v>11.57939935443586</v>
       </c>
       <c r="D234" t="n">
-        <v>11.19010448455811</v>
+        <v>11.19010639190674</v>
       </c>
       <c r="E234" t="n">
-        <v>11.52141753456788</v>
+        <v>11.52141949838869</v>
       </c>
       <c r="F234" t="n">
         <v>602179</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444934844971</v>
+        <v>11.02444744110107</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495411294023</v>
+        <v>11.21495217263222</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192443961648</v>
+        <v>10.89192255519609</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495411294023</v>
+        <v>11.21495217263222</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000366210938</v>
+        <v>10.66000461578369</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566060926712</v>
+        <v>10.82566157776158</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000366210938</v>
+        <v>10.66000461578369</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566060926712</v>
+        <v>10.82566157776158</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76768016815186</v>
       </c>
       <c r="C242" t="n">
-        <v>11.03273176734258</v>
+        <v>11.0327307901932</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172224457312</v>
+        <v>10.65172130116907</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000484319739</v>
+        <v>10.66000389905977</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76768016815186</v>
       </c>
       <c r="C243" t="n">
-        <v>10.9250554887138</v>
+        <v>10.92505452110112</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000484319739</v>
+        <v>10.66000389905977</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081318066541</v>
+        <v>10.80081222405664</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525680541992</v>
+        <v>10.34525775909424</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061017469088</v>
+        <v>10.56061114821748</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32868994537994</v>
+        <v>10.32869089752705</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151842038292</v>
+        <v>10.41151938016555</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838745117188</v>
+        <v>10.37838649749756</v>
       </c>
       <c r="C249" t="n">
-        <v>10.55232700328979</v>
+        <v>10.5523260336321</v>
       </c>
       <c r="D249" t="n">
-        <v>10.23757912343294</v>
+        <v>10.23757818269756</v>
       </c>
       <c r="E249" t="n">
-        <v>10.3452570589639</v>
+        <v>10.34525610833395</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434448242188</v>
+        <v>10.73434543609619</v>
       </c>
       <c r="C251" t="n">
-        <v>10.92543536845984</v>
+        <v>10.9254363391113</v>
       </c>
       <c r="D251" t="n">
-        <v>10.4103192818045</v>
+        <v>10.41032020669135</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389329081236</v>
+        <v>10.88389425777308</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5452,16 +5452,16 @@
         <v>44684</v>
       </c>
       <c r="B252" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C252" t="n">
-        <v>10.72603559055428</v>
+        <v>10.72603654719261</v>
       </c>
       <c r="D252" t="n">
-        <v>10.51001962438067</v>
+        <v>10.51002056175287</v>
       </c>
       <c r="E252" t="n">
-        <v>10.71772667416696</v>
+        <v>10.71772763006424</v>
       </c>
       <c r="F252" t="n">
         <v>311097</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.85066032409668</v>
+        <v>10.85065937042236</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344396650661</v>
+        <v>11.03344299676728</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633543802578</v>
+        <v>10.62633450406758</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772684186504</v>
+        <v>10.71772589987437</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5532,16 +5532,16 @@
         <v>44690</v>
       </c>
       <c r="B256" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C256" t="n">
-        <v>10.95036047311521</v>
+        <v>10.95036144976073</v>
       </c>
       <c r="D256" t="n">
-        <v>10.61802719010177</v>
+        <v>10.618028137107</v>
       </c>
       <c r="E256" t="n">
-        <v>10.95036047311521</v>
+        <v>10.95036144976073</v>
       </c>
       <c r="F256" t="n">
         <v>340595</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389316500986</v>
+        <v>10.88389415417323</v>
       </c>
       <c r="D257" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727700192804</v>
+        <v>10.86727798958128</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5572,16 +5572,16 @@
         <v>44692</v>
       </c>
       <c r="B258" t="n">
-        <v>10.62633514404297</v>
+        <v>10.62633609771729</v>
       </c>
       <c r="C258" t="n">
-        <v>10.80080986510865</v>
+        <v>10.80081083444142</v>
       </c>
       <c r="D258" t="n">
-        <v>10.4684782555522</v>
+        <v>10.46847919505945</v>
       </c>
       <c r="E258" t="n">
-        <v>10.51001949806391</v>
+        <v>10.51002044129933</v>
       </c>
       <c r="F258" t="n">
         <v>211647</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75927027618541</v>
+        <v>10.75926935728049</v>
       </c>
       <c r="E261" t="n">
-        <v>10.8755867747725</v>
+        <v>10.87558584593347</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.10821914672852</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085213080912</v>
+        <v>11.34085115716256</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95866949049548</v>
+        <v>10.95866854966046</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806847565188</v>
+        <v>11.15806751769784</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5672,16 +5672,16 @@
         <v>44699</v>
       </c>
       <c r="B263" t="n">
-        <v>11.11652660369873</v>
+        <v>11.11652755737305</v>
       </c>
       <c r="C263" t="n">
-        <v>11.24945925299112</v>
+        <v>11.24946021806958</v>
       </c>
       <c r="D263" t="n">
-        <v>10.80911839143009</v>
+        <v>10.8091193187322</v>
       </c>
       <c r="E263" t="n">
-        <v>11.01682711672944</v>
+        <v>11.01682806185065</v>
       </c>
       <c r="F263" t="n">
         <v>416658</v>
@@ -5692,16 +5692,16 @@
         <v>44700</v>
       </c>
       <c r="B264" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269481658936</v>
       </c>
       <c r="C264" t="n">
-        <v>11.40731747287078</v>
+        <v>11.4073194012873</v>
       </c>
       <c r="D264" t="n">
-        <v>11.05005994527452</v>
+        <v>11.05006181329636</v>
       </c>
       <c r="E264" t="n">
-        <v>11.1248351842914</v>
+        <v>11.12483706495406</v>
       </c>
       <c r="F264" t="n">
         <v>530225</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423513134702</v>
+        <v>11.32423415912707</v>
       </c>
       <c r="D265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100196715428</v>
+        <v>11.29100099778751</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772819255772</v>
+        <v>10.71772727720074</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05006152265314</v>
+        <v>11.05006057891294</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190235137939</v>
+        <v>10.99190330505371</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="D268" t="n">
-        <v>10.89220202682084</v>
+        <v>10.892202971845</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="C269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="D269" t="n">
-        <v>10.8672769842127</v>
+        <v>10.86727791027506</v>
       </c>
       <c r="E269" t="n">
-        <v>11.0168266253622</v>
+        <v>11.01682756416854</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329296112061</v>
+        <v>11.08329391479492</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776768180519</v>
+        <v>11.25776865049238</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667596331338</v>
+        <v>11.06667691555787</v>
       </c>
       <c r="E270" t="n">
-        <v>11.199609441577</v>
+        <v>11.1996104052599</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776958465576</v>
+        <v>11.25776863098145</v>
       </c>
       <c r="C271" t="n">
-        <v>11.27438658527168</v>
+        <v>11.2743856301897</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160375215421</v>
+        <v>11.09160281255622</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160375215421</v>
+        <v>11.09160281255622</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085178375244</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085178375244</v>
       </c>
       <c r="D272" t="n">
-        <v>11.13314295164785</v>
+        <v>11.1331438878556</v>
       </c>
       <c r="E272" t="n">
-        <v>11.24945859561594</v>
+        <v>11.2494595416049</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34916019439697</v>
+        <v>11.34915924072266</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39900940010609</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19961053841137</v>
+        <v>11.19960959730377</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39900940010609</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622848510742</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="C274" t="n">
-        <v>11.34916115288518</v>
+        <v>11.349159222931</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622848510742</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="E274" t="n">
-        <v>11.34916115288518</v>
+        <v>11.349159222931</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D277" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250303440952</v>
+        <v>10.79250209732709</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5992,16 +5992,16 @@
         <v>44721</v>
       </c>
       <c r="B279" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C279" t="n">
-        <v>10.82573590935088</v>
+        <v>10.82573687488132</v>
       </c>
       <c r="D279" t="n">
-        <v>10.62633527175769</v>
+        <v>10.6263362195039</v>
       </c>
       <c r="E279" t="n">
-        <v>10.79250191326441</v>
+        <v>10.79250287583077</v>
       </c>
       <c r="F279" t="n">
         <v>205537</v>
@@ -6012,16 +6012,16 @@
         <v>44722</v>
       </c>
       <c r="B280" t="n">
-        <v>10.39370536804199</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C280" t="n">
-        <v>10.65126346711301</v>
+        <v>10.65126151249989</v>
       </c>
       <c r="D280" t="n">
-        <v>10.39370536804199</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="E280" t="n">
-        <v>10.63464646551131</v>
+        <v>10.63464451394758</v>
       </c>
       <c r="F280" t="n">
         <v>218179</v>
@@ -6032,16 +6032,16 @@
         <v>44725</v>
       </c>
       <c r="B281" t="n">
-        <v>10.25246143341064</v>
+        <v>10.25246238708496</v>
       </c>
       <c r="C281" t="n">
-        <v>10.47678631275402</v>
+        <v>10.47678728729483</v>
       </c>
       <c r="D281" t="n">
-        <v>10.18599427692247</v>
+        <v>10.18599522441408</v>
       </c>
       <c r="E281" t="n">
-        <v>10.3853949116556</v>
+        <v>10.38539587769526</v>
       </c>
       <c r="F281" t="n">
         <v>299930</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.1776876449585</v>
+        <v>10.17768669128418</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216239046842</v>
+        <v>10.35216142044539</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798814812347</v>
+        <v>10.07798720379124</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599572767854</v>
+        <v>10.18599477322573</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6112,16 +6112,16 @@
         <v>44732</v>
       </c>
       <c r="B285" t="n">
-        <v>10.07798671722412</v>
+        <v>10.07798767089844</v>
       </c>
       <c r="C285" t="n">
-        <v>10.2607695195021</v>
+        <v>10.26077049047305</v>
       </c>
       <c r="D285" t="n">
-        <v>9.945054073651551</v>
+        <v>9.945055014746524</v>
       </c>
       <c r="E285" t="n">
-        <v>10.17768619990355</v>
+        <v>10.17768716301237</v>
       </c>
       <c r="F285" t="n">
         <v>293715</v>
@@ -6172,16 +6172,16 @@
         <v>44735</v>
       </c>
       <c r="B288" t="n">
-        <v>9.637645721435547</v>
+        <v>9.63764762878418</v>
       </c>
       <c r="C288" t="n">
-        <v>9.945053915591304</v>
+        <v>9.945055883777885</v>
       </c>
       <c r="D288" t="n">
-        <v>9.629337640027153</v>
+        <v>9.629339545731565</v>
       </c>
       <c r="E288" t="n">
-        <v>9.93674583418291</v>
+        <v>9.936747800725271</v>
       </c>
       <c r="F288" t="n">
         <v>565728</v>
@@ -6192,16 +6192,16 @@
         <v>44736</v>
       </c>
       <c r="B289" t="n">
-        <v>9.388399124145508</v>
+        <v>9.388396263122559</v>
       </c>
       <c r="C289" t="n">
-        <v>9.795506908792499</v>
+        <v>9.795503923707427</v>
       </c>
       <c r="D289" t="n">
-        <v>9.388399124145508</v>
+        <v>9.388396263122559</v>
       </c>
       <c r="E289" t="n">
-        <v>9.695806566175177</v>
+        <v>9.695803611472812</v>
       </c>
       <c r="F289" t="n">
         <v>325741</v>
@@ -6212,16 +6212,16 @@
         <v>44739</v>
       </c>
       <c r="B290" t="n">
-        <v>9.35516357421875</v>
+        <v>9.355164527893066</v>
       </c>
       <c r="C290" t="n">
-        <v>9.554562539248643</v>
+        <v>9.55456351324988</v>
       </c>
       <c r="D290" t="n">
-        <v>9.263771338499145</v>
+        <v>9.26377228285685</v>
       </c>
       <c r="E290" t="n">
-        <v>9.496405133830134</v>
+        <v>9.49640610190275</v>
       </c>
       <c r="F290" t="n">
         <v>312467</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496406309403417</v>
+        <v>9.496405321144287</v>
       </c>
       <c r="D291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488098226848217</v>
+        <v>9.488097239453682</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072680473327637</v>
+        <v>9.072681427001953</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255463275673385</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974782970578</v>
+        <v>8.93974876940689</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255463275673385</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6432,16 +6432,16 @@
         <v>44754</v>
       </c>
       <c r="B301" t="n">
-        <v>8.690499305725098</v>
+        <v>8.690498352050781</v>
       </c>
       <c r="C301" t="n">
-        <v>8.864974055335237</v>
+        <v>8.864973082514485</v>
       </c>
       <c r="D301" t="n">
-        <v>8.574182805985005</v>
+        <v>8.57418186507498</v>
       </c>
       <c r="E301" t="n">
-        <v>8.864974055335237</v>
+        <v>8.864973082514485</v>
       </c>
       <c r="F301" t="n">
         <v>237774</v>
@@ -6452,16 +6452,16 @@
         <v>44755</v>
       </c>
       <c r="B302" t="n">
-        <v>8.599106788635254</v>
+        <v>8.59910774230957</v>
       </c>
       <c r="C302" t="n">
-        <v>8.823430841751456</v>
+        <v>8.823431820304181</v>
       </c>
       <c r="D302" t="n">
-        <v>8.549256628062132</v>
+        <v>8.549257576207872</v>
       </c>
       <c r="E302" t="n">
-        <v>8.56587362649698</v>
+        <v>8.56587457648561</v>
       </c>
       <c r="F302" t="n">
         <v>184467</v>
@@ -6512,16 +6512,16 @@
         <v>44760</v>
       </c>
       <c r="B305" t="n">
-        <v>8.57418155670166</v>
+        <v>8.574182510375977</v>
       </c>
       <c r="C305" t="n">
-        <v>8.723731201044597</v>
+        <v>8.723732171352765</v>
       </c>
       <c r="D305" t="n">
-        <v>8.482790153754944</v>
+        <v>8.482791097264135</v>
       </c>
       <c r="E305" t="n">
-        <v>8.58249047313784</v>
+        <v>8.582491427736327</v>
       </c>
       <c r="F305" t="n">
         <v>154548</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864973068237305</v>
+        <v>8.864974975585938</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873281984958936</v>
+        <v>8.873283894095279</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615723930679971</v>
+        <v>8.615725784401254</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632340094660361</v>
+        <v>8.632341951956706</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039448738098145</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039448738098145</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815123823192138</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815123823192138</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="C311" t="n">
-        <v>9.122532260843132</v>
+        <v>9.122531267357015</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039448926379578</v>
+        <v>9.039447941941624</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6712,16 +6712,16 @@
         <v>44774</v>
       </c>
       <c r="B315" t="n">
-        <v>8.923130989074707</v>
+        <v>8.923131942749023</v>
       </c>
       <c r="C315" t="n">
-        <v>9.122530792751455</v>
+        <v>9.122531767736954</v>
       </c>
       <c r="D315" t="n">
-        <v>8.864972747782797</v>
+        <v>8.864973695241357</v>
       </c>
       <c r="E315" t="n">
-        <v>9.122530792751455</v>
+        <v>9.122531767736954</v>
       </c>
       <c r="F315" t="n">
         <v>159078</v>
@@ -6732,16 +6732,16 @@
         <v>44775</v>
       </c>
       <c r="B316" t="n">
-        <v>9.114224433898926</v>
+        <v>9.114221572875977</v>
       </c>
       <c r="C316" t="n">
-        <v>9.205616697058979</v>
+        <v>9.205613807347317</v>
       </c>
       <c r="D316" t="n">
-        <v>8.906516490246783</v>
+        <v>8.906513694424905</v>
       </c>
       <c r="E316" t="n">
-        <v>9.006216837428061</v>
+        <v>9.006214010309503</v>
       </c>
       <c r="F316" t="n">
         <v>198584</v>
@@ -6772,16 +6772,16 @@
         <v>44777</v>
       </c>
       <c r="B318" t="n">
-        <v>9.26377010345459</v>
+        <v>9.263772964477539</v>
       </c>
       <c r="C318" t="n">
-        <v>9.297004094593545</v>
+        <v>9.297006965880481</v>
       </c>
       <c r="D318" t="n">
-        <v>8.948054700216032</v>
+        <v>8.948057463733431</v>
       </c>
       <c r="E318" t="n">
-        <v>8.972979776204609</v>
+        <v>8.972982547419868</v>
       </c>
       <c r="F318" t="n">
         <v>175407</v>
@@ -6812,16 +6812,16 @@
         <v>44781</v>
       </c>
       <c r="B320" t="n">
-        <v>9.637645721435547</v>
+        <v>9.63764762878418</v>
       </c>
       <c r="C320" t="n">
-        <v>9.670879716531882</v>
+        <v>9.670881630457723</v>
       </c>
       <c r="D320" t="n">
-        <v>9.371779603784519</v>
+        <v>9.371781458516631</v>
       </c>
       <c r="E320" t="n">
-        <v>9.371779603784519</v>
+        <v>9.371781458516631</v>
       </c>
       <c r="F320" t="n">
         <v>274752</v>
@@ -6832,16 +6832,16 @@
         <v>44782</v>
       </c>
       <c r="B321" t="n">
-        <v>9.26377010345459</v>
+        <v>9.263772964477539</v>
       </c>
       <c r="C321" t="n">
-        <v>9.920126820651559</v>
+        <v>9.920129884383732</v>
       </c>
       <c r="D321" t="n">
-        <v>9.105912401835312</v>
+        <v>9.105915214105485</v>
       </c>
       <c r="E321" t="n">
-        <v>9.68749472579783</v>
+        <v>9.687497717683902</v>
       </c>
       <c r="F321" t="n">
         <v>480605</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.770580291748047</v>
+        <v>9.77057933807373</v>
       </c>
       <c r="C324" t="n">
-        <v>9.86197170166864</v>
+        <v>9.861970739073907</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262965348279</v>
+        <v>9.654262023027314</v>
       </c>
       <c r="E324" t="n">
-        <v>9.82042962051198</v>
+        <v>9.820428661972032</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953364372253418</v>
+        <v>9.953363418579102</v>
       </c>
       <c r="C325" t="n">
-        <v>10.11953104846331</v>
+        <v>10.11953007886785</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704114357938586</v>
+        <v>9.704113428145977</v>
       </c>
       <c r="E325" t="n">
-        <v>9.729039442843225</v>
+        <v>9.72903851066244</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="D327" t="n">
-        <v>10.30231297394502</v>
+        <v>10.30231205007301</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847963535633</v>
+        <v>10.46847869658313</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494372351503</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092019610571</v>
+        <v>10.21092112410713</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494372351503</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7012,16 +7012,16 @@
         <v>44795</v>
       </c>
       <c r="B330" t="n">
-        <v>10.39370536804199</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C330" t="n">
-        <v>10.54325420879935</v>
+        <v>10.54325227400702</v>
       </c>
       <c r="D330" t="n">
-        <v>10.2192306075163</v>
+        <v>10.21922873218552</v>
       </c>
       <c r="E330" t="n">
-        <v>10.47678870658731</v>
+        <v>10.47678678399206</v>
       </c>
       <c r="F330" t="n">
         <v>111565</v>
@@ -7112,16 +7112,16 @@
         <v>44802</v>
       </c>
       <c r="B335" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C335" t="n">
-        <v>10.75927052205955</v>
+        <v>10.75926956021513</v>
       </c>
       <c r="D335" t="n">
-        <v>10.56817960414618</v>
+        <v>10.56817865938468</v>
       </c>
       <c r="E335" t="n">
-        <v>10.75927052205955</v>
+        <v>10.75926956021513</v>
       </c>
       <c r="F335" t="n">
         <v>128948</v>
@@ -7132,16 +7132,16 @@
         <v>44803</v>
       </c>
       <c r="B336" t="n">
-        <v>10.39370536804199</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C336" t="n">
-        <v>10.79250422443531</v>
+        <v>10.79250224390311</v>
       </c>
       <c r="D336" t="n">
-        <v>10.31893011293173</v>
+        <v>10.3189282193051</v>
       </c>
       <c r="E336" t="n">
-        <v>10.70111280245493</v>
+        <v>10.70111083869397</v>
       </c>
       <c r="F336" t="n">
         <v>123575</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539505004883</v>
+        <v>10.38539600372314</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648593632885</v>
+        <v>10.57648690755074</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907773332736</v>
+        <v>10.26907867632044</v>
       </c>
       <c r="E337" t="n">
-        <v>10.40201121334375</v>
+        <v>10.4020121685439</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753810882568</v>
+        <v>10.22753524780273</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370477645853</v>
+        <v>10.39370186895259</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937985862734</v>
+        <v>10.16937701387342</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385460922237</v>
+        <v>10.34385171566137</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314342498779</v>
+        <v>11.13314437866211</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913016668102</v>
+        <v>11.1913026254664</v>
       </c>
       <c r="D344" t="n">
-        <v>10.94205170125786</v>
+        <v>10.9420526385631</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006010313701</v>
+        <v>11.05006104969434</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7312,16 +7312,16 @@
         <v>44817</v>
       </c>
       <c r="B345" t="n">
-        <v>11.14145183563232</v>
+        <v>11.14145278930664</v>
       </c>
       <c r="C345" t="n">
-        <v>11.19961007917147</v>
+        <v>11.19961103782396</v>
       </c>
       <c r="D345" t="n">
-        <v>10.70111096808326</v>
+        <v>10.70111188406574</v>
       </c>
       <c r="E345" t="n">
-        <v>10.95866902300398</v>
+        <v>10.95866996103265</v>
       </c>
       <c r="F345" t="n">
         <v>335223</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314342498779</v>
+        <v>11.13314437866211</v>
       </c>
       <c r="C346" t="n">
-        <v>11.1497595885191</v>
+        <v>11.14976054361677</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389345943545</v>
+        <v>10.88389439175881</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145150675345</v>
+        <v>11.14145246113944</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7352,16 +7352,16 @@
         <v>44819</v>
       </c>
       <c r="B347" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269481658936</v>
       </c>
       <c r="C347" t="n">
-        <v>11.29100099088769</v>
+        <v>11.29100289964081</v>
       </c>
       <c r="D347" t="n">
-        <v>10.73434449537589</v>
+        <v>10.73434631002577</v>
       </c>
       <c r="E347" t="n">
-        <v>11.05005994527452</v>
+        <v>11.05006181329636</v>
       </c>
       <c r="F347" t="n">
         <v>361349</v>
@@ -7392,16 +7392,16 @@
         <v>44823</v>
       </c>
       <c r="B349" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269481658936</v>
       </c>
       <c r="C349" t="n">
-        <v>11.38239239319849</v>
+        <v>11.38239431740141</v>
       </c>
       <c r="D349" t="n">
-        <v>11.17468450890459</v>
+        <v>11.17468639799431</v>
       </c>
       <c r="E349" t="n">
-        <v>11.3574673135262</v>
+        <v>11.35746923351551</v>
       </c>
       <c r="F349" t="n">
         <v>125366</v>
@@ -7412,16 +7412,16 @@
         <v>44824</v>
       </c>
       <c r="B350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.1580696105957</v>
       </c>
       <c r="C350" t="n">
-        <v>11.30761915031543</v>
+        <v>11.30762011677175</v>
       </c>
       <c r="D350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.1580696105957</v>
       </c>
       <c r="E350" t="n">
-        <v>11.17468565665344</v>
+        <v>11.17468661174801</v>
       </c>
       <c r="F350" t="n">
         <v>127157</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85066145408563</v>
+        <v>10.85066048103983</v>
       </c>
       <c r="D352" t="n">
-        <v>10.59310421404906</v>
+        <v>10.5931032641</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449562740583</v>
+        <v>10.68449466926114</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="D353" t="n">
-        <v>10.3438542219321</v>
+        <v>10.34385329433483</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156296606198</v>
+        <v>10.55156201983819</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7512,16 +7512,16 @@
         <v>44831</v>
       </c>
       <c r="B355" t="n">
-        <v>10.28569602966309</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="C355" t="n">
-        <v>10.58479449503473</v>
+        <v>10.58479547644101</v>
       </c>
       <c r="D355" t="n">
-        <v>10.28569602966309</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="E355" t="n">
-        <v>10.42693676296128</v>
+        <v>10.42693772973123</v>
       </c>
       <c r="F355" t="n">
         <v>115674</v>
@@ -7592,16 +7592,16 @@
         <v>44837</v>
       </c>
       <c r="B359" t="n">
-        <v>10.28569602966309</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="C359" t="n">
-        <v>10.60971957583189</v>
+        <v>10.60972055954919</v>
       </c>
       <c r="D359" t="n">
-        <v>10.1361455448801</v>
+        <v>10.13614648468832</v>
       </c>
       <c r="E359" t="n">
-        <v>10.3604696025917</v>
+        <v>10.36047056319891</v>
       </c>
       <c r="F359" t="n">
         <v>398643</v>
@@ -7632,16 +7632,16 @@
         <v>44839</v>
       </c>
       <c r="B361" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C361" t="n">
-        <v>10.90051210710464</v>
+        <v>10.90051113263368</v>
       </c>
       <c r="D361" t="n">
-        <v>10.55987152112339</v>
+        <v>10.55987057710461</v>
       </c>
       <c r="E361" t="n">
-        <v>10.80081177190503</v>
+        <v>10.80081080634695</v>
       </c>
       <c r="F361" t="n">
         <v>399697</v>
@@ -7652,16 +7652,16 @@
         <v>44840</v>
       </c>
       <c r="B362" t="n">
-        <v>10.88389492034912</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="C362" t="n">
-        <v>10.88389492034912</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="D362" t="n">
-        <v>10.51832925681457</v>
+        <v>10.51832833517203</v>
       </c>
       <c r="E362" t="n">
-        <v>10.53494542257621</v>
+        <v>10.53494449947773</v>
       </c>
       <c r="F362" t="n">
         <v>536757</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389461942159</v>
+        <v>10.88389364339556</v>
       </c>
       <c r="D363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="E363" t="n">
-        <v>10.82573720613229</v>
+        <v>10.82573623532159</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156279823885</v>
+        <v>10.55156188207657</v>
       </c>
       <c r="E364" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558555603027</v>
+        <v>10.87558650970459</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160236333128</v>
+        <v>11.09160333594799</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85066047559313</v>
+        <v>10.85066142708177</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344412055507</v>
+        <v>11.03344508807192</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7852,16 +7852,16 @@
         <v>44855</v>
       </c>
       <c r="B372" t="n">
-        <v>10.68449592590332</v>
+        <v>10.684494972229</v>
       </c>
       <c r="C372" t="n">
-        <v>10.88389492348978</v>
+        <v>10.88389395201756</v>
       </c>
       <c r="D372" t="n">
-        <v>10.68449592590332</v>
+        <v>10.684494972229</v>
       </c>
       <c r="E372" t="n">
-        <v>10.76757925893011</v>
+        <v>10.76757829783996</v>
       </c>
       <c r="F372" t="n">
         <v>132319</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.6512622833252</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866968357269</v>
+        <v>10.95866870237426</v>
       </c>
       <c r="D374" t="n">
-        <v>10.6512622833252</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772777815022</v>
+        <v>10.71772681852483</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19960975646973</v>
+        <v>11.19961166381836</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577640028841</v>
+        <v>11.36577833593604</v>
       </c>
       <c r="D381" t="n">
-        <v>10.8838934671068</v>
+        <v>10.88389532068739</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344394738246</v>
+        <v>11.03344582643224</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8092,16 +8092,16 @@
         <v>44874</v>
       </c>
       <c r="B384" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C384" t="n">
-        <v>10.84235207266271</v>
+        <v>10.84235303967512</v>
       </c>
       <c r="D384" t="n">
-        <v>10.49340262633743</v>
+        <v>10.49340356222759</v>
       </c>
       <c r="E384" t="n">
-        <v>10.79250191326441</v>
+        <v>10.79250287583077</v>
       </c>
       <c r="F384" t="n">
         <v>162870</v>
@@ -8112,16 +8112,16 @@
         <v>44875</v>
       </c>
       <c r="B385" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C385" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="D385" t="n">
-        <v>10.23584626645618</v>
+        <v>10.23584535140422</v>
       </c>
       <c r="E385" t="n">
-        <v>10.58479577019176</v>
+        <v>10.58479482394483</v>
       </c>
       <c r="F385" t="n">
         <v>289395</v>
@@ -8152,16 +8152,16 @@
         <v>44879</v>
       </c>
       <c r="B387" t="n">
-        <v>10.08629703521729</v>
+        <v>10.08629608154297</v>
       </c>
       <c r="C387" t="n">
-        <v>10.50171372532113</v>
+        <v>10.50171273236855</v>
       </c>
       <c r="D387" t="n">
-        <v>9.953364362169316</v>
+        <v>9.95336342106398</v>
       </c>
       <c r="E387" t="n">
-        <v>10.25246371125882</v>
+        <v>10.2524627418732</v>
       </c>
       <c r="F387" t="n">
         <v>430564</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765273094177246</v>
+        <v>8.765274047851562</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873281492987086</v>
+        <v>8.873282458412872</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225232769590827</v>
+        <v>8.225233664507979</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707114854007546</v>
+        <v>8.707115801354162</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8232,16 +8232,16 @@
         <v>44886</v>
       </c>
       <c r="B391" t="n">
-        <v>8.923130989074707</v>
+        <v>8.923131942749023</v>
       </c>
       <c r="C391" t="n">
-        <v>8.923130989074707</v>
+        <v>8.923131942749023</v>
       </c>
       <c r="D391" t="n">
-        <v>8.516024134762748</v>
+        <v>8.516025044926849</v>
       </c>
       <c r="E391" t="n">
-        <v>8.723731185397959</v>
+        <v>8.723732117761093</v>
       </c>
       <c r="F391" t="n">
         <v>232085</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562845230102539</v>
+        <v>8.562846183776855</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039488002680034</v>
+        <v>9.039489009439741</v>
       </c>
       <c r="D392" t="n">
-        <v>8.52939671765821</v>
+        <v>8.529397667607249</v>
       </c>
       <c r="E392" t="n">
-        <v>8.947504383423015</v>
+        <v>8.94750537993818</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.78026294708252</v>
+        <v>8.780261039733887</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880608506884256</v>
+        <v>8.880606577737419</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462501587640029</v>
+        <v>8.462499749319136</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537760547456168</v>
+        <v>8.537758692786666</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081298828125</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081298828125</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621380711839127</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621380711839127</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.82207202911377</v>
+        <v>8.822073936462402</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098022879921743</v>
+        <v>9.098024846931471</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746812247907716</v>
+        <v>8.746814138985041</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081298204051361</v>
+        <v>9.081300167445182</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8332,16 +8332,16 @@
         <v>44893</v>
       </c>
       <c r="B396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="C396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="D396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="E396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="F396" t="n">
         <v>122943</v>
@@ -8352,16 +8352,16 @@
         <v>44894</v>
       </c>
       <c r="B397" t="n">
-        <v>8.705001831054688</v>
+        <v>8.705002784729004</v>
       </c>
       <c r="C397" t="n">
-        <v>8.872244389298597</v>
+        <v>8.87224536129513</v>
       </c>
       <c r="D397" t="n">
-        <v>8.470861409372766</v>
+        <v>8.470862337395888</v>
       </c>
       <c r="E397" t="n">
-        <v>8.604655455967894</v>
+        <v>8.604656398648789</v>
       </c>
       <c r="F397" t="n">
         <v>205221</v>
@@ -8372,16 +8372,16 @@
         <v>44895</v>
       </c>
       <c r="B398" t="n">
-        <v>8.671553611755371</v>
+        <v>8.671554565429688</v>
       </c>
       <c r="C398" t="n">
-        <v>8.905694041331014</v>
+        <v>8.905695020755468</v>
       </c>
       <c r="D398" t="n">
-        <v>8.60465574606199</v>
+        <v>8.604656692379058</v>
       </c>
       <c r="E398" t="n">
-        <v>8.705002124531823</v>
+        <v>8.705003081884717</v>
       </c>
       <c r="F398" t="n">
         <v>181728</v>
@@ -8392,16 +8392,16 @@
         <v>44896</v>
       </c>
       <c r="B399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955865859985352</v>
       </c>
       <c r="C399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955865859985352</v>
       </c>
       <c r="D399" t="n">
-        <v>8.596294234144615</v>
+        <v>8.596293318759741</v>
       </c>
       <c r="E399" t="n">
-        <v>8.721726373019072</v>
+        <v>8.721725444277432</v>
       </c>
       <c r="F399" t="n">
         <v>469965</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947504043579102</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198369137593913</v>
+        <v>9.198370118006814</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822071916641914</v>
+        <v>8.822072856946983</v>
       </c>
       <c r="E400" t="n">
-        <v>9.139833192864064</v>
+        <v>9.139834167037881</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905695681933357</v>
+        <v>8.905693728734814</v>
       </c>
       <c r="D403" t="n">
-        <v>8.679917128923909</v>
+        <v>8.679915225243152</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437414169311523</v>
+        <v>8.437413215637207</v>
       </c>
       <c r="C404" t="n">
-        <v>8.738452529775763</v>
+        <v>8.738451542075317</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412328409401773</v>
+        <v>8.412327458562881</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705004009755438</v>
+        <v>8.705003025835651</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935684680938721</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="C405" t="n">
-        <v>8.47922454343796</v>
+        <v>8.479225052935186</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935684680938721</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462500705285068</v>
+        <v>8.462501213777397</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8592,16 +8592,16 @@
         <v>44910</v>
       </c>
       <c r="B409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253444671630859</v>
       </c>
       <c r="C409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253444671630859</v>
       </c>
       <c r="D409" t="n">
-        <v>8.027667939705447</v>
+        <v>8.027667012119434</v>
       </c>
       <c r="E409" t="n">
-        <v>8.111289647021858</v>
+        <v>8.11128870977347</v>
       </c>
       <c r="F409" t="n">
         <v>145488</v>
@@ -8632,16 +8632,16 @@
         <v>44914</v>
       </c>
       <c r="B411" t="n">
-        <v>8.161463737487793</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="C411" t="n">
-        <v>8.161463737487793</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="D411" t="n">
-        <v>7.952410684884464</v>
+        <v>7.952409755638184</v>
       </c>
       <c r="E411" t="n">
-        <v>8.12801605560634</v>
+        <v>8.128015105840415</v>
       </c>
       <c r="F411" t="n">
         <v>108510</v>
@@ -8652,16 +8652,16 @@
         <v>44915</v>
       </c>
       <c r="B412" t="n">
-        <v>8.429050445556641</v>
+        <v>8.429051399230957</v>
       </c>
       <c r="C412" t="n">
-        <v>8.579570013648471</v>
+        <v>8.579570984352777</v>
       </c>
       <c r="D412" t="n">
-        <v>8.0527540457485</v>
+        <v>8.052754956848128</v>
       </c>
       <c r="E412" t="n">
-        <v>8.0527540457485</v>
+        <v>8.052754956848128</v>
       </c>
       <c r="F412" t="n">
         <v>166979</v>
@@ -8672,16 +8672,16 @@
         <v>44916</v>
       </c>
       <c r="B413" t="n">
-        <v>8.454139709472656</v>
+        <v>8.45413875579834</v>
       </c>
       <c r="C413" t="n">
-        <v>8.613019549838441</v>
+        <v>8.613018578241588</v>
       </c>
       <c r="D413" t="n">
-        <v>8.370517989154285</v>
+        <v>8.370517044912967</v>
       </c>
       <c r="E413" t="n">
-        <v>8.429052269222419</v>
+        <v>8.429051318378106</v>
       </c>
       <c r="F413" t="n">
         <v>125998</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613019250906639</v>
+        <v>8.613017361897933</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730090327401705</v>
+        <v>8.730088412716954</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.73845100402832</v>
+        <v>8.738451957702637</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788623355228307</v>
+        <v>8.788624314378202</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284567447709</v>
+        <v>8.56284660898665</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713364408358071</v>
+        <v>8.713365359294553</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914057601632781</v>
+        <v>8.914055646600298</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830435884216666</v>
+        <v>8.83043394752411</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529397964477539</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771899364464465</v>
+        <v>8.771900345253039</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529397964477539</v>
       </c>
       <c r="E420" t="n">
-        <v>8.705002337276639</v>
+        <v>8.705003310585438</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8832,16 +8832,16 @@
         <v>44929</v>
       </c>
       <c r="B421" t="n">
-        <v>8.102926254272461</v>
+        <v>8.102927207946777</v>
       </c>
       <c r="C421" t="n">
-        <v>8.50430920017612</v>
+        <v>8.504310201091222</v>
       </c>
       <c r="D421" t="n">
-        <v>8.086201579795469</v>
+        <v>8.086202531501375</v>
       </c>
       <c r="E421" t="n">
-        <v>8.47922260853082</v>
+        <v>8.479223606493356</v>
       </c>
       <c r="F421" t="n">
         <v>326162</v>
@@ -8852,16 +8852,16 @@
         <v>44930</v>
       </c>
       <c r="B422" t="n">
-        <v>8.328704833984375</v>
+        <v>8.328705787658691</v>
       </c>
       <c r="C422" t="n">
-        <v>8.345428670198819</v>
+        <v>8.345429625788091</v>
       </c>
       <c r="D422" t="n">
-        <v>8.061115893289037</v>
+        <v>8.061116816323212</v>
       </c>
       <c r="E422" t="n">
-        <v>8.345428670198819</v>
+        <v>8.345429625788091</v>
       </c>
       <c r="F422" t="n">
         <v>248204</v>
@@ -8872,16 +8872,16 @@
         <v>44931</v>
       </c>
       <c r="B423" t="n">
-        <v>8.395602226257324</v>
+        <v>8.395604133605957</v>
       </c>
       <c r="C423" t="n">
-        <v>8.454137329990965</v>
+        <v>8.454139250637853</v>
       </c>
       <c r="D423" t="n">
-        <v>8.270170101153928</v>
+        <v>8.270171980006358</v>
       </c>
       <c r="E423" t="n">
-        <v>8.362153715572447</v>
+        <v>8.362155615322106</v>
       </c>
       <c r="F423" t="n">
         <v>69636</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947504043579102</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947504043579102</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387239591100503</v>
+        <v>8.387240485058745</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395602348999303</v>
+        <v>8.395603243848893</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8912,16 +8912,16 @@
         <v>44935</v>
       </c>
       <c r="B425" t="n">
-        <v>8.813712120056152</v>
+        <v>8.813711166381836</v>
       </c>
       <c r="C425" t="n">
-        <v>8.947506196951567</v>
+        <v>8.947505228800265</v>
       </c>
       <c r="D425" t="n">
-        <v>8.696641042561707</v>
+        <v>8.696640101554889</v>
       </c>
       <c r="E425" t="n">
-        <v>8.905695757956909</v>
+        <v>8.905694794329643</v>
       </c>
       <c r="F425" t="n">
         <v>148121</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964228630065918</v>
+        <v>8.964229583740234</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072936930593318</v>
+        <v>9.072937895832748</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847159251220148</v>
+        <v>8.847160192439846</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922418197631035</v>
+        <v>8.922419146857282</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -9052,16 +9052,16 @@
         <v>44944</v>
       </c>
       <c r="B432" t="n">
-        <v>9.0645751953125</v>
+        <v>9.064576148986816</v>
       </c>
       <c r="C432" t="n">
-        <v>9.357250748692612</v>
+        <v>9.357251733159014</v>
       </c>
       <c r="D432" t="n">
-        <v>8.964228811216161</v>
+        <v>8.964229754333143</v>
       </c>
       <c r="E432" t="n">
-        <v>8.964228811216161</v>
+        <v>8.964229754333143</v>
       </c>
       <c r="F432" t="n">
         <v>306251</v>
@@ -9092,16 +9092,16 @@
         <v>44946</v>
       </c>
       <c r="B434" t="n">
-        <v>9.365612983703613</v>
+        <v>9.36561107635498</v>
       </c>
       <c r="C434" t="n">
-        <v>9.365612983703613</v>
+        <v>9.36561107635498</v>
       </c>
       <c r="D434" t="n">
-        <v>9.039488904654647</v>
+        <v>9.03948706372263</v>
       </c>
       <c r="E434" t="n">
-        <v>9.131472533089941</v>
+        <v>9.131470673425049</v>
       </c>
       <c r="F434" t="n">
         <v>97975</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566304206848145</v>
+        <v>9.566305160522461</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616476556718098</v>
+        <v>9.616477515394145</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407422718528574</v>
+        <v>9.407423656363838</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424147395245551</v>
+        <v>9.424148334748114</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9132,16 +9132,16 @@
         <v>44950</v>
       </c>
       <c r="B436" t="n">
-        <v>9.474320411682129</v>
+        <v>9.474322319030762</v>
       </c>
       <c r="C436" t="n">
-        <v>9.616476380539872</v>
+        <v>9.61647831650702</v>
       </c>
       <c r="D436" t="n">
-        <v>9.348887438954012</v>
+        <v>9.348889321050764</v>
       </c>
       <c r="E436" t="n">
-        <v>9.616476380539872</v>
+        <v>9.61647831650702</v>
       </c>
       <c r="F436" t="n">
         <v>142116</v>
@@ -9152,16 +9152,16 @@
         <v>44951</v>
       </c>
       <c r="B437" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="C437" t="n">
-        <v>9.842255125096191</v>
+        <v>9.842257043856318</v>
       </c>
       <c r="D437" t="n">
-        <v>9.41578552811195</v>
+        <v>9.415787363731287</v>
       </c>
       <c r="E437" t="n">
-        <v>9.541217663679022</v>
+        <v>9.541219523751513</v>
       </c>
       <c r="F437" t="n">
         <v>142538</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C438" t="n">
-        <v>9.95932505997885</v>
+        <v>9.959326039139317</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741909308483715</v>
+        <v>9.741910266268745</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="D439" t="n">
-        <v>9.6499256889996</v>
+        <v>9.649926637741174</v>
       </c>
       <c r="E439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9232,16 +9232,16 @@
         <v>44957</v>
       </c>
       <c r="B441" t="n">
-        <v>9.449235916137695</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="C441" t="n">
-        <v>9.683376397053557</v>
+        <v>9.683374442443164</v>
       </c>
       <c r="D441" t="n">
-        <v>9.449235916137695</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="E441" t="n">
-        <v>9.61647851669141</v>
+        <v>9.616476575584498</v>
       </c>
       <c r="F441" t="n">
         <v>134742</v>
@@ -9252,16 +9252,16 @@
         <v>44958</v>
       </c>
       <c r="B442" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="C442" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="D442" t="n">
-        <v>9.323801065879572</v>
+        <v>9.323802883566421</v>
       </c>
       <c r="E442" t="n">
-        <v>9.449234041587136</v>
+        <v>9.449235883727303</v>
       </c>
       <c r="F442" t="n">
         <v>177092</v>
@@ -9292,16 +9292,16 @@
         <v>44960</v>
       </c>
       <c r="B444" t="n">
-        <v>9.675012588500977</v>
+        <v>9.67501163482666</v>
       </c>
       <c r="C444" t="n">
-        <v>9.867342608471997</v>
+        <v>9.867341635839546</v>
       </c>
       <c r="D444" t="n">
-        <v>9.382337859212104</v>
+        <v>9.382336934386988</v>
       </c>
       <c r="E444" t="n">
-        <v>9.474321489584133</v>
+        <v>9.474320555692112</v>
       </c>
       <c r="F444" t="n">
         <v>1290218</v>
@@ -9312,16 +9312,16 @@
         <v>44963</v>
       </c>
       <c r="B445" t="n">
-        <v>9.608115196228027</v>
+        <v>9.608116149902344</v>
       </c>
       <c r="C445" t="n">
-        <v>9.842255643015774</v>
+        <v>9.842256619930208</v>
       </c>
       <c r="D445" t="n">
-        <v>9.599753277454333</v>
+        <v>9.599754230298668</v>
       </c>
       <c r="E445" t="n">
-        <v>9.666650307924964</v>
+        <v>9.666651267409309</v>
       </c>
       <c r="F445" t="n">
         <v>107772</v>
@@ -9332,16 +9332,16 @@
         <v>44964</v>
       </c>
       <c r="B446" t="n">
-        <v>9.733548164367676</v>
+        <v>9.733549118041992</v>
       </c>
       <c r="C446" t="n">
-        <v>9.733548164367676</v>
+        <v>9.733549118041992</v>
       </c>
       <c r="D446" t="n">
-        <v>9.457596443832067</v>
+        <v>9.457597370469164</v>
       </c>
       <c r="E446" t="n">
-        <v>9.64992645633084</v>
+        <v>9.649927401812063</v>
       </c>
       <c r="F446" t="n">
         <v>121889</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312057495117</v>
+        <v>10.09312152862549</v>
       </c>
       <c r="C447" t="n">
-        <v>10.16001676400513</v>
+        <v>10.1600177240003</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649926286291848</v>
+        <v>9.649927198089818</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741909911469383</v>
+        <v>9.741910831958663</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9392,16 +9392,16 @@
         <v>44967</v>
       </c>
       <c r="B449" t="n">
-        <v>9.373974800109863</v>
+        <v>9.37397575378418</v>
       </c>
       <c r="C449" t="n">
-        <v>10.1432922660117</v>
+        <v>10.1432932979536</v>
       </c>
       <c r="D449" t="n">
-        <v>9.298715017063337</v>
+        <v>9.298715963080996</v>
       </c>
       <c r="E449" t="n">
-        <v>9.95096310957136</v>
+        <v>9.950964121946381</v>
       </c>
       <c r="F449" t="n">
         <v>543394</v>
@@ -9452,16 +9452,16 @@
         <v>44972</v>
       </c>
       <c r="B452" t="n">
-        <v>10.22691440582275</v>
+        <v>10.22691535949707</v>
       </c>
       <c r="C452" t="n">
-        <v>10.34398378423839</v>
+        <v>10.3439847488296</v>
       </c>
       <c r="D452" t="n">
-        <v>9.91751502257609</v>
+        <v>9.917515947398474</v>
       </c>
       <c r="E452" t="n">
-        <v>9.91751502257609</v>
+        <v>9.917515947398474</v>
       </c>
       <c r="F452" t="n">
         <v>361455</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363899230957</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088241395452</v>
+        <v>10.41088144470998</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458513532366</v>
+        <v>10.03458420111209</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820684614614</v>
+        <v>10.11820590414945</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9492,16 +9492,16 @@
         <v>44974</v>
       </c>
       <c r="B454" t="n">
-        <v>10.3523473739624</v>
+        <v>10.35234928131104</v>
       </c>
       <c r="C454" t="n">
-        <v>10.45269291543465</v>
+        <v>10.45269484127125</v>
       </c>
       <c r="D454" t="n">
-        <v>10.09312034165015</v>
+        <v>10.09312220123799</v>
       </c>
       <c r="E454" t="n">
-        <v>10.10148226007104</v>
+        <v>10.10148412119951</v>
       </c>
       <c r="F454" t="n">
         <v>113461</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363899230957</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C455" t="n">
-        <v>10.619937111081</v>
+        <v>10.61993612237364</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992775540123269</v>
+        <v>9.992774609804133</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889878409197</v>
+        <v>10.31889782341103</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9532,16 +9532,16 @@
         <v>44980</v>
       </c>
       <c r="B456" t="n">
-        <v>10.10148429870605</v>
+        <v>10.10148239135742</v>
       </c>
       <c r="C456" t="n">
-        <v>10.4359703445918</v>
+        <v>10.43596837408596</v>
       </c>
       <c r="D456" t="n">
-        <v>10.03458641741637</v>
+        <v>10.0345845226993</v>
       </c>
       <c r="E456" t="n">
-        <v>10.4359703445918</v>
+        <v>10.43596837408596</v>
       </c>
       <c r="F456" t="n">
         <v>107772</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458499908447</v>
+        <v>10.03458404541016</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889864399266</v>
+        <v>10.31889766329754</v>
       </c>
       <c r="D459" t="n">
-        <v>9.90915369476458</v>
+        <v>9.909152753011098</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950964129537878</v>
+        <v>9.950963183810783</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363899230957</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053686505189</v>
+        <v>10.31053590514944</v>
       </c>
       <c r="D460" t="n">
-        <v>9.85061787559855</v>
+        <v>9.850616958514175</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458513532366</v>
+        <v>10.03458420111209</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9632,16 +9632,16 @@
         <v>44987</v>
       </c>
       <c r="B461" t="n">
-        <v>10.47777938842773</v>
+        <v>10.47777843475342</v>
       </c>
       <c r="C461" t="n">
-        <v>10.55303917979261</v>
+        <v>10.55303821926824</v>
       </c>
       <c r="D461" t="n">
-        <v>10.11820679001243</v>
+        <v>10.11820586906596</v>
       </c>
       <c r="E461" t="n">
-        <v>10.20182850037099</v>
+        <v>10.20182757181338</v>
       </c>
       <c r="F461" t="n">
         <v>220181</v>
@@ -9652,16 +9652,16 @@
         <v>44988</v>
       </c>
       <c r="B462" t="n">
-        <v>10.32726097106934</v>
+        <v>10.32726192474365</v>
       </c>
       <c r="C462" t="n">
-        <v>10.64502314438275</v>
+        <v>10.64502412740092</v>
       </c>
       <c r="D462" t="n">
-        <v>10.32726097106934</v>
+        <v>10.32726192474365</v>
       </c>
       <c r="E462" t="n">
-        <v>10.61157378707348</v>
+        <v>10.61157476700276</v>
       </c>
       <c r="F462" t="n">
         <v>104401</v>
@@ -9672,16 +9672,16 @@
         <v>44991</v>
       </c>
       <c r="B463" t="n">
-        <v>10.6366605758667</v>
+        <v>10.63666152954102</v>
       </c>
       <c r="C463" t="n">
-        <v>10.6366605758667</v>
+        <v>10.63666152954102</v>
       </c>
       <c r="D463" t="n">
-        <v>10.20182819893464</v>
+        <v>10.20182911362224</v>
       </c>
       <c r="E463" t="n">
-        <v>10.32726034069602</v>
+        <v>10.32726126662976</v>
       </c>
       <c r="F463" t="n">
         <v>82488</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.7453670501709</v>
       </c>
       <c r="C465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.7453670501709</v>
       </c>
       <c r="D465" t="n">
-        <v>10.50286563988488</v>
+        <v>10.50286470773317</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502245880179</v>
+        <v>10.64502151403336</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9772,16 +9772,16 @@
         <v>44998</v>
       </c>
       <c r="B468" t="n">
-        <v>10.18510437011719</v>
+        <v>10.18510341644287</v>
       </c>
       <c r="C468" t="n">
-        <v>10.77881656430283</v>
+        <v>10.77881555503673</v>
       </c>
       <c r="D468" t="n">
-        <v>10.18510437011719</v>
+        <v>10.18510341644287</v>
       </c>
       <c r="E468" t="n">
-        <v>10.77881656430283</v>
+        <v>10.77881555503673</v>
       </c>
       <c r="F468" t="n">
         <v>154864</v>
@@ -9792,16 +9792,16 @@
         <v>44999</v>
       </c>
       <c r="B469" t="n">
-        <v>9.892428398132324</v>
+        <v>9.892426490783691</v>
       </c>
       <c r="C469" t="n">
-        <v>10.2603646011067</v>
+        <v>10.26036262281668</v>
       </c>
       <c r="D469" t="n">
-        <v>9.892428398132324</v>
+        <v>9.892426490783691</v>
       </c>
       <c r="E469" t="n">
-        <v>10.17674288954717</v>
+        <v>10.17674092738016</v>
       </c>
       <c r="F469" t="n">
         <v>103137</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165615081787</v>
+        <v>10.15165519714355</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837999019679</v>
+        <v>10.16837903495139</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683376046098697</v>
+        <v>9.683375136415892</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833894801212116</v>
+        <v>9.833893877389167</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9852,16 +9852,16 @@
         <v>45002</v>
       </c>
       <c r="B472" t="n">
-        <v>9.942601203918457</v>
+        <v>9.942600250244141</v>
       </c>
       <c r="C472" t="n">
-        <v>10.18510440999109</v>
+        <v>10.18510343305635</v>
       </c>
       <c r="D472" t="n">
-        <v>9.750272030986295</v>
+        <v>9.750271095759805</v>
       </c>
       <c r="E472" t="n">
-        <v>10.18510440999109</v>
+        <v>10.18510343305635</v>
       </c>
       <c r="F472" t="n">
         <v>69952</v>
@@ -9872,16 +9872,16 @@
         <v>45005</v>
       </c>
       <c r="B473" t="n">
-        <v>9.532856941223145</v>
+        <v>9.532855987548828</v>
       </c>
       <c r="C473" t="n">
-        <v>9.909155108574742</v>
+        <v>9.909154117255268</v>
       </c>
       <c r="D473" t="n">
-        <v>9.340527737628216</v>
+        <v>9.340526803194662</v>
       </c>
       <c r="E473" t="n">
-        <v>9.909155108574742</v>
+        <v>9.909154117255268</v>
       </c>
       <c r="F473" t="n">
         <v>182676</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440872192382812</v>
+        <v>9.440871238708496</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583029018449141</v>
+        <v>9.583028050414784</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415786434965732</v>
+        <v>9.415785483825466</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532855823333831</v>
+        <v>9.532854860367744</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9912,16 +9912,16 @@
         <v>45007</v>
       </c>
       <c r="B475" t="n">
-        <v>9.449235916137695</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="C475" t="n">
-        <v>9.507771036366661</v>
+        <v>9.507769117202587</v>
       </c>
       <c r="D475" t="n">
-        <v>9.206733515229313</v>
+        <v>9.206731656830312</v>
       </c>
       <c r="E475" t="n">
-        <v>9.482684436248439</v>
+        <v>9.482682522148149</v>
       </c>
       <c r="F475" t="n">
         <v>116622</v>
@@ -9932,16 +9932,16 @@
         <v>45008</v>
       </c>
       <c r="B476" t="n">
-        <v>9.332164764404297</v>
+        <v>9.332165718078613</v>
       </c>
       <c r="C476" t="n">
-        <v>9.407423717269351</v>
+        <v>9.407424678634545</v>
       </c>
       <c r="D476" t="n">
-        <v>9.131472823196523</v>
+        <v>9.131473756361691</v>
       </c>
       <c r="E476" t="n">
-        <v>9.399061798093364</v>
+        <v>9.399062758604034</v>
       </c>
       <c r="F476" t="n">
         <v>179094</v>
@@ -9952,16 +9952,16 @@
         <v>45009</v>
       </c>
       <c r="B477" t="n">
-        <v>9.641565322875977</v>
+        <v>9.641563415527344</v>
       </c>
       <c r="C477" t="n">
-        <v>9.666651081203783</v>
+        <v>9.666649168892544</v>
       </c>
       <c r="D477" t="n">
-        <v>9.089662676992758</v>
+        <v>9.089660878824608</v>
       </c>
       <c r="E477" t="n">
-        <v>9.373976339447273</v>
+        <v>9.373974485034596</v>
       </c>
       <c r="F477" t="n">
         <v>212279</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820570451678</v>
+        <v>10.11820669929775</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201012665911</v>
+        <v>9.633201959763182</v>
       </c>
       <c r="E483" t="n">
-        <v>10.03458400312928</v>
+        <v>10.0345849896889</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758633144676933</v>
+        <v>9.758634104106184</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683374404907227</v>
+        <v>9.683376312255859</v>
       </c>
       <c r="C490" t="n">
-        <v>9.77535802632328</v>
+        <v>9.775359951790064</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566304188533978</v>
+        <v>9.566306072823117</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608114620035645</v>
+        <v>9.608116512560244</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10252,16 +10252,16 @@
         <v>45033</v>
       </c>
       <c r="B492" t="n">
-        <v>9.649925231933594</v>
+        <v>9.64992618560791</v>
       </c>
       <c r="C492" t="n">
-        <v>9.7251841715194</v>
+        <v>9.725185132631342</v>
       </c>
       <c r="D492" t="n">
-        <v>9.566303534506806</v>
+        <v>9.566304479917033</v>
       </c>
       <c r="E492" t="n">
-        <v>9.616475880850535</v>
+        <v>9.616476831219149</v>
       </c>
       <c r="F492" t="n">
         <v>328796</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766995062773542</v>
+        <v>9.766996023024904</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549580151418876</v>
+        <v>9.549581090294884</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691736119623117</v>
+        <v>9.691737072475323</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.658288955688477</v>
+        <v>9.658287048339844</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716823230678386</v>
+        <v>9.716821311770225</v>
       </c>
       <c r="D494" t="n">
-        <v>9.59975384055798</v>
+        <v>9.599751944769041</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616477679086358</v>
+        <v>9.616475779994744</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10332,16 +10332,16 @@
         <v>45040</v>
       </c>
       <c r="B496" t="n">
-        <v>9.516132354736328</v>
+        <v>9.516131401062012</v>
       </c>
       <c r="C496" t="n">
-        <v>9.700099623785084</v>
+        <v>9.700098651674196</v>
       </c>
       <c r="D496" t="n">
-        <v>9.516132354736328</v>
+        <v>9.516131401062012</v>
       </c>
       <c r="E496" t="n">
-        <v>9.633202587792919</v>
+        <v>9.633201622386224</v>
       </c>
       <c r="F496" t="n">
         <v>136322</v>
@@ -10432,16 +10432,16 @@
         <v>45048</v>
       </c>
       <c r="B501" t="n">
-        <v>9.10916805267334</v>
+        <v>9.109169960021973</v>
       </c>
       <c r="C501" t="n">
-        <v>9.201264350497761</v>
+        <v>9.201266277130236</v>
       </c>
       <c r="D501" t="n">
-        <v>9.017071754848917</v>
+        <v>9.01707364291371</v>
       </c>
       <c r="E501" t="n">
-        <v>9.176147025423896</v>
+        <v>9.176148946797108</v>
       </c>
       <c r="F501" t="n">
         <v>926867</v>
@@ -10472,16 +10472,16 @@
         <v>45050</v>
       </c>
       <c r="B503" t="n">
-        <v>9.209639549255371</v>
+        <v>9.209638595581055</v>
       </c>
       <c r="C503" t="n">
-        <v>9.469183340851389</v>
+        <v>9.469182360300858</v>
       </c>
       <c r="D503" t="n">
-        <v>9.067307726170736</v>
+        <v>9.067306787235129</v>
       </c>
       <c r="E503" t="n">
-        <v>9.159404887127831</v>
+        <v>9.159403938655403</v>
       </c>
       <c r="F503" t="n">
         <v>221234</v>
@@ -10572,16 +10572,16 @@
         <v>45057</v>
       </c>
       <c r="B508" t="n">
-        <v>9.862683296203613</v>
+        <v>9.86268424987793</v>
       </c>
       <c r="C508" t="n">
-        <v>9.929663108067157</v>
+        <v>9.929664068218099</v>
       </c>
       <c r="D508" t="n">
-        <v>9.477553794128655</v>
+        <v>9.477554710562789</v>
       </c>
       <c r="E508" t="n">
-        <v>9.477553794128655</v>
+        <v>9.477554710562789</v>
       </c>
       <c r="F508" t="n">
         <v>216809</v>
@@ -10592,16 +10592,16 @@
         <v>45058</v>
       </c>
       <c r="B509" t="n">
-        <v>10.08036613464355</v>
+        <v>10.08036518096924</v>
       </c>
       <c r="C509" t="n">
-        <v>10.29804906763221</v>
+        <v>10.29804809336354</v>
       </c>
       <c r="D509" t="n">
-        <v>9.762215579178029</v>
+        <v>9.762214655603019</v>
       </c>
       <c r="E509" t="n">
-        <v>9.795705067060208</v>
+        <v>9.795704140316854</v>
       </c>
       <c r="F509" t="n">
         <v>501359</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845940589904785</v>
+        <v>9.845939636230469</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293349078287</v>
+        <v>10.27293249575018</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745472117376274</v>
+        <v>9.745471173433298</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548519539895</v>
+        <v>10.10548421658523</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10712,16 +10712,16 @@
         <v>45068</v>
       </c>
       <c r="B515" t="n">
-        <v>9.904545783996582</v>
+        <v>9.904544830322266</v>
       </c>
       <c r="C515" t="n">
-        <v>9.904545783996582</v>
+        <v>9.904544830322266</v>
       </c>
       <c r="D515" t="n">
-        <v>9.670119366653017</v>
+        <v>9.670118435550807</v>
       </c>
       <c r="E515" t="n">
-        <v>9.737098343036893</v>
+        <v>9.737097405485509</v>
       </c>
       <c r="F515" t="n">
         <v>159710</v>
@@ -10732,16 +10732,16 @@
         <v>45069</v>
       </c>
       <c r="B516" t="n">
-        <v>9.60313892364502</v>
+        <v>9.603140830993652</v>
       </c>
       <c r="C516" t="n">
-        <v>9.99664143573348</v>
+        <v>9.996643421238481</v>
       </c>
       <c r="D516" t="n">
-        <v>9.594766762434734</v>
+        <v>9.59476866812051</v>
       </c>
       <c r="E516" t="n">
-        <v>9.862683491690436</v>
+        <v>9.862685450589087</v>
       </c>
       <c r="F516" t="n">
         <v>117359</v>
@@ -10772,16 +10772,16 @@
         <v>45071</v>
       </c>
       <c r="B518" t="n">
-        <v>9.301734924316406</v>
+        <v>9.30173397064209</v>
       </c>
       <c r="C518" t="n">
-        <v>9.56127953072173</v>
+        <v>9.561278550437214</v>
       </c>
       <c r="D518" t="n">
-        <v>9.293362761868741</v>
+        <v>9.293361809052792</v>
       </c>
       <c r="E518" t="n">
-        <v>9.43569288815803</v>
+        <v>9.435691920749472</v>
       </c>
       <c r="F518" t="n">
         <v>216177</v>
@@ -10792,16 +10792,16 @@
         <v>45072</v>
       </c>
       <c r="B519" t="n">
-        <v>9.37708568572998</v>
+        <v>9.377084732055664</v>
       </c>
       <c r="C519" t="n">
-        <v>9.45243682702116</v>
+        <v>9.452435865683434</v>
       </c>
       <c r="D519" t="n">
-        <v>9.301734544438801</v>
+        <v>9.301733598427894</v>
       </c>
       <c r="E519" t="n">
-        <v>9.326851030756055</v>
+        <v>9.326850082190736</v>
       </c>
       <c r="F519" t="n">
         <v>104401</v>
@@ -10812,16 +10812,16 @@
         <v>45075</v>
       </c>
       <c r="B520" t="n">
-        <v>9.43569278717041</v>
+        <v>9.435691833496094</v>
       </c>
       <c r="C520" t="n">
-        <v>9.502671768374364</v>
+        <v>9.50267080793042</v>
       </c>
       <c r="D520" t="n">
-        <v>9.368713805966456</v>
+        <v>9.368712859061768</v>
       </c>
       <c r="E520" t="n">
-        <v>9.460810115414327</v>
+        <v>9.460809159201379</v>
       </c>
       <c r="F520" t="n">
         <v>106087</v>
@@ -10832,16 +10832,16 @@
         <v>45076</v>
       </c>
       <c r="B521" t="n">
-        <v>9.209639549255371</v>
+        <v>9.209638595581055</v>
       </c>
       <c r="C521" t="n">
-        <v>9.54453449287287</v>
+        <v>9.544533504519595</v>
       </c>
       <c r="D521" t="n">
-        <v>9.151031882660023</v>
+        <v>9.151030935054633</v>
       </c>
       <c r="E521" t="n">
-        <v>9.54453449287287</v>
+        <v>9.544533504519595</v>
       </c>
       <c r="F521" t="n">
         <v>214913</v>
@@ -10892,16 +10892,16 @@
         <v>45079</v>
       </c>
       <c r="B524" t="n">
-        <v>8.933347702026367</v>
+        <v>8.933348655700684</v>
       </c>
       <c r="C524" t="n">
-        <v>9.234753923397504</v>
+        <v>9.234754909248267</v>
       </c>
       <c r="D524" t="n">
-        <v>8.933347702026367</v>
+        <v>8.933348655700684</v>
       </c>
       <c r="E524" t="n">
-        <v>9.084050812711935</v>
+        <v>9.084051782474475</v>
       </c>
       <c r="F524" t="n">
         <v>446577</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958466529846191</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C526" t="n">
-        <v>9.058935006763894</v>
+        <v>9.058934042394197</v>
       </c>
       <c r="D526" t="n">
-        <v>8.832880723406619</v>
+        <v>8.83287978310155</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933349200324322</v>
+        <v>8.933348249323872</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -10952,16 +10952,16 @@
         <v>45084</v>
       </c>
       <c r="B527" t="n">
-        <v>9.117541313171387</v>
+        <v>9.117542266845703</v>
       </c>
       <c r="C527" t="n">
-        <v>9.192892449355798</v>
+        <v>9.192893410911674</v>
       </c>
       <c r="D527" t="n">
-        <v>8.966837358463263</v>
+        <v>8.966838296374284</v>
       </c>
       <c r="E527" t="n">
-        <v>9.092423146217049</v>
+        <v>9.092424097264061</v>
       </c>
       <c r="F527" t="n">
         <v>438781</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.16777515411377</v>
+        <v>9.167776107788086</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226381967416739</v>
+        <v>9.226382927187608</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109168340810799</v>
+        <v>9.109169288388564</v>
       </c>
       <c r="E528" t="n">
-        <v>9.209637644284264</v>
+        <v>9.20963860231331</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -11072,16 +11072,16 @@
         <v>45093</v>
       </c>
       <c r="B533" t="n">
-        <v>9.159402847290039</v>
+        <v>9.159403800964355</v>
       </c>
       <c r="C533" t="n">
-        <v>9.234753982530503</v>
+        <v>9.234754944050357</v>
       </c>
       <c r="D533" t="n">
-        <v>9.075678709446471</v>
+        <v>9.075679654403453</v>
       </c>
       <c r="E533" t="n">
-        <v>9.218009659663574</v>
+        <v>9.218010619440014</v>
       </c>
       <c r="F533" t="n">
         <v>202060</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.99195384979248</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="C535" t="n">
-        <v>8.99195384979248</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899857557908286</v>
+        <v>8.899858501814995</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983581689031073</v>
+        <v>8.983582641817451</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11132,16 +11132,16 @@
         <v>45098</v>
       </c>
       <c r="B536" t="n">
-        <v>9.000327110290527</v>
+        <v>9.000326156616211</v>
       </c>
       <c r="C536" t="n">
-        <v>9.042189601551824</v>
+        <v>9.04218864344176</v>
       </c>
       <c r="D536" t="n">
-        <v>8.857996995277212</v>
+        <v>8.85799605668419</v>
       </c>
       <c r="E536" t="n">
-        <v>9.033817439767434</v>
+        <v>9.033816482544484</v>
       </c>
       <c r="F536" t="n">
         <v>259897</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950092315673828</v>
+        <v>8.950093269348145</v>
       </c>
       <c r="C537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="D537" t="n">
-        <v>8.832878698884004</v>
+        <v>8.83287964006866</v>
       </c>
       <c r="E537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958466529846191</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000328184936123</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841252886190651</v>
+        <v>8.841251944994323</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000328184936123</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11212,16 +11212,16 @@
         <v>45104</v>
       </c>
       <c r="B540" t="n">
-        <v>8.791016578674316</v>
+        <v>8.791015625</v>
       </c>
       <c r="C540" t="n">
-        <v>8.991954336000079</v>
+        <v>8.991953360527468</v>
       </c>
       <c r="D540" t="n">
-        <v>8.724037606622268</v>
+        <v>8.724036660214018</v>
       </c>
       <c r="E540" t="n">
-        <v>8.958464849974055</v>
+        <v>8.958463878134477</v>
       </c>
       <c r="F540" t="n">
         <v>213544</v>
@@ -11232,16 +11232,16 @@
         <v>45105</v>
       </c>
       <c r="B541" t="n">
-        <v>8.657058715820312</v>
+        <v>8.657057762145996</v>
       </c>
       <c r="C541" t="n">
-        <v>8.874740797617315</v>
+        <v>8.874739819962821</v>
       </c>
       <c r="D541" t="n">
-        <v>8.657058715820312</v>
+        <v>8.657057762145996</v>
       </c>
       <c r="E541" t="n">
-        <v>8.874740797617315</v>
+        <v>8.874739819962821</v>
       </c>
       <c r="F541" t="n">
         <v>189418</v>
@@ -11252,16 +11252,16 @@
         <v>45106</v>
       </c>
       <c r="B542" t="n">
-        <v>8.782645225524902</v>
+        <v>8.782646179199219</v>
       </c>
       <c r="C542" t="n">
-        <v>8.84962504490918</v>
+        <v>8.849626005856582</v>
       </c>
       <c r="D542" t="n">
-        <v>8.615196938818752</v>
+        <v>8.615197874310489</v>
       </c>
       <c r="E542" t="n">
-        <v>8.665431593064536</v>
+        <v>8.665432534011066</v>
       </c>
       <c r="F542" t="n">
         <v>269063</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695236206054688</v>
+        <v>9.695237159729004</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843017738918</v>
+        <v>9.753843977178107</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511042768497374</v>
+        <v>9.511043704053456</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611512069195841</v>
+        <v>9.611513014634612</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11372,16 +11372,16 @@
         <v>45114</v>
       </c>
       <c r="B548" t="n">
-        <v>9.628257751464844</v>
+        <v>9.628256797790527</v>
       </c>
       <c r="C548" t="n">
-        <v>9.69523757511187</v>
+        <v>9.695236614803234</v>
       </c>
       <c r="D548" t="n">
-        <v>9.444065129067459</v>
+        <v>9.444064193637333</v>
       </c>
       <c r="E548" t="n">
-        <v>9.444065129067459</v>
+        <v>9.444064193637333</v>
       </c>
       <c r="F548" t="n">
         <v>257790</v>
@@ -11392,16 +11392,16 @@
         <v>45117</v>
       </c>
       <c r="B549" t="n">
-        <v>9.619884490966797</v>
+        <v>9.619885444641113</v>
       </c>
       <c r="C549" t="n">
-        <v>9.745471120239847</v>
+        <v>9.745472086364286</v>
       </c>
       <c r="D549" t="n">
-        <v>9.527788190279663</v>
+        <v>9.527789134823944</v>
       </c>
       <c r="E549" t="n">
-        <v>9.628256652528449</v>
+        <v>9.628257607032745</v>
       </c>
       <c r="F549" t="n">
         <v>614083</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703609466552734</v>
+        <v>9.703608512878418</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703609466552734</v>
+        <v>9.703608512878418</v>
       </c>
       <c r="D550" t="n">
-        <v>9.385458888088531</v>
+        <v>9.385457965682171</v>
       </c>
       <c r="E550" t="n">
-        <v>9.61988532021015</v>
+        <v>9.619884374764274</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11472,16 +11472,16 @@
         <v>45121</v>
       </c>
       <c r="B553" t="n">
-        <v>9.460809707641602</v>
+        <v>9.460808753967285</v>
       </c>
       <c r="C553" t="n">
-        <v>9.720353458912697</v>
+        <v>9.720352479075693</v>
       </c>
       <c r="D553" t="n">
-        <v>9.444064542477484</v>
+        <v>9.444063590491124</v>
       </c>
       <c r="E553" t="n">
-        <v>9.686863969754159</v>
+        <v>9.686862993292984</v>
       </c>
       <c r="F553" t="n">
         <v>130739</v>
@@ -11492,16 +11492,16 @@
         <v>45124</v>
       </c>
       <c r="B554" t="n">
-        <v>9.37708568572998</v>
+        <v>9.377084732055664</v>
       </c>
       <c r="C554" t="n">
-        <v>9.578023464455972</v>
+        <v>9.578022490345754</v>
       </c>
       <c r="D554" t="n">
-        <v>9.259872051570627</v>
+        <v>9.259871109817247</v>
       </c>
       <c r="E554" t="n">
-        <v>9.469181992402371</v>
+        <v>9.469181029361618</v>
       </c>
       <c r="F554" t="n">
         <v>232190</v>
@@ -11532,16 +11532,16 @@
         <v>45126</v>
       </c>
       <c r="B556" t="n">
-        <v>9.594767570495605</v>
+        <v>9.594766616821289</v>
       </c>
       <c r="C556" t="n">
-        <v>9.854312160399585</v>
+        <v>9.85431118092777</v>
       </c>
       <c r="D556" t="n">
-        <v>9.469181777086149</v>
+        <v>9.469180835894464</v>
       </c>
       <c r="E556" t="n">
-        <v>9.854312160399585</v>
+        <v>9.85431118092777</v>
       </c>
       <c r="F556" t="n">
         <v>152546</v>
@@ -11552,16 +11552,16 @@
         <v>45127</v>
       </c>
       <c r="B557" t="n">
-        <v>9.519415855407715</v>
+        <v>9.519417762756348</v>
       </c>
       <c r="C557" t="n">
-        <v>9.628256477236604</v>
+        <v>9.628258406392984</v>
       </c>
       <c r="D557" t="n">
-        <v>9.49429853001039</v>
+        <v>9.494300432326414</v>
       </c>
       <c r="E557" t="n">
-        <v>9.628256477236604</v>
+        <v>9.628258406392984</v>
       </c>
       <c r="F557" t="n">
         <v>109247</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711980587323517</v>
+        <v>9.711981520878043</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753843076590339</v>
+        <v>9.753844014168855</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11672,16 +11672,16 @@
         <v>45135</v>
       </c>
       <c r="B563" t="n">
-        <v>9.527789115905762</v>
+        <v>9.527788162231445</v>
       </c>
       <c r="C563" t="n">
-        <v>9.795705882433666</v>
+        <v>9.795704901942495</v>
       </c>
       <c r="D563" t="n">
-        <v>9.511043949986009</v>
+        <v>9.511042997987781</v>
       </c>
       <c r="E563" t="n">
-        <v>9.795705882433666</v>
+        <v>9.795704901942495</v>
       </c>
       <c r="F563" t="n">
         <v>123785</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728725433349609</v>
+        <v>9.728724479675293</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795705251545078</v>
+        <v>9.795704291304954</v>
       </c>
       <c r="D564" t="n">
-        <v>9.544532825943854</v>
+        <v>9.54453189032532</v>
       </c>
       <c r="E564" t="n">
-        <v>9.544532825943854</v>
+        <v>9.54453189032532</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11712,16 +11712,16 @@
         <v>45139</v>
       </c>
       <c r="B565" t="n">
-        <v>9.896174430847168</v>
+        <v>9.896173477172852</v>
       </c>
       <c r="C565" t="n">
-        <v>9.896174430847168</v>
+        <v>9.896173477172852</v>
       </c>
       <c r="D565" t="n">
-        <v>9.628257662250791</v>
+        <v>9.628256734395071</v>
       </c>
       <c r="E565" t="n">
-        <v>9.753844304694203</v>
+        <v>9.753843364735953</v>
       </c>
       <c r="F565" t="n">
         <v>228819</v>
@@ -11752,16 +11752,16 @@
         <v>45141</v>
       </c>
       <c r="B567" t="n">
-        <v>9.862683296203613</v>
+        <v>9.86268424987793</v>
       </c>
       <c r="C567" t="n">
-        <v>9.8794284594619</v>
+        <v>9.879429414755393</v>
       </c>
       <c r="D567" t="n">
-        <v>9.686862867254819</v>
+        <v>9.686863803928139</v>
       </c>
       <c r="E567" t="n">
-        <v>9.837566813070588</v>
+        <v>9.837567764316258</v>
       </c>
       <c r="F567" t="n">
         <v>144645</v>
@@ -11772,16 +11772,16 @@
         <v>45142</v>
       </c>
       <c r="B568" t="n">
-        <v>9.996641159057617</v>
+        <v>9.996642112731934</v>
       </c>
       <c r="C568" t="n">
-        <v>10.01338716335395</v>
+        <v>10.01338811862582</v>
       </c>
       <c r="D568" t="n">
-        <v>9.770586924449054</v>
+        <v>9.770587856557917</v>
       </c>
       <c r="E568" t="n">
-        <v>9.862683218722113</v>
+        <v>9.862684159616911</v>
       </c>
       <c r="F568" t="n">
         <v>196582</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294521258928</v>
+        <v>10.63294612667715</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109575560148</v>
+        <v>10.95109669703995</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527578824517</v>
+        <v>10.77527669072958</v>
       </c>
       <c r="E578" t="n">
-        <v>11.0934271862458</v>
+        <v>11.09342811537701</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -11992,16 +11992,16 @@
         <v>45159</v>
       </c>
       <c r="B579" t="n">
-        <v>11.16877937316895</v>
+        <v>11.16877841949463</v>
       </c>
       <c r="C579" t="n">
-        <v>11.43669614371307</v>
+        <v>11.436695167162</v>
       </c>
       <c r="D579" t="n">
-        <v>11.04319357098227</v>
+        <v>11.04319262803141</v>
       </c>
       <c r="E579" t="n">
-        <v>11.37808932386998</v>
+        <v>11.37808835232321</v>
       </c>
       <c r="F579" t="n">
         <v>524641</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716468811035</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716468811035</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10180045903246</v>
+        <v>11.10179954134582</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877944178756</v>
+        <v>11.16877851856436</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12032,16 +12032,16 @@
         <v>45161</v>
       </c>
       <c r="B581" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="C581" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="D581" t="n">
-        <v>11.3194807332412</v>
+        <v>11.31948165818213</v>
       </c>
       <c r="E581" t="n">
-        <v>11.47018384052361</v>
+        <v>11.47018477777884</v>
       </c>
       <c r="F581" t="n">
         <v>383262</v>
@@ -12052,16 +12052,16 @@
         <v>45162</v>
       </c>
       <c r="B582" t="n">
-        <v>11.75484561920166</v>
+        <v>11.75484657287598</v>
       </c>
       <c r="C582" t="n">
-        <v>11.75484561920166</v>
+        <v>11.75484657287598</v>
       </c>
       <c r="D582" t="n">
-        <v>11.51204537648651</v>
+        <v>11.51204631046236</v>
       </c>
       <c r="E582" t="n">
-        <v>11.62088683559435</v>
+        <v>11.62088777840055</v>
       </c>
       <c r="F582" t="n">
         <v>205326</v>
@@ -12072,16 +12072,16 @@
         <v>45163</v>
       </c>
       <c r="B583" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="C583" t="n">
-        <v>11.74647357151606</v>
+        <v>11.74647453134756</v>
       </c>
       <c r="D583" t="n">
-        <v>11.55390797594043</v>
+        <v>11.55390892003695</v>
       </c>
       <c r="E583" t="n">
-        <v>11.74647357151606</v>
+        <v>11.74647453134756</v>
       </c>
       <c r="F583" t="n">
         <v>173405</v>
@@ -12132,16 +12132,16 @@
         <v>45168</v>
       </c>
       <c r="B586" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="C586" t="n">
-        <v>12.57534186904209</v>
+        <v>12.57534090704158</v>
       </c>
       <c r="D586" t="n">
-        <v>12.30742510572441</v>
+        <v>12.30742416421925</v>
       </c>
       <c r="E586" t="n">
-        <v>12.51673505077979</v>
+        <v>12.51673409326264</v>
       </c>
       <c r="F586" t="n">
         <v>381576</v>
@@ -12172,16 +12172,16 @@
         <v>45170</v>
       </c>
       <c r="B588" t="n">
-        <v>12.12323188781738</v>
+        <v>12.1232328414917</v>
       </c>
       <c r="C588" t="n">
-        <v>12.26556284528164</v>
+        <v>12.26556381015243</v>
       </c>
       <c r="D588" t="n">
-        <v>12.10648756409787</v>
+        <v>12.10648851645499</v>
       </c>
       <c r="E588" t="n">
-        <v>12.15672137642609</v>
+        <v>12.15672233273486</v>
       </c>
       <c r="F588" t="n">
         <v>195423</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80508024202364</v>
+        <v>11.80507928016331</v>
       </c>
       <c r="D590" t="n">
-        <v>11.5957703116373</v>
+        <v>11.59576936683122</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996291579013</v>
+        <v>11.77996195597632</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12232,16 +12232,16 @@
         <v>45175</v>
       </c>
       <c r="B591" t="n">
-        <v>11.74647521972656</v>
+        <v>11.74647426605225</v>
       </c>
       <c r="C591" t="n">
-        <v>11.90555051052048</v>
+        <v>11.90554954393114</v>
       </c>
       <c r="D591" t="n">
-        <v>11.69624056319386</v>
+        <v>11.696239613598</v>
       </c>
       <c r="E591" t="n">
-        <v>11.69624056319386</v>
+        <v>11.696239613598</v>
       </c>
       <c r="F591" t="n">
         <v>295506</v>
@@ -12252,16 +12252,16 @@
         <v>45177</v>
       </c>
       <c r="B592" t="n">
-        <v>11.77159023284912</v>
+        <v>11.77159118652344</v>
       </c>
       <c r="C592" t="n">
-        <v>11.82182488309172</v>
+        <v>11.82182584083579</v>
       </c>
       <c r="D592" t="n">
-        <v>11.59576979816967</v>
+        <v>11.59577073759991</v>
       </c>
       <c r="E592" t="n">
-        <v>11.74647374889745</v>
+        <v>11.74647470053696</v>
       </c>
       <c r="F592" t="n">
         <v>200375</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393531799316</v>
+        <v>12.27393436431885</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393531799316</v>
+        <v>12.27393436431885</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298367423283</v>
+        <v>11.71298276414397</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135667690049</v>
+        <v>11.72135576616107</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12312,16 +12312,16 @@
         <v>45182</v>
       </c>
       <c r="B595" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="C595" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="D595" t="n">
-        <v>12.14834981665663</v>
+        <v>12.14834888732056</v>
       </c>
       <c r="E595" t="n">
-        <v>12.30742510572441</v>
+        <v>12.30742416421925</v>
       </c>
       <c r="F595" t="n">
         <v>353764</v>
@@ -12352,16 +12352,16 @@
         <v>45184</v>
       </c>
       <c r="B597" t="n">
-        <v>12.03950786590576</v>
+        <v>12.03950691223145</v>
       </c>
       <c r="C597" t="n">
-        <v>12.33254194561951</v>
+        <v>12.33254096873336</v>
       </c>
       <c r="D597" t="n">
-        <v>11.87206042119054</v>
+        <v>11.87205948078009</v>
       </c>
       <c r="E597" t="n">
-        <v>12.29068029473313</v>
+        <v>12.29067932116292</v>
       </c>
       <c r="F597" t="n">
         <v>162660</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C599" t="n">
-        <v>11.8636870561786</v>
+        <v>11.86368608954307</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414247332525</v>
+        <v>11.60414152783702</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786661371372</v>
+        <v>11.68786566140377</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12412,16 +12412,16 @@
         <v>45189</v>
       </c>
       <c r="B600" t="n">
-        <v>11.8385705947876</v>
+        <v>11.83856964111328</v>
       </c>
       <c r="C600" t="n">
-        <v>11.91392173246913</v>
+        <v>11.91392077272479</v>
       </c>
       <c r="D600" t="n">
-        <v>11.62926066398271</v>
+        <v>11.62925972716968</v>
       </c>
       <c r="E600" t="n">
-        <v>11.62926066398271</v>
+        <v>11.62925972716968</v>
       </c>
       <c r="F600" t="n">
         <v>141695</v>
@@ -12452,16 +12452,16 @@
         <v>45191</v>
       </c>
       <c r="B602" t="n">
-        <v>11.54553699493408</v>
+        <v>11.54553604125977</v>
       </c>
       <c r="C602" t="n">
-        <v>11.73810261019376</v>
+        <v>11.73810164061331</v>
       </c>
       <c r="D602" t="n">
-        <v>11.47855801622189</v>
+        <v>11.47855706808011</v>
       </c>
       <c r="E602" t="n">
-        <v>11.52879182967118</v>
+        <v>11.52879087738004</v>
       </c>
       <c r="F602" t="n">
         <v>228714</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27761930113372</v>
+        <v>11.27762027064262</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760626903017</v>
+        <v>10.91760720758964</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901248934153</v>
+        <v>11.21901345381215</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876636505127</v>
+        <v>10.80876445770264</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854563254228</v>
+        <v>11.11854367052903</v>
       </c>
       <c r="D608" t="n">
-        <v>10.71667005341063</v>
+        <v>10.7166681623136</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854563254228</v>
+        <v>11.11854367052903</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12652,16 +12652,16 @@
         <v>45205</v>
       </c>
       <c r="B612" t="n">
-        <v>10.4822416305542</v>
+        <v>10.48224258422852</v>
       </c>
       <c r="C612" t="n">
-        <v>10.59945525826802</v>
+        <v>10.59945622260643</v>
       </c>
       <c r="D612" t="n">
-        <v>10.23944221348118</v>
+        <v>10.23944314506561</v>
       </c>
       <c r="E612" t="n">
-        <v>10.53247544159608</v>
+        <v>10.53247639984067</v>
       </c>
       <c r="F612" t="n">
         <v>125682</v>
@@ -12672,16 +12672,16 @@
         <v>45208</v>
       </c>
       <c r="B613" t="n">
-        <v>10.189208984375</v>
+        <v>10.18920993804932</v>
       </c>
       <c r="C613" t="n">
-        <v>10.41526324989824</v>
+        <v>10.41526422473044</v>
       </c>
       <c r="D613" t="n">
-        <v>10.189208984375</v>
+        <v>10.18920993804932</v>
       </c>
       <c r="E613" t="n">
-        <v>10.39851808448147</v>
+        <v>10.39851905774639</v>
       </c>
       <c r="F613" t="n">
         <v>296138</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457153766474</v>
+        <v>10.62457244623281</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411611417709</v>
+        <v>10.88411704494031</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12752,16 +12752,16 @@
         <v>45215</v>
       </c>
       <c r="B617" t="n">
-        <v>11.02644729614258</v>
+        <v>11.02644824981689</v>
       </c>
       <c r="C617" t="n">
-        <v>11.27761971643121</v>
+        <v>11.27762069182936</v>
       </c>
       <c r="D617" t="n">
-        <v>10.95109615887475</v>
+        <v>10.95109710603197</v>
       </c>
       <c r="E617" t="n">
-        <v>11.1269166007259</v>
+        <v>11.12691756308977</v>
       </c>
       <c r="F617" t="n">
         <v>160026</v>
@@ -12772,16 +12772,16 @@
         <v>45216</v>
       </c>
       <c r="B618" t="n">
-        <v>10.57433795928955</v>
+        <v>10.57433700561523</v>
       </c>
       <c r="C618" t="n">
-        <v>11.02644730684428</v>
+        <v>11.0264463123953</v>
       </c>
       <c r="D618" t="n">
-        <v>10.41526268177113</v>
+        <v>10.41526174244343</v>
       </c>
       <c r="E618" t="n">
-        <v>11.02644730684428</v>
+        <v>11.0264463123953</v>
       </c>
       <c r="F618" t="n">
         <v>572365</v>
@@ -12832,16 +12832,16 @@
         <v>45219</v>
       </c>
       <c r="B621" t="n">
-        <v>10.87574481964111</v>
+        <v>10.8757438659668</v>
       </c>
       <c r="C621" t="n">
-        <v>11.00970361990219</v>
+        <v>11.00970265448127</v>
       </c>
       <c r="D621" t="n">
-        <v>10.27293316256027</v>
+        <v>10.27293226174542</v>
       </c>
       <c r="E621" t="n">
-        <v>10.34828346308703</v>
+        <v>10.34828255566484</v>
       </c>
       <c r="F621" t="n">
         <v>2108154</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295806884766</v>
+        <v>10.99295902252197</v>
       </c>
       <c r="C622" t="n">
-        <v>11.13528902626719</v>
+        <v>11.13528999228917</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039245794601</v>
+        <v>10.80039339491465</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82551062585675</v>
+        <v>10.82551156500447</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12932,16 +12932,16 @@
         <v>45226</v>
       </c>
       <c r="B626" t="n">
-        <v>10.98458576202393</v>
+        <v>10.98458480834961</v>
       </c>
       <c r="C626" t="n">
-        <v>11.53716357835591</v>
+        <v>11.53716257670716</v>
       </c>
       <c r="D626" t="n">
-        <v>10.96784059736098</v>
+        <v>10.96783964514047</v>
       </c>
       <c r="E626" t="n">
-        <v>11.33622580824897</v>
+        <v>11.33622482404551</v>
       </c>
       <c r="F626" t="n">
         <v>172878</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.43200588226318</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668076695393</v>
+        <v>11.07668177956321</v>
       </c>
       <c r="D627" t="n">
-        <v>10.43200588226318</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="E627" t="n">
-        <v>10.99295663578805</v>
+        <v>10.99295764074342</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -12992,16 +12992,16 @@
         <v>45231</v>
       </c>
       <c r="B629" t="n">
-        <v>10.78092384338379</v>
+        <v>10.78092288970947</v>
       </c>
       <c r="C629" t="n">
-        <v>10.78092384338379</v>
+        <v>10.78092288970947</v>
       </c>
       <c r="D629" t="n">
-        <v>10.45935752710632</v>
+        <v>10.45935660187757</v>
       </c>
       <c r="E629" t="n">
-        <v>10.54398033141075</v>
+        <v>10.54397939869632</v>
       </c>
       <c r="F629" t="n">
         <v>233349</v>
@@ -13072,16 +13072,16 @@
         <v>45238</v>
       </c>
       <c r="B633" t="n">
-        <v>11.40713214874268</v>
+        <v>11.40713119506836</v>
       </c>
       <c r="C633" t="n">
-        <v>11.40713214874268</v>
+        <v>11.40713119506836</v>
       </c>
       <c r="D633" t="n">
-        <v>11.01786790952223</v>
+        <v>11.0178669883917</v>
       </c>
       <c r="E633" t="n">
-        <v>11.22096248002823</v>
+        <v>11.22096154191832</v>
       </c>
       <c r="F633" t="n">
         <v>171088</v>
@@ -13192,16 +13192,16 @@
         <v>45247</v>
       </c>
       <c r="B639" t="n">
-        <v>12.85418033599854</v>
+        <v>12.85417938232422</v>
       </c>
       <c r="C639" t="n">
-        <v>12.85418033599854</v>
+        <v>12.85417938232422</v>
       </c>
       <c r="D639" t="n">
-        <v>12.4818392948031</v>
+        <v>12.48183836875342</v>
       </c>
       <c r="E639" t="n">
-        <v>12.70185876909171</v>
+        <v>12.7018578267184</v>
       </c>
       <c r="F639" t="n">
         <v>197425</v>
@@ -13252,16 +13252,16 @@
         <v>45252</v>
       </c>
       <c r="B642" t="n">
-        <v>12.397216796875</v>
+        <v>12.39721584320068</v>
       </c>
       <c r="C642" t="n">
-        <v>12.78648102270015</v>
+        <v>12.7864800390811</v>
       </c>
       <c r="D642" t="n">
-        <v>12.397216796875</v>
+        <v>12.39721584320068</v>
       </c>
       <c r="E642" t="n">
-        <v>12.5749235834792</v>
+        <v>12.57492261613453</v>
       </c>
       <c r="F642" t="n">
         <v>163818</v>
@@ -13292,16 +13292,16 @@
         <v>45254</v>
       </c>
       <c r="B644" t="n">
-        <v>12.65108394622803</v>
+        <v>12.65108489990234</v>
       </c>
       <c r="C644" t="n">
-        <v>12.67647172230335</v>
+        <v>12.67647267789147</v>
       </c>
       <c r="D644" t="n">
-        <v>12.48183834051455</v>
+        <v>12.48183928143066</v>
       </c>
       <c r="E644" t="n">
-        <v>12.48183834051455</v>
+        <v>12.48183928143066</v>
       </c>
       <c r="F644" t="n">
         <v>150966</v>
@@ -13332,16 +13332,16 @@
         <v>45258</v>
       </c>
       <c r="B646" t="n">
-        <v>13.21805763244629</v>
+        <v>13.21805667877197</v>
       </c>
       <c r="C646" t="n">
-        <v>13.37037749874314</v>
+        <v>13.37037653407904</v>
       </c>
       <c r="D646" t="n">
-        <v>12.99803815846524</v>
+        <v>12.99803722066519</v>
       </c>
       <c r="E646" t="n">
-        <v>13.20113188032672</v>
+        <v>13.20113092787359</v>
       </c>
       <c r="F646" t="n">
         <v>249995</v>
@@ -13352,16 +13352,16 @@
         <v>45259</v>
       </c>
       <c r="B647" t="n">
-        <v>12.93033790588379</v>
+        <v>12.93033885955811</v>
       </c>
       <c r="C647" t="n">
-        <v>13.23498015384819</v>
+        <v>13.23498112999133</v>
       </c>
       <c r="D647" t="n">
-        <v>12.90495183123531</v>
+        <v>12.90495278303728</v>
       </c>
       <c r="E647" t="n">
-        <v>13.20959237880287</v>
+        <v>13.20959335307354</v>
       </c>
       <c r="F647" t="n">
         <v>170772</v>
@@ -13372,16 +13372,16 @@
         <v>45260</v>
       </c>
       <c r="B648" t="n">
-        <v>13.37037658691406</v>
+        <v>13.37037754058838</v>
       </c>
       <c r="C648" t="n">
-        <v>13.37037658691406</v>
+        <v>13.37037754058838</v>
       </c>
       <c r="D648" t="n">
-        <v>12.70185788509813</v>
+        <v>12.70185879108874</v>
       </c>
       <c r="E648" t="n">
-        <v>13.09112210075015</v>
+        <v>13.09112303450597</v>
       </c>
       <c r="F648" t="n">
         <v>345125</v>
@@ -13452,16 +13452,16 @@
         <v>45266</v>
       </c>
       <c r="B652" t="n">
-        <v>11.97410297393799</v>
+        <v>11.9741039276123</v>
       </c>
       <c r="C652" t="n">
-        <v>12.82879130950201</v>
+        <v>12.82879233124775</v>
       </c>
       <c r="D652" t="n">
-        <v>11.97410297393799</v>
+        <v>11.9741039276123</v>
       </c>
       <c r="E652" t="n">
-        <v>12.82879130950201</v>
+        <v>12.82879233124775</v>
       </c>
       <c r="F652" t="n">
         <v>140431</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413217772953</v>
+        <v>12.30413126845579</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568877039725</v>
+        <v>12.51568784548951</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13512,16 +13512,16 @@
         <v>45271</v>
       </c>
       <c r="B655" t="n">
-        <v>12.7357063293457</v>
+        <v>12.73570728302002</v>
       </c>
       <c r="C655" t="n">
-        <v>13.05727262952386</v>
+        <v>13.05727360727768</v>
       </c>
       <c r="D655" t="n">
-        <v>12.57492275415741</v>
+        <v>12.57492369579195</v>
       </c>
       <c r="E655" t="n">
-        <v>12.82032912941347</v>
+        <v>12.82033008942451</v>
       </c>
       <c r="F655" t="n">
         <v>302669</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109316972536</v>
+        <v>12.76109408341076</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033791853966</v>
+        <v>12.93033884434287</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13552,16 +13552,16 @@
         <v>45273</v>
       </c>
       <c r="B657" t="n">
-        <v>13.27729320526123</v>
+        <v>13.27729225158691</v>
       </c>
       <c r="C657" t="n">
-        <v>13.2942172576741</v>
+        <v>13.29421630278417</v>
       </c>
       <c r="D657" t="n">
-        <v>12.92187790220829</v>
+        <v>12.92187697406255</v>
       </c>
       <c r="E657" t="n">
-        <v>13.2349822240305</v>
+        <v>13.23498127339527</v>
       </c>
       <c r="F657" t="n">
         <v>131160</v>
@@ -13612,16 +13612,16 @@
         <v>45278</v>
       </c>
       <c r="B660" t="n">
-        <v>13.1672830581665</v>
+        <v>13.16728210449219</v>
       </c>
       <c r="C660" t="n">
-        <v>13.66655704234154</v>
+        <v>13.66655605250602</v>
       </c>
       <c r="D660" t="n">
-        <v>13.15882103222074</v>
+        <v>13.15882007915931</v>
       </c>
       <c r="E660" t="n">
-        <v>13.26883077030978</v>
+        <v>13.26882980928061</v>
       </c>
       <c r="F660" t="n">
         <v>541076</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45499897003174</v>
+        <v>13.45499992370605</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040449719429</v>
+        <v>13.70040546826266</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806519394055</v>
+        <v>13.32806613861795</v>
       </c>
       <c r="E662" t="n">
-        <v>13.38730021927779</v>
+        <v>13.3873011681537</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13692,16 +13692,16 @@
         <v>45282</v>
       </c>
       <c r="B664" t="n">
-        <v>13.88704776763916</v>
+        <v>13.88704872131348</v>
       </c>
       <c r="C664" t="n">
-        <v>14.31516532026503</v>
+        <v>14.31516630333975</v>
       </c>
       <c r="D664" t="n">
-        <v>13.74434251416193</v>
+        <v>13.74434345803615</v>
       </c>
       <c r="E664" t="n">
-        <v>13.89596662195722</v>
+        <v>13.89596757624402</v>
       </c>
       <c r="F664" t="n">
         <v>242936</v>
@@ -13792,16 +13792,16 @@
         <v>45294</v>
       </c>
       <c r="B669" t="n">
-        <v>14.23489284515381</v>
+        <v>14.23489379882812</v>
       </c>
       <c r="C669" t="n">
-        <v>14.35976038913565</v>
+        <v>14.35976135117554</v>
       </c>
       <c r="D669" t="n">
-        <v>13.64623233446546</v>
+        <v>13.64623324870215</v>
       </c>
       <c r="E669" t="n">
-        <v>13.92272308910211</v>
+        <v>13.92272402186245</v>
       </c>
       <c r="F669" t="n">
         <v>120520</v>
@@ -13852,16 +13852,16 @@
         <v>45299</v>
       </c>
       <c r="B672" t="n">
-        <v>13.79785633087158</v>
+        <v>13.7978572845459</v>
       </c>
       <c r="C672" t="n">
-        <v>13.97623879116109</v>
+        <v>13.97623975716477</v>
       </c>
       <c r="D672" t="n">
-        <v>13.66406993370299</v>
+        <v>13.66407087813031</v>
       </c>
       <c r="E672" t="n">
-        <v>13.96731904087866</v>
+        <v>13.96732000626583</v>
       </c>
       <c r="F672" t="n">
         <v>138218</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623920440674</v>
+        <v>13.97623825073242</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461330219005</v>
+        <v>13.82461235886199</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13912,16 +13912,16 @@
         <v>45302</v>
       </c>
       <c r="B675" t="n">
-        <v>14.2081356048584</v>
+        <v>14.20813465118408</v>
       </c>
       <c r="C675" t="n">
-        <v>14.2081356048584</v>
+        <v>14.20813465118408</v>
       </c>
       <c r="D675" t="n">
-        <v>13.64623340505142</v>
+        <v>13.64623248909294</v>
       </c>
       <c r="E675" t="n">
-        <v>14.13678386911013</v>
+        <v>14.13678292022506</v>
       </c>
       <c r="F675" t="n">
         <v>191209</v>
@@ -13992,16 +13992,16 @@
         <v>45308</v>
       </c>
       <c r="B679" t="n">
-        <v>14.37759876251221</v>
+        <v>14.37759780883789</v>
       </c>
       <c r="C679" t="n">
-        <v>14.52922377237277</v>
+        <v>14.52922280864108</v>
       </c>
       <c r="D679" t="n">
-        <v>14.243812358087</v>
+        <v>14.24381141328681</v>
       </c>
       <c r="E679" t="n">
-        <v>14.3240847384004</v>
+        <v>14.3240837882757</v>
       </c>
       <c r="F679" t="n">
         <v>153283</v>
@@ -14012,16 +14012,16 @@
         <v>45309</v>
       </c>
       <c r="B680" t="n">
-        <v>14.44895267486572</v>
+        <v>14.44895172119141</v>
       </c>
       <c r="C680" t="n">
-        <v>14.53814301613819</v>
+        <v>14.53814205657704</v>
       </c>
       <c r="D680" t="n">
-        <v>14.17246010784907</v>
+        <v>14.17245917242409</v>
       </c>
       <c r="E680" t="n">
-        <v>14.53814301613819</v>
+        <v>14.53814205657704</v>
       </c>
       <c r="F680" t="n">
         <v>117781</v>
@@ -14052,16 +14052,16 @@
         <v>45313</v>
       </c>
       <c r="B682" t="n">
-        <v>14.52922344207764</v>
+        <v>14.52922439575195</v>
       </c>
       <c r="C682" t="n">
-        <v>14.79679714094238</v>
+        <v>14.7967981121798</v>
       </c>
       <c r="D682" t="n">
-        <v>14.27948834824271</v>
+        <v>14.27948928552483</v>
       </c>
       <c r="E682" t="n">
-        <v>14.60949582056619</v>
+        <v>14.60949677950945</v>
       </c>
       <c r="F682" t="n">
         <v>189524</v>
@@ -14092,16 +14092,16 @@
         <v>45315</v>
       </c>
       <c r="B684" t="n">
-        <v>14.44895267486572</v>
+        <v>14.44895172119141</v>
       </c>
       <c r="C684" t="n">
-        <v>14.60949654369217</v>
+        <v>14.60949557942147</v>
       </c>
       <c r="D684" t="n">
-        <v>14.41327635913731</v>
+        <v>14.41327540781774</v>
       </c>
       <c r="E684" t="n">
-        <v>14.50246670040977</v>
+        <v>14.50246574320337</v>
       </c>
       <c r="F684" t="n">
         <v>132319</v>
@@ -14112,16 +14112,16 @@
         <v>45316</v>
       </c>
       <c r="B685" t="n">
-        <v>14.57381916046143</v>
+        <v>14.57381820678711</v>
       </c>
       <c r="C685" t="n">
-        <v>14.77003934270851</v>
+        <v>14.77003837619403</v>
       </c>
       <c r="D685" t="n">
-        <v>14.46679021453496</v>
+        <v>14.46678926786436</v>
       </c>
       <c r="E685" t="n">
-        <v>14.60949637186738</v>
+        <v>14.60949541585844</v>
       </c>
       <c r="F685" t="n">
         <v>152967</v>
@@ -14172,16 +14172,16 @@
         <v>45321</v>
       </c>
       <c r="B688" t="n">
-        <v>13.27162933349609</v>
+        <v>13.27163028717041</v>
       </c>
       <c r="C688" t="n">
-        <v>13.78893720355285</v>
+        <v>13.78893819439994</v>
       </c>
       <c r="D688" t="n">
-        <v>13.23595212526723</v>
+        <v>13.23595307637785</v>
       </c>
       <c r="E688" t="n">
-        <v>13.78893720355285</v>
+        <v>13.78893819439994</v>
       </c>
       <c r="F688" t="n">
         <v>335223</v>
@@ -14212,16 +14212,16 @@
         <v>45323</v>
       </c>
       <c r="B690" t="n">
-        <v>13.70866584777832</v>
+        <v>13.708664894104</v>
       </c>
       <c r="C690" t="n">
-        <v>13.70866584777832</v>
+        <v>13.708664894104</v>
       </c>
       <c r="D690" t="n">
-        <v>13.05757063872765</v>
+        <v>13.05756973034824</v>
       </c>
       <c r="E690" t="n">
-        <v>13.48568820831384</v>
+        <v>13.48568727015147</v>
       </c>
       <c r="F690" t="n">
         <v>1088052</v>
@@ -14252,16 +14252,16 @@
         <v>45327</v>
       </c>
       <c r="B692" t="n">
-        <v>13.21811580657959</v>
+        <v>13.21811485290527</v>
       </c>
       <c r="C692" t="n">
-        <v>13.76218119194509</v>
+        <v>13.76218019901698</v>
       </c>
       <c r="D692" t="n">
-        <v>13.21811580657959</v>
+        <v>13.21811485290527</v>
       </c>
       <c r="E692" t="n">
-        <v>13.76218119194509</v>
+        <v>13.76218019901698</v>
       </c>
       <c r="F692" t="n">
         <v>142538</v>
@@ -14332,16 +14332,16 @@
         <v>45331</v>
       </c>
       <c r="B696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.8692102432251</v>
       </c>
       <c r="C696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.8692102432251</v>
       </c>
       <c r="D696" t="n">
-        <v>13.49460665160678</v>
+        <v>13.49460757952268</v>
       </c>
       <c r="E696" t="n">
-        <v>13.74434263966654</v>
+        <v>13.74434358475478</v>
       </c>
       <c r="F696" t="n">
         <v>146541</v>
@@ -14352,16 +14352,16 @@
         <v>45336</v>
       </c>
       <c r="B697" t="n">
-        <v>13.53920078277588</v>
+        <v>13.5392017364502</v>
       </c>
       <c r="C697" t="n">
-        <v>13.86920822735105</v>
+        <v>13.86920920427044</v>
       </c>
       <c r="D697" t="n">
-        <v>13.43217184988765</v>
+        <v>13.43217279602306</v>
       </c>
       <c r="E697" t="n">
-        <v>13.86920822735105</v>
+        <v>13.86920920427044</v>
       </c>
       <c r="F697" t="n">
         <v>116200</v>
@@ -14392,16 +14392,16 @@
         <v>45338</v>
       </c>
       <c r="B699" t="n">
-        <v>13.88704776763916</v>
+        <v>13.88704872131348</v>
       </c>
       <c r="C699" t="n">
-        <v>14.12786400300335</v>
+        <v>14.1278649732154</v>
       </c>
       <c r="D699" t="n">
-        <v>13.29838635680286</v>
+        <v>13.29838727005164</v>
       </c>
       <c r="E699" t="n">
-        <v>13.51244513311579</v>
+        <v>13.51244606106478</v>
       </c>
       <c r="F699" t="n">
         <v>253260</v>
@@ -14432,16 +14432,16 @@
         <v>45342</v>
       </c>
       <c r="B701" t="n">
-        <v>13.91380405426025</v>
+        <v>13.91380500793457</v>
       </c>
       <c r="C701" t="n">
-        <v>14.19921545164344</v>
+        <v>14.1992164248803</v>
       </c>
       <c r="D701" t="n">
-        <v>13.55704092765261</v>
+        <v>13.55704185687382</v>
       </c>
       <c r="E701" t="n">
-        <v>13.56595978179354</v>
+        <v>13.56596071162605</v>
       </c>
       <c r="F701" t="n">
         <v>381787</v>
@@ -14452,16 +14452,16 @@
         <v>45343</v>
       </c>
       <c r="B702" t="n">
-        <v>13.75326061248779</v>
+        <v>13.75326156616211</v>
       </c>
       <c r="C702" t="n">
-        <v>14.09218601891464</v>
+        <v>14.09218699609062</v>
       </c>
       <c r="D702" t="n">
-        <v>13.52136324418864</v>
+        <v>13.5213641817828</v>
       </c>
       <c r="E702" t="n">
-        <v>13.85137069288472</v>
+        <v>13.85137165336216</v>
       </c>
       <c r="F702" t="n">
         <v>146120</v>
@@ -14472,16 +14472,16 @@
         <v>45344</v>
       </c>
       <c r="B703" t="n">
-        <v>13.71758556365967</v>
+        <v>13.71758460998535</v>
       </c>
       <c r="C703" t="n">
-        <v>13.83353516215277</v>
+        <v>13.8335342004174</v>
       </c>
       <c r="D703" t="n">
-        <v>13.37866010389759</v>
+        <v>13.37865917378605</v>
       </c>
       <c r="E703" t="n">
-        <v>13.77110048724197</v>
+        <v>13.77109952984718</v>
       </c>
       <c r="F703" t="n">
         <v>122205</v>
@@ -14512,16 +14512,16 @@
         <v>45348</v>
       </c>
       <c r="B705" t="n">
-        <v>13.53920078277588</v>
+        <v>13.5392017364502</v>
       </c>
       <c r="C705" t="n">
-        <v>13.73542094111948</v>
+        <v>13.73542190861516</v>
       </c>
       <c r="D705" t="n">
-        <v>13.30730431346953</v>
+        <v>13.30730525080952</v>
       </c>
       <c r="E705" t="n">
-        <v>13.52136307534302</v>
+        <v>13.52136402776089</v>
       </c>
       <c r="F705" t="n">
         <v>310571</v>
@@ -14532,16 +14532,16 @@
         <v>45349</v>
       </c>
       <c r="B706" t="n">
-        <v>13.64623260498047</v>
+        <v>13.64623355865479</v>
       </c>
       <c r="C706" t="n">
-        <v>13.91380451066463</v>
+        <v>13.91380548303835</v>
       </c>
       <c r="D706" t="n">
-        <v>13.56596022678783</v>
+        <v>13.56596117485227</v>
       </c>
       <c r="E706" t="n">
-        <v>13.6283931039193</v>
+        <v>13.6283940563469</v>
       </c>
       <c r="F706" t="n">
         <v>240197</v>
@@ -14572,16 +14572,16 @@
         <v>45351</v>
       </c>
       <c r="B708" t="n">
-        <v>13.64623260498047</v>
+        <v>13.64623355865479</v>
       </c>
       <c r="C708" t="n">
-        <v>13.73542204541239</v>
+        <v>13.73542300531976</v>
       </c>
       <c r="D708" t="n">
-        <v>13.46785013972823</v>
+        <v>13.46785108093619</v>
       </c>
       <c r="E708" t="n">
-        <v>13.46785013972823</v>
+        <v>13.46785108093619</v>
       </c>
       <c r="F708" t="n">
         <v>71953</v>
@@ -14612,16 +14612,16 @@
         <v>45355</v>
       </c>
       <c r="B710" t="n">
-        <v>13.57487869262695</v>
+        <v>13.57487964630127</v>
       </c>
       <c r="C710" t="n">
-        <v>13.58379754680512</v>
+        <v>13.58379850110602</v>
       </c>
       <c r="D710" t="n">
-        <v>13.25379008514498</v>
+        <v>13.2537910162619</v>
       </c>
       <c r="E710" t="n">
-        <v>13.4143348369345</v>
+        <v>13.41433577933015</v>
       </c>
       <c r="F710" t="n">
         <v>828997</v>
@@ -14632,16 +14632,16 @@
         <v>45356</v>
       </c>
       <c r="B711" t="n">
-        <v>13.57487869262695</v>
+        <v>13.57487964630127</v>
       </c>
       <c r="C711" t="n">
-        <v>13.62839271379305</v>
+        <v>13.62839367122688</v>
       </c>
       <c r="D711" t="n">
-        <v>13.33406246103974</v>
+        <v>13.33406339779602</v>
       </c>
       <c r="E711" t="n">
-        <v>13.62839271379305</v>
+        <v>13.62839367122688</v>
       </c>
       <c r="F711" t="n">
         <v>182781</v>
@@ -14712,16 +14712,16 @@
         <v>45362</v>
       </c>
       <c r="B715" t="n">
-        <v>13.73542213439941</v>
+        <v>13.7354211807251</v>
       </c>
       <c r="C715" t="n">
-        <v>13.86920943225391</v>
+        <v>13.8692084692905</v>
       </c>
       <c r="D715" t="n">
-        <v>13.25379055041456</v>
+        <v>13.25378963018077</v>
       </c>
       <c r="E715" t="n">
-        <v>13.42325416233122</v>
+        <v>13.42325323033127</v>
       </c>
       <c r="F715" t="n">
         <v>388635</v>
@@ -14752,16 +14752,16 @@
         <v>45364</v>
       </c>
       <c r="B717" t="n">
-        <v>15.79573535919189</v>
+        <v>15.79573631286621</v>
       </c>
       <c r="C717" t="n">
-        <v>15.99195551836995</v>
+        <v>15.99195648389114</v>
       </c>
       <c r="D717" t="n">
-        <v>15.33194241860686</v>
+        <v>15.33194334427948</v>
       </c>
       <c r="E717" t="n">
-        <v>15.33194241860686</v>
+        <v>15.33194334427948</v>
       </c>
       <c r="F717" t="n">
         <v>474916</v>
@@ -14772,16 +14772,16 @@
         <v>45365</v>
       </c>
       <c r="B718" t="n">
-        <v>15.78681659698486</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="C718" t="n">
-        <v>15.99195651884814</v>
+        <v>15.99195748491486</v>
       </c>
       <c r="D718" t="n">
-        <v>15.58167667512159</v>
+        <v>15.5816776164035</v>
       </c>
       <c r="E718" t="n">
-        <v>15.78681659698486</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="F718" t="n">
         <v>580477</v>
@@ -14812,16 +14812,16 @@
         <v>45369</v>
       </c>
       <c r="B720" t="n">
-        <v>15.82249546051025</v>
+        <v>15.82249355316162</v>
       </c>
       <c r="C720" t="n">
-        <v>16.02763540381883</v>
+        <v>16.02763347174127</v>
       </c>
       <c r="D720" t="n">
-        <v>15.63519501988546</v>
+        <v>15.63519313511526</v>
       </c>
       <c r="E720" t="n">
-        <v>15.87601038417287</v>
+        <v>15.8760084703732</v>
       </c>
       <c r="F720" t="n">
         <v>188049</v>
@@ -14852,16 +14852,16 @@
         <v>45371</v>
       </c>
       <c r="B722" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="C722" t="n">
-        <v>16.29520886762698</v>
+        <v>16.2952069476677</v>
       </c>
       <c r="D722" t="n">
-        <v>16.08114916459959</v>
+        <v>16.08114726986159</v>
       </c>
       <c r="E722" t="n">
-        <v>16.15250359373834</v>
+        <v>16.15250169059311</v>
       </c>
       <c r="F722" t="n">
         <v>449422</v>
@@ -14892,16 +14892,16 @@
         <v>45373</v>
       </c>
       <c r="B724" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="C724" t="n">
-        <v>16.65197205234856</v>
+        <v>16.65197009035419</v>
       </c>
       <c r="D724" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="E724" t="n">
-        <v>16.42007643032814</v>
+        <v>16.42007449565653</v>
       </c>
       <c r="F724" t="n">
         <v>404437</v>
@@ -14992,16 +14992,16 @@
         <v>45383</v>
       </c>
       <c r="B729" t="n">
-        <v>16.41115570068359</v>
+        <v>16.41115379333496</v>
       </c>
       <c r="C729" t="n">
-        <v>16.52710350478439</v>
+        <v>16.52710158395999</v>
       </c>
       <c r="D729" t="n">
-        <v>16.06331049618689</v>
+        <v>16.06330862926576</v>
       </c>
       <c r="E729" t="n">
-        <v>16.25061272517437</v>
+        <v>16.25061083648447</v>
       </c>
       <c r="F729" t="n">
         <v>424348</v>
@@ -15072,16 +15072,16 @@
         <v>45387</v>
       </c>
       <c r="B733" t="n">
-        <v>15.78681659698486</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="C733" t="n">
-        <v>16.24169160837016</v>
+        <v>16.24169258952326</v>
       </c>
       <c r="D733" t="n">
-        <v>15.71546397029202</v>
+        <v>15.71546491965596</v>
       </c>
       <c r="E733" t="n">
-        <v>15.84033151505304</v>
+        <v>15.84033247196016</v>
       </c>
       <c r="F733" t="n">
         <v>540022</v>
@@ -15192,16 +15192,16 @@
         <v>45397</v>
       </c>
       <c r="B739" t="n">
-        <v>14.85654163360596</v>
+        <v>14.85654258728027</v>
       </c>
       <c r="C739" t="n">
-        <v>14.99990999176365</v>
+        <v>14.9999109546411</v>
       </c>
       <c r="D739" t="n">
-        <v>14.70421230501488</v>
+        <v>14.70421324891084</v>
       </c>
       <c r="E739" t="n">
-        <v>14.96406790222423</v>
+        <v>14.96406886280089</v>
       </c>
       <c r="F739" t="n">
         <v>465171</v>
@@ -15212,16 +15212,16 @@
         <v>45398</v>
       </c>
       <c r="B740" t="n">
-        <v>14.85654163360596</v>
+        <v>14.85654258728027</v>
       </c>
       <c r="C740" t="n">
-        <v>15.09847528994855</v>
+        <v>15.09847625915312</v>
       </c>
       <c r="D740" t="n">
-        <v>14.61460708116632</v>
+        <v>14.61460801931033</v>
       </c>
       <c r="E740" t="n">
-        <v>14.79381842496049</v>
+        <v>14.79381937460846</v>
       </c>
       <c r="F740" t="n">
         <v>232795</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051544189453</v>
+        <v>15.77051448822021</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804172020233</v>
+        <v>15.87804076002569</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847665051934</v>
+        <v>15.09847573748455</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808098634539</v>
+        <v>15.18808006789204</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15312,16 +15312,16 @@
         <v>45405</v>
       </c>
       <c r="B745" t="n">
-        <v>16.22750091552734</v>
+        <v>16.22750282287598</v>
       </c>
       <c r="C745" t="n">
-        <v>16.44255346205622</v>
+        <v>16.44255539468171</v>
       </c>
       <c r="D745" t="n">
-        <v>15.59130424676128</v>
+        <v>15.59130607933261</v>
       </c>
       <c r="E745" t="n">
-        <v>15.77051470220201</v>
+        <v>15.77051655583738</v>
       </c>
       <c r="F745" t="n">
         <v>640292</v>
@@ -15332,16 +15332,16 @@
         <v>45406</v>
       </c>
       <c r="B746" t="n">
-        <v>16.63072395324707</v>
+        <v>16.6307258605957</v>
       </c>
       <c r="C746" t="n">
-        <v>16.83681551736777</v>
+        <v>16.83681744835269</v>
       </c>
       <c r="D746" t="n">
-        <v>16.21854082500566</v>
+        <v>16.21854268508173</v>
       </c>
       <c r="E746" t="n">
-        <v>16.21854082500566</v>
+        <v>16.21854268508173</v>
       </c>
       <c r="F746" t="n">
         <v>883364</v>
@@ -15392,16 +15392,16 @@
         <v>45411</v>
       </c>
       <c r="B749" t="n">
-        <v>16.50527763366699</v>
+        <v>16.50527954101562</v>
       </c>
       <c r="C749" t="n">
-        <v>16.50527763366699</v>
+        <v>16.50527954101562</v>
       </c>
       <c r="D749" t="n">
-        <v>16.23646106795836</v>
+        <v>16.23646294424257</v>
       </c>
       <c r="E749" t="n">
-        <v>16.40671054399719</v>
+        <v>16.40671243995541</v>
       </c>
       <c r="F749" t="n">
         <v>222938</v>
@@ -15432,16 +15432,16 @@
         <v>45414</v>
       </c>
       <c r="B751" t="n">
-        <v>16.18269920349121</v>
+        <v>16.18270111083984</v>
       </c>
       <c r="C751" t="n">
-        <v>16.48735607331619</v>
+        <v>16.48735801657273</v>
       </c>
       <c r="D751" t="n">
-        <v>15.94972472168906</v>
+        <v>15.94972660157852</v>
       </c>
       <c r="E751" t="n">
-        <v>16.20958032302404</v>
+        <v>16.20958223354097</v>
       </c>
       <c r="F751" t="n">
         <v>484781</v>
@@ -15512,16 +15512,16 @@
         <v>45420</v>
       </c>
       <c r="B755" t="n">
-        <v>16.97122383117676</v>
+        <v>16.97122573852539</v>
       </c>
       <c r="C755" t="n">
-        <v>16.97122383117676</v>
+        <v>16.97122573852539</v>
       </c>
       <c r="D755" t="n">
-        <v>16.45151266999193</v>
+        <v>16.45151451893167</v>
       </c>
       <c r="E755" t="n">
-        <v>16.57696087145495</v>
+        <v>16.57696273449346</v>
       </c>
       <c r="F755" t="n">
         <v>667766</v>
@@ -15532,16 +15532,16 @@
         <v>45421</v>
       </c>
       <c r="B756" t="n">
-        <v>16.84577751159668</v>
+        <v>16.84577941894531</v>
       </c>
       <c r="C756" t="n">
-        <v>16.96226475621242</v>
+        <v>16.96226667675022</v>
       </c>
       <c r="D756" t="n">
-        <v>16.34398823407645</v>
+        <v>16.34399008461042</v>
       </c>
       <c r="E756" t="n">
-        <v>16.89058057370953</v>
+        <v>16.89058248613095</v>
       </c>
       <c r="F756" t="n">
         <v>727748</v>
@@ -15552,16 +15552,16 @@
         <v>45422</v>
       </c>
       <c r="B757" t="n">
-        <v>16.1020565032959</v>
+        <v>16.10205459594727</v>
       </c>
       <c r="C757" t="n">
-        <v>16.83681856624717</v>
+        <v>16.83681657186323</v>
       </c>
       <c r="D757" t="n">
-        <v>16.0751735874776</v>
+        <v>16.07517168331335</v>
       </c>
       <c r="E757" t="n">
-        <v>16.82785938650213</v>
+        <v>16.82785739317944</v>
       </c>
       <c r="F757" t="n">
         <v>188543</v>
@@ -15632,16 +15632,16 @@
         <v>45428</v>
       </c>
       <c r="B761" t="n">
-        <v>15.8153190612793</v>
+        <v>15.81531715393066</v>
       </c>
       <c r="C761" t="n">
-        <v>16.1289369359749</v>
+        <v>16.12893499080353</v>
       </c>
       <c r="D761" t="n">
-        <v>15.63610859113976</v>
+        <v>15.63610670540415</v>
       </c>
       <c r="E761" t="n">
-        <v>15.80635808972374</v>
+        <v>15.80635618345582</v>
       </c>
       <c r="F761" t="n">
         <v>286904</v>
@@ -15652,16 +15652,16 @@
         <v>45429</v>
       </c>
       <c r="B762" t="n">
-        <v>15.41209316253662</v>
+        <v>15.41209411621094</v>
       </c>
       <c r="C762" t="n">
-        <v>15.87804032767277</v>
+        <v>15.87804131017911</v>
       </c>
       <c r="D762" t="n">
-        <v>15.27768577448818</v>
+        <v>15.27768671984559</v>
       </c>
       <c r="E762" t="n">
-        <v>15.83323726759193</v>
+        <v>15.83323824732593</v>
       </c>
       <c r="F762" t="n">
         <v>361357</v>
@@ -15752,16 +15752,16 @@
         <v>45436</v>
       </c>
       <c r="B767" t="n">
-        <v>14.81173896789551</v>
+        <v>14.81173992156982</v>
       </c>
       <c r="C767" t="n">
-        <v>14.9013441941292</v>
+        <v>14.90134515357287</v>
       </c>
       <c r="D767" t="n">
-        <v>14.74005478690855</v>
+        <v>14.74005573596738</v>
       </c>
       <c r="E767" t="n">
-        <v>14.78485695197687</v>
+        <v>14.78485790392035</v>
       </c>
       <c r="F767" t="n">
         <v>297600</v>
@@ -15812,16 +15812,16 @@
         <v>45441</v>
       </c>
       <c r="B770" t="n">
-        <v>14.77589797973633</v>
+        <v>14.77589702606201</v>
       </c>
       <c r="C770" t="n">
-        <v>14.84758216607118</v>
+        <v>14.84758120777018</v>
       </c>
       <c r="D770" t="n">
-        <v>14.52500422366149</v>
+        <v>14.5250032861805</v>
       </c>
       <c r="E770" t="n">
-        <v>14.84758216607118</v>
+        <v>14.84758120777018</v>
       </c>
       <c r="F770" t="n">
         <v>377820</v>
@@ -15832,16 +15832,16 @@
         <v>45443</v>
       </c>
       <c r="B771" t="n">
-        <v>14.63252830505371</v>
+        <v>14.63252925872803</v>
       </c>
       <c r="C771" t="n">
-        <v>14.81173875494456</v>
+        <v>14.8117397202989</v>
       </c>
       <c r="D771" t="n">
-        <v>14.51604196067319</v>
+        <v>14.51604290675551</v>
       </c>
       <c r="E771" t="n">
-        <v>14.81173875494456</v>
+        <v>14.8117397202989</v>
       </c>
       <c r="F771" t="n">
         <v>293511</v>
@@ -15912,16 +15912,16 @@
         <v>45449</v>
       </c>
       <c r="B775" t="n">
-        <v>13.9784107208252</v>
+        <v>13.97841167449951</v>
       </c>
       <c r="C775" t="n">
-        <v>14.10385803673439</v>
+        <v>14.10385899896733</v>
       </c>
       <c r="D775" t="n">
-        <v>13.79920026952634</v>
+        <v>13.79920121097406</v>
       </c>
       <c r="E775" t="n">
-        <v>13.9784107208252</v>
+        <v>13.97841167449951</v>
       </c>
       <c r="F775" t="n">
         <v>568356</v>
@@ -15952,16 +15952,16 @@
         <v>45453</v>
       </c>
       <c r="B777" t="n">
-        <v>13.27949142456055</v>
+        <v>13.27949047088623</v>
       </c>
       <c r="C777" t="n">
-        <v>13.53038698013227</v>
+        <v>13.53038600843974</v>
       </c>
       <c r="D777" t="n">
-        <v>13.27949142456055</v>
+        <v>13.27949047088623</v>
       </c>
       <c r="E777" t="n">
-        <v>13.43182077300439</v>
+        <v>13.43181980839046</v>
       </c>
       <c r="F777" t="n">
         <v>375304</v>
@@ -15972,16 +15972,16 @@
         <v>45454</v>
       </c>
       <c r="B778" t="n">
-        <v>13.42285823822021</v>
+        <v>13.42285919189453</v>
       </c>
       <c r="C778" t="n">
-        <v>13.42285823822021</v>
+        <v>13.42285919189453</v>
       </c>
       <c r="D778" t="n">
-        <v>13.23468771357661</v>
+        <v>13.23468865388169</v>
       </c>
       <c r="E778" t="n">
-        <v>13.378056073723</v>
+        <v>13.37805702421418</v>
       </c>
       <c r="F778" t="n">
         <v>377820</v>
@@ -15992,16 +15992,16 @@
         <v>45455</v>
       </c>
       <c r="B779" t="n">
-        <v>13.15404319763184</v>
+        <v>13.15404415130615</v>
       </c>
       <c r="C779" t="n">
-        <v>13.61999039058967</v>
+        <v>13.61999137804538</v>
       </c>
       <c r="D779" t="n">
-        <v>13.02859677254798</v>
+        <v>13.02859771712737</v>
       </c>
       <c r="E779" t="n">
-        <v>13.42285888587674</v>
+        <v>13.42285985904032</v>
       </c>
       <c r="F779" t="n">
         <v>631798</v>
@@ -16012,16 +16012,16 @@
         <v>45456</v>
       </c>
       <c r="B780" t="n">
-        <v>13.01067447662354</v>
+        <v>13.01067543029785</v>
       </c>
       <c r="C780" t="n">
-        <v>13.26157000825715</v>
+        <v>13.26157098032195</v>
       </c>
       <c r="D780" t="n">
-        <v>13.01067447662354</v>
+        <v>13.01067543029785</v>
       </c>
       <c r="E780" t="n">
-        <v>13.15404283978727</v>
+        <v>13.1540438039704</v>
       </c>
       <c r="F780" t="n">
         <v>210250</v>
@@ -16032,16 +16032,16 @@
         <v>45457</v>
       </c>
       <c r="B781" t="n">
-        <v>13.07339954376221</v>
+        <v>13.07339859008789</v>
       </c>
       <c r="C781" t="n">
-        <v>13.27053105759112</v>
+        <v>13.27053008953652</v>
       </c>
       <c r="D781" t="n">
-        <v>12.9031491519523</v>
+        <v>12.90314821069736</v>
       </c>
       <c r="E781" t="n">
-        <v>13.06443857235778</v>
+        <v>13.06443761933714</v>
       </c>
       <c r="F781" t="n">
         <v>928770</v>
@@ -16072,16 +16072,16 @@
         <v>45461</v>
       </c>
       <c r="B783" t="n">
-        <v>13.47662258148193</v>
+        <v>13.47662162780762</v>
       </c>
       <c r="C783" t="n">
-        <v>13.55726684324567</v>
+        <v>13.55726588386456</v>
       </c>
       <c r="D783" t="n">
-        <v>13.06443850910792</v>
+        <v>13.06443758460185</v>
       </c>
       <c r="E783" t="n">
-        <v>13.08235955573288</v>
+        <v>13.08235862995862</v>
       </c>
       <c r="F783" t="n">
         <v>385685</v>
@@ -16172,16 +16172,16 @@
         <v>45468</v>
       </c>
       <c r="B788" t="n">
-        <v>12.72393894195557</v>
+        <v>12.72393989562988</v>
       </c>
       <c r="C788" t="n">
-        <v>13.24364837439928</v>
+        <v>13.24364936702643</v>
       </c>
       <c r="D788" t="n">
-        <v>12.71497797100114</v>
+        <v>12.71497892400382</v>
       </c>
       <c r="E788" t="n">
-        <v>13.20780628277578</v>
+        <v>13.20780727271652</v>
       </c>
       <c r="F788" t="n">
         <v>394179</v>
@@ -16192,16 +16192,16 @@
         <v>45469</v>
       </c>
       <c r="B789" t="n">
-        <v>12.84042453765869</v>
+        <v>12.84042549133301</v>
       </c>
       <c r="C789" t="n">
-        <v>12.89418767193683</v>
+        <v>12.8941886296042</v>
       </c>
       <c r="D789" t="n">
-        <v>12.67017416439606</v>
+        <v>12.67017510542567</v>
       </c>
       <c r="E789" t="n">
-        <v>12.78666140338055</v>
+        <v>12.78666235306181</v>
       </c>
       <c r="F789" t="n">
         <v>397115</v>
@@ -16272,16 +16272,16 @@
         <v>45475</v>
       </c>
       <c r="B793" t="n">
-        <v>13.29741287231445</v>
+        <v>13.29741382598877</v>
       </c>
       <c r="C793" t="n">
-        <v>13.5483066263438</v>
+        <v>13.54830759801191</v>
       </c>
       <c r="D793" t="n">
-        <v>13.27053085460948</v>
+        <v>13.27053180635585</v>
       </c>
       <c r="E793" t="n">
-        <v>13.36013608679751</v>
+        <v>13.36013704497026</v>
       </c>
       <c r="F793" t="n">
         <v>528404</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61103057861328</v>
+        <v>13.61102962493896</v>
       </c>
       <c r="C795" t="n">
-        <v>13.7006358097591</v>
+        <v>13.70063484980648</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766220877997</v>
+        <v>13.46766126515094</v>
       </c>
       <c r="E795" t="n">
-        <v>13.593108636287</v>
+        <v>13.59310768386841</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16392,16 +16392,16 @@
         <v>45483</v>
       </c>
       <c r="B799" t="n">
-        <v>13.63791179656982</v>
+        <v>13.63791084289551</v>
       </c>
       <c r="C799" t="n">
-        <v>13.78128016741929</v>
+        <v>13.78127920371949</v>
       </c>
       <c r="D799" t="n">
-        <v>13.56622850724222</v>
+        <v>13.56622755858058</v>
       </c>
       <c r="E799" t="n">
-        <v>13.71855695322121</v>
+        <v>13.71855599390753</v>
       </c>
       <c r="F799" t="n">
         <v>395437</v>
@@ -16412,16 +16412,16 @@
         <v>45484</v>
       </c>
       <c r="B800" t="n">
-        <v>14.01425361633301</v>
+        <v>14.01425266265869</v>
       </c>
       <c r="C800" t="n">
-        <v>14.05905578368349</v>
+        <v>14.05905482696037</v>
       </c>
       <c r="D800" t="n">
-        <v>13.64687261810947</v>
+        <v>13.64687168943554</v>
       </c>
       <c r="E800" t="n">
-        <v>13.64687261810947</v>
+        <v>13.64687168943554</v>
       </c>
       <c r="F800" t="n">
         <v>415676</v>
@@ -16532,16 +16532,16 @@
         <v>45492</v>
       </c>
       <c r="B806" t="n">
-        <v>13.79023933410645</v>
+        <v>13.79024028778076</v>
       </c>
       <c r="C806" t="n">
-        <v>13.89776560516017</v>
+        <v>13.89776656627055</v>
       </c>
       <c r="D806" t="n">
-        <v>13.65583194333782</v>
+        <v>13.65583288771709</v>
       </c>
       <c r="E806" t="n">
-        <v>13.89776560516017</v>
+        <v>13.89776656627055</v>
       </c>
       <c r="F806" t="n">
         <v>491387</v>
@@ -16552,16 +16552,16 @@
         <v>45495</v>
       </c>
       <c r="B807" t="n">
-        <v>13.98737239837646</v>
+        <v>13.98737335205078</v>
       </c>
       <c r="C807" t="n">
-        <v>14.11281972062591</v>
+        <v>14.11282068285336</v>
       </c>
       <c r="D807" t="n">
-        <v>13.79023999588737</v>
+        <v>13.79024093612098</v>
       </c>
       <c r="E807" t="n">
-        <v>13.79920096695374</v>
+        <v>13.79920190779832</v>
       </c>
       <c r="F807" t="n">
         <v>314378</v>
@@ -16592,16 +16592,16 @@
         <v>45497</v>
       </c>
       <c r="B809" t="n">
-        <v>13.58414745330811</v>
+        <v>13.58414840698242</v>
       </c>
       <c r="C809" t="n">
-        <v>13.77231887141577</v>
+        <v>13.77231983830065</v>
       </c>
       <c r="D809" t="n">
-        <v>13.5214233485732</v>
+        <v>13.52142429784398</v>
       </c>
       <c r="E809" t="n">
-        <v>13.7275158114484</v>
+        <v>13.72751677518789</v>
       </c>
       <c r="F809" t="n">
         <v>613342</v>
@@ -16712,16 +16712,16 @@
         <v>45505</v>
       </c>
       <c r="B815" t="n">
-        <v>13.36013507843018</v>
+        <v>13.36013603210449</v>
       </c>
       <c r="C815" t="n">
-        <v>13.64687179979016</v>
+        <v>13.64687277393235</v>
       </c>
       <c r="D815" t="n">
-        <v>13.29741186868121</v>
+        <v>13.29741281787821</v>
       </c>
       <c r="E815" t="n">
-        <v>13.44077933326414</v>
+        <v>13.44078029269502</v>
       </c>
       <c r="F815" t="n">
         <v>623514</v>
@@ -16752,16 +16752,16 @@
         <v>45509</v>
       </c>
       <c r="B817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770042419434</v>
       </c>
       <c r="C817" t="n">
-        <v>13.23468850107574</v>
+        <v>13.23468751329381</v>
       </c>
       <c r="D817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770042419434</v>
       </c>
       <c r="E817" t="n">
-        <v>13.04651706913838</v>
+        <v>13.04651609540078</v>
       </c>
       <c r="F817" t="n">
         <v>596040</v>
@@ -16792,16 +16792,16 @@
         <v>45511</v>
       </c>
       <c r="B819" t="n">
-        <v>12.93899154663086</v>
+        <v>12.93899059295654</v>
       </c>
       <c r="C819" t="n">
-        <v>13.00171565963084</v>
+        <v>13.00171470133341</v>
       </c>
       <c r="D819" t="n">
-        <v>12.75082099982525</v>
+        <v>12.75082006002013</v>
       </c>
       <c r="E819" t="n">
-        <v>13.00171565963084</v>
+        <v>13.00171470133341</v>
       </c>
       <c r="F819" t="n">
         <v>296971</v>
@@ -16812,16 +16812,16 @@
         <v>45512</v>
       </c>
       <c r="B820" t="n">
-        <v>12.80458354949951</v>
+        <v>12.8045825958252</v>
       </c>
       <c r="C820" t="n">
-        <v>13.1002803654145</v>
+        <v>13.10027938971694</v>
       </c>
       <c r="D820" t="n">
-        <v>12.80458354949951</v>
+        <v>12.8045825958252</v>
       </c>
       <c r="E820" t="n">
-        <v>13.00171505880854</v>
+        <v>13.00171409045204</v>
       </c>
       <c r="F820" t="n">
         <v>258486</v>
@@ -16912,16 +16912,16 @@
         <v>45519</v>
       </c>
       <c r="B825" t="n">
-        <v>12.50888538360596</v>
+        <v>12.50888633728027</v>
       </c>
       <c r="C825" t="n">
-        <v>12.75978000474051</v>
+        <v>12.75978097754297</v>
       </c>
       <c r="D825" t="n">
-        <v>12.2221486737379</v>
+        <v>12.22214960555148</v>
       </c>
       <c r="E825" t="n">
-        <v>12.4551222505057</v>
+        <v>12.45512320008113</v>
       </c>
       <c r="F825" t="n">
         <v>551893</v>
@@ -16992,16 +16992,16 @@
         <v>45525</v>
       </c>
       <c r="B829" t="n">
-        <v>12.08774185180664</v>
+        <v>12.08774089813232</v>
       </c>
       <c r="C829" t="n">
-        <v>12.49992592198841</v>
+        <v>12.49992493579443</v>
       </c>
       <c r="D829" t="n">
-        <v>12.08774185180664</v>
+        <v>12.08774089813232</v>
       </c>
       <c r="E829" t="n">
-        <v>12.49992592198841</v>
+        <v>12.49992493579443</v>
       </c>
       <c r="F829" t="n">
         <v>645535</v>
@@ -17012,16 +17012,16 @@
         <v>45526</v>
       </c>
       <c r="B830" t="n">
-        <v>11.43362426757812</v>
+        <v>11.43362331390381</v>
       </c>
       <c r="C830" t="n">
-        <v>12.0877420273615</v>
+        <v>12.08774101912747</v>
       </c>
       <c r="D830" t="n">
-        <v>11.43362426757812</v>
+        <v>11.43362331390381</v>
       </c>
       <c r="E830" t="n">
-        <v>12.0877420273615</v>
+        <v>12.08774101912747</v>
       </c>
       <c r="F830" t="n">
         <v>1040029</v>
@@ -17092,16 +17092,16 @@
         <v>45532</v>
       </c>
       <c r="B834" t="n">
-        <v>11.9354133605957</v>
+        <v>11.93541240692139</v>
       </c>
       <c r="C834" t="n">
-        <v>12.21318913273821</v>
+        <v>12.2131881568688</v>
       </c>
       <c r="D834" t="n">
-        <v>11.89957126766782</v>
+        <v>11.89957031685739</v>
       </c>
       <c r="E834" t="n">
-        <v>12.21318913273821</v>
+        <v>12.2131881568688</v>
       </c>
       <c r="F834" t="n">
         <v>555773</v>
@@ -17112,16 +17112,16 @@
         <v>45533</v>
       </c>
       <c r="B835" t="n">
-        <v>11.42466449737549</v>
+        <v>11.42466354370117</v>
       </c>
       <c r="C835" t="n">
-        <v>12.12358444475269</v>
+        <v>12.123583432736</v>
       </c>
       <c r="D835" t="n">
-        <v>11.29921627039831</v>
+        <v>11.29921532719579</v>
       </c>
       <c r="E835" t="n">
-        <v>11.93541389648125</v>
+        <v>11.93541290017211</v>
       </c>
       <c r="F835" t="n">
         <v>1428127</v>
@@ -17252,16 +17252,16 @@
         <v>45544</v>
       </c>
       <c r="B842" t="n">
-        <v>11.23649120330811</v>
+        <v>11.23649215698242</v>
       </c>
       <c r="C842" t="n">
-        <v>11.41570075039603</v>
+        <v>11.41570171928039</v>
       </c>
       <c r="D842" t="n">
-        <v>11.20960918878185</v>
+        <v>11.20961014017461</v>
       </c>
       <c r="E842" t="n">
-        <v>11.35297754332981</v>
+        <v>11.35297850689067</v>
       </c>
       <c r="F842" t="n">
         <v>579052</v>
@@ -17272,16 +17272,16 @@
         <v>45545</v>
       </c>
       <c r="B843" t="n">
-        <v>11.36193943023682</v>
+        <v>11.36194038391113</v>
       </c>
       <c r="C843" t="n">
-        <v>11.49634772151831</v>
+        <v>11.4963486864743</v>
       </c>
       <c r="D843" t="n">
-        <v>11.11104478953531</v>
+        <v>11.11104572215057</v>
       </c>
       <c r="E843" t="n">
-        <v>11.29025524717924</v>
+        <v>11.29025619483669</v>
       </c>
       <c r="F843" t="n">
         <v>726909</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37986087799072</v>
+        <v>11.37985992431641</v>
       </c>
       <c r="C844" t="n">
-        <v>11.5232292491703</v>
+        <v>11.52322828348119</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089990674344</v>
+        <v>11.37089895382008</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882184923801</v>
+        <v>11.38882089481273</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17312,16 +17312,16 @@
         <v>45547</v>
       </c>
       <c r="B845" t="n">
-        <v>11.34401798248291</v>
+        <v>11.34401893615723</v>
       </c>
       <c r="C845" t="n">
-        <v>11.47842537290442</v>
+        <v>11.47842633787816</v>
       </c>
       <c r="D845" t="n">
-        <v>11.2902548470949</v>
+        <v>11.29025579624943</v>
       </c>
       <c r="E845" t="n">
-        <v>11.39778111787093</v>
+        <v>11.39778207606503</v>
       </c>
       <c r="F845" t="n">
         <v>413998</v>
@@ -17352,16 +17352,16 @@
         <v>45551</v>
       </c>
       <c r="B847" t="n">
-        <v>11.46946620941162</v>
+        <v>11.4694652557373</v>
       </c>
       <c r="C847" t="n">
-        <v>11.62179465706196</v>
+        <v>11.62179369072169</v>
       </c>
       <c r="D847" t="n">
-        <v>11.46946620941162</v>
+        <v>11.4694652557373</v>
       </c>
       <c r="E847" t="n">
-        <v>11.59491353528131</v>
+        <v>11.59491257117618</v>
       </c>
       <c r="F847" t="n">
         <v>377086</v>
@@ -17372,16 +17372,16 @@
         <v>45552</v>
       </c>
       <c r="B848" t="n">
-        <v>11.53219032287598</v>
+        <v>11.53218936920166</v>
       </c>
       <c r="C848" t="n">
-        <v>11.63075563088909</v>
+        <v>11.63075466906374</v>
       </c>
       <c r="D848" t="n">
-        <v>11.3977820256524</v>
+        <v>11.39778108309321</v>
       </c>
       <c r="E848" t="n">
-        <v>11.52322935154908</v>
+        <v>11.5232283986158</v>
       </c>
       <c r="F848" t="n">
         <v>1190193</v>
@@ -17392,16 +17392,16 @@
         <v>45553</v>
       </c>
       <c r="B849" t="n">
-        <v>11.42466449737549</v>
+        <v>11.42466354370117</v>
       </c>
       <c r="C849" t="n">
-        <v>11.7114003575755</v>
+        <v>11.71139937996589</v>
       </c>
       <c r="D849" t="n">
-        <v>11.39778247842404</v>
+        <v>11.39778152699371</v>
       </c>
       <c r="E849" t="n">
-        <v>11.6307560929155</v>
+        <v>11.63075512203768</v>
       </c>
       <c r="F849" t="n">
         <v>662418</v>
@@ -17412,16 +17412,16 @@
         <v>45554</v>
       </c>
       <c r="B850" t="n">
-        <v>11.06624221801758</v>
+        <v>11.06624126434326</v>
       </c>
       <c r="C850" t="n">
-        <v>11.55907144645077</v>
+        <v>11.55907045030507</v>
       </c>
       <c r="D850" t="n">
-        <v>11.06624221801758</v>
+        <v>11.06624126434326</v>
       </c>
       <c r="E850" t="n">
-        <v>11.46946621365356</v>
+        <v>11.46946522522993</v>
       </c>
       <c r="F850" t="n">
         <v>825270</v>
@@ -17452,16 +17452,16 @@
         <v>45558</v>
       </c>
       <c r="B852" t="n">
-        <v>10.73470306396484</v>
+        <v>10.73470211029053</v>
       </c>
       <c r="C852" t="n">
-        <v>10.8870324043523</v>
+        <v>10.887031437145</v>
       </c>
       <c r="D852" t="n">
-        <v>10.66301887933477</v>
+        <v>10.6630179320289</v>
       </c>
       <c r="E852" t="n">
-        <v>10.82430829475243</v>
+        <v>10.82430733311756</v>
       </c>
       <c r="F852" t="n">
         <v>654029</v>
@@ -17472,16 +17472,16 @@
         <v>45559</v>
       </c>
       <c r="B853" t="n">
-        <v>10.69886112213135</v>
+        <v>10.69886016845703</v>
       </c>
       <c r="C853" t="n">
-        <v>10.95871674311883</v>
+        <v>10.95871576628153</v>
       </c>
       <c r="D853" t="n">
-        <v>10.68990104697512</v>
+        <v>10.68990009409949</v>
       </c>
       <c r="E853" t="n">
-        <v>10.91391367904632</v>
+        <v>10.91391270620266</v>
       </c>
       <c r="F853" t="n">
         <v>530081</v>
@@ -17492,16 +17492,16 @@
         <v>45560</v>
       </c>
       <c r="B854" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420413970947</v>
       </c>
       <c r="C854" t="n">
-        <v>10.76158418418261</v>
+        <v>10.76158517156435</v>
       </c>
       <c r="D854" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420413970947</v>
       </c>
       <c r="E854" t="n">
-        <v>10.6988609706855</v>
+        <v>10.69886195231235</v>
       </c>
       <c r="F854" t="n">
         <v>618376</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276733398438</v>
+        <v>10.49276924133301</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029359905444</v>
+        <v>10.60029552594893</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212308323033</v>
+        <v>10.41212497591966</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900509754635</v>
+        <v>10.43900699512222</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -17612,16 +17612,16 @@
         <v>45568</v>
       </c>
       <c r="B860" t="n">
-        <v>10.73470306396484</v>
+        <v>10.73470211029053</v>
       </c>
       <c r="C860" t="n">
-        <v>10.7884662024374</v>
+        <v>10.78846524398675</v>
       </c>
       <c r="D860" t="n">
-        <v>10.6002947697349</v>
+        <v>10.60029382800146</v>
       </c>
       <c r="E860" t="n">
-        <v>10.72574298893464</v>
+        <v>10.72574203605634</v>
       </c>
       <c r="F860" t="n">
         <v>701113</v>
@@ -17632,16 +17632,16 @@
         <v>45569</v>
       </c>
       <c r="B861" t="n">
-        <v>10.86879062652588</v>
+        <v>10.86878967285156</v>
       </c>
       <c r="C861" t="n">
-        <v>10.86879062652588</v>
+        <v>10.86878967285156</v>
       </c>
       <c r="D861" t="n">
-        <v>10.55125535483793</v>
+        <v>10.55125442902552</v>
       </c>
       <c r="E861" t="n">
-        <v>10.7599212349831</v>
+        <v>10.75992029086146</v>
       </c>
       <c r="F861" t="n">
         <v>575487</v>
@@ -17672,16 +17672,16 @@
         <v>45573</v>
       </c>
       <c r="B863" t="n">
-        <v>10.96858596801758</v>
+        <v>10.96858692169189</v>
       </c>
       <c r="C863" t="n">
-        <v>11.07745534817464</v>
+        <v>11.07745631131471</v>
       </c>
       <c r="D863" t="n">
-        <v>10.91415218522925</v>
+        <v>10.91415313417077</v>
       </c>
       <c r="E863" t="n">
-        <v>10.95951397331626</v>
+        <v>10.9595149262018</v>
       </c>
       <c r="F863" t="n">
         <v>482893</v>
@@ -17692,16 +17692,16 @@
         <v>45574</v>
       </c>
       <c r="B864" t="n">
-        <v>11.17725276947021</v>
+        <v>11.17725372314453</v>
       </c>
       <c r="C864" t="n">
-        <v>11.34055684022943</v>
+        <v>11.34055780783731</v>
       </c>
       <c r="D864" t="n">
-        <v>10.84157263322136</v>
+        <v>10.84157355825452</v>
       </c>
       <c r="E864" t="n">
-        <v>10.98673180722956</v>
+        <v>10.9867327446481</v>
       </c>
       <c r="F864" t="n">
         <v>1130107</v>
@@ -17772,16 +17772,16 @@
         <v>45580</v>
       </c>
       <c r="B868" t="n">
-        <v>10.97765922546387</v>
+        <v>10.97766017913818</v>
       </c>
       <c r="C868" t="n">
-        <v>11.17725309554795</v>
+        <v>11.17725406656181</v>
       </c>
       <c r="D868" t="n">
-        <v>10.94136943090312</v>
+        <v>10.9413703814248</v>
       </c>
       <c r="E868" t="n">
-        <v>10.97765922546387</v>
+        <v>10.97766017913818</v>
       </c>
       <c r="F868" t="n">
         <v>332520</v>
@@ -17792,16 +17792,16 @@
         <v>45581</v>
       </c>
       <c r="B869" t="n">
-        <v>11.21354389190674</v>
+        <v>11.21354293823242</v>
       </c>
       <c r="C869" t="n">
-        <v>11.2770505844165</v>
+        <v>11.27704962534115</v>
       </c>
       <c r="D869" t="n">
-        <v>10.96858730309262</v>
+        <v>10.96858637025104</v>
       </c>
       <c r="E869" t="n">
-        <v>10.97766020618848</v>
+        <v>10.97765927257528</v>
       </c>
       <c r="F869" t="n">
         <v>1586680</v>
@@ -17812,16 +17812,16 @@
         <v>45582</v>
       </c>
       <c r="B870" t="n">
-        <v>10.97765922546387</v>
+        <v>10.97766017913818</v>
       </c>
       <c r="C870" t="n">
-        <v>11.11374550142154</v>
+        <v>11.11374646691823</v>
       </c>
       <c r="D870" t="n">
-        <v>10.88693473906201</v>
+        <v>10.88693568485472</v>
       </c>
       <c r="E870" t="n">
-        <v>11.11374550142154</v>
+        <v>11.11374646691823</v>
       </c>
       <c r="F870" t="n">
         <v>397220</v>
@@ -17952,16 +17952,16 @@
         <v>45593</v>
       </c>
       <c r="B877" t="n">
-        <v>11.19539928436279</v>
+        <v>11.19539833068848</v>
       </c>
       <c r="C877" t="n">
-        <v>11.36777628205736</v>
+        <v>11.3677753136992</v>
       </c>
       <c r="D877" t="n">
-        <v>11.09560279145304</v>
+        <v>11.09560184627984</v>
       </c>
       <c r="E877" t="n">
-        <v>11.10467478749469</v>
+        <v>11.10467384154869</v>
       </c>
       <c r="F877" t="n">
         <v>439060</v>
@@ -17972,16 +17972,16 @@
         <v>45594</v>
       </c>
       <c r="B878" t="n">
-        <v>11.20447063446045</v>
+        <v>11.20446968078613</v>
       </c>
       <c r="C878" t="n">
-        <v>11.39499252054494</v>
+        <v>11.39499155065426</v>
       </c>
       <c r="D878" t="n">
-        <v>11.19539863894181</v>
+        <v>11.19539768603966</v>
       </c>
       <c r="E878" t="n">
-        <v>11.19539863894181</v>
+        <v>11.19539768603966</v>
       </c>
       <c r="F878" t="n">
         <v>428784</v>
@@ -17992,16 +17992,16 @@
         <v>45595</v>
       </c>
       <c r="B879" t="n">
-        <v>11.23168849945068</v>
+        <v>11.23168754577637</v>
       </c>
       <c r="C879" t="n">
-        <v>11.45849927618946</v>
+        <v>11.45849830325681</v>
       </c>
       <c r="D879" t="n">
-        <v>11.15003600286733</v>
+        <v>11.15003505612607</v>
       </c>
       <c r="E879" t="n">
-        <v>11.20447069815947</v>
+        <v>11.2044697467962</v>
       </c>
       <c r="F879" t="n">
         <v>531864</v>
@@ -18012,16 +18012,16 @@
         <v>45596</v>
       </c>
       <c r="B880" t="n">
-        <v>11.29519557952881</v>
+        <v>11.29519653320312</v>
       </c>
       <c r="C880" t="n">
-        <v>11.36777516992267</v>
+        <v>11.36777612972502</v>
       </c>
       <c r="D880" t="n">
-        <v>11.1591083938952</v>
+        <v>11.15910933607942</v>
       </c>
       <c r="E880" t="n">
-        <v>11.32241156499114</v>
+        <v>11.32241252096335</v>
       </c>
       <c r="F880" t="n">
         <v>510157</v>
@@ -18112,16 +18112,16 @@
         <v>45603</v>
       </c>
       <c r="B885" t="n">
-        <v>11.34055709838867</v>
+        <v>11.34055805206299</v>
       </c>
       <c r="C885" t="n">
-        <v>12.27501884869364</v>
+        <v>12.27501988095071</v>
       </c>
       <c r="D885" t="n">
-        <v>11.34055709838867</v>
+        <v>11.34055805206299</v>
       </c>
       <c r="E885" t="n">
-        <v>12.12985967138101</v>
+        <v>12.12986069143104</v>
       </c>
       <c r="F885" t="n">
         <v>628128</v>
@@ -18352,16 +18352,16 @@
         <v>45623</v>
       </c>
       <c r="B897" t="n">
-        <v>10.39702320098877</v>
+        <v>10.39702415466309</v>
       </c>
       <c r="C897" t="n">
-        <v>10.66012284508218</v>
+        <v>10.6601238228895</v>
       </c>
       <c r="D897" t="n">
-        <v>10.39702320098877</v>
+        <v>10.39702415466309</v>
       </c>
       <c r="E897" t="n">
-        <v>10.58754416477826</v>
+        <v>10.58754513592825</v>
       </c>
       <c r="F897" t="n">
         <v>1060897</v>
@@ -18512,16 +18512,16 @@
         <v>45635</v>
       </c>
       <c r="B905" t="n">
-        <v>9.516995429992676</v>
+        <v>9.516996383666992</v>
       </c>
       <c r="C905" t="n">
-        <v>9.997834753365625</v>
+        <v>9.997835755223649</v>
       </c>
       <c r="D905" t="n">
-        <v>9.516995429992676</v>
+        <v>9.516996383666992</v>
       </c>
       <c r="E905" t="n">
-        <v>9.979689856119661</v>
+        <v>9.979690856159429</v>
       </c>
       <c r="F905" t="n">
         <v>642914</v>
@@ -18532,16 +18532,16 @@
         <v>45636</v>
       </c>
       <c r="B906" t="n">
-        <v>9.725662231445312</v>
+        <v>9.725661277770996</v>
       </c>
       <c r="C906" t="n">
-        <v>9.734735134587304</v>
+        <v>9.734734180023322</v>
       </c>
       <c r="D906" t="n">
-        <v>9.516996346663277</v>
+        <v>9.516995413450219</v>
       </c>
       <c r="E906" t="n">
-        <v>9.516996346663277</v>
+        <v>9.516995413450219</v>
       </c>
       <c r="F906" t="n">
         <v>570454</v>
@@ -18592,16 +18592,16 @@
         <v>45639</v>
       </c>
       <c r="B909" t="n">
-        <v>9.507923126220703</v>
+        <v>9.50792407989502</v>
       </c>
       <c r="C909" t="n">
-        <v>9.716588984127226</v>
+        <v>9.716589958731378</v>
       </c>
       <c r="D909" t="n">
-        <v>9.507923126220703</v>
+        <v>9.50792407989502</v>
       </c>
       <c r="E909" t="n">
-        <v>9.707516989443993</v>
+        <v>9.707517963138196</v>
       </c>
       <c r="F909" t="n">
         <v>532074</v>
@@ -18652,16 +18652,16 @@
         <v>45644</v>
       </c>
       <c r="B912" t="n">
-        <v>9.299256324768066</v>
+        <v>9.299257278442383</v>
       </c>
       <c r="C912" t="n">
-        <v>9.6530813545484</v>
+        <v>9.653082344508826</v>
       </c>
       <c r="D912" t="n">
-        <v>9.29018342283001</v>
+        <v>9.290184375573865</v>
       </c>
       <c r="E912" t="n">
-        <v>9.589574670142779</v>
+        <v>9.589575653590352</v>
       </c>
       <c r="F912" t="n">
         <v>551054</v>
@@ -18672,16 +18672,16 @@
         <v>45645</v>
       </c>
       <c r="B913" t="n">
-        <v>9.362765312194824</v>
+        <v>9.362764358520508</v>
       </c>
       <c r="C913" t="n">
-        <v>9.507924506521427</v>
+        <v>9.507923538061457</v>
       </c>
       <c r="D913" t="n">
-        <v>9.299257711031771</v>
+        <v>9.299256763826225</v>
       </c>
       <c r="E913" t="n">
-        <v>9.299257711031771</v>
+        <v>9.299256763826225</v>
       </c>
       <c r="F913" t="n">
         <v>386524</v>
@@ -18712,16 +18712,16 @@
         <v>45649</v>
       </c>
       <c r="B915" t="n">
-        <v>9.444416046142578</v>
+        <v>9.444416999816895</v>
       </c>
       <c r="C915" t="n">
-        <v>9.707517515568773</v>
+        <v>9.70751849581044</v>
       </c>
       <c r="D915" t="n">
-        <v>9.408126250862431</v>
+        <v>9.408127200872292</v>
       </c>
       <c r="E915" t="n">
-        <v>9.662154817823463</v>
+        <v>9.662155793484516</v>
       </c>
       <c r="F915" t="n">
         <v>379289</v>
@@ -18732,16 +18732,16 @@
         <v>45652</v>
       </c>
       <c r="B916" t="n">
-        <v>9.353692054748535</v>
+        <v>9.353691101074219</v>
       </c>
       <c r="C916" t="n">
-        <v>9.516996142182833</v>
+        <v>9.516995171858524</v>
       </c>
       <c r="D916" t="n">
-        <v>9.326474253197672</v>
+        <v>9.3264733022984</v>
       </c>
       <c r="E916" t="n">
-        <v>9.44441654776759</v>
+        <v>9.444415584843277</v>
       </c>
       <c r="F916" t="n">
         <v>662104</v>
@@ -18752,16 +18752,16 @@
         <v>45653</v>
       </c>
       <c r="B917" t="n">
-        <v>9.253893852233887</v>
+        <v>9.253894805908203</v>
       </c>
       <c r="C917" t="n">
-        <v>9.435343729747528</v>
+        <v>9.435344702121442</v>
       </c>
       <c r="D917" t="n">
-        <v>9.199460068457073</v>
+        <v>9.199461016521633</v>
       </c>
       <c r="E917" t="n">
-        <v>9.353691239501879</v>
+        <v>9.35369220346097</v>
       </c>
       <c r="F917" t="n">
         <v>457726</v>
@@ -18772,16 +18772,16 @@
         <v>45656</v>
       </c>
       <c r="B918" t="n">
-        <v>9.435343742370605</v>
+        <v>9.435344696044922</v>
       </c>
       <c r="C918" t="n">
-        <v>9.444415737248805</v>
+        <v>9.44441669184007</v>
       </c>
       <c r="D918" t="n">
-        <v>9.217604070520975</v>
+        <v>9.217605002187325</v>
       </c>
       <c r="E918" t="n">
-        <v>9.326473452800682</v>
+        <v>9.326474395470969</v>
       </c>
       <c r="F918" t="n">
         <v>305150</v>
@@ -26612,19 +26612,19 @@
         <v>46231</v>
       </c>
       <c r="B1310" t="n">
-        <v>5.98</v>
+        <v>5.7</v>
       </c>
       <c r="C1310" t="n">
         <v>6.12</v>
       </c>
       <c r="D1310" t="n">
-        <v>5.93</v>
+        <v>5.68</v>
       </c>
       <c r="E1310" t="n">
         <v>5.93</v>
       </c>
       <c r="F1310" t="n">
-        <v>192600</v>
+        <v>800900</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.28566360473633</v>
+        <v>13.2856616973877</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24647174220278</v>
+        <v>14.24646969691628</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83010733362354</v>
+        <v>12.83010549167658</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24647174220278</v>
+        <v>14.24646969691628</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970443725586</v>
+        <v>13.16970252990723</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606824847914</v>
+        <v>13.76606625476003</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404745317332</v>
+        <v>13.00404556981654</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647251293245</v>
+        <v>13.42647056839647</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -512,16 +512,16 @@
         <v>44321</v>
       </c>
       <c r="B5" t="n">
-        <v>12.93778324127197</v>
+        <v>12.93778419494629</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3353587586459</v>
+        <v>13.33535974162644</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92949897903101</v>
+        <v>12.92949993209467</v>
       </c>
       <c r="E5" t="n">
-        <v>13.32707532857593</v>
+        <v>13.32707631094588</v>
       </c>
       <c r="F5" t="n">
         <v>876510</v>
@@ -532,16 +532,16 @@
         <v>44322</v>
       </c>
       <c r="B6" t="n">
-        <v>12.64788246154785</v>
+        <v>12.64788436889648</v>
       </c>
       <c r="C6" t="n">
-        <v>13.12828726003102</v>
+        <v>13.12828923982652</v>
       </c>
       <c r="D6" t="n">
-        <v>12.598186044731</v>
+        <v>12.59818794458523</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12828726003102</v>
+        <v>13.12828923982652</v>
       </c>
       <c r="F6" t="n">
         <v>671078</v>
@@ -552,16 +552,16 @@
         <v>44323</v>
       </c>
       <c r="B7" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="C7" t="n">
-        <v>12.85495449619264</v>
+        <v>12.85495739835445</v>
       </c>
       <c r="D7" t="n">
-        <v>12.26687258210669</v>
+        <v>12.26687535150188</v>
       </c>
       <c r="E7" t="n">
-        <v>12.71414617400787</v>
+        <v>12.71414904438049</v>
       </c>
       <c r="F7" t="n">
         <v>847960</v>
@@ -572,16 +572,16 @@
         <v>44326</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51535892486572</v>
+        <v>12.51535797119141</v>
       </c>
       <c r="C8" t="n">
-        <v>12.80525818830482</v>
+        <v>12.80525721254009</v>
       </c>
       <c r="D8" t="n">
-        <v>12.51535892486572</v>
+        <v>12.51535797119141</v>
       </c>
       <c r="E8" t="n">
-        <v>12.67273328625897</v>
+        <v>12.67273232059268</v>
       </c>
       <c r="F8" t="n">
         <v>633995</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C9" t="n">
-        <v>12.5484900443603</v>
+        <v>12.54849100757134</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717612770272</v>
+        <v>12.2171770654824</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566200256348</v>
+        <v>12.46566104888916</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75556044155362</v>
+        <v>12.75555946570089</v>
       </c>
       <c r="D10" t="n">
-        <v>12.30000503842248</v>
+        <v>12.3000040974216</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141969554326</v>
+        <v>12.34141875137399</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162372589111</v>
+        <v>13.4016227722168</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172507017088</v>
+        <v>13.93172407877397</v>
       </c>
       <c r="D11" t="n">
-        <v>12.4656633578597</v>
+        <v>12.46566247078936</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273500163479</v>
+        <v>12.672734099829</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98142147064209</v>
+        <v>13.98142051696777</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778523820564</v>
+        <v>14.57778424385328</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495615574281</v>
+        <v>13.67495522297252</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9897049017596</v>
+        <v>13.98970394752027</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889507293701</v>
+        <v>13.84889316558838</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24647062182232</v>
+        <v>14.24646865971732</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323894097274</v>
+        <v>13.68323705643921</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222914697741</v>
+        <v>14.12222720198366</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -712,16 +712,16 @@
         <v>44335</v>
       </c>
       <c r="B15" t="n">
-        <v>13.48444938659668</v>
+        <v>13.484450340271</v>
       </c>
       <c r="C15" t="n">
-        <v>13.94828817352505</v>
+        <v>13.9482891600039</v>
       </c>
       <c r="D15" t="n">
-        <v>13.36020625997589</v>
+        <v>13.36020720486323</v>
       </c>
       <c r="E15" t="n">
-        <v>13.77434862842691</v>
+        <v>13.77434960260406</v>
       </c>
       <c r="F15" t="n">
         <v>804661</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21940040588379</v>
+        <v>13.21939754486084</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48445105518772</v>
+        <v>13.4844481368009</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687466514628</v>
+        <v>13.08687183280536</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687466514628</v>
+        <v>13.08687183280536</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -772,16 +772,16 @@
         <v>44340</v>
       </c>
       <c r="B18" t="n">
-        <v>13.42647075653076</v>
+        <v>13.42646980285645</v>
       </c>
       <c r="C18" t="n">
-        <v>14.02283448973993</v>
+        <v>14.02283349370625</v>
       </c>
       <c r="D18" t="n">
-        <v>13.3270762462152</v>
+        <v>13.32707529960082</v>
       </c>
       <c r="E18" t="n">
-        <v>13.40162212895187</v>
+        <v>13.40162117704254</v>
       </c>
       <c r="F18" t="n">
         <v>1040223</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.26909637451172</v>
+        <v>13.26909732818604</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182412334521</v>
+        <v>13.64182510380815</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253117759573</v>
+        <v>13.25253213007947</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162211069491</v>
+        <v>13.4016230738941</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -812,16 +812,16 @@
         <v>44342</v>
       </c>
       <c r="B20" t="n">
-        <v>13.27737808227539</v>
+        <v>13.27737903594971</v>
       </c>
       <c r="C20" t="n">
-        <v>13.51758091098307</v>
+        <v>13.51758188191043</v>
       </c>
       <c r="D20" t="n">
-        <v>13.26081288647065</v>
+        <v>13.26081383895514</v>
       </c>
       <c r="E20" t="n">
-        <v>13.36848915571444</v>
+        <v>13.36849011593299</v>
       </c>
       <c r="F20" t="n">
         <v>382946</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970443725586</v>
+        <v>13.16970252990723</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45132031159078</v>
+        <v>13.45131836345614</v>
       </c>
       <c r="D21" t="n">
-        <v>13.1531392381503</v>
+        <v>13.15313733320078</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707798961446</v>
+        <v>13.32707605947365</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889537811279</v>
+        <v>13.02889442443848</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879381777798</v>
+        <v>13.31879284288401</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263209299946</v>
+        <v>12.96263114417541</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111753978956</v>
+        <v>13.21111657277715</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980270385742</v>
+        <v>12.87980365753174</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111660958277</v>
+        <v>13.21111758778895</v>
       </c>
       <c r="D23" t="n">
-        <v>12.61475207857974</v>
+        <v>12.6147530126286</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374225471193</v>
+        <v>13.05374322126546</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253009796143</v>
+        <v>13.25253105163574</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707514235259</v>
+        <v>13.32707610139129</v>
       </c>
       <c r="D24" t="n">
-        <v>12.8466719883597</v>
+        <v>12.84667291282778</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061070266274</v>
+        <v>13.02061163964774</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95435047149658</v>
+        <v>12.95434856414795</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879482233806</v>
+        <v>13.31879286133005</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808718138539</v>
+        <v>12.88808528379311</v>
       </c>
       <c r="E25" t="n">
-        <v>13.252532364398</v>
+        <v>13.25253041314621</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -932,16 +932,16 @@
         <v>44351</v>
       </c>
       <c r="B26" t="n">
-        <v>12.97919654846191</v>
+        <v>12.97919750213623</v>
       </c>
       <c r="C26" t="n">
-        <v>13.23596373052036</v>
+        <v>13.23596470306119</v>
       </c>
       <c r="D26" t="n">
-        <v>12.85495425621803</v>
+        <v>12.85495520076337</v>
       </c>
       <c r="E26" t="n">
-        <v>12.98747914603258</v>
+        <v>12.98748010031548</v>
       </c>
       <c r="F26" t="n">
         <v>460799</v>
@@ -952,16 +952,16 @@
         <v>44354</v>
       </c>
       <c r="B27" t="n">
-        <v>12.76384353637695</v>
+        <v>12.76384449005127</v>
       </c>
       <c r="C27" t="n">
-        <v>13.07859057440149</v>
+        <v>13.07859155159272</v>
       </c>
       <c r="D27" t="n">
-        <v>12.69758025748196</v>
+        <v>12.69758120620529</v>
       </c>
       <c r="E27" t="n">
-        <v>12.86323720646297</v>
+        <v>12.86323816756367</v>
       </c>
       <c r="F27" t="n">
         <v>662018</v>
@@ -992,16 +992,16 @@
         <v>44356</v>
       </c>
       <c r="B29" t="n">
-        <v>12.73071193695068</v>
+        <v>12.73071098327637</v>
       </c>
       <c r="C29" t="n">
-        <v>12.73899453504518</v>
+        <v>12.7389935807504</v>
       </c>
       <c r="D29" t="n">
-        <v>12.53192375748563</v>
+        <v>12.5319228187028</v>
       </c>
       <c r="E29" t="n">
-        <v>12.53192375748563</v>
+        <v>12.5319228187028</v>
       </c>
       <c r="F29" t="n">
         <v>453530</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95435047149658</v>
+        <v>12.95434856414795</v>
       </c>
       <c r="C30" t="n">
-        <v>13.00404689886607</v>
+        <v>13.00404498420033</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72243103653523</v>
+        <v>12.72242916333352</v>
       </c>
       <c r="E30" t="n">
-        <v>12.82182472344533</v>
+        <v>12.82182283560928</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667205810547</v>
+        <v>12.84667110443115</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555932114021</v>
+        <v>12.75555837422966</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1052,16 +1052,16 @@
         <v>44361</v>
       </c>
       <c r="B32" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="C32" t="n">
-        <v>13.00404458393173</v>
+        <v>13.00404751975243</v>
       </c>
       <c r="D32" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="E32" t="n">
-        <v>12.93778296995845</v>
+        <v>12.93778589081979</v>
       </c>
       <c r="F32" t="n">
         <v>396641</v>
@@ -1092,16 +1092,16 @@
         <v>44363</v>
       </c>
       <c r="B34" t="n">
-        <v>12.77212524414062</v>
+        <v>12.77212810516357</v>
       </c>
       <c r="C34" t="n">
-        <v>12.88808410174148</v>
+        <v>12.88808698873982</v>
       </c>
       <c r="D34" t="n">
-        <v>12.67273158098092</v>
+        <v>12.67273441973917</v>
       </c>
       <c r="E34" t="n">
-        <v>12.83010425685559</v>
+        <v>12.83010713086614</v>
       </c>
       <c r="F34" t="n">
         <v>265902</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414852142334</v>
+        <v>12.71414661407471</v>
       </c>
       <c r="C35" t="n">
-        <v>12.86323946886009</v>
+        <v>12.86323753914516</v>
       </c>
       <c r="D35" t="n">
-        <v>12.58990620392123</v>
+        <v>12.58990431521116</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384578129263</v>
+        <v>12.76384386648853</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1152,16 +1152,16 @@
         <v>44368</v>
       </c>
       <c r="B37" t="n">
-        <v>12.51535892486572</v>
+        <v>12.51535797119141</v>
       </c>
       <c r="C37" t="n">
-        <v>12.76384436445825</v>
+        <v>12.76384339184927</v>
       </c>
       <c r="D37" t="n">
-        <v>12.48222686718322</v>
+        <v>12.48222591603358</v>
       </c>
       <c r="E37" t="n">
-        <v>12.71414711010554</v>
+        <v>12.7141461412835</v>
       </c>
       <c r="F37" t="n">
         <v>462485</v>
@@ -1172,16 +1172,16 @@
         <v>44369</v>
       </c>
       <c r="B38" t="n">
-        <v>12.39939785003662</v>
+        <v>12.39939880371094</v>
       </c>
       <c r="C38" t="n">
-        <v>12.66444847481437</v>
+        <v>12.66444944887451</v>
       </c>
       <c r="D38" t="n">
-        <v>12.22545913168119</v>
+        <v>12.22546007197737</v>
       </c>
       <c r="E38" t="n">
-        <v>12.51535838255857</v>
+        <v>12.51535934515176</v>
       </c>
       <c r="F38" t="n">
         <v>779904</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313655853271</v>
       </c>
       <c r="C40" t="n">
-        <v>12.51535774406464</v>
+        <v>12.5153587118295</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717602295992</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717602295992</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657028198242</v>
+        <v>12.31657218933105</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424654557586</v>
+        <v>12.42424846959927</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293266081497</v>
+        <v>12.09293453353099</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596394810812</v>
+        <v>12.41596587084889</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1252,16 +1252,16 @@
         <v>44375</v>
       </c>
       <c r="B42" t="n">
-        <v>12.17576122283936</v>
+        <v>12.17576313018799</v>
       </c>
       <c r="C42" t="n">
-        <v>12.42424663826379</v>
+        <v>12.42424858453798</v>
       </c>
       <c r="D42" t="n">
-        <v>12.13434740302076</v>
+        <v>12.13434930388187</v>
       </c>
       <c r="E42" t="n">
-        <v>12.34141816645564</v>
+        <v>12.34142009975465</v>
       </c>
       <c r="F42" t="n">
         <v>425086</v>
@@ -1272,16 +1272,16 @@
         <v>44376</v>
       </c>
       <c r="B43" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="C43" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="D43" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152193682892</v>
       </c>
       <c r="E43" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152193682892</v>
       </c>
       <c r="F43" t="n">
         <v>538653</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43252913940544</v>
+        <v>12.43253006532078</v>
       </c>
       <c r="E44" t="n">
-        <v>12.5899034842721</v>
+        <v>12.58990442190792</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1312,16 +1312,16 @@
         <v>44378</v>
       </c>
       <c r="B45" t="n">
-        <v>12.51535892486572</v>
+        <v>12.51535797119141</v>
       </c>
       <c r="C45" t="n">
-        <v>12.90465186483921</v>
+        <v>12.90465088150065</v>
       </c>
       <c r="D45" t="n">
-        <v>12.51535892486572</v>
+        <v>12.51535797119141</v>
       </c>
       <c r="E45" t="n">
-        <v>12.77212696279336</v>
+        <v>12.77212598955324</v>
       </c>
       <c r="F45" t="n">
         <v>412760</v>
@@ -1352,16 +1352,16 @@
         <v>44382</v>
       </c>
       <c r="B47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="C47" t="n">
-        <v>12.64788378432207</v>
+        <v>12.64788281412843</v>
       </c>
       <c r="D47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="E47" t="n">
-        <v>12.55677270642959</v>
+        <v>12.5567717432249</v>
       </c>
       <c r="F47" t="n">
         <v>186679</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798263549805</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C48" t="n">
-        <v>12.49879177825338</v>
+        <v>12.49879274279404</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25858897447011</v>
+        <v>12.25858992047414</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394232278276</v>
+        <v>12.47394328540577</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.2171745300293</v>
+        <v>12.21717643737793</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020580617806</v>
+        <v>12.54020776395842</v>
       </c>
       <c r="D51" t="n">
-        <v>12.2171745300293</v>
+        <v>12.21717643737793</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424611694648</v>
+        <v>12.42424805662318</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121631622314</v>
+        <v>12.10121726989746</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030723427872</v>
+        <v>12.25030819970261</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293288642992</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293288642992</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495597839355</v>
+        <v>12.03495502471924</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172405694066</v>
+        <v>12.29172308291952</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010817945743</v>
+        <v>12.01010722775211</v>
       </c>
       <c r="E54" t="n">
-        <v>12.10121927207005</v>
+        <v>12.1012183131449</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1532,16 +1532,16 @@
         <v>44396</v>
       </c>
       <c r="B56" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C56" t="n">
-        <v>12.02667163783278</v>
+        <v>12.02667065225621</v>
       </c>
       <c r="D56" t="n">
-        <v>11.53798501475665</v>
+        <v>11.53798406922757</v>
       </c>
       <c r="E56" t="n">
-        <v>12.01010644093992</v>
+        <v>12.01010545672085</v>
       </c>
       <c r="F56" t="n">
         <v>557721</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879039764404</v>
+        <v>10.85879135131836</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525564966597</v>
+        <v>11.16525663025563</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798291576008</v>
+        <v>10.71798385706797</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76767933141345</v>
+        <v>10.76768027708593</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697479248047</v>
+        <v>11.15697574615479</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697479248047</v>
+        <v>11.15697574615479</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707552191041</v>
+        <v>10.86707645080476</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707552191041</v>
+        <v>10.86707645080476</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.29778099060059</v>
+        <v>11.2977819442749</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47172053283982</v>
+        <v>11.47172150119681</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05757983553765</v>
+        <v>11.05758076893598</v>
       </c>
       <c r="E62" t="n">
-        <v>11.1818221279454</v>
+        <v>11.18182307183133</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C63" t="n">
-        <v>11.51313582037561</v>
+        <v>11.5131367879722</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495313710418</v>
+        <v>11.21495407964066</v>
       </c>
       <c r="E63" t="n">
-        <v>11.3640448948254</v>
+        <v>11.36404584989197</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1712,16 +1712,16 @@
         <v>44407</v>
       </c>
       <c r="B65" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626655578613</v>
       </c>
       <c r="C65" t="n">
-        <v>11.92727785279649</v>
+        <v>11.92727686765228</v>
       </c>
       <c r="D65" t="n">
-        <v>11.09899471480624</v>
+        <v>11.09899379807482</v>
       </c>
       <c r="E65" t="n">
-        <v>11.2066709901555</v>
+        <v>11.20667006453047</v>
       </c>
       <c r="F65" t="n">
         <v>977013</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071319580078</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727922662398</v>
+        <v>11.92727827162325</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61253213052343</v>
+        <v>11.61253120072406</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61253213052343</v>
+        <v>11.61253120072406</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273170471191</v>
+        <v>11.8527307510376</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556018308474</v>
+        <v>11.93555922274602</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030754683281</v>
+        <v>11.43030662714687</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727758489877</v>
+        <v>11.92727662522647</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515727996826</v>
+        <v>11.45515632629395</v>
       </c>
       <c r="C68" t="n">
-        <v>11.8527328495186</v>
+        <v>11.85273186274499</v>
       </c>
       <c r="D68" t="n">
-        <v>11.4468746809823</v>
+        <v>11.44687372799754</v>
       </c>
       <c r="E68" t="n">
-        <v>11.8527328495186</v>
+        <v>11.85273186274499</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="C69" t="n">
-        <v>11.66222697699479</v>
+        <v>11.6622279694364</v>
       </c>
       <c r="D69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768109665717</v>
+        <v>11.58768208275502</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1832,16 +1832,16 @@
         <v>44417</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C71" t="n">
-        <v>12.03495292569004</v>
+        <v>12.0349548369848</v>
       </c>
       <c r="D71" t="n">
-        <v>11.59596360543989</v>
+        <v>11.59596544701789</v>
       </c>
       <c r="E71" t="n">
-        <v>11.62909482778872</v>
+        <v>11.62909667462835</v>
       </c>
       <c r="F71" t="n">
         <v>438360</v>
@@ -1852,16 +1852,16 @@
         <v>44418</v>
       </c>
       <c r="B72" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2503090271009</v>
+        <v>12.2503080475979</v>
       </c>
       <c r="D72" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="E72" t="n">
-        <v>12.05152082987733</v>
+        <v>12.05151986626892</v>
       </c>
       <c r="F72" t="n">
         <v>351025</v>
@@ -1872,16 +1872,16 @@
         <v>44419</v>
       </c>
       <c r="B73" t="n">
-        <v>11.88586330413818</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C73" t="n">
-        <v>12.01838819869508</v>
+        <v>12.01838916300267</v>
       </c>
       <c r="D73" t="n">
-        <v>11.71192375590401</v>
+        <v>11.71192469562211</v>
       </c>
       <c r="E73" t="n">
-        <v>12.01838819869508</v>
+        <v>12.01838916300267</v>
       </c>
       <c r="F73" t="n">
         <v>262426</v>
@@ -1912,16 +1912,16 @@
         <v>44421</v>
       </c>
       <c r="B75" t="n">
-        <v>12.50707530975342</v>
+        <v>12.50707721710205</v>
       </c>
       <c r="C75" t="n">
-        <v>12.61475157586925</v>
+        <v>12.61475349963868</v>
       </c>
       <c r="D75" t="n">
-        <v>11.87758041186906</v>
+        <v>11.87758222321873</v>
       </c>
       <c r="E75" t="n">
-        <v>12.00182187330842</v>
+        <v>12.0018237036051</v>
       </c>
       <c r="F75" t="n">
         <v>464803</v>
@@ -1932,16 +1932,16 @@
         <v>44424</v>
       </c>
       <c r="B76" t="n">
-        <v>11.74505519866943</v>
+        <v>11.74505615234375</v>
       </c>
       <c r="C76" t="n">
-        <v>12.50707585310151</v>
+        <v>12.50707686865033</v>
       </c>
       <c r="D76" t="n">
-        <v>11.40545869373233</v>
+        <v>11.40545961983211</v>
       </c>
       <c r="E76" t="n">
-        <v>12.50707585310151</v>
+        <v>12.50707686865033</v>
       </c>
       <c r="F76" t="n">
         <v>788964</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859004974365</v>
+        <v>11.43859195709229</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727661782967</v>
+        <v>11.92727860666524</v>
       </c>
       <c r="D77" t="n">
-        <v>11.32262952368701</v>
+        <v>11.32263141169959</v>
       </c>
       <c r="E77" t="n">
-        <v>11.84444814617262</v>
+        <v>11.8444501211968</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495597839355</v>
+        <v>12.03495502471924</v>
       </c>
       <c r="C78" t="n">
-        <v>12.33313871950986</v>
+        <v>12.33313774220694</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313805382515</v>
+        <v>11.51313714150074</v>
       </c>
       <c r="E78" t="n">
-        <v>11.57940051533047</v>
+        <v>11.5793995977553</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071319580078</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C82" t="n">
-        <v>12.32485564466939</v>
+        <v>12.32485465783526</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990484640257</v>
+        <v>11.76990390400258</v>
       </c>
       <c r="E82" t="n">
-        <v>12.0101077163977</v>
+        <v>12.010106754765</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010503212249</v>
+        <v>12.01010696614738</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071053374038</v>
+        <v>11.91071245175947</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848892211914</v>
+        <v>11.72848796844482</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697434704441</v>
+        <v>11.97697337316509</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081265360541</v>
+        <v>11.62081170868654</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444862065007</v>
+        <v>11.84444765754676</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2112,16 +2112,16 @@
         <v>44435</v>
       </c>
       <c r="B85" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C85" t="n">
-        <v>11.89414625217492</v>
+        <v>11.8941472165949</v>
       </c>
       <c r="D85" t="n">
-        <v>11.355762395888</v>
+        <v>11.35576331665388</v>
       </c>
       <c r="E85" t="n">
-        <v>11.87758105595312</v>
+        <v>11.87758201902993</v>
       </c>
       <c r="F85" t="n">
         <v>370831</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C86" t="n">
-        <v>11.96869289533168</v>
+        <v>11.9686919095953</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55455048079756</v>
+        <v>11.55454952916977</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101495216464</v>
+        <v>11.86101397529656</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58767986297607</v>
       </c>
       <c r="C89" t="n">
-        <v>11.6290964280881</v>
+        <v>11.62909451392255</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010621525682</v>
+        <v>11.19010437334967</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55455054341664</v>
+        <v>11.55454864152145</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889312744141</v>
+        <v>11.38889408111572</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111611650414</v>
+        <v>11.57111708543731</v>
       </c>
       <c r="D93" t="n">
-        <v>11.18182317547715</v>
+        <v>11.181824111812</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141886201694</v>
+        <v>11.52141982678859</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909661287153</v>
+        <v>11.62909565647244</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38061115885603</v>
+        <v>11.38061022289286</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485430194932</v>
+        <v>11.50485335576816</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444975488591</v>
+        <v>11.84444877938214</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545954443371</v>
+        <v>11.40545860508498</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596513833651</v>
+        <v>11.59596418329782</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364284515381</v>
+        <v>11.70364093780518</v>
       </c>
       <c r="C96" t="n">
-        <v>11.83616775881459</v>
+        <v>11.8361658298683</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172258190522</v>
+        <v>11.47172071235275</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313724155255</v>
+        <v>11.51313536525071</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84445000728142</v>
+        <v>11.84444903317125</v>
       </c>
       <c r="D97" t="n">
-        <v>11.58768195445007</v>
+        <v>11.587681001457</v>
       </c>
       <c r="E97" t="n">
-        <v>11.7036424987275</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192509754336</v>
+        <v>11.71192413433229</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313690076518</v>
+        <v>11.51313595390284</v>
       </c>
       <c r="E98" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889312744141</v>
+        <v>11.38889408111572</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424734210526</v>
+        <v>11.60424831381274</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606547952412</v>
+        <v>11.30606642626268</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596474374774</v>
+        <v>11.59596571476166</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81960105895996</v>
+        <v>11.81960010528564</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05152047689957</v>
+        <v>12.05151950451265</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58768164102035</v>
+        <v>11.58768070605864</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535875139833</v>
+        <v>11.69535780774861</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.05152130126953</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424908162149</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="D104" t="n">
-        <v>11.99354144281858</v>
+        <v>11.99354049373239</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34142059352426</v>
+        <v>12.34141961690932</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2512,16 +2512,16 @@
         <v>44466</v>
       </c>
       <c r="B105" t="n">
-        <v>11.88586330413818</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C105" t="n">
-        <v>12.16747912115709</v>
+        <v>12.16748009742714</v>
       </c>
       <c r="D105" t="n">
-        <v>11.88586330413818</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="E105" t="n">
-        <v>12.05151942233431</v>
+        <v>12.05152038930021</v>
       </c>
       <c r="F105" t="n">
         <v>207539</v>
@@ -2532,16 +2532,16 @@
         <v>44467</v>
       </c>
       <c r="B106" t="n">
-        <v>11.9438419342041</v>
+        <v>11.94384288787842</v>
       </c>
       <c r="C106" t="n">
-        <v>12.09293285183314</v>
+        <v>12.09293381741185</v>
       </c>
       <c r="D106" t="n">
-        <v>11.74505459881269</v>
+        <v>11.74505553661453</v>
       </c>
       <c r="E106" t="n">
-        <v>11.86101346170553</v>
+        <v>11.86101440876628</v>
       </c>
       <c r="F106" t="n">
         <v>282337</v>
@@ -2572,16 +2572,16 @@
         <v>44469</v>
       </c>
       <c r="B108" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="D108" t="n">
-        <v>11.51313638724631</v>
+        <v>11.51313544375356</v>
       </c>
       <c r="E108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="F108" t="n">
         <v>264322</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C109" t="n">
-        <v>11.76162152260959</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889375767189</v>
+        <v>11.38889282102754</v>
       </c>
       <c r="E109" t="n">
-        <v>11.76162152260959</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545794086782</v>
+        <v>11.40545977752449</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596350798623</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2672,16 +2672,16 @@
         <v>44476</v>
       </c>
       <c r="B113" t="n">
-        <v>11.3309154510498</v>
+        <v>11.33091259002686</v>
       </c>
       <c r="C113" t="n">
-        <v>11.5297036604115</v>
+        <v>11.52970074919511</v>
       </c>
       <c r="D113" t="n">
-        <v>11.28121819066659</v>
+        <v>11.28121534219206</v>
       </c>
       <c r="E113" t="n">
-        <v>11.45515776983669</v>
+        <v>11.45515487744292</v>
       </c>
       <c r="F113" t="n">
         <v>136744</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677289399093</v>
+        <v>11.73677192873634</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687444589615</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687444589615</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667236328125</v>
+        <v>12.02667045593262</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495496222729</v>
+        <v>12.03495305356509</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768213657487</v>
+        <v>11.58768029884711</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768213657487</v>
+        <v>11.58768029884711</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22546032458287</v>
+        <v>12.22545936636416</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727844663413</v>
+        <v>11.92727751178659</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465198439289</v>
+        <v>12.08465103721058</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D122" t="n">
-        <v>11.41374053834268</v>
+        <v>11.41374237633313</v>
       </c>
       <c r="E122" t="n">
-        <v>11.67879114707672</v>
+        <v>11.6787930277491</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030643463135</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81960031587073</v>
+        <v>11.81959932971621</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212553603579</v>
+        <v>11.13212460723993</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76162046503097</v>
+        <v>11.76161948371394</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172147956523</v>
+        <v>11.47172236012447</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141873349808</v>
+        <v>11.52141961787203</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C125" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D125" t="n">
-        <v>11.84445005892279</v>
+        <v>11.8444491374672</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030905306453</v>
+        <v>12.25030810003457</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.05152130126953</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030950626865</v>
+        <v>12.25030853686361</v>
       </c>
       <c r="D126" t="n">
-        <v>11.84445049711202</v>
+        <v>11.84444955982386</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717744529286</v>
+        <v>12.21717647850966</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C127" t="n">
-        <v>12.0598042338624</v>
+        <v>12.05980324204109</v>
       </c>
       <c r="D127" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010697662508</v>
+        <v>12.01010598889097</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030643463135</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72848924057554</v>
+        <v>11.72848826202277</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030643463135</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596434275382</v>
+        <v>11.59596337525811</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -3012,16 +3012,16 @@
         <v>44503</v>
       </c>
       <c r="B130" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C130" t="n">
-        <v>12.01838773060111</v>
+        <v>12.01838963926511</v>
       </c>
       <c r="D130" t="n">
-        <v>11.43859009124023</v>
+        <v>11.43859190782543</v>
       </c>
       <c r="E130" t="n">
-        <v>11.50485253593789</v>
+        <v>11.50485436304635</v>
       </c>
       <c r="F130" t="n">
         <v>128737</v>
@@ -3032,16 +3032,16 @@
         <v>44504</v>
       </c>
       <c r="B131" t="n">
-        <v>11.77818584442139</v>
+        <v>11.77818775177002</v>
       </c>
       <c r="C131" t="n">
-        <v>12.08465027787762</v>
+        <v>12.08465223485482</v>
       </c>
       <c r="D131" t="n">
-        <v>11.73677119200559</v>
+        <v>11.73677309264758</v>
       </c>
       <c r="E131" t="n">
-        <v>12.01010523500273</v>
+        <v>12.01010717990818</v>
       </c>
       <c r="F131" t="n">
         <v>218179</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020588356491</v>
+        <v>11.72020683994276</v>
       </c>
       <c r="D133" t="n">
-        <v>11.38060939858799</v>
+        <v>11.3806103272545</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859007784422</v>
+        <v>11.43859101124201</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.05152130126953</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C134" t="n">
-        <v>12.05152130126953</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283380401568</v>
+        <v>11.56283288901272</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707695224708</v>
+        <v>11.68707602741238</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374080657959</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374080657959</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929572969245</v>
+        <v>11.86929758022087</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05151785205058</v>
+        <v>12.05151973098904</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232845306396</v>
+        <v>12.19232749938965</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374310913982</v>
+        <v>12.23374215222609</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465134587198</v>
+        <v>12.08465040062008</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374310913982</v>
+        <v>12.23374215222609</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3152,16 +3152,16 @@
         <v>44512</v>
       </c>
       <c r="B137" t="n">
-        <v>11.88586330413818</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C137" t="n">
-        <v>12.23374240060653</v>
+        <v>12.23374338219328</v>
       </c>
       <c r="D137" t="n">
-        <v>11.88586330413818</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="E137" t="n">
-        <v>12.14263132755591</v>
+        <v>12.14263230183227</v>
       </c>
       <c r="F137" t="n">
         <v>236720</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576306753439</v>
+        <v>12.17576211321089</v>
       </c>
       <c r="D138" t="n">
-        <v>11.68707642451825</v>
+        <v>11.6870755084975</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242981810988</v>
+        <v>11.90242888520996</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.05152130126953</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364276803549</v>
+        <v>12.52364177700074</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131926830736</v>
+        <v>11.81131833364097</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424908162149</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313655853271</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566049440077</v>
+        <v>12.46566145832273</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010514638517</v>
+        <v>12.01010607508077</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05151896632442</v>
+        <v>12.05151989822239</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798263549805</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49050834903954</v>
+        <v>12.49050931294096</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293204058597</v>
+        <v>12.09293297380614</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485224732631</v>
+        <v>12.32485319844393</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.98748111724854</v>
+        <v>12.9874792098999</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374357221301</v>
+        <v>13.05374165513303</v>
       </c>
       <c r="D142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798348367227</v>
       </c>
       <c r="E142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798348367227</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010673522949</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010673522949</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283391635538</v>
+        <v>12.38283207549919</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131937051061</v>
+        <v>12.63131749271409</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3332,16 +3332,16 @@
         <v>44526</v>
       </c>
       <c r="B146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="C146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="D146" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152193682892</v>
       </c>
       <c r="E146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="F146" t="n">
         <v>386739</v>
@@ -3352,16 +3352,16 @@
         <v>44529</v>
       </c>
       <c r="B147" t="n">
-        <v>12.67273235321045</v>
+        <v>12.6727352142334</v>
       </c>
       <c r="C147" t="n">
-        <v>12.98747938848116</v>
+        <v>12.98748232056206</v>
       </c>
       <c r="D147" t="n">
-        <v>12.35798365359779</v>
+        <v>12.3579864435624</v>
       </c>
       <c r="E147" t="n">
-        <v>12.75555916263431</v>
+        <v>12.75556204235641</v>
       </c>
       <c r="F147" t="n">
         <v>340279</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37454986572266</v>
+        <v>12.37455177307129</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818666500764</v>
+        <v>12.59818860682649</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90242847360634</v>
+        <v>11.90243030818464</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818666500764</v>
+        <v>12.59818860682649</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808597564697</v>
+        <v>11.24808502197266</v>
       </c>
       <c r="C150" t="n">
-        <v>11.8196010912967</v>
+        <v>11.8196000891662</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182352238896</v>
+        <v>11.18182257433274</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333863803869</v>
+        <v>11.75333764152628</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58767986297607</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67051025368041</v>
+        <v>11.6705083326981</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2480860703887</v>
+        <v>11.248084218938</v>
       </c>
       <c r="E151" t="n">
-        <v>11.33919715242866</v>
+        <v>11.33919528598094</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3472,16 +3472,16 @@
         <v>44537</v>
       </c>
       <c r="B153" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010704040527</v>
       </c>
       <c r="C153" t="n">
-        <v>12.09293277284322</v>
+        <v>12.09293469334588</v>
       </c>
       <c r="D153" t="n">
-        <v>11.78646834198837</v>
+        <v>11.78647021382081</v>
       </c>
       <c r="E153" t="n">
-        <v>11.89414543875028</v>
+        <v>11.89414732768312</v>
       </c>
       <c r="F153" t="n">
         <v>308042</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374080657959</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626568386882</v>
+        <v>12.36626761187925</v>
       </c>
       <c r="D154" t="n">
-        <v>11.8941443522269</v>
+        <v>11.89414620662944</v>
       </c>
       <c r="E154" t="n">
-        <v>12.01010403594042</v>
+        <v>12.0101059084221</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C155" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99354099911369</v>
+        <v>11.99354006605936</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22546042433754</v>
+        <v>12.22545947324071</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000495910645</v>
+        <v>12.30000400543213</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626824363818</v>
+        <v>12.36626728482618</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778279902904</v>
+        <v>12.11778185948322</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668737329261</v>
+        <v>12.2668727818206</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485485076904</v>
+        <v>12.32485198974609</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303589683919</v>
+        <v>12.62303296659815</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374376753817</v>
+        <v>12.23374092766524</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000539004934</v>
+        <v>12.30000253479481</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192490357129</v>
+        <v>12.53192392863263</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606590942955</v>
+        <v>12.12606496606526</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909725070942</v>
+        <v>12.44909628221446</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3612,16 +3612,16 @@
         <v>44546</v>
       </c>
       <c r="B160" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="C160" t="n">
-        <v>12.56505530473681</v>
+        <v>12.56505434089677</v>
       </c>
       <c r="D160" t="n">
-        <v>12.31657153032308</v>
+        <v>12.31657058554373</v>
       </c>
       <c r="E160" t="n">
-        <v>12.54849010812237</v>
+        <v>12.54848914555302</v>
       </c>
       <c r="F160" t="n">
         <v>252523</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606685638428</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606685638428</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25859120464801</v>
+        <v>12.25858939858541</v>
       </c>
       <c r="E161" t="n">
-        <v>12.42424816866975</v>
+        <v>12.42424633820085</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202507019043</v>
+        <v>13.06202602386475</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16141957643138</v>
+        <v>13.16142053736261</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273389729204</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273389729204</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.82182312011719</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="C164" t="n">
-        <v>12.82182312011719</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43253018818525</v>
+        <v>12.43252926346614</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72242944563595</v>
+        <v>12.72242849935444</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3812,16 +3812,16 @@
         <v>44564</v>
       </c>
       <c r="B170" t="n">
-        <v>12.92949867248535</v>
+        <v>12.92949962615967</v>
       </c>
       <c r="C170" t="n">
-        <v>13.6004090584999</v>
+        <v>13.60041006166028</v>
       </c>
       <c r="D170" t="n">
-        <v>12.78869118285713</v>
+        <v>12.78869212614555</v>
       </c>
       <c r="E170" t="n">
-        <v>13.16970149539972</v>
+        <v>13.1697024667913</v>
       </c>
       <c r="F170" t="n">
         <v>289922</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586274131581</v>
+        <v>11.88586465533357</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202396798849</v>
+        <v>11.42202580731284</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55454885627004</v>
+        <v>11.55455071693529</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071108497109</v>
+        <v>11.91071205965744</v>
       </c>
       <c r="D178" t="n">
-        <v>11.59596404465037</v>
+        <v>11.5959649935801</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273123562185</v>
+        <v>11.85273220556355</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.57939910888672</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818730142888</v>
+        <v>11.77818633138246</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798528351884</v>
+        <v>11.53798433325535</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333867333973</v>
+        <v>11.75333770533982</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4032,16 +4032,16 @@
         <v>44579</v>
       </c>
       <c r="B181" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="C181" t="n">
-        <v>11.72020740703434</v>
+        <v>11.72020643480869</v>
       </c>
       <c r="D181" t="n">
-        <v>11.46343936054156</v>
+        <v>11.46343840961558</v>
       </c>
       <c r="E181" t="n">
-        <v>11.57939906978533</v>
+        <v>11.57939810924015</v>
       </c>
       <c r="F181" t="n">
         <v>311203</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010511899131</v>
+        <v>12.01010609902517</v>
       </c>
       <c r="D182" t="n">
-        <v>11.5628315373786</v>
+        <v>11.56283248091458</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596359185958</v>
+        <v>11.59596453809916</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4072,16 +4072,16 @@
         <v>44581</v>
       </c>
       <c r="B183" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C183" t="n">
-        <v>12.21717590021027</v>
+        <v>12.21717689082265</v>
       </c>
       <c r="D183" t="n">
-        <v>11.67050944581244</v>
+        <v>11.67051039209914</v>
       </c>
       <c r="E183" t="n">
-        <v>11.67050944581244</v>
+        <v>11.67051039209914</v>
       </c>
       <c r="F183" t="n">
         <v>1415690</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434741069664</v>
+        <v>12.13434840086876</v>
       </c>
       <c r="D184" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84444817527024</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.5711145401001</v>
+        <v>11.57111549377441</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101293265804</v>
+        <v>11.86101391022536</v>
       </c>
       <c r="D185" t="n">
-        <v>11.488286071296</v>
+        <v>11.48828701814372</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707422999165</v>
+        <v>11.68707519322319</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616733551025</v>
+        <v>11.83616542816162</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444993427506</v>
+        <v>11.84444802559172</v>
       </c>
       <c r="D186" t="n">
-        <v>11.46343957286996</v>
+        <v>11.46343772558484</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172217163477</v>
+        <v>11.47172032301494</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374131522813</v>
+        <v>11.41374227447133</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242823980222</v>
+        <v>11.08242917120093</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818227449497</v>
+        <v>11.1818236847018</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4192,16 +4192,16 @@
         <v>44589</v>
       </c>
       <c r="B189" t="n">
-        <v>11.53798484802246</v>
+        <v>11.53798389434814</v>
       </c>
       <c r="C189" t="n">
-        <v>11.57939867182719</v>
+        <v>11.57939771472981</v>
       </c>
       <c r="D189" t="n">
-        <v>11.14040847794448</v>
+        <v>11.14040755713192</v>
       </c>
       <c r="E189" t="n">
-        <v>11.36404529013473</v>
+        <v>11.36404435083742</v>
       </c>
       <c r="F189" t="n">
         <v>538653</v>
@@ -4232,16 +4232,16 @@
         <v>44593</v>
       </c>
       <c r="B191" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C191" t="n">
-        <v>11.81960037266376</v>
+        <v>11.81960133103929</v>
       </c>
       <c r="D191" t="n">
-        <v>11.61253042686511</v>
+        <v>11.61253136845066</v>
       </c>
       <c r="E191" t="n">
-        <v>11.68707547420526</v>
+        <v>11.6870764218352</v>
       </c>
       <c r="F191" t="n">
         <v>160869</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586282728598</v>
+        <v>11.88586379718157</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626634230906</v>
+        <v>11.54626728449331</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788214802975</v>
+        <v>11.82788311319406</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.48828792572021</v>
+        <v>11.48828887939453</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84444965011515</v>
+        <v>11.84445063335543</v>
       </c>
       <c r="D193" t="n">
-        <v>11.48828792572021</v>
+        <v>11.48828887939453</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67051008720073</v>
+        <v>11.67051105600181</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4312,16 +4312,16 @@
         <v>44599</v>
       </c>
       <c r="B195" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C195" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="D195" t="n">
-        <v>11.15697421602923</v>
+        <v>11.15697512067666</v>
       </c>
       <c r="E195" t="n">
-        <v>11.43859087351007</v>
+        <v>11.43859180099198</v>
       </c>
       <c r="F195" t="n">
         <v>474179</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.59596538543701</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697574919057</v>
+        <v>11.97697476418123</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970293056798</v>
+        <v>11.52970198234322</v>
       </c>
       <c r="E196" t="n">
-        <v>11.7036424987275</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313503672479</v>
+        <v>11.51313689072104</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596350798623</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4392,16 +4392,16 @@
         <v>44603</v>
       </c>
       <c r="B199" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626655578613</v>
       </c>
       <c r="C199" t="n">
-        <v>11.81960074527618</v>
+        <v>11.81959976902566</v>
       </c>
       <c r="D199" t="n">
-        <v>11.52141888217337</v>
+        <v>11.52141793055145</v>
       </c>
       <c r="E199" t="n">
-        <v>11.71192446992692</v>
+        <v>11.71192350257001</v>
       </c>
       <c r="F199" t="n">
         <v>419186</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.604248046875</v>
+        <v>11.60424613952637</v>
       </c>
       <c r="C200" t="n">
-        <v>11.8444500711998</v>
+        <v>11.84444812437002</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313696289563</v>
+        <v>11.5131350705226</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253147790664</v>
+        <v>11.61252956919649</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84444817527024</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081221663484</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081221663484</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4472,16 +4472,16 @@
         <v>44609</v>
       </c>
       <c r="B203" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C203" t="n">
-        <v>11.9852573279079</v>
+        <v>11.98525829971548</v>
       </c>
       <c r="D203" t="n">
-        <v>11.68707547420526</v>
+        <v>11.6870764218352</v>
       </c>
       <c r="E203" t="n">
-        <v>11.69535807231616</v>
+        <v>11.69535902061768</v>
       </c>
       <c r="F203" t="n">
         <v>1539476</v>
@@ -4492,16 +4492,16 @@
         <v>44610</v>
       </c>
       <c r="B204" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="C204" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="D204" t="n">
-        <v>11.48000486688096</v>
+        <v>11.48000394896948</v>
       </c>
       <c r="E204" t="n">
-        <v>11.76162154896194</v>
+        <v>11.76162060853312</v>
       </c>
       <c r="F204" t="n">
         <v>336065</v>
@@ -4512,16 +4512,16 @@
         <v>44613</v>
       </c>
       <c r="B205" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="C205" t="n">
-        <v>11.92727819751663</v>
+        <v>11.92727720811385</v>
       </c>
       <c r="D205" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="E205" t="n">
-        <v>11.92727819751663</v>
+        <v>11.92727720811385</v>
       </c>
       <c r="F205" t="n">
         <v>449843</v>
@@ -4532,16 +4532,16 @@
         <v>44614</v>
       </c>
       <c r="B206" t="n">
-        <v>11.54626750946045</v>
+        <v>11.54626655578613</v>
       </c>
       <c r="C206" t="n">
-        <v>11.72848966667094</v>
+        <v>11.72848869794582</v>
       </c>
       <c r="D206" t="n">
-        <v>11.51313628380136</v>
+        <v>11.51313533286355</v>
       </c>
       <c r="E206" t="n">
-        <v>11.51313628380136</v>
+        <v>11.51313533286355</v>
       </c>
       <c r="F206" t="n">
         <v>213649</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.14263153076172</v>
+        <v>12.1426305770874</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576192278439</v>
+        <v>12.17576096650803</v>
       </c>
       <c r="D208" t="n">
-        <v>11.42202469999357</v>
+        <v>11.42202380291525</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596425113861</v>
+        <v>11.59596334039918</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.7389965057373</v>
+        <v>12.73899459838867</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202703527593</v>
+        <v>13.06202507956149</v>
       </c>
       <c r="D213" t="n">
-        <v>12.10950147758278</v>
+        <v>12.10949966448541</v>
       </c>
       <c r="E213" t="n">
-        <v>12.84667445847837</v>
+        <v>12.84667253500764</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.15919780731201</v>
+        <v>12.1591968536377</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697538601619</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="D214" t="n">
-        <v>12.1426326098286</v>
+        <v>12.14263165745353</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697538601619</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081293822948</v>
+        <v>12.44081389317532</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293382504164</v>
+        <v>12.09293475328459</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576230420604</v>
+        <v>12.17576323880683</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919710767578</v>
+        <v>12.15919804100504</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111568429664</v>
+        <v>12.39111663542777</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071319580078</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45738056257043</v>
+        <v>12.45737956512522</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990484640257</v>
+        <v>11.76990390400258</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081453174723</v>
+        <v>12.44081353562843</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.79475212097168</v>
+        <v>11.794753074646</v>
       </c>
       <c r="C220" t="n">
-        <v>11.80303471876141</v>
+        <v>11.80303567310543</v>
       </c>
       <c r="D220" t="n">
-        <v>11.4634382233306</v>
+        <v>11.46343915021626</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596394882123</v>
+        <v>11.59596488642237</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222667694092</v>
+        <v>11.6622257232666</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444882573873</v>
+        <v>11.84444785716326</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404482760432</v>
+        <v>11.36404389831371</v>
       </c>
       <c r="E222" t="n">
-        <v>11.5379843784125</v>
+        <v>11.53798343489805</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.96869087219238</v>
+        <v>11.96869277954102</v>
       </c>
       <c r="C225" t="n">
-        <v>12.20889201732872</v>
+        <v>12.20889396295617</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798333318461</v>
+        <v>11.53798517189504</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677065995349</v>
+        <v>11.73677253034297</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10949925876433</v>
+        <v>12.10950024971806</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495338152774</v>
+        <v>12.03495436638118</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.604248046875</v>
+        <v>11.60424613952637</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78647021483374</v>
+        <v>11.7864682775339</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030847777682</v>
+        <v>11.43030659901801</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535913085437</v>
+        <v>11.69535720853013</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -4972,16 +4972,16 @@
         <v>44648</v>
       </c>
       <c r="B228" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C228" t="n">
-        <v>11.76990311965631</v>
+        <v>11.76990407400221</v>
       </c>
       <c r="D228" t="n">
-        <v>11.52970194924304</v>
+        <v>11.52970288411256</v>
       </c>
       <c r="E228" t="n">
-        <v>11.65394341741962</v>
+        <v>11.65394436236309</v>
       </c>
       <c r="F228" t="n">
         <v>221866</v>
@@ -4992,16 +4992,16 @@
         <v>44649</v>
       </c>
       <c r="B229" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C229" t="n">
-        <v>12.17576207748474</v>
+        <v>12.17576306473914</v>
       </c>
       <c r="D229" t="n">
-        <v>11.76162052154541</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="E229" t="n">
-        <v>11.83616640105658</v>
+        <v>11.83616736077534</v>
       </c>
       <c r="F229" t="n">
         <v>841955</v>
@@ -5092,16 +5092,16 @@
         <v>44656</v>
       </c>
       <c r="B234" t="n">
-        <v>11.19010639190674</v>
+        <v>11.19010543823242</v>
       </c>
       <c r="C234" t="n">
-        <v>11.57939935443586</v>
+        <v>11.57939836758414</v>
       </c>
       <c r="D234" t="n">
-        <v>11.19010639190674</v>
+        <v>11.19010543823242</v>
       </c>
       <c r="E234" t="n">
-        <v>11.52141949838869</v>
+        <v>11.52141851647829</v>
       </c>
       <c r="F234" t="n">
         <v>602179</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444744110107</v>
+        <v>11.02444839477539</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495217263222</v>
+        <v>11.21495314278623</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192255519609</v>
+        <v>10.89192349740629</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495217263222</v>
+        <v>11.21495314278623</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364028930664</v>
+        <v>10.88364219665527</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.07414696737361</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394303949338</v>
+        <v>10.83394493813262</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.07414696737361</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192390441895</v>
+        <v>10.89192295074463</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303498280762</v>
+        <v>10.98303402115581</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313571876591</v>
+        <v>10.69313478249707</v>
       </c>
       <c r="E237" t="n">
-        <v>10.9333377283516</v>
+        <v>10.93333677105118</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5172,16 +5172,16 @@
         <v>44662</v>
       </c>
       <c r="B238" t="n">
-        <v>10.8422269821167</v>
+        <v>10.84222602844238</v>
       </c>
       <c r="C238" t="n">
-        <v>11.07414640045497</v>
+        <v>11.07414542638119</v>
       </c>
       <c r="D238" t="n">
-        <v>10.80909575552138</v>
+        <v>10.80909480476127</v>
       </c>
       <c r="E238" t="n">
-        <v>10.8422269821167</v>
+        <v>10.84222602844238</v>
       </c>
       <c r="F238" t="n">
         <v>406860</v>
@@ -5212,16 +5212,16 @@
         <v>44664</v>
       </c>
       <c r="B240" t="n">
-        <v>10.80909538269043</v>
+        <v>10.8090934753418</v>
       </c>
       <c r="C240" t="n">
-        <v>10.8919238624073</v>
+        <v>10.89192194044294</v>
       </c>
       <c r="D240" t="n">
-        <v>10.6517218537481</v>
+        <v>10.65171997416924</v>
       </c>
       <c r="E240" t="n">
-        <v>10.81737798101081</v>
+        <v>10.81737607220064</v>
       </c>
       <c r="F240" t="n">
         <v>281389</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000556945801</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82566254625604</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000556945801</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82566254625604</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5292,16 +5292,16 @@
         <v>44671</v>
       </c>
       <c r="B244" t="n">
-        <v>10.6517219543457</v>
+        <v>10.65172100067139</v>
       </c>
       <c r="C244" t="n">
-        <v>10.90848916207064</v>
+        <v>10.90848818540733</v>
       </c>
       <c r="D244" t="n">
-        <v>10.6517219543457</v>
+        <v>10.65172100067139</v>
       </c>
       <c r="E244" t="n">
-        <v>10.76768082843923</v>
+        <v>10.76767986438283</v>
       </c>
       <c r="F244" t="n">
         <v>446683</v>
@@ -5312,16 +5312,16 @@
         <v>44673</v>
       </c>
       <c r="B245" t="n">
-        <v>10.23757934570312</v>
+        <v>10.23757743835449</v>
       </c>
       <c r="C245" t="n">
-        <v>10.64343830945661</v>
+        <v>10.64343632649298</v>
       </c>
       <c r="D245" t="n">
-        <v>10.23757934570312</v>
+        <v>10.23757743835449</v>
       </c>
       <c r="E245" t="n">
-        <v>10.64343830945661</v>
+        <v>10.64343632649298</v>
       </c>
       <c r="F245" t="n">
         <v>624092</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434661865234</v>
+        <v>10.49434947967529</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919607588605</v>
+        <v>10.51919894368359</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707386403591</v>
+        <v>10.04707660312106</v>
       </c>
       <c r="E246" t="n">
-        <v>10.1547501297465</v>
+        <v>10.1547528981869</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5352,16 +5352,16 @@
         <v>44677</v>
       </c>
       <c r="B247" t="n">
-        <v>10.35354042053223</v>
+        <v>10.35353946685791</v>
       </c>
       <c r="C247" t="n">
-        <v>10.66828749142892</v>
+        <v>10.66828650876296</v>
       </c>
       <c r="D247" t="n">
-        <v>10.35354042053223</v>
+        <v>10.35353946685791</v>
       </c>
       <c r="E247" t="n">
-        <v>10.48606532782114</v>
+        <v>10.48606436193982</v>
       </c>
       <c r="F247" t="n">
         <v>670551</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525775909424</v>
+        <v>10.34525680541992</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061114821748</v>
+        <v>10.56061017469088</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32869089752705</v>
+        <v>10.32868994537994</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151938016555</v>
+        <v>10.41151842038292</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838649749756</v>
+        <v>10.37838840484619</v>
       </c>
       <c r="C249" t="n">
-        <v>10.5523260336321</v>
+        <v>10.55232797294748</v>
       </c>
       <c r="D249" t="n">
-        <v>10.23757818269756</v>
+        <v>10.23758006416832</v>
       </c>
       <c r="E249" t="n">
-        <v>10.34525610833395</v>
+        <v>10.34525800959385</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394336700439</v>
+        <v>10.83394241333008</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525643404281</v>
+        <v>11.16525545120416</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576152345272</v>
+        <v>10.53576059602632</v>
       </c>
       <c r="E250" t="n">
-        <v>10.56889274693946</v>
+        <v>10.56889181659663</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5492,16 +5492,16 @@
         <v>44686</v>
       </c>
       <c r="B254" t="n">
-        <v>10.81742763519287</v>
+        <v>10.81742858886719</v>
       </c>
       <c r="C254" t="n">
-        <v>10.9669772875351</v>
+        <v>10.96697825439385</v>
       </c>
       <c r="D254" t="n">
-        <v>10.68449498188042</v>
+        <v>10.68449592383528</v>
       </c>
       <c r="E254" t="n">
-        <v>10.83404463422265</v>
+        <v>10.83404558936194</v>
       </c>
       <c r="F254" t="n">
         <v>391269</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.85065937042236</v>
+        <v>10.850661277771</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344299676728</v>
+        <v>11.03344493624595</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633450406758</v>
+        <v>10.62633637198398</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772589987437</v>
+        <v>10.71772778385571</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727809906006</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727809906006</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340354046572</v>
+        <v>10.49340261960133</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802811508668</v>
+        <v>10.61802718328567</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.16637706756592</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="C261" t="n">
-        <v>11.16637706756592</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75926935728049</v>
+        <v>10.75927027618541</v>
       </c>
       <c r="E261" t="n">
-        <v>10.87558584593347</v>
+        <v>10.8755867747725</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085115716256</v>
+        <v>11.34085213080912</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95866854966046</v>
+        <v>10.95866949049548</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806751769784</v>
+        <v>11.15806847565188</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5672,16 +5672,16 @@
         <v>44699</v>
       </c>
       <c r="B263" t="n">
-        <v>11.11652755737305</v>
+        <v>11.11652660369873</v>
       </c>
       <c r="C263" t="n">
-        <v>11.24946021806958</v>
+        <v>11.24945925299112</v>
       </c>
       <c r="D263" t="n">
-        <v>10.8091193187322</v>
+        <v>10.80911839143009</v>
       </c>
       <c r="E263" t="n">
-        <v>11.01682806185065</v>
+        <v>11.01682711672944</v>
       </c>
       <c r="F263" t="n">
         <v>416658</v>
@@ -5692,16 +5692,16 @@
         <v>44700</v>
       </c>
       <c r="B264" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C264" t="n">
-        <v>11.4073194012873</v>
+        <v>11.40731747287078</v>
       </c>
       <c r="D264" t="n">
-        <v>11.05006181329636</v>
+        <v>11.05005994527452</v>
       </c>
       <c r="E264" t="n">
-        <v>11.12483706495406</v>
+        <v>11.1248351842914</v>
       </c>
       <c r="F264" t="n">
         <v>530225</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423415912707</v>
+        <v>11.32423513134702</v>
       </c>
       <c r="D265" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100099778751</v>
+        <v>11.29100196715428</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5732,16 +5732,16 @@
         <v>44704</v>
       </c>
       <c r="B266" t="n">
-        <v>10.9669771194458</v>
+        <v>10.96697807312012</v>
       </c>
       <c r="C266" t="n">
-        <v>11.19961009390851</v>
+        <v>11.19961106781229</v>
       </c>
       <c r="D266" t="n">
-        <v>10.72603606296127</v>
+        <v>10.72603699568366</v>
       </c>
       <c r="E266" t="n">
-        <v>11.14975993231466</v>
+        <v>11.14976090188353</v>
       </c>
       <c r="F266" t="n">
         <v>653906</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.16637706756592</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="C267" t="n">
-        <v>11.16637706756592</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772727720074</v>
+        <v>10.71772819255772</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05006057891294</v>
+        <v>11.05006152265314</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190330505371</v>
+        <v>10.99190235137939</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="D268" t="n">
-        <v>10.892202971845</v>
+        <v>10.89220202682084</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.19130229949951</v>
+        <v>11.19130325317383</v>
       </c>
       <c r="C269" t="n">
-        <v>11.19130229949951</v>
+        <v>11.19130325317383</v>
       </c>
       <c r="D269" t="n">
-        <v>10.86727791027506</v>
+        <v>10.86727883633742</v>
       </c>
       <c r="E269" t="n">
-        <v>11.01682756416854</v>
+        <v>11.01682850297487</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34915924072266</v>
+        <v>11.34916019439697</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19960959730377</v>
+        <v>11.19961053841137</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="C274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="E274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712760925293</v>
+        <v>10.91712856292725</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24945923185963</v>
+        <v>11.24946021456504</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051061075688</v>
+        <v>10.90051156297961</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622690433039</v>
+        <v>11.21622788413276</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344429480254</v>
+        <v>11.03344331983751</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="E276" t="n">
-        <v>11.00851921397176</v>
+        <v>11.00851824120922</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -6032,16 +6032,16 @@
         <v>44725</v>
       </c>
       <c r="B281" t="n">
-        <v>10.25246238708496</v>
+        <v>10.25246334075928</v>
       </c>
       <c r="C281" t="n">
-        <v>10.47678728729483</v>
+        <v>10.47678826183563</v>
       </c>
       <c r="D281" t="n">
-        <v>10.18599522441408</v>
+        <v>10.18599617190568</v>
       </c>
       <c r="E281" t="n">
-        <v>10.38539587769526</v>
+        <v>10.38539684373493</v>
       </c>
       <c r="F281" t="n">
         <v>299930</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768669128418</v>
+        <v>10.17768573760986</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216142044539</v>
+        <v>10.35216045042237</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798720379124</v>
+        <v>10.07798625945901</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599477322573</v>
+        <v>10.18599381877293</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6112,16 +6112,16 @@
         <v>44732</v>
       </c>
       <c r="B285" t="n">
-        <v>10.07798767089844</v>
+        <v>10.07798671722412</v>
       </c>
       <c r="C285" t="n">
-        <v>10.26077049047305</v>
+        <v>10.2607695195021</v>
       </c>
       <c r="D285" t="n">
-        <v>9.945055014746524</v>
+        <v>9.945054073651551</v>
       </c>
       <c r="E285" t="n">
-        <v>10.17768716301237</v>
+        <v>10.17768619990355</v>
       </c>
       <c r="F285" t="n">
         <v>293715</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911820411682129</v>
+        <v>9.911822319030762</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21922862107171</v>
+        <v>10.21923058757544</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787195845454841</v>
+        <v>9.787197728821756</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783721685627</v>
+        <v>10.12783916577339</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6172,16 +6172,16 @@
         <v>44735</v>
       </c>
       <c r="B288" t="n">
-        <v>9.63764762878418</v>
+        <v>9.637646675109863</v>
       </c>
       <c r="C288" t="n">
-        <v>9.945055883777885</v>
+        <v>9.945054899684594</v>
       </c>
       <c r="D288" t="n">
-        <v>9.629339545731565</v>
+        <v>9.629338592879359</v>
       </c>
       <c r="E288" t="n">
-        <v>9.936747800725271</v>
+        <v>9.93674681745409</v>
       </c>
       <c r="F288" t="n">
         <v>565728</v>
@@ -6212,16 +6212,16 @@
         <v>44739</v>
       </c>
       <c r="B290" t="n">
-        <v>9.355164527893066</v>
+        <v>9.355165481567383</v>
       </c>
       <c r="C290" t="n">
-        <v>9.55456351324988</v>
+        <v>9.554564487251117</v>
       </c>
       <c r="D290" t="n">
-        <v>9.26377228285685</v>
+        <v>9.263773227214553</v>
       </c>
       <c r="E290" t="n">
-        <v>9.49640610190275</v>
+        <v>9.496407069975366</v>
       </c>
       <c r="F290" t="n">
         <v>312467</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.16407299041748</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496405321144287</v>
+        <v>9.496406309403417</v>
       </c>
       <c r="D291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.16407299041748</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488097239453682</v>
+        <v>9.488098226848217</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6312,16 +6312,16 @@
         <v>44746</v>
       </c>
       <c r="B295" t="n">
-        <v>9.222231864929199</v>
+        <v>9.222232818603516</v>
       </c>
       <c r="C295" t="n">
-        <v>9.297006275706005</v>
+        <v>9.297007237112771</v>
       </c>
       <c r="D295" t="n">
-        <v>8.873282388686833</v>
+        <v>8.873283306276161</v>
       </c>
       <c r="E295" t="n">
-        <v>8.972981881299734</v>
+        <v>8.972982809199021</v>
       </c>
       <c r="F295" t="n">
         <v>166874</v>
@@ -6332,16 +6332,16 @@
         <v>44747</v>
       </c>
       <c r="B296" t="n">
-        <v>9.031140327453613</v>
+        <v>9.031139373779297</v>
       </c>
       <c r="C296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213922179017237</v>
       </c>
       <c r="D296" t="n">
-        <v>9.022831410169822</v>
+        <v>9.022830457372914</v>
       </c>
       <c r="E296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213922179017237</v>
       </c>
       <c r="F296" t="n">
         <v>222182</v>
@@ -6432,16 +6432,16 @@
         <v>44754</v>
       </c>
       <c r="B301" t="n">
-        <v>8.690498352050781</v>
+        <v>8.690500259399414</v>
       </c>
       <c r="C301" t="n">
-        <v>8.864973082514485</v>
+        <v>8.864975028155989</v>
       </c>
       <c r="D301" t="n">
-        <v>8.57418186507498</v>
+        <v>8.574183746895031</v>
       </c>
       <c r="E301" t="n">
-        <v>8.864973082514485</v>
+        <v>8.864975028155989</v>
       </c>
       <c r="F301" t="n">
         <v>237774</v>
@@ -6452,16 +6452,16 @@
         <v>44755</v>
       </c>
       <c r="B302" t="n">
-        <v>8.59910774230957</v>
+        <v>8.599106788635254</v>
       </c>
       <c r="C302" t="n">
-        <v>8.823431820304181</v>
+        <v>8.823430841751456</v>
       </c>
       <c r="D302" t="n">
-        <v>8.549257576207872</v>
+        <v>8.549256628062132</v>
       </c>
       <c r="E302" t="n">
-        <v>8.56587457648561</v>
+        <v>8.56587362649698</v>
       </c>
       <c r="F302" t="n">
         <v>184467</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557564735412598</v>
+        <v>8.557565689086914</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673882055340277</v>
+        <v>8.673883021977259</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482790329061535</v>
+        <v>8.482791274402823</v>
       </c>
       <c r="E306" t="n">
-        <v>8.499407327545896</v>
+        <v>8.49940827473902</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864974975585938</v>
+        <v>8.864972114562988</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873283894095279</v>
+        <v>8.873281030390764</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615725784401254</v>
+        <v>8.615723003819328</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632341951956706</v>
+        <v>8.632339166012187</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6572,16 +6572,16 @@
         <v>44763</v>
       </c>
       <c r="B308" t="n">
-        <v>8.823431968688965</v>
+        <v>8.823431015014648</v>
       </c>
       <c r="C308" t="n">
-        <v>8.881591053273359</v>
+        <v>8.881590093312958</v>
       </c>
       <c r="D308" t="n">
-        <v>8.756966470654801</v>
+        <v>8.756965524164361</v>
       </c>
       <c r="E308" t="n">
-        <v>8.756966470654801</v>
+        <v>8.756965524164361</v>
       </c>
       <c r="F308" t="n">
         <v>93866</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039448738098145</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039448738098145</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815123823192138</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815123823192138</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756965637207031</v>
+        <v>8.756966590881348</v>
       </c>
       <c r="C311" t="n">
-        <v>9.122531267357015</v>
+        <v>9.122532260843132</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756965637207031</v>
+        <v>8.756966590881348</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039447941941624</v>
+        <v>9.039448926379578</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.93974781036377</v>
+        <v>8.939749717712402</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172379936198697</v>
+        <v>9.172381893180782</v>
       </c>
       <c r="D317" t="n">
-        <v>8.93974781036377</v>
+        <v>8.939749717712402</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114221696057117</v>
+        <v>9.114223640630795</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6772,16 +6772,16 @@
         <v>44777</v>
       </c>
       <c r="B318" t="n">
-        <v>9.263772964477539</v>
+        <v>9.263771057128906</v>
       </c>
       <c r="C318" t="n">
-        <v>9.297006965880481</v>
+        <v>9.29700505168919</v>
       </c>
       <c r="D318" t="n">
-        <v>8.948057463733431</v>
+        <v>8.948055621388498</v>
       </c>
       <c r="E318" t="n">
-        <v>8.972982547419868</v>
+        <v>8.972980699943028</v>
       </c>
       <c r="F318" t="n">
         <v>175407</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.380088806152344</v>
+        <v>9.38008975982666</v>
       </c>
       <c r="C319" t="n">
-        <v>9.529638463032139</v>
+        <v>9.52963943191118</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197305984936092</v>
+        <v>9.197306920026865</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305314395078184</v>
+        <v>9.305315341150182</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6812,16 +6812,16 @@
         <v>44781</v>
       </c>
       <c r="B320" t="n">
-        <v>9.63764762878418</v>
+        <v>9.637646675109863</v>
       </c>
       <c r="C320" t="n">
-        <v>9.670881630457723</v>
+        <v>9.670880673494802</v>
       </c>
       <c r="D320" t="n">
-        <v>9.371781458516631</v>
+        <v>9.371780531150575</v>
       </c>
       <c r="E320" t="n">
-        <v>9.371781458516631</v>
+        <v>9.371780531150575</v>
       </c>
       <c r="F320" t="n">
         <v>274752</v>
@@ -6832,16 +6832,16 @@
         <v>44782</v>
       </c>
       <c r="B321" t="n">
-        <v>9.263772964477539</v>
+        <v>9.263771057128906</v>
       </c>
       <c r="C321" t="n">
-        <v>9.920129884383732</v>
+        <v>9.920127841895617</v>
       </c>
       <c r="D321" t="n">
-        <v>9.105915214105485</v>
+        <v>9.105913339258702</v>
       </c>
       <c r="E321" t="n">
-        <v>9.687497717683902</v>
+        <v>9.687495723093187</v>
       </c>
       <c r="F321" t="n">
         <v>480605</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513022422790527</v>
+        <v>9.513021469116211</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596105752085279</v>
+        <v>9.596104790081913</v>
       </c>
       <c r="D322" t="n">
-        <v>9.205615022604585</v>
+        <v>9.205614099747661</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288697517167847</v>
+        <v>9.288696585981958</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6872,16 +6872,16 @@
         <v>44784</v>
       </c>
       <c r="B323" t="n">
-        <v>9.762272834777832</v>
+        <v>9.762271881103516</v>
       </c>
       <c r="C323" t="n">
-        <v>9.77058091764879</v>
+        <v>9.770579963162858</v>
       </c>
       <c r="D323" t="n">
-        <v>9.446556503634687</v>
+        <v>9.446555580802631</v>
       </c>
       <c r="E323" t="n">
-        <v>9.446556503634687</v>
+        <v>9.446555580802631</v>
       </c>
       <c r="F323" t="n">
         <v>1309919</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.77057933807373</v>
+        <v>9.770578384399414</v>
       </c>
       <c r="C324" t="n">
-        <v>9.861970739073907</v>
+        <v>9.861969776479176</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262023027314</v>
+        <v>9.654261080706352</v>
       </c>
       <c r="E324" t="n">
-        <v>9.820428661972032</v>
+        <v>9.820427703432088</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953363418579102</v>
+        <v>9.953361511230469</v>
       </c>
       <c r="C325" t="n">
-        <v>10.11953007886785</v>
+        <v>10.11952813967694</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704113428145977</v>
+        <v>9.704111568560759</v>
       </c>
       <c r="E325" t="n">
-        <v>9.72903851066244</v>
+        <v>9.729036646300864</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C327" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D327" t="n">
-        <v>10.30231205007301</v>
+        <v>10.30231297394502</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847869658313</v>
+        <v>10.46847963535633</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494453430176</v>
+        <v>10.53494358062744</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.75926845704052</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216171794617</v>
+        <v>10.35216078081824</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.75926845704052</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389380981785</v>
+        <v>10.88389284806778</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633575420836</v>
+        <v>10.62633481521728</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573640085461</v>
+        <v>10.82573544424359</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096130371094</v>
+        <v>10.75096225738525</v>
       </c>
       <c r="C334" t="n">
-        <v>10.7758863848787</v>
+        <v>10.77588734076402</v>
       </c>
       <c r="D334" t="n">
-        <v>10.32723742805339</v>
+        <v>10.32723834414087</v>
       </c>
       <c r="E334" t="n">
-        <v>10.7758863848787</v>
+        <v>10.77588734076402</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539600372314</v>
+        <v>10.38539695739746</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648690755074</v>
+        <v>10.57648787877263</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907867632044</v>
+        <v>10.26907961931352</v>
       </c>
       <c r="E337" t="n">
-        <v>10.4020121685439</v>
+        <v>10.40201312374406</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7172,16 +7172,16 @@
         <v>44805</v>
       </c>
       <c r="B338" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="C338" t="n">
-        <v>10.71772749611192</v>
+        <v>10.71772651584117</v>
       </c>
       <c r="D338" t="n">
-        <v>10.31892869453579</v>
+        <v>10.3189277507402</v>
       </c>
       <c r="E338" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="F338" t="n">
         <v>1368072</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753524780273</v>
+        <v>10.22753715515137</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370186895259</v>
+        <v>10.39370380728989</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937701387342</v>
+        <v>10.16937891037603</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385171566137</v>
+        <v>10.34385364470204</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="D340" t="n">
-        <v>10.2524617502037</v>
+        <v>10.25246083437947</v>
       </c>
       <c r="E340" t="n">
-        <v>10.35216123591951</v>
+        <v>10.3521603111894</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7252,16 +7252,16 @@
         <v>44812</v>
       </c>
       <c r="B342" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C342" t="n">
-        <v>10.90881937119658</v>
+        <v>10.90881840426656</v>
       </c>
       <c r="D342" t="n">
-        <v>10.57648689318649</v>
+        <v>10.57648595571358</v>
       </c>
       <c r="E342" t="n">
-        <v>10.57648689318649</v>
+        <v>10.57648595571358</v>
       </c>
       <c r="F342" t="n">
         <v>294768</v>
@@ -7312,16 +7312,16 @@
         <v>44817</v>
       </c>
       <c r="B345" t="n">
-        <v>11.14145278930664</v>
+        <v>11.14145183563232</v>
       </c>
       <c r="C345" t="n">
-        <v>11.19961103782396</v>
+        <v>11.19961007917147</v>
       </c>
       <c r="D345" t="n">
-        <v>10.70111188406574</v>
+        <v>10.70111096808326</v>
       </c>
       <c r="E345" t="n">
-        <v>10.95866996103265</v>
+        <v>10.95866902300398</v>
       </c>
       <c r="F345" t="n">
         <v>335223</v>
@@ -7352,16 +7352,16 @@
         <v>44819</v>
       </c>
       <c r="B347" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C347" t="n">
-        <v>11.29100289964081</v>
+        <v>11.29100099088769</v>
       </c>
       <c r="D347" t="n">
-        <v>10.73434631002577</v>
+        <v>10.73434449537589</v>
       </c>
       <c r="E347" t="n">
-        <v>11.05006181329636</v>
+        <v>11.05005994527452</v>
       </c>
       <c r="F347" t="n">
         <v>361349</v>
@@ -7392,16 +7392,16 @@
         <v>44823</v>
       </c>
       <c r="B349" t="n">
-        <v>11.28269481658936</v>
+        <v>11.28269290924072</v>
       </c>
       <c r="C349" t="n">
-        <v>11.38239431740141</v>
+        <v>11.38239239319849</v>
       </c>
       <c r="D349" t="n">
-        <v>11.17468639799431</v>
+        <v>11.17468450890459</v>
       </c>
       <c r="E349" t="n">
-        <v>11.35746923351551</v>
+        <v>11.3574673135262</v>
       </c>
       <c r="F349" t="n">
         <v>125366</v>
@@ -7412,16 +7412,16 @@
         <v>44824</v>
       </c>
       <c r="B350" t="n">
-        <v>11.1580696105957</v>
+        <v>11.15806865692139</v>
       </c>
       <c r="C350" t="n">
-        <v>11.30762011677175</v>
+        <v>11.30761915031543</v>
       </c>
       <c r="D350" t="n">
-        <v>11.1580696105957</v>
+        <v>11.15806865692139</v>
       </c>
       <c r="E350" t="n">
-        <v>11.17468661174801</v>
+        <v>11.17468565665344</v>
       </c>
       <c r="F350" t="n">
         <v>127157</v>
@@ -7432,16 +7432,16 @@
         <v>44825</v>
       </c>
       <c r="B351" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C351" t="n">
-        <v>11.16637743815185</v>
+        <v>11.16637644839254</v>
       </c>
       <c r="D351" t="n">
-        <v>10.67618638617008</v>
+        <v>10.67618543986006</v>
       </c>
       <c r="E351" t="n">
-        <v>11.12483619142489</v>
+        <v>11.12483520534769</v>
       </c>
       <c r="F351" t="n">
         <v>359874</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85066048103983</v>
+        <v>10.85066145408563</v>
       </c>
       <c r="D352" t="n">
-        <v>10.5931032641</v>
+        <v>10.59310421404906</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449466926114</v>
+        <v>10.68449562740583</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C353" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D353" t="n">
-        <v>10.34385329433483</v>
+        <v>10.3438542219321</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156201983819</v>
+        <v>10.55156296606198</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7492,16 +7492,16 @@
         <v>44830</v>
       </c>
       <c r="B354" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="C354" t="n">
-        <v>10.60971992210769</v>
+        <v>10.60971895171559</v>
       </c>
       <c r="D354" t="n">
-        <v>10.34385377614644</v>
+        <v>10.34385283007114</v>
       </c>
       <c r="E354" t="n">
-        <v>10.60971992210769</v>
+        <v>10.60971895171559</v>
       </c>
       <c r="F354" t="n">
         <v>121152</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389364339556</v>
+        <v>10.88389461942159</v>
       </c>
       <c r="D363" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="E363" t="n">
-        <v>10.82573623532159</v>
+        <v>10.82573720613229</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7712,16 +7712,16 @@
         <v>44845</v>
       </c>
       <c r="B365" t="n">
-        <v>11.06667613983154</v>
+        <v>11.06667709350586</v>
       </c>
       <c r="C365" t="n">
-        <v>11.1746845404728</v>
+        <v>11.17468550345477</v>
       </c>
       <c r="D365" t="n">
-        <v>10.80081001379502</v>
+        <v>10.80081094455824</v>
       </c>
       <c r="E365" t="n">
-        <v>10.8174270118673</v>
+        <v>10.81742794406249</v>
       </c>
       <c r="F365" t="n">
         <v>221655</v>
@@ -7732,16 +7732,16 @@
         <v>44847</v>
       </c>
       <c r="B366" t="n">
-        <v>10.9669771194458</v>
+        <v>10.96697807312012</v>
       </c>
       <c r="C366" t="n">
-        <v>11.15806801433649</v>
+        <v>11.15806898462782</v>
       </c>
       <c r="D366" t="n">
-        <v>10.85896954896772</v>
+        <v>10.85897049324983</v>
       </c>
       <c r="E366" t="n">
-        <v>10.85896954896772</v>
+        <v>10.85897049324983</v>
       </c>
       <c r="F366" t="n">
         <v>180569</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558650970459</v>
+        <v>10.87558555603027</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160333594799</v>
+        <v>11.09160236333128</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85066142708177</v>
+        <v>10.85066047559313</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344508807192</v>
+        <v>11.03344412055507</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7772,16 +7772,16 @@
         <v>44851</v>
       </c>
       <c r="B368" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="D368" t="n">
-        <v>10.79250300417271</v>
+        <v>10.79250206495899</v>
       </c>
       <c r="E368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="F368" t="n">
         <v>132003</v>
@@ -7792,16 +7792,16 @@
         <v>44852</v>
       </c>
       <c r="B369" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C369" t="n">
-        <v>11.09160302709703</v>
+        <v>11.09160204396554</v>
       </c>
       <c r="D369" t="n">
-        <v>10.75096163195637</v>
+        <v>10.75096067901846</v>
       </c>
       <c r="E369" t="n">
-        <v>10.95866953505411</v>
+        <v>10.9586685637055</v>
       </c>
       <c r="F369" t="n">
         <v>172246</v>
@@ -7872,16 +7872,16 @@
         <v>44858</v>
       </c>
       <c r="B373" t="n">
-        <v>10.84235286712646</v>
+        <v>10.84235191345215</v>
       </c>
       <c r="C373" t="n">
-        <v>10.95866935775788</v>
+        <v>10.95866839385256</v>
       </c>
       <c r="D373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618527438544</v>
       </c>
       <c r="E373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618527438544</v>
       </c>
       <c r="F373" t="n">
         <v>186469</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.6512622833252</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866870237426</v>
+        <v>10.95866968357269</v>
       </c>
       <c r="D374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.6512622833252</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772681852483</v>
+        <v>10.71772777815022</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -7952,16 +7952,16 @@
         <v>44862</v>
       </c>
       <c r="B377" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C377" t="n">
-        <v>10.99190282718986</v>
+        <v>10.99190187062344</v>
       </c>
       <c r="D377" t="n">
-        <v>10.68449542753418</v>
+        <v>10.68449449771977</v>
       </c>
       <c r="E377" t="n">
-        <v>10.89220249831554</v>
+        <v>10.89220155042551</v>
       </c>
       <c r="F377" t="n">
         <v>271802</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19961166381836</v>
+        <v>11.19961071014404</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577833593604</v>
+        <v>11.36577736811222</v>
       </c>
       <c r="D381" t="n">
-        <v>10.88389532068739</v>
+        <v>10.8838943938971</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344582643224</v>
+        <v>11.03344488690735</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8052,16 +8052,16 @@
         <v>44872</v>
       </c>
       <c r="B382" t="n">
-        <v>10.86727809906006</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="C382" t="n">
-        <v>11.24115182292292</v>
+        <v>11.24115083643875</v>
       </c>
       <c r="D382" t="n">
-        <v>10.72603652494829</v>
+        <v>10.72603558366884</v>
       </c>
       <c r="E382" t="n">
-        <v>11.11652724830197</v>
+        <v>11.11652627275442</v>
       </c>
       <c r="F382" t="n">
         <v>110617</v>
@@ -8132,16 +8132,16 @@
         <v>44876</v>
       </c>
       <c r="B386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="C386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="D386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="E386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="F386" t="n">
         <v>372832</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765274047851562</v>
+        <v>8.765273094177246</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873282458412872</v>
+        <v>8.873281492987086</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225233664507979</v>
+        <v>8.225232769590827</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707115801354162</v>
+        <v>8.707114854007546</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8212,16 +8212,16 @@
         <v>44883</v>
       </c>
       <c r="B390" t="n">
-        <v>8.557564735412598</v>
+        <v>8.557565689086914</v>
       </c>
       <c r="C390" t="n">
-        <v>8.914823107609253</v>
+        <v>8.914824101097249</v>
       </c>
       <c r="D390" t="n">
-        <v>8.39139892422611</v>
+        <v>8.391399859382533</v>
       </c>
       <c r="E390" t="n">
-        <v>8.848356783134658</v>
+        <v>8.848357769215497</v>
       </c>
       <c r="F390" t="n">
         <v>571733</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562846183776855</v>
+        <v>8.562847137451172</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039489009439741</v>
+        <v>9.039490016199446</v>
       </c>
       <c r="D392" t="n">
-        <v>8.529397667607249</v>
+        <v>8.529398617556286</v>
       </c>
       <c r="E392" t="n">
-        <v>8.94750537993818</v>
+        <v>8.947506376453346</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.780261039733887</v>
+        <v>8.780261993408203</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880606577737419</v>
+        <v>8.880607542310836</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462499749319136</v>
+        <v>8.462500668479581</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537758692786666</v>
+        <v>8.537759620121415</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081300735473633</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081300735473633</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621382522590984</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621382522590984</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.822073936462402</v>
+        <v>8.822072982788086</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098024846931471</v>
+        <v>9.098023863426608</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746814138985041</v>
+        <v>8.746813193446378</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081300167445182</v>
+        <v>9.081299185748271</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8332,16 +8332,16 @@
         <v>44893</v>
       </c>
       <c r="B396" t="n">
-        <v>8.537760734558105</v>
+        <v>8.537759780883789</v>
       </c>
       <c r="C396" t="n">
-        <v>8.888971461771821</v>
+        <v>8.888970468867001</v>
       </c>
       <c r="D396" t="n">
-        <v>8.537760734558105</v>
+        <v>8.537759780883789</v>
       </c>
       <c r="E396" t="n">
-        <v>8.888971461771821</v>
+        <v>8.888970468867001</v>
       </c>
       <c r="F396" t="n">
         <v>122943</v>
@@ -8372,16 +8372,16 @@
         <v>44895</v>
       </c>
       <c r="B398" t="n">
-        <v>8.671554565429688</v>
+        <v>8.671553611755371</v>
       </c>
       <c r="C398" t="n">
-        <v>8.905695020755468</v>
+        <v>8.905694041331014</v>
       </c>
       <c r="D398" t="n">
-        <v>8.604656692379058</v>
+        <v>8.60465574606199</v>
       </c>
       <c r="E398" t="n">
-        <v>8.705003081884717</v>
+        <v>8.705002124531823</v>
       </c>
       <c r="F398" t="n">
         <v>181728</v>
@@ -8392,16 +8392,16 @@
         <v>44896</v>
       </c>
       <c r="B399" t="n">
-        <v>8.955865859985352</v>
+        <v>8.955866813659668</v>
       </c>
       <c r="C399" t="n">
-        <v>8.955865859985352</v>
+        <v>8.955866813659668</v>
       </c>
       <c r="D399" t="n">
-        <v>8.596293318759741</v>
+        <v>8.596294234144615</v>
       </c>
       <c r="E399" t="n">
-        <v>8.721725444277432</v>
+        <v>8.721726373019072</v>
       </c>
       <c r="F399" t="n">
         <v>469965</v>
@@ -8432,16 +8432,16 @@
         <v>44900</v>
       </c>
       <c r="B401" t="n">
-        <v>8.746813774108887</v>
+        <v>8.746814727783203</v>
       </c>
       <c r="C401" t="n">
-        <v>9.089662548080438</v>
+        <v>9.08966353913592</v>
       </c>
       <c r="D401" t="n">
-        <v>8.663192900587594</v>
+        <v>8.66319384514464</v>
       </c>
       <c r="E401" t="n">
-        <v>8.947505718869293</v>
+        <v>8.947506694425265</v>
       </c>
       <c r="F401" t="n">
         <v>131055</v>
@@ -8452,16 +8452,16 @@
         <v>44901</v>
       </c>
       <c r="B402" t="n">
-        <v>8.746813774108887</v>
+        <v>8.746814727783203</v>
       </c>
       <c r="C402" t="n">
-        <v>8.863884005207408</v>
+        <v>8.863884971646016</v>
       </c>
       <c r="D402" t="n">
-        <v>8.688278658559627</v>
+        <v>8.688279605851797</v>
       </c>
       <c r="E402" t="n">
-        <v>8.771900372221511</v>
+        <v>8.771901328631047</v>
       </c>
       <c r="F402" t="n">
         <v>122416</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905693728734814</v>
+        <v>8.905694705334085</v>
       </c>
       <c r="D403" t="n">
-        <v>8.679915225243152</v>
+        <v>8.67991617708353</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780260760050309</v>
+        <v>8.780261722894588</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437413215637207</v>
+        <v>8.437414169311523</v>
       </c>
       <c r="C404" t="n">
-        <v>8.738451542075317</v>
+        <v>8.738452529775763</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412327458562881</v>
+        <v>8.412328409401773</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705003025835651</v>
+        <v>8.705004009755438</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935685157775879</v>
+        <v>7.935684204101562</v>
       </c>
       <c r="C405" t="n">
-        <v>8.479225052935186</v>
+        <v>8.479224033940735</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935685157775879</v>
+        <v>7.935684204101562</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462501213777397</v>
+        <v>8.462500196792739</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952410221099854</v>
+        <v>7.952409744262695</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027669181225434</v>
+        <v>8.027668699875649</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818616140814081</v>
+        <v>7.818615671999396</v>
       </c>
       <c r="E406" t="n">
-        <v>7.935685540993802</v>
+        <v>7.935685065159479</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8592,16 +8592,16 @@
         <v>44910</v>
       </c>
       <c r="B409" t="n">
-        <v>8.253444671630859</v>
+        <v>8.253445625305176</v>
       </c>
       <c r="C409" t="n">
-        <v>8.253444671630859</v>
+        <v>8.253445625305176</v>
       </c>
       <c r="D409" t="n">
-        <v>8.027667012119434</v>
+        <v>8.027667939705447</v>
       </c>
       <c r="E409" t="n">
-        <v>8.11128870977347</v>
+        <v>8.111289647021858</v>
       </c>
       <c r="F409" t="n">
         <v>145488</v>
@@ -8632,16 +8632,16 @@
         <v>44914</v>
       </c>
       <c r="B411" t="n">
-        <v>8.161462783813477</v>
+        <v>8.16146183013916</v>
       </c>
       <c r="C411" t="n">
-        <v>8.161462783813477</v>
+        <v>8.16146183013916</v>
       </c>
       <c r="D411" t="n">
-        <v>7.952409755638184</v>
+        <v>7.952408826391903</v>
       </c>
       <c r="E411" t="n">
-        <v>8.128015105840415</v>
+        <v>8.128014156074491</v>
       </c>
       <c r="F411" t="n">
         <v>108510</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780260760050309</v>
+        <v>8.780261722894588</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613017361897933</v>
+        <v>8.613018306402285</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730088412716954</v>
+        <v>8.730089370059329</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.738451957702637</v>
+        <v>8.73845100402832</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788624314378202</v>
+        <v>8.788623355228307</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284660898665</v>
+        <v>8.56284567447709</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713365359294553</v>
+        <v>8.713364408358071</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8772,16 +8772,16 @@
         <v>44923</v>
       </c>
       <c r="B418" t="n">
-        <v>8.746813774108887</v>
+        <v>8.746814727783203</v>
       </c>
       <c r="C418" t="n">
-        <v>8.930781880221272</v>
+        <v>8.930782853953826</v>
       </c>
       <c r="D418" t="n">
-        <v>8.679916739235615</v>
+        <v>8.679917685616079</v>
       </c>
       <c r="E418" t="n">
-        <v>8.688278658559627</v>
+        <v>8.688279605851797</v>
       </c>
       <c r="F418" t="n">
         <v>114515</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914055646600298</v>
+        <v>8.914056624116538</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="E419" t="n">
-        <v>8.83043394752411</v>
+        <v>8.830434915870388</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8872,16 +8872,16 @@
         <v>44931</v>
       </c>
       <c r="B423" t="n">
-        <v>8.395604133605957</v>
+        <v>8.395603179931641</v>
       </c>
       <c r="C423" t="n">
-        <v>8.454139250637853</v>
+        <v>8.454138290314409</v>
       </c>
       <c r="D423" t="n">
-        <v>8.270171980006358</v>
+        <v>8.270171040580143</v>
       </c>
       <c r="E423" t="n">
-        <v>8.362155615322106</v>
+        <v>8.362154665447276</v>
       </c>
       <c r="F423" t="n">
         <v>69636</v>
@@ -8912,16 +8912,16 @@
         <v>44935</v>
       </c>
       <c r="B425" t="n">
-        <v>8.813711166381836</v>
+        <v>8.813712120056152</v>
       </c>
       <c r="C425" t="n">
-        <v>8.947505228800265</v>
+        <v>8.947506196951567</v>
       </c>
       <c r="D425" t="n">
-        <v>8.696640101554889</v>
+        <v>8.696641042561707</v>
       </c>
       <c r="E425" t="n">
-        <v>8.905694794329643</v>
+        <v>8.905695757956909</v>
       </c>
       <c r="F425" t="n">
         <v>148121</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964229583740234</v>
+        <v>8.964228630065918</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072937895832748</v>
+        <v>9.072936930593318</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847160192439846</v>
+        <v>8.847159251220148</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922419146857282</v>
+        <v>8.922418197631035</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -8972,16 +8972,16 @@
         <v>44938</v>
       </c>
       <c r="B428" t="n">
-        <v>9.131471633911133</v>
+        <v>9.131472587585449</v>
       </c>
       <c r="C428" t="n">
-        <v>9.323800790753337</v>
+        <v>9.323801764514162</v>
       </c>
       <c r="D428" t="n">
-        <v>8.788622910661372</v>
+        <v>8.788623828529191</v>
       </c>
       <c r="E428" t="n">
-        <v>8.964228231329717</v>
+        <v>8.964229167537438</v>
       </c>
       <c r="F428" t="n">
         <v>167506</v>
@@ -9072,16 +9072,16 @@
         <v>44945</v>
       </c>
       <c r="B433" t="n">
-        <v>9.131471633911133</v>
+        <v>9.131472587585449</v>
       </c>
       <c r="C433" t="n">
-        <v>9.281991200318688</v>
+        <v>9.281992169712995</v>
       </c>
       <c r="D433" t="n">
-        <v>8.989314825730977</v>
+        <v>8.989315764558695</v>
       </c>
       <c r="E433" t="n">
-        <v>9.056211850707355</v>
+        <v>9.056212796521677</v>
       </c>
       <c r="F433" t="n">
         <v>125260</v>
@@ -9092,16 +9092,16 @@
         <v>44946</v>
       </c>
       <c r="B434" t="n">
-        <v>9.36561107635498</v>
+        <v>9.365612983703613</v>
       </c>
       <c r="C434" t="n">
-        <v>9.36561107635498</v>
+        <v>9.365612983703613</v>
       </c>
       <c r="D434" t="n">
-        <v>9.03948706372263</v>
+        <v>9.039488904654647</v>
       </c>
       <c r="E434" t="n">
-        <v>9.131470673425049</v>
+        <v>9.131472533089941</v>
       </c>
       <c r="F434" t="n">
         <v>97975</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566305160522461</v>
+        <v>9.566306114196777</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616477515394145</v>
+        <v>9.616478474070194</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407423656363838</v>
+        <v>9.407424594199101</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424148334748114</v>
+        <v>9.424149274250677</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9152,16 +9152,16 @@
         <v>44951</v>
       </c>
       <c r="B437" t="n">
-        <v>9.783721923828125</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="C437" t="n">
-        <v>9.842257043856318</v>
+        <v>9.842255125096191</v>
       </c>
       <c r="D437" t="n">
-        <v>9.415787363731287</v>
+        <v>9.41578552811195</v>
       </c>
       <c r="E437" t="n">
-        <v>9.541219523751513</v>
+        <v>9.541217663679022</v>
       </c>
       <c r="F437" t="n">
         <v>142538</v>
@@ -9252,16 +9252,16 @@
         <v>44958</v>
       </c>
       <c r="B442" t="n">
-        <v>9.783721923828125</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="C442" t="n">
-        <v>9.783721923828125</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="D442" t="n">
-        <v>9.323802883566421</v>
+        <v>9.323801065879572</v>
       </c>
       <c r="E442" t="n">
-        <v>9.449235883727303</v>
+        <v>9.449234041587136</v>
       </c>
       <c r="F442" t="n">
         <v>177092</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.66664981842041</v>
+        <v>9.666651725769043</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725184927153217</v>
+        <v>9.725186846051544</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457595978680457</v>
+        <v>9.457597844780201</v>
       </c>
       <c r="E443" t="n">
-        <v>9.700098331961943</v>
+        <v>9.700100245910377</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9292,16 +9292,16 @@
         <v>44960</v>
       </c>
       <c r="B444" t="n">
-        <v>9.67501163482666</v>
+        <v>9.675012588500977</v>
       </c>
       <c r="C444" t="n">
-        <v>9.867341635839546</v>
+        <v>9.867342608471997</v>
       </c>
       <c r="D444" t="n">
-        <v>9.382336934386988</v>
+        <v>9.382337859212104</v>
       </c>
       <c r="E444" t="n">
-        <v>9.474320555692112</v>
+        <v>9.474321489584133</v>
       </c>
       <c r="F444" t="n">
         <v>1290218</v>
@@ -9312,16 +9312,16 @@
         <v>44963</v>
       </c>
       <c r="B445" t="n">
-        <v>9.608116149902344</v>
+        <v>9.608115196228027</v>
       </c>
       <c r="C445" t="n">
-        <v>9.842256619930208</v>
+        <v>9.842255643015774</v>
       </c>
       <c r="D445" t="n">
-        <v>9.599754230298668</v>
+        <v>9.599753277454333</v>
       </c>
       <c r="E445" t="n">
-        <v>9.666651267409309</v>
+        <v>9.666650307924964</v>
       </c>
       <c r="F445" t="n">
         <v>107772</v>
@@ -9332,16 +9332,16 @@
         <v>44964</v>
       </c>
       <c r="B446" t="n">
-        <v>9.733549118041992</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="C446" t="n">
-        <v>9.733549118041992</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="D446" t="n">
-        <v>9.457597370469164</v>
+        <v>9.457596443832067</v>
       </c>
       <c r="E446" t="n">
-        <v>9.649927401812063</v>
+        <v>9.64992645633084</v>
       </c>
       <c r="F446" t="n">
         <v>121889</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312152862549</v>
+        <v>10.09312057495117</v>
       </c>
       <c r="C447" t="n">
-        <v>10.1600177240003</v>
+        <v>10.16001676400513</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649927198089818</v>
+        <v>9.649926286291848</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741910831958663</v>
+        <v>9.741909911469383</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9372,16 +9372,16 @@
         <v>44966</v>
       </c>
       <c r="B448" t="n">
-        <v>10.00949859619141</v>
+        <v>10.00949954986572</v>
       </c>
       <c r="C448" t="n">
-        <v>10.14329265094199</v>
+        <v>10.14329361736379</v>
       </c>
       <c r="D448" t="n">
-        <v>9.88406561968711</v>
+        <v>9.884066561410558</v>
       </c>
       <c r="E448" t="n">
-        <v>10.09312030048077</v>
+        <v>10.09312126212231</v>
       </c>
       <c r="F448" t="n">
         <v>166136</v>
@@ -9392,16 +9392,16 @@
         <v>44967</v>
       </c>
       <c r="B449" t="n">
-        <v>9.37397575378418</v>
+        <v>9.373976707458496</v>
       </c>
       <c r="C449" t="n">
-        <v>10.1432932979536</v>
+        <v>10.14329432989549</v>
       </c>
       <c r="D449" t="n">
-        <v>9.298715963080996</v>
+        <v>9.298716909098653</v>
       </c>
       <c r="E449" t="n">
-        <v>9.950964121946381</v>
+        <v>9.950965134321402</v>
       </c>
       <c r="F449" t="n">
         <v>543394</v>
@@ -9432,16 +9432,16 @@
         <v>44971</v>
       </c>
       <c r="B451" t="n">
-        <v>9.909153938293457</v>
+        <v>9.909152984619141</v>
       </c>
       <c r="C451" t="n">
-        <v>9.909153938293457</v>
+        <v>9.909152984619141</v>
       </c>
       <c r="D451" t="n">
-        <v>9.532855815383055</v>
+        <v>9.532854897924329</v>
       </c>
       <c r="E451" t="n">
-        <v>9.566305172192413</v>
+        <v>9.566304251514461</v>
       </c>
       <c r="F451" t="n">
         <v>266324</v>
@@ -9492,16 +9492,16 @@
         <v>44974</v>
       </c>
       <c r="B454" t="n">
-        <v>10.35234928131104</v>
+        <v>10.35234832763672</v>
       </c>
       <c r="C454" t="n">
-        <v>10.45269484127125</v>
+        <v>10.45269387835295</v>
       </c>
       <c r="D454" t="n">
-        <v>10.09312220123799</v>
+        <v>10.09312127144407</v>
       </c>
       <c r="E454" t="n">
-        <v>10.10148412119951</v>
+        <v>10.10148319063527</v>
       </c>
       <c r="F454" t="n">
         <v>113461</v>
@@ -9552,16 +9552,16 @@
         <v>44981</v>
       </c>
       <c r="B457" t="n">
-        <v>10.00113773345947</v>
+        <v>10.00113677978516</v>
       </c>
       <c r="C457" t="n">
-        <v>10.21019075603841</v>
+        <v>10.21018978242951</v>
       </c>
       <c r="D457" t="n">
-        <v>10.00113773345947</v>
+        <v>10.00113677978516</v>
       </c>
       <c r="E457" t="n">
-        <v>10.10148328511423</v>
+        <v>10.10148232187131</v>
       </c>
       <c r="F457" t="n">
         <v>69320</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458404541016</v>
+        <v>10.03458499908447</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889766329754</v>
+        <v>10.31889864399266</v>
       </c>
       <c r="D459" t="n">
-        <v>9.909152753011098</v>
+        <v>9.90915369476458</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950963183810783</v>
+        <v>9.950964129537878</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9632,16 +9632,16 @@
         <v>44987</v>
       </c>
       <c r="B461" t="n">
-        <v>10.47777843475342</v>
+        <v>10.47777938842773</v>
       </c>
       <c r="C461" t="n">
-        <v>10.55303821926824</v>
+        <v>10.55303917979261</v>
       </c>
       <c r="D461" t="n">
-        <v>10.11820586906596</v>
+        <v>10.11820679001243</v>
       </c>
       <c r="E461" t="n">
-        <v>10.20182757181338</v>
+        <v>10.20182850037099</v>
       </c>
       <c r="F461" t="n">
         <v>220181</v>
@@ -9652,16 +9652,16 @@
         <v>44988</v>
       </c>
       <c r="B462" t="n">
-        <v>10.32726192474365</v>
+        <v>10.32726001739502</v>
       </c>
       <c r="C462" t="n">
-        <v>10.64502412740092</v>
+        <v>10.64502216136458</v>
       </c>
       <c r="D462" t="n">
-        <v>10.32726192474365</v>
+        <v>10.32726001739502</v>
       </c>
       <c r="E462" t="n">
-        <v>10.61157476700276</v>
+        <v>10.6115728071442</v>
       </c>
       <c r="F462" t="n">
         <v>104401</v>
@@ -9732,16 +9732,16 @@
         <v>44994</v>
       </c>
       <c r="B466" t="n">
-        <v>10.70355796813965</v>
+        <v>10.70355892181396</v>
       </c>
       <c r="C466" t="n">
-        <v>10.820628195114</v>
+        <v>10.82062915921913</v>
       </c>
       <c r="D466" t="n">
-        <v>10.63666093562304</v>
+        <v>10.63666188333691</v>
       </c>
       <c r="E466" t="n">
-        <v>10.68683328994021</v>
+        <v>10.68683424212438</v>
       </c>
       <c r="F466" t="n">
         <v>86176</v>
@@ -9772,16 +9772,16 @@
         <v>44998</v>
       </c>
       <c r="B468" t="n">
-        <v>10.18510341644287</v>
+        <v>10.18510437011719</v>
       </c>
       <c r="C468" t="n">
-        <v>10.77881555503673</v>
+        <v>10.77881656430283</v>
       </c>
       <c r="D468" t="n">
-        <v>10.18510341644287</v>
+        <v>10.18510437011719</v>
       </c>
       <c r="E468" t="n">
-        <v>10.77881555503673</v>
+        <v>10.77881656430283</v>
       </c>
       <c r="F468" t="n">
         <v>154864</v>
@@ -9792,16 +9792,16 @@
         <v>44999</v>
       </c>
       <c r="B469" t="n">
-        <v>9.892426490783691</v>
+        <v>9.892428398132324</v>
       </c>
       <c r="C469" t="n">
-        <v>10.26036262281668</v>
+        <v>10.2603646011067</v>
       </c>
       <c r="D469" t="n">
-        <v>9.892426490783691</v>
+        <v>9.892428398132324</v>
       </c>
       <c r="E469" t="n">
-        <v>10.17674092738016</v>
+        <v>10.17674288954717</v>
       </c>
       <c r="F469" t="n">
         <v>103137</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758633613586426</v>
+        <v>9.758634567260742</v>
       </c>
       <c r="C470" t="n">
-        <v>9.967687457030143</v>
+        <v>9.9676884311345</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675011908180837</v>
+        <v>9.675012853683121</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892427670122959</v>
+        <v>9.892428636872463</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9852,16 +9852,16 @@
         <v>45002</v>
       </c>
       <c r="B472" t="n">
-        <v>9.942600250244141</v>
+        <v>9.942601203918457</v>
       </c>
       <c r="C472" t="n">
-        <v>10.18510343305635</v>
+        <v>10.18510440999109</v>
       </c>
       <c r="D472" t="n">
-        <v>9.750271095759805</v>
+        <v>9.750272030986295</v>
       </c>
       <c r="E472" t="n">
-        <v>10.18510343305635</v>
+        <v>10.18510440999109</v>
       </c>
       <c r="F472" t="n">
         <v>69952</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440871238708496</v>
+        <v>9.440873146057129</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583028050414784</v>
+        <v>9.583029986483497</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415785483825466</v>
+        <v>9.415787386105999</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532854860367744</v>
+        <v>9.532856786299918</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9932,16 +9932,16 @@
         <v>45008</v>
       </c>
       <c r="B476" t="n">
-        <v>9.332165718078613</v>
+        <v>9.332164764404297</v>
       </c>
       <c r="C476" t="n">
-        <v>9.407424678634545</v>
+        <v>9.407423717269351</v>
       </c>
       <c r="D476" t="n">
-        <v>9.131473756361691</v>
+        <v>9.131472823196523</v>
       </c>
       <c r="E476" t="n">
-        <v>9.399062758604034</v>
+        <v>9.399061798093364</v>
       </c>
       <c r="F476" t="n">
         <v>179094</v>
@@ -9952,16 +9952,16 @@
         <v>45009</v>
       </c>
       <c r="B477" t="n">
-        <v>9.641563415527344</v>
+        <v>9.641565322875977</v>
       </c>
       <c r="C477" t="n">
-        <v>9.666649168892544</v>
+        <v>9.666651081203783</v>
       </c>
       <c r="D477" t="n">
-        <v>9.089660878824608</v>
+        <v>9.089662676992758</v>
       </c>
       <c r="E477" t="n">
-        <v>9.373974485034596</v>
+        <v>9.373976339447273</v>
       </c>
       <c r="F477" t="n">
         <v>212279</v>
@@ -9972,16 +9972,16 @@
         <v>45012</v>
       </c>
       <c r="B478" t="n">
-        <v>10.46941757202148</v>
+        <v>10.4694185256958</v>
       </c>
       <c r="C478" t="n">
-        <v>10.54467736412381</v>
+        <v>10.54467832465365</v>
       </c>
       <c r="D478" t="n">
-        <v>9.87570451484077</v>
+        <v>9.875705414432909</v>
       </c>
       <c r="E478" t="n">
-        <v>10.3188988279574</v>
+        <v>10.31889976792075</v>
       </c>
       <c r="F478" t="n">
         <v>649270</v>
@@ -9992,16 +9992,16 @@
         <v>45013</v>
       </c>
       <c r="B479" t="n">
-        <v>10.70355796813965</v>
+        <v>10.70355892181396</v>
       </c>
       <c r="C479" t="n">
-        <v>10.74536840342739</v>
+        <v>10.74536936082696</v>
       </c>
       <c r="D479" t="n">
-        <v>10.32726068998773</v>
+        <v>10.3272616101344</v>
       </c>
       <c r="E479" t="n">
-        <v>10.46941751419095</v>
+        <v>10.46941844700363</v>
       </c>
       <c r="F479" t="n">
         <v>226923</v>
@@ -10132,16 +10132,16 @@
         <v>45022</v>
       </c>
       <c r="B486" t="n">
-        <v>9.541217803955078</v>
+        <v>9.541219711303711</v>
       </c>
       <c r="C486" t="n">
-        <v>9.633201427399317</v>
+        <v>9.633203353136047</v>
       </c>
       <c r="D486" t="n">
-        <v>9.39069907103355</v>
+        <v>9.390700948292555</v>
       </c>
       <c r="E486" t="n">
-        <v>9.52449312690135</v>
+        <v>9.524495030906616</v>
       </c>
       <c r="F486" t="n">
         <v>123364</v>
@@ -10152,16 +10152,16 @@
         <v>45026</v>
       </c>
       <c r="B487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="C487" t="n">
-        <v>9.700098570263346</v>
+        <v>9.700099553607547</v>
       </c>
       <c r="D487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="E487" t="n">
-        <v>9.574666431365994</v>
+        <v>9.574667401994555</v>
       </c>
       <c r="F487" t="n">
         <v>160237</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574666976928711</v>
+        <v>9.574666023254395</v>
       </c>
       <c r="C489" t="n">
-        <v>9.78372083371632</v>
+        <v>9.783719859219421</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574666976928711</v>
+        <v>9.574666023254395</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700099122973164</v>
+        <v>9.700098156805314</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683376312255859</v>
+        <v>9.683374404907227</v>
       </c>
       <c r="C490" t="n">
-        <v>9.775359951790064</v>
+        <v>9.77535802632328</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566306072823117</v>
+        <v>9.566304188533978</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608116512560244</v>
+        <v>9.608114620035645</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.658287048339844</v>
+        <v>9.65828800201416</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716821311770225</v>
+        <v>9.716822271224306</v>
       </c>
       <c r="D494" t="n">
-        <v>9.599751944769041</v>
+        <v>9.59975289266351</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616475779994744</v>
+        <v>9.616476729540551</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10352,16 +10352,16 @@
         <v>45041</v>
       </c>
       <c r="B497" t="n">
-        <v>9.248542785644531</v>
+        <v>9.248543739318848</v>
       </c>
       <c r="C497" t="n">
-        <v>9.633201978480185</v>
+        <v>9.633202971819085</v>
       </c>
       <c r="D497" t="n">
-        <v>9.248542785644531</v>
+        <v>9.248543739318848</v>
       </c>
       <c r="E497" t="n">
-        <v>9.633201978480185</v>
+        <v>9.633202971819085</v>
       </c>
       <c r="F497" t="n">
         <v>58153</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.281991958618164</v>
+        <v>9.28199291229248</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382337504280539</v>
+        <v>9.382338468264816</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215094088036043</v>
+        <v>9.215095034836967</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248542603256835</v>
+        <v>9.248543553494413</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10392,16 +10392,16 @@
         <v>45043</v>
       </c>
       <c r="B499" t="n">
-        <v>9.315439224243164</v>
+        <v>9.31544017791748</v>
       </c>
       <c r="C499" t="n">
-        <v>9.365612414939283</v>
+        <v>9.365613373750113</v>
       </c>
       <c r="D499" t="n">
-        <v>9.139833896947247</v>
+        <v>9.139834832643849</v>
       </c>
       <c r="E499" t="n">
-        <v>9.365612414939283</v>
+        <v>9.365613373750113</v>
       </c>
       <c r="F499" t="n">
         <v>124734</v>
@@ -10432,16 +10432,16 @@
         <v>45048</v>
       </c>
       <c r="B501" t="n">
-        <v>9.109169960021973</v>
+        <v>9.109169006347656</v>
       </c>
       <c r="C501" t="n">
-        <v>9.201266277130236</v>
+        <v>9.201265313813998</v>
       </c>
       <c r="D501" t="n">
-        <v>9.01707364291371</v>
+        <v>9.017072698881314</v>
       </c>
       <c r="E501" t="n">
-        <v>9.176148946797108</v>
+        <v>9.176147986110502</v>
       </c>
       <c r="F501" t="n">
         <v>926867</v>
@@ -10472,16 +10472,16 @@
         <v>45050</v>
       </c>
       <c r="B503" t="n">
-        <v>9.209638595581055</v>
+        <v>9.209637641906738</v>
       </c>
       <c r="C503" t="n">
-        <v>9.469182360300858</v>
+        <v>9.469181379750328</v>
       </c>
       <c r="D503" t="n">
-        <v>9.067306787235129</v>
+        <v>9.067305848299521</v>
       </c>
       <c r="E503" t="n">
-        <v>9.159403938655403</v>
+        <v>9.159402990182974</v>
       </c>
       <c r="F503" t="n">
         <v>221234</v>
@@ -10552,16 +10552,16 @@
         <v>45056</v>
       </c>
       <c r="B507" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586394309997559</v>
       </c>
       <c r="C507" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586394309997559</v>
       </c>
       <c r="D507" t="n">
-        <v>9.418946980877298</v>
+        <v>9.41894604386108</v>
       </c>
       <c r="E507" t="n">
-        <v>9.452436469202278</v>
+        <v>9.452435528854458</v>
       </c>
       <c r="F507" t="n">
         <v>185415</v>
@@ -10592,16 +10592,16 @@
         <v>45058</v>
       </c>
       <c r="B509" t="n">
-        <v>10.08036518096924</v>
+        <v>10.08036613464355</v>
       </c>
       <c r="C509" t="n">
-        <v>10.29804809336354</v>
+        <v>10.29804906763221</v>
       </c>
       <c r="D509" t="n">
-        <v>9.762214655603019</v>
+        <v>9.762215579178029</v>
       </c>
       <c r="E509" t="n">
-        <v>9.795704140316854</v>
+        <v>9.795705067060208</v>
       </c>
       <c r="F509" t="n">
         <v>501359</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845939636230469</v>
+        <v>9.845938682556152</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293249575018</v>
+        <v>10.27293150071748</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745471173433298</v>
+        <v>9.745470229490321</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548421658523</v>
+        <v>10.10548323777152</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10672,16 +10672,16 @@
         <v>45064</v>
       </c>
       <c r="B513" t="n">
-        <v>9.871057510375977</v>
+        <v>9.87105655670166</v>
       </c>
       <c r="C513" t="n">
-        <v>10.10548477775711</v>
+        <v>10.10548380143403</v>
       </c>
       <c r="D513" t="n">
-        <v>9.670119732453616</v>
+        <v>9.670118798192538</v>
       </c>
       <c r="E513" t="n">
-        <v>9.728725708129195</v>
+        <v>9.728724768206007</v>
       </c>
       <c r="F513" t="n">
         <v>659595</v>
@@ -10712,16 +10712,16 @@
         <v>45068</v>
       </c>
       <c r="B515" t="n">
-        <v>9.904544830322266</v>
+        <v>9.904545783996582</v>
       </c>
       <c r="C515" t="n">
-        <v>9.904544830322266</v>
+        <v>9.904545783996582</v>
       </c>
       <c r="D515" t="n">
-        <v>9.670118435550807</v>
+        <v>9.670119366653017</v>
       </c>
       <c r="E515" t="n">
-        <v>9.737097405485509</v>
+        <v>9.737098343036893</v>
       </c>
       <c r="F515" t="n">
         <v>159710</v>
@@ -10732,16 +10732,16 @@
         <v>45069</v>
       </c>
       <c r="B516" t="n">
-        <v>9.603140830993652</v>
+        <v>9.603139877319336</v>
       </c>
       <c r="C516" t="n">
-        <v>9.996643421238481</v>
+        <v>9.996642428485981</v>
       </c>
       <c r="D516" t="n">
-        <v>9.59476866812051</v>
+        <v>9.594767715277623</v>
       </c>
       <c r="E516" t="n">
-        <v>9.862685450589087</v>
+        <v>9.862684471139762</v>
       </c>
       <c r="F516" t="n">
         <v>117359</v>
@@ -10772,16 +10772,16 @@
         <v>45071</v>
       </c>
       <c r="B518" t="n">
-        <v>9.30173397064209</v>
+        <v>9.301733016967773</v>
       </c>
       <c r="C518" t="n">
-        <v>9.561278550437214</v>
+        <v>9.561277570152697</v>
       </c>
       <c r="D518" t="n">
-        <v>9.293361809052792</v>
+        <v>9.293360856236845</v>
       </c>
       <c r="E518" t="n">
-        <v>9.435691920749472</v>
+        <v>9.435690953340915</v>
       </c>
       <c r="F518" t="n">
         <v>216177</v>
@@ -10792,16 +10792,16 @@
         <v>45072</v>
       </c>
       <c r="B519" t="n">
-        <v>9.377084732055664</v>
+        <v>9.37708568572998</v>
       </c>
       <c r="C519" t="n">
-        <v>9.452435865683434</v>
+        <v>9.45243682702116</v>
       </c>
       <c r="D519" t="n">
-        <v>9.301733598427894</v>
+        <v>9.301734544438801</v>
       </c>
       <c r="E519" t="n">
-        <v>9.326850082190736</v>
+        <v>9.326851030756055</v>
       </c>
       <c r="F519" t="n">
         <v>104401</v>
@@ -10832,16 +10832,16 @@
         <v>45076</v>
       </c>
       <c r="B521" t="n">
-        <v>9.209638595581055</v>
+        <v>9.209637641906738</v>
       </c>
       <c r="C521" t="n">
-        <v>9.544533504519595</v>
+        <v>9.544532516166321</v>
       </c>
       <c r="D521" t="n">
-        <v>9.151030935054633</v>
+        <v>9.151029987449244</v>
       </c>
       <c r="E521" t="n">
-        <v>9.544533504519595</v>
+        <v>9.544532516166321</v>
       </c>
       <c r="F521" t="n">
         <v>214913</v>
@@ -10852,16 +10852,16 @@
         <v>45077</v>
       </c>
       <c r="B522" t="n">
-        <v>9.084051132202148</v>
+        <v>9.084050178527832</v>
       </c>
       <c r="C522" t="n">
-        <v>9.234754248188015</v>
+        <v>9.234753278692377</v>
       </c>
       <c r="D522" t="n">
-        <v>9.084051132202148</v>
+        <v>9.084050178527832</v>
       </c>
       <c r="E522" t="n">
-        <v>9.209637763165091</v>
+        <v>9.209636796306267</v>
       </c>
       <c r="F522" t="n">
         <v>138113</v>
@@ -10892,16 +10892,16 @@
         <v>45079</v>
       </c>
       <c r="B524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="C524" t="n">
-        <v>9.234754909248267</v>
+        <v>9.234753923397504</v>
       </c>
       <c r="D524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="E524" t="n">
-        <v>9.084051782474475</v>
+        <v>9.084050812711935</v>
       </c>
       <c r="F524" t="n">
         <v>446577</v>
@@ -10952,16 +10952,16 @@
         <v>45084</v>
       </c>
       <c r="B527" t="n">
-        <v>9.117542266845703</v>
+        <v>9.117541313171387</v>
       </c>
       <c r="C527" t="n">
-        <v>9.192893410911674</v>
+        <v>9.192892449355798</v>
       </c>
       <c r="D527" t="n">
-        <v>8.966838296374284</v>
+        <v>8.966837358463263</v>
       </c>
       <c r="E527" t="n">
-        <v>9.092424097264061</v>
+        <v>9.092423146217049</v>
       </c>
       <c r="F527" t="n">
         <v>438781</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.167776107788086</v>
+        <v>9.16777515411377</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226382927187608</v>
+        <v>9.226381967416739</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109169288388564</v>
+        <v>9.109168340810799</v>
       </c>
       <c r="E528" t="n">
-        <v>9.20963860231331</v>
+        <v>9.209637644284264</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -10992,16 +10992,16 @@
         <v>45089</v>
       </c>
       <c r="B529" t="n">
-        <v>9.18451976776123</v>
+        <v>9.184518814086914</v>
       </c>
       <c r="C529" t="n">
-        <v>9.24312658291799</v>
+        <v>9.243125623158235</v>
       </c>
       <c r="D529" t="n">
-        <v>9.134285955605209</v>
+        <v>9.13428500714692</v>
       </c>
       <c r="E529" t="n">
-        <v>9.209637935593761</v>
+        <v>9.209636979311302</v>
       </c>
       <c r="F529" t="n">
         <v>222709</v>
@@ -11212,16 +11212,16 @@
         <v>45104</v>
       </c>
       <c r="B540" t="n">
-        <v>8.791015625</v>
+        <v>8.791017532348633</v>
       </c>
       <c r="C540" t="n">
-        <v>8.991953360527468</v>
+        <v>8.991955311472692</v>
       </c>
       <c r="D540" t="n">
-        <v>8.724036660214018</v>
+        <v>8.724038553030516</v>
       </c>
       <c r="E540" t="n">
-        <v>8.958463878134477</v>
+        <v>8.958465821813633</v>
       </c>
       <c r="F540" t="n">
         <v>213544</v>
@@ -11232,16 +11232,16 @@
         <v>45105</v>
       </c>
       <c r="B541" t="n">
-        <v>8.657057762145996</v>
+        <v>8.657059669494629</v>
       </c>
       <c r="C541" t="n">
-        <v>8.874739819962821</v>
+        <v>8.87474177527181</v>
       </c>
       <c r="D541" t="n">
-        <v>8.657057762145996</v>
+        <v>8.657059669494629</v>
       </c>
       <c r="E541" t="n">
-        <v>8.874739819962821</v>
+        <v>8.87474177527181</v>
       </c>
       <c r="F541" t="n">
         <v>189418</v>
@@ -11252,16 +11252,16 @@
         <v>45106</v>
       </c>
       <c r="B542" t="n">
-        <v>8.782646179199219</v>
+        <v>8.782645225524902</v>
       </c>
       <c r="C542" t="n">
-        <v>8.849626005856582</v>
+        <v>8.84962504490918</v>
       </c>
       <c r="D542" t="n">
-        <v>8.615197874310489</v>
+        <v>8.615196938818752</v>
       </c>
       <c r="E542" t="n">
-        <v>8.665432534011066</v>
+        <v>8.665431593064536</v>
       </c>
       <c r="F542" t="n">
         <v>269063</v>
@@ -11272,16 +11272,16 @@
         <v>45107</v>
       </c>
       <c r="B543" t="n">
-        <v>9.050561904907227</v>
+        <v>9.05056095123291</v>
       </c>
       <c r="C543" t="n">
-        <v>9.176147698316207</v>
+        <v>9.176146731408684</v>
       </c>
       <c r="D543" t="n">
-        <v>8.765900829258186</v>
+        <v>8.765899905579127</v>
       </c>
       <c r="E543" t="n">
-        <v>8.782645153088882</v>
+        <v>8.782644227645445</v>
       </c>
       <c r="F543" t="n">
         <v>473547</v>
@@ -11292,16 +11292,16 @@
         <v>45110</v>
       </c>
       <c r="B544" t="n">
-        <v>9.410573959350586</v>
+        <v>9.410574913024902</v>
       </c>
       <c r="C544" t="n">
-        <v>9.418946120374542</v>
+        <v>9.4189470748973</v>
       </c>
       <c r="D544" t="n">
-        <v>9.00032629280234</v>
+        <v>9.000327204901865</v>
       </c>
       <c r="E544" t="n">
-        <v>9.067305263333189</v>
+        <v>9.06730618222041</v>
       </c>
       <c r="F544" t="n">
         <v>368934</v>
@@ -11312,16 +11312,16 @@
         <v>45111</v>
       </c>
       <c r="B545" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586394309997559</v>
       </c>
       <c r="C545" t="n">
-        <v>9.5947674254607</v>
+        <v>9.594766470953505</v>
       </c>
       <c r="D545" t="n">
-        <v>9.318478515902356</v>
+        <v>9.318477588880949</v>
       </c>
       <c r="E545" t="n">
-        <v>9.335222839480007</v>
+        <v>9.335221910792841</v>
       </c>
       <c r="F545" t="n">
         <v>135795</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695237159729004</v>
+        <v>9.695236206054688</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843977178107</v>
+        <v>9.753843017738918</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511043704053456</v>
+        <v>9.511042768497374</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611513014634612</v>
+        <v>9.611512069195841</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11392,16 +11392,16 @@
         <v>45117</v>
       </c>
       <c r="B549" t="n">
-        <v>9.619885444641113</v>
+        <v>9.619884490966797</v>
       </c>
       <c r="C549" t="n">
-        <v>9.745472086364286</v>
+        <v>9.745471120239847</v>
       </c>
       <c r="D549" t="n">
-        <v>9.527789134823944</v>
+        <v>9.527788190279663</v>
       </c>
       <c r="E549" t="n">
-        <v>9.628257607032745</v>
+        <v>9.628256652528449</v>
       </c>
       <c r="F549" t="n">
         <v>614083</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="D550" t="n">
-        <v>9.385457965682171</v>
+        <v>9.385458888088531</v>
       </c>
       <c r="E550" t="n">
-        <v>9.619884374764274</v>
+        <v>9.61988532021015</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11432,16 +11432,16 @@
         <v>45119</v>
       </c>
       <c r="B551" t="n">
-        <v>9.778960227966309</v>
+        <v>9.778959274291992</v>
       </c>
       <c r="C551" t="n">
-        <v>9.912919025122674</v>
+        <v>9.912918058384282</v>
       </c>
       <c r="D551" t="n">
-        <v>9.594767617899787</v>
+        <v>9.594766682188503</v>
       </c>
       <c r="E551" t="n">
-        <v>9.753843742096077</v>
+        <v>9.753842790871198</v>
       </c>
       <c r="F551" t="n">
         <v>281073</v>
@@ -11492,16 +11492,16 @@
         <v>45124</v>
       </c>
       <c r="B554" t="n">
-        <v>9.377084732055664</v>
+        <v>9.37708568572998</v>
       </c>
       <c r="C554" t="n">
-        <v>9.578022490345754</v>
+        <v>9.578023464455972</v>
       </c>
       <c r="D554" t="n">
-        <v>9.259871109817247</v>
+        <v>9.259872051570627</v>
       </c>
       <c r="E554" t="n">
-        <v>9.469181029361618</v>
+        <v>9.469181992402371</v>
       </c>
       <c r="F554" t="n">
         <v>232190</v>
@@ -11532,16 +11532,16 @@
         <v>45126</v>
       </c>
       <c r="B556" t="n">
-        <v>9.594766616821289</v>
+        <v>9.594767570495605</v>
       </c>
       <c r="C556" t="n">
-        <v>9.85431118092777</v>
+        <v>9.854312160399585</v>
       </c>
       <c r="D556" t="n">
-        <v>9.469180835894464</v>
+        <v>9.469181777086149</v>
       </c>
       <c r="E556" t="n">
-        <v>9.85431118092777</v>
+        <v>9.854312160399585</v>
       </c>
       <c r="F556" t="n">
         <v>152546</v>
@@ -11552,16 +11552,16 @@
         <v>45127</v>
       </c>
       <c r="B557" t="n">
-        <v>9.519417762756348</v>
+        <v>9.519416809082031</v>
       </c>
       <c r="C557" t="n">
-        <v>9.628258406392984</v>
+        <v>9.628257441814794</v>
       </c>
       <c r="D557" t="n">
-        <v>9.494300432326414</v>
+        <v>9.494299481168403</v>
       </c>
       <c r="E557" t="n">
-        <v>9.628258406392984</v>
+        <v>9.628257441814794</v>
       </c>
       <c r="F557" t="n">
         <v>109247</v>
@@ -11572,16 +11572,16 @@
         <v>45128</v>
       </c>
       <c r="B558" t="n">
-        <v>9.737098693847656</v>
+        <v>9.737099647521973</v>
       </c>
       <c r="C558" t="n">
-        <v>9.753843859131761</v>
+        <v>9.753844814446138</v>
       </c>
       <c r="D558" t="n">
-        <v>9.527788754229716</v>
+        <v>9.527789687403725</v>
       </c>
       <c r="E558" t="n">
-        <v>9.628257222425235</v>
+        <v>9.628258165439362</v>
       </c>
       <c r="F558" t="n">
         <v>205537</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711981520878043</v>
+        <v>9.711980587323517</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753844014168855</v>
+        <v>9.753843076590339</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11612,16 +11612,16 @@
         <v>45132</v>
       </c>
       <c r="B560" t="n">
-        <v>9.770586967468262</v>
+        <v>9.770587921142578</v>
       </c>
       <c r="C560" t="n">
-        <v>10.04687585150392</v>
+        <v>10.04687683214587</v>
       </c>
       <c r="D560" t="n">
-        <v>9.661746350758847</v>
+        <v>9.661747293809594</v>
       </c>
       <c r="E560" t="n">
-        <v>9.921290912763636</v>
+        <v>9.92129188114766</v>
       </c>
       <c r="F560" t="n">
         <v>194370</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728724479675293</v>
+        <v>9.728725433349609</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795704291304954</v>
+        <v>9.795705251545078</v>
       </c>
       <c r="D564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="E564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11792,16 +11792,16 @@
         <v>45145</v>
       </c>
       <c r="B569" t="n">
-        <v>9.879429817199707</v>
+        <v>9.879428863525391</v>
       </c>
       <c r="C569" t="n">
-        <v>9.988270449243014</v>
+        <v>9.988269485062169</v>
       </c>
       <c r="D569" t="n">
-        <v>9.770588343986683</v>
+        <v>9.770587400818977</v>
       </c>
       <c r="E569" t="n">
-        <v>9.988270449243014</v>
+        <v>9.988269485062169</v>
       </c>
       <c r="F569" t="n">
         <v>215967</v>
@@ -11852,16 +11852,16 @@
         <v>45148</v>
       </c>
       <c r="B572" t="n">
-        <v>9.778960227966309</v>
+        <v>9.778959274291992</v>
       </c>
       <c r="C572" t="n">
-        <v>9.837567885172595</v>
+        <v>9.837566925782678</v>
       </c>
       <c r="D572" t="n">
-        <v>9.54453296381994</v>
+        <v>9.544532033007691</v>
       </c>
       <c r="E572" t="n">
-        <v>9.5780232939863</v>
+        <v>9.578022359907973</v>
       </c>
       <c r="F572" t="n">
         <v>202060</v>
@@ -11932,16 +11932,16 @@
         <v>45154</v>
       </c>
       <c r="B576" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C576" t="n">
-        <v>11.2608749384303</v>
+        <v>11.26087395777899</v>
       </c>
       <c r="D576" t="n">
-        <v>10.78364824878957</v>
+        <v>10.78364730969746</v>
       </c>
       <c r="E576" t="n">
-        <v>11.05993716353692</v>
+        <v>11.05993620038423</v>
       </c>
       <c r="F576" t="n">
         <v>525379</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294612667715</v>
+        <v>10.63294521258928</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109669703995</v>
+        <v>10.95109575560148</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527669072958</v>
+        <v>10.77527578824517</v>
       </c>
       <c r="E578" t="n">
-        <v>11.09342811537701</v>
+        <v>11.0934271862458</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716278076172</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716278076172</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10179954134582</v>
+        <v>11.10179862365917</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877851856436</v>
+        <v>11.16877759534116</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12092,16 +12092,16 @@
         <v>45166</v>
       </c>
       <c r="B584" t="n">
-        <v>11.91392135620117</v>
+        <v>11.91392230987549</v>
       </c>
       <c r="C584" t="n">
-        <v>11.99764549411287</v>
+        <v>11.99764645448905</v>
       </c>
       <c r="D584" t="n">
-        <v>11.57065348428376</v>
+        <v>11.57065441048049</v>
       </c>
       <c r="E584" t="n">
-        <v>11.77996256730853</v>
+        <v>11.77996351025984</v>
       </c>
       <c r="F584" t="n">
         <v>779167</v>
@@ -12172,16 +12172,16 @@
         <v>45170</v>
       </c>
       <c r="B588" t="n">
-        <v>12.1232328414917</v>
+        <v>12.12323188781738</v>
       </c>
       <c r="C588" t="n">
-        <v>12.26556381015243</v>
+        <v>12.26556284528164</v>
       </c>
       <c r="D588" t="n">
-        <v>12.10648851645499</v>
+        <v>12.10648756409787</v>
       </c>
       <c r="E588" t="n">
-        <v>12.15672233273486</v>
+        <v>12.15672137642609</v>
       </c>
       <c r="F588" t="n">
         <v>195423</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625227825024</v>
+        <v>12.05625325429223</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66274975627503</v>
+        <v>11.66275070046011</v>
       </c>
       <c r="E589" t="n">
-        <v>11.9976454659665</v>
+        <v>11.99764643726385</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12232,16 +12232,16 @@
         <v>45175</v>
       </c>
       <c r="B591" t="n">
-        <v>11.74647426605225</v>
+        <v>11.74647521972656</v>
       </c>
       <c r="C591" t="n">
-        <v>11.90554954393114</v>
+        <v>11.90555051052048</v>
       </c>
       <c r="D591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="E591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="F591" t="n">
         <v>295506</v>
@@ -12252,16 +12252,16 @@
         <v>45177</v>
       </c>
       <c r="B592" t="n">
-        <v>11.77159118652344</v>
+        <v>11.77159023284912</v>
       </c>
       <c r="C592" t="n">
-        <v>11.82182584083579</v>
+        <v>11.82182488309172</v>
       </c>
       <c r="D592" t="n">
-        <v>11.59577073759991</v>
+        <v>11.59576979816967</v>
       </c>
       <c r="E592" t="n">
-        <v>11.74647470053696</v>
+        <v>11.74647374889745</v>
       </c>
       <c r="F592" t="n">
         <v>200375</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879096769665</v>
+        <v>11.52879190103679</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393436431885</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393436431885</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298276414397</v>
+        <v>11.71298367423283</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135576616107</v>
+        <v>11.72135667690049</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12332,16 +12332,16 @@
         <v>45183</v>
       </c>
       <c r="B596" t="n">
-        <v>12.34091377258301</v>
+        <v>12.34091472625732</v>
       </c>
       <c r="C596" t="n">
-        <v>12.51673421563881</v>
+        <v>12.51673518290008</v>
       </c>
       <c r="D596" t="n">
-        <v>12.2655626347989</v>
+        <v>12.26556358265027</v>
       </c>
       <c r="E596" t="n">
-        <v>12.47487256588872</v>
+        <v>12.47487352991503</v>
       </c>
       <c r="F596" t="n">
         <v>207012</v>
@@ -12372,16 +12372,16 @@
         <v>45187</v>
       </c>
       <c r="B598" t="n">
-        <v>11.69623947143555</v>
+        <v>11.69624042510986</v>
       </c>
       <c r="C598" t="n">
-        <v>11.93066672514645</v>
+        <v>11.93066769793522</v>
       </c>
       <c r="D598" t="n">
-        <v>11.69623947143555</v>
+        <v>11.69624042510986</v>
       </c>
       <c r="E598" t="n">
-        <v>11.90554939922461</v>
+        <v>11.9055503699654</v>
       </c>
       <c r="F598" t="n">
         <v>209119</v>
@@ -12412,16 +12412,16 @@
         <v>45189</v>
       </c>
       <c r="B600" t="n">
-        <v>11.83856964111328</v>
+        <v>11.8385705947876</v>
       </c>
       <c r="C600" t="n">
-        <v>11.91392077272479</v>
+        <v>11.91392173246913</v>
       </c>
       <c r="D600" t="n">
-        <v>11.62925972716968</v>
+        <v>11.62926066398271</v>
       </c>
       <c r="E600" t="n">
-        <v>11.62925972716968</v>
+        <v>11.62926066398271</v>
       </c>
       <c r="F600" t="n">
         <v>141695</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27762027064262</v>
+        <v>11.27761930113372</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760720758964</v>
+        <v>10.91760626903017</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901345381215</v>
+        <v>11.21901248934153</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876445770264</v>
+        <v>10.80876541137695</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854367052903</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="D608" t="n">
-        <v>10.7166681623136</v>
+        <v>10.71666910786212</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854367052903</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12592,16 +12592,16 @@
         <v>45202</v>
       </c>
       <c r="B609" t="n">
-        <v>10.5827112197876</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="C609" t="n">
-        <v>10.89248877953021</v>
+        <v>10.89248976112052</v>
       </c>
       <c r="D609" t="n">
-        <v>10.56596605487654</v>
+        <v>10.56596700704184</v>
       </c>
       <c r="E609" t="n">
-        <v>10.89248877953021</v>
+        <v>10.89248976112052</v>
       </c>
       <c r="F609" t="n">
         <v>176144</v>
@@ -12612,16 +12612,16 @@
         <v>45203</v>
       </c>
       <c r="B610" t="n">
-        <v>10.50735950469971</v>
+        <v>10.50735855102539</v>
       </c>
       <c r="C610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="D610" t="n">
-        <v>10.44037968453425</v>
+        <v>10.44037873693919</v>
       </c>
       <c r="E610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="F610" t="n">
         <v>180674</v>
@@ -12632,16 +12632,16 @@
         <v>45204</v>
       </c>
       <c r="B611" t="n">
-        <v>10.5827112197876</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="C611" t="n">
-        <v>10.5827112197876</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="D611" t="n">
-        <v>10.3315387931398</v>
+        <v>10.33153972417939</v>
       </c>
       <c r="E611" t="n">
-        <v>10.50735923944235</v>
+        <v>10.50736018632623</v>
       </c>
       <c r="F611" t="n">
         <v>99766</v>
@@ -12672,16 +12672,16 @@
         <v>45208</v>
       </c>
       <c r="B613" t="n">
-        <v>10.18920993804932</v>
+        <v>10.18920803070068</v>
       </c>
       <c r="C613" t="n">
-        <v>10.41526422473044</v>
+        <v>10.41526227506603</v>
       </c>
       <c r="D613" t="n">
-        <v>10.18920993804932</v>
+        <v>10.18920803070068</v>
       </c>
       <c r="E613" t="n">
-        <v>10.39851905774639</v>
+        <v>10.39851711121656</v>
       </c>
       <c r="F613" t="n">
         <v>296138</v>
@@ -12692,16 +12692,16 @@
         <v>45209</v>
       </c>
       <c r="B614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="D614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="E614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="F614" t="n">
         <v>338699</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691783905029</v>
+        <v>11.12691688537598</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226898470401</v>
+        <v>11.20226802457144</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690475362312</v>
+        <v>10.76690383080508</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970419810472</v>
+        <v>11.00970325447664</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12772,16 +12772,16 @@
         <v>45216</v>
       </c>
       <c r="B618" t="n">
-        <v>10.57433700561523</v>
+        <v>10.57433795928955</v>
       </c>
       <c r="C618" t="n">
-        <v>11.0264463123953</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="D618" t="n">
-        <v>10.41526174244343</v>
+        <v>10.41526268177113</v>
       </c>
       <c r="E618" t="n">
-        <v>11.0264463123953</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="F618" t="n">
         <v>572365</v>
@@ -12832,16 +12832,16 @@
         <v>45219</v>
       </c>
       <c r="B621" t="n">
-        <v>10.8757438659668</v>
+        <v>10.87574291229248</v>
       </c>
       <c r="C621" t="n">
-        <v>11.00970265448127</v>
+        <v>11.00970168906035</v>
       </c>
       <c r="D621" t="n">
-        <v>10.27293226174542</v>
+        <v>10.27293136093056</v>
       </c>
       <c r="E621" t="n">
-        <v>10.34828255566484</v>
+        <v>10.34828164824265</v>
       </c>
       <c r="F621" t="n">
         <v>2108154</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295902252197</v>
+        <v>10.99295806884766</v>
       </c>
       <c r="C622" t="n">
-        <v>11.13528999228917</v>
+        <v>11.13528902626719</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039339491465</v>
+        <v>10.80039245794601</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82551156500447</v>
+        <v>10.82551062585675</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12892,16 +12892,16 @@
         <v>45224</v>
       </c>
       <c r="B624" t="n">
-        <v>11.25250244140625</v>
+        <v>11.25250339508057</v>
       </c>
       <c r="C624" t="n">
-        <v>11.37808823153628</v>
+        <v>11.37808919585427</v>
       </c>
       <c r="D624" t="n">
-        <v>11.06830899588992</v>
+        <v>11.06830993395344</v>
       </c>
       <c r="E624" t="n">
-        <v>11.26087460310301</v>
+        <v>11.26087555748688</v>
       </c>
       <c r="F624" t="n">
         <v>356609</v>
@@ -12932,16 +12932,16 @@
         <v>45226</v>
       </c>
       <c r="B626" t="n">
-        <v>10.98458480834961</v>
+        <v>10.98458576202393</v>
       </c>
       <c r="C626" t="n">
-        <v>11.53716257670716</v>
+        <v>11.53716357835591</v>
       </c>
       <c r="D626" t="n">
-        <v>10.96783964514047</v>
+        <v>10.96784059736098</v>
       </c>
       <c r="E626" t="n">
-        <v>11.33622482404551</v>
+        <v>11.33622580824897</v>
       </c>
       <c r="F626" t="n">
         <v>172878</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668177956321</v>
+        <v>11.07668279217249</v>
       </c>
       <c r="D627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="E627" t="n">
-        <v>10.99295764074342</v>
+        <v>10.9929586456988</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -13212,16 +13212,16 @@
         <v>45250</v>
       </c>
       <c r="B640" t="n">
-        <v>12.99803733825684</v>
+        <v>12.99803638458252</v>
       </c>
       <c r="C640" t="n">
-        <v>13.12497196915852</v>
+        <v>13.12497100617093</v>
       </c>
       <c r="D640" t="n">
-        <v>12.59184906996684</v>
+        <v>12.59184814609482</v>
       </c>
       <c r="E640" t="n">
-        <v>12.73570690132464</v>
+        <v>12.73570596689768</v>
       </c>
       <c r="F640" t="n">
         <v>416026</v>
@@ -13252,16 +13252,16 @@
         <v>45252</v>
       </c>
       <c r="B642" t="n">
-        <v>12.39721584320068</v>
+        <v>12.397216796875</v>
       </c>
       <c r="C642" t="n">
-        <v>12.7864800390811</v>
+        <v>12.78648102270015</v>
       </c>
       <c r="D642" t="n">
-        <v>12.39721584320068</v>
+        <v>12.397216796875</v>
       </c>
       <c r="E642" t="n">
-        <v>12.57492261613453</v>
+        <v>12.5749235834792</v>
       </c>
       <c r="F642" t="n">
         <v>163818</v>
@@ -13312,16 +13312,16 @@
         <v>45257</v>
       </c>
       <c r="B645" t="n">
-        <v>13.20959281921387</v>
+        <v>13.20959377288818</v>
       </c>
       <c r="C645" t="n">
-        <v>13.20959281921387</v>
+        <v>13.20959377288818</v>
       </c>
       <c r="D645" t="n">
-        <v>12.48183825026513</v>
+        <v>12.48183915139878</v>
       </c>
       <c r="E645" t="n">
-        <v>12.6849336558116</v>
+        <v>12.68493457160784</v>
       </c>
       <c r="F645" t="n">
         <v>390742</v>
@@ -13392,16 +13392,16 @@
         <v>45261</v>
       </c>
       <c r="B649" t="n">
-        <v>13.22651958465576</v>
+        <v>13.22651863098145</v>
       </c>
       <c r="C649" t="n">
-        <v>13.35345337266199</v>
+        <v>13.35345240983534</v>
       </c>
       <c r="D649" t="n">
-        <v>12.9895760602716</v>
+        <v>12.98957512368167</v>
       </c>
       <c r="E649" t="n">
-        <v>12.9895760602716</v>
+        <v>12.98957512368167</v>
       </c>
       <c r="F649" t="n">
         <v>156128</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413126845579</v>
+        <v>12.30413217772953</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568784548951</v>
+        <v>12.51568877039725</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13512,16 +13512,16 @@
         <v>45271</v>
       </c>
       <c r="B655" t="n">
-        <v>12.73570728302002</v>
+        <v>12.73570823669434</v>
       </c>
       <c r="C655" t="n">
-        <v>13.05727360727768</v>
+        <v>13.0572745850315</v>
       </c>
       <c r="D655" t="n">
-        <v>12.57492369579195</v>
+        <v>12.57492463742648</v>
       </c>
       <c r="E655" t="n">
-        <v>12.82033008942451</v>
+        <v>12.82033104943554</v>
       </c>
       <c r="F655" t="n">
         <v>302669</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109408341076</v>
+        <v>12.76109316972536</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033884434287</v>
+        <v>12.93033791853966</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13552,16 +13552,16 @@
         <v>45273</v>
       </c>
       <c r="B657" t="n">
-        <v>13.27729225158691</v>
+        <v>13.2772912979126</v>
       </c>
       <c r="C657" t="n">
-        <v>13.29421630278417</v>
+        <v>13.29421534789424</v>
       </c>
       <c r="D657" t="n">
-        <v>12.92187697406255</v>
+        <v>12.92187604591681</v>
       </c>
       <c r="E657" t="n">
-        <v>13.23498127339527</v>
+        <v>13.23498032276005</v>
       </c>
       <c r="F657" t="n">
         <v>131160</v>
@@ -13632,16 +13632,16 @@
         <v>45279</v>
       </c>
       <c r="B661" t="n">
-        <v>13.39576435089111</v>
+        <v>13.3957633972168</v>
       </c>
       <c r="C661" t="n">
-        <v>13.45500023198255</v>
+        <v>13.4549992740911</v>
       </c>
       <c r="D661" t="n">
-        <v>13.17574572835084</v>
+        <v>13.17574479034014</v>
       </c>
       <c r="E661" t="n">
-        <v>13.20959383160479</v>
+        <v>13.20959289118437</v>
       </c>
       <c r="F661" t="n">
         <v>220918</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45499992370605</v>
+        <v>13.45499897003174</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040546826266</v>
+        <v>13.70040449719429</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806613861795</v>
+        <v>13.32806519394055</v>
       </c>
       <c r="E662" t="n">
-        <v>13.3873011681537</v>
+        <v>13.38730021927779</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13832,16 +13832,16 @@
         <v>45296</v>
       </c>
       <c r="B671" t="n">
-        <v>13.96731948852539</v>
+        <v>13.96732044219971</v>
       </c>
       <c r="C671" t="n">
-        <v>14.27056950151718</v>
+        <v>14.27057047589709</v>
       </c>
       <c r="D671" t="n">
-        <v>13.8692094010509</v>
+        <v>13.86921034802636</v>
       </c>
       <c r="E671" t="n">
-        <v>13.97623923909369</v>
+        <v>13.97624019337704</v>
       </c>
       <c r="F671" t="n">
         <v>90074</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623825073242</v>
+        <v>13.97623920440674</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461235886199</v>
+        <v>13.82461330219005</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13952,16 +13952,16 @@
         <v>45306</v>
       </c>
       <c r="B677" t="n">
-        <v>14.35084056854248</v>
+        <v>14.3508415222168</v>
       </c>
       <c r="C677" t="n">
-        <v>14.43111294475096</v>
+        <v>14.43111390375971</v>
       </c>
       <c r="D677" t="n">
-        <v>13.91380416674507</v>
+        <v>13.91380509137646</v>
       </c>
       <c r="E677" t="n">
-        <v>14.07434891916202</v>
+        <v>14.07434985446229</v>
       </c>
       <c r="F677" t="n">
         <v>161817</v>
@@ -14212,16 +14212,16 @@
         <v>45323</v>
       </c>
       <c r="B690" t="n">
-        <v>13.708664894104</v>
+        <v>13.70866584777832</v>
       </c>
       <c r="C690" t="n">
-        <v>13.708664894104</v>
+        <v>13.70866584777832</v>
       </c>
       <c r="D690" t="n">
-        <v>13.05756973034824</v>
+        <v>13.05757063872765</v>
       </c>
       <c r="E690" t="n">
-        <v>13.48568727015147</v>
+        <v>13.48568820831384</v>
       </c>
       <c r="F690" t="n">
         <v>1088052</v>
@@ -14332,16 +14332,16 @@
         <v>45331</v>
       </c>
       <c r="B696" t="n">
-        <v>13.8692102432251</v>
+        <v>13.86920928955078</v>
       </c>
       <c r="C696" t="n">
-        <v>13.8692102432251</v>
+        <v>13.86920928955078</v>
       </c>
       <c r="D696" t="n">
-        <v>13.49460757952268</v>
+        <v>13.49460665160678</v>
       </c>
       <c r="E696" t="n">
-        <v>13.74434358475478</v>
+        <v>13.74434263966654</v>
       </c>
       <c r="F696" t="n">
         <v>146541</v>
@@ -14532,16 +14532,16 @@
         <v>45349</v>
       </c>
       <c r="B706" t="n">
-        <v>13.64623355865479</v>
+        <v>13.64623260498047</v>
       </c>
       <c r="C706" t="n">
-        <v>13.91380548303835</v>
+        <v>13.91380451066463</v>
       </c>
       <c r="D706" t="n">
-        <v>13.56596117485227</v>
+        <v>13.56596022678783</v>
       </c>
       <c r="E706" t="n">
-        <v>13.6283940563469</v>
+        <v>13.6283931039193</v>
       </c>
       <c r="F706" t="n">
         <v>240197</v>
@@ -14572,16 +14572,16 @@
         <v>45351</v>
       </c>
       <c r="B708" t="n">
-        <v>13.64623355865479</v>
+        <v>13.64623260498047</v>
       </c>
       <c r="C708" t="n">
-        <v>13.73542300531976</v>
+        <v>13.73542204541239</v>
       </c>
       <c r="D708" t="n">
-        <v>13.46785108093619</v>
+        <v>13.46785013972823</v>
       </c>
       <c r="E708" t="n">
-        <v>13.46785108093619</v>
+        <v>13.46785013972823</v>
       </c>
       <c r="F708" t="n">
         <v>71953</v>
@@ -14612,16 +14612,16 @@
         <v>45355</v>
       </c>
       <c r="B710" t="n">
-        <v>13.57487964630127</v>
+        <v>13.57487869262695</v>
       </c>
       <c r="C710" t="n">
-        <v>13.58379850110602</v>
+        <v>13.58379754680512</v>
       </c>
       <c r="D710" t="n">
-        <v>13.2537910162619</v>
+        <v>13.25379008514498</v>
       </c>
       <c r="E710" t="n">
-        <v>13.41433577933015</v>
+        <v>13.4143348369345</v>
       </c>
       <c r="F710" t="n">
         <v>828997</v>
@@ -14632,16 +14632,16 @@
         <v>45356</v>
       </c>
       <c r="B711" t="n">
-        <v>13.57487964630127</v>
+        <v>13.57487869262695</v>
       </c>
       <c r="C711" t="n">
-        <v>13.62839367122688</v>
+        <v>13.62839271379305</v>
       </c>
       <c r="D711" t="n">
-        <v>13.33406339779602</v>
+        <v>13.33406246103974</v>
       </c>
       <c r="E711" t="n">
-        <v>13.62839367122688</v>
+        <v>13.62839271379305</v>
       </c>
       <c r="F711" t="n">
         <v>182781</v>
@@ -14732,16 +14732,16 @@
         <v>45363</v>
       </c>
       <c r="B716" t="n">
-        <v>15.42113399505615</v>
+        <v>15.42113494873047</v>
       </c>
       <c r="C716" t="n">
-        <v>15.98303706065691</v>
+        <v>15.98303804908045</v>
       </c>
       <c r="D716" t="n">
-        <v>13.85137169862826</v>
+        <v>13.85137255522528</v>
       </c>
       <c r="E716" t="n">
-        <v>14.09218704214369</v>
+        <v>14.09218791363322</v>
       </c>
       <c r="F716" t="n">
         <v>1351743</v>
@@ -14772,16 +14772,16 @@
         <v>45365</v>
       </c>
       <c r="B718" t="n">
-        <v>15.78681755065918</v>
+        <v>15.78681564331055</v>
       </c>
       <c r="C718" t="n">
-        <v>15.99195748491486</v>
+        <v>15.99195555278141</v>
       </c>
       <c r="D718" t="n">
-        <v>15.5816776164035</v>
+        <v>15.58167573383968</v>
       </c>
       <c r="E718" t="n">
-        <v>15.78681755065918</v>
+        <v>15.78681564331055</v>
       </c>
       <c r="F718" t="n">
         <v>580477</v>
@@ -14832,16 +14832,16 @@
         <v>45370</v>
       </c>
       <c r="B721" t="n">
-        <v>16.15250205993652</v>
+        <v>16.15250015258789</v>
       </c>
       <c r="C721" t="n">
-        <v>16.15250205993652</v>
+        <v>16.15250015258789</v>
       </c>
       <c r="D721" t="n">
-        <v>15.61735464537877</v>
+        <v>15.61735280122237</v>
       </c>
       <c r="E721" t="n">
-        <v>15.83141432807958</v>
+        <v>15.8314124586462</v>
       </c>
       <c r="F721" t="n">
         <v>227239</v>
@@ -14912,16 +14912,16 @@
         <v>45376</v>
       </c>
       <c r="B725" t="n">
-        <v>15.59951591491699</v>
+        <v>15.59951686859131</v>
       </c>
       <c r="C725" t="n">
-        <v>16.24169133660133</v>
+        <v>16.24169232953496</v>
       </c>
       <c r="D725" t="n">
-        <v>15.48356633031139</v>
+        <v>15.48356727689714</v>
       </c>
       <c r="E725" t="n">
-        <v>15.80465404115356</v>
+        <v>15.80465500736896</v>
       </c>
       <c r="F725" t="n">
         <v>355555</v>
@@ -14952,16 +14952,16 @@
         <v>45378</v>
       </c>
       <c r="B727" t="n">
-        <v>15.4300537109375</v>
+        <v>15.43005275726318</v>
       </c>
       <c r="C727" t="n">
-        <v>15.75114143230092</v>
+        <v>15.75114045878136</v>
       </c>
       <c r="D727" t="n">
-        <v>14.90382606442144</v>
+        <v>14.9038251432713</v>
       </c>
       <c r="E727" t="n">
-        <v>15.23383353633731</v>
+        <v>15.23383259479063</v>
       </c>
       <c r="F727" t="n">
         <v>340806</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196426391602</v>
+        <v>16.32196617126465</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55385985657521</v>
+        <v>16.55386179102265</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26059101143806</v>
+        <v>15.26059279475697</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005372674877</v>
+        <v>15.43005552987071</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -15032,16 +15032,16 @@
         <v>45385</v>
       </c>
       <c r="B731" t="n">
-        <v>16.1346607208252</v>
+        <v>16.13466262817383</v>
       </c>
       <c r="C731" t="n">
-        <v>16.6162931598592</v>
+        <v>16.6162951241437</v>
       </c>
       <c r="D731" t="n">
-        <v>16.0187129340293</v>
+        <v>16.01871482767124</v>
       </c>
       <c r="E731" t="n">
-        <v>16.53602078798786</v>
+        <v>16.53602274278301</v>
       </c>
       <c r="F731" t="n">
         <v>812246</v>
@@ -15072,16 +15072,16 @@
         <v>45387</v>
       </c>
       <c r="B733" t="n">
-        <v>15.78681755065918</v>
+        <v>15.78681564331055</v>
       </c>
       <c r="C733" t="n">
-        <v>16.24169258952326</v>
+        <v>16.24169062721705</v>
       </c>
       <c r="D733" t="n">
-        <v>15.71546491965596</v>
+        <v>15.71546302092809</v>
       </c>
       <c r="E733" t="n">
-        <v>15.84033247196016</v>
+        <v>15.84033055814591</v>
       </c>
       <c r="F733" t="n">
         <v>540022</v>
@@ -15152,16 +15152,16 @@
         <v>45393</v>
       </c>
       <c r="B737" t="n">
-        <v>14.95510864257812</v>
+        <v>14.95510768890381</v>
       </c>
       <c r="C737" t="n">
-        <v>15.20600329805515</v>
+        <v>15.2060023283815</v>
       </c>
       <c r="D737" t="n">
-        <v>14.75797802365761</v>
+        <v>14.75797708255414</v>
       </c>
       <c r="E737" t="n">
-        <v>15.02679372595442</v>
+        <v>15.02679276770881</v>
       </c>
       <c r="F737" t="n">
         <v>214129</v>
@@ -15172,16 +15172,16 @@
         <v>45394</v>
       </c>
       <c r="B738" t="n">
-        <v>14.96406841278076</v>
+        <v>14.96406936645508</v>
       </c>
       <c r="C738" t="n">
-        <v>15.14327886659233</v>
+        <v>15.1432798316879</v>
       </c>
       <c r="D738" t="n">
-        <v>14.76693691358803</v>
+        <v>14.76693785469897</v>
       </c>
       <c r="E738" t="n">
-        <v>14.96406841278076</v>
+        <v>14.96406936645508</v>
       </c>
       <c r="F738" t="n">
         <v>376247</v>
@@ -15232,16 +15232,16 @@
         <v>45399</v>
       </c>
       <c r="B741" t="n">
-        <v>14.89238452911377</v>
+        <v>14.89238548278809</v>
       </c>
       <c r="C741" t="n">
-        <v>15.08951513615217</v>
+        <v>15.08951610245028</v>
       </c>
       <c r="D741" t="n">
-        <v>14.74901526709996</v>
+        <v>14.74901621159323</v>
       </c>
       <c r="E741" t="n">
-        <v>14.91030557485336</v>
+        <v>14.9103065296753</v>
       </c>
       <c r="F741" t="n">
         <v>190430</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051448822021</v>
+        <v>15.77051544189453</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804076002569</v>
+        <v>15.87804172020233</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847573748455</v>
+        <v>15.09847665051934</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808006789204</v>
+        <v>15.18808098634539</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15312,16 +15312,16 @@
         <v>45405</v>
       </c>
       <c r="B745" t="n">
-        <v>16.22750282287598</v>
+        <v>16.22750091552734</v>
       </c>
       <c r="C745" t="n">
-        <v>16.44255539468171</v>
+        <v>16.44255346205622</v>
       </c>
       <c r="D745" t="n">
-        <v>15.59130607933261</v>
+        <v>15.59130424676128</v>
       </c>
       <c r="E745" t="n">
-        <v>15.77051655583738</v>
+        <v>15.77051470220201</v>
       </c>
       <c r="F745" t="n">
         <v>640292</v>
@@ -15372,16 +15372,16 @@
         <v>45408</v>
       </c>
       <c r="B748" t="n">
-        <v>16.41567230224609</v>
+        <v>16.41567420959473</v>
       </c>
       <c r="C748" t="n">
-        <v>16.74721209206137</v>
+        <v>16.74721403793184</v>
       </c>
       <c r="D748" t="n">
-        <v>16.14685751582961</v>
+        <v>16.14685939194446</v>
       </c>
       <c r="E748" t="n">
-        <v>16.48735648424971</v>
+        <v>16.48735839992738</v>
       </c>
       <c r="F748" t="n">
         <v>618795</v>
@@ -15452,16 +15452,16 @@
         <v>45415</v>
       </c>
       <c r="B752" t="n">
-        <v>16.26334381103516</v>
+        <v>16.26334190368652</v>
       </c>
       <c r="C752" t="n">
-        <v>16.45151524660383</v>
+        <v>16.45151331718664</v>
       </c>
       <c r="D752" t="n">
-        <v>16.17373947497985</v>
+        <v>16.17373757813992</v>
       </c>
       <c r="E752" t="n">
-        <v>16.23646268943799</v>
+        <v>16.23646078524195</v>
       </c>
       <c r="F752" t="n">
         <v>303682</v>
@@ -15712,16 +15712,16 @@
         <v>45434</v>
       </c>
       <c r="B765" t="n">
-        <v>14.92822742462158</v>
+        <v>14.92822647094727</v>
       </c>
       <c r="C765" t="n">
-        <v>15.10743789166969</v>
+        <v>15.1074369265467</v>
       </c>
       <c r="D765" t="n">
-        <v>14.82966121969655</v>
+        <v>14.82966027231904</v>
       </c>
       <c r="E765" t="n">
-        <v>15.06263482685909</v>
+        <v>15.0626338645983</v>
       </c>
       <c r="F765" t="n">
         <v>235522</v>
@@ -15732,16 +15732,16 @@
         <v>45435</v>
       </c>
       <c r="B766" t="n">
-        <v>14.87446308135986</v>
+        <v>14.87446403503418</v>
       </c>
       <c r="C766" t="n">
-        <v>14.9461472623808</v>
+        <v>14.94614822065114</v>
       </c>
       <c r="D766" t="n">
-        <v>14.73109471931798</v>
+        <v>14.73109566380025</v>
       </c>
       <c r="E766" t="n">
-        <v>14.93718629170465</v>
+        <v>14.93718724940046</v>
       </c>
       <c r="F766" t="n">
         <v>226398</v>
@@ -15752,16 +15752,16 @@
         <v>45436</v>
       </c>
       <c r="B767" t="n">
-        <v>14.81173992156982</v>
+        <v>14.81173896789551</v>
       </c>
       <c r="C767" t="n">
-        <v>14.90134515357287</v>
+        <v>14.9013441941292</v>
       </c>
       <c r="D767" t="n">
-        <v>14.74005573596738</v>
+        <v>14.74005478690855</v>
       </c>
       <c r="E767" t="n">
-        <v>14.78485790392035</v>
+        <v>14.78485695197687</v>
       </c>
       <c r="F767" t="n">
         <v>297600</v>
@@ -15772,16 +15772,16 @@
         <v>45439</v>
       </c>
       <c r="B768" t="n">
-        <v>14.93718719482422</v>
+        <v>14.9371862411499</v>
       </c>
       <c r="C768" t="n">
-        <v>15.0715954904135</v>
+        <v>15.0715945281578</v>
       </c>
       <c r="D768" t="n">
-        <v>14.74005568509783</v>
+        <v>14.7400547440095</v>
       </c>
       <c r="E768" t="n">
-        <v>14.90134510214669</v>
+        <v>14.90134415076074</v>
       </c>
       <c r="F768" t="n">
         <v>153938</v>
@@ -15812,16 +15812,16 @@
         <v>45441</v>
       </c>
       <c r="B770" t="n">
-        <v>14.77589702606201</v>
+        <v>14.77589797973633</v>
       </c>
       <c r="C770" t="n">
-        <v>14.84758120777018</v>
+        <v>14.84758216607118</v>
       </c>
       <c r="D770" t="n">
-        <v>14.5250032861805</v>
+        <v>14.52500422366149</v>
       </c>
       <c r="E770" t="n">
-        <v>14.84758120777018</v>
+        <v>14.84758216607118</v>
       </c>
       <c r="F770" t="n">
         <v>377820</v>
@@ -15852,16 +15852,16 @@
         <v>45446</v>
       </c>
       <c r="B772" t="n">
-        <v>14.33683204650879</v>
+        <v>14.33683109283447</v>
       </c>
       <c r="C772" t="n">
-        <v>15.36729261993504</v>
+        <v>15.36729159771533</v>
       </c>
       <c r="D772" t="n">
-        <v>14.33683204650879</v>
+        <v>14.33683109283447</v>
       </c>
       <c r="E772" t="n">
-        <v>14.69525295968364</v>
+        <v>14.69525198216746</v>
       </c>
       <c r="F772" t="n">
         <v>2218059</v>
@@ -15872,16 +15872,16 @@
         <v>45447</v>
       </c>
       <c r="B773" t="n">
-        <v>14.18450355529785</v>
+        <v>14.18450450897217</v>
       </c>
       <c r="C773" t="n">
-        <v>14.39059513158153</v>
+        <v>14.39059609911211</v>
       </c>
       <c r="D773" t="n">
-        <v>14.0142531741053</v>
+        <v>14.01425411633309</v>
       </c>
       <c r="E773" t="n">
-        <v>14.39059513158153</v>
+        <v>14.39059609911211</v>
       </c>
       <c r="F773" t="n">
         <v>553151</v>
@@ -15932,16 +15932,16 @@
         <v>45450</v>
       </c>
       <c r="B776" t="n">
-        <v>13.44078063964844</v>
+        <v>13.44077968597412</v>
       </c>
       <c r="C776" t="n">
-        <v>13.99633309128065</v>
+        <v>13.99633209818778</v>
       </c>
       <c r="D776" t="n">
-        <v>13.44078063964844</v>
+        <v>13.44077968597412</v>
       </c>
       <c r="E776" t="n">
-        <v>13.9784120444538</v>
+        <v>13.9784110526325</v>
       </c>
       <c r="F776" t="n">
         <v>667347</v>
@@ -15992,16 +15992,16 @@
         <v>45455</v>
       </c>
       <c r="B779" t="n">
-        <v>13.15404415130615</v>
+        <v>13.15404319763184</v>
       </c>
       <c r="C779" t="n">
-        <v>13.61999137804538</v>
+        <v>13.61999039058967</v>
       </c>
       <c r="D779" t="n">
-        <v>13.02859771712737</v>
+        <v>13.02859677254798</v>
       </c>
       <c r="E779" t="n">
-        <v>13.42285985904032</v>
+        <v>13.42285888587674</v>
       </c>
       <c r="F779" t="n">
         <v>631798</v>
@@ -16012,16 +16012,16 @@
         <v>45456</v>
       </c>
       <c r="B780" t="n">
-        <v>13.01067543029785</v>
+        <v>13.01067447662354</v>
       </c>
       <c r="C780" t="n">
-        <v>13.26157098032195</v>
+        <v>13.26157000825715</v>
       </c>
       <c r="D780" t="n">
-        <v>13.01067543029785</v>
+        <v>13.01067447662354</v>
       </c>
       <c r="E780" t="n">
-        <v>13.1540438039704</v>
+        <v>13.15404283978727</v>
       </c>
       <c r="F780" t="n">
         <v>210250</v>
@@ -16032,16 +16032,16 @@
         <v>45457</v>
       </c>
       <c r="B781" t="n">
-        <v>13.07339859008789</v>
+        <v>13.07339954376221</v>
       </c>
       <c r="C781" t="n">
-        <v>13.27053008953652</v>
+        <v>13.27053105759112</v>
       </c>
       <c r="D781" t="n">
-        <v>12.90314821069736</v>
+        <v>12.9031491519523</v>
       </c>
       <c r="E781" t="n">
-        <v>13.06443761933714</v>
+        <v>13.06443857235778</v>
       </c>
       <c r="F781" t="n">
         <v>928770</v>
@@ -16152,16 +16152,16 @@
         <v>45467</v>
       </c>
       <c r="B787" t="n">
-        <v>13.18988609313965</v>
+        <v>13.18988704681396</v>
       </c>
       <c r="C787" t="n">
-        <v>13.23468825948488</v>
+        <v>13.23468921639855</v>
       </c>
       <c r="D787" t="n">
-        <v>12.90314846492238</v>
+        <v>12.90314939786458</v>
       </c>
       <c r="E787" t="n">
-        <v>12.90314846492238</v>
+        <v>12.90314939786458</v>
       </c>
       <c r="F787" t="n">
         <v>668186</v>
@@ -16212,16 +16212,16 @@
         <v>45470</v>
       </c>
       <c r="B790" t="n">
-        <v>13.18092441558838</v>
+        <v>13.1809253692627</v>
       </c>
       <c r="C790" t="n">
-        <v>13.26156956522237</v>
+        <v>13.26157052473157</v>
       </c>
       <c r="D790" t="n">
-        <v>12.83146359400282</v>
+        <v>12.83146452239273</v>
       </c>
       <c r="E790" t="n">
-        <v>12.90314777318991</v>
+        <v>12.90314870676636</v>
       </c>
       <c r="F790" t="n">
         <v>447659</v>
@@ -16272,16 +16272,16 @@
         <v>45475</v>
       </c>
       <c r="B793" t="n">
-        <v>13.29741382598877</v>
+        <v>13.29741287231445</v>
       </c>
       <c r="C793" t="n">
-        <v>13.54830759801191</v>
+        <v>13.5483066263438</v>
       </c>
       <c r="D793" t="n">
-        <v>13.27053180635585</v>
+        <v>13.27053085460948</v>
       </c>
       <c r="E793" t="n">
-        <v>13.36013704497026</v>
+        <v>13.36013608679751</v>
       </c>
       <c r="F793" t="n">
         <v>528404</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61102962493896</v>
+        <v>13.61103057861328</v>
       </c>
       <c r="C795" t="n">
-        <v>13.70063484980648</v>
+        <v>13.7006358097591</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766126515094</v>
+        <v>13.46766220877997</v>
       </c>
       <c r="E795" t="n">
-        <v>13.59310768386841</v>
+        <v>13.593108636287</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16332,16 +16332,16 @@
         <v>45478</v>
       </c>
       <c r="B796" t="n">
-        <v>13.54830646514893</v>
+        <v>13.54830551147461</v>
       </c>
       <c r="C796" t="n">
-        <v>13.88880634341223</v>
+        <v>13.8888053657699</v>
       </c>
       <c r="D796" t="n">
-        <v>13.27949077178316</v>
+        <v>13.27948983703096</v>
       </c>
       <c r="E796" t="n">
-        <v>13.87088619328496</v>
+        <v>13.87088521690404</v>
       </c>
       <c r="F796" t="n">
         <v>907063</v>
@@ -16392,16 +16392,16 @@
         <v>45483</v>
       </c>
       <c r="B799" t="n">
-        <v>13.63791084289551</v>
+        <v>13.63791179656982</v>
       </c>
       <c r="C799" t="n">
-        <v>13.78127920371949</v>
+        <v>13.78128016741929</v>
       </c>
       <c r="D799" t="n">
-        <v>13.56622755858058</v>
+        <v>13.56622850724222</v>
       </c>
       <c r="E799" t="n">
-        <v>13.71855599390753</v>
+        <v>13.71855695322121</v>
       </c>
       <c r="F799" t="n">
         <v>395437</v>
@@ -16572,16 +16572,16 @@
         <v>45496</v>
       </c>
       <c r="B808" t="n">
-        <v>13.75439739227295</v>
+        <v>13.75439834594727</v>
       </c>
       <c r="C808" t="n">
-        <v>13.94256881669735</v>
+        <v>13.94256978341871</v>
       </c>
       <c r="D808" t="n">
-        <v>13.66479306152438</v>
+        <v>13.66479400898589</v>
       </c>
       <c r="E808" t="n">
-        <v>13.88880568058996</v>
+        <v>13.8888066435836</v>
       </c>
       <c r="F808" t="n">
         <v>454685</v>
@@ -16752,16 +16752,16 @@
         <v>45509</v>
       </c>
       <c r="B817" t="n">
-        <v>12.77770042419434</v>
+        <v>12.77770137786865</v>
       </c>
       <c r="C817" t="n">
-        <v>13.23468751329381</v>
+        <v>13.23468850107574</v>
       </c>
       <c r="D817" t="n">
-        <v>12.77770042419434</v>
+        <v>12.77770137786865</v>
       </c>
       <c r="E817" t="n">
-        <v>13.04651609540078</v>
+        <v>13.04651706913838</v>
       </c>
       <c r="F817" t="n">
         <v>596040</v>
@@ -16952,16 +16952,16 @@
         <v>45523</v>
       </c>
       <c r="B827" t="n">
-        <v>12.33863639831543</v>
+        <v>12.33863544464111</v>
       </c>
       <c r="C827" t="n">
-        <v>12.44616267657907</v>
+        <v>12.44616171459386</v>
       </c>
       <c r="D827" t="n">
-        <v>12.03397950599891</v>
+        <v>12.03397857587205</v>
       </c>
       <c r="E827" t="n">
-        <v>12.28487325918361</v>
+        <v>12.28487230966474</v>
       </c>
       <c r="F827" t="n">
         <v>2509053</v>
@@ -16972,16 +16972,16 @@
         <v>45524</v>
       </c>
       <c r="B828" t="n">
-        <v>12.41032028198242</v>
+        <v>12.41031932830811</v>
       </c>
       <c r="C828" t="n">
-        <v>12.47304349472877</v>
+        <v>12.47304253623447</v>
       </c>
       <c r="D828" t="n">
-        <v>12.19526773068562</v>
+        <v>12.19526679353708</v>
       </c>
       <c r="E828" t="n">
-        <v>12.35655714415822</v>
+        <v>12.35655619461535</v>
       </c>
       <c r="F828" t="n">
         <v>514247</v>
@@ -17032,16 +17032,16 @@
         <v>45527</v>
       </c>
       <c r="B831" t="n">
-        <v>11.94437217712402</v>
+        <v>11.94437313079834</v>
       </c>
       <c r="C831" t="n">
-        <v>12.0877405337279</v>
+        <v>12.08774149884918</v>
       </c>
       <c r="D831" t="n">
-        <v>11.55907016679962</v>
+        <v>11.55907108971027</v>
       </c>
       <c r="E831" t="n">
-        <v>11.5769912113751</v>
+        <v>11.57699213571662</v>
       </c>
       <c r="F831" t="n">
         <v>1022098</v>
@@ -17092,16 +17092,16 @@
         <v>45532</v>
       </c>
       <c r="B834" t="n">
-        <v>11.93541240692139</v>
+        <v>11.9354133605957</v>
       </c>
       <c r="C834" t="n">
-        <v>12.2131881568688</v>
+        <v>12.21318913273821</v>
       </c>
       <c r="D834" t="n">
-        <v>11.89957031685739</v>
+        <v>11.89957126766782</v>
       </c>
       <c r="E834" t="n">
-        <v>12.2131881568688</v>
+        <v>12.21318913273821</v>
       </c>
       <c r="F834" t="n">
         <v>555773</v>
@@ -17152,16 +17152,16 @@
         <v>45537</v>
       </c>
       <c r="B837" t="n">
-        <v>11.6845178604126</v>
+        <v>11.68451881408691</v>
       </c>
       <c r="C837" t="n">
-        <v>11.6845178604126</v>
+        <v>11.68451881408691</v>
       </c>
       <c r="D837" t="n">
-        <v>11.42466315363044</v>
+        <v>11.42466408609577</v>
       </c>
       <c r="E837" t="n">
-        <v>11.56803061881927</v>
+        <v>11.56803156298606</v>
       </c>
       <c r="F837" t="n">
         <v>1157790</v>
@@ -17192,16 +17192,16 @@
         <v>45539</v>
       </c>
       <c r="B839" t="n">
-        <v>11.64867687225342</v>
+        <v>11.6486759185791</v>
       </c>
       <c r="C839" t="n">
-        <v>11.85476846305313</v>
+        <v>11.85476749250614</v>
       </c>
       <c r="D839" t="n">
-        <v>11.50530849740244</v>
+        <v>11.50530755546566</v>
       </c>
       <c r="E839" t="n">
-        <v>11.50530849740244</v>
+        <v>11.50530755546566</v>
       </c>
       <c r="F839" t="n">
         <v>552941</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37985992431641</v>
+        <v>11.37986087799072</v>
       </c>
       <c r="C844" t="n">
-        <v>11.52322828348119</v>
+        <v>11.5232292491703</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089895382008</v>
+        <v>11.37089990674344</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882089481273</v>
+        <v>11.38882184923801</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17472,16 +17472,16 @@
         <v>45559</v>
       </c>
       <c r="B853" t="n">
-        <v>10.69886016845703</v>
+        <v>10.69886112213135</v>
       </c>
       <c r="C853" t="n">
-        <v>10.95871576628153</v>
+        <v>10.95871674311883</v>
       </c>
       <c r="D853" t="n">
-        <v>10.68990009409949</v>
+        <v>10.68990104697512</v>
       </c>
       <c r="E853" t="n">
-        <v>10.91391270620266</v>
+        <v>10.91391367904632</v>
       </c>
       <c r="F853" t="n">
         <v>530081</v>
@@ -17492,16 +17492,16 @@
         <v>45560</v>
       </c>
       <c r="B854" t="n">
-        <v>10.39420413970947</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="C854" t="n">
-        <v>10.76158517156435</v>
+        <v>10.76158418418261</v>
       </c>
       <c r="D854" t="n">
-        <v>10.39420413970947</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="E854" t="n">
-        <v>10.69886195231235</v>
+        <v>10.6988609706855</v>
       </c>
       <c r="F854" t="n">
         <v>618376</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276924133301</v>
+        <v>10.49276828765869</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029552594893</v>
+        <v>10.60029456250169</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212497591966</v>
+        <v>10.41212402957499</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900699512222</v>
+        <v>10.43900604633429</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -26612,19 +26612,19 @@
         <v>46231</v>
       </c>
       <c r="B1310" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="C1310" t="n">
         <v>6.12</v>
       </c>
       <c r="D1310" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="E1310" t="n">
         <v>5.93</v>
       </c>
       <c r="F1310" t="n">
-        <v>800900</v>
+        <v>1636800</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -452,16 +452,16 @@
         <v>44316</v>
       </c>
       <c r="B2" t="n">
-        <v>13.41818809509277</v>
+        <v>13.41818714141846</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80970374344109</v>
+        <v>14.80970269086723</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42424798962781</v>
+        <v>12.42424710659606</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50707647044507</v>
+        <v>12.50707558152642</v>
       </c>
       <c r="F2" t="n">
         <v>8063577</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606625476003</v>
+        <v>13.76606525790047</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404556981654</v>
+        <v>13.00404462813815</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647056839647</v>
+        <v>13.42646959612849</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -532,16 +532,16 @@
         <v>44322</v>
       </c>
       <c r="B6" t="n">
-        <v>12.64788436889648</v>
+        <v>12.64788341522217</v>
       </c>
       <c r="C6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="D6" t="n">
-        <v>12.59818794458523</v>
+        <v>12.59818699465811</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="F6" t="n">
         <v>671078</v>
@@ -552,16 +552,16 @@
         <v>44323</v>
       </c>
       <c r="B7" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="C7" t="n">
-        <v>12.85495739835445</v>
+        <v>12.85495546357991</v>
       </c>
       <c r="D7" t="n">
-        <v>12.26687535150188</v>
+        <v>12.26687350523842</v>
       </c>
       <c r="E7" t="n">
-        <v>12.71414904438049</v>
+        <v>12.71414713079874</v>
       </c>
       <c r="F7" t="n">
         <v>847960</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C9" t="n">
-        <v>12.54849100757134</v>
+        <v>12.5484900443603</v>
       </c>
       <c r="D9" t="n">
-        <v>12.2171770654824</v>
+        <v>12.21717612770272</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566104888916</v>
+        <v>12.46566200256348</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75555946570089</v>
+        <v>12.75556044155362</v>
       </c>
       <c r="D10" t="n">
-        <v>12.3000040974216</v>
+        <v>12.30000503842248</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141875137399</v>
+        <v>12.34141969554326</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.4016227722168</v>
+        <v>13.40162181854248</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172407877397</v>
+        <v>13.93172308737706</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566247078936</v>
+        <v>12.46566158371901</v>
       </c>
       <c r="E11" t="n">
-        <v>12.672734099829</v>
+        <v>12.67273319802321</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83232975006104</v>
+        <v>13.8323278427124</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677323706887</v>
+        <v>14.19677127946689</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101582480272</v>
+        <v>13.50101396313917</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56727910915701</v>
+        <v>13.56727723835638</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98142051696777</v>
+        <v>13.98142147064209</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778424385328</v>
+        <v>14.57778523820564</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495522297252</v>
+        <v>13.67495615574281</v>
       </c>
       <c r="E13" t="n">
-        <v>13.98970394752027</v>
+        <v>13.9897049017596</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889316558838</v>
+        <v>13.8488941192627</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24646865971732</v>
+        <v>14.24646964076982</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323705643921</v>
+        <v>13.68323799870598</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222720198366</v>
+        <v>14.12222817448053</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="D16" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21939754486084</v>
+        <v>13.21939945220947</v>
       </c>
       <c r="C17" t="n">
-        <v>13.4844481368009</v>
+        <v>13.48445008239211</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687183280536</v>
+        <v>13.08687372103264</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687183280536</v>
+        <v>13.08687372103264</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -772,16 +772,16 @@
         <v>44340</v>
       </c>
       <c r="B18" t="n">
-        <v>13.42646980285645</v>
+        <v>13.42647075653076</v>
       </c>
       <c r="C18" t="n">
-        <v>14.02283349370625</v>
+        <v>14.02283448973993</v>
       </c>
       <c r="D18" t="n">
-        <v>13.32707529960082</v>
+        <v>13.3270762462152</v>
       </c>
       <c r="E18" t="n">
-        <v>13.40162117704254</v>
+        <v>13.40162212895187</v>
       </c>
       <c r="F18" t="n">
         <v>1040223</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.26909732818604</v>
+        <v>13.26909637451172</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182510380815</v>
+        <v>13.64182412334521</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253213007947</v>
+        <v>13.25253117759573</v>
       </c>
       <c r="E19" t="n">
-        <v>13.4016230738941</v>
+        <v>13.40162211069491</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131836345614</v>
+        <v>13.45131738938882</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313733320078</v>
+        <v>13.15313638072602</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707605947365</v>
+        <v>13.32707509440325</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253105163574</v>
+        <v>13.25253009796143</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707610139129</v>
+        <v>13.32707514235259</v>
       </c>
       <c r="D24" t="n">
-        <v>12.84667291282778</v>
+        <v>12.8466719883597</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061163964774</v>
+        <v>13.02061070266274</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95434856414795</v>
+        <v>12.95434951782227</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879286133005</v>
+        <v>13.31879384183405</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808528379311</v>
+        <v>12.88808623258925</v>
       </c>
       <c r="E25" t="n">
-        <v>13.25253041314621</v>
+        <v>13.2525313887721</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -992,16 +992,16 @@
         <v>44356</v>
       </c>
       <c r="B29" t="n">
-        <v>12.73071098327637</v>
+        <v>12.73071193695068</v>
       </c>
       <c r="C29" t="n">
-        <v>12.7389935807504</v>
+        <v>12.73899453504518</v>
       </c>
       <c r="D29" t="n">
-        <v>12.5319228187028</v>
+        <v>12.53192375748563</v>
       </c>
       <c r="E29" t="n">
-        <v>12.5319228187028</v>
+        <v>12.53192375748563</v>
       </c>
       <c r="F29" t="n">
         <v>453530</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95434856414795</v>
+        <v>12.95434951782227</v>
       </c>
       <c r="C30" t="n">
-        <v>13.00404498420033</v>
+        <v>13.0040459415332</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72242916333352</v>
+        <v>12.72243009993438</v>
       </c>
       <c r="E30" t="n">
-        <v>12.82182283560928</v>
+        <v>12.8218237795273</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667110443115</v>
+        <v>12.84667205810547</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576214769721</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555837422966</v>
+        <v>12.75555932114021</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576214769721</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1052,16 +1052,16 @@
         <v>44361</v>
       </c>
       <c r="B32" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="C32" t="n">
-        <v>13.00404751975243</v>
+        <v>13.00404556253863</v>
       </c>
       <c r="D32" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="E32" t="n">
-        <v>12.93778589081979</v>
+        <v>12.9377839435789</v>
       </c>
       <c r="F32" t="n">
         <v>396641</v>
@@ -1072,16 +1072,16 @@
         <v>44362</v>
       </c>
       <c r="B33" t="n">
-        <v>12.74727821350098</v>
+        <v>12.74727725982666</v>
       </c>
       <c r="C33" t="n">
-        <v>12.9377846431884</v>
+        <v>12.93778367526155</v>
       </c>
       <c r="D33" t="n">
-        <v>12.70586438734755</v>
+        <v>12.70586343677157</v>
       </c>
       <c r="E33" t="n">
-        <v>12.82182409918244</v>
+        <v>12.82182313993105</v>
       </c>
       <c r="F33" t="n">
         <v>320579</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414661407471</v>
+        <v>12.71414756774902</v>
       </c>
       <c r="C35" t="n">
-        <v>12.86323753914516</v>
+        <v>12.86323850400263</v>
       </c>
       <c r="D35" t="n">
-        <v>12.58990431521116</v>
+        <v>12.5899052595662</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384386648853</v>
+        <v>12.76384482389058</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="C39" t="n">
-        <v>12.4905092885157</v>
+        <v>12.49051027219619</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424684284646</v>
+        <v>12.42424782130851</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.33313655853271</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C40" t="n">
-        <v>12.5153587118295</v>
+        <v>12.51535967959436</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717602295992</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717602295992</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657218933105</v>
+        <v>12.31657028198242</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424846959927</v>
+        <v>12.42424654557586</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293453353099</v>
+        <v>12.09293266081497</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596587084889</v>
+        <v>12.41596394810812</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1272,16 +1272,16 @@
         <v>44376</v>
       </c>
       <c r="B43" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="C43" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="D43" t="n">
-        <v>12.05152193682892</v>
+        <v>12.05152012297789</v>
       </c>
       <c r="E43" t="n">
-        <v>12.05152193682892</v>
+        <v>12.05152012297789</v>
       </c>
       <c r="F43" t="n">
         <v>538653</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525779724121</v>
+        <v>12.80525684356689</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525779724121</v>
+        <v>12.80525684356689</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43253006532078</v>
+        <v>12.43252913940544</v>
       </c>
       <c r="E44" t="n">
-        <v>12.58990442190792</v>
+        <v>12.5899034842721</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1332,16 +1332,16 @@
         <v>44379</v>
       </c>
       <c r="B46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49051189422607</v>
       </c>
       <c r="C46" t="n">
-        <v>12.74727718624468</v>
+        <v>12.74727913280265</v>
       </c>
       <c r="D46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49051189422607</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51535861343547</v>
+        <v>12.51536052457858</v>
       </c>
       <c r="F46" t="n">
         <v>443206</v>
@@ -1352,16 +1352,16 @@
         <v>44382</v>
       </c>
       <c r="B47" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="C47" t="n">
-        <v>12.64788281412843</v>
+        <v>12.64788378432207</v>
       </c>
       <c r="D47" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="E47" t="n">
-        <v>12.5567717432249</v>
+        <v>12.55677270642959</v>
       </c>
       <c r="F47" t="n">
         <v>186679</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798454284668</v>
       </c>
       <c r="C48" t="n">
-        <v>12.49879274279404</v>
+        <v>12.4987937073347</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25858992047414</v>
+        <v>12.25859086647818</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394328540577</v>
+        <v>12.47394424802878</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54849097075757</v>
+        <v>12.54848903140645</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768346117107</v>
+        <v>12.40768154358154</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C50" t="n">
-        <v>12.6561672526666</v>
+        <v>12.65616529667426</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576320308654</v>
+        <v>12.17576132133995</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25859168836578</v>
+        <v>12.25858979381817</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1452,16 +1452,16 @@
         <v>44390</v>
       </c>
       <c r="B52" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293270111084</v>
       </c>
       <c r="C52" t="n">
-        <v>12.3082870318438</v>
+        <v>12.30828606118626</v>
       </c>
       <c r="D52" t="n">
-        <v>12.05151983187154</v>
+        <v>12.05151888146321</v>
       </c>
       <c r="E52" t="n">
-        <v>12.21717595569702</v>
+        <v>12.2171749922247</v>
       </c>
       <c r="F52" t="n">
         <v>433935</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121726989746</v>
+        <v>12.10121822357178</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030819970261</v>
+        <v>12.25030916512651</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293383945143</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293383945143</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495502471924</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172308291952</v>
+        <v>12.29172113487724</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010722775211</v>
+        <v>12.01010532434145</v>
       </c>
       <c r="E54" t="n">
-        <v>12.1012183131449</v>
+        <v>12.10121639529459</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16747882566446</v>
+        <v>12.16747978390493</v>
       </c>
       <c r="D55" t="n">
-        <v>11.89414561315063</v>
+        <v>11.89414654986496</v>
       </c>
       <c r="E55" t="n">
-        <v>12.0680851571606</v>
+        <v>12.06808610757341</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1532,16 +1532,16 @@
         <v>44396</v>
       </c>
       <c r="B56" t="n">
-        <v>11.63737773895264</v>
+        <v>11.63737869262695</v>
       </c>
       <c r="C56" t="n">
-        <v>12.02667065225621</v>
+        <v>12.02667163783278</v>
       </c>
       <c r="D56" t="n">
-        <v>11.53798406922757</v>
+        <v>11.53798501475665</v>
       </c>
       <c r="E56" t="n">
-        <v>12.01010545672085</v>
+        <v>12.01010644093992</v>
       </c>
       <c r="F56" t="n">
         <v>557721</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303508758545</v>
+        <v>10.98303413391113</v>
       </c>
       <c r="C58" t="n">
-        <v>11.6705098973207</v>
+        <v>11.67050888395185</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303508758545</v>
+        <v>10.98303413391113</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970239530374</v>
+        <v>11.52970139416144</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C59" t="n">
-        <v>11.34747866392074</v>
+        <v>11.3474776588947</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172130116907</v>
+        <v>10.65172035776503</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414544398869</v>
+        <v>11.07414446317129</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697574615479</v>
+        <v>11.15697288513184</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697574615479</v>
+        <v>11.15697288513184</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707645080476</v>
+        <v>10.86707366412172</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707645080476</v>
+        <v>10.86707366412172</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.2977819442749</v>
+        <v>11.29778099060059</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47172150119681</v>
+        <v>11.47172053283982</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05758076893598</v>
+        <v>11.05757983553765</v>
       </c>
       <c r="E62" t="n">
-        <v>11.18182307183133</v>
+        <v>11.1818221279454</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747982025146</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C63" t="n">
-        <v>11.5131367879722</v>
+        <v>11.51313582037561</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495407964066</v>
+        <v>11.21495313710418</v>
       </c>
       <c r="E63" t="n">
-        <v>11.36404584989197</v>
+        <v>11.3640448948254</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1692,16 +1692,16 @@
         <v>44406</v>
       </c>
       <c r="B64" t="n">
-        <v>11.30606460571289</v>
+        <v>11.30606555938721</v>
       </c>
       <c r="C64" t="n">
-        <v>11.45515552548068</v>
+        <v>11.45515649173092</v>
       </c>
       <c r="D64" t="n">
-        <v>11.01616536389469</v>
+        <v>11.01616629311581</v>
       </c>
       <c r="E64" t="n">
-        <v>11.3391958287534</v>
+        <v>11.33919678522236</v>
       </c>
       <c r="F64" t="n">
         <v>449738</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727827162325</v>
+        <v>11.92727731662251</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61253120072406</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61253120072406</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.8527307510376</v>
+        <v>11.85273265838623</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93555922274602</v>
+        <v>11.93556114342346</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030662714687</v>
+        <v>11.43030846651876</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727662522647</v>
+        <v>11.92727854457107</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515632629395</v>
+        <v>11.45515537261963</v>
       </c>
       <c r="C68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.85273087597138</v>
       </c>
       <c r="D68" t="n">
-        <v>11.44687372799754</v>
+        <v>11.44687277501277</v>
       </c>
       <c r="E68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.85273087597138</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20667171478271</v>
+        <v>11.2066707611084</v>
       </c>
       <c r="C69" t="n">
-        <v>11.6622279694364</v>
+        <v>11.66222697699479</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20667171478271</v>
+        <v>11.2066707611084</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768208275502</v>
+        <v>11.58768109665717</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1832,16 +1832,16 @@
         <v>44417</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C71" t="n">
-        <v>12.0349548369848</v>
+        <v>12.03495388133742</v>
       </c>
       <c r="D71" t="n">
-        <v>11.59596544701789</v>
+        <v>11.59596452622889</v>
       </c>
       <c r="E71" t="n">
-        <v>11.62909667462835</v>
+        <v>11.62909575120853</v>
       </c>
       <c r="F71" t="n">
         <v>438360</v>
@@ -1852,16 +1852,16 @@
         <v>44418</v>
       </c>
       <c r="B72" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2503080475979</v>
+        <v>12.2503090271009</v>
       </c>
       <c r="D72" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="E72" t="n">
-        <v>12.05151986626892</v>
+        <v>12.05152082987733</v>
       </c>
       <c r="F72" t="n">
         <v>351025</v>
@@ -1892,16 +1892,16 @@
         <v>44420</v>
       </c>
       <c r="B74" t="n">
-        <v>12.07636833190918</v>
+        <v>12.0763692855835</v>
       </c>
       <c r="C74" t="n">
-        <v>12.24202528616934</v>
+        <v>12.24202625292564</v>
       </c>
       <c r="D74" t="n">
-        <v>11.81131770439553</v>
+        <v>11.81131863713872</v>
       </c>
       <c r="E74" t="n">
-        <v>11.95212520012855</v>
+        <v>11.95212614399135</v>
       </c>
       <c r="F74" t="n">
         <v>242515</v>
@@ -1912,16 +1912,16 @@
         <v>44421</v>
       </c>
       <c r="B75" t="n">
-        <v>12.50707721710205</v>
+        <v>12.50707626342773</v>
       </c>
       <c r="C75" t="n">
-        <v>12.61475349963868</v>
+        <v>12.61475253775396</v>
       </c>
       <c r="D75" t="n">
-        <v>11.87758222321873</v>
+        <v>11.87758131754389</v>
       </c>
       <c r="E75" t="n">
-        <v>12.0018237036051</v>
+        <v>12.00182278845676</v>
       </c>
       <c r="F75" t="n">
         <v>464803</v>
@@ -1932,16 +1932,16 @@
         <v>44424</v>
       </c>
       <c r="B76" t="n">
-        <v>11.74505615234375</v>
+        <v>11.74505519866943</v>
       </c>
       <c r="C76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="D76" t="n">
-        <v>11.40545961983211</v>
+        <v>11.40545869373233</v>
       </c>
       <c r="E76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="F76" t="n">
         <v>788964</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859195709229</v>
+        <v>11.43859100341797</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727860666524</v>
+        <v>11.92727761224746</v>
       </c>
       <c r="D77" t="n">
-        <v>11.32263141169959</v>
+        <v>11.3226304676933</v>
       </c>
       <c r="E77" t="n">
-        <v>11.8444501211968</v>
+        <v>11.84444913368471</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495502471924</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C78" t="n">
-        <v>12.33313774220694</v>
+        <v>12.3331357876011</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313714150074</v>
+        <v>11.51313531685193</v>
       </c>
       <c r="E78" t="n">
-        <v>11.5793995977553</v>
+        <v>11.57939776260494</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -1992,16 +1992,16 @@
         <v>44427</v>
       </c>
       <c r="B79" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293270111084</v>
       </c>
       <c r="C79" t="n">
-        <v>12.19232816125147</v>
+        <v>12.19232719973869</v>
       </c>
       <c r="D79" t="n">
-        <v>11.54626719790453</v>
+        <v>11.54626628734149</v>
       </c>
       <c r="E79" t="n">
-        <v>11.59596445113769</v>
+        <v>11.59596353665541</v>
       </c>
       <c r="F79" t="n">
         <v>301405</v>
@@ -2012,16 +2012,16 @@
         <v>44428</v>
       </c>
       <c r="B80" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293270111084</v>
       </c>
       <c r="C80" t="n">
-        <v>12.12606487955025</v>
+        <v>12.12606392326314</v>
       </c>
       <c r="D80" t="n">
-        <v>11.87758110989754</v>
+        <v>11.87758017320638</v>
       </c>
       <c r="E80" t="n">
-        <v>12.05980326219108</v>
+        <v>12.05980231112949</v>
       </c>
       <c r="F80" t="n">
         <v>324055</v>
@@ -2032,16 +2032,16 @@
         <v>44431</v>
       </c>
       <c r="B81" t="n">
-        <v>11.99353981018066</v>
+        <v>11.9935417175293</v>
       </c>
       <c r="C81" t="n">
-        <v>12.39111533388724</v>
+        <v>12.39111730446284</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95212515568412</v>
+        <v>11.95212705644652</v>
       </c>
       <c r="E81" t="n">
-        <v>12.21717578221218</v>
+        <v>12.21717772512593</v>
       </c>
       <c r="F81" t="n">
         <v>344599</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C82" t="n">
-        <v>12.32485465783526</v>
+        <v>12.32485367100113</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990390400258</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E82" t="n">
-        <v>12.010106754765</v>
+        <v>12.0101057931323</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010696614738</v>
+        <v>12.01010503212249</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071245175947</v>
+        <v>11.91071053374038</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848796844482</v>
+        <v>11.72848987579346</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697337316509</v>
+        <v>11.97697532092373</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081170868654</v>
+        <v>11.62081359852429</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444765754676</v>
+        <v>11.84444958375337</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="D87" t="n">
-        <v>11.38889235890981</v>
+        <v>11.388893311891</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141761779785</v>
+        <v>11.52141857147217</v>
       </c>
       <c r="C88" t="n">
-        <v>11.6373773109646</v>
+        <v>11.63737827423737</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576150768174</v>
+        <v>11.35576244764404</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313502033478</v>
+        <v>11.51313597332352</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58767986297607</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C89" t="n">
-        <v>11.62909451392255</v>
+        <v>11.62909547100532</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010437334967</v>
+        <v>11.19010529430325</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55454864152145</v>
+        <v>11.55454959246905</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465129852295</v>
+        <v>11.26465034484863</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596437620398</v>
+        <v>11.59596339448043</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838801724993</v>
+        <v>11.19838706918552</v>
       </c>
       <c r="E90" t="n">
-        <v>11.35576237408096</v>
+        <v>11.3557614126931</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2232,16 +2232,16 @@
         <v>44445</v>
       </c>
       <c r="B91" t="n">
-        <v>11.61253070831299</v>
+        <v>11.6125316619873</v>
       </c>
       <c r="C91" t="n">
-        <v>11.72848958118911</v>
+        <v>11.7284905443865</v>
       </c>
       <c r="D91" t="n">
-        <v>11.26465159317151</v>
+        <v>11.2646525182764</v>
       </c>
       <c r="E91" t="n">
-        <v>11.34747924063002</v>
+        <v>11.3474801725371</v>
       </c>
       <c r="F91" t="n">
         <v>145382</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566135406494</v>
+        <v>11.64566040039062</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67050998170969</v>
+        <v>11.67050902600049</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010595448147</v>
+        <v>11.19010503811302</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313644952104</v>
+        <v>11.51313550669932</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909565647244</v>
+        <v>11.62909470007334</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38061022289286</v>
+        <v>11.38060928692969</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485335576816</v>
+        <v>11.50485240958699</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444903317125</v>
+        <v>11.84444805906109</v>
       </c>
       <c r="D97" t="n">
-        <v>11.587681001457</v>
+        <v>11.58768004846393</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192413433229</v>
+        <v>11.71192317112123</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313595390284</v>
+        <v>11.51313500704049</v>
       </c>
       <c r="E98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="C100" t="n">
-        <v>11.64566120833546</v>
+        <v>11.64565927206673</v>
       </c>
       <c r="D100" t="n">
-        <v>11.05758091156711</v>
+        <v>11.05757907307569</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26465169645404</v>
+        <v>11.26464982353394</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81960010528564</v>
+        <v>11.81960105895996</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05151950451265</v>
+        <v>12.05152047689957</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58768070605864</v>
+        <v>11.58768164102035</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535780774861</v>
+        <v>11.69535875139833</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677298006055</v>
+        <v>11.73677116615927</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76162160886144</v>
+        <v>11.76161979111983</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2572,16 +2572,16 @@
         <v>44469</v>
       </c>
       <c r="B108" t="n">
-        <v>11.63737773895264</v>
+        <v>11.63737869262695</v>
       </c>
       <c r="C108" t="n">
-        <v>11.94384217806649</v>
+        <v>11.94384315685534</v>
       </c>
       <c r="D108" t="n">
-        <v>11.51313544375356</v>
+        <v>11.51313638724631</v>
       </c>
       <c r="E108" t="n">
-        <v>11.94384217806649</v>
+        <v>11.94384315685534</v>
       </c>
       <c r="F108" t="n">
         <v>264322</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889282102754</v>
+        <v>11.38889188438319</v>
       </c>
       <c r="E109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545977752449</v>
+        <v>11.40545794086782</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596350798623</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010550156678</v>
+        <v>12.01010650652883</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444855256879</v>
+        <v>11.84444954366927</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2652,16 +2652,16 @@
         <v>44475</v>
       </c>
       <c r="B112" t="n">
-        <v>11.38061046600342</v>
+        <v>11.3806095123291</v>
       </c>
       <c r="C112" t="n">
-        <v>11.62909590489109</v>
+        <v>11.62909493039415</v>
       </c>
       <c r="D112" t="n">
-        <v>11.18182311349852</v>
+        <v>11.18182217648222</v>
       </c>
       <c r="E112" t="n">
-        <v>11.40545909310929</v>
+        <v>11.4054581373527</v>
       </c>
       <c r="F112" t="n">
         <v>433409</v>
@@ -2672,16 +2672,16 @@
         <v>44476</v>
       </c>
       <c r="B113" t="n">
-        <v>11.33091259002686</v>
+        <v>11.33091354370117</v>
       </c>
       <c r="C113" t="n">
-        <v>11.52970074919511</v>
+        <v>11.52970171960058</v>
       </c>
       <c r="D113" t="n">
-        <v>11.28121534219206</v>
+        <v>11.28121629168357</v>
       </c>
       <c r="E113" t="n">
-        <v>11.45515487744292</v>
+        <v>11.45515584157418</v>
       </c>
       <c r="F113" t="n">
         <v>136744</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.4054594039917</v>
+        <v>11.40545749664307</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939896630289</v>
+        <v>11.57939702986614</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38061077620852</v>
+        <v>11.38060887301535</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43859146248331</v>
+        <v>11.43858954959396</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677192873634</v>
+        <v>11.73677096348174</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667045593262</v>
+        <v>12.02667140960693</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495305356509</v>
+        <v>12.03495400789619</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768121771099</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768121771099</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2752,16 +2752,16 @@
         <v>44483</v>
       </c>
       <c r="B117" t="n">
-        <v>11.93556022644043</v>
+        <v>11.9355583190918</v>
       </c>
       <c r="C117" t="n">
-        <v>12.0266713033302</v>
+        <v>12.02666938142166</v>
       </c>
       <c r="D117" t="n">
-        <v>11.81960052273145</v>
+        <v>11.81959863391363</v>
       </c>
       <c r="E117" t="n">
-        <v>12.01838870511413</v>
+        <v>12.01838678452919</v>
       </c>
       <c r="F117" t="n">
         <v>96605</v>
@@ -2772,16 +2772,16 @@
         <v>44484</v>
       </c>
       <c r="B118" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293270111084</v>
       </c>
       <c r="C118" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293270111084</v>
       </c>
       <c r="D118" t="n">
-        <v>11.84444905296142</v>
+        <v>11.84444811888313</v>
       </c>
       <c r="E118" t="n">
-        <v>11.92727753095967</v>
+        <v>11.92727659034935</v>
       </c>
       <c r="F118" t="n">
         <v>256632</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22545936636416</v>
+        <v>12.22546032458287</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727751178659</v>
+        <v>11.92727844663413</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465103721058</v>
+        <v>12.08465198439289</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2812,16 +2812,16 @@
         <v>44488</v>
       </c>
       <c r="B120" t="n">
-        <v>12.07636833190918</v>
+        <v>12.0763692855835</v>
       </c>
       <c r="C120" t="n">
-        <v>12.29172170671058</v>
+        <v>12.29172267739142</v>
       </c>
       <c r="D120" t="n">
-        <v>11.93556000400514</v>
+        <v>11.93556094655978</v>
       </c>
       <c r="E120" t="n">
-        <v>12.10949955632701</v>
+        <v>12.10950051261771</v>
       </c>
       <c r="F120" t="n">
         <v>251785</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D122" t="n">
-        <v>11.41374237633313</v>
+        <v>11.41374053834268</v>
       </c>
       <c r="E122" t="n">
-        <v>11.6787930277491</v>
+        <v>11.67879114707672</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81959932971621</v>
+        <v>11.81960031587073</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212460723993</v>
+        <v>11.13212553603579</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76161948371394</v>
+        <v>11.76162046503097</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C124" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172236012447</v>
+        <v>11.47172147956523</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141961787203</v>
+        <v>11.52141873349808</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="D125" t="n">
-        <v>11.8444491374672</v>
+        <v>11.84444821601161</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030810003457</v>
+        <v>12.25030714700461</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980324204109</v>
+        <v>12.05980225021978</v>
       </c>
       <c r="D127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010598889097</v>
+        <v>12.01010500115686</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72848826202277</v>
+        <v>11.72848924057554</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030643463135</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596337525811</v>
+        <v>11.59596434275382</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -3012,16 +3012,16 @@
         <v>44503</v>
       </c>
       <c r="B130" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C130" t="n">
-        <v>12.01838963926511</v>
+        <v>12.01838868493311</v>
       </c>
       <c r="D130" t="n">
-        <v>11.43859190782543</v>
+        <v>11.43859099953283</v>
       </c>
       <c r="E130" t="n">
-        <v>11.50485436304635</v>
+        <v>11.50485344949212</v>
       </c>
       <c r="F130" t="n">
         <v>128737</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727787522379</v>
+        <v>11.92727589213198</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899473567608</v>
+        <v>11.09899289029898</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81960076750101</v>
+        <v>11.81959880231217</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020683994276</v>
+        <v>11.72020779632061</v>
       </c>
       <c r="D133" t="n">
-        <v>11.3806103272545</v>
+        <v>11.38061125592101</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859101124201</v>
+        <v>11.43859194463979</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374176025391</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374176025391</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929758022087</v>
+        <v>11.86929665495666</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05151973098904</v>
+        <v>12.05151879151981</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232749938965</v>
+        <v>12.19232845306396</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465040062008</v>
+        <v>12.08465134587198</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576211321089</v>
+        <v>12.17576306753439</v>
       </c>
       <c r="D138" t="n">
-        <v>11.6870755084975</v>
+        <v>11.68707642451825</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242888520996</v>
+        <v>11.90242981810988</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.33313655853271</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566145832273</v>
+        <v>12.46566242224469</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010607508077</v>
+        <v>12.01010700377637</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05151989822239</v>
+        <v>12.05152083012037</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798454284668</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49050931294096</v>
+        <v>12.49051027684238</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293297380614</v>
+        <v>12.09293390702631</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485319844393</v>
+        <v>12.32485414956155</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.9874792098999</v>
+        <v>12.98748111724854</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374165513303</v>
+        <v>13.05374357221301</v>
       </c>
       <c r="D142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="E142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89636829992451</v>
+        <v>12.89636928852036</v>
       </c>
       <c r="D144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010502169696</v>
+        <v>12.83010600521327</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3332,16 +3332,16 @@
         <v>44526</v>
       </c>
       <c r="B146" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="C146" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="D146" t="n">
-        <v>12.05152193682892</v>
+        <v>12.05152012297789</v>
       </c>
       <c r="E146" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="F146" t="n">
         <v>386739</v>
@@ -3352,16 +3352,16 @@
         <v>44529</v>
       </c>
       <c r="B147" t="n">
-        <v>12.6727352142334</v>
+        <v>12.67273330688477</v>
       </c>
       <c r="C147" t="n">
-        <v>12.98748232056206</v>
+        <v>12.98748036584146</v>
       </c>
       <c r="D147" t="n">
-        <v>12.3579864435624</v>
+        <v>12.357984583586</v>
       </c>
       <c r="E147" t="n">
-        <v>12.75556204235641</v>
+        <v>12.75556012254167</v>
       </c>
       <c r="F147" t="n">
         <v>340279</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455177307129</v>
+        <v>12.37455081939697</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818860682649</v>
+        <v>12.59818763591707</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90243030818464</v>
+        <v>11.90242939089549</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818860682649</v>
+        <v>12.59818763591707</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58767986297607</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C151" t="n">
-        <v>11.6705083326981</v>
+        <v>11.67050929318926</v>
       </c>
       <c r="D151" t="n">
-        <v>11.248084218938</v>
+        <v>11.24808514466335</v>
       </c>
       <c r="E151" t="n">
-        <v>11.33919528598094</v>
+        <v>11.3391962192048</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.7699031829834</v>
+        <v>11.76990222930908</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212533542978</v>
+        <v>11.95212436699063</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485338464032</v>
+        <v>11.50485245244207</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970201127774</v>
+        <v>11.52970107706609</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3472,16 +3472,16 @@
         <v>44537</v>
       </c>
       <c r="B153" t="n">
-        <v>12.01010704040527</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C153" t="n">
-        <v>12.09293469334588</v>
+        <v>12.09293373309455</v>
       </c>
       <c r="D153" t="n">
-        <v>11.78647021382081</v>
+        <v>11.78646927790459</v>
       </c>
       <c r="E153" t="n">
-        <v>11.89414732768312</v>
+        <v>11.8941463832167</v>
       </c>
       <c r="F153" t="n">
         <v>308042</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374176025391</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626761187925</v>
+        <v>12.36626664787403</v>
       </c>
       <c r="D154" t="n">
-        <v>11.89414620662944</v>
+        <v>11.89414527942817</v>
       </c>
       <c r="E154" t="n">
-        <v>12.0101059084221</v>
+        <v>12.01010497218126</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99354006605936</v>
+        <v>11.99353913300503</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22545947324071</v>
+        <v>12.22545852214389</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485198974609</v>
+        <v>12.32485485076904</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303296659815</v>
+        <v>12.62303589683919</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374092766524</v>
+        <v>12.23374376753817</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000253479481</v>
+        <v>12.30000539004934</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192392863263</v>
+        <v>12.53192295369397</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606496606526</v>
+        <v>12.12606402270097</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909628221446</v>
+        <v>12.44909531371949</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3592,16 +3592,16 @@
         <v>44545</v>
       </c>
       <c r="B159" t="n">
-        <v>12.54848957061768</v>
+        <v>12.54848861694336</v>
       </c>
       <c r="C159" t="n">
-        <v>12.54848957061768</v>
+        <v>12.54848861694336</v>
       </c>
       <c r="D159" t="n">
-        <v>12.05151954656443</v>
+        <v>12.05151863065941</v>
       </c>
       <c r="E159" t="n">
-        <v>12.32485360070486</v>
+        <v>12.32485266402669</v>
       </c>
       <c r="F159" t="n">
         <v>233455</v>
@@ -3612,16 +3612,16 @@
         <v>44546</v>
       </c>
       <c r="B160" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="C160" t="n">
-        <v>12.56505434089677</v>
+        <v>12.56505530473681</v>
       </c>
       <c r="D160" t="n">
-        <v>12.31657058554373</v>
+        <v>12.31657153032308</v>
       </c>
       <c r="E160" t="n">
-        <v>12.54848914555302</v>
+        <v>12.54849010812237</v>
       </c>
       <c r="F160" t="n">
         <v>252523</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606590270996</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606590270996</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25858939858541</v>
+        <v>12.25859030161671</v>
       </c>
       <c r="E161" t="n">
-        <v>12.42424633820085</v>
+        <v>12.4242472534353</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.7224292755127</v>
+        <v>12.72242832183838</v>
       </c>
       <c r="C163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.06202397044703</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737864826929</v>
+        <v>12.45737771446318</v>
       </c>
       <c r="E163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.06202397044703</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.8218240737915</v>
       </c>
       <c r="C164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.8218240737915</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43252926346614</v>
+        <v>12.43253111290434</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72242849935444</v>
+        <v>12.72243039191747</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828866415499</v>
+        <v>13.12828770746268</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384435172153</v>
+        <v>12.76384342158722</v>
       </c>
       <c r="E166" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="D167" t="n">
-        <v>12.92121704861566</v>
+        <v>12.9212161070132</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C168" t="n">
-        <v>13.37677327132853</v>
+        <v>13.3767722965285</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04546018437347</v>
+        <v>13.04545923371708</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3792,16 +3792,16 @@
         <v>44560</v>
       </c>
       <c r="B169" t="n">
-        <v>13.13657093048096</v>
+        <v>13.13657188415527</v>
       </c>
       <c r="C169" t="n">
-        <v>13.33535911049843</v>
+        <v>13.33536007860415</v>
       </c>
       <c r="D169" t="n">
-        <v>13.10343887366887</v>
+        <v>13.1034398249379</v>
       </c>
       <c r="E169" t="n">
-        <v>13.21111681005164</v>
+        <v>13.21111776913776</v>
       </c>
       <c r="F169" t="n">
         <v>310044</v>
@@ -3812,16 +3812,16 @@
         <v>44564</v>
       </c>
       <c r="B170" t="n">
-        <v>12.92949962615967</v>
+        <v>12.92950057983398</v>
       </c>
       <c r="C170" t="n">
-        <v>13.60041006166028</v>
+        <v>13.60041106482067</v>
       </c>
       <c r="D170" t="n">
-        <v>12.78869212614555</v>
+        <v>12.78869306943397</v>
       </c>
       <c r="E170" t="n">
-        <v>13.1697024667913</v>
+        <v>13.16970343818287</v>
       </c>
       <c r="F170" t="n">
         <v>289922</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98747925372556</v>
+        <v>12.98748125957582</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92949857373721</v>
+        <v>12.92950057063265</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3852,16 +3852,16 @@
         <v>44566</v>
       </c>
       <c r="B172" t="n">
-        <v>11.61253070831299</v>
+        <v>11.6125316619873</v>
       </c>
       <c r="C172" t="n">
-        <v>12.39939835219506</v>
+        <v>12.39939937049056</v>
       </c>
       <c r="D172" t="n">
-        <v>11.61253070831299</v>
+        <v>11.6125316619873</v>
       </c>
       <c r="E172" t="n">
-        <v>12.35798452846581</v>
+        <v>12.35798554336021</v>
       </c>
       <c r="F172" t="n">
         <v>223973</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586465533357</v>
+        <v>11.88586274131581</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202580731284</v>
+        <v>11.42202396798849</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55455071693529</v>
+        <v>11.55454885627004</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071205965744</v>
+        <v>11.91071108497109</v>
       </c>
       <c r="D178" t="n">
-        <v>11.5959649935801</v>
+        <v>11.59596404465037</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273220556355</v>
+        <v>11.85273123562185</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010609902517</v>
+        <v>12.01010707905902</v>
       </c>
       <c r="D182" t="n">
-        <v>11.56283248091458</v>
+        <v>11.56283342445056</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596453809916</v>
+        <v>11.59596548433874</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434840086876</v>
+        <v>12.13434939104088</v>
       </c>
       <c r="D184" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84444914178635</v>
+        <v>11.84445010830247</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111549377441</v>
+        <v>11.57111740112305</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101391022536</v>
+        <v>11.86101586536</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828701814372</v>
+        <v>11.48828891183915</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707519322319</v>
+        <v>11.68707711968628</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616542816162</v>
+        <v>11.83616638183594</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444802559172</v>
+        <v>11.84444897993339</v>
       </c>
       <c r="D186" t="n">
-        <v>11.46343772558484</v>
+        <v>11.4634386492274</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172032301494</v>
+        <v>11.47172124732486</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747982025146</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374227447133</v>
+        <v>11.41374131522813</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242917120093</v>
+        <v>11.08242823980222</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818236847018</v>
+        <v>11.1818227449497</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4192,16 +4192,16 @@
         <v>44589</v>
       </c>
       <c r="B189" t="n">
-        <v>11.53798389434814</v>
+        <v>11.53798484802246</v>
       </c>
       <c r="C189" t="n">
-        <v>11.57939771472981</v>
+        <v>11.57939867182719</v>
       </c>
       <c r="D189" t="n">
-        <v>11.14040755713192</v>
+        <v>11.14040847794448</v>
       </c>
       <c r="E189" t="n">
-        <v>11.36404435083742</v>
+        <v>11.36404529013473</v>
       </c>
       <c r="F189" t="n">
         <v>538653</v>
@@ -4212,16 +4212,16 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>11.67879295349121</v>
+        <v>11.67879199981689</v>
       </c>
       <c r="C190" t="n">
-        <v>11.78647006600311</v>
+        <v>11.78646910353603</v>
       </c>
       <c r="D190" t="n">
-        <v>11.45515696188252</v>
+        <v>11.45515602647001</v>
       </c>
       <c r="E190" t="n">
-        <v>11.55455064346737</v>
+        <v>11.55454969993852</v>
       </c>
       <c r="F190" t="n">
         <v>318367</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586379718157</v>
+        <v>11.88586476707715</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626728449331</v>
+        <v>11.54626822667756</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788311319406</v>
+        <v>11.82788407835838</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.48828887939453</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84445063335543</v>
+        <v>11.84444965011515</v>
       </c>
       <c r="D193" t="n">
-        <v>11.48828887939453</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67051105600181</v>
+        <v>11.67051008720073</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4292,16 +4292,16 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>11.30606460571289</v>
+        <v>11.30606555938721</v>
       </c>
       <c r="C194" t="n">
-        <v>11.6290950705716</v>
+        <v>11.62909605149376</v>
       </c>
       <c r="D194" t="n">
-        <v>11.19838750670299</v>
+        <v>11.19838845129467</v>
       </c>
       <c r="E194" t="n">
-        <v>11.48828674852119</v>
+        <v>11.48828771756607</v>
       </c>
       <c r="F194" t="n">
         <v>381155</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697476418123</v>
+        <v>11.97697377917189</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970198234322</v>
+        <v>11.52970103411845</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444808959961</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313689072104</v>
+        <v>11.51313503672479</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596350798623</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424613952637</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444812437002</v>
+        <v>11.84444909778491</v>
       </c>
       <c r="D200" t="n">
-        <v>11.5131350705226</v>
+        <v>11.51313601670912</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61252956919649</v>
+        <v>11.61253052355157</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.6870756149292</v>
+        <v>11.68707656860352</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84444914178635</v>
+        <v>11.84445010830247</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081316490208</v>
+        <v>11.62081411316933</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081316490208</v>
+        <v>11.62081411316933</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4492,16 +4492,16 @@
         <v>44610</v>
       </c>
       <c r="B204" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="C204" t="n">
-        <v>11.92727756500244</v>
+        <v>11.92727851867676</v>
       </c>
       <c r="D204" t="n">
-        <v>11.48000394896948</v>
+        <v>11.48000486688096</v>
       </c>
       <c r="E204" t="n">
-        <v>11.76162060853312</v>
+        <v>11.76162154896194</v>
       </c>
       <c r="F204" t="n">
         <v>336065</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.1426305770874</v>
+        <v>12.14263153076172</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576096650803</v>
+        <v>12.17576192278439</v>
       </c>
       <c r="D208" t="n">
-        <v>11.42202380291525</v>
+        <v>11.42202469999357</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596334039918</v>
+        <v>11.59596425113861</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4592,16 +4592,16 @@
         <v>44617</v>
       </c>
       <c r="B209" t="n">
-        <v>11.99353981018066</v>
+        <v>11.9935417175293</v>
       </c>
       <c r="C209" t="n">
-        <v>12.31657111943808</v>
+        <v>12.31657307815881</v>
       </c>
       <c r="D209" t="n">
-        <v>11.8196002585056</v>
+        <v>11.81960213819239</v>
       </c>
       <c r="E209" t="n">
-        <v>12.09293348306456</v>
+        <v>12.0929354062199</v>
       </c>
       <c r="F209" t="n">
         <v>373254</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="D210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="E210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.73899459838867</v>
+        <v>12.73899364471436</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202507956149</v>
+        <v>13.06202410170427</v>
       </c>
       <c r="D213" t="n">
-        <v>12.10949966448541</v>
+        <v>12.10949875793673</v>
       </c>
       <c r="E213" t="n">
-        <v>12.84667253500764</v>
+        <v>12.84667157327227</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.1591968536377</v>
+        <v>12.15919589996338</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697337862279</v>
       </c>
       <c r="D214" t="n">
-        <v>12.14263165745353</v>
+        <v>12.14263070507846</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697337862279</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081389317532</v>
+        <v>12.44081293822948</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293475328459</v>
+        <v>12.09293382504164</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576323880683</v>
+        <v>12.17576230420604</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C216" t="n">
-        <v>12.42424869537354</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919804100504</v>
+        <v>12.15919710767578</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111663542777</v>
+        <v>12.39111568429664</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071224212646</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45737956512522</v>
+        <v>12.45737856768</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990390400258</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081353562843</v>
+        <v>12.44081253950964</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242924788999</v>
+        <v>11.90242726892965</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242924788999</v>
+        <v>11.90242726892965</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141761779785</v>
+        <v>11.52141857147217</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303425325166</v>
+        <v>11.80303523023652</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515517375141</v>
+        <v>11.45515612194091</v>
       </c>
       <c r="E219" t="n">
-        <v>11.546266242358</v>
+        <v>11.54626719808914</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.794753074646</v>
+        <v>11.79475212097168</v>
       </c>
       <c r="C220" t="n">
-        <v>11.80303567310543</v>
+        <v>11.80303471876141</v>
       </c>
       <c r="D220" t="n">
-        <v>11.46343915021626</v>
+        <v>11.4634382233306</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596488642237</v>
+        <v>11.59596394882123</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.6622257232666</v>
+        <v>11.66222763061523</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444785716326</v>
+        <v>11.84444979431419</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404389831371</v>
+        <v>11.36404575689492</v>
       </c>
       <c r="E222" t="n">
-        <v>11.53798343489805</v>
+        <v>11.53798532192695</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4872,16 +4872,16 @@
         <v>44641</v>
       </c>
       <c r="B223" t="n">
-        <v>11.67879295349121</v>
+        <v>11.67879199981689</v>
       </c>
       <c r="C223" t="n">
-        <v>11.75333883880816</v>
+        <v>11.75333787904653</v>
       </c>
       <c r="D223" t="n">
-        <v>11.55455064346737</v>
+        <v>11.55454969993852</v>
       </c>
       <c r="E223" t="n">
-        <v>11.69535898317423</v>
+        <v>11.69535802814715</v>
       </c>
       <c r="F223" t="n">
         <v>273488</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10950024971806</v>
+        <v>12.10949925876433</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495436638118</v>
+        <v>12.03495338152774</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424613952637</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C227" t="n">
-        <v>11.7864682775339</v>
+        <v>11.78646924618382</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030659901801</v>
+        <v>11.43030753839741</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535720853013</v>
+        <v>11.69535816969225</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="C230" t="n">
-        <v>11.8941466495024</v>
+        <v>11.89414467191917</v>
       </c>
       <c r="D230" t="n">
-        <v>11.3557627752306</v>
+        <v>11.3557608871619</v>
       </c>
       <c r="E230" t="n">
-        <v>11.84444939483481</v>
+        <v>11.8444474255145</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374111175537</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23151896512815</v>
+        <v>11.2315199035769</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374111175537</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909531428845</v>
+        <v>11.62909628595667</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636759097204</v>
+        <v>11.25636853149702</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313561513094</v>
+        <v>11.51313657711016</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47171974182129</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283272794649</v>
+        <v>11.56283080544925</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919674628439</v>
+        <v>11.33919486097004</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41374179611474</v>
+        <v>11.41373989840614</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364219665527</v>
+        <v>10.88364124298096</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394493813262</v>
+        <v>10.833943988813</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192295074463</v>
+        <v>10.89192485809326</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303402115581</v>
+        <v>10.98303594445944</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313478249707</v>
+        <v>10.69313665503474</v>
       </c>
       <c r="E237" t="n">
-        <v>10.93333677105118</v>
+        <v>10.93333868565203</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798419952393</v>
+        <v>10.71798324584961</v>
       </c>
       <c r="C239" t="n">
-        <v>11.00788345960393</v>
+        <v>11.0078824801347</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798419952393</v>
+        <v>10.71798324584961</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333757893863</v>
+        <v>10.93333660610241</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000556945801</v>
+        <v>10.66000366210938</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566254625604</v>
+        <v>10.82566060926712</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000556945801</v>
+        <v>10.66000366210938</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566254625604</v>
+        <v>10.82566060926712</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C242" t="n">
-        <v>11.0327307901932</v>
+        <v>11.03272981304382</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172130116907</v>
+        <v>10.65172035776503</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000389905977</v>
+        <v>10.66000295492215</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C243" t="n">
-        <v>10.92505452110112</v>
+        <v>10.92505355348844</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000389905977</v>
+        <v>10.66000295492215</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081222405664</v>
+        <v>10.80081126744788</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5292,16 +5292,16 @@
         <v>44671</v>
       </c>
       <c r="B244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="C244" t="n">
-        <v>10.90848818540733</v>
+        <v>10.90848916207064</v>
       </c>
       <c r="D244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="E244" t="n">
-        <v>10.76767986438283</v>
+        <v>10.76768082843923</v>
       </c>
       <c r="F244" t="n">
         <v>446683</v>
@@ -5312,16 +5312,16 @@
         <v>44673</v>
       </c>
       <c r="B245" t="n">
-        <v>10.23757743835449</v>
+        <v>10.23758029937744</v>
       </c>
       <c r="C245" t="n">
-        <v>10.64343632649298</v>
+        <v>10.64343930093843</v>
       </c>
       <c r="D245" t="n">
-        <v>10.23757743835449</v>
+        <v>10.23758029937744</v>
       </c>
       <c r="E245" t="n">
-        <v>10.64343632649298</v>
+        <v>10.64343930093843</v>
       </c>
       <c r="F245" t="n">
         <v>624092</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434947967529</v>
+        <v>10.49434661865234</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919894368359</v>
+        <v>10.51919607588605</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707660312106</v>
+        <v>10.04707386403591</v>
       </c>
       <c r="E246" t="n">
-        <v>10.1547528981869</v>
+        <v>10.1547501297465</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394241333008</v>
+        <v>10.83394432067871</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525545120416</v>
+        <v>11.16525741688146</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576059602632</v>
+        <v>10.53576245087913</v>
       </c>
       <c r="E250" t="n">
-        <v>10.56889181659663</v>
+        <v>10.5688936772823</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434543609619</v>
+        <v>10.73434448242188</v>
       </c>
       <c r="C251" t="n">
-        <v>10.9254363391113</v>
+        <v>10.92543536845984</v>
       </c>
       <c r="D251" t="n">
-        <v>10.41032020669135</v>
+        <v>10.4103192818045</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389425777308</v>
+        <v>10.88389329081236</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.850661277771</v>
+        <v>10.85066032409668</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344493624595</v>
+        <v>11.03344396650661</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633637198398</v>
+        <v>10.62633543802578</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772778385571</v>
+        <v>10.71772684186504</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.49340438842773</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389415417323</v>
+        <v>10.8838951433366</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.49340438842773</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727798958128</v>
+        <v>10.86727897723452</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727905273438</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727905273438</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340261960133</v>
+        <v>10.49340446133011</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802718328567</v>
+        <v>10.61802904688768</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75927027618541</v>
+        <v>10.75926935728049</v>
       </c>
       <c r="E261" t="n">
-        <v>10.8755867747725</v>
+        <v>10.87558584593347</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085213080912</v>
+        <v>11.34085310445568</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95866949049548</v>
+        <v>10.95867043133051</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806847565188</v>
+        <v>11.15806943360591</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5692,16 +5692,16 @@
         <v>44700</v>
       </c>
       <c r="B264" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269386291504</v>
       </c>
       <c r="C264" t="n">
-        <v>11.40731747287078</v>
+        <v>11.40731843707905</v>
       </c>
       <c r="D264" t="n">
-        <v>11.05005994527452</v>
+        <v>11.05006087928544</v>
       </c>
       <c r="E264" t="n">
-        <v>11.1248351842914</v>
+        <v>11.12483612462273</v>
       </c>
       <c r="F264" t="n">
         <v>530225</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423513134702</v>
+        <v>11.32423610356696</v>
       </c>
       <c r="D265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100196715428</v>
+        <v>11.29100293652106</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5732,16 +5732,16 @@
         <v>44704</v>
       </c>
       <c r="B266" t="n">
-        <v>10.96697807312012</v>
+        <v>10.9669771194458</v>
       </c>
       <c r="C266" t="n">
-        <v>11.19961106781229</v>
+        <v>11.19961009390851</v>
       </c>
       <c r="D266" t="n">
-        <v>10.72603699568366</v>
+        <v>10.72603606296127</v>
       </c>
       <c r="E266" t="n">
-        <v>11.14976090188353</v>
+        <v>11.14975993231466</v>
       </c>
       <c r="F266" t="n">
         <v>653906</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772819255772</v>
+        <v>10.71772727720074</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05006152265314</v>
+        <v>11.05006057891294</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.19130325317383</v>
+        <v>11.1913013458252</v>
       </c>
       <c r="C269" t="n">
-        <v>11.19130325317383</v>
+        <v>11.1913013458252</v>
       </c>
       <c r="D269" t="n">
-        <v>10.86727883633742</v>
+        <v>10.8672769842127</v>
       </c>
       <c r="E269" t="n">
-        <v>11.01682850297487</v>
+        <v>11.0168266253622</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329391479492</v>
+        <v>11.08329200744629</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776865049238</v>
+        <v>11.25776671311801</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667691555787</v>
+        <v>11.06667501106889</v>
       </c>
       <c r="E270" t="n">
-        <v>11.1996104052599</v>
+        <v>11.1996084778941</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776863098145</v>
+        <v>11.25776767730713</v>
       </c>
       <c r="C271" t="n">
-        <v>11.2743856301897</v>
+        <v>11.27438467510771</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160187295824</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160187295824</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085178375244</v>
+        <v>11.34085083007812</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085178375244</v>
+        <v>11.34085083007812</v>
       </c>
       <c r="D272" t="n">
-        <v>11.1331438878556</v>
+        <v>11.13314295164785</v>
       </c>
       <c r="E272" t="n">
-        <v>11.2494595416049</v>
+        <v>11.24945859561594</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="C274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.349159222931</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="E274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.349159222931</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712856292725</v>
+        <v>10.91712760925293</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24946021456504</v>
+        <v>11.24945923185963</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051156297961</v>
+        <v>10.90051061075688</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622788413276</v>
+        <v>11.21622690433039</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344331983751</v>
+        <v>11.03344429480254</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="E276" t="n">
-        <v>11.00851824120922</v>
+        <v>11.00851921397176</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D277" t="n">
-        <v>10.6429532860445</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250209732709</v>
+        <v>10.79250303440952</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -6012,16 +6012,16 @@
         <v>44722</v>
       </c>
       <c r="B280" t="n">
-        <v>10.39370346069336</v>
+        <v>10.39370441436768</v>
       </c>
       <c r="C280" t="n">
-        <v>10.65126151249989</v>
+        <v>10.65126248980645</v>
       </c>
       <c r="D280" t="n">
-        <v>10.39370346069336</v>
+        <v>10.39370441436768</v>
       </c>
       <c r="E280" t="n">
-        <v>10.63464451394758</v>
+        <v>10.63464548972945</v>
       </c>
       <c r="F280" t="n">
         <v>218179</v>
@@ -6032,16 +6032,16 @@
         <v>44725</v>
       </c>
       <c r="B281" t="n">
-        <v>10.25246334075928</v>
+        <v>10.25246238708496</v>
       </c>
       <c r="C281" t="n">
-        <v>10.47678826183563</v>
+        <v>10.47678728729483</v>
       </c>
       <c r="D281" t="n">
-        <v>10.18599617190568</v>
+        <v>10.18599522441408</v>
       </c>
       <c r="E281" t="n">
-        <v>10.38539684373493</v>
+        <v>10.38539587769526</v>
       </c>
       <c r="F281" t="n">
         <v>299930</v>
@@ -6052,16 +6052,16 @@
         <v>44726</v>
       </c>
       <c r="B282" t="n">
-        <v>10.21092128753662</v>
+        <v>10.21092224121094</v>
       </c>
       <c r="C282" t="n">
-        <v>10.4684793554173</v>
+        <v>10.46848033314689</v>
       </c>
       <c r="D282" t="n">
-        <v>10.10291204230291</v>
+        <v>10.10291298588943</v>
       </c>
       <c r="E282" t="n">
-        <v>10.46017127298836</v>
+        <v>10.46017224994199</v>
       </c>
       <c r="F282" t="n">
         <v>156655</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768573760986</v>
+        <v>10.17768669128418</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216045042237</v>
+        <v>10.35216142044539</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798625945901</v>
+        <v>10.07798720379124</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599381877293</v>
+        <v>10.18599477322573</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911822319030762</v>
+        <v>9.911821365356445</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21923058757544</v>
+        <v>10.21922960432357</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787197728821756</v>
+        <v>9.787196787138297</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783916577339</v>
+        <v>10.12783819131483</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6172,16 +6172,16 @@
         <v>44735</v>
       </c>
       <c r="B288" t="n">
-        <v>9.637646675109863</v>
+        <v>9.637645721435547</v>
       </c>
       <c r="C288" t="n">
-        <v>9.945054899684594</v>
+        <v>9.945053915591304</v>
       </c>
       <c r="D288" t="n">
-        <v>9.629338592879359</v>
+        <v>9.629337640027153</v>
       </c>
       <c r="E288" t="n">
-        <v>9.93674681745409</v>
+        <v>9.93674583418291</v>
       </c>
       <c r="F288" t="n">
         <v>565728</v>
@@ -6192,16 +6192,16 @@
         <v>44736</v>
       </c>
       <c r="B289" t="n">
-        <v>9.388396263122559</v>
+        <v>9.388397216796875</v>
       </c>
       <c r="C289" t="n">
-        <v>9.795503923707427</v>
+        <v>9.795504918735785</v>
       </c>
       <c r="D289" t="n">
-        <v>9.388396263122559</v>
+        <v>9.388397216796875</v>
       </c>
       <c r="E289" t="n">
-        <v>9.695803611472812</v>
+        <v>9.6958045963736</v>
       </c>
       <c r="F289" t="n">
         <v>325741</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072681427001953</v>
+        <v>9.07268238067627</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255465221448427</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974876940689</v>
+        <v>8.939749709107998</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255465221448427</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.898205757141113</v>
+        <v>8.89820671081543</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039447317111145</v>
+        <v>9.039448285923172</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657264714402972</v>
+        <v>8.657265642254186</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823430519016487</v>
+        <v>8.823431464676691</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6312,16 +6312,16 @@
         <v>44746</v>
       </c>
       <c r="B295" t="n">
-        <v>9.222232818603516</v>
+        <v>9.222231864929199</v>
       </c>
       <c r="C295" t="n">
-        <v>9.297007237112771</v>
+        <v>9.297006275706005</v>
       </c>
       <c r="D295" t="n">
-        <v>8.873283306276161</v>
+        <v>8.873282388686833</v>
       </c>
       <c r="E295" t="n">
-        <v>8.972982809199021</v>
+        <v>8.972981881299734</v>
       </c>
       <c r="F295" t="n">
         <v>166874</v>
@@ -6372,16 +6372,16 @@
         <v>44749</v>
       </c>
       <c r="B298" t="n">
-        <v>9.056064605712891</v>
+        <v>9.056065559387207</v>
       </c>
       <c r="C298" t="n">
-        <v>9.355163898352176</v>
+        <v>9.355164883523981</v>
       </c>
       <c r="D298" t="n">
-        <v>9.056064605712891</v>
+        <v>9.056065559387207</v>
       </c>
       <c r="E298" t="n">
-        <v>9.230539332207711</v>
+        <v>9.230540304255577</v>
       </c>
       <c r="F298" t="n">
         <v>150966</v>
@@ -6392,16 +6392,16 @@
         <v>44750</v>
       </c>
       <c r="B299" t="n">
-        <v>8.914823532104492</v>
+        <v>8.914822578430176</v>
       </c>
       <c r="C299" t="n">
-        <v>9.130839514298627</v>
+        <v>9.13083853751573</v>
       </c>
       <c r="D299" t="n">
-        <v>8.898206532828883</v>
+        <v>8.89820558093219</v>
       </c>
       <c r="E299" t="n">
-        <v>8.981289859744001</v>
+        <v>8.981288898959365</v>
       </c>
       <c r="F299" t="n">
         <v>122521</v>
@@ -6412,16 +6412,16 @@
         <v>44753</v>
       </c>
       <c r="B300" t="n">
-        <v>8.840048789978027</v>
+        <v>8.840046882629395</v>
       </c>
       <c r="C300" t="n">
-        <v>8.964674204800824</v>
+        <v>8.964672270562733</v>
       </c>
       <c r="D300" t="n">
-        <v>8.798507541524769</v>
+        <v>8.798505643139169</v>
       </c>
       <c r="E300" t="n">
-        <v>8.889898955907146</v>
+        <v>8.889897037802729</v>
       </c>
       <c r="F300" t="n">
         <v>130423</v>
@@ -6432,16 +6432,16 @@
         <v>44754</v>
       </c>
       <c r="B301" t="n">
-        <v>8.690500259399414</v>
+        <v>8.690499305725098</v>
       </c>
       <c r="C301" t="n">
-        <v>8.864975028155989</v>
+        <v>8.864974055335237</v>
       </c>
       <c r="D301" t="n">
-        <v>8.574183746895031</v>
+        <v>8.574182805985005</v>
       </c>
       <c r="E301" t="n">
-        <v>8.864975028155989</v>
+        <v>8.864974055335237</v>
       </c>
       <c r="F301" t="n">
         <v>237774</v>
@@ -6472,16 +6472,16 @@
         <v>44756</v>
       </c>
       <c r="B303" t="n">
-        <v>8.499407768249512</v>
+        <v>8.499408721923828</v>
       </c>
       <c r="C303" t="n">
-        <v>8.565874096170459</v>
+        <v>8.565875057302616</v>
       </c>
       <c r="D303" t="n">
-        <v>8.349858113061646</v>
+        <v>8.349859049955773</v>
       </c>
       <c r="E303" t="n">
-        <v>8.358166195368899</v>
+        <v>8.358167133195233</v>
       </c>
       <c r="F303" t="n">
         <v>213754</v>
@@ -6492,16 +6492,16 @@
         <v>44757</v>
       </c>
       <c r="B304" t="n">
-        <v>8.499407768249512</v>
+        <v>8.499408721923828</v>
       </c>
       <c r="C304" t="n">
-        <v>8.58249109551643</v>
+        <v>8.582492058513093</v>
       </c>
       <c r="D304" t="n">
-        <v>8.424632523289844</v>
+        <v>8.424633468574021</v>
       </c>
       <c r="E304" t="n">
-        <v>8.540949014517237</v>
+        <v>8.54094997285268</v>
       </c>
       <c r="F304" t="n">
         <v>109458</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557565689086914</v>
+        <v>8.557563781738281</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673883021977259</v>
+        <v>8.673881088703297</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482791274402823</v>
+        <v>8.482789383720247</v>
       </c>
       <c r="E306" t="n">
-        <v>8.49940827473902</v>
+        <v>8.499406380352772</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864972114562988</v>
+        <v>8.864973068237305</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873281030390764</v>
+        <v>8.873281984958936</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615723003819328</v>
+        <v>8.615723930679971</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632339166012187</v>
+        <v>8.632340094660361</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6572,16 +6572,16 @@
         <v>44763</v>
       </c>
       <c r="B308" t="n">
-        <v>8.823431015014648</v>
+        <v>8.823431968688965</v>
       </c>
       <c r="C308" t="n">
-        <v>8.881590093312958</v>
+        <v>8.881591053273359</v>
       </c>
       <c r="D308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="E308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="F308" t="n">
         <v>93866</v>
@@ -6592,16 +6592,16 @@
         <v>44764</v>
       </c>
       <c r="B309" t="n">
-        <v>8.848356246948242</v>
+        <v>8.848357200622559</v>
       </c>
       <c r="C309" t="n">
-        <v>8.956363808991638</v>
+        <v>8.956364774306991</v>
       </c>
       <c r="D309" t="n">
-        <v>8.806814170620388</v>
+        <v>8.806815119817307</v>
       </c>
       <c r="E309" t="n">
-        <v>8.82343033336643</v>
+        <v>8.823431284354236</v>
       </c>
       <c r="F309" t="n">
         <v>116832</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039446830749512</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039446830749512</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815121963176683</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815121963176683</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="C311" t="n">
-        <v>9.122532260843132</v>
+        <v>9.122531267357015</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039448926379578</v>
+        <v>9.039447941941624</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6652,16 +6652,16 @@
         <v>44769</v>
       </c>
       <c r="B312" t="n">
-        <v>9.047757148742676</v>
+        <v>9.047758102416992</v>
       </c>
       <c r="C312" t="n">
-        <v>9.072681395907718</v>
+        <v>9.072682352209164</v>
       </c>
       <c r="D312" t="n">
-        <v>8.756965917835734</v>
+        <v>8.756966840859347</v>
       </c>
       <c r="E312" t="n">
-        <v>8.765274000224082</v>
+        <v>8.765274924123403</v>
       </c>
       <c r="F312" t="n">
         <v>161185</v>
@@ -6672,16 +6672,16 @@
         <v>44770</v>
       </c>
       <c r="B313" t="n">
-        <v>9.047757148742676</v>
+        <v>9.047758102416992</v>
       </c>
       <c r="C313" t="n">
-        <v>9.172380888762323</v>
+        <v>9.172381855572542</v>
       </c>
       <c r="D313" t="n">
-        <v>8.914823656871727</v>
+        <v>8.914824596534254</v>
       </c>
       <c r="E313" t="n">
-        <v>8.914823656871727</v>
+        <v>8.914824596534254</v>
       </c>
       <c r="F313" t="n">
         <v>129685</v>
@@ -6692,16 +6692,16 @@
         <v>44771</v>
       </c>
       <c r="B314" t="n">
-        <v>8.914823532104492</v>
+        <v>8.914822578430176</v>
       </c>
       <c r="C314" t="n">
-        <v>9.114222515023016</v>
+        <v>9.114221540017745</v>
       </c>
       <c r="D314" t="n">
-        <v>8.906514615100955</v>
+        <v>8.906513662315495</v>
       </c>
       <c r="E314" t="n">
-        <v>9.097606350478872</v>
+        <v>9.097605377251137</v>
       </c>
       <c r="F314" t="n">
         <v>141168</v>
@@ -6732,16 +6732,16 @@
         <v>44775</v>
       </c>
       <c r="B316" t="n">
-        <v>9.114221572875977</v>
+        <v>9.114222526550293</v>
       </c>
       <c r="C316" t="n">
-        <v>9.205613807347317</v>
+        <v>9.205614770584537</v>
       </c>
       <c r="D316" t="n">
-        <v>8.906513694424905</v>
+        <v>8.906514626365531</v>
       </c>
       <c r="E316" t="n">
-        <v>9.006214010309503</v>
+        <v>9.006214952682356</v>
       </c>
       <c r="F316" t="n">
         <v>198584</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.939749717712402</v>
+        <v>8.939748764038086</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172381893180782</v>
+        <v>9.172380914689739</v>
       </c>
       <c r="D317" t="n">
-        <v>8.939749717712402</v>
+        <v>8.939748764038086</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114223640630795</v>
+        <v>9.114222668343956</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6772,16 +6772,16 @@
         <v>44777</v>
       </c>
       <c r="B318" t="n">
-        <v>9.263771057128906</v>
+        <v>9.263772010803223</v>
       </c>
       <c r="C318" t="n">
-        <v>9.29700505168919</v>
+        <v>9.297006008784836</v>
       </c>
       <c r="D318" t="n">
-        <v>8.948055621388498</v>
+        <v>8.948056542560964</v>
       </c>
       <c r="E318" t="n">
-        <v>8.972980699943028</v>
+        <v>8.972981623681449</v>
       </c>
       <c r="F318" t="n">
         <v>175407</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.38008975982666</v>
+        <v>9.380088806152344</v>
       </c>
       <c r="C319" t="n">
-        <v>9.52963943191118</v>
+        <v>9.529638463032139</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197306920026865</v>
+        <v>9.197305984936092</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305315341150182</v>
+        <v>9.305314395078184</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6812,16 +6812,16 @@
         <v>44781</v>
       </c>
       <c r="B320" t="n">
-        <v>9.637646675109863</v>
+        <v>9.637645721435547</v>
       </c>
       <c r="C320" t="n">
-        <v>9.670880673494802</v>
+        <v>9.670879716531882</v>
       </c>
       <c r="D320" t="n">
-        <v>9.371780531150575</v>
+        <v>9.371779603784519</v>
       </c>
       <c r="E320" t="n">
-        <v>9.371780531150575</v>
+        <v>9.371779603784519</v>
       </c>
       <c r="F320" t="n">
         <v>274752</v>
@@ -6832,16 +6832,16 @@
         <v>44782</v>
       </c>
       <c r="B321" t="n">
-        <v>9.263771057128906</v>
+        <v>9.263772010803223</v>
       </c>
       <c r="C321" t="n">
-        <v>9.920127841895617</v>
+        <v>9.920128863139675</v>
       </c>
       <c r="D321" t="n">
-        <v>9.105913339258702</v>
+        <v>9.105914276682094</v>
       </c>
       <c r="E321" t="n">
-        <v>9.687495723093187</v>
+        <v>9.687496720388545</v>
       </c>
       <c r="F321" t="n">
         <v>480605</v>
@@ -6872,16 +6872,16 @@
         <v>44784</v>
       </c>
       <c r="B323" t="n">
-        <v>9.762271881103516</v>
+        <v>9.762272834777832</v>
       </c>
       <c r="C323" t="n">
-        <v>9.770579963162858</v>
+        <v>9.77058091764879</v>
       </c>
       <c r="D323" t="n">
-        <v>9.446555580802631</v>
+        <v>9.446556503634687</v>
       </c>
       <c r="E323" t="n">
-        <v>9.446555580802631</v>
+        <v>9.446556503634687</v>
       </c>
       <c r="F323" t="n">
         <v>1309919</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.770578384399414</v>
+        <v>9.770580291748047</v>
       </c>
       <c r="C324" t="n">
-        <v>9.861969776479176</v>
+        <v>9.86197170166864</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654261080706352</v>
+        <v>9.654262965348279</v>
       </c>
       <c r="E324" t="n">
-        <v>9.820427703432088</v>
+        <v>9.82042962051198</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953361511230469</v>
+        <v>9.953362464904785</v>
       </c>
       <c r="C325" t="n">
-        <v>10.11952813967694</v>
+        <v>10.1195291092724</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704111568560759</v>
+        <v>9.704112498353368</v>
       </c>
       <c r="E325" t="n">
-        <v>9.729036646300864</v>
+        <v>9.72903757848165</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="C327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="D327" t="n">
-        <v>10.30231297394502</v>
+        <v>10.302311126201</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847963535633</v>
+        <v>10.46847775780993</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494358062744</v>
+        <v>10.53494548797607</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75926845704052</v>
+        <v>10.75927040500311</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216078081824</v>
+        <v>10.3521626550741</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75926845704052</v>
+        <v>10.75927040500311</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340343475342</v>
+        <v>10.49340438842773</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494563841447</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092112410713</v>
+        <v>10.21092205210854</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494563841447</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7012,16 +7012,16 @@
         <v>44795</v>
       </c>
       <c r="B330" t="n">
-        <v>10.39370346069336</v>
+        <v>10.39370441436768</v>
       </c>
       <c r="C330" t="n">
-        <v>10.54325227400702</v>
+        <v>10.54325324140318</v>
       </c>
       <c r="D330" t="n">
-        <v>10.21922873218552</v>
+        <v>10.21922966985091</v>
       </c>
       <c r="E330" t="n">
-        <v>10.47678678399206</v>
+        <v>10.47678774528968</v>
       </c>
       <c r="F330" t="n">
         <v>111565</v>
@@ -7032,16 +7032,16 @@
         <v>44796</v>
       </c>
       <c r="B331" t="n">
-        <v>10.48509502410889</v>
+        <v>10.48509407043457</v>
       </c>
       <c r="C331" t="n">
-        <v>10.48509502410889</v>
+        <v>10.48509407043457</v>
       </c>
       <c r="D331" t="n">
-        <v>10.29400412889686</v>
+        <v>10.29400319260326</v>
       </c>
       <c r="E331" t="n">
-        <v>10.38539553548497</v>
+        <v>10.38539459087885</v>
       </c>
       <c r="F331" t="n">
         <v>120309</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250144958496</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389284806778</v>
+        <v>10.88389380981785</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633481521728</v>
+        <v>10.62633575420836</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573544424359</v>
+        <v>10.82573640085461</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096225738525</v>
+        <v>10.75096035003662</v>
       </c>
       <c r="C334" t="n">
-        <v>10.77588734076402</v>
+        <v>10.77588542899338</v>
       </c>
       <c r="D334" t="n">
-        <v>10.32723834414087</v>
+        <v>10.3272365119659</v>
       </c>
       <c r="E334" t="n">
-        <v>10.77588734076402</v>
+        <v>10.77588542899338</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7132,16 +7132,16 @@
         <v>44803</v>
       </c>
       <c r="B336" t="n">
-        <v>10.39370346069336</v>
+        <v>10.39370441436768</v>
       </c>
       <c r="C336" t="n">
-        <v>10.79250224390311</v>
+        <v>10.79250323416921</v>
       </c>
       <c r="D336" t="n">
-        <v>10.3189282193051</v>
+        <v>10.31892916611842</v>
       </c>
       <c r="E336" t="n">
-        <v>10.70111083869397</v>
+        <v>10.70111182057445</v>
       </c>
       <c r="F336" t="n">
         <v>123575</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539695739746</v>
+        <v>10.38539600372314</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648787877263</v>
+        <v>10.57648690755074</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907961931352</v>
+        <v>10.26907867632044</v>
       </c>
       <c r="E337" t="n">
-        <v>10.40201312374406</v>
+        <v>10.4020121685439</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7172,16 +7172,16 @@
         <v>44805</v>
       </c>
       <c r="B338" t="n">
-        <v>10.42693614959717</v>
+        <v>10.4269380569458</v>
       </c>
       <c r="C338" t="n">
-        <v>10.71772651584117</v>
+        <v>10.71772847638267</v>
       </c>
       <c r="D338" t="n">
-        <v>10.3189277507402</v>
+        <v>10.31892963833138</v>
       </c>
       <c r="E338" t="n">
-        <v>10.42693614959717</v>
+        <v>10.4269380569458</v>
       </c>
       <c r="F338" t="n">
         <v>1368072</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618656158447</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618656158447</v>
       </c>
       <c r="D340" t="n">
-        <v>10.25246083437947</v>
+        <v>10.25246266602793</v>
       </c>
       <c r="E340" t="n">
-        <v>10.3521603111894</v>
+        <v>10.35216216064962</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7252,16 +7252,16 @@
         <v>44812</v>
       </c>
       <c r="B342" t="n">
-        <v>10.75926876068115</v>
+        <v>10.75927066802979</v>
       </c>
       <c r="C342" t="n">
-        <v>10.90881840426656</v>
+        <v>10.9088203381266</v>
       </c>
       <c r="D342" t="n">
-        <v>10.57648595571358</v>
+        <v>10.57648783065941</v>
       </c>
       <c r="E342" t="n">
-        <v>10.57648595571358</v>
+        <v>10.57648783065941</v>
       </c>
       <c r="F342" t="n">
         <v>294768</v>
@@ -7272,16 +7272,16 @@
         <v>44813</v>
       </c>
       <c r="B343" t="n">
-        <v>11.0500602722168</v>
+        <v>11.05006122589111</v>
       </c>
       <c r="C343" t="n">
-        <v>11.0500602722168</v>
+        <v>11.05006122589111</v>
       </c>
       <c r="D343" t="n">
-        <v>10.68449465215745</v>
+        <v>10.68449557428166</v>
       </c>
       <c r="E343" t="n">
-        <v>10.76757797527951</v>
+        <v>10.76757890457422</v>
       </c>
       <c r="F343" t="n">
         <v>298877</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314437866211</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913026254664</v>
+        <v>11.1913016668102</v>
       </c>
       <c r="D344" t="n">
-        <v>10.9420526385631</v>
+        <v>10.94205170125786</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006104969434</v>
+        <v>11.05006010313701</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7312,16 +7312,16 @@
         <v>44817</v>
       </c>
       <c r="B345" t="n">
-        <v>11.14145183563232</v>
+        <v>11.14145088195801</v>
       </c>
       <c r="C345" t="n">
-        <v>11.19961007917147</v>
+        <v>11.19960912051899</v>
       </c>
       <c r="D345" t="n">
-        <v>10.70111096808326</v>
+        <v>10.70111005210078</v>
       </c>
       <c r="E345" t="n">
-        <v>10.95866902300398</v>
+        <v>10.95866808497532</v>
       </c>
       <c r="F345" t="n">
         <v>335223</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314437866211</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C346" t="n">
-        <v>11.14976054361677</v>
+        <v>11.1497595885191</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389439175881</v>
+        <v>10.88389345943545</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145246113944</v>
+        <v>11.14145150675345</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7352,16 +7352,16 @@
         <v>44819</v>
       </c>
       <c r="B347" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269386291504</v>
       </c>
       <c r="C347" t="n">
-        <v>11.29100099088769</v>
+        <v>11.29100194526425</v>
       </c>
       <c r="D347" t="n">
-        <v>10.73434449537589</v>
+        <v>10.73434540270083</v>
       </c>
       <c r="E347" t="n">
-        <v>11.05005994527452</v>
+        <v>11.05006087928544</v>
       </c>
       <c r="F347" t="n">
         <v>361349</v>
@@ -7392,16 +7392,16 @@
         <v>44823</v>
       </c>
       <c r="B349" t="n">
-        <v>11.28269290924072</v>
+        <v>11.28269386291504</v>
       </c>
       <c r="C349" t="n">
-        <v>11.38239239319849</v>
+        <v>11.38239335529995</v>
       </c>
       <c r="D349" t="n">
-        <v>11.17468450890459</v>
+        <v>11.17468545344945</v>
       </c>
       <c r="E349" t="n">
-        <v>11.3574673135262</v>
+        <v>11.35746827352085</v>
       </c>
       <c r="F349" t="n">
         <v>125366</v>
@@ -7432,16 +7432,16 @@
         <v>44825</v>
       </c>
       <c r="B351" t="n">
-        <v>10.75926876068115</v>
+        <v>10.75927066802979</v>
       </c>
       <c r="C351" t="n">
-        <v>11.16637644839254</v>
+        <v>11.16637842791116</v>
       </c>
       <c r="D351" t="n">
-        <v>10.67618543986006</v>
+        <v>10.6761873324801</v>
       </c>
       <c r="E351" t="n">
-        <v>11.12483520534769</v>
+        <v>11.12483717750209</v>
       </c>
       <c r="F351" t="n">
         <v>359874</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85066145408563</v>
+        <v>10.85065950799402</v>
       </c>
       <c r="D352" t="n">
-        <v>10.59310421404906</v>
+        <v>10.59310231415095</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449562740583</v>
+        <v>10.68449371111645</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="C353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="D353" t="n">
-        <v>10.3438542219321</v>
+        <v>10.34385236673755</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156296606198</v>
+        <v>10.55156107361439</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7492,16 +7492,16 @@
         <v>44830</v>
       </c>
       <c r="B354" t="n">
-        <v>10.42693614959717</v>
+        <v>10.4269380569458</v>
       </c>
       <c r="C354" t="n">
-        <v>10.60971895171559</v>
+        <v>10.60972089249979</v>
       </c>
       <c r="D354" t="n">
-        <v>10.34385283007114</v>
+        <v>10.34385472222175</v>
       </c>
       <c r="E354" t="n">
-        <v>10.60971895171559</v>
+        <v>10.60972089249979</v>
       </c>
       <c r="F354" t="n">
         <v>121152</v>
@@ -7512,16 +7512,16 @@
         <v>44831</v>
       </c>
       <c r="B355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="C355" t="n">
-        <v>10.58479547644101</v>
+        <v>10.58479449503473</v>
       </c>
       <c r="D355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="E355" t="n">
-        <v>10.42693772973123</v>
+        <v>10.42693676296128</v>
       </c>
       <c r="F355" t="n">
         <v>115674</v>
@@ -7532,16 +7532,16 @@
         <v>44832</v>
       </c>
       <c r="B356" t="n">
-        <v>10.21092128753662</v>
+        <v>10.21092224121094</v>
       </c>
       <c r="C356" t="n">
-        <v>10.4435534386675</v>
+        <v>10.44355441406907</v>
       </c>
       <c r="D356" t="n">
-        <v>10.19430512267873</v>
+        <v>10.19430607480114</v>
       </c>
       <c r="E356" t="n">
-        <v>10.40201219179128</v>
+        <v>10.40201316331301</v>
       </c>
       <c r="F356" t="n">
         <v>104928</v>
@@ -7552,16 +7552,16 @@
         <v>44833</v>
       </c>
       <c r="B357" t="n">
-        <v>10.12783718109131</v>
+        <v>10.12783622741699</v>
       </c>
       <c r="C357" t="n">
-        <v>10.20261242140248</v>
+        <v>10.20261146068705</v>
       </c>
       <c r="D357" t="n">
-        <v>9.978287535200392</v>
+        <v>9.978286595608219</v>
       </c>
       <c r="E357" t="n">
-        <v>10.17768650656734</v>
+        <v>10.17768554819902</v>
       </c>
       <c r="F357" t="n">
         <v>97132</v>
@@ -7572,16 +7572,16 @@
         <v>44834</v>
       </c>
       <c r="B358" t="n">
-        <v>10.18599510192871</v>
+        <v>10.18599414825439</v>
       </c>
       <c r="C358" t="n">
-        <v>10.26907842821965</v>
+        <v>10.26907746676657</v>
       </c>
       <c r="D358" t="n">
-        <v>9.920128958636587</v>
+        <v>9.920128029854263</v>
       </c>
       <c r="E358" t="n">
-        <v>10.17768701971906</v>
+        <v>10.17768606682259</v>
       </c>
       <c r="F358" t="n">
         <v>188154</v>
@@ -7592,16 +7592,16 @@
         <v>44837</v>
       </c>
       <c r="B359" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="C359" t="n">
-        <v>10.60972055954919</v>
+        <v>10.60971957583189</v>
       </c>
       <c r="D359" t="n">
-        <v>10.13614648468832</v>
+        <v>10.1361455448801</v>
       </c>
       <c r="E359" t="n">
-        <v>10.36047056319891</v>
+        <v>10.3604696025917</v>
       </c>
       <c r="F359" t="n">
         <v>398643</v>
@@ -7652,16 +7652,16 @@
         <v>44840</v>
       </c>
       <c r="B362" t="n">
-        <v>10.8838939666748</v>
+        <v>10.88389301300049</v>
       </c>
       <c r="C362" t="n">
-        <v>10.8838939666748</v>
+        <v>10.88389301300049</v>
       </c>
       <c r="D362" t="n">
-        <v>10.51832833517203</v>
+        <v>10.5183274135295</v>
       </c>
       <c r="E362" t="n">
-        <v>10.53494449947773</v>
+        <v>10.53494357637925</v>
       </c>
       <c r="F362" t="n">
         <v>536757</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389461942159</v>
+        <v>10.88389266736954</v>
       </c>
       <c r="D363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.6346435546875</v>
       </c>
       <c r="E363" t="n">
-        <v>10.82573720613229</v>
+        <v>10.8257352645109</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359298706055</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156188207657</v>
+        <v>10.55156279823885</v>
       </c>
       <c r="E364" t="n">
-        <v>10.6429532860445</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7732,16 +7732,16 @@
         <v>44847</v>
       </c>
       <c r="B366" t="n">
-        <v>10.96697807312012</v>
+        <v>10.9669771194458</v>
       </c>
       <c r="C366" t="n">
-        <v>11.15806898462782</v>
+        <v>11.15806801433649</v>
       </c>
       <c r="D366" t="n">
-        <v>10.85897049324983</v>
+        <v>10.85896954896772</v>
       </c>
       <c r="E366" t="n">
-        <v>10.85897049324983</v>
+        <v>10.85896954896772</v>
       </c>
       <c r="F366" t="n">
         <v>180569</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558555603027</v>
+        <v>10.87558650970459</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160236333128</v>
+        <v>11.09160333594799</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85066047559313</v>
+        <v>10.85066142708177</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344412055507</v>
+        <v>11.03344508807192</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7772,16 +7772,16 @@
         <v>44851</v>
       </c>
       <c r="B368" t="n">
-        <v>10.95866870880127</v>
+        <v>10.95866966247559</v>
       </c>
       <c r="C368" t="n">
-        <v>11.02513503244562</v>
+        <v>11.02513599190414</v>
       </c>
       <c r="D368" t="n">
-        <v>10.79250206495899</v>
+        <v>10.79250300417271</v>
       </c>
       <c r="E368" t="n">
-        <v>11.02513503244562</v>
+        <v>11.02513599190414</v>
       </c>
       <c r="F368" t="n">
         <v>132003</v>
@@ -7792,16 +7792,16 @@
         <v>44852</v>
       </c>
       <c r="B369" t="n">
-        <v>10.75926876068115</v>
+        <v>10.75927066802979</v>
       </c>
       <c r="C369" t="n">
-        <v>11.09160204396554</v>
+        <v>11.09160401022853</v>
       </c>
       <c r="D369" t="n">
-        <v>10.75096067901846</v>
+        <v>10.75096258489428</v>
       </c>
       <c r="E369" t="n">
-        <v>10.9586685637055</v>
+        <v>10.95867050640272</v>
       </c>
       <c r="F369" t="n">
         <v>172246</v>
@@ -7852,16 +7852,16 @@
         <v>44855</v>
       </c>
       <c r="B372" t="n">
-        <v>10.684494972229</v>
+        <v>10.68449401855469</v>
       </c>
       <c r="C372" t="n">
-        <v>10.88389395201756</v>
+        <v>10.88389298054533</v>
       </c>
       <c r="D372" t="n">
-        <v>10.684494972229</v>
+        <v>10.68449401855469</v>
       </c>
       <c r="E372" t="n">
-        <v>10.76757829783996</v>
+        <v>10.76757733674981</v>
       </c>
       <c r="F372" t="n">
         <v>132319</v>
@@ -7872,16 +7872,16 @@
         <v>44858</v>
       </c>
       <c r="B373" t="n">
-        <v>10.84235191345215</v>
+        <v>10.84235286712646</v>
       </c>
       <c r="C373" t="n">
-        <v>10.95866839385256</v>
+        <v>10.95866935775788</v>
       </c>
       <c r="D373" t="n">
-        <v>10.67618527438544</v>
+        <v>10.67618621344403</v>
       </c>
       <c r="E373" t="n">
-        <v>10.67618527438544</v>
+        <v>10.67618621344403</v>
       </c>
       <c r="F373" t="n">
         <v>186469</v>
@@ -7952,16 +7952,16 @@
         <v>44862</v>
       </c>
       <c r="B377" t="n">
-        <v>10.95866870880127</v>
+        <v>10.95866966247559</v>
       </c>
       <c r="C377" t="n">
-        <v>10.99190187062344</v>
+        <v>10.99190282718986</v>
       </c>
       <c r="D377" t="n">
-        <v>10.68449449771977</v>
+        <v>10.68449542753418</v>
       </c>
       <c r="E377" t="n">
-        <v>10.89220155042551</v>
+        <v>10.89220249831554</v>
       </c>
       <c r="F377" t="n">
         <v>271802</v>
@@ -7972,16 +7972,16 @@
         <v>44865</v>
       </c>
       <c r="B378" t="n">
-        <v>10.59310340881348</v>
+        <v>10.59310436248779</v>
       </c>
       <c r="C378" t="n">
-        <v>10.90051079085215</v>
+        <v>10.90051177220169</v>
       </c>
       <c r="D378" t="n">
-        <v>10.48509500363324</v>
+        <v>10.4850959475838</v>
       </c>
       <c r="E378" t="n">
-        <v>10.6180276548722</v>
+        <v>10.61802861079039</v>
       </c>
       <c r="F378" t="n">
         <v>218495</v>
@@ -8052,16 +8052,16 @@
         <v>44872</v>
       </c>
       <c r="B382" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727905273438</v>
       </c>
       <c r="C382" t="n">
-        <v>11.24115083643875</v>
+        <v>11.24115280940709</v>
       </c>
       <c r="D382" t="n">
-        <v>10.72603558366884</v>
+        <v>10.72603746622774</v>
       </c>
       <c r="E382" t="n">
-        <v>11.11652627275442</v>
+        <v>11.11652822384952</v>
       </c>
       <c r="F382" t="n">
         <v>110617</v>
@@ -8132,16 +8132,16 @@
         <v>44876</v>
       </c>
       <c r="B386" t="n">
-        <v>10.21922969818115</v>
+        <v>10.21922874450684</v>
       </c>
       <c r="C386" t="n">
-        <v>10.6512625193344</v>
+        <v>10.65126152534211</v>
       </c>
       <c r="D386" t="n">
-        <v>10.21922969818115</v>
+        <v>10.21922874450684</v>
       </c>
       <c r="E386" t="n">
-        <v>10.6512625193344</v>
+        <v>10.65126152534211</v>
       </c>
       <c r="F386" t="n">
         <v>372832</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.707115173339844</v>
+        <v>8.707114219665527</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629515547199</v>
+        <v>10.08629405073862</v>
       </c>
       <c r="D388" t="n">
-        <v>8.707115173339844</v>
+        <v>8.707114219665527</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629515547199</v>
+        <v>10.08629405073862</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765273094177246</v>
+        <v>8.765274047851562</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873281492987086</v>
+        <v>8.873282458412872</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225232769590827</v>
+        <v>8.225233664507979</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707114854007546</v>
+        <v>8.707115801354162</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8212,16 +8212,16 @@
         <v>44883</v>
       </c>
       <c r="B390" t="n">
-        <v>8.557565689086914</v>
+        <v>8.557563781738281</v>
       </c>
       <c r="C390" t="n">
-        <v>8.914824101097249</v>
+        <v>8.914822114121259</v>
       </c>
       <c r="D390" t="n">
-        <v>8.391399859382533</v>
+        <v>8.391397989069686</v>
       </c>
       <c r="E390" t="n">
-        <v>8.848357769215497</v>
+        <v>8.84835579705382</v>
       </c>
       <c r="F390" t="n">
         <v>571733</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562847137451172</v>
+        <v>8.562845230102539</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039490016199446</v>
+        <v>9.039488002680034</v>
       </c>
       <c r="D392" t="n">
-        <v>8.529398617556286</v>
+        <v>8.52939671765821</v>
       </c>
       <c r="E392" t="n">
-        <v>8.947506376453346</v>
+        <v>8.947504383423015</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081300735473633</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081300735473633</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621382522590984</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621382522590984</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.822072982788086</v>
+        <v>8.822073936462402</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098023863426608</v>
+        <v>9.098024846931471</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746813193446378</v>
+        <v>8.746814138985041</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081299185748271</v>
+        <v>9.081300167445182</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8372,16 +8372,16 @@
         <v>44895</v>
       </c>
       <c r="B398" t="n">
-        <v>8.671553611755371</v>
+        <v>8.671554565429688</v>
       </c>
       <c r="C398" t="n">
-        <v>8.905694041331014</v>
+        <v>8.905695020755468</v>
       </c>
       <c r="D398" t="n">
-        <v>8.60465574606199</v>
+        <v>8.604656692379058</v>
       </c>
       <c r="E398" t="n">
-        <v>8.705002124531823</v>
+        <v>8.705003081884717</v>
       </c>
       <c r="F398" t="n">
         <v>181728</v>
@@ -8392,16 +8392,16 @@
         <v>44896</v>
       </c>
       <c r="B399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955867767333984</v>
       </c>
       <c r="C399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955867767333984</v>
       </c>
       <c r="D399" t="n">
-        <v>8.596294234144615</v>
+        <v>8.596295149529491</v>
       </c>
       <c r="E399" t="n">
-        <v>8.721726373019072</v>
+        <v>8.721727301760714</v>
       </c>
       <c r="F399" t="n">
         <v>469965</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947503089904785</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198370118006814</v>
+        <v>9.198368157181012</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822072856946983</v>
+        <v>8.822070976336846</v>
       </c>
       <c r="E400" t="n">
-        <v>9.139834167037881</v>
+        <v>9.139832218690247</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8432,16 +8432,16 @@
         <v>44900</v>
       </c>
       <c r="B401" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C401" t="n">
-        <v>9.08966353913592</v>
+        <v>9.089662548080438</v>
       </c>
       <c r="D401" t="n">
-        <v>8.66319384514464</v>
+        <v>8.663192900587594</v>
       </c>
       <c r="E401" t="n">
-        <v>8.947506694425265</v>
+        <v>8.947505718869293</v>
       </c>
       <c r="F401" t="n">
         <v>131055</v>
@@ -8452,16 +8452,16 @@
         <v>44901</v>
       </c>
       <c r="B402" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C402" t="n">
-        <v>8.863884971646016</v>
+        <v>8.863884005207408</v>
       </c>
       <c r="D402" t="n">
-        <v>8.688279605851797</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="E402" t="n">
-        <v>8.771901328631047</v>
+        <v>8.771900372221511</v>
       </c>
       <c r="F402" t="n">
         <v>122416</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905694705334085</v>
+        <v>8.905695681933357</v>
       </c>
       <c r="D403" t="n">
-        <v>8.67991617708353</v>
+        <v>8.679917128923909</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437414169311523</v>
+        <v>8.437413215637207</v>
       </c>
       <c r="C404" t="n">
-        <v>8.738452529775763</v>
+        <v>8.738451542075317</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412328409401773</v>
+        <v>8.412327458562881</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705004009755438</v>
+        <v>8.705003025835651</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935684680938721</v>
       </c>
       <c r="C405" t="n">
-        <v>8.479224033940735</v>
+        <v>8.47922454343796</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935684680938721</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462500196792739</v>
+        <v>8.462500705285068</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952409744262695</v>
+        <v>7.952410221099854</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027668699875649</v>
+        <v>8.027669181225434</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818615671999396</v>
+        <v>7.818616140814081</v>
       </c>
       <c r="E406" t="n">
-        <v>7.935685065159479</v>
+        <v>7.935685540993802</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8632,16 +8632,16 @@
         <v>44914</v>
       </c>
       <c r="B411" t="n">
-        <v>8.16146183013916</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="C411" t="n">
-        <v>8.16146183013916</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="D411" t="n">
-        <v>7.952408826391903</v>
+        <v>7.952409755638184</v>
       </c>
       <c r="E411" t="n">
-        <v>8.128014156074491</v>
+        <v>8.128015105840415</v>
       </c>
       <c r="F411" t="n">
         <v>108510</v>
@@ -8652,16 +8652,16 @@
         <v>44915</v>
       </c>
       <c r="B412" t="n">
-        <v>8.429051399230957</v>
+        <v>8.429050445556641</v>
       </c>
       <c r="C412" t="n">
-        <v>8.579570984352777</v>
+        <v>8.579570013648471</v>
       </c>
       <c r="D412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="E412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="F412" t="n">
         <v>166979</v>
@@ -8712,16 +8712,16 @@
         <v>44918</v>
       </c>
       <c r="B415" t="n">
-        <v>8.688278198242188</v>
+        <v>8.688277244567871</v>
       </c>
       <c r="C415" t="n">
-        <v>8.763537988592692</v>
+        <v>8.763537026657437</v>
       </c>
       <c r="D415" t="n">
-        <v>8.504310942017245</v>
+        <v>8.50431000853621</v>
       </c>
       <c r="E415" t="n">
-        <v>8.529397538800746</v>
+        <v>8.529396602566065</v>
       </c>
       <c r="F415" t="n">
         <v>92391</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613018306402285</v>
+        <v>8.613019250906639</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730089370059329</v>
+        <v>8.730090327401705</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.73845100402832</v>
+        <v>8.738451957702637</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788623355228307</v>
+        <v>8.788624314378202</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284567447709</v>
+        <v>8.56284660898665</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713364408358071</v>
+        <v>8.713365359294553</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8772,16 +8772,16 @@
         <v>44923</v>
       </c>
       <c r="B418" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C418" t="n">
-        <v>8.930782853953826</v>
+        <v>8.930781880221272</v>
       </c>
       <c r="D418" t="n">
-        <v>8.679917685616079</v>
+        <v>8.679916739235615</v>
       </c>
       <c r="E418" t="n">
-        <v>8.688279605851797</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="F418" t="n">
         <v>114515</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914056624116538</v>
+        <v>8.914057601632781</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830434915870388</v>
+        <v>8.830435884216666</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529397964477539</v>
+        <v>8.529397010803223</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771900345253039</v>
+        <v>8.771899364464465</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529397964477539</v>
+        <v>8.529397010803223</v>
       </c>
       <c r="E420" t="n">
-        <v>8.705003310585438</v>
+        <v>8.705002337276639</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8852,16 +8852,16 @@
         <v>44930</v>
       </c>
       <c r="B422" t="n">
-        <v>8.328705787658691</v>
+        <v>8.328704833984375</v>
       </c>
       <c r="C422" t="n">
-        <v>8.345429625788091</v>
+        <v>8.345428670198819</v>
       </c>
       <c r="D422" t="n">
-        <v>8.061116816323212</v>
+        <v>8.061115893289037</v>
       </c>
       <c r="E422" t="n">
-        <v>8.345429625788091</v>
+        <v>8.345428670198819</v>
       </c>
       <c r="F422" t="n">
         <v>248204</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947503089904785</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947503089904785</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387240485058745</v>
+        <v>8.387238697142262</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395603243848893</v>
+        <v>8.395601454149713</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8912,16 +8912,16 @@
         <v>44935</v>
       </c>
       <c r="B425" t="n">
-        <v>8.813712120056152</v>
+        <v>8.813711166381836</v>
       </c>
       <c r="C425" t="n">
-        <v>8.947506196951567</v>
+        <v>8.947505228800265</v>
       </c>
       <c r="D425" t="n">
-        <v>8.696641042561707</v>
+        <v>8.696640101554889</v>
       </c>
       <c r="E425" t="n">
-        <v>8.905695757956909</v>
+        <v>8.905694794329643</v>
       </c>
       <c r="F425" t="n">
         <v>148121</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139834941690628</v>
+        <v>9.139833970240518</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006040871394767</v>
+        <v>9.006039914165292</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847160202883281</v>
+        <v>8.847159262540833</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C431" t="n">
-        <v>9.064575987184355</v>
+        <v>9.06457502373333</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905695318672869</v>
+        <v>8.905694372108872</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964229594321862</v>
+        <v>8.964228641536403</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566306114196777</v>
+        <v>9.566305160522461</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616478474070194</v>
+        <v>9.616477515394145</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407424594199101</v>
+        <v>9.407423656363838</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424149274250677</v>
+        <v>9.424148334748114</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C438" t="n">
-        <v>9.959326039139317</v>
+        <v>9.95932505997885</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741910266268745</v>
+        <v>9.741909308483715</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="D439" t="n">
-        <v>9.649926637741174</v>
+        <v>9.6499256889996</v>
       </c>
       <c r="E439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.666651725769043</v>
+        <v>9.666650772094727</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725186846051544</v>
+        <v>9.725185886602381</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457597844780201</v>
+        <v>9.457596911730329</v>
       </c>
       <c r="E443" t="n">
-        <v>9.700100245910377</v>
+        <v>9.70009928893616</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9312,16 +9312,16 @@
         <v>44963</v>
       </c>
       <c r="B445" t="n">
-        <v>9.608115196228027</v>
+        <v>9.608116149902344</v>
       </c>
       <c r="C445" t="n">
-        <v>9.842255643015774</v>
+        <v>9.842256619930208</v>
       </c>
       <c r="D445" t="n">
-        <v>9.599753277454333</v>
+        <v>9.599754230298668</v>
       </c>
       <c r="E445" t="n">
-        <v>9.666650307924964</v>
+        <v>9.666651267409309</v>
       </c>
       <c r="F445" t="n">
         <v>107772</v>
@@ -9332,16 +9332,16 @@
         <v>44964</v>
       </c>
       <c r="B446" t="n">
-        <v>9.733548164367676</v>
+        <v>9.733547210693359</v>
       </c>
       <c r="C446" t="n">
-        <v>9.733548164367676</v>
+        <v>9.733547210693359</v>
       </c>
       <c r="D446" t="n">
-        <v>9.457596443832067</v>
+        <v>9.457595517194969</v>
       </c>
       <c r="E446" t="n">
-        <v>9.64992645633084</v>
+        <v>9.649925510849618</v>
       </c>
       <c r="F446" t="n">
         <v>121889</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312057495117</v>
+        <v>10.09312152862549</v>
       </c>
       <c r="C447" t="n">
-        <v>10.16001676400513</v>
+        <v>10.1600177240003</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649926286291848</v>
+        <v>9.649927198089818</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741909911469383</v>
+        <v>9.741910831958663</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9392,16 +9392,16 @@
         <v>44967</v>
       </c>
       <c r="B449" t="n">
-        <v>9.373976707458496</v>
+        <v>9.373974800109863</v>
       </c>
       <c r="C449" t="n">
-        <v>10.14329432989549</v>
+        <v>10.1432922660117</v>
       </c>
       <c r="D449" t="n">
-        <v>9.298716909098653</v>
+        <v>9.298715017063337</v>
       </c>
       <c r="E449" t="n">
-        <v>9.950965134321402</v>
+        <v>9.95096310957136</v>
       </c>
       <c r="F449" t="n">
         <v>543394</v>
@@ -9432,16 +9432,16 @@
         <v>44971</v>
       </c>
       <c r="B451" t="n">
-        <v>9.909152984619141</v>
+        <v>9.909153938293457</v>
       </c>
       <c r="C451" t="n">
-        <v>9.909152984619141</v>
+        <v>9.909153938293457</v>
       </c>
       <c r="D451" t="n">
-        <v>9.532854897924329</v>
+        <v>9.532855815383055</v>
       </c>
       <c r="E451" t="n">
-        <v>9.566304251514461</v>
+        <v>9.566305172192413</v>
       </c>
       <c r="F451" t="n">
         <v>266324</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088144470998</v>
+        <v>10.41088241395452</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458513532366</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820590414945</v>
+        <v>10.11820684614614</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C455" t="n">
-        <v>10.61993612237364</v>
+        <v>10.619937111081</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992774609804133</v>
+        <v>9.992775540123269</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889782341103</v>
+        <v>10.31889878409197</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363899230957</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053590514944</v>
+        <v>10.31053686505189</v>
       </c>
       <c r="D460" t="n">
-        <v>9.850616958514175</v>
+        <v>9.85061787559855</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458513532366</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9672,16 +9672,16 @@
         <v>44991</v>
       </c>
       <c r="B463" t="n">
-        <v>10.63666152954102</v>
+        <v>10.6366605758667</v>
       </c>
       <c r="C463" t="n">
-        <v>10.63666152954102</v>
+        <v>10.6366605758667</v>
       </c>
       <c r="D463" t="n">
-        <v>10.20182911362224</v>
+        <v>10.20182819893464</v>
       </c>
       <c r="E463" t="n">
-        <v>10.32726126662976</v>
+        <v>10.32726034069602</v>
       </c>
       <c r="F463" t="n">
         <v>82488</v>
@@ -9692,16 +9692,16 @@
         <v>44992</v>
       </c>
       <c r="B464" t="n">
-        <v>10.66174697875977</v>
+        <v>10.66174793243408</v>
       </c>
       <c r="C464" t="n">
-        <v>10.73700592639459</v>
+        <v>10.73700688680069</v>
       </c>
       <c r="D464" t="n">
-        <v>10.37743334512914</v>
+        <v>10.3774342733721</v>
       </c>
       <c r="E464" t="n">
-        <v>10.66174697875977</v>
+        <v>10.66174793243408</v>
       </c>
       <c r="F464" t="n">
         <v>103874</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.7453670501709</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="C465" t="n">
-        <v>10.7453670501709</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="D465" t="n">
-        <v>10.50286470773317</v>
+        <v>10.50286563988488</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502151403336</v>
+        <v>10.64502245880179</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9732,16 +9732,16 @@
         <v>44994</v>
       </c>
       <c r="B466" t="n">
-        <v>10.70355892181396</v>
+        <v>10.70355701446533</v>
       </c>
       <c r="C466" t="n">
-        <v>10.82062915921913</v>
+        <v>10.82062723100886</v>
       </c>
       <c r="D466" t="n">
-        <v>10.63666188333691</v>
+        <v>10.63665998790917</v>
       </c>
       <c r="E466" t="n">
-        <v>10.68683424212438</v>
+        <v>10.68683233775605</v>
       </c>
       <c r="F466" t="n">
         <v>86176</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758634567260742</v>
+        <v>9.758633613586426</v>
       </c>
       <c r="C470" t="n">
-        <v>9.9676884311345</v>
+        <v>9.967687457030143</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675012853683121</v>
+        <v>9.675011908180837</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892428636872463</v>
+        <v>9.892427670122959</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9992,16 +9992,16 @@
         <v>45013</v>
       </c>
       <c r="B479" t="n">
-        <v>10.70355892181396</v>
+        <v>10.70355701446533</v>
       </c>
       <c r="C479" t="n">
-        <v>10.74536936082696</v>
+        <v>10.74536744602781</v>
       </c>
       <c r="D479" t="n">
-        <v>10.3272616101344</v>
+        <v>10.32725976984105</v>
       </c>
       <c r="E479" t="n">
-        <v>10.46941844700363</v>
+        <v>10.46941658137827</v>
       </c>
       <c r="F479" t="n">
         <v>226923</v>
@@ -10012,16 +10012,16 @@
         <v>45014</v>
       </c>
       <c r="B480" t="n">
-        <v>10.72028255462646</v>
+        <v>10.72028160095215</v>
       </c>
       <c r="C480" t="n">
-        <v>10.72028255462646</v>
+        <v>10.72028160095215</v>
       </c>
       <c r="D480" t="n">
-        <v>10.4526935867087</v>
+        <v>10.45269265683905</v>
       </c>
       <c r="E480" t="n">
-        <v>10.70355787657011</v>
+        <v>10.70355692438362</v>
       </c>
       <c r="F480" t="n">
         <v>215756</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820669929775</v>
+        <v>10.11820570451678</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201959763182</v>
+        <v>9.633201012665911</v>
       </c>
       <c r="E483" t="n">
-        <v>10.0345849896889</v>
+        <v>10.03458400312928</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10092,16 +10092,16 @@
         <v>45020</v>
       </c>
       <c r="B484" t="n">
-        <v>9.599753379821777</v>
+        <v>9.599754333496094</v>
       </c>
       <c r="C484" t="n">
-        <v>9.758634038918892</v>
+        <v>9.758635008376988</v>
       </c>
       <c r="D484" t="n">
-        <v>9.53285550849724</v>
+        <v>9.532856455525678</v>
       </c>
       <c r="E484" t="n">
-        <v>9.700098926597763</v>
+        <v>9.70009989024077</v>
       </c>
       <c r="F484" t="n">
         <v>529909</v>
@@ -10132,16 +10132,16 @@
         <v>45022</v>
       </c>
       <c r="B486" t="n">
-        <v>9.541219711303711</v>
+        <v>9.541218757629395</v>
       </c>
       <c r="C486" t="n">
-        <v>9.633203353136047</v>
+        <v>9.633202390267682</v>
       </c>
       <c r="D486" t="n">
-        <v>9.390700948292555</v>
+        <v>9.390700009663053</v>
       </c>
       <c r="E486" t="n">
-        <v>9.524495030906616</v>
+        <v>9.524494078903984</v>
       </c>
       <c r="F486" t="n">
         <v>123364</v>
@@ -10152,16 +10152,16 @@
         <v>45026</v>
       </c>
       <c r="B487" t="n">
-        <v>9.407423973083496</v>
+        <v>9.40742301940918</v>
       </c>
       <c r="C487" t="n">
-        <v>9.700099553607547</v>
+        <v>9.700098570263346</v>
       </c>
       <c r="D487" t="n">
-        <v>9.407423973083496</v>
+        <v>9.40742301940918</v>
       </c>
       <c r="E487" t="n">
-        <v>9.574667401994555</v>
+        <v>9.574666431365994</v>
       </c>
       <c r="F487" t="n">
         <v>160237</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758634104106184</v>
+        <v>9.758633144676933</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574667930603027</v>
       </c>
       <c r="C489" t="n">
-        <v>9.783719859219421</v>
+        <v>9.783721808213219</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574667930603027</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700098156805314</v>
+        <v>9.700100089141012</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683374404907227</v>
+        <v>9.683375358581543</v>
       </c>
       <c r="C490" t="n">
-        <v>9.77535802632328</v>
+        <v>9.775358989056672</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566304188533978</v>
+        <v>9.566305130678549</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608114620035645</v>
+        <v>9.608115566297945</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766996023024904</v>
+        <v>9.766995062773542</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549581090294884</v>
+        <v>9.549580151418876</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691737072475323</v>
+        <v>9.691736119623117</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.65828800201416</v>
+        <v>9.658288955688477</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716822271224306</v>
+        <v>9.716823230678386</v>
       </c>
       <c r="D494" t="n">
-        <v>9.59975289266351</v>
+        <v>9.59975384055798</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616476729540551</v>
+        <v>9.616477679086358</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10312,16 +10312,16 @@
         <v>45036</v>
       </c>
       <c r="B495" t="n">
-        <v>9.599753379821777</v>
+        <v>9.599754333496094</v>
       </c>
       <c r="C495" t="n">
-        <v>9.775358716785163</v>
+        <v>9.77535968790475</v>
       </c>
       <c r="D495" t="n">
-        <v>9.549581026504057</v>
+        <v>9.549581975194069</v>
       </c>
       <c r="E495" t="n">
-        <v>9.658288492142907</v>
+        <v>9.658289451632312</v>
       </c>
       <c r="F495" t="n">
         <v>169823</v>
@@ -10452,16 +10452,16 @@
         <v>45049</v>
       </c>
       <c r="B502" t="n">
-        <v>9.151029586791992</v>
+        <v>9.151030540466309</v>
       </c>
       <c r="C502" t="n">
-        <v>9.259871047038219</v>
+        <v>9.259872012055444</v>
       </c>
       <c r="D502" t="n">
-        <v>8.941720509836294</v>
+        <v>8.941721441697471</v>
       </c>
       <c r="E502" t="n">
-        <v>9.100795778437256</v>
+        <v>9.100796726876458</v>
       </c>
       <c r="F502" t="n">
         <v>158340</v>
@@ -10492,16 +10492,16 @@
         <v>45051</v>
       </c>
       <c r="B504" t="n">
-        <v>9.418947219848633</v>
+        <v>9.418946266174316</v>
       </c>
       <c r="C504" t="n">
-        <v>9.4775548773664</v>
+        <v>9.477553917758021</v>
       </c>
       <c r="D504" t="n">
-        <v>9.125913979277989</v>
+        <v>9.125913055273472</v>
       </c>
       <c r="E504" t="n">
-        <v>9.125913979277989</v>
+        <v>9.125913055273472</v>
       </c>
       <c r="F504" t="n">
         <v>204589</v>
@@ -10512,16 +10512,16 @@
         <v>45054</v>
       </c>
       <c r="B505" t="n">
-        <v>9.385458946228027</v>
+        <v>9.385457038879395</v>
       </c>
       <c r="C505" t="n">
-        <v>9.519416908270202</v>
+        <v>9.519414973698122</v>
       </c>
       <c r="D505" t="n">
-        <v>9.326851286372412</v>
+        <v>9.32684939093425</v>
       </c>
       <c r="E505" t="n">
-        <v>9.41894759556884</v>
+        <v>9.418945681414517</v>
       </c>
       <c r="F505" t="n">
         <v>225237</v>
@@ -10552,16 +10552,16 @@
         <v>45056</v>
       </c>
       <c r="B507" t="n">
-        <v>9.586394309997559</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="C507" t="n">
-        <v>9.586394309997559</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="D507" t="n">
-        <v>9.41894604386108</v>
+        <v>9.418947917893513</v>
       </c>
       <c r="E507" t="n">
-        <v>9.452435528854458</v>
+        <v>9.452437409550097</v>
       </c>
       <c r="F507" t="n">
         <v>185415</v>
@@ -10612,16 +10612,16 @@
         <v>45061</v>
       </c>
       <c r="B510" t="n">
-        <v>10.18083381652832</v>
+        <v>10.18083477020264</v>
       </c>
       <c r="C510" t="n">
-        <v>10.32316560114518</v>
+        <v>10.32316656815221</v>
       </c>
       <c r="D510" t="n">
-        <v>10.00501507010967</v>
+        <v>10.00501600731443</v>
       </c>
       <c r="E510" t="n">
-        <v>10.07199319956127</v>
+        <v>10.0719941430401</v>
       </c>
       <c r="F510" t="n">
         <v>215124</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845938682556152</v>
+        <v>9.845939636230469</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293150071748</v>
+        <v>10.27293249575018</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745470229490321</v>
+        <v>9.745471173433298</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548323777152</v>
+        <v>10.10548421658523</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10652,16 +10652,16 @@
         <v>45063</v>
       </c>
       <c r="B512" t="n">
-        <v>9.787333488464355</v>
+        <v>9.787332534790039</v>
       </c>
       <c r="C512" t="n">
-        <v>9.904546282450122</v>
+        <v>9.904545317354632</v>
       </c>
       <c r="D512" t="n">
-        <v>9.594767870207617</v>
+        <v>9.594766935296825</v>
       </c>
       <c r="E512" t="n">
-        <v>9.81244997499506</v>
+        <v>9.812449018873401</v>
       </c>
       <c r="F512" t="n">
         <v>227976</v>
@@ -10732,16 +10732,16 @@
         <v>45069</v>
       </c>
       <c r="B516" t="n">
-        <v>9.603139877319336</v>
+        <v>9.60313892364502</v>
       </c>
       <c r="C516" t="n">
-        <v>9.996642428485981</v>
+        <v>9.99664143573348</v>
       </c>
       <c r="D516" t="n">
-        <v>9.594767715277623</v>
+        <v>9.594766762434734</v>
       </c>
       <c r="E516" t="n">
-        <v>9.862684471139762</v>
+        <v>9.862683491690436</v>
       </c>
       <c r="F516" t="n">
         <v>117359</v>
@@ -10752,16 +10752,16 @@
         <v>45070</v>
       </c>
       <c r="B517" t="n">
-        <v>9.351967811584473</v>
+        <v>9.351966857910156</v>
       </c>
       <c r="C517" t="n">
-        <v>9.678491367489009</v>
+        <v>9.678490380517195</v>
       </c>
       <c r="D517" t="n">
-        <v>9.29336183910025</v>
+        <v>9.293360891402324</v>
       </c>
       <c r="E517" t="n">
-        <v>9.619884553835126</v>
+        <v>9.61988357283979</v>
       </c>
       <c r="F517" t="n">
         <v>244411</v>
@@ -10772,16 +10772,16 @@
         <v>45071</v>
       </c>
       <c r="B518" t="n">
-        <v>9.301733016967773</v>
+        <v>9.30173397064209</v>
       </c>
       <c r="C518" t="n">
-        <v>9.561277570152697</v>
+        <v>9.561278550437214</v>
       </c>
       <c r="D518" t="n">
-        <v>9.293360856236845</v>
+        <v>9.293361809052792</v>
       </c>
       <c r="E518" t="n">
-        <v>9.435690953340915</v>
+        <v>9.435691920749472</v>
       </c>
       <c r="F518" t="n">
         <v>216177</v>
@@ -10852,16 +10852,16 @@
         <v>45077</v>
       </c>
       <c r="B522" t="n">
-        <v>9.084050178527832</v>
+        <v>9.084052085876465</v>
       </c>
       <c r="C522" t="n">
-        <v>9.234753278692377</v>
+        <v>9.234755217683652</v>
       </c>
       <c r="D522" t="n">
-        <v>9.084050178527832</v>
+        <v>9.084052085876465</v>
       </c>
       <c r="E522" t="n">
-        <v>9.209636796306267</v>
+        <v>9.209638730023915</v>
       </c>
       <c r="F522" t="n">
         <v>138113</v>
@@ -10912,16 +10912,16 @@
         <v>45082</v>
       </c>
       <c r="B525" t="n">
-        <v>8.874741554260254</v>
+        <v>8.874740600585938</v>
       </c>
       <c r="C525" t="n">
-        <v>9.142658308994628</v>
+        <v>9.142657326530141</v>
       </c>
       <c r="D525" t="n">
-        <v>8.849625068240838</v>
+        <v>8.849624117265524</v>
       </c>
       <c r="E525" t="n">
-        <v>8.933348370644952</v>
+        <v>8.933347410672782</v>
       </c>
       <c r="F525" t="n">
         <v>464803</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958463668823242</v>
       </c>
       <c r="C526" t="n">
-        <v>9.058934042394197</v>
+        <v>9.058932113654803</v>
       </c>
       <c r="D526" t="n">
-        <v>8.83287978310155</v>
+        <v>8.832877902491413</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933348249323872</v>
+        <v>8.933346347322974</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.16777515411377</v>
+        <v>9.167774200439453</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226381967416739</v>
+        <v>9.226381007645871</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109168340810799</v>
+        <v>9.109167393233035</v>
       </c>
       <c r="E528" t="n">
-        <v>9.209637644284264</v>
+        <v>9.209636686255218</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -10992,16 +10992,16 @@
         <v>45089</v>
       </c>
       <c r="B529" t="n">
-        <v>9.184518814086914</v>
+        <v>9.18451976776123</v>
       </c>
       <c r="C529" t="n">
-        <v>9.243125623158235</v>
+        <v>9.24312658291799</v>
       </c>
       <c r="D529" t="n">
-        <v>9.13428500714692</v>
+        <v>9.134285955605209</v>
       </c>
       <c r="E529" t="n">
-        <v>9.209636979311302</v>
+        <v>9.209637935593761</v>
       </c>
       <c r="F529" t="n">
         <v>222709</v>
@@ -11032,16 +11032,16 @@
         <v>45091</v>
       </c>
       <c r="B531" t="n">
-        <v>9.100795745849609</v>
+        <v>9.100796699523926</v>
       </c>
       <c r="C531" t="n">
-        <v>9.218009366873643</v>
+        <v>9.218010332830801</v>
       </c>
       <c r="D531" t="n">
-        <v>9.042188935337592</v>
+        <v>9.04218988287049</v>
       </c>
       <c r="E531" t="n">
-        <v>9.142657392856929</v>
+        <v>9.142658350917937</v>
       </c>
       <c r="F531" t="n">
         <v>269590</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.99195384979248</v>
       </c>
       <c r="C535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.99195384979248</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899858501814995</v>
+        <v>8.899857557908286</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983582641817451</v>
+        <v>8.983581689031073</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11132,16 +11132,16 @@
         <v>45098</v>
       </c>
       <c r="B536" t="n">
-        <v>9.000326156616211</v>
+        <v>9.000327110290527</v>
       </c>
       <c r="C536" t="n">
-        <v>9.04218864344176</v>
+        <v>9.042189601551824</v>
       </c>
       <c r="D536" t="n">
-        <v>8.85799605668419</v>
+        <v>8.857996995277212</v>
       </c>
       <c r="E536" t="n">
-        <v>9.033816482544484</v>
+        <v>9.033817439767434</v>
       </c>
       <c r="F536" t="n">
         <v>259897</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950093269348145</v>
+        <v>8.950092315673828</v>
       </c>
       <c r="C537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="D537" t="n">
-        <v>8.83287964006866</v>
+        <v>8.832878698884004</v>
       </c>
       <c r="E537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11172,16 +11172,16 @@
         <v>45100</v>
       </c>
       <c r="B538" t="n">
-        <v>8.983583450317383</v>
+        <v>8.983582496643066</v>
       </c>
       <c r="C538" t="n">
-        <v>9.008700778695582</v>
+        <v>9.008699822354874</v>
       </c>
       <c r="D538" t="n">
-        <v>8.874741974401767</v>
+        <v>8.874741032281783</v>
       </c>
       <c r="E538" t="n">
-        <v>8.899859302779966</v>
+        <v>8.89985835799359</v>
       </c>
       <c r="F538" t="n">
         <v>372938</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958463668823242</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000325310544016</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841251944994323</v>
+        <v>8.841250062601667</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000325310544016</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11272,16 +11272,16 @@
         <v>45107</v>
       </c>
       <c r="B543" t="n">
-        <v>9.05056095123291</v>
+        <v>9.050562858581543</v>
       </c>
       <c r="C543" t="n">
-        <v>9.176146731408684</v>
+        <v>9.176148665223728</v>
       </c>
       <c r="D543" t="n">
-        <v>8.765899905579127</v>
+        <v>8.765901752937241</v>
       </c>
       <c r="E543" t="n">
-        <v>8.782644227645445</v>
+        <v>8.782646078532318</v>
       </c>
       <c r="F543" t="n">
         <v>473547</v>
@@ -11292,16 +11292,16 @@
         <v>45110</v>
       </c>
       <c r="B544" t="n">
-        <v>9.410574913024902</v>
+        <v>9.410573959350586</v>
       </c>
       <c r="C544" t="n">
-        <v>9.4189470748973</v>
+        <v>9.418946120374542</v>
       </c>
       <c r="D544" t="n">
-        <v>9.000327204901865</v>
+        <v>9.00032629280234</v>
       </c>
       <c r="E544" t="n">
-        <v>9.06730618222041</v>
+        <v>9.067305263333189</v>
       </c>
       <c r="F544" t="n">
         <v>368934</v>
@@ -11312,16 +11312,16 @@
         <v>45111</v>
       </c>
       <c r="B545" t="n">
-        <v>9.586394309997559</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="C545" t="n">
-        <v>9.594766470953505</v>
+        <v>9.594768379967897</v>
       </c>
       <c r="D545" t="n">
-        <v>9.318477588880949</v>
+        <v>9.318479442923763</v>
       </c>
       <c r="E545" t="n">
-        <v>9.335221910792841</v>
+        <v>9.335223768167175</v>
       </c>
       <c r="F545" t="n">
         <v>135795</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695236206054688</v>
+        <v>9.695237159729004</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843017738918</v>
+        <v>9.753843977178107</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511042768497374</v>
+        <v>9.511043704053456</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611512069195841</v>
+        <v>9.611513014634612</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11352,16 +11352,16 @@
         <v>45113</v>
       </c>
       <c r="B547" t="n">
-        <v>9.418947219848633</v>
+        <v>9.418946266174316</v>
       </c>
       <c r="C547" t="n">
-        <v>9.703609139587735</v>
+        <v>9.703608157091221</v>
       </c>
       <c r="D547" t="n">
-        <v>9.410575057847394</v>
+        <v>9.410574105020764</v>
       </c>
       <c r="E547" t="n">
-        <v>9.695236977586497</v>
+        <v>9.695235995937669</v>
       </c>
       <c r="F547" t="n">
         <v>248414</v>
@@ -11392,16 +11392,16 @@
         <v>45117</v>
       </c>
       <c r="B549" t="n">
-        <v>9.619884490966797</v>
+        <v>9.619885444641113</v>
       </c>
       <c r="C549" t="n">
-        <v>9.745471120239847</v>
+        <v>9.745472086364286</v>
       </c>
       <c r="D549" t="n">
-        <v>9.527788190279663</v>
+        <v>9.527789134823944</v>
       </c>
       <c r="E549" t="n">
-        <v>9.628256652528449</v>
+        <v>9.628257607032745</v>
       </c>
       <c r="F549" t="n">
         <v>614083</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703609466552734</v>
+        <v>9.703608512878418</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703609466552734</v>
+        <v>9.703608512878418</v>
       </c>
       <c r="D550" t="n">
-        <v>9.385458888088531</v>
+        <v>9.385457965682171</v>
       </c>
       <c r="E550" t="n">
-        <v>9.61988532021015</v>
+        <v>9.619884374764274</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11432,16 +11432,16 @@
         <v>45119</v>
       </c>
       <c r="B551" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C551" t="n">
-        <v>9.912918058384282</v>
+        <v>9.912919025122674</v>
       </c>
       <c r="D551" t="n">
-        <v>9.594766682188503</v>
+        <v>9.594767617899787</v>
       </c>
       <c r="E551" t="n">
-        <v>9.753842790871198</v>
+        <v>9.753843742096077</v>
       </c>
       <c r="F551" t="n">
         <v>281073</v>
@@ -11572,16 +11572,16 @@
         <v>45128</v>
       </c>
       <c r="B558" t="n">
-        <v>9.737099647521973</v>
+        <v>9.73709774017334</v>
       </c>
       <c r="C558" t="n">
-        <v>9.753844814446138</v>
+        <v>9.753842903817384</v>
       </c>
       <c r="D558" t="n">
-        <v>9.527789687403725</v>
+        <v>9.527787821055707</v>
       </c>
       <c r="E558" t="n">
-        <v>9.628258165439362</v>
+        <v>9.628256279411108</v>
       </c>
       <c r="F558" t="n">
         <v>205537</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711980587323517</v>
+        <v>9.711981520878043</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753843076590339</v>
+        <v>9.753844014168855</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11612,16 +11612,16 @@
         <v>45132</v>
       </c>
       <c r="B560" t="n">
-        <v>9.770587921142578</v>
+        <v>9.770586967468262</v>
       </c>
       <c r="C560" t="n">
-        <v>10.04687683214587</v>
+        <v>10.04687585150392</v>
       </c>
       <c r="D560" t="n">
-        <v>9.661747293809594</v>
+        <v>9.661746350758847</v>
       </c>
       <c r="E560" t="n">
-        <v>9.92129188114766</v>
+        <v>9.921290912763636</v>
       </c>
       <c r="F560" t="n">
         <v>194370</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578023910522461</v>
+        <v>9.578022956848145</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695237550140671</v>
+        <v>9.695236584795509</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469182433399908</v>
+        <v>9.469181490562828</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686864546475267</v>
+        <v>9.686863581963795</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11852,16 +11852,16 @@
         <v>45148</v>
       </c>
       <c r="B572" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C572" t="n">
-        <v>9.837566925782678</v>
+        <v>9.837567885172595</v>
       </c>
       <c r="D572" t="n">
-        <v>9.544532033007691</v>
+        <v>9.54453296381994</v>
       </c>
       <c r="E572" t="n">
-        <v>9.578022359907973</v>
+        <v>9.5780232939863</v>
       </c>
       <c r="F572" t="n">
         <v>202060</v>
@@ -11892,16 +11892,16 @@
         <v>45152</v>
       </c>
       <c r="B574" t="n">
-        <v>10.74178695678711</v>
+        <v>10.74178600311279</v>
       </c>
       <c r="C574" t="n">
-        <v>10.88411707930441</v>
+        <v>10.88411611299378</v>
       </c>
       <c r="D574" t="n">
-        <v>10.23107076112871</v>
+        <v>10.23106985279666</v>
       </c>
       <c r="E574" t="n">
-        <v>10.45712587058279</v>
+        <v>10.45712494218117</v>
       </c>
       <c r="F574" t="n">
         <v>441415</v>
@@ -11932,16 +11932,16 @@
         <v>45154</v>
       </c>
       <c r="B576" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="C576" t="n">
-        <v>11.26087395777899</v>
+        <v>11.2608749384303</v>
       </c>
       <c r="D576" t="n">
-        <v>10.78364730969746</v>
+        <v>10.78364824878957</v>
       </c>
       <c r="E576" t="n">
-        <v>11.05993620038423</v>
+        <v>11.05993716353692</v>
       </c>
       <c r="F576" t="n">
         <v>525379</v>
@@ -11992,16 +11992,16 @@
         <v>45159</v>
       </c>
       <c r="B579" t="n">
-        <v>11.16877841949463</v>
+        <v>11.16877746582031</v>
       </c>
       <c r="C579" t="n">
-        <v>11.436695167162</v>
+        <v>11.43669419061094</v>
       </c>
       <c r="D579" t="n">
-        <v>11.04319262803141</v>
+        <v>11.04319168508056</v>
       </c>
       <c r="E579" t="n">
-        <v>11.37808835232321</v>
+        <v>11.37808738077644</v>
       </c>
       <c r="F579" t="n">
         <v>524641</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716278076172</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716278076172</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10179862365917</v>
+        <v>11.10179954134582</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877759534116</v>
+        <v>11.16877851856436</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12172,16 +12172,16 @@
         <v>45170</v>
       </c>
       <c r="B588" t="n">
-        <v>12.12323188781738</v>
+        <v>12.1232328414917</v>
       </c>
       <c r="C588" t="n">
-        <v>12.26556284528164</v>
+        <v>12.26556381015243</v>
       </c>
       <c r="D588" t="n">
-        <v>12.10648756409787</v>
+        <v>12.10648851645499</v>
       </c>
       <c r="E588" t="n">
-        <v>12.15672137642609</v>
+        <v>12.15672233273486</v>
       </c>
       <c r="F588" t="n">
         <v>195423</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625325429223</v>
+        <v>12.05625227825024</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66275070046011</v>
+        <v>11.66274975627503</v>
       </c>
       <c r="E589" t="n">
-        <v>11.99764643726385</v>
+        <v>11.9976454659665</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461082458496</v>
+        <v>11.70461177825928</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80507928016331</v>
+        <v>11.80508024202364</v>
       </c>
       <c r="D590" t="n">
-        <v>11.59576936683122</v>
+        <v>11.5957703116373</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996195597632</v>
+        <v>11.77996291579013</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12232,16 +12232,16 @@
         <v>45175</v>
       </c>
       <c r="B591" t="n">
-        <v>11.74647521972656</v>
+        <v>11.74647426605225</v>
       </c>
       <c r="C591" t="n">
-        <v>11.90555051052048</v>
+        <v>11.90554954393114</v>
       </c>
       <c r="D591" t="n">
-        <v>11.69624056319386</v>
+        <v>11.696239613598</v>
       </c>
       <c r="E591" t="n">
-        <v>11.69624056319386</v>
+        <v>11.696239613598</v>
       </c>
       <c r="F591" t="n">
         <v>295506</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879190103679</v>
+        <v>11.52879096769665</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393531799316</v>
+        <v>12.27393627166748</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393531799316</v>
+        <v>12.27393627166748</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298367423283</v>
+        <v>11.71298458432168</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135667690049</v>
+        <v>11.72135758763992</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12332,16 +12332,16 @@
         <v>45183</v>
       </c>
       <c r="B596" t="n">
-        <v>12.34091472625732</v>
+        <v>12.34091377258301</v>
       </c>
       <c r="C596" t="n">
-        <v>12.51673518290008</v>
+        <v>12.51673421563881</v>
       </c>
       <c r="D596" t="n">
-        <v>12.26556358265027</v>
+        <v>12.2655626347989</v>
       </c>
       <c r="E596" t="n">
-        <v>12.47487352991503</v>
+        <v>12.47487256588872</v>
       </c>
       <c r="F596" t="n">
         <v>207012</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461082458496</v>
+        <v>11.70461177825928</v>
       </c>
       <c r="C599" t="n">
-        <v>11.86368608954307</v>
+        <v>11.8636870561786</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414152783702</v>
+        <v>11.60414247332525</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786566140377</v>
+        <v>11.68786661371372</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12412,16 +12412,16 @@
         <v>45189</v>
       </c>
       <c r="B600" t="n">
-        <v>11.8385705947876</v>
+        <v>11.83857154846191</v>
       </c>
       <c r="C600" t="n">
-        <v>11.91392173246913</v>
+        <v>11.91392269221347</v>
       </c>
       <c r="D600" t="n">
-        <v>11.62926066398271</v>
+        <v>11.62926160079574</v>
       </c>
       <c r="E600" t="n">
-        <v>11.62926066398271</v>
+        <v>11.62926160079574</v>
       </c>
       <c r="F600" t="n">
         <v>141695</v>
@@ -12432,16 +12432,16 @@
         <v>45190</v>
       </c>
       <c r="B601" t="n">
-        <v>11.44506740570068</v>
+        <v>11.44506645202637</v>
       </c>
       <c r="C601" t="n">
-        <v>11.83019862679808</v>
+        <v>11.83019764103224</v>
       </c>
       <c r="D601" t="n">
-        <v>11.44506740570068</v>
+        <v>11.44506645202637</v>
       </c>
       <c r="E601" t="n">
-        <v>11.83019862679808</v>
+        <v>11.83019764103224</v>
       </c>
       <c r="F601" t="n">
         <v>277385</v>
@@ -12452,16 +12452,16 @@
         <v>45191</v>
       </c>
       <c r="B602" t="n">
-        <v>11.54553604125977</v>
+        <v>11.54553699493408</v>
       </c>
       <c r="C602" t="n">
-        <v>11.73810164061331</v>
+        <v>11.73810261019376</v>
       </c>
       <c r="D602" t="n">
-        <v>11.47855706808011</v>
+        <v>11.47855801622189</v>
       </c>
       <c r="E602" t="n">
-        <v>11.52879087738004</v>
+        <v>11.52879182967118</v>
       </c>
       <c r="F602" t="n">
         <v>228714</v>
@@ -12512,16 +12512,16 @@
         <v>45196</v>
       </c>
       <c r="B605" t="n">
-        <v>10.7669038772583</v>
+        <v>10.76690292358398</v>
       </c>
       <c r="C605" t="n">
-        <v>11.12691693338246</v>
+        <v>11.12691594782012</v>
       </c>
       <c r="D605" t="n">
-        <v>10.63294592203521</v>
+        <v>10.63294498022617</v>
       </c>
       <c r="E605" t="n">
-        <v>11.09342744457668</v>
+        <v>11.09342646198067</v>
       </c>
       <c r="F605" t="n">
         <v>269906</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876541137695</v>
+        <v>10.80876636505127</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854465153565</v>
+        <v>11.11854563254228</v>
       </c>
       <c r="D608" t="n">
-        <v>10.71666910786212</v>
+        <v>10.71667005341063</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854465153565</v>
+        <v>11.11854563254228</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12592,16 +12592,16 @@
         <v>45202</v>
       </c>
       <c r="B609" t="n">
-        <v>10.58271217346191</v>
+        <v>10.58271026611328</v>
       </c>
       <c r="C609" t="n">
-        <v>10.89248976112052</v>
+        <v>10.8924877979399</v>
       </c>
       <c r="D609" t="n">
-        <v>10.56596700704184</v>
+        <v>10.56596510271123</v>
       </c>
       <c r="E609" t="n">
-        <v>10.89248976112052</v>
+        <v>10.8924877979399</v>
       </c>
       <c r="F609" t="n">
         <v>176144</v>
@@ -12612,16 +12612,16 @@
         <v>45203</v>
       </c>
       <c r="B610" t="n">
-        <v>10.50735855102539</v>
+        <v>10.50735950469971</v>
       </c>
       <c r="C610" t="n">
-        <v>10.75015795872518</v>
+        <v>10.75015893443658</v>
       </c>
       <c r="D610" t="n">
-        <v>10.44037873693919</v>
+        <v>10.44037968453425</v>
       </c>
       <c r="E610" t="n">
-        <v>10.75015795872518</v>
+        <v>10.75015893443658</v>
       </c>
       <c r="F610" t="n">
         <v>180674</v>
@@ -12632,16 +12632,16 @@
         <v>45204</v>
       </c>
       <c r="B611" t="n">
-        <v>10.58271217346191</v>
+        <v>10.58271026611328</v>
       </c>
       <c r="C611" t="n">
-        <v>10.58271217346191</v>
+        <v>10.58271026611328</v>
       </c>
       <c r="D611" t="n">
-        <v>10.33153972417939</v>
+        <v>10.3315378621002</v>
       </c>
       <c r="E611" t="n">
-        <v>10.50736018632623</v>
+        <v>10.50735829255848</v>
       </c>
       <c r="F611" t="n">
         <v>99766</v>
@@ -12672,16 +12672,16 @@
         <v>45208</v>
       </c>
       <c r="B613" t="n">
-        <v>10.18920803070068</v>
+        <v>10.189208984375</v>
       </c>
       <c r="C613" t="n">
-        <v>10.41526227506603</v>
+        <v>10.41526324989824</v>
       </c>
       <c r="D613" t="n">
-        <v>10.18920803070068</v>
+        <v>10.189208984375</v>
       </c>
       <c r="E613" t="n">
-        <v>10.39851711121656</v>
+        <v>10.39851808448147</v>
       </c>
       <c r="F613" t="n">
         <v>296138</v>
@@ -12692,16 +12692,16 @@
         <v>45209</v>
       </c>
       <c r="B614" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="C614" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="D614" t="n">
-        <v>10.15571755386226</v>
+        <v>10.15571843827122</v>
       </c>
       <c r="E614" t="n">
-        <v>10.15571755386226</v>
+        <v>10.15571843827122</v>
       </c>
       <c r="F614" t="n">
         <v>338699</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203380584717</v>
+        <v>11.15203285217285</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203380584717</v>
+        <v>11.15203285217285</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457244623281</v>
+        <v>10.62457153766474</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411704494031</v>
+        <v>10.88411611417709</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691688537598</v>
+        <v>11.12691593170166</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226802457144</v>
+        <v>11.20226706443887</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690383080508</v>
+        <v>10.76690290798703</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970325447664</v>
+        <v>11.00970231084856</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12752,16 +12752,16 @@
         <v>45215</v>
       </c>
       <c r="B617" t="n">
-        <v>11.02644824981689</v>
+        <v>11.02644729614258</v>
       </c>
       <c r="C617" t="n">
-        <v>11.27762069182936</v>
+        <v>11.27761971643121</v>
       </c>
       <c r="D617" t="n">
-        <v>10.95109710603197</v>
+        <v>10.95109615887475</v>
       </c>
       <c r="E617" t="n">
-        <v>11.12691756308977</v>
+        <v>11.1269166007259</v>
       </c>
       <c r="F617" t="n">
         <v>160026</v>
@@ -12772,16 +12772,16 @@
         <v>45216</v>
       </c>
       <c r="B618" t="n">
-        <v>10.57433795928955</v>
+        <v>10.57433891296387</v>
       </c>
       <c r="C618" t="n">
-        <v>11.02644730684428</v>
+        <v>11.02644830129326</v>
       </c>
       <c r="D618" t="n">
-        <v>10.41526268177113</v>
+        <v>10.41526362109882</v>
       </c>
       <c r="E618" t="n">
-        <v>11.02644730684428</v>
+        <v>11.02644830129326</v>
       </c>
       <c r="F618" t="n">
         <v>572365</v>
@@ -12792,16 +12792,16 @@
         <v>45217</v>
       </c>
       <c r="B619" t="n">
-        <v>10.24781513214111</v>
+        <v>10.2478141784668</v>
       </c>
       <c r="C619" t="n">
-        <v>10.60782820352242</v>
+        <v>10.60782721634484</v>
       </c>
       <c r="D619" t="n">
-        <v>10.23107080761346</v>
+        <v>10.23106985549739</v>
       </c>
       <c r="E619" t="n">
-        <v>10.57433871329738</v>
+        <v>10.57433772923638</v>
       </c>
       <c r="F619" t="n">
         <v>234192</v>
@@ -12812,16 +12812,16 @@
         <v>45218</v>
       </c>
       <c r="B620" t="n">
-        <v>10.34828281402588</v>
+        <v>10.3482837677002</v>
       </c>
       <c r="C620" t="n">
-        <v>10.4906137675105</v>
+        <v>10.49061473430172</v>
       </c>
       <c r="D620" t="n">
-        <v>10.28130467985089</v>
+        <v>10.28130562735265</v>
       </c>
       <c r="E620" t="n">
-        <v>10.30642116472789</v>
+        <v>10.30642211454433</v>
       </c>
       <c r="F620" t="n">
         <v>130844</v>
@@ -12832,16 +12832,16 @@
         <v>45219</v>
       </c>
       <c r="B621" t="n">
-        <v>10.87574291229248</v>
+        <v>10.8757438659668</v>
       </c>
       <c r="C621" t="n">
-        <v>11.00970168906035</v>
+        <v>11.00970265448127</v>
       </c>
       <c r="D621" t="n">
-        <v>10.27293136093056</v>
+        <v>10.27293226174542</v>
       </c>
       <c r="E621" t="n">
-        <v>10.34828164824265</v>
+        <v>10.34828255566484</v>
       </c>
       <c r="F621" t="n">
         <v>2108154</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295806884766</v>
+        <v>10.99295711517334</v>
       </c>
       <c r="C622" t="n">
-        <v>11.13528902626719</v>
+        <v>11.1352880602452</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039245794601</v>
+        <v>10.80039152097738</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82551062585675</v>
+        <v>10.82550968670904</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12892,16 +12892,16 @@
         <v>45224</v>
       </c>
       <c r="B624" t="n">
-        <v>11.25250339508057</v>
+        <v>11.25250244140625</v>
       </c>
       <c r="C624" t="n">
-        <v>11.37808919585427</v>
+        <v>11.37808823153628</v>
       </c>
       <c r="D624" t="n">
-        <v>11.06830993395344</v>
+        <v>11.06830899588992</v>
       </c>
       <c r="E624" t="n">
-        <v>11.26087555748688</v>
+        <v>11.26087460310301</v>
       </c>
       <c r="F624" t="n">
         <v>356609</v>
@@ -12972,16 +12972,16 @@
         <v>45230</v>
       </c>
       <c r="B628" t="n">
-        <v>10.68783855438232</v>
+        <v>10.68783950805664</v>
       </c>
       <c r="C628" t="n">
-        <v>10.70476345459523</v>
+        <v>10.70476440977975</v>
       </c>
       <c r="D628" t="n">
-        <v>10.06163084967988</v>
+        <v>10.06163174747778</v>
       </c>
       <c r="E628" t="n">
-        <v>10.57782967869298</v>
+        <v>10.57783062255122</v>
       </c>
       <c r="F628" t="n">
         <v>335223</v>
@@ -13132,16 +13132,16 @@
         <v>45243</v>
       </c>
       <c r="B636" t="n">
-        <v>12.36336708068848</v>
+        <v>12.36336803436279</v>
       </c>
       <c r="C636" t="n">
-        <v>12.51568778136439</v>
+        <v>12.51568874678828</v>
       </c>
       <c r="D636" t="n">
-        <v>12.04180077917336</v>
+        <v>12.04180170804298</v>
       </c>
       <c r="E636" t="n">
-        <v>12.13488645477382</v>
+        <v>12.1348873908238</v>
       </c>
       <c r="F636" t="n">
         <v>539496</v>
@@ -13152,16 +13152,16 @@
         <v>45244</v>
       </c>
       <c r="B637" t="n">
-        <v>12.27028274536133</v>
+        <v>12.27028369903564</v>
       </c>
       <c r="C637" t="n">
-        <v>12.6510840871611</v>
+        <v>12.65108507043216</v>
       </c>
       <c r="D637" t="n">
-        <v>12.27028274536133</v>
+        <v>12.27028369903564</v>
       </c>
       <c r="E637" t="n">
-        <v>12.36336757448117</v>
+        <v>12.36336853539025</v>
       </c>
       <c r="F637" t="n">
         <v>455532</v>
@@ -13372,16 +13372,16 @@
         <v>45260</v>
       </c>
       <c r="B648" t="n">
-        <v>13.37037754058838</v>
+        <v>13.37037658691406</v>
       </c>
       <c r="C648" t="n">
-        <v>13.37037754058838</v>
+        <v>13.37037658691406</v>
       </c>
       <c r="D648" t="n">
-        <v>12.70185879108874</v>
+        <v>12.70185788509813</v>
       </c>
       <c r="E648" t="n">
-        <v>13.09112303450597</v>
+        <v>13.09112210075015</v>
       </c>
       <c r="F648" t="n">
         <v>345125</v>
@@ -13392,16 +13392,16 @@
         <v>45261</v>
       </c>
       <c r="B649" t="n">
-        <v>13.22651863098145</v>
+        <v>13.22651958465576</v>
       </c>
       <c r="C649" t="n">
-        <v>13.35345240983534</v>
+        <v>13.35345337266199</v>
       </c>
       <c r="D649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="E649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="F649" t="n">
         <v>156128</v>
@@ -13412,16 +13412,16 @@
         <v>45264</v>
       </c>
       <c r="B650" t="n">
-        <v>12.76109409332275</v>
+        <v>12.76109504699707</v>
       </c>
       <c r="C650" t="n">
-        <v>13.22651909919413</v>
+        <v>13.22652008765104</v>
       </c>
       <c r="D650" t="n">
-        <v>12.76109409332275</v>
+        <v>12.76109504699707</v>
       </c>
       <c r="E650" t="n">
-        <v>13.22651909919413</v>
+        <v>13.22652008765104</v>
       </c>
       <c r="F650" t="n">
         <v>177619</v>
@@ -13512,16 +13512,16 @@
         <v>45271</v>
       </c>
       <c r="B655" t="n">
-        <v>12.73570823669434</v>
+        <v>12.73570728302002</v>
       </c>
       <c r="C655" t="n">
-        <v>13.0572745850315</v>
+        <v>13.05727360727768</v>
       </c>
       <c r="D655" t="n">
-        <v>12.57492463742648</v>
+        <v>12.57492369579195</v>
       </c>
       <c r="E655" t="n">
-        <v>12.82033104943554</v>
+        <v>12.82033008942451</v>
       </c>
       <c r="F655" t="n">
         <v>302669</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109316972536</v>
+        <v>12.76109408341076</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033791853966</v>
+        <v>12.93033884434287</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13552,16 +13552,16 @@
         <v>45273</v>
       </c>
       <c r="B657" t="n">
-        <v>13.2772912979126</v>
+        <v>13.27729225158691</v>
       </c>
       <c r="C657" t="n">
-        <v>13.29421534789424</v>
+        <v>13.29421630278417</v>
       </c>
       <c r="D657" t="n">
-        <v>12.92187604591681</v>
+        <v>12.92187697406255</v>
       </c>
       <c r="E657" t="n">
-        <v>13.23498032276005</v>
+        <v>13.23498127339527</v>
       </c>
       <c r="F657" t="n">
         <v>131160</v>
@@ -13572,16 +13572,16 @@
         <v>45274</v>
       </c>
       <c r="B658" t="n">
-        <v>13.32806587219238</v>
+        <v>13.32806491851807</v>
       </c>
       <c r="C658" t="n">
-        <v>13.35345279874222</v>
+        <v>13.35345184325137</v>
       </c>
       <c r="D658" t="n">
-        <v>12.97265060089158</v>
+        <v>12.97264967264859</v>
       </c>
       <c r="E658" t="n">
-        <v>13.2772920190927</v>
+        <v>13.27729106905145</v>
       </c>
       <c r="F658" t="n">
         <v>222288</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45499897003174</v>
+        <v>13.45499992370605</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040449719429</v>
+        <v>13.70040546826266</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806519394055</v>
+        <v>13.32806613861795</v>
       </c>
       <c r="E662" t="n">
-        <v>13.38730021927779</v>
+        <v>13.3873011681537</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13832,16 +13832,16 @@
         <v>45296</v>
       </c>
       <c r="B671" t="n">
-        <v>13.96732044219971</v>
+        <v>13.96731948852539</v>
       </c>
       <c r="C671" t="n">
-        <v>14.27057047589709</v>
+        <v>14.27056950151718</v>
       </c>
       <c r="D671" t="n">
-        <v>13.86921034802636</v>
+        <v>13.8692094010509</v>
       </c>
       <c r="E671" t="n">
-        <v>13.97624019337704</v>
+        <v>13.97623923909369</v>
       </c>
       <c r="F671" t="n">
         <v>90074</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623920440674</v>
+        <v>13.97623825073242</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461330219005</v>
+        <v>13.82461235886199</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13952,16 +13952,16 @@
         <v>45306</v>
       </c>
       <c r="B677" t="n">
-        <v>14.3508415222168</v>
+        <v>14.35084056854248</v>
       </c>
       <c r="C677" t="n">
-        <v>14.43111390375971</v>
+        <v>14.43111294475096</v>
       </c>
       <c r="D677" t="n">
-        <v>13.91380509137646</v>
+        <v>13.91380416674507</v>
       </c>
       <c r="E677" t="n">
-        <v>14.07434985446229</v>
+        <v>14.07434891916202</v>
       </c>
       <c r="F677" t="n">
         <v>161817</v>
@@ -14212,16 +14212,16 @@
         <v>45323</v>
       </c>
       <c r="B690" t="n">
-        <v>13.70866584777832</v>
+        <v>13.708664894104</v>
       </c>
       <c r="C690" t="n">
-        <v>13.70866584777832</v>
+        <v>13.708664894104</v>
       </c>
       <c r="D690" t="n">
-        <v>13.05757063872765</v>
+        <v>13.05756973034824</v>
       </c>
       <c r="E690" t="n">
-        <v>13.48568820831384</v>
+        <v>13.48568727015147</v>
       </c>
       <c r="F690" t="n">
         <v>1088052</v>
@@ -14332,16 +14332,16 @@
         <v>45331</v>
       </c>
       <c r="B696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.8692102432251</v>
       </c>
       <c r="C696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.8692102432251</v>
       </c>
       <c r="D696" t="n">
-        <v>13.49460665160678</v>
+        <v>13.49460757952268</v>
       </c>
       <c r="E696" t="n">
-        <v>13.74434263966654</v>
+        <v>13.74434358475478</v>
       </c>
       <c r="F696" t="n">
         <v>146541</v>
@@ -14532,16 +14532,16 @@
         <v>45349</v>
       </c>
       <c r="B706" t="n">
-        <v>13.64623260498047</v>
+        <v>13.64623355865479</v>
       </c>
       <c r="C706" t="n">
-        <v>13.91380451066463</v>
+        <v>13.91380548303835</v>
       </c>
       <c r="D706" t="n">
-        <v>13.56596022678783</v>
+        <v>13.56596117485227</v>
       </c>
       <c r="E706" t="n">
-        <v>13.6283931039193</v>
+        <v>13.6283940563469</v>
       </c>
       <c r="F706" t="n">
         <v>240197</v>
@@ -14572,16 +14572,16 @@
         <v>45351</v>
       </c>
       <c r="B708" t="n">
-        <v>13.64623260498047</v>
+        <v>13.64623355865479</v>
       </c>
       <c r="C708" t="n">
-        <v>13.73542204541239</v>
+        <v>13.73542300531976</v>
       </c>
       <c r="D708" t="n">
-        <v>13.46785013972823</v>
+        <v>13.46785108093619</v>
       </c>
       <c r="E708" t="n">
-        <v>13.46785013972823</v>
+        <v>13.46785108093619</v>
       </c>
       <c r="F708" t="n">
         <v>71953</v>
@@ -14612,16 +14612,16 @@
         <v>45355</v>
       </c>
       <c r="B710" t="n">
-        <v>13.57487869262695</v>
+        <v>13.57487964630127</v>
       </c>
       <c r="C710" t="n">
-        <v>13.58379754680512</v>
+        <v>13.58379850110602</v>
       </c>
       <c r="D710" t="n">
-        <v>13.25379008514498</v>
+        <v>13.2537910162619</v>
       </c>
       <c r="E710" t="n">
-        <v>13.4143348369345</v>
+        <v>13.41433577933015</v>
       </c>
       <c r="F710" t="n">
         <v>828997</v>
@@ -14632,16 +14632,16 @@
         <v>45356</v>
       </c>
       <c r="B711" t="n">
-        <v>13.57487869262695</v>
+        <v>13.57487964630127</v>
       </c>
       <c r="C711" t="n">
-        <v>13.62839271379305</v>
+        <v>13.62839367122688</v>
       </c>
       <c r="D711" t="n">
-        <v>13.33406246103974</v>
+        <v>13.33406339779602</v>
       </c>
       <c r="E711" t="n">
-        <v>13.62839271379305</v>
+        <v>13.62839367122688</v>
       </c>
       <c r="F711" t="n">
         <v>182781</v>
@@ -14732,16 +14732,16 @@
         <v>45363</v>
       </c>
       <c r="B716" t="n">
-        <v>15.42113494873047</v>
+        <v>15.42113399505615</v>
       </c>
       <c r="C716" t="n">
-        <v>15.98303804908045</v>
+        <v>15.98303706065691</v>
       </c>
       <c r="D716" t="n">
-        <v>13.85137255522528</v>
+        <v>13.85137169862826</v>
       </c>
       <c r="E716" t="n">
-        <v>14.09218791363322</v>
+        <v>14.09218704214369</v>
       </c>
       <c r="F716" t="n">
         <v>1351743</v>
@@ -14772,16 +14772,16 @@
         <v>45365</v>
       </c>
       <c r="B718" t="n">
-        <v>15.78681564331055</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="C718" t="n">
-        <v>15.99195555278141</v>
+        <v>15.99195748491486</v>
       </c>
       <c r="D718" t="n">
-        <v>15.58167573383968</v>
+        <v>15.5816776164035</v>
       </c>
       <c r="E718" t="n">
-        <v>15.78681564331055</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="F718" t="n">
         <v>580477</v>
@@ -14832,16 +14832,16 @@
         <v>45370</v>
       </c>
       <c r="B721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="C721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="D721" t="n">
-        <v>15.61735280122237</v>
+        <v>15.61735464537877</v>
       </c>
       <c r="E721" t="n">
-        <v>15.8314124586462</v>
+        <v>15.83141432807958</v>
       </c>
       <c r="F721" t="n">
         <v>227239</v>
@@ -14912,16 +14912,16 @@
         <v>45376</v>
       </c>
       <c r="B725" t="n">
-        <v>15.59951686859131</v>
+        <v>15.59951591491699</v>
       </c>
       <c r="C725" t="n">
-        <v>16.24169232953496</v>
+        <v>16.24169133660133</v>
       </c>
       <c r="D725" t="n">
-        <v>15.48356727689714</v>
+        <v>15.48356633031139</v>
       </c>
       <c r="E725" t="n">
-        <v>15.80465500736896</v>
+        <v>15.80465404115356</v>
       </c>
       <c r="F725" t="n">
         <v>355555</v>
@@ -14952,16 +14952,16 @@
         <v>45378</v>
       </c>
       <c r="B727" t="n">
-        <v>15.43005275726318</v>
+        <v>15.4300537109375</v>
       </c>
       <c r="C727" t="n">
-        <v>15.75114045878136</v>
+        <v>15.75114143230092</v>
       </c>
       <c r="D727" t="n">
-        <v>14.9038251432713</v>
+        <v>14.90382606442144</v>
       </c>
       <c r="E727" t="n">
-        <v>15.23383259479063</v>
+        <v>15.23383353633731</v>
       </c>
       <c r="F727" t="n">
         <v>340806</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196617126465</v>
+        <v>16.32196426391602</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55386179102265</v>
+        <v>16.55385985657521</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26059279475697</v>
+        <v>15.26059101143806</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005552987071</v>
+        <v>15.43005372674877</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -15032,16 +15032,16 @@
         <v>45385</v>
       </c>
       <c r="B731" t="n">
-        <v>16.13466262817383</v>
+        <v>16.1346607208252</v>
       </c>
       <c r="C731" t="n">
-        <v>16.6162951241437</v>
+        <v>16.6162931598592</v>
       </c>
       <c r="D731" t="n">
-        <v>16.01871482767124</v>
+        <v>16.0187129340293</v>
       </c>
       <c r="E731" t="n">
-        <v>16.53602274278301</v>
+        <v>16.53602078798786</v>
       </c>
       <c r="F731" t="n">
         <v>812246</v>
@@ -15072,16 +15072,16 @@
         <v>45387</v>
       </c>
       <c r="B733" t="n">
-        <v>15.78681564331055</v>
+        <v>15.78681755065918</v>
       </c>
       <c r="C733" t="n">
-        <v>16.24169062721705</v>
+        <v>16.24169258952326</v>
       </c>
       <c r="D733" t="n">
-        <v>15.71546302092809</v>
+        <v>15.71546491965596</v>
       </c>
       <c r="E733" t="n">
-        <v>15.84033055814591</v>
+        <v>15.84033247196016</v>
       </c>
       <c r="F733" t="n">
         <v>540022</v>
@@ -15152,16 +15152,16 @@
         <v>45393</v>
       </c>
       <c r="B737" t="n">
-        <v>14.95510768890381</v>
+        <v>14.95510864257812</v>
       </c>
       <c r="C737" t="n">
-        <v>15.2060023283815</v>
+        <v>15.20600329805515</v>
       </c>
       <c r="D737" t="n">
-        <v>14.75797708255414</v>
+        <v>14.75797802365761</v>
       </c>
       <c r="E737" t="n">
-        <v>15.02679276770881</v>
+        <v>15.02679372595442</v>
       </c>
       <c r="F737" t="n">
         <v>214129</v>
@@ -15172,16 +15172,16 @@
         <v>45394</v>
       </c>
       <c r="B738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="C738" t="n">
-        <v>15.1432798316879</v>
+        <v>15.14327886659233</v>
       </c>
       <c r="D738" t="n">
-        <v>14.76693785469897</v>
+        <v>14.76693691358803</v>
       </c>
       <c r="E738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="F738" t="n">
         <v>376247</v>
@@ -15232,16 +15232,16 @@
         <v>45399</v>
       </c>
       <c r="B741" t="n">
-        <v>14.89238548278809</v>
+        <v>14.89238452911377</v>
       </c>
       <c r="C741" t="n">
-        <v>15.08951610245028</v>
+        <v>15.08951513615217</v>
       </c>
       <c r="D741" t="n">
-        <v>14.74901621159323</v>
+        <v>14.74901526709996</v>
       </c>
       <c r="E741" t="n">
-        <v>14.9103065296753</v>
+        <v>14.91030557485336</v>
       </c>
       <c r="F741" t="n">
         <v>190430</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051544189453</v>
+        <v>15.77051448822021</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804172020233</v>
+        <v>15.87804076002569</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847665051934</v>
+        <v>15.09847573748455</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808098634539</v>
+        <v>15.18808006789204</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15312,16 +15312,16 @@
         <v>45405</v>
       </c>
       <c r="B745" t="n">
-        <v>16.22750091552734</v>
+        <v>16.22750282287598</v>
       </c>
       <c r="C745" t="n">
-        <v>16.44255346205622</v>
+        <v>16.44255539468171</v>
       </c>
       <c r="D745" t="n">
-        <v>15.59130424676128</v>
+        <v>15.59130607933261</v>
       </c>
       <c r="E745" t="n">
-        <v>15.77051470220201</v>
+        <v>15.77051655583738</v>
       </c>
       <c r="F745" t="n">
         <v>640292</v>
@@ -15372,16 +15372,16 @@
         <v>45408</v>
       </c>
       <c r="B748" t="n">
-        <v>16.41567420959473</v>
+        <v>16.41567230224609</v>
       </c>
       <c r="C748" t="n">
-        <v>16.74721403793184</v>
+        <v>16.74721209206137</v>
       </c>
       <c r="D748" t="n">
-        <v>16.14685939194446</v>
+        <v>16.14685751582961</v>
       </c>
       <c r="E748" t="n">
-        <v>16.48735839992738</v>
+        <v>16.48735648424971</v>
       </c>
       <c r="F748" t="n">
         <v>618795</v>
@@ -15452,16 +15452,16 @@
         <v>45415</v>
       </c>
       <c r="B752" t="n">
-        <v>16.26334190368652</v>
+        <v>16.26334381103516</v>
       </c>
       <c r="C752" t="n">
-        <v>16.45151331718664</v>
+        <v>16.45151524660383</v>
       </c>
       <c r="D752" t="n">
-        <v>16.17373757813992</v>
+        <v>16.17373947497985</v>
       </c>
       <c r="E752" t="n">
-        <v>16.23646078524195</v>
+        <v>16.23646268943799</v>
       </c>
       <c r="F752" t="n">
         <v>303682</v>
@@ -15712,16 +15712,16 @@
         <v>45434</v>
       </c>
       <c r="B765" t="n">
-        <v>14.92822647094727</v>
+        <v>14.92822742462158</v>
       </c>
       <c r="C765" t="n">
-        <v>15.1074369265467</v>
+        <v>15.10743789166969</v>
       </c>
       <c r="D765" t="n">
-        <v>14.82966027231904</v>
+        <v>14.82966121969655</v>
       </c>
       <c r="E765" t="n">
-        <v>15.0626338645983</v>
+        <v>15.06263482685909</v>
       </c>
       <c r="F765" t="n">
         <v>235522</v>
@@ -15732,16 +15732,16 @@
         <v>45435</v>
       </c>
       <c r="B766" t="n">
-        <v>14.87446403503418</v>
+        <v>14.87446308135986</v>
       </c>
       <c r="C766" t="n">
-        <v>14.94614822065114</v>
+        <v>14.9461472623808</v>
       </c>
       <c r="D766" t="n">
-        <v>14.73109566380025</v>
+        <v>14.73109471931798</v>
       </c>
       <c r="E766" t="n">
-        <v>14.93718724940046</v>
+        <v>14.93718629170465</v>
       </c>
       <c r="F766" t="n">
         <v>226398</v>
@@ -15752,16 +15752,16 @@
         <v>45436</v>
       </c>
       <c r="B767" t="n">
-        <v>14.81173896789551</v>
+        <v>14.81173992156982</v>
       </c>
       <c r="C767" t="n">
-        <v>14.9013441941292</v>
+        <v>14.90134515357287</v>
       </c>
       <c r="D767" t="n">
-        <v>14.74005478690855</v>
+        <v>14.74005573596738</v>
       </c>
       <c r="E767" t="n">
-        <v>14.78485695197687</v>
+        <v>14.78485790392035</v>
       </c>
       <c r="F767" t="n">
         <v>297600</v>
@@ -15772,16 +15772,16 @@
         <v>45439</v>
       </c>
       <c r="B768" t="n">
-        <v>14.9371862411499</v>
+        <v>14.93718719482422</v>
       </c>
       <c r="C768" t="n">
-        <v>15.0715945281578</v>
+        <v>15.0715954904135</v>
       </c>
       <c r="D768" t="n">
-        <v>14.7400547440095</v>
+        <v>14.74005568509783</v>
       </c>
       <c r="E768" t="n">
-        <v>14.90134415076074</v>
+        <v>14.90134510214669</v>
       </c>
       <c r="F768" t="n">
         <v>153938</v>
@@ -15812,16 +15812,16 @@
         <v>45441</v>
       </c>
       <c r="B770" t="n">
-        <v>14.77589797973633</v>
+        <v>14.77589702606201</v>
       </c>
       <c r="C770" t="n">
-        <v>14.84758216607118</v>
+        <v>14.84758120777018</v>
       </c>
       <c r="D770" t="n">
-        <v>14.52500422366149</v>
+        <v>14.5250032861805</v>
       </c>
       <c r="E770" t="n">
-        <v>14.84758216607118</v>
+        <v>14.84758120777018</v>
       </c>
       <c r="F770" t="n">
         <v>377820</v>
@@ -15852,16 +15852,16 @@
         <v>45446</v>
       </c>
       <c r="B772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="C772" t="n">
-        <v>15.36729159771533</v>
+        <v>15.36729261993504</v>
       </c>
       <c r="D772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="E772" t="n">
-        <v>14.69525198216746</v>
+        <v>14.69525295968364</v>
       </c>
       <c r="F772" t="n">
         <v>2218059</v>
@@ -15872,16 +15872,16 @@
         <v>45447</v>
       </c>
       <c r="B773" t="n">
-        <v>14.18450450897217</v>
+        <v>14.18450355529785</v>
       </c>
       <c r="C773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="D773" t="n">
-        <v>14.01425411633309</v>
+        <v>14.0142531741053</v>
       </c>
       <c r="E773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="F773" t="n">
         <v>553151</v>
@@ -15932,16 +15932,16 @@
         <v>45450</v>
       </c>
       <c r="B776" t="n">
-        <v>13.44077968597412</v>
+        <v>13.44078063964844</v>
       </c>
       <c r="C776" t="n">
-        <v>13.99633209818778</v>
+        <v>13.99633309128065</v>
       </c>
       <c r="D776" t="n">
-        <v>13.44077968597412</v>
+        <v>13.44078063964844</v>
       </c>
       <c r="E776" t="n">
-        <v>13.9784110526325</v>
+        <v>13.9784120444538</v>
       </c>
       <c r="F776" t="n">
         <v>667347</v>
@@ -15992,16 +15992,16 @@
         <v>45455</v>
       </c>
       <c r="B779" t="n">
-        <v>13.15404319763184</v>
+        <v>13.15404415130615</v>
       </c>
       <c r="C779" t="n">
-        <v>13.61999039058967</v>
+        <v>13.61999137804538</v>
       </c>
       <c r="D779" t="n">
-        <v>13.02859677254798</v>
+        <v>13.02859771712737</v>
       </c>
       <c r="E779" t="n">
-        <v>13.42285888587674</v>
+        <v>13.42285985904032</v>
       </c>
       <c r="F779" t="n">
         <v>631798</v>
@@ -16012,16 +16012,16 @@
         <v>45456</v>
       </c>
       <c r="B780" t="n">
-        <v>13.01067447662354</v>
+        <v>13.01067543029785</v>
       </c>
       <c r="C780" t="n">
-        <v>13.26157000825715</v>
+        <v>13.26157098032195</v>
       </c>
       <c r="D780" t="n">
-        <v>13.01067447662354</v>
+        <v>13.01067543029785</v>
       </c>
       <c r="E780" t="n">
-        <v>13.15404283978727</v>
+        <v>13.1540438039704</v>
       </c>
       <c r="F780" t="n">
         <v>210250</v>
@@ -16032,16 +16032,16 @@
         <v>45457</v>
       </c>
       <c r="B781" t="n">
-        <v>13.07339954376221</v>
+        <v>13.07339859008789</v>
       </c>
       <c r="C781" t="n">
-        <v>13.27053105759112</v>
+        <v>13.27053008953652</v>
       </c>
       <c r="D781" t="n">
-        <v>12.9031491519523</v>
+        <v>12.90314821069736</v>
       </c>
       <c r="E781" t="n">
-        <v>13.06443857235778</v>
+        <v>13.06443761933714</v>
       </c>
       <c r="F781" t="n">
         <v>928770</v>
@@ -16152,16 +16152,16 @@
         <v>45467</v>
       </c>
       <c r="B787" t="n">
-        <v>13.18988704681396</v>
+        <v>13.18988609313965</v>
       </c>
       <c r="C787" t="n">
-        <v>13.23468921639855</v>
+        <v>13.23468825948488</v>
       </c>
       <c r="D787" t="n">
-        <v>12.90314939786458</v>
+        <v>12.90314846492238</v>
       </c>
       <c r="E787" t="n">
-        <v>12.90314939786458</v>
+        <v>12.90314846492238</v>
       </c>
       <c r="F787" t="n">
         <v>668186</v>
@@ -16212,16 +16212,16 @@
         <v>45470</v>
       </c>
       <c r="B790" t="n">
-        <v>13.1809253692627</v>
+        <v>13.18092441558838</v>
       </c>
       <c r="C790" t="n">
-        <v>13.26157052473157</v>
+        <v>13.26156956522237</v>
       </c>
       <c r="D790" t="n">
-        <v>12.83146452239273</v>
+        <v>12.83146359400282</v>
       </c>
       <c r="E790" t="n">
-        <v>12.90314870676636</v>
+        <v>12.90314777318991</v>
       </c>
       <c r="F790" t="n">
         <v>447659</v>
@@ -16272,16 +16272,16 @@
         <v>45475</v>
       </c>
       <c r="B793" t="n">
-        <v>13.29741287231445</v>
+        <v>13.29741382598877</v>
       </c>
       <c r="C793" t="n">
-        <v>13.5483066263438</v>
+        <v>13.54830759801191</v>
       </c>
       <c r="D793" t="n">
-        <v>13.27053085460948</v>
+        <v>13.27053180635585</v>
       </c>
       <c r="E793" t="n">
-        <v>13.36013608679751</v>
+        <v>13.36013704497026</v>
       </c>
       <c r="F793" t="n">
         <v>528404</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61103057861328</v>
+        <v>13.61102962493896</v>
       </c>
       <c r="C795" t="n">
-        <v>13.7006358097591</v>
+        <v>13.70063484980648</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766220877997</v>
+        <v>13.46766126515094</v>
       </c>
       <c r="E795" t="n">
-        <v>13.593108636287</v>
+        <v>13.59310768386841</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16332,16 +16332,16 @@
         <v>45478</v>
       </c>
       <c r="B796" t="n">
-        <v>13.54830551147461</v>
+        <v>13.54830646514893</v>
       </c>
       <c r="C796" t="n">
-        <v>13.8888053657699</v>
+        <v>13.88880634341223</v>
       </c>
       <c r="D796" t="n">
-        <v>13.27948983703096</v>
+        <v>13.27949077178316</v>
       </c>
       <c r="E796" t="n">
-        <v>13.87088521690404</v>
+        <v>13.87088619328496</v>
       </c>
       <c r="F796" t="n">
         <v>907063</v>
@@ -16392,16 +16392,16 @@
         <v>45483</v>
       </c>
       <c r="B799" t="n">
-        <v>13.63791179656982</v>
+        <v>13.63791084289551</v>
       </c>
       <c r="C799" t="n">
-        <v>13.78128016741929</v>
+        <v>13.78127920371949</v>
       </c>
       <c r="D799" t="n">
-        <v>13.56622850724222</v>
+        <v>13.56622755858058</v>
       </c>
       <c r="E799" t="n">
-        <v>13.71855695322121</v>
+        <v>13.71855599390753</v>
       </c>
       <c r="F799" t="n">
         <v>395437</v>
@@ -16572,16 +16572,16 @@
         <v>45496</v>
       </c>
       <c r="B808" t="n">
-        <v>13.75439834594727</v>
+        <v>13.75439739227295</v>
       </c>
       <c r="C808" t="n">
-        <v>13.94256978341871</v>
+        <v>13.94256881669735</v>
       </c>
       <c r="D808" t="n">
-        <v>13.66479400898589</v>
+        <v>13.66479306152438</v>
       </c>
       <c r="E808" t="n">
-        <v>13.8888066435836</v>
+        <v>13.88880568058996</v>
       </c>
       <c r="F808" t="n">
         <v>454685</v>
@@ -16752,16 +16752,16 @@
         <v>45509</v>
       </c>
       <c r="B817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770042419434</v>
       </c>
       <c r="C817" t="n">
-        <v>13.23468850107574</v>
+        <v>13.23468751329381</v>
       </c>
       <c r="D817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770042419434</v>
       </c>
       <c r="E817" t="n">
-        <v>13.04651706913838</v>
+        <v>13.04651609540078</v>
       </c>
       <c r="F817" t="n">
         <v>596040</v>
@@ -16952,16 +16952,16 @@
         <v>45523</v>
       </c>
       <c r="B827" t="n">
-        <v>12.33863544464111</v>
+        <v>12.33863639831543</v>
       </c>
       <c r="C827" t="n">
-        <v>12.44616171459386</v>
+        <v>12.44616267657907</v>
       </c>
       <c r="D827" t="n">
-        <v>12.03397857587205</v>
+        <v>12.03397950599891</v>
       </c>
       <c r="E827" t="n">
-        <v>12.28487230966474</v>
+        <v>12.28487325918361</v>
       </c>
       <c r="F827" t="n">
         <v>2509053</v>
@@ -16972,16 +16972,16 @@
         <v>45524</v>
       </c>
       <c r="B828" t="n">
-        <v>12.41031932830811</v>
+        <v>12.41032028198242</v>
       </c>
       <c r="C828" t="n">
-        <v>12.47304253623447</v>
+        <v>12.47304349472877</v>
       </c>
       <c r="D828" t="n">
-        <v>12.19526679353708</v>
+        <v>12.19526773068562</v>
       </c>
       <c r="E828" t="n">
-        <v>12.35655619461535</v>
+        <v>12.35655714415822</v>
       </c>
       <c r="F828" t="n">
         <v>514247</v>
@@ -17032,16 +17032,16 @@
         <v>45527</v>
       </c>
       <c r="B831" t="n">
-        <v>11.94437313079834</v>
+        <v>11.94437217712402</v>
       </c>
       <c r="C831" t="n">
-        <v>12.08774149884918</v>
+        <v>12.0877405337279</v>
       </c>
       <c r="D831" t="n">
-        <v>11.55907108971027</v>
+        <v>11.55907016679962</v>
       </c>
       <c r="E831" t="n">
-        <v>11.57699213571662</v>
+        <v>11.5769912113751</v>
       </c>
       <c r="F831" t="n">
         <v>1022098</v>
@@ -17092,16 +17092,16 @@
         <v>45532</v>
       </c>
       <c r="B834" t="n">
-        <v>11.9354133605957</v>
+        <v>11.93541240692139</v>
       </c>
       <c r="C834" t="n">
-        <v>12.21318913273821</v>
+        <v>12.2131881568688</v>
       </c>
       <c r="D834" t="n">
-        <v>11.89957126766782</v>
+        <v>11.89957031685739</v>
       </c>
       <c r="E834" t="n">
-        <v>12.21318913273821</v>
+        <v>12.2131881568688</v>
       </c>
       <c r="F834" t="n">
         <v>555773</v>
@@ -17152,16 +17152,16 @@
         <v>45537</v>
       </c>
       <c r="B837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="C837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="D837" t="n">
-        <v>11.42466408609577</v>
+        <v>11.42466315363044</v>
       </c>
       <c r="E837" t="n">
-        <v>11.56803156298606</v>
+        <v>11.56803061881927</v>
       </c>
       <c r="F837" t="n">
         <v>1157790</v>
@@ -17192,16 +17192,16 @@
         <v>45539</v>
       </c>
       <c r="B839" t="n">
-        <v>11.6486759185791</v>
+        <v>11.64867687225342</v>
       </c>
       <c r="C839" t="n">
-        <v>11.85476749250614</v>
+        <v>11.85476846305313</v>
       </c>
       <c r="D839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="E839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="F839" t="n">
         <v>552941</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37986087799072</v>
+        <v>11.37985992431641</v>
       </c>
       <c r="C844" t="n">
-        <v>11.5232292491703</v>
+        <v>11.52322828348119</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089990674344</v>
+        <v>11.37089895382008</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882184923801</v>
+        <v>11.38882089481273</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17472,16 +17472,16 @@
         <v>45559</v>
       </c>
       <c r="B853" t="n">
-        <v>10.69886112213135</v>
+        <v>10.69886016845703</v>
       </c>
       <c r="C853" t="n">
-        <v>10.95871674311883</v>
+        <v>10.95871576628153</v>
       </c>
       <c r="D853" t="n">
-        <v>10.68990104697512</v>
+        <v>10.68990009409949</v>
       </c>
       <c r="E853" t="n">
-        <v>10.91391367904632</v>
+        <v>10.91391270620266</v>
       </c>
       <c r="F853" t="n">
         <v>530081</v>
@@ -17492,16 +17492,16 @@
         <v>45560</v>
       </c>
       <c r="B854" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420413970947</v>
       </c>
       <c r="C854" t="n">
-        <v>10.76158418418261</v>
+        <v>10.76158517156435</v>
       </c>
       <c r="D854" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420413970947</v>
       </c>
       <c r="E854" t="n">
-        <v>10.6988609706855</v>
+        <v>10.69886195231235</v>
       </c>
       <c r="F854" t="n">
         <v>618376</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276828765869</v>
+        <v>10.49276924133301</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029456250169</v>
+        <v>10.60029552594893</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212402957499</v>
+        <v>10.41212497591966</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900604633429</v>
+        <v>10.43900699512222</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -26615,13 +26615,13 @@
         <v>5.5</v>
       </c>
       <c r="C1310" t="n">
-        <v>6.12</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="D1310" t="n">
         <v>5.5</v>
       </c>
       <c r="E1310" t="n">
-        <v>5.93</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="F1310" t="n">
         <v>1636800</v>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1310"/>
+  <dimension ref="A1:F1311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44316</v>
       </c>
       <c r="B2" t="n">
-        <v>13.41818714141846</v>
+        <v>13.41818904876709</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80970269086723</v>
+        <v>14.80970479601495</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42424710659606</v>
+        <v>12.42424887265957</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50707558152642</v>
+        <v>12.50707735936371</v>
       </c>
       <c r="F2" t="n">
         <v>8063577</v>
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2856616973877</v>
+        <v>13.28566265106201</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83010549167658</v>
+        <v>12.83010641265006</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970157623291</v>
+        <v>13.16970348358154</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606525790047</v>
+        <v>13.76606725161959</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404462813815</v>
+        <v>13.00404651149493</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42646959612849</v>
+        <v>13.42647154066446</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -552,16 +552,16 @@
         <v>44323</v>
       </c>
       <c r="B7" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C7" t="n">
-        <v>12.85495546357991</v>
+        <v>12.85495449619264</v>
       </c>
       <c r="D7" t="n">
-        <v>12.26687350523842</v>
+        <v>12.26687258210669</v>
       </c>
       <c r="E7" t="n">
-        <v>12.71414713079874</v>
+        <v>12.71414617400787</v>
       </c>
       <c r="F7" t="n">
         <v>847960</v>
@@ -572,16 +572,16 @@
         <v>44326</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51535797119141</v>
+        <v>12.51535987854004</v>
       </c>
       <c r="C8" t="n">
-        <v>12.80525721254009</v>
+        <v>12.80525916406956</v>
       </c>
       <c r="D8" t="n">
-        <v>12.51535797119141</v>
+        <v>12.51535987854004</v>
       </c>
       <c r="E8" t="n">
-        <v>12.67273232059268</v>
+        <v>12.67273425192526</v>
       </c>
       <c r="F8" t="n">
         <v>633995</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="C9" t="n">
-        <v>12.5484900443603</v>
+        <v>12.5484881179382</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717612770272</v>
+        <v>12.21717425214336</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162181854248</v>
+        <v>13.4016227722168</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172308737706</v>
+        <v>13.93172407877397</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566158371901</v>
+        <v>12.46566247078936</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273319802321</v>
+        <v>12.672734099829</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.8323278427124</v>
+        <v>13.83232879638672</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677127946689</v>
+        <v>14.19677225826788</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101396313917</v>
+        <v>13.50101489397095</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56727723835638</v>
+        <v>13.5672781737567</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.8488941192627</v>
+        <v>13.84889507293701</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24646964076982</v>
+        <v>14.24647062182232</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323799870598</v>
+        <v>13.68323894097274</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222817448053</v>
+        <v>14.12222914697741</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253096774176</v>
       </c>
       <c r="D16" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838856883414</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253096774176</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.26909637451172</v>
+        <v>13.2690954208374</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182412334521</v>
+        <v>13.64182314288226</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253117759573</v>
+        <v>13.25253022511198</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162211069491</v>
+        <v>13.40162114749573</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970157623291</v>
+        <v>13.16970348358154</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131738938882</v>
+        <v>13.45131933752346</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313638072602</v>
+        <v>13.15313828567554</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707509440325</v>
+        <v>13.32707702454405</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889442443848</v>
+        <v>13.02889537811279</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879284288401</v>
+        <v>13.31879381777798</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263114417541</v>
+        <v>12.96263209299946</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111657277715</v>
+        <v>13.21111753978956</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980365753174</v>
+        <v>12.87980270385742</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111758778895</v>
+        <v>13.21111660958277</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6147530126286</v>
+        <v>12.61475207857974</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374322126546</v>
+        <v>13.05374225471193</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253009796143</v>
+        <v>13.25253105163574</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707514235259</v>
+        <v>13.32707610139129</v>
       </c>
       <c r="D24" t="n">
-        <v>12.8466719883597</v>
+        <v>12.84667291282778</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061070266274</v>
+        <v>13.02061163964774</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -952,16 +952,16 @@
         <v>44354</v>
       </c>
       <c r="B27" t="n">
-        <v>12.76384449005127</v>
+        <v>12.76384353637695</v>
       </c>
       <c r="C27" t="n">
-        <v>13.07859155159272</v>
+        <v>13.07859057440149</v>
       </c>
       <c r="D27" t="n">
-        <v>12.69758120620529</v>
+        <v>12.69758025748196</v>
       </c>
       <c r="E27" t="n">
-        <v>12.86323816756367</v>
+        <v>12.86323720646297</v>
       </c>
       <c r="F27" t="n">
         <v>662018</v>
@@ -972,16 +972,16 @@
         <v>44355</v>
       </c>
       <c r="B28" t="n">
-        <v>12.44909572601318</v>
+        <v>12.4490966796875</v>
       </c>
       <c r="C28" t="n">
-        <v>12.73899413986676</v>
+        <v>12.73899511574901</v>
       </c>
       <c r="D28" t="n">
-        <v>12.42424710032951</v>
+        <v>12.42424805210027</v>
       </c>
       <c r="E28" t="n">
-        <v>12.69758031850796</v>
+        <v>12.69758129121766</v>
       </c>
       <c r="F28" t="n">
         <v>727440</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667205810547</v>
+        <v>12.84667301177979</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555932114021</v>
+        <v>12.75556026805076</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1052,16 +1052,16 @@
         <v>44361</v>
       </c>
       <c r="B32" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C32" t="n">
-        <v>13.00404556253863</v>
+        <v>13.00404458393173</v>
       </c>
       <c r="D32" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="E32" t="n">
-        <v>12.9377839435789</v>
+        <v>12.93778296995845</v>
       </c>
       <c r="F32" t="n">
         <v>396641</v>
@@ -1072,16 +1072,16 @@
         <v>44362</v>
       </c>
       <c r="B33" t="n">
-        <v>12.74727725982666</v>
+        <v>12.74727821350098</v>
       </c>
       <c r="C33" t="n">
-        <v>12.93778367526155</v>
+        <v>12.9377846431884</v>
       </c>
       <c r="D33" t="n">
-        <v>12.70586343677157</v>
+        <v>12.70586438734755</v>
       </c>
       <c r="E33" t="n">
-        <v>12.82182313993105</v>
+        <v>12.82182409918244</v>
       </c>
       <c r="F33" t="n">
         <v>320579</v>
@@ -1092,16 +1092,16 @@
         <v>44363</v>
       </c>
       <c r="B34" t="n">
-        <v>12.77212810516357</v>
+        <v>12.77212619781494</v>
       </c>
       <c r="C34" t="n">
-        <v>12.88808698873982</v>
+        <v>12.88808506407426</v>
       </c>
       <c r="D34" t="n">
-        <v>12.67273441973917</v>
+        <v>12.67273252723367</v>
       </c>
       <c r="E34" t="n">
-        <v>12.83010713086614</v>
+        <v>12.83010521485911</v>
       </c>
       <c r="F34" t="n">
         <v>265902</v>
@@ -1132,16 +1132,16 @@
         <v>44365</v>
       </c>
       <c r="B36" t="n">
-        <v>12.65616607666016</v>
+        <v>12.65616512298584</v>
       </c>
       <c r="C36" t="n">
-        <v>12.74727715234998</v>
+        <v>12.74727619181022</v>
       </c>
       <c r="D36" t="n">
-        <v>12.54848980475637</v>
+        <v>12.54848885919573</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6396008804462</v>
+        <v>12.63959992802011</v>
       </c>
       <c r="F36" t="n">
         <v>365879</v>
@@ -1152,16 +1152,16 @@
         <v>44368</v>
       </c>
       <c r="B37" t="n">
-        <v>12.51535797119141</v>
+        <v>12.51535987854004</v>
       </c>
       <c r="C37" t="n">
-        <v>12.76384339184927</v>
+        <v>12.76384533706724</v>
       </c>
       <c r="D37" t="n">
-        <v>12.48222591603358</v>
+        <v>12.48222781833286</v>
       </c>
       <c r="E37" t="n">
-        <v>12.7141461412835</v>
+        <v>12.71414807892758</v>
       </c>
       <c r="F37" t="n">
         <v>462485</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657028198242</v>
+        <v>12.31657218933105</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424654557586</v>
+        <v>12.42424846959927</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293266081497</v>
+        <v>12.09293453353099</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596394810812</v>
+        <v>12.41596587084889</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1252,16 +1252,16 @@
         <v>44375</v>
       </c>
       <c r="B42" t="n">
-        <v>12.17576313018799</v>
+        <v>12.17576122283936</v>
       </c>
       <c r="C42" t="n">
-        <v>12.42424858453798</v>
+        <v>12.42424663826379</v>
       </c>
       <c r="D42" t="n">
-        <v>12.13434930388187</v>
+        <v>12.13434740302076</v>
       </c>
       <c r="E42" t="n">
-        <v>12.34142009975465</v>
+        <v>12.34141816645564</v>
       </c>
       <c r="F42" t="n">
         <v>425086</v>
@@ -1272,16 +1272,16 @@
         <v>44376</v>
       </c>
       <c r="B43" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C43" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="D43" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="E43" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="F43" t="n">
         <v>538653</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43252913940544</v>
+        <v>12.43253006532078</v>
       </c>
       <c r="E44" t="n">
-        <v>12.5899034842721</v>
+        <v>12.58990442190792</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1312,16 +1312,16 @@
         <v>44378</v>
       </c>
       <c r="B45" t="n">
-        <v>12.51535797119141</v>
+        <v>12.51535987854004</v>
       </c>
       <c r="C45" t="n">
-        <v>12.90465088150065</v>
+        <v>12.90465284817777</v>
       </c>
       <c r="D45" t="n">
-        <v>12.51535797119141</v>
+        <v>12.51535987854004</v>
       </c>
       <c r="E45" t="n">
-        <v>12.77212598955324</v>
+        <v>12.77212793603348</v>
       </c>
       <c r="F45" t="n">
         <v>412760</v>
@@ -1332,16 +1332,16 @@
         <v>44379</v>
       </c>
       <c r="B46" t="n">
-        <v>12.49051189422607</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="C46" t="n">
-        <v>12.74727913280265</v>
+        <v>12.7472762129657</v>
       </c>
       <c r="D46" t="n">
-        <v>12.49051189422607</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51536052457858</v>
+        <v>12.51535765786391</v>
       </c>
       <c r="F46" t="n">
         <v>443206</v>
@@ -1352,16 +1352,16 @@
         <v>44382</v>
       </c>
       <c r="B47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="C47" t="n">
-        <v>12.64788378432207</v>
+        <v>12.64788281412843</v>
       </c>
       <c r="D47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="E47" t="n">
-        <v>12.55677270642959</v>
+        <v>12.5567717432249</v>
       </c>
       <c r="F47" t="n">
         <v>186679</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C48" t="n">
-        <v>12.4987937073347</v>
+        <v>12.49879274279404</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25859086647818</v>
+        <v>12.25858992047414</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394424802878</v>
+        <v>12.47394328540577</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54848903140645</v>
+        <v>12.54849097075757</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768154358154</v>
+        <v>12.40768346117107</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C50" t="n">
-        <v>12.65616529667426</v>
+        <v>12.6561672526666</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576132133995</v>
+        <v>12.17576320308654</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25858979381817</v>
+        <v>12.25859168836578</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1452,16 +1452,16 @@
         <v>44390</v>
       </c>
       <c r="B52" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C52" t="n">
-        <v>12.30828606118626</v>
+        <v>12.30828800250133</v>
       </c>
       <c r="D52" t="n">
-        <v>12.05151888146321</v>
+        <v>12.05152078227987</v>
       </c>
       <c r="E52" t="n">
-        <v>12.2171749922247</v>
+        <v>12.21717691916935</v>
       </c>
       <c r="F52" t="n">
         <v>433935</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121822357178</v>
+        <v>12.10121726989746</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030916512651</v>
+        <v>12.25030819970261</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495311737061</v>
+        <v>12.03495407104492</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172113487724</v>
+        <v>12.29172210889838</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010532434145</v>
+        <v>12.01010627604678</v>
       </c>
       <c r="E54" t="n">
-        <v>12.10121639529459</v>
+        <v>12.10121735421974</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1552,16 +1552,16 @@
         <v>44397</v>
       </c>
       <c r="B57" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C57" t="n">
-        <v>11.86929761452057</v>
+        <v>11.86929859769704</v>
       </c>
       <c r="D57" t="n">
-        <v>11.37232758142605</v>
+        <v>11.37232852343671</v>
       </c>
       <c r="E57" t="n">
-        <v>11.67879203295168</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="F57" t="n">
         <v>1030110</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303318023682</v>
       </c>
       <c r="C58" t="n">
-        <v>11.67050888395185</v>
+        <v>11.67050787058301</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303318023682</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970139416144</v>
+        <v>11.52970039301913</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C59" t="n">
-        <v>11.3474776588947</v>
+        <v>11.34747966894678</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172035776503</v>
+        <v>10.65172224457312</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414446317129</v>
+        <v>11.07414642480609</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879135131836</v>
+        <v>10.85879230499268</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525663025563</v>
+        <v>11.16525761084529</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798385706797</v>
+        <v>10.71798479837585</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76768027708593</v>
+        <v>10.76768122275841</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697288513184</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697288513184</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707366412172</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707366412172</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.29778099060059</v>
+        <v>11.29778003692627</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47172053283982</v>
+        <v>11.47171956448282</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05757983553765</v>
+        <v>11.05757890213932</v>
       </c>
       <c r="E62" t="n">
-        <v>11.1818221279454</v>
+        <v>11.18182118405946</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747791290283</v>
       </c>
       <c r="C63" t="n">
-        <v>11.51313582037561</v>
+        <v>11.51313485277901</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495313710418</v>
+        <v>11.2149521945677</v>
       </c>
       <c r="E63" t="n">
-        <v>11.3640448948254</v>
+        <v>11.36404393975882</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1692,16 +1692,16 @@
         <v>44406</v>
       </c>
       <c r="B64" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C64" t="n">
-        <v>11.45515649173092</v>
+        <v>11.45515552548068</v>
       </c>
       <c r="D64" t="n">
-        <v>11.01616629311581</v>
+        <v>11.01616536389469</v>
       </c>
       <c r="E64" t="n">
-        <v>11.33919678522236</v>
+        <v>11.3391958287534</v>
       </c>
       <c r="F64" t="n">
         <v>449738</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727731662251</v>
+        <v>11.92727827162325</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61253027092469</v>
+        <v>11.61253120072406</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61253027092469</v>
+        <v>11.61253120072406</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273265838623</v>
+        <v>11.85273170471191</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556114342346</v>
+        <v>11.93556018308474</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030846651876</v>
+        <v>11.43030754683281</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727854457107</v>
+        <v>11.92727758489877</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="C69" t="n">
-        <v>11.66222697699479</v>
+        <v>11.6622279694364</v>
       </c>
       <c r="D69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768109665717</v>
+        <v>11.58768208275502</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1852,16 +1852,16 @@
         <v>44418</v>
       </c>
       <c r="B72" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727661132812</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2503090271009</v>
+        <v>12.2503070680949</v>
       </c>
       <c r="D72" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727661132812</v>
       </c>
       <c r="E72" t="n">
-        <v>12.05152082987733</v>
+        <v>12.05151890266051</v>
       </c>
       <c r="F72" t="n">
         <v>351025</v>
@@ -1932,16 +1932,16 @@
         <v>44424</v>
       </c>
       <c r="B76" t="n">
-        <v>11.74505519866943</v>
+        <v>11.74505710601807</v>
       </c>
       <c r="C76" t="n">
-        <v>12.50707585310151</v>
+        <v>12.50707788419916</v>
       </c>
       <c r="D76" t="n">
-        <v>11.40545869373233</v>
+        <v>11.40546054593189</v>
       </c>
       <c r="E76" t="n">
-        <v>12.50707585310151</v>
+        <v>12.50707788419916</v>
       </c>
       <c r="F76" t="n">
         <v>788964</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495311737061</v>
+        <v>12.03495407104492</v>
       </c>
       <c r="C78" t="n">
-        <v>12.3331357876011</v>
+        <v>12.33313676490402</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313531685193</v>
+        <v>11.51313622917634</v>
       </c>
       <c r="E78" t="n">
-        <v>11.57939776260494</v>
+        <v>11.57939868018012</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -1992,16 +1992,16 @@
         <v>44427</v>
       </c>
       <c r="B79" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C79" t="n">
-        <v>12.19232719973869</v>
+        <v>12.19232912276424</v>
       </c>
       <c r="D79" t="n">
-        <v>11.54626628734149</v>
+        <v>11.54626810846757</v>
       </c>
       <c r="E79" t="n">
-        <v>11.59596353665541</v>
+        <v>11.59596536561996</v>
       </c>
       <c r="F79" t="n">
         <v>301405</v>
@@ -2012,16 +2012,16 @@
         <v>44428</v>
       </c>
       <c r="B80" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C80" t="n">
-        <v>12.12606392326314</v>
+        <v>12.12606583583737</v>
       </c>
       <c r="D80" t="n">
-        <v>11.87758017320638</v>
+        <v>11.8775820465887</v>
       </c>
       <c r="E80" t="n">
-        <v>12.05980231112949</v>
+        <v>12.05980421325266</v>
       </c>
       <c r="F80" t="n">
         <v>324055</v>
@@ -2032,16 +2032,16 @@
         <v>44431</v>
       </c>
       <c r="B81" t="n">
-        <v>11.9935417175293</v>
+        <v>11.99353981018066</v>
       </c>
       <c r="C81" t="n">
-        <v>12.39111730446284</v>
+        <v>12.39111533388724</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95212705644652</v>
+        <v>11.95212515568412</v>
       </c>
       <c r="E81" t="n">
-        <v>12.21717772512593</v>
+        <v>12.21717578221218</v>
       </c>
       <c r="F81" t="n">
         <v>344599</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C82" t="n">
-        <v>12.32485367100113</v>
+        <v>12.32485465783526</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990296160259</v>
+        <v>11.76990390400258</v>
       </c>
       <c r="E82" t="n">
-        <v>12.0101057931323</v>
+        <v>12.010106754765</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010503212249</v>
+        <v>12.01010599913494</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071053374038</v>
+        <v>11.91071149274992</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2112,16 +2112,16 @@
         <v>44435</v>
       </c>
       <c r="B85" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C85" t="n">
-        <v>11.8941472165949</v>
+        <v>11.89414625217492</v>
       </c>
       <c r="D85" t="n">
-        <v>11.35576331665388</v>
+        <v>11.355762395888</v>
       </c>
       <c r="E85" t="n">
-        <v>11.87758201902993</v>
+        <v>11.87758105595312</v>
       </c>
       <c r="F85" t="n">
         <v>370831</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="D87" t="n">
-        <v>11.388893311891</v>
+        <v>11.38889235890981</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141761779785</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737827423737</v>
+        <v>11.6373773109646</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576244764404</v>
+        <v>11.35576150768174</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313597332352</v>
+        <v>11.51313502033478</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465034484863</v>
+        <v>11.26465129852295</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596339448043</v>
+        <v>11.59596437620398</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838706918552</v>
+        <v>11.19838801724993</v>
       </c>
       <c r="E90" t="n">
-        <v>11.3557614126931</v>
+        <v>11.35576237408096</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2232,16 +2232,16 @@
         <v>44445</v>
       </c>
       <c r="B91" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="C91" t="n">
-        <v>11.7284905443865</v>
+        <v>11.72848958118911</v>
       </c>
       <c r="D91" t="n">
-        <v>11.2646525182764</v>
+        <v>11.26465159317151</v>
       </c>
       <c r="E91" t="n">
-        <v>11.3474801725371</v>
+        <v>11.34747924063002</v>
       </c>
       <c r="F91" t="n">
         <v>145382</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566040039062</v>
+        <v>11.64566135406494</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67050902600049</v>
+        <v>11.67050998170969</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010503811302</v>
+        <v>11.19010595448147</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313550669932</v>
+        <v>11.51313644952104</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111708543731</v>
+        <v>11.57111611650414</v>
       </c>
       <c r="D93" t="n">
-        <v>11.181824111812</v>
+        <v>11.18182317547715</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141982678859</v>
+        <v>11.52141886201694</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909470007334</v>
+        <v>11.62909565647244</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38060928692969</v>
+        <v>11.38061022289286</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485240958699</v>
+        <v>11.50485335576816</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444805906109</v>
+        <v>11.84444903317125</v>
       </c>
       <c r="D97" t="n">
-        <v>11.58768004846393</v>
+        <v>11.587681001457</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364057366772</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192317112123</v>
+        <v>11.71192413433229</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313500704049</v>
+        <v>11.51313595390284</v>
       </c>
       <c r="E98" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424831381274</v>
+        <v>11.60424734210526</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606642626268</v>
+        <v>11.30606547952412</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596571476166</v>
+        <v>11.59596474374774</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C100" t="n">
-        <v>11.64565927206673</v>
+        <v>11.6456602402011</v>
       </c>
       <c r="D100" t="n">
-        <v>11.05757907307569</v>
+        <v>11.0575799923214</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26464982353394</v>
+        <v>11.26465075999399</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2432,16 +2432,16 @@
         <v>44460</v>
       </c>
       <c r="B101" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C101" t="n">
-        <v>11.67879203295168</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="D101" t="n">
-        <v>11.33919635684255</v>
+        <v>11.33919729610883</v>
       </c>
       <c r="E101" t="n">
-        <v>11.48000385327967</v>
+        <v>11.48000480420954</v>
       </c>
       <c r="F101" t="n">
         <v>218811</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677116615927</v>
+        <v>11.73677298006055</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76161979111983</v>
+        <v>11.76162160886144</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2532,16 +2532,16 @@
         <v>44467</v>
       </c>
       <c r="B106" t="n">
-        <v>11.94384288787842</v>
+        <v>11.9438419342041</v>
       </c>
       <c r="C106" t="n">
-        <v>12.09293381741185</v>
+        <v>12.09293285183314</v>
       </c>
       <c r="D106" t="n">
-        <v>11.74505553661453</v>
+        <v>11.74505459881269</v>
       </c>
       <c r="E106" t="n">
-        <v>11.86101440876628</v>
+        <v>11.86101346170553</v>
       </c>
       <c r="F106" t="n">
         <v>282337</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C109" t="n">
-        <v>11.7616195880132</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889188438319</v>
+        <v>11.38889282102754</v>
       </c>
       <c r="E109" t="n">
-        <v>11.7616195880132</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545794086782</v>
+        <v>11.40545885919616</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596350798623</v>
+        <v>11.59596444165342</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010650652883</v>
+        <v>12.01010550156678</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444954366927</v>
+        <v>11.84444855256879</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2652,16 +2652,16 @@
         <v>44475</v>
       </c>
       <c r="B112" t="n">
-        <v>11.3806095123291</v>
+        <v>11.38061046600342</v>
       </c>
       <c r="C112" t="n">
-        <v>11.62909493039415</v>
+        <v>11.62909590489109</v>
       </c>
       <c r="D112" t="n">
-        <v>11.18182217648222</v>
+        <v>11.18182311349852</v>
       </c>
       <c r="E112" t="n">
-        <v>11.4054581373527</v>
+        <v>11.40545909310929</v>
       </c>
       <c r="F112" t="n">
         <v>433409</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.40545749664307</v>
+        <v>11.4054594039917</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939702986614</v>
+        <v>11.57939896630289</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38060887301535</v>
+        <v>11.38061077620852</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43858954959396</v>
+        <v>11.43859146248331</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677096348174</v>
+        <v>11.73677192873634</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687256307056</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687256307056</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667140960693</v>
+        <v>12.02667236328125</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495400789619</v>
+        <v>12.03495496222729</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768121771099</v>
+        <v>11.58768213657487</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768121771099</v>
+        <v>11.58768213657487</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2752,16 +2752,16 @@
         <v>44483</v>
       </c>
       <c r="B117" t="n">
-        <v>11.9355583190918</v>
+        <v>11.93555927276611</v>
       </c>
       <c r="C117" t="n">
-        <v>12.02666938142166</v>
+        <v>12.02667034237593</v>
       </c>
       <c r="D117" t="n">
-        <v>11.81959863391363</v>
+        <v>11.81959957832254</v>
       </c>
       <c r="E117" t="n">
-        <v>12.01838678452919</v>
+        <v>12.01838774482166</v>
       </c>
       <c r="F117" t="n">
         <v>96605</v>
@@ -2772,16 +2772,16 @@
         <v>44484</v>
       </c>
       <c r="B118" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C118" t="n">
-        <v>12.09293270111084</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="D118" t="n">
-        <v>11.84444811888313</v>
+        <v>11.84444998703971</v>
       </c>
       <c r="E118" t="n">
-        <v>11.92727659034935</v>
+        <v>11.92727847157</v>
       </c>
       <c r="F118" t="n">
         <v>256632</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22546032458287</v>
+        <v>12.22545936636416</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727844663413</v>
+        <v>11.92727751178659</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465198439289</v>
+        <v>12.08465103721058</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D122" t="n">
-        <v>11.41374053834268</v>
+        <v>11.4137414573379</v>
       </c>
       <c r="E122" t="n">
-        <v>11.67879114707672</v>
+        <v>11.67879208741291</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030834197998</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81960031587073</v>
+        <v>11.81960130202524</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212553603579</v>
+        <v>11.13212646483165</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76162046503097</v>
+        <v>11.76162144634801</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="C124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172147956523</v>
+        <v>11.47171971844675</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141873349808</v>
+        <v>11.52141696475016</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C125" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D125" t="n">
-        <v>11.84444821601161</v>
+        <v>11.8444491374672</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030714700461</v>
+        <v>12.25030810003457</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980225021978</v>
+        <v>12.05980324204109</v>
       </c>
       <c r="D127" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010500115686</v>
+        <v>12.01010598889097</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030834197998</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72848924057554</v>
+        <v>11.72849021912831</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.43030834197998</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596434275382</v>
+        <v>11.59596531024953</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -2992,16 +2992,16 @@
         <v>44501</v>
       </c>
       <c r="B129" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C129" t="n">
-        <v>11.6539434064713</v>
+        <v>11.65394437180921</v>
       </c>
       <c r="D129" t="n">
-        <v>11.36404498332293</v>
+        <v>11.36404592464751</v>
       </c>
       <c r="E129" t="n">
-        <v>11.50485331193106</v>
+        <v>11.5048542649193</v>
       </c>
       <c r="F129" t="n">
         <v>1267357</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727589213198</v>
+        <v>11.92727688367788</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899289029898</v>
+        <v>11.09899381298753</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81959880231217</v>
+        <v>11.81959978490659</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020779632061</v>
+        <v>11.72020683994276</v>
       </c>
       <c r="D133" t="n">
-        <v>11.38061125592101</v>
+        <v>11.3806103272545</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859194463979</v>
+        <v>11.43859101124201</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374176025391</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374176025391</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929665495666</v>
+        <v>11.86929758022087</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05151879151981</v>
+        <v>12.05151973098904</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232845306396</v>
+        <v>12.19232749938965</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374310913982</v>
+        <v>12.23374215222609</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465134587198</v>
+        <v>12.08465040062008</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374310913982</v>
+        <v>12.23374215222609</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576306753439</v>
+        <v>12.17576211321089</v>
       </c>
       <c r="D138" t="n">
-        <v>11.68707642451825</v>
+        <v>11.6870755084975</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242981810988</v>
+        <v>11.90242888520996</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49051027684238</v>
+        <v>12.49050931294096</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293390702631</v>
+        <v>12.09293297380614</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485414956155</v>
+        <v>12.32485319844393</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.98748111724854</v>
+        <v>12.98748016357422</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374357221301</v>
+        <v>13.05374261367302</v>
       </c>
       <c r="D142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="E142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3332,16 +3332,16 @@
         <v>44526</v>
       </c>
       <c r="B146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="D146" t="n">
-        <v>12.05152012297789</v>
+        <v>12.05151921605237</v>
       </c>
       <c r="E146" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="F146" t="n">
         <v>386739</v>
@@ -3352,16 +3352,16 @@
         <v>44529</v>
       </c>
       <c r="B147" t="n">
-        <v>12.67273330688477</v>
+        <v>12.67273235321045</v>
       </c>
       <c r="C147" t="n">
-        <v>12.98748036584146</v>
+        <v>12.98747938848116</v>
       </c>
       <c r="D147" t="n">
-        <v>12.357984583586</v>
+        <v>12.35798365359779</v>
       </c>
       <c r="E147" t="n">
-        <v>12.75556012254167</v>
+        <v>12.75555916263431</v>
       </c>
       <c r="F147" t="n">
         <v>340279</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455081939697</v>
+        <v>12.37455177307129</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818860682649</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90242939089549</v>
+        <v>11.90243030818464</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818860682649</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3392,16 +3392,16 @@
         <v>44531</v>
       </c>
       <c r="B149" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C149" t="n">
-        <v>12.58990445376748</v>
+        <v>12.58990549663439</v>
       </c>
       <c r="D149" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E149" t="n">
-        <v>12.37455024571821</v>
+        <v>12.37455127074656</v>
       </c>
       <c r="F149" t="n">
         <v>554877</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808502197266</v>
+        <v>11.24808597564697</v>
       </c>
       <c r="C150" t="n">
-        <v>11.8196000891662</v>
+        <v>11.8196010912967</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182257433274</v>
+        <v>11.18182352238896</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333764152628</v>
+        <v>11.75333863803869</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.76990222930908</v>
+        <v>11.7699031829834</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212436699063</v>
+        <v>11.95212533542978</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485245244207</v>
+        <v>11.50485338464032</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970107706609</v>
+        <v>11.52970201127774</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374176025391</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626664787403</v>
+        <v>12.36626761187925</v>
       </c>
       <c r="D154" t="n">
-        <v>11.89414527942817</v>
+        <v>11.89414620662944</v>
       </c>
       <c r="E154" t="n">
-        <v>12.01010497218126</v>
+        <v>12.0101059084221</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C155" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99353913300503</v>
+        <v>11.99354006605936</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22545852214389</v>
+        <v>12.22545947324071</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000400543213</v>
+        <v>12.30000495910645</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626728482618</v>
+        <v>12.36626824363818</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778185948322</v>
+        <v>12.11778279902904</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668727818206</v>
+        <v>12.2668737329261</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192295369397</v>
+        <v>12.53192392863263</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606402270097</v>
+        <v>12.12606496606526</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909531371949</v>
+        <v>12.44909628221446</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3592,16 +3592,16 @@
         <v>44545</v>
       </c>
       <c r="B159" t="n">
-        <v>12.54848861694336</v>
+        <v>12.54849052429199</v>
       </c>
       <c r="C159" t="n">
-        <v>12.54848861694336</v>
+        <v>12.54849052429199</v>
       </c>
       <c r="D159" t="n">
-        <v>12.05151863065941</v>
+        <v>12.05152046246946</v>
       </c>
       <c r="E159" t="n">
-        <v>12.32485266402669</v>
+        <v>12.32485453738304</v>
       </c>
       <c r="F159" t="n">
         <v>233455</v>
@@ -3612,16 +3612,16 @@
         <v>44546</v>
       </c>
       <c r="B160" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252944946289</v>
       </c>
       <c r="C160" t="n">
-        <v>12.56505530473681</v>
+        <v>12.56505434089677</v>
       </c>
       <c r="D160" t="n">
-        <v>12.31657153032308</v>
+        <v>12.31657058554373</v>
       </c>
       <c r="E160" t="n">
-        <v>12.54849010812237</v>
+        <v>12.54848914555302</v>
       </c>
       <c r="F160" t="n">
         <v>252523</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606590270996</v>
+        <v>12.94606685638428</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606590270996</v>
+        <v>12.94606685638428</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25859030161671</v>
+        <v>12.25859120464801</v>
       </c>
       <c r="E161" t="n">
-        <v>12.4242472534353</v>
+        <v>12.42424816866975</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202602386475</v>
+        <v>13.06202411651611</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16142053736261</v>
+        <v>13.16141861550016</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273389729204</v>
+        <v>12.67273204678879</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273389729204</v>
+        <v>12.67273204678879</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.72242832183838</v>
+        <v>12.7224292755127</v>
       </c>
       <c r="C163" t="n">
-        <v>13.06202397044703</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737771446318</v>
+        <v>12.45737864826929</v>
       </c>
       <c r="E163" t="n">
-        <v>13.06202397044703</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="C164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43253111290434</v>
+        <v>12.43252926346614</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72243039191747</v>
+        <v>12.72242849935444</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495625873149</v>
+        <v>12.85495434892158</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020834813482</v>
+        <v>12.54020648508576</v>
       </c>
       <c r="E165" t="n">
-        <v>12.81354160008474</v>
+        <v>12.81353969642765</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828770746268</v>
+        <v>13.12828866415499</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384342158722</v>
+        <v>12.76384435172153</v>
       </c>
       <c r="E166" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838856883414</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970248796023</v>
       </c>
       <c r="D167" t="n">
-        <v>12.9212161070132</v>
+        <v>12.92121704861566</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C168" t="n">
-        <v>13.3767722965285</v>
+        <v>13.37677327132853</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04545923371708</v>
+        <v>13.04546018437347</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970248796023</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970092773438</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98748125957582</v>
+        <v>12.98747925372556</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970092773438</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92950057063265</v>
+        <v>12.92949857373721</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3852,16 +3852,16 @@
         <v>44566</v>
       </c>
       <c r="B172" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="C172" t="n">
-        <v>12.39939937049056</v>
+        <v>12.39939835219506</v>
       </c>
       <c r="D172" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="E172" t="n">
-        <v>12.35798554336021</v>
+        <v>12.35798452846581</v>
       </c>
       <c r="F172" t="n">
         <v>223973</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616633728321</v>
+        <v>11.83616537688813</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47172120414394</v>
+        <v>11.47172027332021</v>
       </c>
       <c r="E173" t="n">
-        <v>11.63737815849552</v>
+        <v>11.63737721423026</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.69535827636719</v>
+        <v>11.69535732269287</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78646935368979</v>
+        <v>11.78646839258601</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657009304013</v>
+        <v>11.49656915557559</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333812849712</v>
+        <v>11.75333717009495</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586274131581</v>
+        <v>11.88586369832469</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202396798849</v>
+        <v>11.42202488765067</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55454885627004</v>
+        <v>11.55454978660266</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727741252527</v>
+        <v>11.92727644473738</v>
       </c>
       <c r="D176" t="n">
-        <v>11.61253036429669</v>
+        <v>11.6125294220476</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444893534948</v>
+        <v>11.84444797428235</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838848776734</v>
+        <v>12.01838751258662</v>
       </c>
       <c r="D177" t="n">
-        <v>11.6456607565618</v>
+        <v>11.64565981162448</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818648647726</v>
+        <v>11.77818553078671</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071108497109</v>
+        <v>11.91071205965744</v>
       </c>
       <c r="D178" t="n">
-        <v>11.59596404465037</v>
+        <v>11.5959649935801</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273123562185</v>
+        <v>11.85273220556355</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131771091337</v>
+        <v>11.81131675253453</v>
       </c>
       <c r="D179" t="n">
-        <v>11.5297018871209</v>
+        <v>11.52970095159257</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67050938293163</v>
+        <v>11.67050843597808</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4032,16 +4032,16 @@
         <v>44579</v>
       </c>
       <c r="B181" t="n">
-        <v>11.49656963348389</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="C181" t="n">
-        <v>11.72020643480869</v>
+        <v>11.72020837925999</v>
       </c>
       <c r="D181" t="n">
-        <v>11.46343840961558</v>
+        <v>11.46344031146755</v>
       </c>
       <c r="E181" t="n">
-        <v>11.57939810924015</v>
+        <v>11.57940003033051</v>
       </c>
       <c r="F181" t="n">
         <v>311203</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010707905902</v>
+        <v>12.01010609902517</v>
       </c>
       <c r="D182" t="n">
-        <v>11.56283342445056</v>
+        <v>11.56283248091458</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596548433874</v>
+        <v>11.59596453809916</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4072,16 +4072,16 @@
         <v>44581</v>
       </c>
       <c r="B183" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C183" t="n">
-        <v>12.21717689082265</v>
+        <v>12.21717590021027</v>
       </c>
       <c r="D183" t="n">
-        <v>11.67051039209914</v>
+        <v>11.67050944581244</v>
       </c>
       <c r="E183" t="n">
-        <v>11.67051039209914</v>
+        <v>11.67050944581244</v>
       </c>
       <c r="F183" t="n">
         <v>1415690</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434939104088</v>
+        <v>12.13434840086876</v>
       </c>
       <c r="D184" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84445010830247</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111740112305</v>
+        <v>11.57111644744873</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101586536</v>
+        <v>11.86101488779268</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828891183915</v>
+        <v>11.48828796499143</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707711968628</v>
+        <v>11.68707615645473</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4152,16 +4152,16 @@
         <v>44587</v>
       </c>
       <c r="B187" t="n">
-        <v>11.01616668701172</v>
+        <v>11.0161657333374</v>
       </c>
       <c r="C187" t="n">
-        <v>12.08465187904177</v>
+        <v>12.08465083286823</v>
       </c>
       <c r="D187" t="n">
-        <v>10.90020697635688</v>
+        <v>10.90020603272125</v>
       </c>
       <c r="E187" t="n">
-        <v>11.88586451692297</v>
+        <v>11.88586348795854</v>
       </c>
       <c r="F187" t="n">
         <v>1763028</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747791290283</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374131522813</v>
+        <v>11.41374035598493</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242823980222</v>
+        <v>11.08242730840351</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818227449497</v>
+        <v>11.18182180519759</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4192,16 +4192,16 @@
         <v>44589</v>
       </c>
       <c r="B189" t="n">
-        <v>11.53798484802246</v>
+        <v>11.53798389434814</v>
       </c>
       <c r="C189" t="n">
-        <v>11.57939867182719</v>
+        <v>11.57939771472981</v>
       </c>
       <c r="D189" t="n">
-        <v>11.14040847794448</v>
+        <v>11.14040755713192</v>
       </c>
       <c r="E189" t="n">
-        <v>11.36404529013473</v>
+        <v>11.36404435083742</v>
       </c>
       <c r="F189" t="n">
         <v>538653</v>
@@ -4232,16 +4232,16 @@
         <v>44593</v>
       </c>
       <c r="B191" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C191" t="n">
-        <v>11.81960133103929</v>
+        <v>11.81960037266376</v>
       </c>
       <c r="D191" t="n">
-        <v>11.61253136845066</v>
+        <v>11.61253042686511</v>
       </c>
       <c r="E191" t="n">
-        <v>11.6870764218352</v>
+        <v>11.68707547420526</v>
       </c>
       <c r="F191" t="n">
         <v>160869</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586476707715</v>
+        <v>11.88586379718157</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626822667756</v>
+        <v>11.54626728449331</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788407835838</v>
+        <v>11.82788311319406</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4292,16 +4292,16 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C194" t="n">
-        <v>11.62909605149376</v>
+        <v>11.6290950705716</v>
       </c>
       <c r="D194" t="n">
-        <v>11.19838845129467</v>
+        <v>11.19838750670299</v>
       </c>
       <c r="E194" t="n">
-        <v>11.48828771756607</v>
+        <v>11.48828674852119</v>
       </c>
       <c r="F194" t="n">
         <v>381155</v>
@@ -4312,16 +4312,16 @@
         <v>44599</v>
       </c>
       <c r="B195" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C195" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="D195" t="n">
-        <v>11.15697512067666</v>
+        <v>11.15697421602923</v>
       </c>
       <c r="E195" t="n">
-        <v>11.43859180099198</v>
+        <v>11.43859087351007</v>
       </c>
       <c r="F195" t="n">
         <v>474179</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697377917189</v>
+        <v>11.97697476418123</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970103411845</v>
+        <v>11.52970198234322</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364057366772</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444808959961</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313503672479</v>
+        <v>11.51313596372292</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596350798623</v>
+        <v>11.59596444165342</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788276672363</v>
+        <v>11.82788372039795</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84444974984068</v>
       </c>
       <c r="D198" t="n">
-        <v>11.6290954224653</v>
+        <v>11.62909636011153</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84444974984068</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444909778491</v>
+        <v>11.8444500711998</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313601670912</v>
+        <v>11.51313696289563</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253052355157</v>
+        <v>11.61253147790664</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.68707656860352</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84445010830247</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081411316933</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081411316933</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.69535827636719</v>
+        <v>11.69535732269287</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81959961507706</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394362074808</v>
+        <v>11.65394267045083</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81959961507706</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4472,16 +4472,16 @@
         <v>44609</v>
       </c>
       <c r="B203" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C203" t="n">
-        <v>11.98525829971548</v>
+        <v>11.9852573279079</v>
       </c>
       <c r="D203" t="n">
-        <v>11.6870764218352</v>
+        <v>11.68707547420526</v>
       </c>
       <c r="E203" t="n">
-        <v>11.69535902061768</v>
+        <v>11.69535807231616</v>
       </c>
       <c r="F203" t="n">
         <v>1539476</v>
@@ -4492,16 +4492,16 @@
         <v>44610</v>
       </c>
       <c r="B204" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727661132812</v>
       </c>
       <c r="C204" t="n">
-        <v>11.92727851867676</v>
+        <v>11.92727661132812</v>
       </c>
       <c r="D204" t="n">
-        <v>11.48000486688096</v>
+        <v>11.48000303105801</v>
       </c>
       <c r="E204" t="n">
-        <v>11.76162154896194</v>
+        <v>11.76161966810431</v>
       </c>
       <c r="F204" t="n">
         <v>336065</v>
@@ -4512,16 +4512,16 @@
         <v>44613</v>
       </c>
       <c r="B205" t="n">
-        <v>11.49656963348389</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="C205" t="n">
-        <v>11.92727720811385</v>
+        <v>11.92727918691941</v>
       </c>
       <c r="D205" t="n">
-        <v>11.49656963348389</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="E205" t="n">
-        <v>11.92727720811385</v>
+        <v>11.92727918691941</v>
       </c>
       <c r="F205" t="n">
         <v>449843</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899398228799</v>
+        <v>11.91899301517222</v>
       </c>
       <c r="D207" t="n">
-        <v>11.54626708325345</v>
+        <v>11.54626614638101</v>
       </c>
       <c r="E207" t="n">
-        <v>11.54626708325345</v>
+        <v>11.54626614638101</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4592,16 +4592,16 @@
         <v>44617</v>
       </c>
       <c r="B209" t="n">
-        <v>11.9935417175293</v>
+        <v>11.99353981018066</v>
       </c>
       <c r="C209" t="n">
-        <v>12.31657307815881</v>
+        <v>12.31657111943808</v>
       </c>
       <c r="D209" t="n">
-        <v>11.81960213819239</v>
+        <v>11.8196002585056</v>
       </c>
       <c r="E209" t="n">
-        <v>12.0929354062199</v>
+        <v>12.09293348306456</v>
       </c>
       <c r="F209" t="n">
         <v>373254</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687400817871</v>
       </c>
       <c r="D210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.010106267532</v>
       </c>
       <c r="E210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.010106267532</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="C212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000549162855</v>
+        <v>12.30000366426548</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586448620852</v>
+        <v>12.70586259854859</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.73899364471436</v>
+        <v>12.73899459838867</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202410170427</v>
+        <v>13.06202507956149</v>
       </c>
       <c r="D213" t="n">
-        <v>12.10949875793673</v>
+        <v>12.10949966448541</v>
       </c>
       <c r="E213" t="n">
-        <v>12.84667157327227</v>
+        <v>12.84667253500764</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.15919589996338</v>
+        <v>12.1591968536377</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697337862279</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="D214" t="n">
-        <v>12.14263070507846</v>
+        <v>12.14263165745353</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697337862279</v>
+        <v>12.79697438231949</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081293822948</v>
+        <v>12.44081102833779</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293382504164</v>
+        <v>12.09293196855574</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576230420604</v>
+        <v>12.17576043500445</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="C216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424583435059</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919710767578</v>
+        <v>12.15919524101725</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111568429664</v>
+        <v>12.39111378203438</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071128845215</v>
+        <v>11.91071224212646</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45737856768</v>
+        <v>12.45737956512522</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990296160259</v>
+        <v>11.76990390400258</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081253950964</v>
+        <v>12.44081353562843</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242726892965</v>
+        <v>11.90242825840982</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242726892965</v>
+        <v>11.90242825840982</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141761779785</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303523023652</v>
+        <v>11.80303425325166</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515612194091</v>
+        <v>11.45515517375141</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626719808914</v>
+        <v>11.546266242358</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4832,16 +4832,16 @@
         <v>44637</v>
       </c>
       <c r="B221" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C221" t="n">
-        <v>11.80303516535357</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="D221" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E221" t="n">
-        <v>11.80303516535357</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="F221" t="n">
         <v>333116</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222763061523</v>
+        <v>11.66222667694092</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444979431419</v>
+        <v>11.84444882573873</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404575689492</v>
+        <v>11.36404482760432</v>
       </c>
       <c r="E222" t="n">
-        <v>11.53798532192695</v>
+        <v>11.5379843784125</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333690643311</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475251478082</v>
+        <v>11.79475155774609</v>
       </c>
       <c r="D224" t="n">
-        <v>11.57939830768957</v>
+        <v>11.57939736812883</v>
       </c>
       <c r="E224" t="n">
-        <v>11.67879198099791</v>
+        <v>11.6787910333723</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10949925876433</v>
+        <v>12.10950024971806</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495338152774</v>
+        <v>12.03495436638118</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78646924618382</v>
+        <v>11.78647021483374</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030753839741</v>
+        <v>11.43030847777682</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535816969225</v>
+        <v>11.69535913085437</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -4972,16 +4972,16 @@
         <v>44648</v>
       </c>
       <c r="B228" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C228" t="n">
-        <v>11.76990407400221</v>
+        <v>11.76990311965631</v>
       </c>
       <c r="D228" t="n">
-        <v>11.52970288411256</v>
+        <v>11.52970194924304</v>
       </c>
       <c r="E228" t="n">
-        <v>11.65394436236309</v>
+        <v>11.65394341741962</v>
       </c>
       <c r="F228" t="n">
         <v>221866</v>
@@ -4992,16 +4992,16 @@
         <v>44649</v>
       </c>
       <c r="B229" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="C229" t="n">
-        <v>12.17576306473914</v>
+        <v>12.17576207748474</v>
       </c>
       <c r="D229" t="n">
-        <v>11.76162147521973</v>
+        <v>11.76162052154541</v>
       </c>
       <c r="E229" t="n">
-        <v>11.83616736077534</v>
+        <v>11.83616640105658</v>
       </c>
       <c r="F229" t="n">
         <v>841955</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C230" t="n">
-        <v>11.89414467191917</v>
+        <v>11.89414566071079</v>
       </c>
       <c r="D230" t="n">
-        <v>11.3557608871619</v>
+        <v>11.35576183119625</v>
       </c>
       <c r="E230" t="n">
-        <v>11.8444474255145</v>
+        <v>11.84444841017465</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374206542969</v>
+        <v>11.41374111175537</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283300077933</v>
+        <v>11.56283203464774</v>
       </c>
       <c r="D231" t="n">
-        <v>11.2315199035769</v>
+        <v>11.23151896512815</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283300077933</v>
+        <v>11.56283203464774</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374206542969</v>
+        <v>11.41374111175537</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909628595667</v>
+        <v>11.62909531428845</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636853149702</v>
+        <v>11.25636759097204</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313657711016</v>
+        <v>11.51313561513094</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283080544925</v>
+        <v>11.56283176669787</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919486097004</v>
+        <v>11.33919580362721</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41373989840614</v>
+        <v>11.41374084726044</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364124298096</v>
+        <v>10.88364028930664</v>
       </c>
       <c r="C236" t="n">
-        <v>11.0741459970064</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="D236" t="n">
-        <v>10.833943988813</v>
+        <v>10.83394303949338</v>
       </c>
       <c r="E236" t="n">
-        <v>11.0741459970064</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192485809326</v>
+        <v>10.89192295074463</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303594445944</v>
+        <v>10.98303402115581</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313665503474</v>
+        <v>10.69313478249707</v>
       </c>
       <c r="E237" t="n">
-        <v>10.93333868565203</v>
+        <v>10.93333677105118</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5172,16 +5172,16 @@
         <v>44662</v>
       </c>
       <c r="B238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="C238" t="n">
-        <v>11.07414542638119</v>
+        <v>11.07414640045497</v>
       </c>
       <c r="D238" t="n">
-        <v>10.80909480476127</v>
+        <v>10.80909575552138</v>
       </c>
       <c r="E238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="F238" t="n">
         <v>406860</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798324584961</v>
+        <v>10.71798419952393</v>
       </c>
       <c r="C239" t="n">
-        <v>11.0078824801347</v>
+        <v>11.00788345960393</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798324584961</v>
+        <v>10.71798419952393</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333660610241</v>
+        <v>10.93333757893863</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5212,16 +5212,16 @@
         <v>44664</v>
       </c>
       <c r="B240" t="n">
-        <v>10.8090934753418</v>
+        <v>10.80909538269043</v>
       </c>
       <c r="C240" t="n">
-        <v>10.89192194044294</v>
+        <v>10.8919238624073</v>
       </c>
       <c r="D240" t="n">
-        <v>10.65171997416924</v>
+        <v>10.6517218537481</v>
       </c>
       <c r="E240" t="n">
-        <v>10.81737607220064</v>
+        <v>10.81737798101081</v>
       </c>
       <c r="F240" t="n">
         <v>281389</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000366210938</v>
+        <v>10.66000461578369</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566060926712</v>
+        <v>10.82566157776158</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000366210938</v>
+        <v>10.66000461578369</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566060926712</v>
+        <v>10.82566157776158</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C242" t="n">
-        <v>11.03272981304382</v>
+        <v>11.03273176734258</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172035776503</v>
+        <v>10.65172224457312</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000295492215</v>
+        <v>10.66000484319739</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C243" t="n">
-        <v>10.92505355348844</v>
+        <v>10.9250554887138</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000295492215</v>
+        <v>10.66000484319739</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081126744788</v>
+        <v>10.80081318066541</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5312,16 +5312,16 @@
         <v>44673</v>
       </c>
       <c r="B245" t="n">
-        <v>10.23758029937744</v>
+        <v>10.23757934570312</v>
       </c>
       <c r="C245" t="n">
-        <v>10.64343930093843</v>
+        <v>10.64343830945661</v>
       </c>
       <c r="D245" t="n">
-        <v>10.23758029937744</v>
+        <v>10.23757934570312</v>
       </c>
       <c r="E245" t="n">
-        <v>10.64343930093843</v>
+        <v>10.64343830945661</v>
       </c>
       <c r="F245" t="n">
         <v>624092</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434661865234</v>
+        <v>10.49434757232666</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919607588605</v>
+        <v>10.51919703181856</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707386403591</v>
+        <v>10.04707477706429</v>
       </c>
       <c r="E246" t="n">
-        <v>10.1547501297465</v>
+        <v>10.15475105255997</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394432067871</v>
+        <v>10.83394336700439</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525741688146</v>
+        <v>11.16525643404281</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576245087913</v>
+        <v>10.53576152345272</v>
       </c>
       <c r="E250" t="n">
-        <v>10.5688936772823</v>
+        <v>10.56889274693946</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434448242188</v>
+        <v>10.73434543609619</v>
       </c>
       <c r="C251" t="n">
-        <v>10.92543536845984</v>
+        <v>10.9254363391113</v>
       </c>
       <c r="D251" t="n">
-        <v>10.4103192818045</v>
+        <v>10.41032020669135</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389329081236</v>
+        <v>10.88389425777308</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5492,16 +5492,16 @@
         <v>44686</v>
       </c>
       <c r="B254" t="n">
-        <v>10.81742858886719</v>
+        <v>10.81742763519287</v>
       </c>
       <c r="C254" t="n">
-        <v>10.96697825439385</v>
+        <v>10.9669772875351</v>
       </c>
       <c r="D254" t="n">
-        <v>10.68449592383528</v>
+        <v>10.68449498188042</v>
       </c>
       <c r="E254" t="n">
-        <v>10.83404558936194</v>
+        <v>10.83404463422265</v>
       </c>
       <c r="F254" t="n">
         <v>391269</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340438842773</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C257" t="n">
-        <v>10.8838951433366</v>
+        <v>10.88389415417323</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340438842773</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727897723452</v>
+        <v>10.86727798958128</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5592,16 +5592,16 @@
         <v>44693</v>
       </c>
       <c r="B259" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C259" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="D259" t="n">
-        <v>10.36047010025277</v>
+        <v>10.36046917836759</v>
       </c>
       <c r="E259" t="n">
-        <v>10.5349448394823</v>
+        <v>10.53494390207218</v>
       </c>
       <c r="F259" t="n">
         <v>307094</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340446133011</v>
+        <v>10.49340261960133</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802904688768</v>
+        <v>10.61802718328567</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.10822010040283</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085310445568</v>
+        <v>11.34085213080912</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95867043133051</v>
+        <v>10.95866949049548</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806943360591</v>
+        <v>11.15806847565188</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5672,16 +5672,16 @@
         <v>44699</v>
       </c>
       <c r="B263" t="n">
-        <v>11.11652660369873</v>
+        <v>11.11652755737305</v>
       </c>
       <c r="C263" t="n">
-        <v>11.24945925299112</v>
+        <v>11.24946021806958</v>
       </c>
       <c r="D263" t="n">
-        <v>10.80911839143009</v>
+        <v>10.8091193187322</v>
       </c>
       <c r="E263" t="n">
-        <v>11.01682711672944</v>
+        <v>11.01682806185065</v>
       </c>
       <c r="F263" t="n">
         <v>416658</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.10822010040283</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423610356696</v>
+        <v>11.32423513134702</v>
       </c>
       <c r="D265" t="n">
-        <v>11.10822010040283</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100293652106</v>
+        <v>11.29100196715428</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190235137939</v>
+        <v>10.99190330505371</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="D268" t="n">
-        <v>10.89220202682084</v>
+        <v>10.892202971845</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="C269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="D269" t="n">
-        <v>10.8672769842127</v>
+        <v>10.86727791027506</v>
       </c>
       <c r="E269" t="n">
-        <v>11.0168266253622</v>
+        <v>11.01682756416854</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329200744629</v>
+        <v>11.08329296112061</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776671311801</v>
+        <v>11.25776768180519</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667501106889</v>
+        <v>11.06667596331338</v>
       </c>
       <c r="E270" t="n">
-        <v>11.1996084778941</v>
+        <v>11.199609441577</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776767730713</v>
+        <v>11.25776958465576</v>
       </c>
       <c r="C271" t="n">
-        <v>11.27438467510771</v>
+        <v>11.27438658527168</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160187295824</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160187295824</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085273742676</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085273742676</v>
       </c>
       <c r="D272" t="n">
-        <v>11.13314295164785</v>
+        <v>11.13314482406336</v>
       </c>
       <c r="E272" t="n">
-        <v>11.24945859561594</v>
+        <v>11.24946048759386</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="C274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="E274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712760925293</v>
+        <v>10.91712856292725</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24945923185963</v>
+        <v>11.24946021456504</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051061075688</v>
+        <v>10.90051156297961</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622690433039</v>
+        <v>11.21622788413276</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344429480254</v>
+        <v>11.03344331983751</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="E276" t="n">
-        <v>11.00851921397176</v>
+        <v>11.00851824120922</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D277" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250303440952</v>
+        <v>10.79250209732709</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5972,16 +5972,16 @@
         <v>44720</v>
       </c>
       <c r="B278" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588558197021</v>
       </c>
       <c r="C278" t="n">
-        <v>10.9752855183135</v>
+        <v>10.97528454699222</v>
       </c>
       <c r="D278" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588558197021</v>
       </c>
       <c r="E278" t="n">
-        <v>10.95866935379015</v>
+        <v>10.95866838393941</v>
       </c>
       <c r="F278" t="n">
         <v>141800</v>
@@ -6012,16 +6012,16 @@
         <v>44722</v>
       </c>
       <c r="B280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C280" t="n">
-        <v>10.65126248980645</v>
+        <v>10.65126151249989</v>
       </c>
       <c r="D280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="E280" t="n">
-        <v>10.63464548972945</v>
+        <v>10.63464451394758</v>
       </c>
       <c r="F280" t="n">
         <v>218179</v>
@@ -6032,16 +6032,16 @@
         <v>44725</v>
       </c>
       <c r="B281" t="n">
-        <v>10.25246238708496</v>
+        <v>10.25246143341064</v>
       </c>
       <c r="C281" t="n">
-        <v>10.47678728729483</v>
+        <v>10.47678631275402</v>
       </c>
       <c r="D281" t="n">
-        <v>10.18599522441408</v>
+        <v>10.18599427692247</v>
       </c>
       <c r="E281" t="n">
-        <v>10.38539587769526</v>
+        <v>10.3853949116556</v>
       </c>
       <c r="F281" t="n">
         <v>299930</v>
@@ -6052,16 +6052,16 @@
         <v>44726</v>
       </c>
       <c r="B282" t="n">
-        <v>10.21092224121094</v>
+        <v>10.21092128753662</v>
       </c>
       <c r="C282" t="n">
-        <v>10.46848033314689</v>
+        <v>10.4684793554173</v>
       </c>
       <c r="D282" t="n">
-        <v>10.10291298588943</v>
+        <v>10.10291204230291</v>
       </c>
       <c r="E282" t="n">
-        <v>10.46017224994199</v>
+        <v>10.46017127298836</v>
       </c>
       <c r="F282" t="n">
         <v>156655</v>
@@ -6072,16 +6072,16 @@
         <v>44727</v>
       </c>
       <c r="B283" t="n">
-        <v>10.29400444030762</v>
+        <v>10.2940034866333</v>
       </c>
       <c r="C283" t="n">
-        <v>10.36877885035474</v>
+        <v>10.36877788975305</v>
       </c>
       <c r="D283" t="n">
-        <v>10.16107095005616</v>
+        <v>10.16107000869729</v>
       </c>
       <c r="E283" t="n">
-        <v>10.29400444030762</v>
+        <v>10.2940034866333</v>
       </c>
       <c r="F283" t="n">
         <v>138113</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768669128418</v>
+        <v>10.1776876449585</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216142044539</v>
+        <v>10.35216239046842</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798720379124</v>
+        <v>10.07798814812347</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599477322573</v>
+        <v>10.18599572767854</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911821365356445</v>
+        <v>9.911819458007812</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21922960432357</v>
+        <v>10.21922763781985</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787196787138297</v>
+        <v>9.787194903771384</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783819131483</v>
+        <v>10.12783624239772</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6152,16 +6152,16 @@
         <v>44734</v>
       </c>
       <c r="B287" t="n">
-        <v>9.83704662322998</v>
+        <v>9.837045669555664</v>
       </c>
       <c r="C287" t="n">
-        <v>10.13614593484008</v>
+        <v>10.13614495216891</v>
       </c>
       <c r="D287" t="n">
-        <v>9.820429623815432</v>
+        <v>9.820428671752088</v>
       </c>
       <c r="E287" t="n">
-        <v>9.920129116108306</v>
+        <v>9.920128154379375</v>
       </c>
       <c r="F287" t="n">
         <v>227344</v>
@@ -6172,16 +6172,16 @@
         <v>44735</v>
       </c>
       <c r="B288" t="n">
-        <v>9.637645721435547</v>
+        <v>9.637646675109863</v>
       </c>
       <c r="C288" t="n">
-        <v>9.945053915591304</v>
+        <v>9.945054899684594</v>
       </c>
       <c r="D288" t="n">
-        <v>9.629337640027153</v>
+        <v>9.629338592879359</v>
       </c>
       <c r="E288" t="n">
-        <v>9.93674583418291</v>
+        <v>9.93674681745409</v>
       </c>
       <c r="F288" t="n">
         <v>565728</v>
@@ -6212,16 +6212,16 @@
         <v>44739</v>
       </c>
       <c r="B290" t="n">
-        <v>9.355165481567383</v>
+        <v>9.355164527893066</v>
       </c>
       <c r="C290" t="n">
-        <v>9.554564487251117</v>
+        <v>9.55456351324988</v>
       </c>
       <c r="D290" t="n">
-        <v>9.263773227214553</v>
+        <v>9.26377228285685</v>
       </c>
       <c r="E290" t="n">
-        <v>9.496407069975366</v>
+        <v>9.49640610190275</v>
       </c>
       <c r="F290" t="n">
         <v>312467</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496406309403417</v>
+        <v>9.496405321144287</v>
       </c>
       <c r="D291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488098226848217</v>
+        <v>9.488097239453682</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.07268238067627</v>
+        <v>9.072681427001953</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255465221448427</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="D292" t="n">
-        <v>8.939749709107998</v>
+        <v>8.93974876940689</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255465221448427</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.89820671081543</v>
+        <v>8.898207664489746</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039448285923172</v>
+        <v>9.039449254735196</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657265642254186</v>
+        <v>8.657266570105399</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823431464676691</v>
+        <v>8.823432410336896</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6312,16 +6312,16 @@
         <v>44746</v>
       </c>
       <c r="B295" t="n">
-        <v>9.222231864929199</v>
+        <v>9.222229957580566</v>
       </c>
       <c r="C295" t="n">
-        <v>9.297006275706005</v>
+        <v>9.297004352892476</v>
       </c>
       <c r="D295" t="n">
-        <v>8.873282388686833</v>
+        <v>8.873280553508183</v>
       </c>
       <c r="E295" t="n">
-        <v>8.972981881299734</v>
+        <v>8.972980025501164</v>
       </c>
       <c r="F295" t="n">
         <v>166874</v>
@@ -6372,16 +6372,16 @@
         <v>44749</v>
       </c>
       <c r="B298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="C298" t="n">
-        <v>9.355164883523981</v>
+        <v>9.355163898352176</v>
       </c>
       <c r="D298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="E298" t="n">
-        <v>9.230540304255577</v>
+        <v>9.230539332207711</v>
       </c>
       <c r="F298" t="n">
         <v>150966</v>
@@ -6412,16 +6412,16 @@
         <v>44753</v>
       </c>
       <c r="B300" t="n">
-        <v>8.840046882629395</v>
+        <v>8.840048789978027</v>
       </c>
       <c r="C300" t="n">
-        <v>8.964672270562733</v>
+        <v>8.964674204800824</v>
       </c>
       <c r="D300" t="n">
-        <v>8.798505643139169</v>
+        <v>8.798507541524769</v>
       </c>
       <c r="E300" t="n">
-        <v>8.889897037802729</v>
+        <v>8.889898955907146</v>
       </c>
       <c r="F300" t="n">
         <v>130423</v>
@@ -6472,16 +6472,16 @@
         <v>44756</v>
       </c>
       <c r="B303" t="n">
-        <v>8.499408721923828</v>
+        <v>8.499407768249512</v>
       </c>
       <c r="C303" t="n">
-        <v>8.565875057302616</v>
+        <v>8.565874096170459</v>
       </c>
       <c r="D303" t="n">
-        <v>8.349859049955773</v>
+        <v>8.349858113061646</v>
       </c>
       <c r="E303" t="n">
-        <v>8.358167133195233</v>
+        <v>8.358166195368899</v>
       </c>
       <c r="F303" t="n">
         <v>213754</v>
@@ -6492,16 +6492,16 @@
         <v>44757</v>
       </c>
       <c r="B304" t="n">
-        <v>8.499408721923828</v>
+        <v>8.499407768249512</v>
       </c>
       <c r="C304" t="n">
-        <v>8.582492058513093</v>
+        <v>8.58249109551643</v>
       </c>
       <c r="D304" t="n">
-        <v>8.424633468574021</v>
+        <v>8.424632523289844</v>
       </c>
       <c r="E304" t="n">
-        <v>8.54094997285268</v>
+        <v>8.540949014517237</v>
       </c>
       <c r="F304" t="n">
         <v>109458</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557563781738281</v>
+        <v>8.557564735412598</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673881088703297</v>
+        <v>8.673882055340277</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482789383720247</v>
+        <v>8.482790329061535</v>
       </c>
       <c r="E306" t="n">
-        <v>8.499406380352772</v>
+        <v>8.499407327545896</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864973068237305</v>
+        <v>8.864974975585938</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873281984958936</v>
+        <v>8.873283894095279</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615723930679971</v>
+        <v>8.615725784401254</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632340094660361</v>
+        <v>8.632341951956706</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6592,16 +6592,16 @@
         <v>44764</v>
       </c>
       <c r="B309" t="n">
-        <v>8.848357200622559</v>
+        <v>8.848356246948242</v>
       </c>
       <c r="C309" t="n">
-        <v>8.956364774306991</v>
+        <v>8.956363808991638</v>
       </c>
       <c r="D309" t="n">
-        <v>8.806815119817307</v>
+        <v>8.806814170620388</v>
       </c>
       <c r="E309" t="n">
-        <v>8.823431284354236</v>
+        <v>8.82343033336643</v>
       </c>
       <c r="F309" t="n">
         <v>116832</v>
@@ -6652,16 +6652,16 @@
         <v>44769</v>
       </c>
       <c r="B312" t="n">
-        <v>9.047758102416992</v>
+        <v>9.047757148742676</v>
       </c>
       <c r="C312" t="n">
-        <v>9.072682352209164</v>
+        <v>9.072681395907718</v>
       </c>
       <c r="D312" t="n">
-        <v>8.756966840859347</v>
+        <v>8.756965917835734</v>
       </c>
       <c r="E312" t="n">
-        <v>8.765274924123403</v>
+        <v>8.765274000224082</v>
       </c>
       <c r="F312" t="n">
         <v>161185</v>
@@ -6672,16 +6672,16 @@
         <v>44770</v>
       </c>
       <c r="B313" t="n">
-        <v>9.047758102416992</v>
+        <v>9.047757148742676</v>
       </c>
       <c r="C313" t="n">
-        <v>9.172381855572542</v>
+        <v>9.172380888762323</v>
       </c>
       <c r="D313" t="n">
-        <v>8.914824596534254</v>
+        <v>8.914823656871727</v>
       </c>
       <c r="E313" t="n">
-        <v>8.914824596534254</v>
+        <v>8.914823656871727</v>
       </c>
       <c r="F313" t="n">
         <v>129685</v>
@@ -6772,16 +6772,16 @@
         <v>44777</v>
       </c>
       <c r="B318" t="n">
-        <v>9.263772010803223</v>
+        <v>9.263771057128906</v>
       </c>
       <c r="C318" t="n">
-        <v>9.297006008784836</v>
+        <v>9.29700505168919</v>
       </c>
       <c r="D318" t="n">
-        <v>8.948056542560964</v>
+        <v>8.948055621388498</v>
       </c>
       <c r="E318" t="n">
-        <v>8.972981623681449</v>
+        <v>8.972980699943028</v>
       </c>
       <c r="F318" t="n">
         <v>175407</v>
@@ -6812,16 +6812,16 @@
         <v>44781</v>
       </c>
       <c r="B320" t="n">
-        <v>9.637645721435547</v>
+        <v>9.637646675109863</v>
       </c>
       <c r="C320" t="n">
-        <v>9.670879716531882</v>
+        <v>9.670880673494802</v>
       </c>
       <c r="D320" t="n">
-        <v>9.371779603784519</v>
+        <v>9.371780531150575</v>
       </c>
       <c r="E320" t="n">
-        <v>9.371779603784519</v>
+        <v>9.371780531150575</v>
       </c>
       <c r="F320" t="n">
         <v>274752</v>
@@ -6832,16 +6832,16 @@
         <v>44782</v>
       </c>
       <c r="B321" t="n">
-        <v>9.263772010803223</v>
+        <v>9.263771057128906</v>
       </c>
       <c r="C321" t="n">
-        <v>9.920128863139675</v>
+        <v>9.920127841895617</v>
       </c>
       <c r="D321" t="n">
-        <v>9.105914276682094</v>
+        <v>9.105913339258702</v>
       </c>
       <c r="E321" t="n">
-        <v>9.687496720388545</v>
+        <v>9.687495723093187</v>
       </c>
       <c r="F321" t="n">
         <v>480605</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513021469116211</v>
+        <v>9.513022422790527</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596104790081913</v>
+        <v>9.596105752085279</v>
       </c>
       <c r="D322" t="n">
-        <v>9.205614099747661</v>
+        <v>9.205615022604585</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288696585981958</v>
+        <v>9.288697517167847</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.770580291748047</v>
+        <v>9.770581245422363</v>
       </c>
       <c r="C324" t="n">
-        <v>9.86197170166864</v>
+        <v>9.861972664263373</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262965348279</v>
+        <v>9.654263907669241</v>
       </c>
       <c r="E324" t="n">
-        <v>9.82042962051198</v>
+        <v>9.820430579051925</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C327" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D327" t="n">
-        <v>10.302311126201</v>
+        <v>10.30231297394502</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847775780993</v>
+        <v>10.46847963535633</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494548797607</v>
+        <v>10.53494453430176</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75927040500311</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="D328" t="n">
-        <v>10.3521626550741</v>
+        <v>10.35216171794617</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75927040500311</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340438842773</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494563841447</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092205210854</v>
+        <v>10.21092112410713</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494563841447</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7012,16 +7012,16 @@
         <v>44795</v>
       </c>
       <c r="B330" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C330" t="n">
-        <v>10.54325324140318</v>
+        <v>10.54325227400702</v>
       </c>
       <c r="D330" t="n">
-        <v>10.21922966985091</v>
+        <v>10.21922873218552</v>
       </c>
       <c r="E330" t="n">
-        <v>10.47678774528968</v>
+        <v>10.47678678399206</v>
       </c>
       <c r="F330" t="n">
         <v>111565</v>
@@ -7052,16 +7052,16 @@
         <v>44797</v>
       </c>
       <c r="B332" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588558197021</v>
       </c>
       <c r="C332" t="n">
-        <v>10.8257366986775</v>
+        <v>10.82573574059141</v>
       </c>
       <c r="D332" t="n">
-        <v>10.3853958178368</v>
+        <v>10.38539489872122</v>
       </c>
       <c r="E332" t="n">
-        <v>10.3853958178368</v>
+        <v>10.38539489872122</v>
       </c>
       <c r="F332" t="n">
         <v>196055</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250144958496</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389380981785</v>
+        <v>10.88389284806778</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633575420836</v>
+        <v>10.62633481521728</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573640085461</v>
+        <v>10.82573544424359</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096035003662</v>
+        <v>10.75096130371094</v>
       </c>
       <c r="C334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="D334" t="n">
-        <v>10.3272365119659</v>
+        <v>10.32723742805339</v>
       </c>
       <c r="E334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7112,16 +7112,16 @@
         <v>44802</v>
       </c>
       <c r="B335" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="C335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75926859837071</v>
       </c>
       <c r="D335" t="n">
-        <v>10.56817865938468</v>
+        <v>10.56817771462318</v>
       </c>
       <c r="E335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75926859837071</v>
       </c>
       <c r="F335" t="n">
         <v>128948</v>
@@ -7132,16 +7132,16 @@
         <v>44803</v>
       </c>
       <c r="B336" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C336" t="n">
-        <v>10.79250323416921</v>
+        <v>10.79250224390311</v>
       </c>
       <c r="D336" t="n">
-        <v>10.31892916611842</v>
+        <v>10.3189282193051</v>
       </c>
       <c r="E336" t="n">
-        <v>10.70111182057445</v>
+        <v>10.70111083869397</v>
       </c>
       <c r="F336" t="n">
         <v>123575</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539600372314</v>
+        <v>10.38539505004883</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648690755074</v>
+        <v>10.57648593632885</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907867632044</v>
+        <v>10.26907773332736</v>
       </c>
       <c r="E337" t="n">
-        <v>10.4020121685439</v>
+        <v>10.40201121334375</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753715515137</v>
+        <v>10.22753810882568</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370380728989</v>
+        <v>10.39370477645853</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937891037603</v>
+        <v>10.16937985862734</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385364470204</v>
+        <v>10.34385460922237</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618656158447</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618656158447</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="D340" t="n">
-        <v>10.25246266602793</v>
+        <v>10.2524617502037</v>
       </c>
       <c r="E340" t="n">
-        <v>10.35216216064962</v>
+        <v>10.35216123591951</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7232,16 +7232,16 @@
         <v>44810</v>
       </c>
       <c r="B341" t="n">
-        <v>10.57648658752441</v>
+        <v>10.5764856338501</v>
       </c>
       <c r="C341" t="n">
-        <v>10.63464483210026</v>
+        <v>10.63464387318185</v>
       </c>
       <c r="D341" t="n">
-        <v>10.50171217863059</v>
+        <v>10.50171123169863</v>
       </c>
       <c r="E341" t="n">
-        <v>10.63464483210026</v>
+        <v>10.63464387318185</v>
       </c>
       <c r="F341" t="n">
         <v>83753</v>
@@ -7252,16 +7252,16 @@
         <v>44812</v>
       </c>
       <c r="B342" t="n">
-        <v>10.75927066802979</v>
+        <v>10.75926971435547</v>
       </c>
       <c r="C342" t="n">
-        <v>10.9088203381266</v>
+        <v>10.90881937119658</v>
       </c>
       <c r="D342" t="n">
-        <v>10.57648783065941</v>
+        <v>10.57648689318649</v>
       </c>
       <c r="E342" t="n">
-        <v>10.57648783065941</v>
+        <v>10.57648689318649</v>
       </c>
       <c r="F342" t="n">
         <v>294768</v>
@@ -7312,16 +7312,16 @@
         <v>44817</v>
       </c>
       <c r="B345" t="n">
-        <v>11.14145088195801</v>
+        <v>11.14145183563232</v>
       </c>
       <c r="C345" t="n">
-        <v>11.19960912051899</v>
+        <v>11.19961007917147</v>
       </c>
       <c r="D345" t="n">
-        <v>10.70111005210078</v>
+        <v>10.70111096808326</v>
       </c>
       <c r="E345" t="n">
-        <v>10.95866808497532</v>
+        <v>10.95866902300398</v>
       </c>
       <c r="F345" t="n">
         <v>335223</v>
@@ -7432,16 +7432,16 @@
         <v>44825</v>
       </c>
       <c r="B351" t="n">
-        <v>10.75927066802979</v>
+        <v>10.75926971435547</v>
       </c>
       <c r="C351" t="n">
-        <v>11.16637842791116</v>
+        <v>11.16637743815185</v>
       </c>
       <c r="D351" t="n">
-        <v>10.6761873324801</v>
+        <v>10.67618638617008</v>
       </c>
       <c r="E351" t="n">
-        <v>11.12483717750209</v>
+        <v>11.12483619142489</v>
       </c>
       <c r="F351" t="n">
         <v>359874</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85065950799402</v>
+        <v>10.85066145408563</v>
       </c>
       <c r="D352" t="n">
-        <v>10.59310231415095</v>
+        <v>10.59310421404906</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449371111645</v>
+        <v>10.68449562740583</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C353" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D353" t="n">
-        <v>10.34385236673755</v>
+        <v>10.3438542219321</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156107361439</v>
+        <v>10.55156296606198</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7532,16 +7532,16 @@
         <v>44832</v>
       </c>
       <c r="B356" t="n">
-        <v>10.21092224121094</v>
+        <v>10.21092128753662</v>
       </c>
       <c r="C356" t="n">
-        <v>10.44355441406907</v>
+        <v>10.4435534386675</v>
       </c>
       <c r="D356" t="n">
-        <v>10.19430607480114</v>
+        <v>10.19430512267873</v>
       </c>
       <c r="E356" t="n">
-        <v>10.40201316331301</v>
+        <v>10.40201219179128</v>
       </c>
       <c r="F356" t="n">
         <v>104928</v>
@@ -7552,16 +7552,16 @@
         <v>44833</v>
       </c>
       <c r="B357" t="n">
-        <v>10.12783622741699</v>
+        <v>10.12783813476562</v>
       </c>
       <c r="C357" t="n">
-        <v>10.20261146068705</v>
+        <v>10.2026133821179</v>
       </c>
       <c r="D357" t="n">
-        <v>9.978286595608219</v>
+        <v>9.978288474792565</v>
       </c>
       <c r="E357" t="n">
-        <v>10.17768554819902</v>
+        <v>10.17768746493565</v>
       </c>
       <c r="F357" t="n">
         <v>97132</v>
@@ -7572,16 +7572,16 @@
         <v>44834</v>
       </c>
       <c r="B358" t="n">
-        <v>10.18599414825439</v>
+        <v>10.18599605560303</v>
       </c>
       <c r="C358" t="n">
-        <v>10.26907746676657</v>
+        <v>10.26907938967273</v>
       </c>
       <c r="D358" t="n">
-        <v>9.920128029854263</v>
+        <v>9.920129887418911</v>
       </c>
       <c r="E358" t="n">
-        <v>10.17768606682259</v>
+        <v>10.17768797261552</v>
       </c>
       <c r="F358" t="n">
         <v>188154</v>
@@ -7612,16 +7612,16 @@
         <v>44838</v>
       </c>
       <c r="B360" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C360" t="n">
-        <v>10.75926974270069</v>
+        <v>10.75926878532992</v>
       </c>
       <c r="D360" t="n">
-        <v>10.32723777056884</v>
+        <v>10.32723685164071</v>
       </c>
       <c r="E360" t="n">
-        <v>10.38539601697868</v>
+        <v>10.38539509287557</v>
       </c>
       <c r="F360" t="n">
         <v>266324</v>
@@ -7632,16 +7632,16 @@
         <v>44839</v>
       </c>
       <c r="B361" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="C361" t="n">
-        <v>10.90051113263368</v>
+        <v>10.90051015816272</v>
       </c>
       <c r="D361" t="n">
-        <v>10.55987057710461</v>
+        <v>10.55986963308583</v>
       </c>
       <c r="E361" t="n">
-        <v>10.80081080634695</v>
+        <v>10.80080984078888</v>
       </c>
       <c r="F361" t="n">
         <v>399697</v>
@@ -7652,16 +7652,16 @@
         <v>44840</v>
       </c>
       <c r="B362" t="n">
-        <v>10.88389301300049</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="C362" t="n">
-        <v>10.88389301300049</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="D362" t="n">
-        <v>10.5183274135295</v>
+        <v>10.51832833517203</v>
       </c>
       <c r="E362" t="n">
-        <v>10.53494357637925</v>
+        <v>10.53494449947773</v>
       </c>
       <c r="F362" t="n">
         <v>536757</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389266736954</v>
+        <v>10.88389461942159</v>
       </c>
       <c r="D363" t="n">
-        <v>10.6346435546875</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="E363" t="n">
-        <v>10.8257352645109</v>
+        <v>10.82573720613229</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156279823885</v>
+        <v>10.55156188207657</v>
       </c>
       <c r="E364" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7712,16 +7712,16 @@
         <v>44845</v>
       </c>
       <c r="B365" t="n">
-        <v>11.06667709350586</v>
+        <v>11.06667804718018</v>
       </c>
       <c r="C365" t="n">
-        <v>11.17468550345477</v>
+        <v>11.17468646643675</v>
       </c>
       <c r="D365" t="n">
-        <v>10.80081094455824</v>
+        <v>10.80081187532146</v>
       </c>
       <c r="E365" t="n">
-        <v>10.81742794406249</v>
+        <v>10.81742887625768</v>
       </c>
       <c r="F365" t="n">
         <v>221655</v>
@@ -7772,16 +7772,16 @@
         <v>44851</v>
       </c>
       <c r="B368" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="D368" t="n">
-        <v>10.79250300417271</v>
+        <v>10.79250206495899</v>
       </c>
       <c r="E368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="F368" t="n">
         <v>132003</v>
@@ -7792,16 +7792,16 @@
         <v>44852</v>
       </c>
       <c r="B369" t="n">
-        <v>10.75927066802979</v>
+        <v>10.75926971435547</v>
       </c>
       <c r="C369" t="n">
-        <v>11.09160401022853</v>
+        <v>11.09160302709703</v>
       </c>
       <c r="D369" t="n">
-        <v>10.75096258489428</v>
+        <v>10.75096163195637</v>
       </c>
       <c r="E369" t="n">
-        <v>10.95867050640272</v>
+        <v>10.95866953505411</v>
       </c>
       <c r="F369" t="n">
         <v>172246</v>
@@ -7832,16 +7832,16 @@
         <v>44854</v>
       </c>
       <c r="B371" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C371" t="n">
-        <v>11.04175289232892</v>
+        <v>11.04175190982251</v>
       </c>
       <c r="D371" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="E371" t="n">
-        <v>10.95866956392465</v>
+        <v>10.95866858881108</v>
       </c>
       <c r="F371" t="n">
         <v>119045</v>
@@ -7852,16 +7852,16 @@
         <v>44855</v>
       </c>
       <c r="B372" t="n">
-        <v>10.68449401855469</v>
+        <v>10.684494972229</v>
       </c>
       <c r="C372" t="n">
-        <v>10.88389298054533</v>
+        <v>10.88389395201756</v>
       </c>
       <c r="D372" t="n">
-        <v>10.68449401855469</v>
+        <v>10.684494972229</v>
       </c>
       <c r="E372" t="n">
-        <v>10.76757733674981</v>
+        <v>10.76757829783996</v>
       </c>
       <c r="F372" t="n">
         <v>132319</v>
@@ -7872,16 +7872,16 @@
         <v>44858</v>
       </c>
       <c r="B373" t="n">
-        <v>10.84235286712646</v>
+        <v>10.84235382080078</v>
       </c>
       <c r="C373" t="n">
-        <v>10.95866935775788</v>
+        <v>10.95867032166319</v>
       </c>
       <c r="D373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618715250262</v>
       </c>
       <c r="E373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618715250262</v>
       </c>
       <c r="F373" t="n">
         <v>186469</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.6512622833252</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866968357269</v>
+        <v>10.95866870237426</v>
       </c>
       <c r="D374" t="n">
-        <v>10.6512622833252</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772777815022</v>
+        <v>10.71772681852483</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -7912,16 +7912,16 @@
         <v>44860</v>
       </c>
       <c r="B375" t="n">
-        <v>10.71772766113281</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C375" t="n">
-        <v>10.96697764634563</v>
+        <v>10.9669766704928</v>
       </c>
       <c r="D375" t="n">
-        <v>10.65126216703347</v>
+        <v>10.65126121927332</v>
       </c>
       <c r="E375" t="n">
-        <v>10.65126216703347</v>
+        <v>10.65126121927332</v>
       </c>
       <c r="F375" t="n">
         <v>230294</v>
@@ -7952,16 +7952,16 @@
         <v>44862</v>
       </c>
       <c r="B377" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C377" t="n">
-        <v>10.99190282718986</v>
+        <v>10.99190187062344</v>
       </c>
       <c r="D377" t="n">
-        <v>10.68449542753418</v>
+        <v>10.68449449771977</v>
       </c>
       <c r="E377" t="n">
-        <v>10.89220249831554</v>
+        <v>10.89220155042551</v>
       </c>
       <c r="F377" t="n">
         <v>271802</v>
@@ -8012,16 +8012,16 @@
         <v>44868</v>
       </c>
       <c r="B380" t="n">
-        <v>11.00851917266846</v>
+        <v>11.00852012634277</v>
       </c>
       <c r="C380" t="n">
-        <v>11.0168272546704</v>
+        <v>11.01682820906445</v>
       </c>
       <c r="D380" t="n">
-        <v>10.59310338633121</v>
+        <v>10.59310430401782</v>
       </c>
       <c r="E380" t="n">
-        <v>10.80081044476839</v>
+        <v>10.80081138044879</v>
       </c>
       <c r="F380" t="n">
         <v>251575</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19961071014404</v>
+        <v>11.19960975646973</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577736811222</v>
+        <v>11.36577640028841</v>
       </c>
       <c r="D381" t="n">
-        <v>10.8838943938971</v>
+        <v>10.8838934671068</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344488690735</v>
+        <v>11.03344394738246</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8052,16 +8052,16 @@
         <v>44872</v>
       </c>
       <c r="B382" t="n">
-        <v>10.86727905273438</v>
+        <v>10.86727714538574</v>
       </c>
       <c r="C382" t="n">
-        <v>11.24115280940709</v>
+        <v>11.24115083643875</v>
       </c>
       <c r="D382" t="n">
-        <v>10.72603746622774</v>
+        <v>10.72603558366884</v>
       </c>
       <c r="E382" t="n">
-        <v>11.11652822384952</v>
+        <v>11.11652627275442</v>
       </c>
       <c r="F382" t="n">
         <v>110617</v>
@@ -8072,16 +8072,16 @@
         <v>44873</v>
       </c>
       <c r="B383" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588558197021</v>
       </c>
       <c r="C383" t="n">
-        <v>10.91712810775032</v>
+        <v>10.91712714157601</v>
       </c>
       <c r="D383" t="n">
-        <v>10.62633604654561</v>
+        <v>10.62633510610663</v>
       </c>
       <c r="E383" t="n">
-        <v>10.9005111084955</v>
+        <v>10.90051014379181</v>
       </c>
       <c r="F383" t="n">
         <v>103348</v>
@@ -8112,16 +8112,16 @@
         <v>44875</v>
       </c>
       <c r="B385" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="C385" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="D385" t="n">
-        <v>10.23584535140422</v>
+        <v>10.23584443635226</v>
       </c>
       <c r="E385" t="n">
-        <v>10.58479482394483</v>
+        <v>10.58479387769789</v>
       </c>
       <c r="F385" t="n">
         <v>289395</v>
@@ -8132,16 +8132,16 @@
         <v>44876</v>
       </c>
       <c r="B386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="C386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="D386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="E386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="F386" t="n">
         <v>372832</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.707114219665527</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629405073862</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="D388" t="n">
-        <v>8.707114219665527</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629405073862</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8212,16 +8212,16 @@
         <v>44883</v>
       </c>
       <c r="B390" t="n">
-        <v>8.557563781738281</v>
+        <v>8.557564735412598</v>
       </c>
       <c r="C390" t="n">
-        <v>8.914822114121259</v>
+        <v>8.914823107609253</v>
       </c>
       <c r="D390" t="n">
-        <v>8.391397989069686</v>
+        <v>8.39139892422611</v>
       </c>
       <c r="E390" t="n">
-        <v>8.84835579705382</v>
+        <v>8.848356783134658</v>
       </c>
       <c r="F390" t="n">
         <v>571733</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562845230102539</v>
+        <v>8.562844276428223</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039488002680034</v>
+        <v>9.039486995920329</v>
       </c>
       <c r="D392" t="n">
-        <v>8.52939671765821</v>
+        <v>8.529395767709174</v>
       </c>
       <c r="E392" t="n">
-        <v>8.947504383423015</v>
+        <v>8.947503386907851</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8332,16 +8332,16 @@
         <v>44893</v>
       </c>
       <c r="B396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="C396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="D396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="E396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="F396" t="n">
         <v>122943</v>
@@ -8352,16 +8352,16 @@
         <v>44894</v>
       </c>
       <c r="B397" t="n">
-        <v>8.705002784729004</v>
+        <v>8.705001831054688</v>
       </c>
       <c r="C397" t="n">
-        <v>8.87224536129513</v>
+        <v>8.872244389298597</v>
       </c>
       <c r="D397" t="n">
-        <v>8.470862337395888</v>
+        <v>8.470861409372766</v>
       </c>
       <c r="E397" t="n">
-        <v>8.604656398648789</v>
+        <v>8.604655455967894</v>
       </c>
       <c r="F397" t="n">
         <v>205221</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947503089904785</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198368157181012</v>
+        <v>9.198369137593913</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822070976336846</v>
+        <v>8.822071916641914</v>
       </c>
       <c r="E400" t="n">
-        <v>9.139832218690247</v>
+        <v>9.139833192864064</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905695681933357</v>
+        <v>8.905693728734814</v>
       </c>
       <c r="D403" t="n">
-        <v>8.679917128923909</v>
+        <v>8.679915225243152</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935684680938721</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="C405" t="n">
-        <v>8.47922454343796</v>
+        <v>8.479225052935186</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935684680938721</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462500705285068</v>
+        <v>8.462501213777397</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952410221099854</v>
+        <v>7.952408313751221</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027669181225434</v>
+        <v>8.027667255826291</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818616140814081</v>
+        <v>7.818614265555337</v>
       </c>
       <c r="E406" t="n">
-        <v>7.935685540993802</v>
+        <v>7.935683637656506</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8572,16 +8572,16 @@
         <v>44909</v>
       </c>
       <c r="B408" t="n">
-        <v>8.13637638092041</v>
+        <v>8.136375427246094</v>
       </c>
       <c r="C408" t="n">
-        <v>8.161462137413377</v>
+        <v>8.16146118079873</v>
       </c>
       <c r="D408" t="n">
-        <v>7.634646128531304</v>
+        <v>7.634645233665385</v>
       </c>
       <c r="E408" t="n">
-        <v>8.002582319062418</v>
+        <v>8.002581381070261</v>
       </c>
       <c r="F408" t="n">
         <v>518426</v>
@@ -8592,16 +8592,16 @@
         <v>44910</v>
       </c>
       <c r="B409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253443717956543</v>
       </c>
       <c r="C409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253443717956543</v>
       </c>
       <c r="D409" t="n">
-        <v>8.027667939705447</v>
+        <v>8.027666084533418</v>
       </c>
       <c r="E409" t="n">
-        <v>8.111289647021858</v>
+        <v>8.111287772525083</v>
       </c>
       <c r="F409" t="n">
         <v>145488</v>
@@ -8652,16 +8652,16 @@
         <v>44915</v>
       </c>
       <c r="B412" t="n">
-        <v>8.429050445556641</v>
+        <v>8.429051399230957</v>
       </c>
       <c r="C412" t="n">
-        <v>8.579570013648471</v>
+        <v>8.579570984352777</v>
       </c>
       <c r="D412" t="n">
-        <v>8.0527540457485</v>
+        <v>8.052754956848128</v>
       </c>
       <c r="E412" t="n">
-        <v>8.0527540457485</v>
+        <v>8.052754956848128</v>
       </c>
       <c r="F412" t="n">
         <v>166979</v>
@@ -8672,16 +8672,16 @@
         <v>44916</v>
       </c>
       <c r="B413" t="n">
-        <v>8.45413875579834</v>
+        <v>8.454139709472656</v>
       </c>
       <c r="C413" t="n">
-        <v>8.613018578241588</v>
+        <v>8.613019549838441</v>
       </c>
       <c r="D413" t="n">
-        <v>8.370517044912967</v>
+        <v>8.370517989154285</v>
       </c>
       <c r="E413" t="n">
-        <v>8.429051318378106</v>
+        <v>8.429052269222419</v>
       </c>
       <c r="F413" t="n">
         <v>125998</v>
@@ -8692,16 +8692,16 @@
         <v>44917</v>
       </c>
       <c r="B414" t="n">
-        <v>8.487586975097656</v>
+        <v>8.48758602142334</v>
       </c>
       <c r="C414" t="n">
-        <v>8.571208683056653</v>
+        <v>8.571207719986512</v>
       </c>
       <c r="D414" t="n">
-        <v>8.403965267138661</v>
+        <v>8.403964322860167</v>
       </c>
       <c r="E414" t="n">
-        <v>8.462500378695903</v>
+        <v>8.462499427840344</v>
       </c>
       <c r="F414" t="n">
         <v>90284</v>
@@ -8712,16 +8712,16 @@
         <v>44918</v>
       </c>
       <c r="B415" t="n">
-        <v>8.688277244567871</v>
+        <v>8.688279151916504</v>
       </c>
       <c r="C415" t="n">
-        <v>8.763537026657437</v>
+        <v>8.763538950527945</v>
       </c>
       <c r="D415" t="n">
-        <v>8.50431000853621</v>
+        <v>8.50431187549828</v>
       </c>
       <c r="E415" t="n">
-        <v>8.529396602566065</v>
+        <v>8.529398475035427</v>
       </c>
       <c r="F415" t="n">
         <v>92391</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613019250906639</v>
+        <v>8.613017361897933</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730090327401705</v>
+        <v>8.730088412716954</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914057601632781</v>
+        <v>8.914055646600298</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830435884216666</v>
+        <v>8.83043394752411</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529398918151855</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771899364464465</v>
+        <v>8.771901326041613</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529398918151855</v>
       </c>
       <c r="E420" t="n">
-        <v>8.705002337276639</v>
+        <v>8.705004283894235</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8832,16 +8832,16 @@
         <v>44929</v>
       </c>
       <c r="B421" t="n">
-        <v>8.102927207946777</v>
+        <v>8.102926254272461</v>
       </c>
       <c r="C421" t="n">
-        <v>8.504310201091222</v>
+        <v>8.50430920017612</v>
       </c>
       <c r="D421" t="n">
-        <v>8.086202531501375</v>
+        <v>8.086201579795469</v>
       </c>
       <c r="E421" t="n">
-        <v>8.479223606493356</v>
+        <v>8.47922260853082</v>
       </c>
       <c r="F421" t="n">
         <v>326162</v>
@@ -8852,16 +8852,16 @@
         <v>44930</v>
       </c>
       <c r="B422" t="n">
-        <v>8.328704833984375</v>
+        <v>8.328703880310059</v>
       </c>
       <c r="C422" t="n">
-        <v>8.345428670198819</v>
+        <v>8.345427714609547</v>
       </c>
       <c r="D422" t="n">
-        <v>8.061115893289037</v>
+        <v>8.061114970254863</v>
       </c>
       <c r="E422" t="n">
-        <v>8.345428670198819</v>
+        <v>8.345427714609547</v>
       </c>
       <c r="F422" t="n">
         <v>248204</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947503089904785</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947503089904785</v>
+        <v>8.947504043579102</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387238697142262</v>
+        <v>8.387239591100503</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395601454149713</v>
+        <v>8.395602348999303</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964228630065918</v>
+        <v>8.964229583740234</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072936930593318</v>
+        <v>9.072937895832748</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847159251220148</v>
+        <v>8.847160192439846</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922418197631035</v>
+        <v>8.922419146857282</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139833970240518</v>
+        <v>9.139834941690628</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006039914165292</v>
+        <v>9.006040871394767</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847159262540833</v>
+        <v>8.847160202883281</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C431" t="n">
-        <v>9.06457502373333</v>
+        <v>9.064575987184355</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905694372108872</v>
+        <v>8.905695318672869</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964228641536403</v>
+        <v>8.964229594321862</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9052,16 +9052,16 @@
         <v>44944</v>
       </c>
       <c r="B432" t="n">
-        <v>9.064576148986816</v>
+        <v>9.0645751953125</v>
       </c>
       <c r="C432" t="n">
-        <v>9.357251733159014</v>
+        <v>9.357250748692612</v>
       </c>
       <c r="D432" t="n">
-        <v>8.964229754333143</v>
+        <v>8.964228811216161</v>
       </c>
       <c r="E432" t="n">
-        <v>8.964229754333143</v>
+        <v>8.964228811216161</v>
       </c>
       <c r="F432" t="n">
         <v>306251</v>
@@ -9092,16 +9092,16 @@
         <v>44946</v>
       </c>
       <c r="B434" t="n">
-        <v>9.365612983703613</v>
+        <v>9.365612030029297</v>
       </c>
       <c r="C434" t="n">
-        <v>9.365612983703613</v>
+        <v>9.365612030029297</v>
       </c>
       <c r="D434" t="n">
-        <v>9.039488904654647</v>
+        <v>9.039487984188639</v>
       </c>
       <c r="E434" t="n">
-        <v>9.131472533089941</v>
+        <v>9.131471603257495</v>
       </c>
       <c r="F434" t="n">
         <v>97975</v>
@@ -9132,16 +9132,16 @@
         <v>44950</v>
       </c>
       <c r="B436" t="n">
-        <v>9.474322319030762</v>
+        <v>9.474321365356445</v>
       </c>
       <c r="C436" t="n">
-        <v>9.61647831650702</v>
+        <v>9.616477348523446</v>
       </c>
       <c r="D436" t="n">
-        <v>9.348889321050764</v>
+        <v>9.348888380002389</v>
       </c>
       <c r="E436" t="n">
-        <v>9.61647831650702</v>
+        <v>9.616477348523446</v>
       </c>
       <c r="F436" t="n">
         <v>142116</v>
@@ -9152,16 +9152,16 @@
         <v>44951</v>
       </c>
       <c r="B437" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="C437" t="n">
-        <v>9.842255125096191</v>
+        <v>9.842257043856318</v>
       </c>
       <c r="D437" t="n">
-        <v>9.41578552811195</v>
+        <v>9.415787363731287</v>
       </c>
       <c r="E437" t="n">
-        <v>9.541217663679022</v>
+        <v>9.541219523751513</v>
       </c>
       <c r="F437" t="n">
         <v>142538</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C438" t="n">
-        <v>9.95932505997885</v>
+        <v>9.959326039139317</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741909308483715</v>
+        <v>9.741910266268745</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="D439" t="n">
-        <v>9.6499256889996</v>
+        <v>9.649926637741174</v>
       </c>
       <c r="E439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9232,16 +9232,16 @@
         <v>44957</v>
       </c>
       <c r="B441" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="C441" t="n">
-        <v>9.683374442443164</v>
+        <v>9.68337541974836</v>
       </c>
       <c r="D441" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="E441" t="n">
-        <v>9.616476575584498</v>
+        <v>9.616477546137954</v>
       </c>
       <c r="F441" t="n">
         <v>134742</v>
@@ -9252,16 +9252,16 @@
         <v>44958</v>
       </c>
       <c r="B442" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="C442" t="n">
-        <v>9.783720016479492</v>
+        <v>9.783721923828125</v>
       </c>
       <c r="D442" t="n">
-        <v>9.323801065879572</v>
+        <v>9.323802883566421</v>
       </c>
       <c r="E442" t="n">
-        <v>9.449234041587136</v>
+        <v>9.449235883727303</v>
       </c>
       <c r="F442" t="n">
         <v>177092</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.666650772094727</v>
+        <v>9.66664981842041</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725185886602381</v>
+        <v>9.725184927153217</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457596911730329</v>
+        <v>9.457595978680457</v>
       </c>
       <c r="E443" t="n">
-        <v>9.70009928893616</v>
+        <v>9.700098331961943</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9292,16 +9292,16 @@
         <v>44960</v>
       </c>
       <c r="B444" t="n">
-        <v>9.675012588500977</v>
+        <v>9.67501163482666</v>
       </c>
       <c r="C444" t="n">
-        <v>9.867342608471997</v>
+        <v>9.867341635839546</v>
       </c>
       <c r="D444" t="n">
-        <v>9.382337859212104</v>
+        <v>9.382336934386988</v>
       </c>
       <c r="E444" t="n">
-        <v>9.474321489584133</v>
+        <v>9.474320555692112</v>
       </c>
       <c r="F444" t="n">
         <v>1290218</v>
@@ -9312,16 +9312,16 @@
         <v>44963</v>
       </c>
       <c r="B445" t="n">
-        <v>9.608116149902344</v>
+        <v>9.608115196228027</v>
       </c>
       <c r="C445" t="n">
-        <v>9.842256619930208</v>
+        <v>9.842255643015774</v>
       </c>
       <c r="D445" t="n">
-        <v>9.599754230298668</v>
+        <v>9.599753277454333</v>
       </c>
       <c r="E445" t="n">
-        <v>9.666651267409309</v>
+        <v>9.666650307924964</v>
       </c>
       <c r="F445" t="n">
         <v>107772</v>
@@ -9332,16 +9332,16 @@
         <v>44964</v>
       </c>
       <c r="B446" t="n">
-        <v>9.733547210693359</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="C446" t="n">
-        <v>9.733547210693359</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="D446" t="n">
-        <v>9.457595517194969</v>
+        <v>9.457596443832067</v>
       </c>
       <c r="E446" t="n">
-        <v>9.649925510849618</v>
+        <v>9.64992645633084</v>
       </c>
       <c r="F446" t="n">
         <v>121889</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312152862549</v>
+        <v>10.09312057495117</v>
       </c>
       <c r="C447" t="n">
-        <v>10.1600177240003</v>
+        <v>10.16001676400513</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649927198089818</v>
+        <v>9.649926286291848</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741910831958663</v>
+        <v>9.741909911469383</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9392,16 +9392,16 @@
         <v>44967</v>
       </c>
       <c r="B449" t="n">
-        <v>9.373974800109863</v>
+        <v>9.37397575378418</v>
       </c>
       <c r="C449" t="n">
-        <v>10.1432922660117</v>
+        <v>10.1432932979536</v>
       </c>
       <c r="D449" t="n">
-        <v>9.298715017063337</v>
+        <v>9.298715963080996</v>
       </c>
       <c r="E449" t="n">
-        <v>9.95096310957136</v>
+        <v>9.950964121946381</v>
       </c>
       <c r="F449" t="n">
         <v>543394</v>
@@ -9552,16 +9552,16 @@
         <v>44981</v>
       </c>
       <c r="B457" t="n">
-        <v>10.00113677978516</v>
+        <v>10.00113773345947</v>
       </c>
       <c r="C457" t="n">
-        <v>10.21018978242951</v>
+        <v>10.21019075603841</v>
       </c>
       <c r="D457" t="n">
-        <v>10.00113677978516</v>
+        <v>10.00113773345947</v>
       </c>
       <c r="E457" t="n">
-        <v>10.10148232187131</v>
+        <v>10.10148328511423</v>
       </c>
       <c r="F457" t="n">
         <v>69320</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458499908447</v>
+        <v>10.03458404541016</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889864399266</v>
+        <v>10.31889766329754</v>
       </c>
       <c r="D459" t="n">
-        <v>9.90915369476458</v>
+        <v>9.909152753011098</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950964129537878</v>
+        <v>9.950963183810783</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.7453670501709</v>
       </c>
       <c r="C465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.7453670501709</v>
       </c>
       <c r="D465" t="n">
-        <v>10.50286563988488</v>
+        <v>10.50286470773317</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502245880179</v>
+        <v>10.64502151403336</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9792,16 +9792,16 @@
         <v>44999</v>
       </c>
       <c r="B469" t="n">
-        <v>9.892428398132324</v>
+        <v>9.892427444458008</v>
       </c>
       <c r="C469" t="n">
-        <v>10.2603646011067</v>
+        <v>10.26036361196169</v>
       </c>
       <c r="D469" t="n">
-        <v>9.892428398132324</v>
+        <v>9.892427444458008</v>
       </c>
       <c r="E469" t="n">
-        <v>10.17674288954717</v>
+        <v>10.17674190846367</v>
       </c>
       <c r="F469" t="n">
         <v>103137</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758633613586426</v>
+        <v>9.758634567260742</v>
       </c>
       <c r="C470" t="n">
-        <v>9.967687457030143</v>
+        <v>9.9676884311345</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675011908180837</v>
+        <v>9.675012853683121</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892427670122959</v>
+        <v>9.892428636872463</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165519714355</v>
+        <v>10.15165615081787</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837903495139</v>
+        <v>10.16837999019679</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683375136415892</v>
+        <v>9.683376046098697</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833893877389167</v>
+        <v>9.833894801212116</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9852,16 +9852,16 @@
         <v>45002</v>
       </c>
       <c r="B472" t="n">
-        <v>9.942601203918457</v>
+        <v>9.942600250244141</v>
       </c>
       <c r="C472" t="n">
-        <v>10.18510440999109</v>
+        <v>10.18510343305635</v>
       </c>
       <c r="D472" t="n">
-        <v>9.750272030986295</v>
+        <v>9.750271095759805</v>
       </c>
       <c r="E472" t="n">
-        <v>10.18510440999109</v>
+        <v>10.18510343305635</v>
       </c>
       <c r="F472" t="n">
         <v>69952</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440873146057129</v>
+        <v>9.44087028503418</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583029986483497</v>
+        <v>9.583027082380426</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415787386105999</v>
+        <v>9.415784532685199</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532856786299918</v>
+        <v>9.532853897401656</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9912,16 +9912,16 @@
         <v>45007</v>
       </c>
       <c r="B475" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="C475" t="n">
-        <v>9.507769117202587</v>
+        <v>9.507770076784624</v>
       </c>
       <c r="D475" t="n">
-        <v>9.206731656830312</v>
+        <v>9.206732586029814</v>
       </c>
       <c r="E475" t="n">
-        <v>9.482682522148149</v>
+        <v>9.482683479198295</v>
       </c>
       <c r="F475" t="n">
         <v>116622</v>
@@ -9952,16 +9952,16 @@
         <v>45009</v>
       </c>
       <c r="B477" t="n">
-        <v>9.641565322875977</v>
+        <v>9.64156436920166</v>
       </c>
       <c r="C477" t="n">
-        <v>9.666651081203783</v>
+        <v>9.666650125048163</v>
       </c>
       <c r="D477" t="n">
-        <v>9.089662676992758</v>
+        <v>9.089661777908683</v>
       </c>
       <c r="E477" t="n">
-        <v>9.373976339447273</v>
+        <v>9.373975412240934</v>
       </c>
       <c r="F477" t="n">
         <v>212279</v>
@@ -9972,16 +9972,16 @@
         <v>45012</v>
       </c>
       <c r="B478" t="n">
-        <v>10.4694185256958</v>
+        <v>10.46941661834717</v>
       </c>
       <c r="C478" t="n">
-        <v>10.54467832465365</v>
+        <v>10.54467640359397</v>
       </c>
       <c r="D478" t="n">
-        <v>9.875705414432909</v>
+        <v>9.875703615248632</v>
       </c>
       <c r="E478" t="n">
-        <v>10.31889976792075</v>
+        <v>10.31889788799405</v>
       </c>
       <c r="F478" t="n">
         <v>649270</v>
@@ -10012,16 +10012,16 @@
         <v>45014</v>
       </c>
       <c r="B480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028350830078</v>
       </c>
       <c r="C480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028350830078</v>
       </c>
       <c r="D480" t="n">
-        <v>10.45269265683905</v>
+        <v>10.45269451657835</v>
       </c>
       <c r="E480" t="n">
-        <v>10.70355692438362</v>
+        <v>10.7035588287566</v>
       </c>
       <c r="F480" t="n">
         <v>215756</v>
@@ -10032,16 +10032,16 @@
         <v>45015</v>
       </c>
       <c r="B481" t="n">
-        <v>11.00459480285645</v>
+        <v>11.00459575653076</v>
       </c>
       <c r="C481" t="n">
-        <v>11.18856205145192</v>
+        <v>11.18856302106911</v>
       </c>
       <c r="D481" t="n">
-        <v>10.61993646859709</v>
+        <v>10.61993738893635</v>
       </c>
       <c r="E481" t="n">
-        <v>10.6617469014086</v>
+        <v>10.66174782537122</v>
       </c>
       <c r="F481" t="n">
         <v>272855</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820570451678</v>
+        <v>10.11820669929775</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201012665911</v>
+        <v>9.633201959763182</v>
       </c>
       <c r="E483" t="n">
-        <v>10.03458400312928</v>
+        <v>10.0345849896889</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10092,16 +10092,16 @@
         <v>45020</v>
       </c>
       <c r="B484" t="n">
-        <v>9.599754333496094</v>
+        <v>9.599752426147461</v>
       </c>
       <c r="C484" t="n">
-        <v>9.758635008376988</v>
+        <v>9.758633069460794</v>
       </c>
       <c r="D484" t="n">
-        <v>9.532856455525678</v>
+        <v>9.532854561468801</v>
       </c>
       <c r="E484" t="n">
-        <v>9.70009989024077</v>
+        <v>9.700097962954755</v>
       </c>
       <c r="F484" t="n">
         <v>529909</v>
@@ -10152,16 +10152,16 @@
         <v>45026</v>
       </c>
       <c r="B487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="C487" t="n">
-        <v>9.700098570263346</v>
+        <v>9.700099553607547</v>
       </c>
       <c r="D487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="E487" t="n">
-        <v>9.574666431365994</v>
+        <v>9.574667401994555</v>
       </c>
       <c r="F487" t="n">
         <v>160237</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758633144676933</v>
+        <v>9.758634104106184</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574667930603027</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="C489" t="n">
-        <v>9.783721808213219</v>
+        <v>9.78372083371632</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574667930603027</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700100089141012</v>
+        <v>9.700099122973164</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683375358581543</v>
+        <v>9.683376312255859</v>
       </c>
       <c r="C490" t="n">
-        <v>9.775358989056672</v>
+        <v>9.775359951790064</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566305130678549</v>
+        <v>9.566306072823117</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608115566297945</v>
+        <v>9.608116512560244</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766995062773542</v>
+        <v>9.766996023024904</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549580151418876</v>
+        <v>9.549581090294884</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691736119623117</v>
+        <v>9.691737072475323</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.658288955688477</v>
+        <v>9.65828800201416</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716823230678386</v>
+        <v>9.716822271224306</v>
       </c>
       <c r="D494" t="n">
-        <v>9.59975384055798</v>
+        <v>9.59975289266351</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616477679086358</v>
+        <v>9.616476729540551</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10312,16 +10312,16 @@
         <v>45036</v>
       </c>
       <c r="B495" t="n">
-        <v>9.599754333496094</v>
+        <v>9.599752426147461</v>
       </c>
       <c r="C495" t="n">
-        <v>9.77535968790475</v>
+        <v>9.775357745665575</v>
       </c>
       <c r="D495" t="n">
-        <v>9.549581975194069</v>
+        <v>9.549580077814044</v>
       </c>
       <c r="E495" t="n">
-        <v>9.658289451632312</v>
+        <v>9.658287532653498</v>
       </c>
       <c r="F495" t="n">
         <v>169823</v>
@@ -10332,16 +10332,16 @@
         <v>45040</v>
       </c>
       <c r="B496" t="n">
-        <v>9.516131401062012</v>
+        <v>9.516130447387695</v>
       </c>
       <c r="C496" t="n">
-        <v>9.700098651674196</v>
+        <v>9.700097679563306</v>
       </c>
       <c r="D496" t="n">
-        <v>9.516131401062012</v>
+        <v>9.516130447387695</v>
       </c>
       <c r="E496" t="n">
-        <v>9.633201622386224</v>
+        <v>9.633200656979527</v>
       </c>
       <c r="F496" t="n">
         <v>136322</v>
@@ -10352,16 +10352,16 @@
         <v>45041</v>
       </c>
       <c r="B497" t="n">
-        <v>9.248543739318848</v>
+        <v>9.248542785644531</v>
       </c>
       <c r="C497" t="n">
-        <v>9.633202971819085</v>
+        <v>9.633201978480185</v>
       </c>
       <c r="D497" t="n">
-        <v>9.248543739318848</v>
+        <v>9.248542785644531</v>
       </c>
       <c r="E497" t="n">
-        <v>9.633202971819085</v>
+        <v>9.633201978480185</v>
       </c>
       <c r="F497" t="n">
         <v>58153</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.28199291229248</v>
+        <v>9.281991004943848</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382338468264816</v>
+        <v>9.382336540296262</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215095034836967</v>
+        <v>9.215093141235121</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248543553494413</v>
+        <v>9.248541653019259</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10392,16 +10392,16 @@
         <v>45043</v>
       </c>
       <c r="B499" t="n">
-        <v>9.31544017791748</v>
+        <v>9.315439224243164</v>
       </c>
       <c r="C499" t="n">
-        <v>9.365613373750113</v>
+        <v>9.365612414939283</v>
       </c>
       <c r="D499" t="n">
-        <v>9.139834832643849</v>
+        <v>9.139833896947247</v>
       </c>
       <c r="E499" t="n">
-        <v>9.365613373750113</v>
+        <v>9.365612414939283</v>
       </c>
       <c r="F499" t="n">
         <v>124734</v>
@@ -10412,16 +10412,16 @@
         <v>45044</v>
       </c>
       <c r="B500" t="n">
-        <v>9.1761474609375</v>
+        <v>9.176148414611816</v>
       </c>
       <c r="C500" t="n">
-        <v>9.393830394462805</v>
+        <v>9.393831370760845</v>
       </c>
       <c r="D500" t="n">
-        <v>9.1761474609375</v>
+        <v>9.176148414611816</v>
       </c>
       <c r="E500" t="n">
-        <v>9.326850577363659</v>
+        <v>9.326851546700507</v>
       </c>
       <c r="F500" t="n">
         <v>147595</v>
@@ -10472,16 +10472,16 @@
         <v>45050</v>
       </c>
       <c r="B503" t="n">
-        <v>9.209637641906738</v>
+        <v>9.209638595581055</v>
       </c>
       <c r="C503" t="n">
-        <v>9.469181379750328</v>
+        <v>9.469182360300858</v>
       </c>
       <c r="D503" t="n">
-        <v>9.067305848299521</v>
+        <v>9.067306787235129</v>
       </c>
       <c r="E503" t="n">
-        <v>9.159402990182974</v>
+        <v>9.159403938655403</v>
       </c>
       <c r="F503" t="n">
         <v>221234</v>
@@ -10492,16 +10492,16 @@
         <v>45051</v>
       </c>
       <c r="B504" t="n">
-        <v>9.418946266174316</v>
+        <v>9.418947219848633</v>
       </c>
       <c r="C504" t="n">
-        <v>9.477553917758021</v>
+        <v>9.4775548773664</v>
       </c>
       <c r="D504" t="n">
-        <v>9.125913055273472</v>
+        <v>9.125913979277989</v>
       </c>
       <c r="E504" t="n">
-        <v>9.125913055273472</v>
+        <v>9.125913979277989</v>
       </c>
       <c r="F504" t="n">
         <v>204589</v>
@@ -10512,16 +10512,16 @@
         <v>45054</v>
       </c>
       <c r="B505" t="n">
-        <v>9.385457038879395</v>
+        <v>9.385458946228027</v>
       </c>
       <c r="C505" t="n">
-        <v>9.519414973698122</v>
+        <v>9.519416908270202</v>
       </c>
       <c r="D505" t="n">
-        <v>9.32684939093425</v>
+        <v>9.326851286372412</v>
       </c>
       <c r="E505" t="n">
-        <v>9.418945681414517</v>
+        <v>9.41894759556884</v>
       </c>
       <c r="F505" t="n">
         <v>225237</v>
@@ -10552,16 +10552,16 @@
         <v>45056</v>
       </c>
       <c r="B507" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="C507" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="D507" t="n">
-        <v>9.418947917893513</v>
+        <v>9.418946980877298</v>
       </c>
       <c r="E507" t="n">
-        <v>9.452437409550097</v>
+        <v>9.452436469202278</v>
       </c>
       <c r="F507" t="n">
         <v>185415</v>
@@ -10612,16 +10612,16 @@
         <v>45061</v>
       </c>
       <c r="B510" t="n">
-        <v>10.18083477020264</v>
+        <v>10.18083381652832</v>
       </c>
       <c r="C510" t="n">
-        <v>10.32316656815221</v>
+        <v>10.32316560114518</v>
       </c>
       <c r="D510" t="n">
-        <v>10.00501600731443</v>
+        <v>10.00501507010967</v>
       </c>
       <c r="E510" t="n">
-        <v>10.0719941430401</v>
+        <v>10.07199319956127</v>
       </c>
       <c r="F510" t="n">
         <v>215124</v>
@@ -10652,16 +10652,16 @@
         <v>45063</v>
       </c>
       <c r="B512" t="n">
-        <v>9.787332534790039</v>
+        <v>9.787333488464355</v>
       </c>
       <c r="C512" t="n">
-        <v>9.904545317354632</v>
+        <v>9.904546282450122</v>
       </c>
       <c r="D512" t="n">
-        <v>9.594766935296825</v>
+        <v>9.594767870207617</v>
       </c>
       <c r="E512" t="n">
-        <v>9.812449018873401</v>
+        <v>9.81244997499506</v>
       </c>
       <c r="F512" t="n">
         <v>227976</v>
@@ -10732,16 +10732,16 @@
         <v>45069</v>
       </c>
       <c r="B516" t="n">
-        <v>9.60313892364502</v>
+        <v>9.603139877319336</v>
       </c>
       <c r="C516" t="n">
-        <v>9.99664143573348</v>
+        <v>9.996642428485981</v>
       </c>
       <c r="D516" t="n">
-        <v>9.594766762434734</v>
+        <v>9.594767715277623</v>
       </c>
       <c r="E516" t="n">
-        <v>9.862683491690436</v>
+        <v>9.862684471139762</v>
       </c>
       <c r="F516" t="n">
         <v>117359</v>
@@ -10752,16 +10752,16 @@
         <v>45070</v>
       </c>
       <c r="B517" t="n">
-        <v>9.351966857910156</v>
+        <v>9.351967811584473</v>
       </c>
       <c r="C517" t="n">
-        <v>9.678490380517195</v>
+        <v>9.678491367489009</v>
       </c>
       <c r="D517" t="n">
-        <v>9.293360891402324</v>
+        <v>9.29336183910025</v>
       </c>
       <c r="E517" t="n">
-        <v>9.61988357283979</v>
+        <v>9.619884553835126</v>
       </c>
       <c r="F517" t="n">
         <v>244411</v>
@@ -10832,16 +10832,16 @@
         <v>45076</v>
       </c>
       <c r="B521" t="n">
-        <v>9.209637641906738</v>
+        <v>9.209638595581055</v>
       </c>
       <c r="C521" t="n">
-        <v>9.544532516166321</v>
+        <v>9.544533504519595</v>
       </c>
       <c r="D521" t="n">
-        <v>9.151029987449244</v>
+        <v>9.151030935054633</v>
       </c>
       <c r="E521" t="n">
-        <v>9.544532516166321</v>
+        <v>9.544533504519595</v>
       </c>
       <c r="F521" t="n">
         <v>214913</v>
@@ -10852,16 +10852,16 @@
         <v>45077</v>
       </c>
       <c r="B522" t="n">
-        <v>9.084052085876465</v>
+        <v>9.084051132202148</v>
       </c>
       <c r="C522" t="n">
-        <v>9.234755217683652</v>
+        <v>9.234754248188015</v>
       </c>
       <c r="D522" t="n">
-        <v>9.084052085876465</v>
+        <v>9.084051132202148</v>
       </c>
       <c r="E522" t="n">
-        <v>9.209638730023915</v>
+        <v>9.209637763165091</v>
       </c>
       <c r="F522" t="n">
         <v>138113</v>
@@ -10912,16 +10912,16 @@
         <v>45082</v>
       </c>
       <c r="B525" t="n">
-        <v>8.874740600585938</v>
+        <v>8.874741554260254</v>
       </c>
       <c r="C525" t="n">
-        <v>9.142657326530141</v>
+        <v>9.142658308994628</v>
       </c>
       <c r="D525" t="n">
-        <v>8.849624117265524</v>
+        <v>8.849625068240838</v>
       </c>
       <c r="E525" t="n">
-        <v>8.933347410672782</v>
+        <v>8.933348370644952</v>
       </c>
       <c r="F525" t="n">
         <v>464803</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958463668823242</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C526" t="n">
-        <v>9.058932113654803</v>
+        <v>9.058934042394197</v>
       </c>
       <c r="D526" t="n">
-        <v>8.832877902491413</v>
+        <v>8.83287978310155</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933346347322974</v>
+        <v>8.933348249323872</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -10952,16 +10952,16 @@
         <v>45084</v>
       </c>
       <c r="B527" t="n">
-        <v>9.117541313171387</v>
+        <v>9.117542266845703</v>
       </c>
       <c r="C527" t="n">
-        <v>9.192892449355798</v>
+        <v>9.192893410911674</v>
       </c>
       <c r="D527" t="n">
-        <v>8.966837358463263</v>
+        <v>8.966838296374284</v>
       </c>
       <c r="E527" t="n">
-        <v>9.092423146217049</v>
+        <v>9.092424097264061</v>
       </c>
       <c r="F527" t="n">
         <v>438781</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.167774200439453</v>
+        <v>9.16777515411377</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226381007645871</v>
+        <v>9.226381967416739</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109167393233035</v>
+        <v>9.109168340810799</v>
       </c>
       <c r="E528" t="n">
-        <v>9.209636686255218</v>
+        <v>9.209637644284264</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -11032,16 +11032,16 @@
         <v>45091</v>
       </c>
       <c r="B531" t="n">
-        <v>9.100796699523926</v>
+        <v>9.100795745849609</v>
       </c>
       <c r="C531" t="n">
-        <v>9.218010332830801</v>
+        <v>9.218009366873643</v>
       </c>
       <c r="D531" t="n">
-        <v>9.04218988287049</v>
+        <v>9.042188935337592</v>
       </c>
       <c r="E531" t="n">
-        <v>9.142658350917937</v>
+        <v>9.142657392856929</v>
       </c>
       <c r="F531" t="n">
         <v>269590</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.99195384979248</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="C535" t="n">
-        <v>8.99195384979248</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899857557908286</v>
+        <v>8.899858501814995</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983581689031073</v>
+        <v>8.983582641817451</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11132,16 +11132,16 @@
         <v>45098</v>
       </c>
       <c r="B536" t="n">
-        <v>9.000327110290527</v>
+        <v>9.000326156616211</v>
       </c>
       <c r="C536" t="n">
-        <v>9.042189601551824</v>
+        <v>9.04218864344176</v>
       </c>
       <c r="D536" t="n">
-        <v>8.857996995277212</v>
+        <v>8.85799605668419</v>
       </c>
       <c r="E536" t="n">
-        <v>9.033817439767434</v>
+        <v>9.033816482544484</v>
       </c>
       <c r="F536" t="n">
         <v>259897</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950092315673828</v>
+        <v>8.950093269348145</v>
       </c>
       <c r="C537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="D537" t="n">
-        <v>8.832878698884004</v>
+        <v>8.83287964006866</v>
       </c>
       <c r="E537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11172,16 +11172,16 @@
         <v>45100</v>
       </c>
       <c r="B538" t="n">
-        <v>8.983582496643066</v>
+        <v>8.983583450317383</v>
       </c>
       <c r="C538" t="n">
-        <v>9.008699822354874</v>
+        <v>9.008700778695582</v>
       </c>
       <c r="D538" t="n">
-        <v>8.874741032281783</v>
+        <v>8.874741974401767</v>
       </c>
       <c r="E538" t="n">
-        <v>8.89985835799359</v>
+        <v>8.899859302779966</v>
       </c>
       <c r="F538" t="n">
         <v>372938</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958463668823242</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000325310544016</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841250062601667</v>
+        <v>8.841251944994323</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000325310544016</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11212,16 +11212,16 @@
         <v>45104</v>
       </c>
       <c r="B540" t="n">
-        <v>8.791017532348633</v>
+        <v>8.791016578674316</v>
       </c>
       <c r="C540" t="n">
-        <v>8.991955311472692</v>
+        <v>8.991954336000079</v>
       </c>
       <c r="D540" t="n">
-        <v>8.724038553030516</v>
+        <v>8.724037606622268</v>
       </c>
       <c r="E540" t="n">
-        <v>8.958465821813633</v>
+        <v>8.958464849974055</v>
       </c>
       <c r="F540" t="n">
         <v>213544</v>
@@ -11232,16 +11232,16 @@
         <v>45105</v>
       </c>
       <c r="B541" t="n">
-        <v>8.657059669494629</v>
+        <v>8.657058715820312</v>
       </c>
       <c r="C541" t="n">
-        <v>8.87474177527181</v>
+        <v>8.874740797617315</v>
       </c>
       <c r="D541" t="n">
-        <v>8.657059669494629</v>
+        <v>8.657058715820312</v>
       </c>
       <c r="E541" t="n">
-        <v>8.87474177527181</v>
+        <v>8.874740797617315</v>
       </c>
       <c r="F541" t="n">
         <v>189418</v>
@@ -11252,16 +11252,16 @@
         <v>45106</v>
       </c>
       <c r="B542" t="n">
-        <v>8.782645225524902</v>
+        <v>8.782646179199219</v>
       </c>
       <c r="C542" t="n">
-        <v>8.84962504490918</v>
+        <v>8.849626005856582</v>
       </c>
       <c r="D542" t="n">
-        <v>8.615196938818752</v>
+        <v>8.615197874310489</v>
       </c>
       <c r="E542" t="n">
-        <v>8.665431593064536</v>
+        <v>8.665432534011066</v>
       </c>
       <c r="F542" t="n">
         <v>269063</v>
@@ -11272,16 +11272,16 @@
         <v>45107</v>
       </c>
       <c r="B543" t="n">
-        <v>9.050562858581543</v>
+        <v>9.050561904907227</v>
       </c>
       <c r="C543" t="n">
-        <v>9.176148665223728</v>
+        <v>9.176147698316207</v>
       </c>
       <c r="D543" t="n">
-        <v>8.765901752937241</v>
+        <v>8.765900829258186</v>
       </c>
       <c r="E543" t="n">
-        <v>8.782646078532318</v>
+        <v>8.782645153088882</v>
       </c>
       <c r="F543" t="n">
         <v>473547</v>
@@ -11292,16 +11292,16 @@
         <v>45110</v>
       </c>
       <c r="B544" t="n">
-        <v>9.410573959350586</v>
+        <v>9.410574913024902</v>
       </c>
       <c r="C544" t="n">
-        <v>9.418946120374542</v>
+        <v>9.4189470748973</v>
       </c>
       <c r="D544" t="n">
-        <v>9.00032629280234</v>
+        <v>9.000327204901865</v>
       </c>
       <c r="E544" t="n">
-        <v>9.067305263333189</v>
+        <v>9.06730618222041</v>
       </c>
       <c r="F544" t="n">
         <v>368934</v>
@@ -11312,16 +11312,16 @@
         <v>45111</v>
       </c>
       <c r="B545" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="C545" t="n">
-        <v>9.594768379967897</v>
+        <v>9.5947674254607</v>
       </c>
       <c r="D545" t="n">
-        <v>9.318479442923763</v>
+        <v>9.318478515902356</v>
       </c>
       <c r="E545" t="n">
-        <v>9.335223768167175</v>
+        <v>9.335222839480007</v>
       </c>
       <c r="F545" t="n">
         <v>135795</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695237159729004</v>
+        <v>9.695236206054688</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843977178107</v>
+        <v>9.753843017738918</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511043704053456</v>
+        <v>9.511042768497374</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611513014634612</v>
+        <v>9.611512069195841</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11352,16 +11352,16 @@
         <v>45113</v>
       </c>
       <c r="B547" t="n">
-        <v>9.418946266174316</v>
+        <v>9.418947219848633</v>
       </c>
       <c r="C547" t="n">
-        <v>9.703608157091221</v>
+        <v>9.703609139587735</v>
       </c>
       <c r="D547" t="n">
-        <v>9.410574105020764</v>
+        <v>9.410575057847394</v>
       </c>
       <c r="E547" t="n">
-        <v>9.695235995937669</v>
+        <v>9.695236977586497</v>
       </c>
       <c r="F547" t="n">
         <v>248414</v>
@@ -11572,16 +11572,16 @@
         <v>45128</v>
       </c>
       <c r="B558" t="n">
-        <v>9.73709774017334</v>
+        <v>9.737098693847656</v>
       </c>
       <c r="C558" t="n">
-        <v>9.753842903817384</v>
+        <v>9.753843859131761</v>
       </c>
       <c r="D558" t="n">
-        <v>9.527787821055707</v>
+        <v>9.527788754229716</v>
       </c>
       <c r="E558" t="n">
-        <v>9.628256279411108</v>
+        <v>9.628257222425235</v>
       </c>
       <c r="F558" t="n">
         <v>205537</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711981520878043</v>
+        <v>9.711980587323517</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753844014168855</v>
+        <v>9.753843076590339</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11792,16 +11792,16 @@
         <v>45145</v>
       </c>
       <c r="B569" t="n">
-        <v>9.879428863525391</v>
+        <v>9.879429817199707</v>
       </c>
       <c r="C569" t="n">
-        <v>9.988269485062169</v>
+        <v>9.988270449243014</v>
       </c>
       <c r="D569" t="n">
-        <v>9.770587400818977</v>
+        <v>9.770588343986683</v>
       </c>
       <c r="E569" t="n">
-        <v>9.988269485062169</v>
+        <v>9.988270449243014</v>
       </c>
       <c r="F569" t="n">
         <v>215967</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578022956848145</v>
+        <v>9.578023910522461</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695236584795509</v>
+        <v>9.695237550140671</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469181490562828</v>
+        <v>9.469182433399908</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686863581963795</v>
+        <v>9.686864546475267</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11892,16 +11892,16 @@
         <v>45152</v>
       </c>
       <c r="B574" t="n">
-        <v>10.74178600311279</v>
+        <v>10.74178695678711</v>
       </c>
       <c r="C574" t="n">
-        <v>10.88411611299378</v>
+        <v>10.88411707930441</v>
       </c>
       <c r="D574" t="n">
-        <v>10.23106985279666</v>
+        <v>10.23107076112871</v>
       </c>
       <c r="E574" t="n">
-        <v>10.45712494218117</v>
+        <v>10.45712587058279</v>
       </c>
       <c r="F574" t="n">
         <v>441415</v>
@@ -11932,16 +11932,16 @@
         <v>45154</v>
       </c>
       <c r="B576" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C576" t="n">
-        <v>11.2608749384303</v>
+        <v>11.26087395777899</v>
       </c>
       <c r="D576" t="n">
-        <v>10.78364824878957</v>
+        <v>10.78364730969746</v>
       </c>
       <c r="E576" t="n">
-        <v>11.05993716353692</v>
+        <v>11.05993620038423</v>
       </c>
       <c r="F576" t="n">
         <v>525379</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294521258928</v>
+        <v>10.63294612667715</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109575560148</v>
+        <v>10.95109669703995</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527578824517</v>
+        <v>10.77527669072958</v>
       </c>
       <c r="E578" t="n">
-        <v>11.0934271862458</v>
+        <v>11.09342811537701</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -11992,16 +11992,16 @@
         <v>45159</v>
       </c>
       <c r="B579" t="n">
-        <v>11.16877746582031</v>
+        <v>11.16877841949463</v>
       </c>
       <c r="C579" t="n">
-        <v>11.43669419061094</v>
+        <v>11.436695167162</v>
       </c>
       <c r="D579" t="n">
-        <v>11.04319168508056</v>
+        <v>11.04319262803141</v>
       </c>
       <c r="E579" t="n">
-        <v>11.37808738077644</v>
+        <v>11.37808835232321</v>
       </c>
       <c r="F579" t="n">
         <v>524641</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716278076172</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716278076172</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10179954134582</v>
+        <v>11.10179862365917</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877851856436</v>
+        <v>11.16877759534116</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12092,16 +12092,16 @@
         <v>45166</v>
       </c>
       <c r="B584" t="n">
-        <v>11.91392230987549</v>
+        <v>11.91392135620117</v>
       </c>
       <c r="C584" t="n">
-        <v>11.99764645448905</v>
+        <v>11.99764549411287</v>
       </c>
       <c r="D584" t="n">
-        <v>11.57065441048049</v>
+        <v>11.57065348428376</v>
       </c>
       <c r="E584" t="n">
-        <v>11.77996351025984</v>
+        <v>11.77996256730853</v>
       </c>
       <c r="F584" t="n">
         <v>779167</v>
@@ -12172,16 +12172,16 @@
         <v>45170</v>
       </c>
       <c r="B588" t="n">
-        <v>12.1232328414917</v>
+        <v>12.12323188781738</v>
       </c>
       <c r="C588" t="n">
-        <v>12.26556381015243</v>
+        <v>12.26556284528164</v>
       </c>
       <c r="D588" t="n">
-        <v>12.10648851645499</v>
+        <v>12.10648756409787</v>
       </c>
       <c r="E588" t="n">
-        <v>12.15672233273486</v>
+        <v>12.15672137642609</v>
       </c>
       <c r="F588" t="n">
         <v>195423</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625227825024</v>
+        <v>12.05625325429223</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66274975627503</v>
+        <v>11.66275070046011</v>
       </c>
       <c r="E589" t="n">
-        <v>11.9976454659665</v>
+        <v>11.99764643726385</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80508024202364</v>
+        <v>11.80507928016331</v>
       </c>
       <c r="D590" t="n">
-        <v>11.5957703116373</v>
+        <v>11.59576936683122</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996291579013</v>
+        <v>11.77996195597632</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12232,16 +12232,16 @@
         <v>45175</v>
       </c>
       <c r="B591" t="n">
-        <v>11.74647426605225</v>
+        <v>11.74647521972656</v>
       </c>
       <c r="C591" t="n">
-        <v>11.90554954393114</v>
+        <v>11.90555051052048</v>
       </c>
       <c r="D591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="E591" t="n">
-        <v>11.696239613598</v>
+        <v>11.69624056319386</v>
       </c>
       <c r="F591" t="n">
         <v>295506</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879096769665</v>
+        <v>11.52879190103679</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393436431885</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393436431885</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298458432168</v>
+        <v>11.71298276414397</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135758763992</v>
+        <v>11.72135576616107</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C599" t="n">
-        <v>11.8636870561786</v>
+        <v>11.86368608954307</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414247332525</v>
+        <v>11.60414152783702</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786661371372</v>
+        <v>11.68786566140377</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12412,16 +12412,16 @@
         <v>45189</v>
       </c>
       <c r="B600" t="n">
-        <v>11.83857154846191</v>
+        <v>11.8385705947876</v>
       </c>
       <c r="C600" t="n">
-        <v>11.91392269221347</v>
+        <v>11.91392173246913</v>
       </c>
       <c r="D600" t="n">
-        <v>11.62926160079574</v>
+        <v>11.62926066398271</v>
       </c>
       <c r="E600" t="n">
-        <v>11.62926160079574</v>
+        <v>11.62926066398271</v>
       </c>
       <c r="F600" t="n">
         <v>141695</v>
@@ -12432,16 +12432,16 @@
         <v>45190</v>
       </c>
       <c r="B601" t="n">
-        <v>11.44506645202637</v>
+        <v>11.44506740570068</v>
       </c>
       <c r="C601" t="n">
-        <v>11.83019764103224</v>
+        <v>11.83019862679808</v>
       </c>
       <c r="D601" t="n">
-        <v>11.44506645202637</v>
+        <v>11.44506740570068</v>
       </c>
       <c r="E601" t="n">
-        <v>11.83019764103224</v>
+        <v>11.83019862679808</v>
       </c>
       <c r="F601" t="n">
         <v>277385</v>
@@ -12452,16 +12452,16 @@
         <v>45191</v>
       </c>
       <c r="B602" t="n">
-        <v>11.54553699493408</v>
+        <v>11.54553604125977</v>
       </c>
       <c r="C602" t="n">
-        <v>11.73810261019376</v>
+        <v>11.73810164061331</v>
       </c>
       <c r="D602" t="n">
-        <v>11.47855801622189</v>
+        <v>11.47855706808011</v>
       </c>
       <c r="E602" t="n">
-        <v>11.52879182967118</v>
+        <v>11.52879087738004</v>
       </c>
       <c r="F602" t="n">
         <v>228714</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27761930113372</v>
+        <v>11.27762027064262</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760626903017</v>
+        <v>10.91760720758964</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901248934153</v>
+        <v>11.21901345381215</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876636505127</v>
+        <v>10.80876541137695</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854563254228</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="D608" t="n">
-        <v>10.71667005341063</v>
+        <v>10.71666910786212</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854563254228</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12592,16 +12592,16 @@
         <v>45202</v>
       </c>
       <c r="B609" t="n">
-        <v>10.58271026611328</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="C609" t="n">
-        <v>10.8924877979399</v>
+        <v>10.89248976112052</v>
       </c>
       <c r="D609" t="n">
-        <v>10.56596510271123</v>
+        <v>10.56596700704184</v>
       </c>
       <c r="E609" t="n">
-        <v>10.8924877979399</v>
+        <v>10.89248976112052</v>
       </c>
       <c r="F609" t="n">
         <v>176144</v>
@@ -12612,16 +12612,16 @@
         <v>45203</v>
       </c>
       <c r="B610" t="n">
-        <v>10.50735950469971</v>
+        <v>10.50735855102539</v>
       </c>
       <c r="C610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="D610" t="n">
-        <v>10.44037968453425</v>
+        <v>10.44037873693919</v>
       </c>
       <c r="E610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="F610" t="n">
         <v>180674</v>
@@ -12632,16 +12632,16 @@
         <v>45204</v>
       </c>
       <c r="B611" t="n">
-        <v>10.58271026611328</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="C611" t="n">
-        <v>10.58271026611328</v>
+        <v>10.58271217346191</v>
       </c>
       <c r="D611" t="n">
-        <v>10.3315378621002</v>
+        <v>10.33153972417939</v>
       </c>
       <c r="E611" t="n">
-        <v>10.50735829255848</v>
+        <v>10.50736018632623</v>
       </c>
       <c r="F611" t="n">
         <v>99766</v>
@@ -12692,16 +12692,16 @@
         <v>45209</v>
       </c>
       <c r="B614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="D614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="E614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="F614" t="n">
         <v>338699</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457153766474</v>
+        <v>10.62457244623281</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411611417709</v>
+        <v>10.88411704494031</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691593170166</v>
+        <v>11.12691688537598</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226706443887</v>
+        <v>11.20226802457144</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690290798703</v>
+        <v>10.76690383080508</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970231084856</v>
+        <v>11.00970325447664</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12752,16 +12752,16 @@
         <v>45215</v>
       </c>
       <c r="B617" t="n">
-        <v>11.02644729614258</v>
+        <v>11.02644920349121</v>
       </c>
       <c r="C617" t="n">
-        <v>11.27761971643121</v>
+        <v>11.2776216672275</v>
       </c>
       <c r="D617" t="n">
-        <v>10.95109615887475</v>
+        <v>10.95109805318919</v>
       </c>
       <c r="E617" t="n">
-        <v>11.1269166007259</v>
+        <v>11.12691852545365</v>
       </c>
       <c r="F617" t="n">
         <v>160026</v>
@@ -12772,16 +12772,16 @@
         <v>45216</v>
       </c>
       <c r="B618" t="n">
-        <v>10.57433891296387</v>
+        <v>10.57433795928955</v>
       </c>
       <c r="C618" t="n">
-        <v>11.02644830129326</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="D618" t="n">
-        <v>10.41526362109882</v>
+        <v>10.41526268177113</v>
       </c>
       <c r="E618" t="n">
-        <v>11.02644830129326</v>
+        <v>11.02644730684428</v>
       </c>
       <c r="F618" t="n">
         <v>572365</v>
@@ -12792,16 +12792,16 @@
         <v>45217</v>
       </c>
       <c r="B619" t="n">
-        <v>10.2478141784668</v>
+        <v>10.24781513214111</v>
       </c>
       <c r="C619" t="n">
-        <v>10.60782721634484</v>
+        <v>10.60782820352242</v>
       </c>
       <c r="D619" t="n">
-        <v>10.23106985549739</v>
+        <v>10.23107080761346</v>
       </c>
       <c r="E619" t="n">
-        <v>10.57433772923638</v>
+        <v>10.57433871329738</v>
       </c>
       <c r="F619" t="n">
         <v>234192</v>
@@ -12812,16 +12812,16 @@
         <v>45218</v>
       </c>
       <c r="B620" t="n">
-        <v>10.3482837677002</v>
+        <v>10.34828281402588</v>
       </c>
       <c r="C620" t="n">
-        <v>10.49061473430172</v>
+        <v>10.4906137675105</v>
       </c>
       <c r="D620" t="n">
-        <v>10.28130562735265</v>
+        <v>10.28130467985089</v>
       </c>
       <c r="E620" t="n">
-        <v>10.30642211454433</v>
+        <v>10.30642116472789</v>
       </c>
       <c r="F620" t="n">
         <v>130844</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295711517334</v>
+        <v>10.99295902252197</v>
       </c>
       <c r="C622" t="n">
-        <v>11.1352880602452</v>
+        <v>11.13528999228917</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039152097738</v>
+        <v>10.80039339491465</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82550968670904</v>
+        <v>10.82551156500447</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12892,16 +12892,16 @@
         <v>45224</v>
       </c>
       <c r="B624" t="n">
-        <v>11.25250244140625</v>
+        <v>11.25250339508057</v>
       </c>
       <c r="C624" t="n">
-        <v>11.37808823153628</v>
+        <v>11.37808919585427</v>
       </c>
       <c r="D624" t="n">
-        <v>11.06830899588992</v>
+        <v>11.06830993395344</v>
       </c>
       <c r="E624" t="n">
-        <v>11.26087460310301</v>
+        <v>11.26087555748688</v>
       </c>
       <c r="F624" t="n">
         <v>356609</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.43200778961182</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668279217249</v>
+        <v>11.07668177956321</v>
       </c>
       <c r="D627" t="n">
-        <v>10.43200778961182</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="E627" t="n">
-        <v>10.9929586456988</v>
+        <v>10.99295764074342</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -12972,16 +12972,16 @@
         <v>45230</v>
       </c>
       <c r="B628" t="n">
-        <v>10.68783950805664</v>
+        <v>10.68783855438232</v>
       </c>
       <c r="C628" t="n">
-        <v>10.70476440977975</v>
+        <v>10.70476345459523</v>
       </c>
       <c r="D628" t="n">
-        <v>10.06163174747778</v>
+        <v>10.06163084967988</v>
       </c>
       <c r="E628" t="n">
-        <v>10.57783062255122</v>
+        <v>10.57782967869298</v>
       </c>
       <c r="F628" t="n">
         <v>335223</v>
@@ -13132,16 +13132,16 @@
         <v>45243</v>
       </c>
       <c r="B636" t="n">
-        <v>12.36336803436279</v>
+        <v>12.36336708068848</v>
       </c>
       <c r="C636" t="n">
-        <v>12.51568874678828</v>
+        <v>12.51568778136439</v>
       </c>
       <c r="D636" t="n">
-        <v>12.04180170804298</v>
+        <v>12.04180077917336</v>
       </c>
       <c r="E636" t="n">
-        <v>12.1348873908238</v>
+        <v>12.13488645477382</v>
       </c>
       <c r="F636" t="n">
         <v>539496</v>
@@ -13152,16 +13152,16 @@
         <v>45244</v>
       </c>
       <c r="B637" t="n">
-        <v>12.27028369903564</v>
+        <v>12.27028274536133</v>
       </c>
       <c r="C637" t="n">
-        <v>12.65108507043216</v>
+        <v>12.6510840871611</v>
       </c>
       <c r="D637" t="n">
-        <v>12.27028369903564</v>
+        <v>12.27028274536133</v>
       </c>
       <c r="E637" t="n">
-        <v>12.36336853539025</v>
+        <v>12.36336757448117</v>
       </c>
       <c r="F637" t="n">
         <v>455532</v>
@@ -13212,16 +13212,16 @@
         <v>45250</v>
       </c>
       <c r="B640" t="n">
-        <v>12.99803638458252</v>
+        <v>12.99803733825684</v>
       </c>
       <c r="C640" t="n">
-        <v>13.12497100617093</v>
+        <v>13.12497196915852</v>
       </c>
       <c r="D640" t="n">
-        <v>12.59184814609482</v>
+        <v>12.59184906996684</v>
       </c>
       <c r="E640" t="n">
-        <v>12.73570596689768</v>
+        <v>12.73570690132464</v>
       </c>
       <c r="F640" t="n">
         <v>416026</v>
@@ -13252,16 +13252,16 @@
         <v>45252</v>
       </c>
       <c r="B642" t="n">
-        <v>12.397216796875</v>
+        <v>12.39721584320068</v>
       </c>
       <c r="C642" t="n">
-        <v>12.78648102270015</v>
+        <v>12.7864800390811</v>
       </c>
       <c r="D642" t="n">
-        <v>12.397216796875</v>
+        <v>12.39721584320068</v>
       </c>
       <c r="E642" t="n">
-        <v>12.5749235834792</v>
+        <v>12.57492261613453</v>
       </c>
       <c r="F642" t="n">
         <v>163818</v>
@@ -13312,16 +13312,16 @@
         <v>45257</v>
       </c>
       <c r="B645" t="n">
-        <v>13.20959377288818</v>
+        <v>13.20959281921387</v>
       </c>
       <c r="C645" t="n">
-        <v>13.20959377288818</v>
+        <v>13.20959281921387</v>
       </c>
       <c r="D645" t="n">
-        <v>12.48183915139878</v>
+        <v>12.48183825026513</v>
       </c>
       <c r="E645" t="n">
-        <v>12.68493457160784</v>
+        <v>12.6849336558116</v>
       </c>
       <c r="F645" t="n">
         <v>390742</v>
@@ -13372,16 +13372,16 @@
         <v>45260</v>
       </c>
       <c r="B648" t="n">
-        <v>13.37037658691406</v>
+        <v>13.37037754058838</v>
       </c>
       <c r="C648" t="n">
-        <v>13.37037658691406</v>
+        <v>13.37037754058838</v>
       </c>
       <c r="D648" t="n">
-        <v>12.70185788509813</v>
+        <v>12.70185879108874</v>
       </c>
       <c r="E648" t="n">
-        <v>13.09112210075015</v>
+        <v>13.09112303450597</v>
       </c>
       <c r="F648" t="n">
         <v>345125</v>
@@ -13412,16 +13412,16 @@
         <v>45264</v>
       </c>
       <c r="B650" t="n">
-        <v>12.76109504699707</v>
+        <v>12.76109409332275</v>
       </c>
       <c r="C650" t="n">
-        <v>13.22652008765104</v>
+        <v>13.22651909919413</v>
       </c>
       <c r="D650" t="n">
-        <v>12.76109504699707</v>
+        <v>12.76109409332275</v>
       </c>
       <c r="E650" t="n">
-        <v>13.22652008765104</v>
+        <v>13.22651909919413</v>
       </c>
       <c r="F650" t="n">
         <v>177619</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413217772953</v>
+        <v>12.30413126845579</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568877039725</v>
+        <v>12.51568784548951</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13572,16 +13572,16 @@
         <v>45274</v>
       </c>
       <c r="B658" t="n">
-        <v>13.32806491851807</v>
+        <v>13.32806587219238</v>
       </c>
       <c r="C658" t="n">
-        <v>13.35345184325137</v>
+        <v>13.35345279874222</v>
       </c>
       <c r="D658" t="n">
-        <v>12.97264967264859</v>
+        <v>12.97265060089158</v>
       </c>
       <c r="E658" t="n">
-        <v>13.27729106905145</v>
+        <v>13.2772920190927</v>
       </c>
       <c r="F658" t="n">
         <v>222288</v>
@@ -13632,16 +13632,16 @@
         <v>45279</v>
       </c>
       <c r="B661" t="n">
-        <v>13.3957633972168</v>
+        <v>13.39576435089111</v>
       </c>
       <c r="C661" t="n">
-        <v>13.4549992740911</v>
+        <v>13.45500023198255</v>
       </c>
       <c r="D661" t="n">
-        <v>13.17574479034014</v>
+        <v>13.17574572835084</v>
       </c>
       <c r="E661" t="n">
-        <v>13.20959289118437</v>
+        <v>13.20959383160479</v>
       </c>
       <c r="F661" t="n">
         <v>220918</v>
@@ -26625,6 +26625,26 @@
       </c>
       <c r="F1310" t="n">
         <v>1636800</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1311" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C1311" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>834400</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1312"/>
+  <dimension ref="A1:F1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.28566074371338</v>
+        <v>13.2856616973877</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24646867427303</v>
+        <v>14.24646969691628</v>
       </c>
       <c r="D3" t="n">
-        <v>12.8301045707031</v>
+        <v>12.83010549167658</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24646867427303</v>
+        <v>14.24646969691628</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -512,16 +512,16 @@
         <v>44321</v>
       </c>
       <c r="B5" t="n">
-        <v>12.93778324127197</v>
+        <v>12.93778419494629</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3353587586459</v>
+        <v>13.33535974162644</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92949897903101</v>
+        <v>12.92949993209467</v>
       </c>
       <c r="E5" t="n">
-        <v>13.32707532857593</v>
+        <v>13.32707631094588</v>
       </c>
       <c r="F5" t="n">
         <v>876510</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C9" t="n">
-        <v>12.54848908114925</v>
+        <v>12.54849100757134</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717518992304</v>
+        <v>12.2171770654824</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566104888916</v>
+        <v>12.46566200256348</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75555946570089</v>
+        <v>12.75556044155362</v>
       </c>
       <c r="D10" t="n">
-        <v>12.3000040974216</v>
+        <v>12.30000503842248</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141875137399</v>
+        <v>12.34141969554326</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162086486816</v>
+        <v>13.40162181854248</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172209598015</v>
+        <v>13.93172308737706</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566069664867</v>
+        <v>12.46566158371901</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273229621742</v>
+        <v>12.67273319802321</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83233070373535</v>
+        <v>13.83232975006104</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677421586986</v>
+        <v>14.19677323706887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101675563449</v>
+        <v>13.50101582480272</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56728004455733</v>
+        <v>13.56727910915701</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98141956329346</v>
+        <v>13.98142051696777</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778324950092</v>
+        <v>14.57778424385328</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495429020224</v>
+        <v>13.67495522297252</v>
       </c>
       <c r="E13" t="n">
-        <v>13.98970299328094</v>
+        <v>13.98970394752027</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.8488941192627</v>
+        <v>13.84889507293701</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24646964076982</v>
+        <v>14.24647062182232</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323799870598</v>
+        <v>13.68323894097274</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222817448053</v>
+        <v>14.12222914697741</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21939945220947</v>
+        <v>13.21940040588379</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48445008239211</v>
+        <v>13.48445105518772</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -812,16 +812,16 @@
         <v>44342</v>
       </c>
       <c r="B20" t="n">
-        <v>13.27737808227539</v>
+        <v>13.27737903594971</v>
       </c>
       <c r="C20" t="n">
-        <v>13.51758091098307</v>
+        <v>13.51758188191043</v>
       </c>
       <c r="D20" t="n">
-        <v>13.26081288647065</v>
+        <v>13.26081383895514</v>
       </c>
       <c r="E20" t="n">
-        <v>13.36848915571444</v>
+        <v>13.36849011593299</v>
       </c>
       <c r="F20" t="n">
         <v>382946</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889633178711</v>
+        <v>13.02889442443848</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879479267196</v>
+        <v>13.31879284288401</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263304182351</v>
+        <v>12.96263114417541</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111850680197</v>
+        <v>13.21111657277715</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980365753174</v>
+        <v>12.87980270385742</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111758778895</v>
+        <v>13.21111660958277</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6147530126286</v>
+        <v>12.61475207857974</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374322126546</v>
+        <v>13.05374225471193</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253009796143</v>
+        <v>13.25253200531006</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707514235259</v>
+        <v>13.32707706042999</v>
       </c>
       <c r="D24" t="n">
-        <v>12.8466719883597</v>
+        <v>12.84667383729587</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061070266274</v>
+        <v>13.02061257663275</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95434951782227</v>
+        <v>12.95434761047363</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879384183405</v>
+        <v>13.31879188082604</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808623258925</v>
+        <v>12.88808433499697</v>
       </c>
       <c r="E25" t="n">
-        <v>13.2525313887721</v>
+        <v>13.25252943752032</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -972,16 +972,16 @@
         <v>44355</v>
       </c>
       <c r="B28" t="n">
-        <v>12.44909572601318</v>
+        <v>12.44909763336182</v>
       </c>
       <c r="C28" t="n">
-        <v>12.73899413986676</v>
+        <v>12.73899609163126</v>
       </c>
       <c r="D28" t="n">
-        <v>12.42424710032951</v>
+        <v>12.42424900387104</v>
       </c>
       <c r="E28" t="n">
-        <v>12.69758031850796</v>
+        <v>12.69758226392737</v>
       </c>
       <c r="F28" t="n">
         <v>727440</v>
@@ -992,16 +992,16 @@
         <v>44356</v>
       </c>
       <c r="B29" t="n">
-        <v>12.73071098327637</v>
+        <v>12.73071193695068</v>
       </c>
       <c r="C29" t="n">
-        <v>12.7389935807504</v>
+        <v>12.73899453504518</v>
       </c>
       <c r="D29" t="n">
-        <v>12.5319228187028</v>
+        <v>12.53192375748563</v>
       </c>
       <c r="E29" t="n">
-        <v>12.5319228187028</v>
+        <v>12.53192375748563</v>
       </c>
       <c r="F29" t="n">
         <v>453530</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95434951782227</v>
+        <v>12.95434761047363</v>
       </c>
       <c r="C30" t="n">
-        <v>13.0040459415332</v>
+        <v>13.00404402686745</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72243009993438</v>
+        <v>12.72242822673267</v>
       </c>
       <c r="E30" t="n">
-        <v>12.8218237795273</v>
+        <v>12.82182189169125</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667301177979</v>
+        <v>12.84667110443115</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576311243925</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75556026805076</v>
+        <v>12.75555837422966</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576311243925</v>
+        <v>12.99576118295518</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1092,16 +1092,16 @@
         <v>44363</v>
       </c>
       <c r="B34" t="n">
-        <v>12.77212619781494</v>
+        <v>12.77212715148926</v>
       </c>
       <c r="C34" t="n">
-        <v>12.88808506407426</v>
+        <v>12.88808602640704</v>
       </c>
       <c r="D34" t="n">
-        <v>12.67273252723367</v>
+        <v>12.67273347348642</v>
       </c>
       <c r="E34" t="n">
-        <v>12.83010521485911</v>
+        <v>12.83010617286263</v>
       </c>
       <c r="F34" t="n">
         <v>265902</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414566040039</v>
+        <v>12.71414661407471</v>
       </c>
       <c r="C35" t="n">
-        <v>12.8632365742877</v>
+        <v>12.86323753914516</v>
       </c>
       <c r="D35" t="n">
-        <v>12.58990337085612</v>
+        <v>12.58990431521116</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384290908647</v>
+        <v>12.76384386648853</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1172,16 +1172,16 @@
         <v>44369</v>
       </c>
       <c r="B38" t="n">
-        <v>12.39939880371094</v>
+        <v>12.3993968963623</v>
       </c>
       <c r="C38" t="n">
-        <v>12.66444944887451</v>
+        <v>12.66444750075422</v>
       </c>
       <c r="D38" t="n">
-        <v>12.22546007197737</v>
+        <v>12.22545819138502</v>
       </c>
       <c r="E38" t="n">
-        <v>12.51535934515176</v>
+        <v>12.51535741996539</v>
       </c>
       <c r="F38" t="n">
         <v>779904</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C39" t="n">
-        <v>12.49051027219619</v>
+        <v>12.4905092885157</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424782130851</v>
+        <v>12.42424684284646</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C40" t="n">
-        <v>12.51535774406464</v>
+        <v>12.51535967959436</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717696766745</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657123565674</v>
+        <v>12.31657218933105</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424750758757</v>
+        <v>12.42424846959927</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293359717298</v>
+        <v>12.09293453353099</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596490947851</v>
+        <v>12.41596587084889</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525684356689</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43252913940544</v>
+        <v>12.43253006532078</v>
       </c>
       <c r="E44" t="n">
-        <v>12.5899034842721</v>
+        <v>12.58990442190792</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54849097075757</v>
+        <v>12.54848903140645</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768346117107</v>
+        <v>12.40768154358154</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C50" t="n">
-        <v>12.6561672526666</v>
+        <v>12.65616529667426</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576320308654</v>
+        <v>12.17576132133995</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25859168836578</v>
+        <v>12.25858979381817</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717548370361</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020776395842</v>
+        <v>12.54020678506824</v>
       </c>
       <c r="D51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717548370361</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424805662318</v>
+        <v>12.42424708678483</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1452,16 +1452,16 @@
         <v>44390</v>
       </c>
       <c r="B52" t="n">
-        <v>12.09293556213379</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C52" t="n">
-        <v>12.30828897315887</v>
+        <v>12.3082870318438</v>
       </c>
       <c r="D52" t="n">
-        <v>12.05152173268821</v>
+        <v>12.05151983187154</v>
       </c>
       <c r="E52" t="n">
-        <v>12.21717788264168</v>
+        <v>12.21717595569702</v>
       </c>
       <c r="F52" t="n">
         <v>433935</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121631622314</v>
+        <v>12.10121822357178</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030723427872</v>
+        <v>12.25030916512651</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293288642992</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293288642992</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10949993133545</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16747978390493</v>
+        <v>12.16747882566446</v>
       </c>
       <c r="D55" t="n">
-        <v>11.89414654986496</v>
+        <v>11.89414561315063</v>
       </c>
       <c r="E55" t="n">
-        <v>12.06808610757341</v>
+        <v>12.0680851571606</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1532,16 +1532,16 @@
         <v>44396</v>
       </c>
       <c r="B56" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C56" t="n">
-        <v>12.02667163783278</v>
+        <v>12.02667065225621</v>
       </c>
       <c r="D56" t="n">
-        <v>11.53798501475665</v>
+        <v>11.53798406922757</v>
       </c>
       <c r="E56" t="n">
-        <v>12.01010644093992</v>
+        <v>12.01010545672085</v>
       </c>
       <c r="F56" t="n">
         <v>557721</v>
@@ -1552,16 +1552,16 @@
         <v>44397</v>
       </c>
       <c r="B57" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C57" t="n">
-        <v>11.86929761452057</v>
+        <v>11.86929859769704</v>
       </c>
       <c r="D57" t="n">
-        <v>11.37232758142605</v>
+        <v>11.37232852343671</v>
       </c>
       <c r="E57" t="n">
-        <v>11.67879203295168</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="F57" t="n">
         <v>1030110</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303604125977</v>
       </c>
       <c r="C58" t="n">
-        <v>11.67050888395185</v>
+        <v>11.67051091068954</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303413391113</v>
+        <v>10.98303604125977</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970139416144</v>
+        <v>11.52970339644604</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C63" t="n">
-        <v>11.51313582037561</v>
+        <v>11.5131367879722</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495313710418</v>
+        <v>11.21495407964066</v>
       </c>
       <c r="E63" t="n">
-        <v>11.3640448948254</v>
+        <v>11.36404584989197</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1692,16 +1692,16 @@
         <v>44406</v>
       </c>
       <c r="B64" t="n">
-        <v>11.30606460571289</v>
+        <v>11.30606555938721</v>
       </c>
       <c r="C64" t="n">
-        <v>11.45515552548068</v>
+        <v>11.45515649173092</v>
       </c>
       <c r="D64" t="n">
-        <v>11.01616536389469</v>
+        <v>11.01616629311581</v>
       </c>
       <c r="E64" t="n">
-        <v>11.3391958287534</v>
+        <v>11.33919678522236</v>
       </c>
       <c r="F64" t="n">
         <v>449738</v>
@@ -1732,16 +1732,16 @@
         <v>44410</v>
       </c>
       <c r="B66" t="n">
-        <v>11.91071033477783</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C66" t="n">
-        <v>11.92727636162177</v>
+        <v>11.92727731662251</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61252934112532</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="E66" t="n">
-        <v>11.61252934112532</v>
+        <v>11.61253027092469</v>
       </c>
       <c r="F66" t="n">
         <v>406966</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273170471191</v>
+        <v>11.85273265838623</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556018308474</v>
+        <v>11.93556114342346</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030754683281</v>
+        <v>11.43030846651876</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727758489877</v>
+        <v>11.92727854457107</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515632629395</v>
+        <v>11.45515727996826</v>
       </c>
       <c r="C68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="D68" t="n">
-        <v>11.44687372799754</v>
+        <v>11.4468746809823</v>
       </c>
       <c r="E68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283283233643</v>
+        <v>11.56283187866211</v>
       </c>
       <c r="C70" t="n">
-        <v>11.59596489052797</v>
+        <v>11.595963934121</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495371086467</v>
+        <v>11.21495278588257</v>
       </c>
       <c r="E70" t="n">
-        <v>11.2812169950767</v>
+        <v>11.28121606462938</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1872,16 +1872,16 @@
         <v>44419</v>
       </c>
       <c r="B73" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586235046387</v>
       </c>
       <c r="C73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.0183872343875</v>
       </c>
       <c r="D73" t="n">
-        <v>11.71192469562211</v>
+        <v>11.71192281618591</v>
       </c>
       <c r="E73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.0183872343875</v>
       </c>
       <c r="F73" t="n">
         <v>262426</v>
@@ -1892,16 +1892,16 @@
         <v>44420</v>
       </c>
       <c r="B74" t="n">
-        <v>12.0763692855835</v>
+        <v>12.07636737823486</v>
       </c>
       <c r="C74" t="n">
-        <v>12.24202625292564</v>
+        <v>12.24202431941305</v>
       </c>
       <c r="D74" t="n">
-        <v>11.81131863713872</v>
+        <v>11.81131677165233</v>
       </c>
       <c r="E74" t="n">
-        <v>11.95212614399135</v>
+        <v>11.95212425626575</v>
       </c>
       <c r="F74" t="n">
         <v>242515</v>
@@ -1912,16 +1912,16 @@
         <v>44421</v>
       </c>
       <c r="B75" t="n">
-        <v>12.50707721710205</v>
+        <v>12.50707530975342</v>
       </c>
       <c r="C75" t="n">
-        <v>12.61475349963868</v>
+        <v>12.61475157586925</v>
       </c>
       <c r="D75" t="n">
-        <v>11.87758222321873</v>
+        <v>11.87758041186906</v>
       </c>
       <c r="E75" t="n">
-        <v>12.0018237036051</v>
+        <v>12.00182187330842</v>
       </c>
       <c r="F75" t="n">
         <v>464803</v>
@@ -1932,16 +1932,16 @@
         <v>44424</v>
       </c>
       <c r="B76" t="n">
-        <v>11.74505615234375</v>
+        <v>11.74505519866943</v>
       </c>
       <c r="C76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="D76" t="n">
-        <v>11.40545961983211</v>
+        <v>11.40545869373233</v>
       </c>
       <c r="E76" t="n">
-        <v>12.50707686865033</v>
+        <v>12.50707585310151</v>
       </c>
       <c r="F76" t="n">
         <v>788964</v>
@@ -1992,16 +1992,16 @@
         <v>44427</v>
       </c>
       <c r="B79" t="n">
-        <v>12.09293556213379</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C79" t="n">
-        <v>12.19233008427702</v>
+        <v>12.19232816125147</v>
       </c>
       <c r="D79" t="n">
-        <v>11.54626901903062</v>
+        <v>11.54626719790453</v>
       </c>
       <c r="E79" t="n">
-        <v>11.59596628010223</v>
+        <v>11.59596445113769</v>
       </c>
       <c r="F79" t="n">
         <v>301405</v>
@@ -2012,16 +2012,16 @@
         <v>44428</v>
       </c>
       <c r="B80" t="n">
-        <v>12.09293556213379</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>12.12606679212448</v>
+        <v>12.12606487955025</v>
       </c>
       <c r="D80" t="n">
-        <v>11.87758298327986</v>
+        <v>11.87758110989754</v>
       </c>
       <c r="E80" t="n">
-        <v>12.05980516431425</v>
+        <v>12.05980326219108</v>
       </c>
       <c r="F80" t="n">
         <v>324055</v>
@@ -2052,16 +2052,16 @@
         <v>44432</v>
       </c>
       <c r="B82" t="n">
-        <v>11.91071033477783</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C82" t="n">
-        <v>12.324852684167</v>
+        <v>12.32485367100113</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76990201920261</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E82" t="n">
-        <v>12.01010483149961</v>
+        <v>12.0101057931323</v>
       </c>
       <c r="F82" t="n">
         <v>265586</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010599913494</v>
+        <v>12.01010696614738</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071149274992</v>
+        <v>11.91071245175947</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848796844482</v>
+        <v>11.72848987579346</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697337316509</v>
+        <v>11.97697532092373</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081170868654</v>
+        <v>11.62081359852429</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444765754676</v>
+        <v>11.84444958375337</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.57939910888672</v>
+        <v>11.57939720153809</v>
       </c>
       <c r="C86" t="n">
-        <v>11.96869289533168</v>
+        <v>11.96869092385892</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55455048079756</v>
+        <v>11.55454857754198</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101495216464</v>
+        <v>11.86101299842849</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="D87" t="n">
-        <v>11.38889235890981</v>
+        <v>11.388893311891</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707503354038</v>
+        <v>11.68707601147242</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737827423737</v>
+        <v>11.63737923751014</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576244764404</v>
+        <v>11.35576338760633</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313597332352</v>
+        <v>11.51313692631225</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C89" t="n">
-        <v>11.62909547100532</v>
+        <v>11.6290964280881</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010529430325</v>
+        <v>11.19010621525682</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55454959246905</v>
+        <v>11.55455054341664</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2232,16 +2232,16 @@
         <v>44445</v>
       </c>
       <c r="B91" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61252975463867</v>
       </c>
       <c r="C91" t="n">
-        <v>11.7284905443865</v>
+        <v>11.72848861799172</v>
       </c>
       <c r="D91" t="n">
-        <v>11.2646525182764</v>
+        <v>11.26465066806662</v>
       </c>
       <c r="E91" t="n">
-        <v>11.3474801725371</v>
+        <v>11.34747830872295</v>
       </c>
       <c r="F91" t="n">
         <v>145382</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889217376709</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111514757098</v>
+        <v>11.57111611650414</v>
       </c>
       <c r="D93" t="n">
-        <v>11.18182223914229</v>
+        <v>11.18182317547715</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141789724528</v>
+        <v>11.52141886201694</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909565647244</v>
+        <v>11.62909470007334</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38061022289286</v>
+        <v>11.38060928692969</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485335576816</v>
+        <v>11.50485240958699</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.57939910888672</v>
+        <v>11.57939720153809</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444975488591</v>
+        <v>11.84444780387837</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545954443371</v>
+        <v>11.40545766573625</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596513833651</v>
+        <v>11.59596322825914</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364189147949</v>
+        <v>11.70364093780518</v>
       </c>
       <c r="C96" t="n">
-        <v>11.83616679434145</v>
+        <v>11.8361658298683</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172164712899</v>
+        <v>11.47172071235275</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313630340163</v>
+        <v>11.51313536525071</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444903317125</v>
+        <v>11.84444805906109</v>
       </c>
       <c r="D97" t="n">
-        <v>11.587681001457</v>
+        <v>11.58768004846393</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192413433229</v>
+        <v>11.71192317112123</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313595390284</v>
+        <v>11.51313500704049</v>
       </c>
       <c r="E98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889217376709</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424637039778</v>
+        <v>11.60424734210526</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606453278556</v>
+        <v>11.30606547952412</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596377273382</v>
+        <v>11.59596474374774</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C100" t="n">
-        <v>11.64566120833546</v>
+        <v>11.6456602402011</v>
       </c>
       <c r="D100" t="n">
-        <v>11.05758091156711</v>
+        <v>11.0575799923214</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26465169645404</v>
+        <v>11.26465075999399</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2432,16 +2432,16 @@
         <v>44460</v>
       </c>
       <c r="B101" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C101" t="n">
-        <v>11.67879203295168</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="D101" t="n">
-        <v>11.33919635684255</v>
+        <v>11.33919729610883</v>
       </c>
       <c r="E101" t="n">
-        <v>11.48000385327967</v>
+        <v>11.48000480420954</v>
       </c>
       <c r="F101" t="n">
         <v>218811</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.34141826629639</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677298006055</v>
+        <v>11.73677116615927</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76162160886144</v>
+        <v>11.76161979111983</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="D104" t="n">
-        <v>11.9935395446462</v>
+        <v>11.99354049373239</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34141864029437</v>
+        <v>12.34141961690932</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2512,16 +2512,16 @@
         <v>44466</v>
       </c>
       <c r="B105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586235046387</v>
       </c>
       <c r="C105" t="n">
-        <v>12.16748009742714</v>
+        <v>12.16747814488704</v>
       </c>
       <c r="D105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586235046387</v>
       </c>
       <c r="E105" t="n">
-        <v>12.05152038930021</v>
+        <v>12.0515184553684</v>
       </c>
       <c r="F105" t="n">
         <v>207539</v>
@@ -2532,16 +2532,16 @@
         <v>44467</v>
       </c>
       <c r="B106" t="n">
-        <v>11.94384384155273</v>
+        <v>11.94384288787842</v>
       </c>
       <c r="C106" t="n">
-        <v>12.09293478299056</v>
+        <v>12.09293381741185</v>
       </c>
       <c r="D106" t="n">
-        <v>11.74505647441637</v>
+        <v>11.74505553661453</v>
       </c>
       <c r="E106" t="n">
-        <v>11.86101535582703</v>
+        <v>11.86101440876628</v>
       </c>
       <c r="F106" t="n">
         <v>282337</v>
@@ -2552,16 +2552,16 @@
         <v>44468</v>
       </c>
       <c r="B107" t="n">
-        <v>11.90242958068848</v>
+        <v>11.90242862701416</v>
       </c>
       <c r="C107" t="n">
-        <v>12.03495448727948</v>
+        <v>12.03495352298669</v>
       </c>
       <c r="D107" t="n">
-        <v>11.61253113947789</v>
+        <v>11.6125302090315</v>
       </c>
       <c r="E107" t="n">
-        <v>12.00182326063173</v>
+        <v>12.00182229899356</v>
       </c>
       <c r="F107" t="n">
         <v>186890</v>
@@ -2572,16 +2572,16 @@
         <v>44469</v>
       </c>
       <c r="B108" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="D108" t="n">
-        <v>11.51313638724631</v>
+        <v>11.51313544375356</v>
       </c>
       <c r="E108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="F108" t="n">
         <v>264322</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889282102754</v>
+        <v>11.38889188438319</v>
       </c>
       <c r="E109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545885919616</v>
+        <v>11.40545977752449</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596444165342</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010550156678</v>
+        <v>12.01010650652883</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717578887939</v>
+        <v>11.39717674255371</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444855256879</v>
+        <v>11.84444954366927</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.40546035766602</v>
+        <v>11.4054594039917</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939993452127</v>
+        <v>11.57939896630289</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38061172780511</v>
+        <v>11.38061077620852</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43859241892798</v>
+        <v>11.43859146248331</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677192873634</v>
+        <v>11.73677096348174</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2752,16 +2752,16 @@
         <v>44483</v>
       </c>
       <c r="B117" t="n">
-        <v>11.93556022644043</v>
+        <v>11.93556118011475</v>
       </c>
       <c r="C117" t="n">
-        <v>12.0266713033302</v>
+        <v>12.02667226428446</v>
       </c>
       <c r="D117" t="n">
-        <v>11.81960052273145</v>
+        <v>11.81960146714036</v>
       </c>
       <c r="E117" t="n">
-        <v>12.01838870511413</v>
+        <v>12.0183896654066</v>
       </c>
       <c r="F117" t="n">
         <v>96605</v>
@@ -2772,16 +2772,16 @@
         <v>44484</v>
       </c>
       <c r="B118" t="n">
-        <v>12.09293556213379</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="C118" t="n">
-        <v>12.09293556213379</v>
+        <v>12.09293365478516</v>
       </c>
       <c r="D118" t="n">
-        <v>11.84445092111801</v>
+        <v>11.84444905296142</v>
       </c>
       <c r="E118" t="n">
-        <v>11.92727941218032</v>
+        <v>11.92727753095967</v>
       </c>
       <c r="F118" t="n">
         <v>256632</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747856140137</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22546032458287</v>
+        <v>12.22545840814544</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727844663413</v>
+        <v>11.92727657693906</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465198439289</v>
+        <v>12.08465009002827</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2812,16 +2812,16 @@
         <v>44488</v>
       </c>
       <c r="B120" t="n">
-        <v>12.0763692855835</v>
+        <v>12.07636737823486</v>
       </c>
       <c r="C120" t="n">
-        <v>12.29172267739142</v>
+        <v>12.29172073602975</v>
       </c>
       <c r="D120" t="n">
-        <v>11.93556094655978</v>
+        <v>11.9355590614505</v>
       </c>
       <c r="E120" t="n">
-        <v>12.10950051261771</v>
+        <v>12.10949860003631</v>
       </c>
       <c r="F120" t="n">
         <v>251785</v>
@@ -2832,16 +2832,16 @@
         <v>44489</v>
       </c>
       <c r="B121" t="n">
-        <v>11.80303573608398</v>
+        <v>11.80303478240967</v>
       </c>
       <c r="C121" t="n">
-        <v>12.20061128248158</v>
+        <v>12.20061029668353</v>
       </c>
       <c r="D121" t="n">
-        <v>11.72848985303822</v>
+        <v>11.72848890538714</v>
       </c>
       <c r="E121" t="n">
-        <v>12.01838912237555</v>
+        <v>12.01838815130088</v>
       </c>
       <c r="F121" t="n">
         <v>129580</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D122" t="n">
-        <v>11.4137414573379</v>
+        <v>11.41374237633313</v>
       </c>
       <c r="E122" t="n">
-        <v>11.67879208741291</v>
+        <v>11.6787930277491</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172059900599</v>
+        <v>11.47172236012447</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141784912412</v>
+        <v>11.52141961787203</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C125" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="D125" t="n">
-        <v>11.8444491374672</v>
+        <v>11.84444821601161</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030810003457</v>
+        <v>12.25030714700461</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030756745856</v>
+        <v>12.25030853686361</v>
       </c>
       <c r="D126" t="n">
-        <v>11.8444486225357</v>
+        <v>11.84444955982386</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717551172646</v>
+        <v>12.21717647850966</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980324204109</v>
+        <v>12.05980225021978</v>
       </c>
       <c r="D127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010598889097</v>
+        <v>12.01010500115686</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2992,16 +2992,16 @@
         <v>44501</v>
       </c>
       <c r="B129" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C129" t="n">
-        <v>11.6539434064713</v>
+        <v>11.65394437180921</v>
       </c>
       <c r="D129" t="n">
-        <v>11.36404498332293</v>
+        <v>11.36404592464751</v>
       </c>
       <c r="E129" t="n">
-        <v>11.50485331193106</v>
+        <v>11.5048542649193</v>
       </c>
       <c r="F129" t="n">
         <v>1267357</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727787522379</v>
+        <v>11.92727688367788</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899473567608</v>
+        <v>11.09899381298753</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81960076750101</v>
+        <v>11.81959978490659</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283197400976</v>
+        <v>11.56283288901272</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707510257767</v>
+        <v>11.68707602741238</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929850548507</v>
+        <v>11.86929758022087</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05152067045827</v>
+        <v>12.05151973098904</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232749938965</v>
+        <v>12.19232940673828</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374406605356</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465040062008</v>
+        <v>12.08465229112388</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374406605356</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3152,16 +3152,16 @@
         <v>44512</v>
       </c>
       <c r="B137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586235046387</v>
       </c>
       <c r="C137" t="n">
-        <v>12.23374338219328</v>
+        <v>12.23374141901978</v>
       </c>
       <c r="D137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586235046387</v>
       </c>
       <c r="E137" t="n">
-        <v>12.14263230183227</v>
+        <v>12.14263035327955</v>
       </c>
       <c r="F137" t="n">
         <v>236720</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16748046875</v>
+        <v>12.16747856140137</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576306753439</v>
+        <v>12.17576115888739</v>
       </c>
       <c r="D138" t="n">
-        <v>11.68707642451825</v>
+        <v>11.68707459247675</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242981810988</v>
+        <v>11.90242795231003</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364078596598</v>
+        <v>12.52364177700074</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131739897459</v>
+        <v>11.81131833364097</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313751220703</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566049440077</v>
+        <v>12.46566242224469</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010514638517</v>
+        <v>12.01010700377637</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05151896632442</v>
+        <v>12.05152083012037</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.98748111724854</v>
+        <v>12.98748016357422</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374357221301</v>
+        <v>13.05374261367302</v>
       </c>
       <c r="D142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="E142" t="n">
-        <v>12.3579852985728</v>
+        <v>12.35798439112253</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89636829992451</v>
+        <v>12.89636928852036</v>
       </c>
       <c r="D144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010502169696</v>
+        <v>12.83010600521327</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010578155518</v>
+        <v>12.83010673522949</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010578155518</v>
+        <v>12.83010673522949</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283299592728</v>
+        <v>12.38283391635538</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131843161235</v>
+        <v>12.63131937051061</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455177307129</v>
+        <v>12.37455081939697</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818860682649</v>
+        <v>12.59818763591707</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90243030818464</v>
+        <v>11.90242939089549</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818860682649</v>
+        <v>12.59818763591707</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3392,16 +3392,16 @@
         <v>44531</v>
       </c>
       <c r="B149" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C149" t="n">
-        <v>12.58990445376748</v>
+        <v>12.58990549663439</v>
       </c>
       <c r="D149" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E149" t="n">
-        <v>12.37455024571821</v>
+        <v>12.37455127074656</v>
       </c>
       <c r="F149" t="n">
         <v>554877</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808502197266</v>
+        <v>11.24808597564697</v>
       </c>
       <c r="C150" t="n">
-        <v>11.8196000891662</v>
+        <v>11.8196010912967</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182257433274</v>
+        <v>11.18182352238896</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333764152628</v>
+        <v>11.75333863803869</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67050929318926</v>
+        <v>11.67051025368041</v>
       </c>
       <c r="D151" t="n">
-        <v>11.24808514466335</v>
+        <v>11.2480860703887</v>
       </c>
       <c r="E151" t="n">
-        <v>11.3391962192048</v>
+        <v>11.33919715242866</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626857588447</v>
+        <v>12.36626761187925</v>
       </c>
       <c r="D154" t="n">
-        <v>11.8941471338307</v>
+        <v>11.89414620662944</v>
       </c>
       <c r="E154" t="n">
-        <v>12.01010684466293</v>
+        <v>12.0101059084221</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C155" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99354006605936</v>
+        <v>11.99353913300503</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22545947324071</v>
+        <v>12.22545852214389</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000495910645</v>
+        <v>12.30000591278076</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626824363818</v>
+        <v>12.36626920245019</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778279902904</v>
+        <v>12.11778373857486</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668737329261</v>
+        <v>12.26687468403161</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485485076904</v>
+        <v>12.32485389709473</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303589683919</v>
+        <v>12.62303492009218</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374376753817</v>
+        <v>12.23374282091386</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000539004934</v>
+        <v>12.30000443829783</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.25859069824219</v>
+        <v>12.25858974456787</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192392863263</v>
+        <v>12.53192295369397</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606496606526</v>
+        <v>12.12606402270097</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909628221446</v>
+        <v>12.44909531371949</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606590270996</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606590270996</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25859030161671</v>
+        <v>12.25858939858541</v>
       </c>
       <c r="E161" t="n">
-        <v>12.4242472534353</v>
+        <v>12.42424633820085</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="C164" t="n">
-        <v>12.8218240737915</v>
+        <v>12.82182216644287</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43253111290434</v>
+        <v>12.43252926346614</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72243039191747</v>
+        <v>12.72242849935444</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.83838844299316</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495530382653</v>
+        <v>12.85495434892158</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020741661029</v>
+        <v>12.54020648508576</v>
       </c>
       <c r="E165" t="n">
-        <v>12.8135406482562</v>
+        <v>12.81353969642765</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3792,16 +3792,16 @@
         <v>44560</v>
       </c>
       <c r="B169" t="n">
-        <v>13.13657093048096</v>
+        <v>13.13657188415527</v>
       </c>
       <c r="C169" t="n">
-        <v>13.33535911049843</v>
+        <v>13.33536007860415</v>
       </c>
       <c r="D169" t="n">
-        <v>13.10343887366887</v>
+        <v>13.1034398249379</v>
       </c>
       <c r="E169" t="n">
-        <v>13.21111681005164</v>
+        <v>13.21111776913776</v>
       </c>
       <c r="F169" t="n">
         <v>310044</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970188140869</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98748025665069</v>
+        <v>12.98748125957582</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970188140869</v>
+        <v>12.34970283508301</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92949957218493</v>
+        <v>12.92950057063265</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3852,16 +3852,16 @@
         <v>44566</v>
       </c>
       <c r="B172" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61252975463867</v>
       </c>
       <c r="C172" t="n">
-        <v>12.39939937049056</v>
+        <v>12.39939733389957</v>
       </c>
       <c r="D172" t="n">
-        <v>11.6125316619873</v>
+        <v>11.61252975463867</v>
       </c>
       <c r="E172" t="n">
-        <v>12.35798554336021</v>
+        <v>12.3579835135714</v>
       </c>
       <c r="F172" t="n">
         <v>223973</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616729767829</v>
+        <v>11.83616633728321</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47172213496768</v>
+        <v>11.47172120414394</v>
       </c>
       <c r="E173" t="n">
-        <v>11.63737910276078</v>
+        <v>11.63737815849552</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.69535827636719</v>
+        <v>11.6953592300415</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78646935368979</v>
+        <v>11.78647031479358</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657009304013</v>
+        <v>11.49657103050467</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333812849712</v>
+        <v>11.75333908689929</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586369832469</v>
+        <v>11.88586465533357</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202488765067</v>
+        <v>11.42202580731284</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55454978660266</v>
+        <v>11.55455071693529</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727838031317</v>
+        <v>11.92727741252527</v>
       </c>
       <c r="D176" t="n">
-        <v>11.61253130654579</v>
+        <v>11.61253036429669</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444989641662</v>
+        <v>11.84444893534948</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838946294805</v>
+        <v>12.01838848776734</v>
       </c>
       <c r="D177" t="n">
-        <v>11.64566170149911</v>
+        <v>11.6456607565618</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818744216781</v>
+        <v>11.77818648647726</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071205965744</v>
+        <v>11.91071108497109</v>
       </c>
       <c r="D178" t="n">
-        <v>11.5959649935801</v>
+        <v>11.59596404465037</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273220556355</v>
+        <v>11.85273123562185</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131866929222</v>
+        <v>11.81131771091337</v>
       </c>
       <c r="D179" t="n">
-        <v>11.52970282264924</v>
+        <v>11.5297018871209</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67051032988519</v>
+        <v>11.67050938293163</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.57939910888672</v>
+        <v>11.57939720153809</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818730142888</v>
+        <v>11.77818536133603</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798528351884</v>
+        <v>11.53798338299186</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333867333973</v>
+        <v>11.75333673733992</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4032,16 +4032,16 @@
         <v>44579</v>
       </c>
       <c r="B181" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="C181" t="n">
-        <v>11.72020740703434</v>
+        <v>11.72020837925999</v>
       </c>
       <c r="D181" t="n">
-        <v>11.46343936054156</v>
+        <v>11.46344031146755</v>
       </c>
       <c r="E181" t="n">
-        <v>11.57939906978533</v>
+        <v>11.57940003033051</v>
       </c>
       <c r="F181" t="n">
         <v>311203</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111740112305</v>
+        <v>11.57111549377441</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101586536</v>
+        <v>11.86101391022536</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828891183915</v>
+        <v>11.48828701814372</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707711968628</v>
+        <v>11.68707519322319</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4152,16 +4152,16 @@
         <v>44587</v>
       </c>
       <c r="B187" t="n">
-        <v>11.0161657333374</v>
+        <v>11.01616668701172</v>
       </c>
       <c r="C187" t="n">
-        <v>12.08465083286823</v>
+        <v>12.08465187904177</v>
       </c>
       <c r="D187" t="n">
-        <v>10.90020603272125</v>
+        <v>10.90020697635688</v>
       </c>
       <c r="E187" t="n">
-        <v>11.88586348795854</v>
+        <v>11.88586451692297</v>
       </c>
       <c r="F187" t="n">
         <v>1763028</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374131522813</v>
+        <v>11.41374227447133</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242823980222</v>
+        <v>11.08242917120093</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818227449497</v>
+        <v>11.1818236847018</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4192,16 +4192,16 @@
         <v>44589</v>
       </c>
       <c r="B189" t="n">
-        <v>11.53798580169678</v>
+        <v>11.53798389434814</v>
       </c>
       <c r="C189" t="n">
-        <v>11.57939962892458</v>
+        <v>11.57939771472981</v>
       </c>
       <c r="D189" t="n">
-        <v>11.14040939875705</v>
+        <v>11.14040755713192</v>
       </c>
       <c r="E189" t="n">
-        <v>11.36404622943204</v>
+        <v>11.36404435083742</v>
       </c>
       <c r="F189" t="n">
         <v>538653</v>
@@ -4292,16 +4292,16 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>11.30606460571289</v>
+        <v>11.30606555938721</v>
       </c>
       <c r="C194" t="n">
-        <v>11.6290950705716</v>
+        <v>11.62909605149376</v>
       </c>
       <c r="D194" t="n">
-        <v>11.19838750670299</v>
+        <v>11.19838845129467</v>
       </c>
       <c r="E194" t="n">
-        <v>11.48828674852119</v>
+        <v>11.48828771756607</v>
       </c>
       <c r="F194" t="n">
         <v>381155</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697476418123</v>
+        <v>11.97697377917189</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970198234322</v>
+        <v>11.52970103411845</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313596372292</v>
+        <v>11.51313689072104</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596444165342</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.604248046875</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C200" t="n">
-        <v>11.8444500711998</v>
+        <v>11.84444909778491</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313696289563</v>
+        <v>11.51313601670912</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253147790664</v>
+        <v>11.61253052355157</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.69535827636719</v>
+        <v>11.6953592300415</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81960154268786</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394362074808</v>
+        <v>11.65394457104532</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81960154268786</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4512,16 +4512,16 @@
         <v>44613</v>
       </c>
       <c r="B205" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="C205" t="n">
-        <v>11.92727819751663</v>
+        <v>11.92727918691941</v>
       </c>
       <c r="D205" t="n">
-        <v>11.4965705871582</v>
+        <v>11.49657154083252</v>
       </c>
       <c r="E205" t="n">
-        <v>11.92727819751663</v>
+        <v>11.92727918691941</v>
       </c>
       <c r="F205" t="n">
         <v>449843</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899494940376</v>
+        <v>11.91899398228799</v>
       </c>
       <c r="D207" t="n">
-        <v>11.5462680201259</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="E207" t="n">
-        <v>11.5462680201259</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.14263153076172</v>
+        <v>12.14263248443604</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576192278439</v>
+        <v>12.17576287906074</v>
       </c>
       <c r="D208" t="n">
-        <v>11.42202469999357</v>
+        <v>11.4220255970719</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596425113861</v>
+        <v>11.59596516187804</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4632,16 +4632,16 @@
         <v>44623</v>
       </c>
       <c r="B211" t="n">
-        <v>12.70586490631104</v>
+        <v>12.7058629989624</v>
       </c>
       <c r="C211" t="n">
-        <v>13.12828994475085</v>
+        <v>13.12828797398962</v>
       </c>
       <c r="D211" t="n">
-        <v>12.59818862104573</v>
+        <v>12.59818672986099</v>
       </c>
       <c r="E211" t="n">
-        <v>13.12828994475085</v>
+        <v>13.12828797398962</v>
       </c>
       <c r="F211" t="n">
         <v>452688</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.83838844299316</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="C212" t="n">
-        <v>12.83838844299316</v>
+        <v>12.83838748931885</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000457794701</v>
+        <v>12.30000366426548</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586354237855</v>
+        <v>12.70586259854859</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081198328363</v>
+        <v>12.44081389317532</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293289679869</v>
+        <v>12.09293475328459</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576136960524</v>
+        <v>12.17576323880683</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919617434651</v>
+        <v>12.15919804100504</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111473316551</v>
+        <v>12.39111663542777</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4752,16 +4752,16 @@
         <v>44631</v>
       </c>
       <c r="B217" t="n">
-        <v>11.91071033477783</v>
+        <v>11.91071128845215</v>
       </c>
       <c r="C217" t="n">
-        <v>12.45737757023478</v>
+        <v>12.45737856768</v>
       </c>
       <c r="D217" t="n">
-        <v>11.76990201920261</v>
+        <v>11.76990296160259</v>
       </c>
       <c r="E217" t="n">
-        <v>12.44081154339084</v>
+        <v>12.44081253950964</v>
       </c>
       <c r="F217" t="n">
         <v>290870</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242924788999</v>
+        <v>11.90242825840982</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242924788999</v>
+        <v>11.90242825840982</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303523023652</v>
+        <v>11.80303620722139</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515612194091</v>
+        <v>11.45515707013042</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626719808914</v>
+        <v>11.54626815382028</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4832,16 +4832,16 @@
         <v>44637</v>
       </c>
       <c r="B221" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C221" t="n">
-        <v>11.80303516535357</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="D221" t="n">
-        <v>11.51313591003418</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E221" t="n">
-        <v>11.80303516535357</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="F221" t="n">
         <v>333116</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333881378174</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475347181555</v>
+        <v>11.79475251478082</v>
       </c>
       <c r="D224" t="n">
-        <v>11.5793992472503</v>
+        <v>11.57939830768957</v>
       </c>
       <c r="E224" t="n">
-        <v>11.67879292862352</v>
+        <v>11.67879198099791</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.9686918258667</v>
+        <v>11.96869373321533</v>
       </c>
       <c r="C225" t="n">
-        <v>12.20889299014245</v>
+        <v>12.2088949357699</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798425253982</v>
+        <v>11.53798609125025</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677159514823</v>
+        <v>11.73677346553771</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10950024971806</v>
+        <v>12.10949925876433</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394401550293</v>
+        <v>11.65394306182861</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495436638118</v>
+        <v>12.03495338152774</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.604248046875</v>
+        <v>11.60424709320068</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78647021483374</v>
+        <v>11.78646924618382</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030847777682</v>
+        <v>11.43030753839741</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535913085437</v>
+        <v>11.69535816969225</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C230" t="n">
-        <v>11.8941466495024</v>
+        <v>11.89414566071079</v>
       </c>
       <c r="D230" t="n">
-        <v>11.3557627752306</v>
+        <v>11.35576183119625</v>
       </c>
       <c r="E230" t="n">
-        <v>11.84444939483481</v>
+        <v>11.84444841017465</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374111175537</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23151896512815</v>
+        <v>11.2315199035769</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283203464774</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374111175537</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909531428845</v>
+        <v>11.62909628595667</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636759097204</v>
+        <v>11.25636853149702</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313561513094</v>
+        <v>11.51313657711016</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47172164916992</v>
+        <v>11.47172069549561</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283272794649</v>
+        <v>11.56283176669787</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919674628439</v>
+        <v>11.33919580362721</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41374179611474</v>
+        <v>11.41374084726044</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444934844971</v>
+        <v>11.02444744110107</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495411294023</v>
+        <v>11.21495217263222</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192443961648</v>
+        <v>10.89192255519609</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495411294023</v>
+        <v>11.21495217263222</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364219665527</v>
+        <v>10.88364028930664</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394493813262</v>
+        <v>10.83394303949338</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414696737361</v>
+        <v>11.07414502663918</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192390441895</v>
+        <v>10.89192485809326</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303498280762</v>
+        <v>10.98303594445944</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313571876591</v>
+        <v>10.69313665503474</v>
       </c>
       <c r="E237" t="n">
-        <v>10.9333377283516</v>
+        <v>10.93333868565203</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5172,16 +5172,16 @@
         <v>44662</v>
       </c>
       <c r="B238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.84222507476807</v>
       </c>
       <c r="C238" t="n">
-        <v>11.07414542638119</v>
+        <v>11.07414445230742</v>
       </c>
       <c r="D238" t="n">
-        <v>10.80909480476127</v>
+        <v>10.80909385400115</v>
       </c>
       <c r="E238" t="n">
-        <v>10.84222602844238</v>
+        <v>10.84222507476807</v>
       </c>
       <c r="F238" t="n">
         <v>406860</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798419952393</v>
+        <v>10.71798324584961</v>
       </c>
       <c r="C239" t="n">
-        <v>11.00788345960393</v>
+        <v>11.0078824801347</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798419952393</v>
+        <v>10.71798324584961</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333757893863</v>
+        <v>10.93333660610241</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5212,16 +5212,16 @@
         <v>44664</v>
       </c>
       <c r="B240" t="n">
-        <v>10.80909633636475</v>
+        <v>10.80909442901611</v>
       </c>
       <c r="C240" t="n">
-        <v>10.89192482338948</v>
+        <v>10.89192290142512</v>
       </c>
       <c r="D240" t="n">
-        <v>10.65172279353752</v>
+        <v>10.65172091395867</v>
       </c>
       <c r="E240" t="n">
-        <v>10.81737893541589</v>
+        <v>10.81737702660573</v>
       </c>
       <c r="F240" t="n">
         <v>281389</v>
@@ -5292,16 +5292,16 @@
         <v>44671</v>
       </c>
       <c r="B244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="C244" t="n">
-        <v>10.90848818540733</v>
+        <v>10.90848916207064</v>
       </c>
       <c r="D244" t="n">
-        <v>10.65172100067139</v>
+        <v>10.6517219543457</v>
       </c>
       <c r="E244" t="n">
-        <v>10.76767986438283</v>
+        <v>10.76768082843923</v>
       </c>
       <c r="F244" t="n">
         <v>446683</v>
@@ -5312,16 +5312,16 @@
         <v>44673</v>
       </c>
       <c r="B245" t="n">
-        <v>10.23757839202881</v>
+        <v>10.23757934570312</v>
       </c>
       <c r="C245" t="n">
-        <v>10.6434373179748</v>
+        <v>10.64343830945661</v>
       </c>
       <c r="D245" t="n">
-        <v>10.23757839202881</v>
+        <v>10.23757934570312</v>
       </c>
       <c r="E245" t="n">
-        <v>10.6434373179748</v>
+        <v>10.64343830945661</v>
       </c>
       <c r="F245" t="n">
         <v>624092</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434757232666</v>
+        <v>10.49434661865234</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919703181856</v>
+        <v>10.51919607588605</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707477706429</v>
+        <v>10.04707386403591</v>
       </c>
       <c r="E246" t="n">
-        <v>10.15475105255997</v>
+        <v>10.1547501297465</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525680541992</v>
+        <v>10.34525775909424</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061017469088</v>
+        <v>10.56061114821748</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32868994537994</v>
+        <v>10.32869089752705</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151842038292</v>
+        <v>10.41151938016555</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838840484619</v>
+        <v>10.37838935852051</v>
       </c>
       <c r="C249" t="n">
-        <v>10.55232797294748</v>
+        <v>10.55232894260518</v>
       </c>
       <c r="D249" t="n">
-        <v>10.23758006416832</v>
+        <v>10.2375810049037</v>
       </c>
       <c r="E249" t="n">
-        <v>10.34525800959385</v>
+        <v>10.3452589602238</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394432067871</v>
+        <v>10.83394336700439</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525741688146</v>
+        <v>11.16525643404281</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576245087913</v>
+        <v>10.53576152345272</v>
       </c>
       <c r="E250" t="n">
-        <v>10.5688936772823</v>
+        <v>10.56889274693946</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434543609619</v>
+        <v>10.73434448242188</v>
       </c>
       <c r="C251" t="n">
-        <v>10.9254363391113</v>
+        <v>10.92543536845984</v>
       </c>
       <c r="D251" t="n">
-        <v>10.41032020669135</v>
+        <v>10.4103192818045</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389425777308</v>
+        <v>10.88389329081236</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5472,16 +5472,16 @@
         <v>44685</v>
       </c>
       <c r="B253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90050983428955</v>
       </c>
       <c r="C253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90050983428955</v>
       </c>
       <c r="D253" t="n">
-        <v>10.48509591818506</v>
+        <v>10.48509408352501</v>
       </c>
       <c r="E253" t="n">
-        <v>10.69280382991162</v>
+        <v>10.69280195890728</v>
       </c>
       <c r="F253" t="n">
         <v>328902</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.85066032409668</v>
+        <v>10.850661277771</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344396650661</v>
+        <v>11.03344493624595</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633543802578</v>
+        <v>10.62633637198398</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772684186504</v>
+        <v>10.71772778385571</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340152740479</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389217584649</v>
+        <v>10.88389316500986</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340152740479</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="E257" t="n">
-        <v>10.8672760142748</v>
+        <v>10.86727700192804</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5592,16 +5592,16 @@
         <v>44693</v>
       </c>
       <c r="B259" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="C259" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="D259" t="n">
-        <v>10.36047010025277</v>
+        <v>10.36046825648242</v>
       </c>
       <c r="E259" t="n">
-        <v>10.5349448394823</v>
+        <v>10.53494296466207</v>
       </c>
       <c r="F259" t="n">
         <v>307094</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C261" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75927027618541</v>
+        <v>10.75926935728049</v>
       </c>
       <c r="E261" t="n">
-        <v>10.8755867747725</v>
+        <v>10.87558584593347</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085213080912</v>
+        <v>11.34085310445568</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95866949049548</v>
+        <v>10.95867043133051</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806847565188</v>
+        <v>11.15806943360591</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423513134702</v>
+        <v>11.32423610356696</v>
       </c>
       <c r="D265" t="n">
-        <v>11.10821914672852</v>
+        <v>11.10822010040283</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100196715428</v>
+        <v>11.29100293652106</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5732,16 +5732,16 @@
         <v>44704</v>
       </c>
       <c r="B266" t="n">
-        <v>10.96697807312012</v>
+        <v>10.9669771194458</v>
       </c>
       <c r="C266" t="n">
-        <v>11.19961106781229</v>
+        <v>11.19961009390851</v>
       </c>
       <c r="D266" t="n">
-        <v>10.72603699568366</v>
+        <v>10.72603606296127</v>
       </c>
       <c r="E266" t="n">
-        <v>11.14976090188353</v>
+        <v>11.14975993231466</v>
       </c>
       <c r="F266" t="n">
         <v>653906</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="C267" t="n">
-        <v>11.16637802124023</v>
+        <v>11.16637706756592</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772819255772</v>
+        <v>10.71772727720074</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05006152265314</v>
+        <v>11.05006057891294</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190235137939</v>
+        <v>10.99190139770508</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19960927620575</v>
       </c>
       <c r="D268" t="n">
-        <v>10.89220202682084</v>
+        <v>10.89220108179667</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19960927620575</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329296112061</v>
+        <v>11.08329486846924</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776768180519</v>
+        <v>11.25776961917957</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667596331338</v>
+        <v>11.06667786780236</v>
       </c>
       <c r="E270" t="n">
-        <v>11.199609441577</v>
+        <v>11.19961136894279</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776958465576</v>
+        <v>11.25776863098145</v>
       </c>
       <c r="C271" t="n">
-        <v>11.27438658527168</v>
+        <v>11.2743856301897</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160375215421</v>
+        <v>11.09160281255622</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160375215421</v>
+        <v>11.09160281255622</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34916019439697</v>
+        <v>11.34915924072266</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39900940010609</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19961053841137</v>
+        <v>11.19960959730377</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39900940010609</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622848510742</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="C274" t="n">
-        <v>11.34916115288518</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622848510742</v>
+        <v>11.21622753143311</v>
       </c>
       <c r="E274" t="n">
-        <v>11.34916115288518</v>
+        <v>11.34916018790809</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712665557861</v>
+        <v>10.91712760925293</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24945824915422</v>
+        <v>11.24945923185963</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90050965853416</v>
+        <v>10.90051061075688</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622592452802</v>
+        <v>11.21622690433039</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344526976758</v>
+        <v>11.03344429480254</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="E276" t="n">
-        <v>11.0085201867343</v>
+        <v>11.00851921397176</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359489440918</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359489440918</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D277" t="n">
-        <v>10.64295513423957</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250397149196</v>
+        <v>10.79250303440952</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5972,16 +5972,16 @@
         <v>44720</v>
       </c>
       <c r="B278" t="n">
-        <v>10.77588748931885</v>
+        <v>10.77588653564453</v>
       </c>
       <c r="C278" t="n">
-        <v>10.97528648963478</v>
+        <v>10.9752855183135</v>
       </c>
       <c r="D278" t="n">
-        <v>10.77588748931885</v>
+        <v>10.77588653564453</v>
       </c>
       <c r="E278" t="n">
-        <v>10.95867032364089</v>
+        <v>10.95866935379015</v>
       </c>
       <c r="F278" t="n">
         <v>141800</v>
@@ -6012,16 +6012,16 @@
         <v>44722</v>
       </c>
       <c r="B280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C280" t="n">
-        <v>10.65126248980645</v>
+        <v>10.65126151249989</v>
       </c>
       <c r="D280" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="E280" t="n">
-        <v>10.63464548972945</v>
+        <v>10.63464451394758</v>
       </c>
       <c r="F280" t="n">
         <v>218179</v>
@@ -6052,16 +6052,16 @@
         <v>44726</v>
       </c>
       <c r="B282" t="n">
-        <v>10.2109203338623</v>
+        <v>10.21092224121094</v>
       </c>
       <c r="C282" t="n">
-        <v>10.46847837768771</v>
+        <v>10.46848033314689</v>
       </c>
       <c r="D282" t="n">
-        <v>10.10291109871638</v>
+        <v>10.10291298588943</v>
       </c>
       <c r="E282" t="n">
-        <v>10.46017029603472</v>
+        <v>10.46017224994199</v>
       </c>
       <c r="F282" t="n">
         <v>156655</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768573760986</v>
+        <v>10.17768859863281</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216045042237</v>
+        <v>10.35216336049145</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798625945901</v>
+        <v>10.0779890924557</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599381877293</v>
+        <v>10.18599668213134</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6112,16 +6112,16 @@
         <v>44732</v>
       </c>
       <c r="B285" t="n">
-        <v>10.07798862457275</v>
+        <v>10.07798671722412</v>
       </c>
       <c r="C285" t="n">
-        <v>10.260771461444</v>
+        <v>10.2607695195021</v>
       </c>
       <c r="D285" t="n">
-        <v>9.945055955841498</v>
+        <v>9.945054073651551</v>
       </c>
       <c r="E285" t="n">
-        <v>10.1776881261212</v>
+        <v>10.17768619990355</v>
       </c>
       <c r="F285" t="n">
         <v>293715</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911822319030762</v>
+        <v>9.911820411682129</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21923058757544</v>
+        <v>10.21922862107171</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787197728821756</v>
+        <v>9.787195845454841</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783916577339</v>
+        <v>10.12783721685627</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6212,16 +6212,16 @@
         <v>44739</v>
       </c>
       <c r="B290" t="n">
-        <v>9.355164527893066</v>
+        <v>9.35516357421875</v>
       </c>
       <c r="C290" t="n">
-        <v>9.55456351324988</v>
+        <v>9.554562539248643</v>
       </c>
       <c r="D290" t="n">
-        <v>9.26377228285685</v>
+        <v>9.263771338499145</v>
       </c>
       <c r="E290" t="n">
-        <v>9.49640610190275</v>
+        <v>9.496405133830134</v>
       </c>
       <c r="F290" t="n">
         <v>312467</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.16407299041748</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496405321144287</v>
+        <v>9.496406309403417</v>
       </c>
       <c r="D291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.16407299041748</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488097239453682</v>
+        <v>9.488098226848217</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072680473327637</v>
+        <v>9.072681427001953</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255463275673385</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974782970578</v>
+        <v>8.93974876940689</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255463275673385</v>
+        <v>9.255464248560907</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6272,16 +6272,16 @@
         <v>44742</v>
       </c>
       <c r="B293" t="n">
-        <v>8.732040405273438</v>
+        <v>8.732038497924805</v>
       </c>
       <c r="C293" t="n">
-        <v>9.056065650190641</v>
+        <v>9.056063672064838</v>
       </c>
       <c r="D293" t="n">
-        <v>8.698808074182256</v>
+        <v>8.698806174092596</v>
       </c>
       <c r="E293" t="n">
-        <v>9.056065650190641</v>
+        <v>9.056063672064838</v>
       </c>
       <c r="F293" t="n">
         <v>345757</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.898207664489746</v>
+        <v>8.89820671081543</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039449254735196</v>
+        <v>9.039448285923172</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657266570105399</v>
+        <v>8.657265642254186</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823432410336896</v>
+        <v>8.823431464676691</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6312,16 +6312,16 @@
         <v>44746</v>
       </c>
       <c r="B295" t="n">
-        <v>9.222231864929199</v>
+        <v>9.222232818603516</v>
       </c>
       <c r="C295" t="n">
-        <v>9.297006275706005</v>
+        <v>9.297007237112771</v>
       </c>
       <c r="D295" t="n">
-        <v>8.873282388686833</v>
+        <v>8.873283306276161</v>
       </c>
       <c r="E295" t="n">
-        <v>8.972981881299734</v>
+        <v>8.972982809199021</v>
       </c>
       <c r="F295" t="n">
         <v>166874</v>
@@ -6352,16 +6352,16 @@
         <v>44748</v>
       </c>
       <c r="B297" t="n">
-        <v>9.080990791320801</v>
+        <v>9.080988883972168</v>
       </c>
       <c r="C297" t="n">
-        <v>9.247157471502737</v>
+        <v>9.24715552925287</v>
       </c>
       <c r="D297" t="n">
-        <v>8.923133029460081</v>
+        <v>8.923131155267498</v>
       </c>
       <c r="E297" t="n">
-        <v>9.031141455051499</v>
+        <v>9.031139558173097</v>
       </c>
       <c r="F297" t="n">
         <v>199743</v>
@@ -6392,16 +6392,16 @@
         <v>44750</v>
       </c>
       <c r="B299" t="n">
-        <v>8.914824485778809</v>
+        <v>8.914822578430176</v>
       </c>
       <c r="C299" t="n">
-        <v>9.130840491081521</v>
+        <v>9.13083853751573</v>
       </c>
       <c r="D299" t="n">
-        <v>8.898207484725576</v>
+        <v>8.89820558093219</v>
       </c>
       <c r="E299" t="n">
-        <v>8.981290820528635</v>
+        <v>8.981288898959365</v>
       </c>
       <c r="F299" t="n">
         <v>122521</v>
@@ -6452,16 +6452,16 @@
         <v>44755</v>
       </c>
       <c r="B302" t="n">
-        <v>8.599105834960938</v>
+        <v>8.59910774230957</v>
       </c>
       <c r="C302" t="n">
-        <v>8.823429863198731</v>
+        <v>8.823431820304181</v>
       </c>
       <c r="D302" t="n">
-        <v>8.549255679916392</v>
+        <v>8.549257576207872</v>
       </c>
       <c r="E302" t="n">
-        <v>8.56587267650835</v>
+        <v>8.56587457648561</v>
       </c>
       <c r="F302" t="n">
         <v>184467</v>
@@ -6472,16 +6472,16 @@
         <v>44756</v>
       </c>
       <c r="B303" t="n">
-        <v>8.499408721923828</v>
+        <v>8.499406814575195</v>
       </c>
       <c r="C303" t="n">
-        <v>8.565875057302616</v>
+        <v>8.565873135038302</v>
       </c>
       <c r="D303" t="n">
-        <v>8.349859049955773</v>
+        <v>8.34985717616752</v>
       </c>
       <c r="E303" t="n">
-        <v>8.358167133195233</v>
+        <v>8.358165257542563</v>
       </c>
       <c r="F303" t="n">
         <v>213754</v>
@@ -6492,16 +6492,16 @@
         <v>44757</v>
       </c>
       <c r="B304" t="n">
-        <v>8.499408721923828</v>
+        <v>8.499406814575195</v>
       </c>
       <c r="C304" t="n">
-        <v>8.582492058513093</v>
+        <v>8.582490132519766</v>
       </c>
       <c r="D304" t="n">
-        <v>8.424633468574021</v>
+        <v>8.42463157800567</v>
       </c>
       <c r="E304" t="n">
-        <v>8.54094997285268</v>
+        <v>8.540948056181794</v>
       </c>
       <c r="F304" t="n">
         <v>109458</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557565689086914</v>
+        <v>8.557564735412598</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673883021977259</v>
+        <v>8.673882055340277</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482791274402823</v>
+        <v>8.482790329061535</v>
       </c>
       <c r="E306" t="n">
-        <v>8.49940827473902</v>
+        <v>8.499407327545896</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864974021911621</v>
+        <v>8.864973068237305</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873282939527108</v>
+        <v>8.873281984958936</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615724857540613</v>
+        <v>8.615723930679971</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632341023308532</v>
+        <v>8.632340094660361</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6572,16 +6572,16 @@
         <v>44763</v>
       </c>
       <c r="B308" t="n">
-        <v>8.823431015014648</v>
+        <v>8.823430061340332</v>
       </c>
       <c r="C308" t="n">
-        <v>8.881590093312958</v>
+        <v>8.881589133352559</v>
       </c>
       <c r="D308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756964577673919</v>
       </c>
       <c r="E308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756964577673919</v>
       </c>
       <c r="F308" t="n">
         <v>93866</v>
@@ -6592,16 +6592,16 @@
         <v>44764</v>
       </c>
       <c r="B309" t="n">
-        <v>8.848357200622559</v>
+        <v>8.848356246948242</v>
       </c>
       <c r="C309" t="n">
-        <v>8.956364774306991</v>
+        <v>8.956363808991638</v>
       </c>
       <c r="D309" t="n">
-        <v>8.806815119817307</v>
+        <v>8.806814170620388</v>
       </c>
       <c r="E309" t="n">
-        <v>8.823431284354236</v>
+        <v>8.82343033336643</v>
       </c>
       <c r="F309" t="n">
         <v>116832</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039448738098145</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039448738098145</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815123823192138</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815123823192138</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756965637207031</v>
+        <v>8.756964683532715</v>
       </c>
       <c r="C311" t="n">
-        <v>9.122531267357015</v>
+        <v>9.1225302738709</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756965637207031</v>
+        <v>8.756964683532715</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039447941941624</v>
+        <v>9.039446957503669</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6692,16 +6692,16 @@
         <v>44771</v>
       </c>
       <c r="B314" t="n">
-        <v>8.914824485778809</v>
+        <v>8.914822578430176</v>
       </c>
       <c r="C314" t="n">
-        <v>9.114223490028287</v>
+        <v>9.114221540017745</v>
       </c>
       <c r="D314" t="n">
-        <v>8.906515567886416</v>
+        <v>8.906513662315495</v>
       </c>
       <c r="E314" t="n">
-        <v>9.097607323706608</v>
+        <v>9.097605377251137</v>
       </c>
       <c r="F314" t="n">
         <v>141168</v>
@@ -6732,16 +6732,16 @@
         <v>44775</v>
       </c>
       <c r="B316" t="n">
-        <v>9.114221572875977</v>
+        <v>9.114222526550293</v>
       </c>
       <c r="C316" t="n">
-        <v>9.205613807347317</v>
+        <v>9.205614770584537</v>
       </c>
       <c r="D316" t="n">
-        <v>8.906513694424905</v>
+        <v>8.906514626365531</v>
       </c>
       <c r="E316" t="n">
-        <v>9.006214010309503</v>
+        <v>9.006214952682356</v>
       </c>
       <c r="F316" t="n">
         <v>198584</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.939749717712402</v>
+        <v>8.939748764038086</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172381893180782</v>
+        <v>9.172380914689739</v>
       </c>
       <c r="D317" t="n">
-        <v>8.939749717712402</v>
+        <v>8.939748764038086</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114223640630795</v>
+        <v>9.114222668343956</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.380087852478027</v>
+        <v>9.38008975982666</v>
       </c>
       <c r="C319" t="n">
-        <v>9.529637494153098</v>
+        <v>9.52963943191118</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197305049845319</v>
+        <v>9.197306920026865</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305313449006189</v>
+        <v>9.305315341150182</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953364372253418</v>
+        <v>9.953362464904785</v>
       </c>
       <c r="C325" t="n">
-        <v>10.11953104846331</v>
+        <v>10.1195291092724</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704114357938586</v>
+        <v>9.704112498353368</v>
       </c>
       <c r="E325" t="n">
-        <v>9.729039442843225</v>
+        <v>9.72903757848165</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C327" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="D327" t="n">
-        <v>10.30231297394502</v>
+        <v>10.30231205007301</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847963535633</v>
+        <v>10.46847869658313</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494358062744</v>
+        <v>10.53494453430176</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75926845704052</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216078081824</v>
+        <v>10.35216171794617</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75926845704052</v>
+        <v>10.75926943102181</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340152740479</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494276606531</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="D329" t="n">
-        <v>10.2109192681043</v>
+        <v>10.21092019610571</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494276606531</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7012,16 +7012,16 @@
         <v>44795</v>
       </c>
       <c r="B330" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C330" t="n">
-        <v>10.54325324140318</v>
+        <v>10.54325227400702</v>
       </c>
       <c r="D330" t="n">
-        <v>10.21922966985091</v>
+        <v>10.21922873218552</v>
       </c>
       <c r="E330" t="n">
-        <v>10.47678774528968</v>
+        <v>10.47678678399206</v>
       </c>
       <c r="F330" t="n">
         <v>111565</v>
@@ -7052,16 +7052,16 @@
         <v>44797</v>
       </c>
       <c r="B332" t="n">
-        <v>10.77588748931885</v>
+        <v>10.77588653564453</v>
       </c>
       <c r="C332" t="n">
-        <v>10.8257376567636</v>
+        <v>10.8257366986775</v>
       </c>
       <c r="D332" t="n">
-        <v>10.38539673695239</v>
+        <v>10.3853958178368</v>
       </c>
       <c r="E332" t="n">
-        <v>10.38539673695239</v>
+        <v>10.3853958178368</v>
       </c>
       <c r="F332" t="n">
         <v>196055</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389477156793</v>
+        <v>10.88389380981785</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633669319944</v>
+        <v>10.62633575420836</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573735746564</v>
+        <v>10.82573640085461</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096130371094</v>
+        <v>10.75096035003662</v>
       </c>
       <c r="C334" t="n">
-        <v>10.7758863848787</v>
+        <v>10.77588542899338</v>
       </c>
       <c r="D334" t="n">
-        <v>10.32723742805339</v>
+        <v>10.3272365119659</v>
       </c>
       <c r="E334" t="n">
-        <v>10.7758863848787</v>
+        <v>10.77588542899338</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7112,16 +7112,16 @@
         <v>44802</v>
       </c>
       <c r="B335" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C335" t="n">
-        <v>10.75927052205955</v>
+        <v>10.75926956021513</v>
       </c>
       <c r="D335" t="n">
-        <v>10.56817960414618</v>
+        <v>10.56817865938468</v>
       </c>
       <c r="E335" t="n">
-        <v>10.75927052205955</v>
+        <v>10.75926956021513</v>
       </c>
       <c r="F335" t="n">
         <v>128948</v>
@@ -7132,16 +7132,16 @@
         <v>44803</v>
       </c>
       <c r="B336" t="n">
-        <v>10.39370441436768</v>
+        <v>10.39370346069336</v>
       </c>
       <c r="C336" t="n">
-        <v>10.79250323416921</v>
+        <v>10.79250224390311</v>
       </c>
       <c r="D336" t="n">
-        <v>10.31892916611842</v>
+        <v>10.3189282193051</v>
       </c>
       <c r="E336" t="n">
-        <v>10.70111182057445</v>
+        <v>10.70111083869397</v>
       </c>
       <c r="F336" t="n">
         <v>123575</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539600372314</v>
+        <v>10.38539505004883</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648690755074</v>
+        <v>10.57648593632885</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907867632044</v>
+        <v>10.26907773332736</v>
       </c>
       <c r="E337" t="n">
-        <v>10.4020121685439</v>
+        <v>10.40201121334375</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753810882568</v>
+        <v>10.22753715515137</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370477645853</v>
+        <v>10.39370380728989</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937985862734</v>
+        <v>10.16937891037603</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385460922237</v>
+        <v>10.34385364470204</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="D340" t="n">
-        <v>10.25246083437947</v>
+        <v>10.2524617502037</v>
       </c>
       <c r="E340" t="n">
-        <v>10.3521603111894</v>
+        <v>10.35216123591951</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7232,16 +7232,16 @@
         <v>44810</v>
       </c>
       <c r="B341" t="n">
-        <v>10.57648658752441</v>
+        <v>10.5764856338501</v>
       </c>
       <c r="C341" t="n">
-        <v>10.63464483210026</v>
+        <v>10.63464387318185</v>
       </c>
       <c r="D341" t="n">
-        <v>10.50171217863059</v>
+        <v>10.50171123169863</v>
       </c>
       <c r="E341" t="n">
-        <v>10.63464483210026</v>
+        <v>10.63464387318185</v>
       </c>
       <c r="F341" t="n">
         <v>83753</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314533233643</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913035841226</v>
+        <v>11.1913016668102</v>
       </c>
       <c r="D344" t="n">
-        <v>10.94205357586834</v>
+        <v>10.94205170125786</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006199625167</v>
+        <v>11.05006010313701</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314533233643</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C346" t="n">
-        <v>11.14976149871444</v>
+        <v>11.1497595885191</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389532408217</v>
+        <v>10.88389345943545</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145341552543</v>
+        <v>11.14145150675345</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7372,16 +7372,16 @@
         <v>44820</v>
       </c>
       <c r="B348" t="n">
-        <v>11.38239288330078</v>
+        <v>11.3823938369751</v>
       </c>
       <c r="C348" t="n">
-        <v>11.38239288330078</v>
+        <v>11.3823938369751</v>
       </c>
       <c r="D348" t="n">
-        <v>11.07498550181278</v>
+        <v>11.07498642973096</v>
       </c>
       <c r="E348" t="n">
-        <v>11.28269339505016</v>
+        <v>11.28269434037115</v>
       </c>
       <c r="F348" t="n">
         <v>238301</v>
@@ -7412,16 +7412,16 @@
         <v>44824</v>
       </c>
       <c r="B350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.15806770324707</v>
       </c>
       <c r="C350" t="n">
-        <v>11.30761915031543</v>
+        <v>11.30761818385911</v>
       </c>
       <c r="D350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.15806770324707</v>
       </c>
       <c r="E350" t="n">
-        <v>11.17468565665344</v>
+        <v>11.17468470155888</v>
       </c>
       <c r="F350" t="n">
         <v>127157</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85066145408563</v>
+        <v>10.85066048103983</v>
       </c>
       <c r="D352" t="n">
-        <v>10.59310421404906</v>
+        <v>10.5931032641</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449562740583</v>
+        <v>10.68449466926114</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C353" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="D353" t="n">
-        <v>10.3438542219321</v>
+        <v>10.34385329433483</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156296606198</v>
+        <v>10.55156201983819</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7532,16 +7532,16 @@
         <v>44832</v>
       </c>
       <c r="B356" t="n">
-        <v>10.2109203338623</v>
+        <v>10.21092224121094</v>
       </c>
       <c r="C356" t="n">
-        <v>10.44355246326593</v>
+        <v>10.44355441406907</v>
       </c>
       <c r="D356" t="n">
-        <v>10.19430417055632</v>
+        <v>10.19430607480114</v>
       </c>
       <c r="E356" t="n">
-        <v>10.40201122026956</v>
+        <v>10.40201316331301</v>
       </c>
       <c r="F356" t="n">
         <v>104928</v>
@@ -7572,16 +7572,16 @@
         <v>44834</v>
       </c>
       <c r="B358" t="n">
-        <v>10.18599414825439</v>
+        <v>10.18599510192871</v>
       </c>
       <c r="C358" t="n">
-        <v>10.26907746676657</v>
+        <v>10.26907842821965</v>
       </c>
       <c r="D358" t="n">
-        <v>9.920128029854263</v>
+        <v>9.920128958636587</v>
       </c>
       <c r="E358" t="n">
-        <v>10.17768606682259</v>
+        <v>10.17768701971906</v>
       </c>
       <c r="F358" t="n">
         <v>188154</v>
@@ -7612,16 +7612,16 @@
         <v>44838</v>
       </c>
       <c r="B360" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="C360" t="n">
-        <v>10.75926974270069</v>
+        <v>10.75926782795914</v>
       </c>
       <c r="D360" t="n">
-        <v>10.32723777056884</v>
+        <v>10.32723593271258</v>
       </c>
       <c r="E360" t="n">
-        <v>10.38539601697868</v>
+        <v>10.38539416877246</v>
       </c>
       <c r="F360" t="n">
         <v>266324</v>
@@ -7632,16 +7632,16 @@
         <v>44839</v>
       </c>
       <c r="B361" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C361" t="n">
-        <v>10.90051210710464</v>
+        <v>10.90051113263368</v>
       </c>
       <c r="D361" t="n">
-        <v>10.55987152112339</v>
+        <v>10.55987057710461</v>
       </c>
       <c r="E361" t="n">
-        <v>10.80081177190503</v>
+        <v>10.80081080634695</v>
       </c>
       <c r="F361" t="n">
         <v>399697</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389461942159</v>
+        <v>10.88389364339556</v>
       </c>
       <c r="D363" t="n">
-        <v>10.63464546203613</v>
+        <v>10.63464450836182</v>
       </c>
       <c r="E363" t="n">
-        <v>10.82573720613229</v>
+        <v>10.82573623532159</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359489440918</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359489440918</v>
+        <v>10.98359394073486</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156371440112</v>
+        <v>10.55156279823885</v>
       </c>
       <c r="E364" t="n">
-        <v>10.64295513423957</v>
+        <v>10.64295421014203</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7732,16 +7732,16 @@
         <v>44847</v>
       </c>
       <c r="B366" t="n">
-        <v>10.96697807312012</v>
+        <v>10.9669771194458</v>
       </c>
       <c r="C366" t="n">
-        <v>11.15806898462782</v>
+        <v>11.15806801433649</v>
       </c>
       <c r="D366" t="n">
-        <v>10.85897049324983</v>
+        <v>10.85896954896772</v>
       </c>
       <c r="E366" t="n">
-        <v>10.85897049324983</v>
+        <v>10.85896954896772</v>
       </c>
       <c r="F366" t="n">
         <v>180569</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558650970459</v>
+        <v>10.87558460235596</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160333594799</v>
+        <v>11.09160139071456</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85066142708177</v>
+        <v>10.85065952410448</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344508807192</v>
+        <v>11.03344315303822</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7772,16 +7772,16 @@
         <v>44851</v>
       </c>
       <c r="B368" t="n">
-        <v>10.95866870880127</v>
+        <v>10.95866966247559</v>
       </c>
       <c r="C368" t="n">
-        <v>11.02513503244562</v>
+        <v>11.02513599190414</v>
       </c>
       <c r="D368" t="n">
-        <v>10.79250206495899</v>
+        <v>10.79250300417271</v>
       </c>
       <c r="E368" t="n">
-        <v>11.02513503244562</v>
+        <v>11.02513599190414</v>
       </c>
       <c r="F368" t="n">
         <v>132003</v>
@@ -7832,16 +7832,16 @@
         <v>44854</v>
       </c>
       <c r="B371" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="C371" t="n">
-        <v>11.04175289232892</v>
+        <v>11.0417509273161</v>
       </c>
       <c r="D371" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="E371" t="n">
-        <v>10.95866956392465</v>
+        <v>10.95866761369751</v>
       </c>
       <c r="F371" t="n">
         <v>119045</v>
@@ -7852,16 +7852,16 @@
         <v>44855</v>
       </c>
       <c r="B372" t="n">
-        <v>10.68449306488037</v>
+        <v>10.684494972229</v>
       </c>
       <c r="C372" t="n">
-        <v>10.8838920090731</v>
+        <v>10.88389395201756</v>
       </c>
       <c r="D372" t="n">
-        <v>10.68449306488037</v>
+        <v>10.684494972229</v>
       </c>
       <c r="E372" t="n">
-        <v>10.76757637565966</v>
+        <v>10.76757829783996</v>
       </c>
       <c r="F372" t="n">
         <v>132319</v>
@@ -7912,16 +7912,16 @@
         <v>44860</v>
       </c>
       <c r="B375" t="n">
-        <v>10.71772766113281</v>
+        <v>10.71772575378418</v>
       </c>
       <c r="C375" t="n">
-        <v>10.96697764634563</v>
+        <v>10.96697569463996</v>
       </c>
       <c r="D375" t="n">
-        <v>10.65126216703347</v>
+        <v>10.65126027151317</v>
       </c>
       <c r="E375" t="n">
-        <v>10.65126216703347</v>
+        <v>10.65126027151317</v>
       </c>
       <c r="F375" t="n">
         <v>230294</v>
@@ -7952,16 +7952,16 @@
         <v>44862</v>
       </c>
       <c r="B377" t="n">
-        <v>10.95866870880127</v>
+        <v>10.95866966247559</v>
       </c>
       <c r="C377" t="n">
-        <v>10.99190187062344</v>
+        <v>10.99190282718986</v>
       </c>
       <c r="D377" t="n">
-        <v>10.68449449771977</v>
+        <v>10.68449542753418</v>
       </c>
       <c r="E377" t="n">
-        <v>10.89220155042551</v>
+        <v>10.89220249831554</v>
       </c>
       <c r="F377" t="n">
         <v>271802</v>
@@ -7972,16 +7972,16 @@
         <v>44865</v>
       </c>
       <c r="B378" t="n">
-        <v>10.59310436248779</v>
+        <v>10.59310340881348</v>
       </c>
       <c r="C378" t="n">
-        <v>10.90051177220169</v>
+        <v>10.90051079085215</v>
       </c>
       <c r="D378" t="n">
-        <v>10.4850959475838</v>
+        <v>10.48509500363324</v>
       </c>
       <c r="E378" t="n">
-        <v>10.61802861079039</v>
+        <v>10.6180276548722</v>
       </c>
       <c r="F378" t="n">
         <v>218495</v>
@@ -7992,16 +7992,16 @@
         <v>44866</v>
       </c>
       <c r="B379" t="n">
-        <v>10.72603607177734</v>
+        <v>10.72603702545166</v>
       </c>
       <c r="C379" t="n">
-        <v>10.79250239746948</v>
+        <v>10.79250335705346</v>
       </c>
       <c r="D379" t="n">
-        <v>10.51832817794084</v>
+        <v>10.51832911314741</v>
       </c>
       <c r="E379" t="n">
-        <v>10.64295358202789</v>
+        <v>10.64295452831517</v>
       </c>
       <c r="F379" t="n">
         <v>132424</v>
@@ -8072,16 +8072,16 @@
         <v>44873</v>
       </c>
       <c r="B383" t="n">
-        <v>10.77588748931885</v>
+        <v>10.77588653564453</v>
       </c>
       <c r="C383" t="n">
-        <v>10.91712907392462</v>
+        <v>10.91712810775032</v>
       </c>
       <c r="D383" t="n">
-        <v>10.62633698698459</v>
+        <v>10.62633604654561</v>
       </c>
       <c r="E383" t="n">
-        <v>10.90051207319919</v>
+        <v>10.9005111084955</v>
       </c>
       <c r="F383" t="n">
         <v>103348</v>
@@ -8112,16 +8112,16 @@
         <v>44875</v>
       </c>
       <c r="B385" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="C385" t="n">
-        <v>10.66787910461426</v>
+        <v>10.66787815093994</v>
       </c>
       <c r="D385" t="n">
-        <v>10.23584626645618</v>
+        <v>10.23584535140422</v>
       </c>
       <c r="E385" t="n">
-        <v>10.58479577019176</v>
+        <v>10.58479482394483</v>
       </c>
       <c r="F385" t="n">
         <v>289395</v>
@@ -8152,16 +8152,16 @@
         <v>44879</v>
       </c>
       <c r="B387" t="n">
-        <v>10.08629512786865</v>
+        <v>10.08629703521729</v>
       </c>
       <c r="C387" t="n">
-        <v>10.50171173941597</v>
+        <v>10.50171372532113</v>
       </c>
       <c r="D387" t="n">
-        <v>9.953362479958644</v>
+        <v>9.953364362169316</v>
       </c>
       <c r="E387" t="n">
-        <v>10.25246177248758</v>
+        <v>10.25246371125882</v>
       </c>
       <c r="F387" t="n">
         <v>430564</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.70711612701416</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629626020535</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="D388" t="n">
-        <v>8.70711612701416</v>
+        <v>8.707115173339844</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629626020535</v>
+        <v>10.08629515547199</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765273094177246</v>
+        <v>8.765275001525879</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873281492987086</v>
+        <v>8.873283423838657</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225232769590827</v>
+        <v>8.225234559425131</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707114854007546</v>
+        <v>8.707116748700779</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8212,16 +8212,16 @@
         <v>44883</v>
       </c>
       <c r="B390" t="n">
-        <v>8.557565689086914</v>
+        <v>8.557564735412598</v>
       </c>
       <c r="C390" t="n">
-        <v>8.914824101097249</v>
+        <v>8.914823107609253</v>
       </c>
       <c r="D390" t="n">
-        <v>8.391399859382533</v>
+        <v>8.39139892422611</v>
       </c>
       <c r="E390" t="n">
-        <v>8.848357769215497</v>
+        <v>8.848356783134658</v>
       </c>
       <c r="F390" t="n">
         <v>571733</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562846183776855</v>
+        <v>8.562845230102539</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039489009439741</v>
+        <v>9.039488002680034</v>
       </c>
       <c r="D392" t="n">
-        <v>8.529397667607249</v>
+        <v>8.52939671765821</v>
       </c>
       <c r="E392" t="n">
-        <v>8.94750537993818</v>
+        <v>8.947504383423015</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.780261993408203</v>
+        <v>8.780261039733887</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880607542310836</v>
+        <v>8.880606577737419</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462500668479581</v>
+        <v>8.462499749319136</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537759620121415</v>
+        <v>8.537758692786666</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081300735473633</v>
+        <v>9.081298828125</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081300735473633</v>
+        <v>9.081298828125</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621382522590984</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621382522590984</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.82207202911377</v>
+        <v>8.822073936462402</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098022879921743</v>
+        <v>9.098024846931471</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746812247907716</v>
+        <v>8.746814138985041</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081298204051361</v>
+        <v>9.081300167445182</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198371098419715</v>
+        <v>9.198370118006814</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822073797252052</v>
+        <v>8.822072856946983</v>
       </c>
       <c r="E400" t="n">
-        <v>9.1398351412117</v>
+        <v>9.139834167037881</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8432,16 +8432,16 @@
         <v>44900</v>
       </c>
       <c r="B401" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C401" t="n">
-        <v>9.08966353913592</v>
+        <v>9.089662548080438</v>
       </c>
       <c r="D401" t="n">
-        <v>8.66319384514464</v>
+        <v>8.663192900587594</v>
       </c>
       <c r="E401" t="n">
-        <v>8.947506694425265</v>
+        <v>8.947505718869293</v>
       </c>
       <c r="F401" t="n">
         <v>131055</v>
@@ -8452,16 +8452,16 @@
         <v>44901</v>
       </c>
       <c r="B402" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C402" t="n">
-        <v>8.863884971646016</v>
+        <v>8.863884005207408</v>
       </c>
       <c r="D402" t="n">
-        <v>8.688279605851797</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="E402" t="n">
-        <v>8.771901328631047</v>
+        <v>8.771900372221511</v>
       </c>
       <c r="F402" t="n">
         <v>122416</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905694705334085</v>
+        <v>8.905695681933357</v>
       </c>
       <c r="D403" t="n">
-        <v>8.67991617708353</v>
+        <v>8.679917128923909</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437413215637207</v>
+        <v>8.437412261962891</v>
       </c>
       <c r="C404" t="n">
-        <v>8.738451542075317</v>
+        <v>8.73845055437487</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412327458562881</v>
+        <v>8.412326507723987</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705003025835651</v>
+        <v>8.705002041915865</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935683727264404</v>
+        <v>7.935684204101562</v>
       </c>
       <c r="C405" t="n">
-        <v>8.479223524443508</v>
+        <v>8.479224033940735</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935683727264404</v>
+        <v>7.935684204101562</v>
       </c>
       <c r="E405" t="n">
-        <v>8.46249968830041</v>
+        <v>8.462500196792739</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8552,16 +8552,16 @@
         <v>44908</v>
       </c>
       <c r="B407" t="n">
-        <v>8.027667999267578</v>
+        <v>8.027668952941895</v>
       </c>
       <c r="C407" t="n">
-        <v>8.245083767790964</v>
+        <v>8.24508474729393</v>
       </c>
       <c r="D407" t="n">
-        <v>7.893873098540508</v>
+        <v>7.893874036320201</v>
       </c>
       <c r="E407" t="n">
-        <v>7.893873098540508</v>
+        <v>7.893874036320201</v>
       </c>
       <c r="F407" t="n">
         <v>284655</v>
@@ -8572,16 +8572,16 @@
         <v>44909</v>
       </c>
       <c r="B408" t="n">
-        <v>8.136375427246094</v>
+        <v>8.136377334594727</v>
       </c>
       <c r="C408" t="n">
-        <v>8.16146118079873</v>
+        <v>8.161463094028024</v>
       </c>
       <c r="D408" t="n">
-        <v>7.634645233665385</v>
+        <v>7.634647023397222</v>
       </c>
       <c r="E408" t="n">
-        <v>8.002581381070261</v>
+        <v>8.002583257054573</v>
       </c>
       <c r="F408" t="n">
         <v>518426</v>
@@ -8592,16 +8592,16 @@
         <v>44910</v>
       </c>
       <c r="B409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253446578979492</v>
       </c>
       <c r="C409" t="n">
-        <v>8.253445625305176</v>
+        <v>8.253446578979492</v>
       </c>
       <c r="D409" t="n">
-        <v>8.027667939705447</v>
+        <v>8.027668867291462</v>
       </c>
       <c r="E409" t="n">
-        <v>8.111289647021858</v>
+        <v>8.111290584270247</v>
       </c>
       <c r="F409" t="n">
         <v>145488</v>
@@ -8612,16 +8612,16 @@
         <v>44911</v>
       </c>
       <c r="B410" t="n">
-        <v>8.027667999267578</v>
+        <v>8.027668952941895</v>
       </c>
       <c r="C410" t="n">
-        <v>8.295256960581183</v>
+        <v>8.295257946044645</v>
       </c>
       <c r="D410" t="n">
-        <v>8.027667999267578</v>
+        <v>8.027668952941895</v>
       </c>
       <c r="E410" t="n">
-        <v>8.253445686542488</v>
+        <v>8.253446667038839</v>
       </c>
       <c r="F410" t="n">
         <v>177935</v>
@@ -8652,16 +8652,16 @@
         <v>44915</v>
       </c>
       <c r="B412" t="n">
-        <v>8.429051399230957</v>
+        <v>8.429050445556641</v>
       </c>
       <c r="C412" t="n">
-        <v>8.579570984352777</v>
+        <v>8.579570013648471</v>
       </c>
       <c r="D412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="E412" t="n">
-        <v>8.052754956848128</v>
+        <v>8.0527540457485</v>
       </c>
       <c r="F412" t="n">
         <v>166979</v>
@@ -8672,16 +8672,16 @@
         <v>44916</v>
       </c>
       <c r="B413" t="n">
-        <v>8.45413875579834</v>
+        <v>8.454137802124023</v>
       </c>
       <c r="C413" t="n">
-        <v>8.613018578241588</v>
+        <v>8.613017606644735</v>
       </c>
       <c r="D413" t="n">
-        <v>8.370517044912967</v>
+        <v>8.370516100671649</v>
       </c>
       <c r="E413" t="n">
-        <v>8.429051318378106</v>
+        <v>8.429050367533794</v>
       </c>
       <c r="F413" t="n">
         <v>125998</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780261722894588</v>
+        <v>8.780262685738871</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613018306402285</v>
+        <v>8.613019250906639</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730089370059329</v>
+        <v>8.730090327401705</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.73845100402832</v>
+        <v>8.738451957702637</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788623355228307</v>
+        <v>8.788624314378202</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284567447709</v>
+        <v>8.56284660898665</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713364408358071</v>
+        <v>8.713365359294553</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8772,16 +8772,16 @@
         <v>44923</v>
       </c>
       <c r="B418" t="n">
-        <v>8.746814727783203</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C418" t="n">
-        <v>8.930782853953826</v>
+        <v>8.930781880221272</v>
       </c>
       <c r="D418" t="n">
-        <v>8.679917685616079</v>
+        <v>8.679916739235615</v>
       </c>
       <c r="E418" t="n">
-        <v>8.688279605851797</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="F418" t="n">
         <v>114515</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914056624116538</v>
+        <v>8.914057601632781</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640014648438</v>
+        <v>8.696640968322754</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830434915870388</v>
+        <v>8.830435884216666</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529396057128906</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771899364464465</v>
+        <v>8.771898383675891</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529397010803223</v>
+        <v>8.529396057128906</v>
       </c>
       <c r="E420" t="n">
-        <v>8.705002337276639</v>
+        <v>8.70500136396784</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8872,16 +8872,16 @@
         <v>44931</v>
       </c>
       <c r="B423" t="n">
-        <v>8.395604133605957</v>
+        <v>8.395603179931641</v>
       </c>
       <c r="C423" t="n">
-        <v>8.454139250637853</v>
+        <v>8.454138290314409</v>
       </c>
       <c r="D423" t="n">
-        <v>8.270171980006358</v>
+        <v>8.270171040580143</v>
       </c>
       <c r="E423" t="n">
-        <v>8.362155615322106</v>
+        <v>8.362154665447276</v>
       </c>
       <c r="F423" t="n">
         <v>69636</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387241379016988</v>
+        <v>8.387240485058745</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395604138698484</v>
+        <v>8.395603243848893</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8912,16 +8912,16 @@
         <v>44935</v>
       </c>
       <c r="B425" t="n">
-        <v>8.813711166381836</v>
+        <v>8.81371021270752</v>
       </c>
       <c r="C425" t="n">
-        <v>8.947505228800265</v>
+        <v>8.947504260648964</v>
       </c>
       <c r="D425" t="n">
-        <v>8.696640101554889</v>
+        <v>8.69663916054807</v>
       </c>
       <c r="E425" t="n">
-        <v>8.905694794329643</v>
+        <v>8.905693830702377</v>
       </c>
       <c r="F425" t="n">
         <v>148121</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964228630065918</v>
+        <v>8.964229583740234</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072936930593318</v>
+        <v>9.072937895832748</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847159251220148</v>
+        <v>8.847160192439846</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922418197631035</v>
+        <v>8.922419146857282</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139834941690628</v>
+        <v>9.139833970240518</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006040871394767</v>
+        <v>9.006039914165292</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847160202883281</v>
+        <v>8.847159262540833</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C431" t="n">
-        <v>9.064575987184355</v>
+        <v>9.06457502373333</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905695318672869</v>
+        <v>8.905694372108872</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964229594321862</v>
+        <v>8.964228641536403</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9052,16 +9052,16 @@
         <v>44944</v>
       </c>
       <c r="B432" t="n">
-        <v>9.064576148986816</v>
+        <v>9.0645751953125</v>
       </c>
       <c r="C432" t="n">
-        <v>9.357251733159014</v>
+        <v>9.357250748692612</v>
       </c>
       <c r="D432" t="n">
-        <v>8.964229754333143</v>
+        <v>8.964228811216161</v>
       </c>
       <c r="E432" t="n">
-        <v>8.964229754333143</v>
+        <v>8.964228811216161</v>
       </c>
       <c r="F432" t="n">
         <v>306251</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566305160522461</v>
+        <v>9.566304206848145</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616477515394145</v>
+        <v>9.616476556718098</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407423656363838</v>
+        <v>9.407422718528574</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424148334748114</v>
+        <v>9.424147395245551</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9212,16 +9212,16 @@
         <v>44956</v>
       </c>
       <c r="B440" t="n">
-        <v>9.616477966308594</v>
+        <v>9.616477012634277</v>
       </c>
       <c r="C440" t="n">
-        <v>9.867343112992316</v>
+        <v>9.867342134439488</v>
       </c>
       <c r="D440" t="n">
-        <v>9.57466752859828</v>
+        <v>9.574666579070339</v>
       </c>
       <c r="E440" t="n">
-        <v>9.725186280552268</v>
+        <v>9.725185316097255</v>
       </c>
       <c r="F440" t="n">
         <v>176882</v>
@@ -9292,16 +9292,16 @@
         <v>44960</v>
       </c>
       <c r="B444" t="n">
-        <v>9.675012588500977</v>
+        <v>9.67501163482666</v>
       </c>
       <c r="C444" t="n">
-        <v>9.867342608471997</v>
+        <v>9.867341635839546</v>
       </c>
       <c r="D444" t="n">
-        <v>9.382337859212104</v>
+        <v>9.382336934386988</v>
       </c>
       <c r="E444" t="n">
-        <v>9.474321489584133</v>
+        <v>9.474320555692112</v>
       </c>
       <c r="F444" t="n">
         <v>1290218</v>
@@ -9332,16 +9332,16 @@
         <v>44964</v>
       </c>
       <c r="B446" t="n">
-        <v>9.733547210693359</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="C446" t="n">
-        <v>9.733547210693359</v>
+        <v>9.733548164367676</v>
       </c>
       <c r="D446" t="n">
-        <v>9.457595517194969</v>
+        <v>9.457596443832067</v>
       </c>
       <c r="E446" t="n">
-        <v>9.649925510849618</v>
+        <v>9.64992645633084</v>
       </c>
       <c r="F446" t="n">
         <v>121889</v>
@@ -9452,16 +9452,16 @@
         <v>44972</v>
       </c>
       <c r="B452" t="n">
-        <v>10.22691631317139</v>
+        <v>10.22691535949707</v>
       </c>
       <c r="C452" t="n">
-        <v>10.3439857134208</v>
+        <v>10.3439847488296</v>
       </c>
       <c r="D452" t="n">
-        <v>9.917516872220858</v>
+        <v>9.917515947398474</v>
       </c>
       <c r="E452" t="n">
-        <v>9.917516872220858</v>
+        <v>9.917515947398474</v>
       </c>
       <c r="F452" t="n">
         <v>361455</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363708496094</v>
+        <v>10.24363994598389</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088047546544</v>
+        <v>10.41088338319906</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458326690051</v>
+        <v>10.03458606953524</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820496215276</v>
+        <v>10.11820778814282</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363708496094</v>
+        <v>10.24363994598389</v>
       </c>
       <c r="C455" t="n">
-        <v>10.61993513366628</v>
+        <v>10.61993809978836</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992773679484996</v>
+        <v>9.992776470442406</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889686273009</v>
+        <v>10.31889974477291</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9532,16 +9532,16 @@
         <v>44980</v>
       </c>
       <c r="B456" t="n">
-        <v>10.10148334503174</v>
+        <v>10.10148239135742</v>
       </c>
       <c r="C456" t="n">
-        <v>10.43596935933888</v>
+        <v>10.43596837408596</v>
       </c>
       <c r="D456" t="n">
-        <v>10.03458547005784</v>
+        <v>10.0345845226993</v>
       </c>
       <c r="E456" t="n">
-        <v>10.43596935933888</v>
+        <v>10.43596837408596</v>
       </c>
       <c r="F456" t="n">
         <v>107772</v>
@@ -9552,16 +9552,16 @@
         <v>44981</v>
       </c>
       <c r="B457" t="n">
-        <v>10.00113773345947</v>
+        <v>10.00113677978516</v>
       </c>
       <c r="C457" t="n">
-        <v>10.21019075603841</v>
+        <v>10.21018978242951</v>
       </c>
       <c r="D457" t="n">
-        <v>10.00113773345947</v>
+        <v>10.00113677978516</v>
       </c>
       <c r="E457" t="n">
-        <v>10.10148328511423</v>
+        <v>10.10148232187131</v>
       </c>
       <c r="F457" t="n">
         <v>69320</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458499908447</v>
+        <v>10.03458404541016</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889864399266</v>
+        <v>10.31889766329754</v>
       </c>
       <c r="D459" t="n">
-        <v>9.90915369476458</v>
+        <v>9.909152753011098</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950964129537878</v>
+        <v>9.950963183810783</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363708496094</v>
+        <v>10.24363994598389</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053494524699</v>
+        <v>10.31053782495434</v>
       </c>
       <c r="D460" t="n">
-        <v>9.850616041429799</v>
+        <v>9.850618792682926</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458326690051</v>
+        <v>10.03458606953524</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9632,16 +9632,16 @@
         <v>44987</v>
       </c>
       <c r="B461" t="n">
-        <v>10.47777938842773</v>
+        <v>10.47778034210205</v>
       </c>
       <c r="C461" t="n">
-        <v>10.55303917979261</v>
+        <v>10.55304014031698</v>
       </c>
       <c r="D461" t="n">
-        <v>10.11820679001243</v>
+        <v>10.1182077109589</v>
       </c>
       <c r="E461" t="n">
-        <v>10.20182850037099</v>
+        <v>10.2018294289286</v>
       </c>
       <c r="F461" t="n">
         <v>220181</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.7453670501709</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="C465" t="n">
-        <v>10.7453670501709</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="D465" t="n">
-        <v>10.50286470773317</v>
+        <v>10.50286563988488</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502151403336</v>
+        <v>10.64502245880179</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9732,16 +9732,16 @@
         <v>44994</v>
       </c>
       <c r="B466" t="n">
-        <v>10.70355796813965</v>
+        <v>10.70355701446533</v>
       </c>
       <c r="C466" t="n">
-        <v>10.820628195114</v>
+        <v>10.82062723100886</v>
       </c>
       <c r="D466" t="n">
-        <v>10.63666093562304</v>
+        <v>10.63665998790917</v>
       </c>
       <c r="E466" t="n">
-        <v>10.68683328994021</v>
+        <v>10.68683233775605</v>
       </c>
       <c r="F466" t="n">
         <v>86176</v>
@@ -9752,16 +9752,16 @@
         <v>44995</v>
       </c>
       <c r="B467" t="n">
-        <v>10.82062911987305</v>
+        <v>10.82062721252441</v>
       </c>
       <c r="C467" t="n">
-        <v>10.82062911987305</v>
+        <v>10.82062721252441</v>
       </c>
       <c r="D467" t="n">
-        <v>10.23527793497566</v>
+        <v>10.23527613080669</v>
       </c>
       <c r="E467" t="n">
-        <v>10.81226720012898</v>
+        <v>10.8122652942543</v>
       </c>
       <c r="F467" t="n">
         <v>153705</v>
@@ -9772,16 +9772,16 @@
         <v>44998</v>
       </c>
       <c r="B468" t="n">
-        <v>10.18510627746582</v>
+        <v>10.18510437011719</v>
       </c>
       <c r="C468" t="n">
-        <v>10.77881858283502</v>
+        <v>10.77881656430283</v>
       </c>
       <c r="D468" t="n">
-        <v>10.18510627746582</v>
+        <v>10.18510437011719</v>
       </c>
       <c r="E468" t="n">
-        <v>10.77881858283502</v>
+        <v>10.77881656430283</v>
       </c>
       <c r="F468" t="n">
         <v>154864</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758633613586426</v>
+        <v>9.758634567260742</v>
       </c>
       <c r="C470" t="n">
-        <v>9.967687457030143</v>
+        <v>9.9676884311345</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675011908180837</v>
+        <v>9.675012853683121</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892427670122959</v>
+        <v>9.892428636872463</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165519714355</v>
+        <v>10.15165615081787</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837903495139</v>
+        <v>10.16837999019679</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683375136415892</v>
+        <v>9.683376046098697</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833893877389167</v>
+        <v>9.833894801212116</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440871238708496</v>
+        <v>9.440873146057129</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583028050414784</v>
+        <v>9.583029986483497</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415785483825466</v>
+        <v>9.415787386105999</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532854860367744</v>
+        <v>9.532856786299918</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9932,16 +9932,16 @@
         <v>45008</v>
       </c>
       <c r="B476" t="n">
-        <v>9.332164764404297</v>
+        <v>9.33216381072998</v>
       </c>
       <c r="C476" t="n">
-        <v>9.407423717269351</v>
+        <v>9.407422755904157</v>
       </c>
       <c r="D476" t="n">
-        <v>9.131472823196523</v>
+        <v>9.131471890031355</v>
       </c>
       <c r="E476" t="n">
-        <v>9.399061798093364</v>
+        <v>9.399060837582692</v>
       </c>
       <c r="F476" t="n">
         <v>179094</v>
@@ -9972,16 +9972,16 @@
         <v>45012</v>
       </c>
       <c r="B478" t="n">
-        <v>10.46941661834717</v>
+        <v>10.46941757202148</v>
       </c>
       <c r="C478" t="n">
-        <v>10.54467640359397</v>
+        <v>10.54467736412381</v>
       </c>
       <c r="D478" t="n">
-        <v>9.875703615248632</v>
+        <v>9.87570451484077</v>
       </c>
       <c r="E478" t="n">
-        <v>10.31889788799405</v>
+        <v>10.3188988279574</v>
       </c>
       <c r="F478" t="n">
         <v>649270</v>
@@ -9992,16 +9992,16 @@
         <v>45013</v>
       </c>
       <c r="B479" t="n">
-        <v>10.70355796813965</v>
+        <v>10.70355701446533</v>
       </c>
       <c r="C479" t="n">
-        <v>10.74536840342739</v>
+        <v>10.74536744602781</v>
       </c>
       <c r="D479" t="n">
-        <v>10.32726068998773</v>
+        <v>10.32725976984105</v>
       </c>
       <c r="E479" t="n">
-        <v>10.46941751419095</v>
+        <v>10.46941658137827</v>
       </c>
       <c r="F479" t="n">
         <v>226923</v>
@@ -10032,16 +10032,16 @@
         <v>45015</v>
       </c>
       <c r="B481" t="n">
-        <v>11.00459480285645</v>
+        <v>11.00459575653076</v>
       </c>
       <c r="C481" t="n">
-        <v>11.18856205145192</v>
+        <v>11.18856302106911</v>
       </c>
       <c r="D481" t="n">
-        <v>10.61993646859709</v>
+        <v>10.61993738893635</v>
       </c>
       <c r="E481" t="n">
-        <v>10.6617469014086</v>
+        <v>10.66174782537122</v>
       </c>
       <c r="F481" t="n">
         <v>272855</v>
@@ -10092,16 +10092,16 @@
         <v>45020</v>
       </c>
       <c r="B484" t="n">
-        <v>9.599752426147461</v>
+        <v>9.599753379821777</v>
       </c>
       <c r="C484" t="n">
-        <v>9.758633069460794</v>
+        <v>9.758634038918892</v>
       </c>
       <c r="D484" t="n">
-        <v>9.532854561468801</v>
+        <v>9.53285550849724</v>
       </c>
       <c r="E484" t="n">
-        <v>9.700097962954755</v>
+        <v>9.700098926597763</v>
       </c>
       <c r="F484" t="n">
         <v>529909</v>
@@ -10112,16 +10112,16 @@
         <v>45021</v>
       </c>
       <c r="B485" t="n">
-        <v>9.616477966308594</v>
+        <v>9.616477012634277</v>
       </c>
       <c r="C485" t="n">
-        <v>9.708461601383775</v>
+        <v>9.708460638587363</v>
       </c>
       <c r="D485" t="n">
-        <v>9.022765718147193</v>
+        <v>9.022764823351826</v>
       </c>
       <c r="E485" t="n">
-        <v>9.633202645477088</v>
+        <v>9.633201690144169</v>
       </c>
       <c r="F485" t="n">
         <v>566992</v>
@@ -10132,16 +10132,16 @@
         <v>45022</v>
       </c>
       <c r="B486" t="n">
-        <v>9.541217803955078</v>
+        <v>9.541218757629395</v>
       </c>
       <c r="C486" t="n">
-        <v>9.633201427399317</v>
+        <v>9.633202390267682</v>
       </c>
       <c r="D486" t="n">
-        <v>9.39069907103355</v>
+        <v>9.390700009663053</v>
       </c>
       <c r="E486" t="n">
-        <v>9.52449312690135</v>
+        <v>9.524494078903984</v>
       </c>
       <c r="F486" t="n">
         <v>123364</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="C489" t="n">
-        <v>9.783719859219421</v>
+        <v>9.78372083371632</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574666023254395</v>
+        <v>9.574666976928711</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700098156805314</v>
+        <v>9.700099122973164</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10252,16 +10252,16 @@
         <v>45033</v>
       </c>
       <c r="B492" t="n">
-        <v>9.649927139282227</v>
+        <v>9.64992618560791</v>
       </c>
       <c r="C492" t="n">
-        <v>9.725186093743282</v>
+        <v>9.725185132631342</v>
       </c>
       <c r="D492" t="n">
-        <v>9.566305425327258</v>
+        <v>9.566304479917033</v>
       </c>
       <c r="E492" t="n">
-        <v>9.616477781587763</v>
+        <v>9.616476831219149</v>
       </c>
       <c r="F492" t="n">
         <v>328796</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.658288955688477</v>
+        <v>9.658287048339844</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716823230678386</v>
+        <v>9.716821311770225</v>
       </c>
       <c r="D494" t="n">
-        <v>9.59975384055798</v>
+        <v>9.599751944769041</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616477679086358</v>
+        <v>9.616475779994744</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10312,16 +10312,16 @@
         <v>45036</v>
       </c>
       <c r="B495" t="n">
-        <v>9.599752426147461</v>
+        <v>9.599753379821777</v>
       </c>
       <c r="C495" t="n">
-        <v>9.775357745665575</v>
+        <v>9.775358716785163</v>
       </c>
       <c r="D495" t="n">
-        <v>9.549580077814044</v>
+        <v>9.549581026504057</v>
       </c>
       <c r="E495" t="n">
-        <v>9.658287532653498</v>
+        <v>9.658288492142907</v>
       </c>
       <c r="F495" t="n">
         <v>169823</v>
@@ -10352,16 +10352,16 @@
         <v>45041</v>
       </c>
       <c r="B497" t="n">
-        <v>9.248543739318848</v>
+        <v>9.248541831970215</v>
       </c>
       <c r="C497" t="n">
-        <v>9.633202971819085</v>
+        <v>9.633200985141286</v>
       </c>
       <c r="D497" t="n">
-        <v>9.248543739318848</v>
+        <v>9.248541831970215</v>
       </c>
       <c r="E497" t="n">
-        <v>9.633202971819085</v>
+        <v>9.633200985141286</v>
       </c>
       <c r="F497" t="n">
         <v>58153</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.281991958618164</v>
+        <v>9.28199291229248</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382337504280539</v>
+        <v>9.382338468264816</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215094088036043</v>
+        <v>9.215095034836967</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248542603256835</v>
+        <v>9.248543553494413</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10392,16 +10392,16 @@
         <v>45043</v>
       </c>
       <c r="B499" t="n">
-        <v>9.315441131591797</v>
+        <v>9.31544017791748</v>
       </c>
       <c r="C499" t="n">
-        <v>9.365614332560945</v>
+        <v>9.365613373750113</v>
       </c>
       <c r="D499" t="n">
-        <v>9.139835768340454</v>
+        <v>9.139834832643849</v>
       </c>
       <c r="E499" t="n">
-        <v>9.365614332560945</v>
+        <v>9.365613373750113</v>
       </c>
       <c r="F499" t="n">
         <v>124734</v>
@@ -10412,16 +10412,16 @@
         <v>45044</v>
       </c>
       <c r="B500" t="n">
-        <v>9.176148414611816</v>
+        <v>9.1761474609375</v>
       </c>
       <c r="C500" t="n">
-        <v>9.393831370760845</v>
+        <v>9.393830394462805</v>
       </c>
       <c r="D500" t="n">
-        <v>9.176148414611816</v>
+        <v>9.1761474609375</v>
       </c>
       <c r="E500" t="n">
-        <v>9.326851546700507</v>
+        <v>9.326850577363659</v>
       </c>
       <c r="F500" t="n">
         <v>147595</v>
@@ -10432,16 +10432,16 @@
         <v>45048</v>
       </c>
       <c r="B501" t="n">
-        <v>9.10916805267334</v>
+        <v>9.109169006347656</v>
       </c>
       <c r="C501" t="n">
-        <v>9.201264350497761</v>
+        <v>9.201265313813998</v>
       </c>
       <c r="D501" t="n">
-        <v>9.017071754848917</v>
+        <v>9.017072698881314</v>
       </c>
       <c r="E501" t="n">
-        <v>9.176147025423896</v>
+        <v>9.176147986110502</v>
       </c>
       <c r="F501" t="n">
         <v>926867</v>
@@ -10512,16 +10512,16 @@
         <v>45054</v>
       </c>
       <c r="B505" t="n">
-        <v>9.385458946228027</v>
+        <v>9.385457992553711</v>
       </c>
       <c r="C505" t="n">
-        <v>9.519416908270202</v>
+        <v>9.519415940984162</v>
       </c>
       <c r="D505" t="n">
-        <v>9.326851286372412</v>
+        <v>9.326850338653331</v>
       </c>
       <c r="E505" t="n">
-        <v>9.41894759556884</v>
+        <v>9.418946638491677</v>
       </c>
       <c r="F505" t="n">
         <v>225237</v>
@@ -10532,16 +10532,16 @@
         <v>45055</v>
       </c>
       <c r="B506" t="n">
-        <v>9.502671241760254</v>
+        <v>9.502670288085938</v>
       </c>
       <c r="C506" t="n">
-        <v>9.594767546104379</v>
+        <v>9.594766583187411</v>
       </c>
       <c r="D506" t="n">
-        <v>9.343595959923981</v>
+        <v>9.343595022214229</v>
       </c>
       <c r="E506" t="n">
-        <v>9.385458451733838</v>
+        <v>9.385457509822828</v>
       </c>
       <c r="F506" t="n">
         <v>112092</v>
@@ -10692,16 +10692,16 @@
         <v>45065</v>
       </c>
       <c r="B514" t="n">
-        <v>9.79570484161377</v>
+        <v>9.795705795288086</v>
       </c>
       <c r="C514" t="n">
-        <v>10.05524941818936</v>
+        <v>10.05525039713199</v>
       </c>
       <c r="D514" t="n">
-        <v>9.703608541764943</v>
+        <v>9.703609486473098</v>
       </c>
       <c r="E514" t="n">
-        <v>9.938035792714553</v>
+        <v>9.938036760245696</v>
       </c>
       <c r="F514" t="n">
         <v>287815</v>
@@ -10892,16 +10892,16 @@
         <v>45079</v>
       </c>
       <c r="B524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="C524" t="n">
-        <v>9.234754909248267</v>
+        <v>9.234753923397504</v>
       </c>
       <c r="D524" t="n">
-        <v>8.933348655700684</v>
+        <v>8.933347702026367</v>
       </c>
       <c r="E524" t="n">
-        <v>9.084051782474475</v>
+        <v>9.084050812711935</v>
       </c>
       <c r="F524" t="n">
         <v>446577</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958464622497559</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C526" t="n">
-        <v>9.0589330780245</v>
+        <v>9.058934042394197</v>
       </c>
       <c r="D526" t="n">
-        <v>8.832878842796482</v>
+        <v>8.83287978310155</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933347298323424</v>
+        <v>8.933348249323872</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -10952,16 +10952,16 @@
         <v>45084</v>
       </c>
       <c r="B527" t="n">
-        <v>9.11754035949707</v>
+        <v>9.117542266845703</v>
       </c>
       <c r="C527" t="n">
-        <v>9.192891487799923</v>
+        <v>9.192893410911674</v>
       </c>
       <c r="D527" t="n">
-        <v>8.966836420552241</v>
+        <v>8.966838296374284</v>
       </c>
       <c r="E527" t="n">
-        <v>9.092422195170036</v>
+        <v>9.092424097264061</v>
       </c>
       <c r="F527" t="n">
         <v>438781</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.167776107788086</v>
+        <v>9.16777515411377</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226382927187608</v>
+        <v>9.226381967416739</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109169288388564</v>
+        <v>9.109168340810799</v>
       </c>
       <c r="E528" t="n">
-        <v>9.20963860231331</v>
+        <v>9.209637644284264</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.991955757141113</v>
       </c>
       <c r="C535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.991955757141113</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899858501814995</v>
+        <v>8.899859445721704</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983582641817451</v>
+        <v>8.983583594603827</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950092315673828</v>
+        <v>8.950093269348145</v>
       </c>
       <c r="C537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="D537" t="n">
-        <v>8.832878698884004</v>
+        <v>8.83287964006866</v>
       </c>
       <c r="E537" t="n">
-        <v>9.00032612203405</v>
+        <v>9.000327081061014</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11172,16 +11172,16 @@
         <v>45100</v>
       </c>
       <c r="B538" t="n">
-        <v>8.983583450317383</v>
+        <v>8.983582496643066</v>
       </c>
       <c r="C538" t="n">
-        <v>9.008700778695582</v>
+        <v>9.008699822354874</v>
       </c>
       <c r="D538" t="n">
-        <v>8.874741974401767</v>
+        <v>8.874741032281783</v>
       </c>
       <c r="E538" t="n">
-        <v>8.899859302779966</v>
+        <v>8.89985835799359</v>
       </c>
       <c r="F538" t="n">
         <v>372938</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958464622497559</v>
+        <v>8.958465576171875</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000326268674719</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841251003797995</v>
+        <v>8.841251944994323</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000326268674719</v>
+        <v>9.000327226805421</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11232,16 +11232,16 @@
         <v>45105</v>
       </c>
       <c r="B541" t="n">
-        <v>8.657059669494629</v>
+        <v>8.657058715820312</v>
       </c>
       <c r="C541" t="n">
-        <v>8.87474177527181</v>
+        <v>8.874740797617315</v>
       </c>
       <c r="D541" t="n">
-        <v>8.657059669494629</v>
+        <v>8.657058715820312</v>
       </c>
       <c r="E541" t="n">
-        <v>8.87474177527181</v>
+        <v>8.874740797617315</v>
       </c>
       <c r="F541" t="n">
         <v>189418</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703607559204102</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703608512878418</v>
+        <v>9.703607559204102</v>
       </c>
       <c r="D550" t="n">
-        <v>9.385457965682171</v>
+        <v>9.38545704327581</v>
       </c>
       <c r="E550" t="n">
-        <v>9.619884374764274</v>
+        <v>9.619883429318397</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11432,16 +11432,16 @@
         <v>45119</v>
       </c>
       <c r="B551" t="n">
-        <v>9.778960227966309</v>
+        <v>9.778959274291992</v>
       </c>
       <c r="C551" t="n">
-        <v>9.912919025122674</v>
+        <v>9.912918058384282</v>
       </c>
       <c r="D551" t="n">
-        <v>9.594767617899787</v>
+        <v>9.594766682188503</v>
       </c>
       <c r="E551" t="n">
-        <v>9.753843742096077</v>
+        <v>9.753842790871198</v>
       </c>
       <c r="F551" t="n">
         <v>281073</v>
@@ -11512,16 +11512,16 @@
         <v>45125</v>
       </c>
       <c r="B555" t="n">
-        <v>9.79570484161377</v>
+        <v>9.795705795288086</v>
       </c>
       <c r="C555" t="n">
-        <v>9.837567331380283</v>
+        <v>9.83756828913018</v>
       </c>
       <c r="D555" t="n">
-        <v>9.310106016743662</v>
+        <v>9.310106923141838</v>
       </c>
       <c r="E555" t="n">
-        <v>9.469181290815333</v>
+        <v>9.469182212700503</v>
       </c>
       <c r="F555" t="n">
         <v>306673</v>
@@ -11572,16 +11572,16 @@
         <v>45128</v>
       </c>
       <c r="B558" t="n">
-        <v>9.737098693847656</v>
+        <v>9.73709774017334</v>
       </c>
       <c r="C558" t="n">
-        <v>9.753843859131761</v>
+        <v>9.753842903817384</v>
       </c>
       <c r="D558" t="n">
-        <v>9.527788754229716</v>
+        <v>9.527787821055707</v>
       </c>
       <c r="E558" t="n">
-        <v>9.628257222425235</v>
+        <v>9.628256279411108</v>
       </c>
       <c r="F558" t="n">
         <v>205537</v>
@@ -11632,16 +11632,16 @@
         <v>45133</v>
       </c>
       <c r="B561" t="n">
-        <v>9.544532775878906</v>
+        <v>9.54453182220459</v>
       </c>
       <c r="C561" t="n">
-        <v>9.820822526707969</v>
+        <v>9.820821545427227</v>
       </c>
       <c r="D561" t="n">
-        <v>9.460809475620675</v>
+        <v>9.460808530311857</v>
       </c>
       <c r="E561" t="n">
-        <v>9.820822526707969</v>
+        <v>9.820821545427227</v>
       </c>
       <c r="F561" t="n">
         <v>168665</v>
@@ -11652,16 +11652,16 @@
         <v>45134</v>
       </c>
       <c r="B562" t="n">
-        <v>9.720352172851562</v>
+        <v>9.720353126525879</v>
       </c>
       <c r="C562" t="n">
-        <v>9.720352172851562</v>
+        <v>9.720353126525879</v>
       </c>
       <c r="D562" t="n">
-        <v>9.502670101536864</v>
+        <v>9.502671033854156</v>
       </c>
       <c r="E562" t="n">
-        <v>9.686862688123885</v>
+        <v>9.686863638512511</v>
       </c>
       <c r="F562" t="n">
         <v>987127</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728724479675293</v>
+        <v>9.728725433349609</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795704291304954</v>
+        <v>9.795705251545078</v>
       </c>
       <c r="D564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="E564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11732,16 +11732,16 @@
         <v>45140</v>
       </c>
       <c r="B566" t="n">
-        <v>9.79570484161377</v>
+        <v>9.795705795288086</v>
       </c>
       <c r="C566" t="n">
-        <v>9.887801141462594</v>
+        <v>9.887802104103073</v>
       </c>
       <c r="D566" t="n">
-        <v>9.6952363802795</v>
+        <v>9.69523732417257</v>
       </c>
       <c r="E566" t="n">
-        <v>9.77058751598779</v>
+        <v>9.770588467216776</v>
       </c>
       <c r="F566" t="n">
         <v>111986</v>
@@ -11772,16 +11772,16 @@
         <v>45142</v>
       </c>
       <c r="B568" t="n">
-        <v>9.996642112731934</v>
+        <v>9.996641159057617</v>
       </c>
       <c r="C568" t="n">
-        <v>10.01338811862582</v>
+        <v>10.01338716335395</v>
       </c>
       <c r="D568" t="n">
-        <v>9.770587856557917</v>
+        <v>9.770586924449054</v>
       </c>
       <c r="E568" t="n">
-        <v>9.862684159616911</v>
+        <v>9.862683218722113</v>
       </c>
       <c r="F568" t="n">
         <v>196582</v>
@@ -11792,16 +11792,16 @@
         <v>45145</v>
       </c>
       <c r="B569" t="n">
-        <v>9.879429817199707</v>
+        <v>9.879428863525391</v>
       </c>
       <c r="C569" t="n">
-        <v>9.988270449243014</v>
+        <v>9.988269485062169</v>
       </c>
       <c r="D569" t="n">
-        <v>9.770588343986683</v>
+        <v>9.770587400818977</v>
       </c>
       <c r="E569" t="n">
-        <v>9.988270449243014</v>
+        <v>9.988269485062169</v>
       </c>
       <c r="F569" t="n">
         <v>215967</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578022956848145</v>
+        <v>9.578022003173828</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695236584795509</v>
+        <v>9.695235619450347</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469181490562828</v>
+        <v>9.469180547725751</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686863581963795</v>
+        <v>9.686862617452325</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11852,16 +11852,16 @@
         <v>45148</v>
       </c>
       <c r="B572" t="n">
-        <v>9.778960227966309</v>
+        <v>9.778959274291992</v>
       </c>
       <c r="C572" t="n">
-        <v>9.837567885172595</v>
+        <v>9.837566925782678</v>
       </c>
       <c r="D572" t="n">
-        <v>9.54453296381994</v>
+        <v>9.544532033007691</v>
       </c>
       <c r="E572" t="n">
-        <v>9.5780232939863</v>
+        <v>9.578022359907973</v>
       </c>
       <c r="F572" t="n">
         <v>202060</v>
@@ -11912,16 +11912,16 @@
         <v>45153</v>
       </c>
       <c r="B575" t="n">
-        <v>11.10179901123047</v>
+        <v>11.10179996490479</v>
       </c>
       <c r="C575" t="n">
-        <v>11.10179901123047</v>
+        <v>11.10179996490479</v>
       </c>
       <c r="D575" t="n">
-        <v>10.54084905234865</v>
+        <v>10.54084995783585</v>
       </c>
       <c r="E575" t="n">
-        <v>10.72504165148921</v>
+        <v>10.72504257279906</v>
       </c>
       <c r="F575" t="n">
         <v>301089</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294612667715</v>
+        <v>10.63294521258928</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109669703995</v>
+        <v>10.95109575560148</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646125793457</v>
+        <v>11.38646221160889</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527578824517</v>
+        <v>10.77527669072958</v>
       </c>
       <c r="E578" t="n">
-        <v>11.0934271862458</v>
+        <v>11.09342811537701</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716468811035</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716373443604</v>
+        <v>11.53716468811035</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10179954134582</v>
+        <v>11.10180045903246</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877851856436</v>
+        <v>11.16877944178756</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12112,16 +12112,16 @@
         <v>45167</v>
       </c>
       <c r="B585" t="n">
-        <v>12.49161624908447</v>
+        <v>12.49161720275879</v>
       </c>
       <c r="C585" t="n">
-        <v>12.71767217435969</v>
+        <v>12.71767314529228</v>
       </c>
       <c r="D585" t="n">
-        <v>11.90554897677267</v>
+        <v>11.90554988570359</v>
       </c>
       <c r="E585" t="n">
-        <v>11.92229414051626</v>
+        <v>11.9222950507256</v>
       </c>
       <c r="F585" t="n">
         <v>842903</v>
@@ -12132,16 +12132,16 @@
         <v>45168</v>
       </c>
       <c r="B586" t="n">
-        <v>12.4665002822876</v>
+        <v>12.46650123596191</v>
       </c>
       <c r="C586" t="n">
-        <v>12.57534090704158</v>
+        <v>12.57534186904209</v>
       </c>
       <c r="D586" t="n">
-        <v>12.30742416421925</v>
+        <v>12.30742510572441</v>
       </c>
       <c r="E586" t="n">
-        <v>12.51673409326264</v>
+        <v>12.51673505077979</v>
       </c>
       <c r="F586" t="n">
         <v>381576</v>
@@ -12152,16 +12152,16 @@
         <v>45169</v>
       </c>
       <c r="B587" t="n">
-        <v>12.26556205749512</v>
+        <v>12.26556301116943</v>
       </c>
       <c r="C587" t="n">
-        <v>12.39114784200412</v>
+        <v>12.39114880544301</v>
       </c>
       <c r="D587" t="n">
-        <v>12.081368620223</v>
+        <v>12.08136955957587</v>
       </c>
       <c r="E587" t="n">
-        <v>12.37440351936005</v>
+        <v>12.37440448149703</v>
       </c>
       <c r="F587" t="n">
         <v>308253</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625325429223</v>
+        <v>12.05625227825024</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66275070046011</v>
+        <v>11.66274975627503</v>
       </c>
       <c r="E589" t="n">
-        <v>11.99764643726385</v>
+        <v>11.9976454659665</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80508024202364</v>
+        <v>11.80507928016331</v>
       </c>
       <c r="D590" t="n">
-        <v>11.5957703116373</v>
+        <v>11.59576936683122</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996291579013</v>
+        <v>11.77996195597632</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996253967285</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879190103679</v>
+        <v>11.52879096769665</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93903865368277</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12312,16 +12312,16 @@
         <v>45182</v>
       </c>
       <c r="B595" t="n">
-        <v>12.4665002822876</v>
+        <v>12.46650123596191</v>
       </c>
       <c r="C595" t="n">
-        <v>12.4665002822876</v>
+        <v>12.46650123596191</v>
       </c>
       <c r="D595" t="n">
-        <v>12.14834888732056</v>
+        <v>12.14834981665663</v>
       </c>
       <c r="E595" t="n">
-        <v>12.30742416421925</v>
+        <v>12.30742510572441</v>
       </c>
       <c r="F595" t="n">
         <v>353764</v>
@@ -12332,16 +12332,16 @@
         <v>45183</v>
       </c>
       <c r="B596" t="n">
-        <v>12.34091377258301</v>
+        <v>12.34091472625732</v>
       </c>
       <c r="C596" t="n">
-        <v>12.51673421563881</v>
+        <v>12.51673518290008</v>
       </c>
       <c r="D596" t="n">
-        <v>12.2655626347989</v>
+        <v>12.26556358265027</v>
       </c>
       <c r="E596" t="n">
-        <v>12.47487256588872</v>
+        <v>12.47487352991503</v>
       </c>
       <c r="F596" t="n">
         <v>207012</v>
@@ -12352,16 +12352,16 @@
         <v>45184</v>
       </c>
       <c r="B597" t="n">
-        <v>12.03950786590576</v>
+        <v>12.03950691223145</v>
       </c>
       <c r="C597" t="n">
-        <v>12.33254194561951</v>
+        <v>12.33254096873336</v>
       </c>
       <c r="D597" t="n">
-        <v>11.87206042119054</v>
+        <v>11.87205948078009</v>
       </c>
       <c r="E597" t="n">
-        <v>12.29068029473313</v>
+        <v>12.29067932116292</v>
       </c>
       <c r="F597" t="n">
         <v>162660</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461177825928</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C599" t="n">
-        <v>11.8636870561786</v>
+        <v>11.86368608954307</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414247332525</v>
+        <v>11.60414152783702</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786661371372</v>
+        <v>11.68786566140377</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12432,16 +12432,16 @@
         <v>45190</v>
       </c>
       <c r="B601" t="n">
-        <v>11.44506740570068</v>
+        <v>11.44506645202637</v>
       </c>
       <c r="C601" t="n">
-        <v>11.83019862679808</v>
+        <v>11.83019764103224</v>
       </c>
       <c r="D601" t="n">
-        <v>11.44506740570068</v>
+        <v>11.44506645202637</v>
       </c>
       <c r="E601" t="n">
-        <v>11.83019862679808</v>
+        <v>11.83019764103224</v>
       </c>
       <c r="F601" t="n">
         <v>277385</v>
@@ -12452,16 +12452,16 @@
         <v>45191</v>
       </c>
       <c r="B602" t="n">
-        <v>11.54553604125977</v>
+        <v>11.54553699493408</v>
       </c>
       <c r="C602" t="n">
-        <v>11.73810164061331</v>
+        <v>11.73810261019376</v>
       </c>
       <c r="D602" t="n">
-        <v>11.47855706808011</v>
+        <v>11.47855801622189</v>
       </c>
       <c r="E602" t="n">
-        <v>11.52879087738004</v>
+        <v>11.52879182967118</v>
       </c>
       <c r="F602" t="n">
         <v>228714</v>
@@ -12472,16 +12472,16 @@
         <v>45194</v>
       </c>
       <c r="B603" t="n">
-        <v>11.11854362487793</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C603" t="n">
-        <v>11.54553561458025</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="D603" t="n">
-        <v>11.10179846161704</v>
+        <v>11.10179941385507</v>
       </c>
       <c r="E603" t="n">
-        <v>11.54553561458025</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="F603" t="n">
         <v>266745</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342765808105</v>
+        <v>11.09342670440674</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27762027064262</v>
+        <v>11.27761930113372</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760720758964</v>
+        <v>10.91760626903017</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901345381215</v>
+        <v>11.21901248934153</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12512,16 +12512,16 @@
         <v>45196</v>
       </c>
       <c r="B605" t="n">
-        <v>10.76690292358398</v>
+        <v>10.7669038772583</v>
       </c>
       <c r="C605" t="n">
-        <v>11.12691594782012</v>
+        <v>11.12691693338246</v>
       </c>
       <c r="D605" t="n">
-        <v>10.63294498022617</v>
+        <v>10.63294592203521</v>
       </c>
       <c r="E605" t="n">
-        <v>11.09342646198067</v>
+        <v>11.09342744457668</v>
       </c>
       <c r="F605" t="n">
         <v>269906</v>
@@ -12532,16 +12532,16 @@
         <v>45197</v>
       </c>
       <c r="B606" t="n">
-        <v>11.10179901123047</v>
+        <v>11.10179996490479</v>
       </c>
       <c r="C606" t="n">
-        <v>11.18552314934063</v>
+        <v>11.18552411020707</v>
       </c>
       <c r="D606" t="n">
-        <v>10.66643399775942</v>
+        <v>10.66643491403472</v>
       </c>
       <c r="E606" t="n">
-        <v>10.66643399775942</v>
+        <v>10.66643491403472</v>
       </c>
       <c r="F606" t="n">
         <v>215545</v>
@@ -12552,16 +12552,16 @@
         <v>45198</v>
       </c>
       <c r="B607" t="n">
-        <v>11.11854362487793</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C607" t="n">
-        <v>11.41994899304756</v>
+        <v>11.41994997257442</v>
       </c>
       <c r="D607" t="n">
-        <v>11.06830813509526</v>
+        <v>11.06830908446071</v>
       </c>
       <c r="E607" t="n">
-        <v>11.12691578592358</v>
+        <v>11.126916740316</v>
       </c>
       <c r="F607" t="n">
         <v>376204</v>
@@ -12572,16 +12572,16 @@
         <v>45201</v>
       </c>
       <c r="B608" t="n">
-        <v>10.80876445770264</v>
+        <v>10.80876541137695</v>
       </c>
       <c r="C608" t="n">
-        <v>11.11854367052903</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="D608" t="n">
-        <v>10.7166681623136</v>
+        <v>10.71666910786212</v>
       </c>
       <c r="E608" t="n">
-        <v>11.11854367052903</v>
+        <v>11.11854465153565</v>
       </c>
       <c r="F608" t="n">
         <v>151282</v>
@@ -12612,16 +12612,16 @@
         <v>45203</v>
       </c>
       <c r="B610" t="n">
-        <v>10.50735855102539</v>
+        <v>10.50735950469971</v>
       </c>
       <c r="C610" t="n">
-        <v>10.75015795872518</v>
+        <v>10.75015893443658</v>
       </c>
       <c r="D610" t="n">
-        <v>10.44037873693919</v>
+        <v>10.44037968453425</v>
       </c>
       <c r="E610" t="n">
-        <v>10.75015795872518</v>
+        <v>10.75015893443658</v>
       </c>
       <c r="F610" t="n">
         <v>180674</v>
@@ -12672,16 +12672,16 @@
         <v>45208</v>
       </c>
       <c r="B613" t="n">
-        <v>10.189208984375</v>
+        <v>10.18920803070068</v>
       </c>
       <c r="C613" t="n">
-        <v>10.41526324989824</v>
+        <v>10.41526227506603</v>
       </c>
       <c r="D613" t="n">
-        <v>10.189208984375</v>
+        <v>10.18920803070068</v>
       </c>
       <c r="E613" t="n">
-        <v>10.39851808448147</v>
+        <v>10.39851711121656</v>
       </c>
       <c r="F613" t="n">
         <v>296138</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203285217285</v>
+        <v>11.15203380584717</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457153766474</v>
+        <v>10.62457244623281</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411611417709</v>
+        <v>10.88411704494031</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12912,16 +12912,16 @@
         <v>45225</v>
       </c>
       <c r="B625" t="n">
-        <v>11.32785511016846</v>
+        <v>11.32785320281982</v>
       </c>
       <c r="C625" t="n">
-        <v>11.63763438768675</v>
+        <v>11.63763242817845</v>
       </c>
       <c r="D625" t="n">
-        <v>11.25250396237332</v>
+        <v>11.25250206771208</v>
       </c>
       <c r="E625" t="n">
-        <v>11.26087612520172</v>
+        <v>11.2608742291308</v>
       </c>
       <c r="F625" t="n">
         <v>344599</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668177956321</v>
+        <v>11.07668279217249</v>
       </c>
       <c r="D627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="E627" t="n">
-        <v>10.99295764074342</v>
+        <v>10.9929586456988</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -12992,16 +12992,16 @@
         <v>45231</v>
       </c>
       <c r="B629" t="n">
-        <v>10.78092288970947</v>
+        <v>10.78092384338379</v>
       </c>
       <c r="C629" t="n">
-        <v>10.78092288970947</v>
+        <v>10.78092384338379</v>
       </c>
       <c r="D629" t="n">
-        <v>10.45935660187757</v>
+        <v>10.45935752710632</v>
       </c>
       <c r="E629" t="n">
-        <v>10.54397939869632</v>
+        <v>10.54398033141075</v>
       </c>
       <c r="F629" t="n">
         <v>233349</v>
@@ -13072,16 +13072,16 @@
         <v>45238</v>
       </c>
       <c r="B633" t="n">
-        <v>11.40713214874268</v>
+        <v>11.40713119506836</v>
       </c>
       <c r="C633" t="n">
-        <v>11.40713214874268</v>
+        <v>11.40713119506836</v>
       </c>
       <c r="D633" t="n">
-        <v>11.01786790952223</v>
+        <v>11.0178669883917</v>
       </c>
       <c r="E633" t="n">
-        <v>11.22096248002823</v>
+        <v>11.22096154191832</v>
       </c>
       <c r="F633" t="n">
         <v>171088</v>
@@ -13092,16 +13092,16 @@
         <v>45239</v>
       </c>
       <c r="B634" t="n">
-        <v>11.33097076416016</v>
+        <v>11.33097171783447</v>
       </c>
       <c r="C634" t="n">
-        <v>11.63561130558296</v>
+        <v>11.63561228489743</v>
       </c>
       <c r="D634" t="n">
-        <v>11.25480999115565</v>
+        <v>11.25481093841988</v>
       </c>
       <c r="E634" t="n">
-        <v>11.3394327888723</v>
+        <v>11.33943374325882</v>
       </c>
       <c r="F634" t="n">
         <v>143591</v>
@@ -13132,16 +13132,16 @@
         <v>45243</v>
       </c>
       <c r="B636" t="n">
-        <v>12.36336708068848</v>
+        <v>12.36336803436279</v>
       </c>
       <c r="C636" t="n">
-        <v>12.51568778136439</v>
+        <v>12.51568874678828</v>
       </c>
       <c r="D636" t="n">
-        <v>12.04180077917336</v>
+        <v>12.04180170804298</v>
       </c>
       <c r="E636" t="n">
-        <v>12.13488645477382</v>
+        <v>12.1348873908238</v>
       </c>
       <c r="F636" t="n">
         <v>539496</v>
@@ -13192,16 +13192,16 @@
         <v>45247</v>
       </c>
       <c r="B639" t="n">
-        <v>12.85417938232422</v>
+        <v>12.85418033599854</v>
       </c>
       <c r="C639" t="n">
-        <v>12.85417938232422</v>
+        <v>12.85418033599854</v>
       </c>
       <c r="D639" t="n">
-        <v>12.48183836875342</v>
+        <v>12.4818392948031</v>
       </c>
       <c r="E639" t="n">
-        <v>12.7018578267184</v>
+        <v>12.70185876909171</v>
       </c>
       <c r="F639" t="n">
         <v>197425</v>
@@ -13212,16 +13212,16 @@
         <v>45250</v>
       </c>
       <c r="B640" t="n">
-        <v>12.99803829193115</v>
+        <v>12.99803733825684</v>
       </c>
       <c r="C640" t="n">
-        <v>13.12497293214611</v>
+        <v>13.12497196915852</v>
       </c>
       <c r="D640" t="n">
-        <v>12.59184999383886</v>
+        <v>12.59184906996684</v>
       </c>
       <c r="E640" t="n">
-        <v>12.7357078357516</v>
+        <v>12.73570690132464</v>
       </c>
       <c r="F640" t="n">
         <v>416026</v>
@@ -13232,16 +13232,16 @@
         <v>45251</v>
       </c>
       <c r="B641" t="n">
-        <v>12.57492351531982</v>
+        <v>12.57492256164551</v>
       </c>
       <c r="C641" t="n">
-        <v>13.10804642283821</v>
+        <v>13.10804542873219</v>
       </c>
       <c r="D641" t="n">
-        <v>12.41414163079623</v>
+        <v>12.41414068931551</v>
       </c>
       <c r="E641" t="n">
-        <v>12.99803754126984</v>
+        <v>12.99803655550682</v>
       </c>
       <c r="F641" t="n">
         <v>206064</v>
@@ -13352,16 +13352,16 @@
         <v>45259</v>
       </c>
       <c r="B647" t="n">
-        <v>12.93033790588379</v>
+        <v>12.93033885955811</v>
       </c>
       <c r="C647" t="n">
-        <v>13.23498015384819</v>
+        <v>13.23498112999133</v>
       </c>
       <c r="D647" t="n">
-        <v>12.90495183123531</v>
+        <v>12.90495278303728</v>
       </c>
       <c r="E647" t="n">
-        <v>13.20959237880287</v>
+        <v>13.20959335307354</v>
       </c>
       <c r="F647" t="n">
         <v>170772</v>
@@ -13612,16 +13612,16 @@
         <v>45278</v>
       </c>
       <c r="B660" t="n">
-        <v>13.16728210449219</v>
+        <v>13.1672830581665</v>
       </c>
       <c r="C660" t="n">
-        <v>13.66655605250602</v>
+        <v>13.66655704234154</v>
       </c>
       <c r="D660" t="n">
-        <v>13.15882007915931</v>
+        <v>13.15882103222074</v>
       </c>
       <c r="E660" t="n">
-        <v>13.26882980928061</v>
+        <v>13.26883077030978</v>
       </c>
       <c r="F660" t="n">
         <v>541076</v>
@@ -13632,16 +13632,16 @@
         <v>45279</v>
       </c>
       <c r="B661" t="n">
-        <v>13.39576435089111</v>
+        <v>13.3957633972168</v>
       </c>
       <c r="C661" t="n">
-        <v>13.45500023198255</v>
+        <v>13.4549992740911</v>
       </c>
       <c r="D661" t="n">
-        <v>13.17574572835084</v>
+        <v>13.17574479034014</v>
       </c>
       <c r="E661" t="n">
-        <v>13.20959383160479</v>
+        <v>13.20959289118437</v>
       </c>
       <c r="F661" t="n">
         <v>220918</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45499992370605</v>
+        <v>13.45500087738037</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040546826266</v>
+        <v>13.70040643933103</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806613861795</v>
+        <v>13.32806708329535</v>
       </c>
       <c r="E662" t="n">
-        <v>13.3873011681537</v>
+        <v>13.38730211702961</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13712,16 +13712,16 @@
         <v>45286</v>
       </c>
       <c r="B665" t="n">
-        <v>14.18137836456299</v>
+        <v>14.1813793182373</v>
       </c>
       <c r="C665" t="n">
-        <v>14.18137836456299</v>
+        <v>14.1813793182373</v>
       </c>
       <c r="D665" t="n">
-        <v>13.77109940684673</v>
+        <v>13.77110033293046</v>
       </c>
       <c r="E665" t="n">
-        <v>13.88704810014603</v>
+        <v>13.88704903402712</v>
       </c>
       <c r="F665" t="n">
         <v>187522</v>
@@ -13772,16 +13772,16 @@
         <v>45293</v>
       </c>
       <c r="B668" t="n">
-        <v>14.08326816558838</v>
+        <v>14.08326721191406</v>
       </c>
       <c r="C668" t="n">
-        <v>14.57381860242266</v>
+        <v>14.57381761552982</v>
       </c>
       <c r="D668" t="n">
-        <v>13.94056290981735</v>
+        <v>13.94056196580658</v>
       </c>
       <c r="E668" t="n">
-        <v>14.27056948586068</v>
+        <v>14.27056851950291</v>
       </c>
       <c r="F668" t="n">
         <v>272434</v>
@@ -13812,16 +13812,16 @@
         <v>45295</v>
       </c>
       <c r="B670" t="n">
-        <v>13.98515892028809</v>
+        <v>13.98515796661377</v>
       </c>
       <c r="C670" t="n">
-        <v>14.35084183229246</v>
+        <v>14.35084085368154</v>
       </c>
       <c r="D670" t="n">
-        <v>13.83353480092614</v>
+        <v>13.83353385759136</v>
       </c>
       <c r="E670" t="n">
-        <v>14.26165149011384</v>
+        <v>14.26165051758498</v>
       </c>
       <c r="F670" t="n">
         <v>190472</v>
@@ -13852,16 +13852,16 @@
         <v>45299</v>
       </c>
       <c r="B672" t="n">
-        <v>13.79785633087158</v>
+        <v>13.7978572845459</v>
       </c>
       <c r="C672" t="n">
-        <v>13.97623879116109</v>
+        <v>13.97623975716477</v>
       </c>
       <c r="D672" t="n">
-        <v>13.66406993370299</v>
+        <v>13.66407087813031</v>
       </c>
       <c r="E672" t="n">
-        <v>13.96731904087866</v>
+        <v>13.96732000626583</v>
       </c>
       <c r="F672" t="n">
         <v>138218</v>
@@ -13872,16 +13872,16 @@
         <v>45300</v>
       </c>
       <c r="B673" t="n">
-        <v>14.18137836456299</v>
+        <v>14.1813793182373</v>
       </c>
       <c r="C673" t="n">
-        <v>14.18137836456299</v>
+        <v>14.1813793182373</v>
       </c>
       <c r="D673" t="n">
-        <v>13.61055554479229</v>
+        <v>13.61055646007971</v>
       </c>
       <c r="E673" t="n">
-        <v>13.78001826137833</v>
+        <v>13.78001918806184</v>
       </c>
       <c r="F673" t="n">
         <v>115358</v>
@@ -13912,16 +13912,16 @@
         <v>45302</v>
       </c>
       <c r="B675" t="n">
-        <v>14.2081356048584</v>
+        <v>14.20813465118408</v>
       </c>
       <c r="C675" t="n">
-        <v>14.2081356048584</v>
+        <v>14.20813465118408</v>
       </c>
       <c r="D675" t="n">
-        <v>13.64623340505142</v>
+        <v>13.64623248909294</v>
       </c>
       <c r="E675" t="n">
-        <v>14.13678386911013</v>
+        <v>14.13678292022506</v>
       </c>
       <c r="F675" t="n">
         <v>191209</v>
@@ -13972,16 +13972,16 @@
         <v>45307</v>
       </c>
       <c r="B678" t="n">
-        <v>14.31516551971436</v>
+        <v>14.31516647338867</v>
       </c>
       <c r="C678" t="n">
-        <v>14.44003217019812</v>
+        <v>14.44003313219104</v>
       </c>
       <c r="D678" t="n">
-        <v>14.13678305428537</v>
+        <v>14.13678399607587</v>
       </c>
       <c r="E678" t="n">
-        <v>14.34192208304131</v>
+        <v>14.34192303849815</v>
       </c>
       <c r="F678" t="n">
         <v>181728</v>
@@ -14052,16 +14052,16 @@
         <v>45313</v>
       </c>
       <c r="B682" t="n">
-        <v>14.52922344207764</v>
+        <v>14.52922439575195</v>
       </c>
       <c r="C682" t="n">
-        <v>14.79679714094238</v>
+        <v>14.7967981121798</v>
       </c>
       <c r="D682" t="n">
-        <v>14.27948834824271</v>
+        <v>14.27948928552483</v>
       </c>
       <c r="E682" t="n">
-        <v>14.60949582056619</v>
+        <v>14.60949677950945</v>
       </c>
       <c r="F682" t="n">
         <v>189524</v>
@@ -14232,16 +14232,16 @@
         <v>45324</v>
       </c>
       <c r="B691" t="n">
-        <v>13.76218032836914</v>
+        <v>13.76218128204346</v>
       </c>
       <c r="C691" t="n">
-        <v>13.76218032836914</v>
+        <v>13.76218128204346</v>
       </c>
       <c r="D691" t="n">
-        <v>13.28946760442967</v>
+        <v>13.28946852534654</v>
       </c>
       <c r="E691" t="n">
-        <v>13.70866540985612</v>
+        <v>13.70866635982202</v>
       </c>
       <c r="F691" t="n">
         <v>554139</v>
@@ -14252,16 +14252,16 @@
         <v>45327</v>
       </c>
       <c r="B692" t="n">
-        <v>13.21811580657959</v>
+        <v>13.21811485290527</v>
       </c>
       <c r="C692" t="n">
-        <v>13.76218119194509</v>
+        <v>13.76218019901698</v>
       </c>
       <c r="D692" t="n">
-        <v>13.21811580657959</v>
+        <v>13.21811485290527</v>
       </c>
       <c r="E692" t="n">
-        <v>13.76218119194509</v>
+        <v>13.76218019901698</v>
       </c>
       <c r="F692" t="n">
         <v>142538</v>
@@ -14272,16 +14272,16 @@
         <v>45328</v>
       </c>
       <c r="B693" t="n">
-        <v>13.41433525085449</v>
+        <v>13.41433620452881</v>
       </c>
       <c r="C693" t="n">
-        <v>13.47676902422233</v>
+        <v>13.47676998233529</v>
       </c>
       <c r="D693" t="n">
-        <v>13.08432867510856</v>
+        <v>13.0843296053215</v>
       </c>
       <c r="E693" t="n">
-        <v>13.20027647129375</v>
+        <v>13.20027740974985</v>
       </c>
       <c r="F693" t="n">
         <v>1178021</v>
@@ -14292,16 +14292,16 @@
         <v>45329</v>
       </c>
       <c r="B694" t="n">
-        <v>14.18137836456299</v>
+        <v>14.1813793182373</v>
       </c>
       <c r="C694" t="n">
-        <v>14.25273099301005</v>
+        <v>14.25273195148271</v>
       </c>
       <c r="D694" t="n">
-        <v>13.5124454566533</v>
+        <v>13.51244636534298</v>
       </c>
       <c r="E694" t="n">
-        <v>13.60163669026068</v>
+        <v>13.60163760494833</v>
       </c>
       <c r="F694" t="n">
         <v>562778</v>
@@ -14332,16 +14332,16 @@
         <v>45331</v>
       </c>
       <c r="B696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.86920833587646</v>
       </c>
       <c r="C696" t="n">
-        <v>13.86920928955078</v>
+        <v>13.86920833587646</v>
       </c>
       <c r="D696" t="n">
-        <v>13.49460665160678</v>
+        <v>13.49460572369088</v>
       </c>
       <c r="E696" t="n">
-        <v>13.74434263966654</v>
+        <v>13.74434169457831</v>
       </c>
       <c r="F696" t="n">
         <v>146541</v>
@@ -14352,16 +14352,16 @@
         <v>45336</v>
       </c>
       <c r="B697" t="n">
-        <v>13.53920078277588</v>
+        <v>13.5392017364502</v>
       </c>
       <c r="C697" t="n">
-        <v>13.86920822735105</v>
+        <v>13.86920920427044</v>
       </c>
       <c r="D697" t="n">
-        <v>13.43217184988765</v>
+        <v>13.43217279602306</v>
       </c>
       <c r="E697" t="n">
-        <v>13.86920822735105</v>
+        <v>13.86920920427044</v>
       </c>
       <c r="F697" t="n">
         <v>116200</v>
@@ -14372,16 +14372,16 @@
         <v>45337</v>
       </c>
       <c r="B698" t="n">
-        <v>13.51244449615479</v>
+        <v>13.5124454498291</v>
       </c>
       <c r="C698" t="n">
-        <v>13.6551506390021</v>
+        <v>13.65515160274826</v>
       </c>
       <c r="D698" t="n">
-        <v>13.3340620416199</v>
+        <v>13.33406298270443</v>
       </c>
       <c r="E698" t="n">
-        <v>13.51244449615479</v>
+        <v>13.5124454498291</v>
       </c>
       <c r="F698" t="n">
         <v>118097</v>
@@ -14452,16 +14452,16 @@
         <v>45343</v>
       </c>
       <c r="B702" t="n">
-        <v>13.75326061248779</v>
+        <v>13.75326156616211</v>
       </c>
       <c r="C702" t="n">
-        <v>14.09218601891464</v>
+        <v>14.09218699609062</v>
       </c>
       <c r="D702" t="n">
-        <v>13.52136324418864</v>
+        <v>13.5213641817828</v>
       </c>
       <c r="E702" t="n">
-        <v>13.85137069288472</v>
+        <v>13.85137165336216</v>
       </c>
       <c r="F702" t="n">
         <v>146120</v>
@@ -14472,16 +14472,16 @@
         <v>45344</v>
       </c>
       <c r="B703" t="n">
-        <v>13.71758556365967</v>
+        <v>13.71758460998535</v>
       </c>
       <c r="C703" t="n">
-        <v>13.83353516215277</v>
+        <v>13.8335342004174</v>
       </c>
       <c r="D703" t="n">
-        <v>13.37866010389759</v>
+        <v>13.37865917378605</v>
       </c>
       <c r="E703" t="n">
-        <v>13.77110048724197</v>
+        <v>13.77109952984718</v>
       </c>
       <c r="F703" t="n">
         <v>122205</v>
@@ -14512,16 +14512,16 @@
         <v>45348</v>
       </c>
       <c r="B705" t="n">
-        <v>13.53920078277588</v>
+        <v>13.5392017364502</v>
       </c>
       <c r="C705" t="n">
-        <v>13.73542094111948</v>
+        <v>13.73542190861516</v>
       </c>
       <c r="D705" t="n">
-        <v>13.30730431346953</v>
+        <v>13.30730525080952</v>
       </c>
       <c r="E705" t="n">
-        <v>13.52136307534302</v>
+        <v>13.52136402776089</v>
       </c>
       <c r="F705" t="n">
         <v>310571</v>
@@ -14692,16 +14692,16 @@
         <v>45359</v>
       </c>
       <c r="B714" t="n">
-        <v>13.41433525085449</v>
+        <v>13.41433620452881</v>
       </c>
       <c r="C714" t="n">
-        <v>13.42325410530787</v>
+        <v>13.42325505961626</v>
       </c>
       <c r="D714" t="n">
-        <v>12.96837998282627</v>
+        <v>12.96838090479599</v>
       </c>
       <c r="E714" t="n">
-        <v>13.15568040683267</v>
+        <v>13.15568134211827</v>
       </c>
       <c r="F714" t="n">
         <v>200691</v>
@@ -14712,16 +14712,16 @@
         <v>45362</v>
       </c>
       <c r="B715" t="n">
-        <v>13.73542213439941</v>
+        <v>13.7354211807251</v>
       </c>
       <c r="C715" t="n">
-        <v>13.86920943225391</v>
+        <v>13.8692084692905</v>
       </c>
       <c r="D715" t="n">
-        <v>13.25379055041456</v>
+        <v>13.25378963018077</v>
       </c>
       <c r="E715" t="n">
-        <v>13.42325416233122</v>
+        <v>13.42325323033127</v>
       </c>
       <c r="F715" t="n">
         <v>388635</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196426391602</v>
+        <v>16.32196617126465</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55385985657521</v>
+        <v>16.55386179102265</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26059101143806</v>
+        <v>15.26059279475697</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005372674877</v>
+        <v>15.43005552987071</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -15092,16 +15092,16 @@
         <v>45390</v>
       </c>
       <c r="B734" t="n">
-        <v>15.22491359710693</v>
+        <v>15.22491264343262</v>
       </c>
       <c r="C734" t="n">
-        <v>15.84033157274394</v>
+        <v>15.84033058052042</v>
       </c>
       <c r="D734" t="n">
-        <v>15.2070758884173</v>
+        <v>15.20707493586032</v>
       </c>
       <c r="E734" t="n">
-        <v>15.7422214866597</v>
+        <v>15.7422205005817</v>
       </c>
       <c r="F734" t="n">
         <v>693201</v>
@@ -15152,16 +15152,16 @@
         <v>45393</v>
       </c>
       <c r="B737" t="n">
-        <v>14.95510864257812</v>
+        <v>14.95510768890381</v>
       </c>
       <c r="C737" t="n">
-        <v>15.20600329805515</v>
+        <v>15.2060023283815</v>
       </c>
       <c r="D737" t="n">
-        <v>14.75797802365761</v>
+        <v>14.75797708255414</v>
       </c>
       <c r="E737" t="n">
-        <v>15.02679372595442</v>
+        <v>15.02679276770881</v>
       </c>
       <c r="F737" t="n">
         <v>214129</v>
@@ -15232,16 +15232,16 @@
         <v>45399</v>
       </c>
       <c r="B741" t="n">
-        <v>14.89238452911377</v>
+        <v>14.89238548278809</v>
       </c>
       <c r="C741" t="n">
-        <v>15.08951513615217</v>
+        <v>15.08951610245028</v>
       </c>
       <c r="D741" t="n">
-        <v>14.74901526709996</v>
+        <v>14.74901621159323</v>
       </c>
       <c r="E741" t="n">
-        <v>14.91030557485336</v>
+        <v>14.9103065296753</v>
       </c>
       <c r="F741" t="n">
         <v>190430</v>
@@ -15452,16 +15452,16 @@
         <v>45415</v>
       </c>
       <c r="B752" t="n">
-        <v>16.26334381103516</v>
+        <v>16.26334190368652</v>
       </c>
       <c r="C752" t="n">
-        <v>16.45151524660383</v>
+        <v>16.45151331718664</v>
       </c>
       <c r="D752" t="n">
-        <v>16.17373947497985</v>
+        <v>16.17373757813992</v>
       </c>
       <c r="E752" t="n">
-        <v>16.23646268943799</v>
+        <v>16.23646078524195</v>
       </c>
       <c r="F752" t="n">
         <v>303682</v>
@@ -15512,16 +15512,16 @@
         <v>45420</v>
       </c>
       <c r="B755" t="n">
-        <v>16.97122383117676</v>
+        <v>16.97122573852539</v>
       </c>
       <c r="C755" t="n">
-        <v>16.97122383117676</v>
+        <v>16.97122573852539</v>
       </c>
       <c r="D755" t="n">
-        <v>16.45151266999193</v>
+        <v>16.45151451893167</v>
       </c>
       <c r="E755" t="n">
-        <v>16.57696087145495</v>
+        <v>16.57696273449346</v>
       </c>
       <c r="F755" t="n">
         <v>667766</v>
@@ -15552,16 +15552,16 @@
         <v>45422</v>
       </c>
       <c r="B757" t="n">
-        <v>16.1020565032959</v>
+        <v>16.10205459594727</v>
       </c>
       <c r="C757" t="n">
-        <v>16.83681856624717</v>
+        <v>16.83681657186323</v>
       </c>
       <c r="D757" t="n">
-        <v>16.0751735874776</v>
+        <v>16.07517168331335</v>
       </c>
       <c r="E757" t="n">
-        <v>16.82785938650213</v>
+        <v>16.82785739317944</v>
       </c>
       <c r="F757" t="n">
         <v>188543</v>
@@ -15632,16 +15632,16 @@
         <v>45428</v>
       </c>
       <c r="B761" t="n">
-        <v>15.8153190612793</v>
+        <v>15.81531715393066</v>
       </c>
       <c r="C761" t="n">
-        <v>16.1289369359749</v>
+        <v>16.12893499080353</v>
       </c>
       <c r="D761" t="n">
-        <v>15.63610859113976</v>
+        <v>15.63610670540415</v>
       </c>
       <c r="E761" t="n">
-        <v>15.80635808972374</v>
+        <v>15.80635618345582</v>
       </c>
       <c r="F761" t="n">
         <v>286904</v>
@@ -15652,16 +15652,16 @@
         <v>45429</v>
       </c>
       <c r="B762" t="n">
-        <v>15.41209316253662</v>
+        <v>15.41209411621094</v>
       </c>
       <c r="C762" t="n">
-        <v>15.87804032767277</v>
+        <v>15.87804131017911</v>
       </c>
       <c r="D762" t="n">
-        <v>15.27768577448818</v>
+        <v>15.27768671984559</v>
       </c>
       <c r="E762" t="n">
-        <v>15.83323726759193</v>
+        <v>15.83323824732593</v>
       </c>
       <c r="F762" t="n">
         <v>361357</v>
@@ -15692,16 +15692,16 @@
         <v>45433</v>
       </c>
       <c r="B764" t="n">
-        <v>15.1701602935791</v>
+        <v>15.17016124725342</v>
       </c>
       <c r="C764" t="n">
-        <v>15.34937075101694</v>
+        <v>15.34937171595735</v>
       </c>
       <c r="D764" t="n">
-        <v>14.97302879039748</v>
+        <v>14.97302973167909</v>
       </c>
       <c r="E764" t="n">
-        <v>15.20600238506667</v>
+        <v>15.2060033409942</v>
       </c>
       <c r="F764" t="n">
         <v>342062</v>
@@ -15712,16 +15712,16 @@
         <v>45434</v>
       </c>
       <c r="B765" t="n">
-        <v>14.92822742462158</v>
+        <v>14.92822647094727</v>
       </c>
       <c r="C765" t="n">
-        <v>15.10743789166969</v>
+        <v>15.1074369265467</v>
       </c>
       <c r="D765" t="n">
-        <v>14.82966121969655</v>
+        <v>14.82966027231904</v>
       </c>
       <c r="E765" t="n">
-        <v>15.06263482685909</v>
+        <v>15.0626338645983</v>
       </c>
       <c r="F765" t="n">
         <v>235522</v>
@@ -15732,16 +15732,16 @@
         <v>45435</v>
       </c>
       <c r="B766" t="n">
-        <v>14.87446308135986</v>
+        <v>14.87446403503418</v>
       </c>
       <c r="C766" t="n">
-        <v>14.9461472623808</v>
+        <v>14.94614822065114</v>
       </c>
       <c r="D766" t="n">
-        <v>14.73109471931798</v>
+        <v>14.73109566380025</v>
       </c>
       <c r="E766" t="n">
-        <v>14.93718629170465</v>
+        <v>14.93718724940046</v>
       </c>
       <c r="F766" t="n">
         <v>226398</v>
@@ -15912,16 +15912,16 @@
         <v>45449</v>
       </c>
       <c r="B775" t="n">
-        <v>13.9784107208252</v>
+        <v>13.97841167449951</v>
       </c>
       <c r="C775" t="n">
-        <v>14.10385803673439</v>
+        <v>14.10385899896733</v>
       </c>
       <c r="D775" t="n">
-        <v>13.79920026952634</v>
+        <v>13.79920121097406</v>
       </c>
       <c r="E775" t="n">
-        <v>13.9784107208252</v>
+        <v>13.97841167449951</v>
       </c>
       <c r="F775" t="n">
         <v>568356</v>
@@ -15952,16 +15952,16 @@
         <v>45453</v>
       </c>
       <c r="B777" t="n">
-        <v>13.27949142456055</v>
+        <v>13.27949047088623</v>
       </c>
       <c r="C777" t="n">
-        <v>13.53038698013227</v>
+        <v>13.53038600843974</v>
       </c>
       <c r="D777" t="n">
-        <v>13.27949142456055</v>
+        <v>13.27949047088623</v>
       </c>
       <c r="E777" t="n">
-        <v>13.43182077300439</v>
+        <v>13.43181980839046</v>
       </c>
       <c r="F777" t="n">
         <v>375304</v>
@@ -16072,16 +16072,16 @@
         <v>45461</v>
       </c>
       <c r="B783" t="n">
-        <v>13.47662258148193</v>
+        <v>13.47662162780762</v>
       </c>
       <c r="C783" t="n">
-        <v>13.55726684324567</v>
+        <v>13.55726588386456</v>
       </c>
       <c r="D783" t="n">
-        <v>13.06443850910792</v>
+        <v>13.06443758460185</v>
       </c>
       <c r="E783" t="n">
-        <v>13.08235955573288</v>
+        <v>13.08235862995862</v>
       </c>
       <c r="F783" t="n">
         <v>385685</v>
@@ -16132,16 +16132,16 @@
         <v>45464</v>
       </c>
       <c r="B786" t="n">
-        <v>12.89418888092041</v>
+        <v>12.89418792724609</v>
       </c>
       <c r="C786" t="n">
-        <v>13.06443837404891</v>
+        <v>13.06443740778267</v>
       </c>
       <c r="D786" t="n">
-        <v>12.75978148067129</v>
+        <v>12.75978053693796</v>
       </c>
       <c r="E786" t="n">
-        <v>13.02859717726665</v>
+        <v>13.02859621365129</v>
       </c>
       <c r="F786" t="n">
         <v>315427</v>
@@ -16272,16 +16272,16 @@
         <v>45475</v>
       </c>
       <c r="B793" t="n">
-        <v>13.29741287231445</v>
+        <v>13.29741191864014</v>
       </c>
       <c r="C793" t="n">
-        <v>13.5483066263438</v>
+        <v>13.54830565467569</v>
       </c>
       <c r="D793" t="n">
-        <v>13.27053085460948</v>
+        <v>13.27052990286311</v>
       </c>
       <c r="E793" t="n">
-        <v>13.36013608679751</v>
+        <v>13.36013512862476</v>
       </c>
       <c r="F793" t="n">
         <v>528404</v>
@@ -16412,16 +16412,16 @@
         <v>45484</v>
       </c>
       <c r="B800" t="n">
-        <v>14.01425361633301</v>
+        <v>14.01425266265869</v>
       </c>
       <c r="C800" t="n">
-        <v>14.05905578368349</v>
+        <v>14.05905482696037</v>
       </c>
       <c r="D800" t="n">
-        <v>13.64687261810947</v>
+        <v>13.64687168943554</v>
       </c>
       <c r="E800" t="n">
-        <v>13.64687261810947</v>
+        <v>13.64687168943554</v>
       </c>
       <c r="F800" t="n">
         <v>415676</v>
@@ -16532,16 +16532,16 @@
         <v>45492</v>
       </c>
       <c r="B806" t="n">
-        <v>13.79023933410645</v>
+        <v>13.79024028778076</v>
       </c>
       <c r="C806" t="n">
-        <v>13.89776560516017</v>
+        <v>13.89776656627055</v>
       </c>
       <c r="D806" t="n">
-        <v>13.65583194333782</v>
+        <v>13.65583288771709</v>
       </c>
       <c r="E806" t="n">
-        <v>13.89776560516017</v>
+        <v>13.89776656627055</v>
       </c>
       <c r="F806" t="n">
         <v>491387</v>
@@ -16592,16 +16592,16 @@
         <v>45497</v>
       </c>
       <c r="B809" t="n">
-        <v>13.58414745330811</v>
+        <v>13.58414840698242</v>
       </c>
       <c r="C809" t="n">
-        <v>13.77231887141577</v>
+        <v>13.77231983830065</v>
       </c>
       <c r="D809" t="n">
-        <v>13.5214233485732</v>
+        <v>13.52142429784398</v>
       </c>
       <c r="E809" t="n">
-        <v>13.7275158114484</v>
+        <v>13.72751677518789</v>
       </c>
       <c r="F809" t="n">
         <v>613342</v>
@@ -16712,16 +16712,16 @@
         <v>45505</v>
       </c>
       <c r="B815" t="n">
-        <v>13.36013507843018</v>
+        <v>13.36013603210449</v>
       </c>
       <c r="C815" t="n">
-        <v>13.64687179979016</v>
+        <v>13.64687277393235</v>
       </c>
       <c r="D815" t="n">
-        <v>13.29741186868121</v>
+        <v>13.29741281787821</v>
       </c>
       <c r="E815" t="n">
-        <v>13.44077933326414</v>
+        <v>13.44078029269502</v>
       </c>
       <c r="F815" t="n">
         <v>623514</v>
@@ -16752,16 +16752,16 @@
         <v>45509</v>
       </c>
       <c r="B817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770233154297</v>
       </c>
       <c r="C817" t="n">
-        <v>13.23468850107574</v>
+        <v>13.23468948885766</v>
       </c>
       <c r="D817" t="n">
-        <v>12.77770137786865</v>
+        <v>12.77770233154297</v>
       </c>
       <c r="E817" t="n">
-        <v>13.04651706913838</v>
+        <v>13.04651804287597</v>
       </c>
       <c r="F817" t="n">
         <v>596040</v>
@@ -16792,16 +16792,16 @@
         <v>45511</v>
       </c>
       <c r="B819" t="n">
-        <v>12.93899154663086</v>
+        <v>12.93899059295654</v>
       </c>
       <c r="C819" t="n">
-        <v>13.00171565963084</v>
+        <v>13.00171470133341</v>
       </c>
       <c r="D819" t="n">
-        <v>12.75082099982525</v>
+        <v>12.75082006002013</v>
       </c>
       <c r="E819" t="n">
-        <v>13.00171565963084</v>
+        <v>13.00171470133341</v>
       </c>
       <c r="F819" t="n">
         <v>296971</v>
@@ -16812,16 +16812,16 @@
         <v>45512</v>
       </c>
       <c r="B820" t="n">
-        <v>12.80458354949951</v>
+        <v>12.8045825958252</v>
       </c>
       <c r="C820" t="n">
-        <v>13.1002803654145</v>
+        <v>13.10027938971694</v>
       </c>
       <c r="D820" t="n">
-        <v>12.80458354949951</v>
+        <v>12.8045825958252</v>
       </c>
       <c r="E820" t="n">
-        <v>13.00171505880854</v>
+        <v>13.00171409045204</v>
       </c>
       <c r="F820" t="n">
         <v>258486</v>
@@ -16952,16 +16952,16 @@
         <v>45523</v>
       </c>
       <c r="B827" t="n">
-        <v>12.33863639831543</v>
+        <v>12.33863544464111</v>
       </c>
       <c r="C827" t="n">
-        <v>12.44616267657907</v>
+        <v>12.44616171459386</v>
       </c>
       <c r="D827" t="n">
-        <v>12.03397950599891</v>
+        <v>12.03397857587205</v>
       </c>
       <c r="E827" t="n">
-        <v>12.28487325918361</v>
+        <v>12.28487230966474</v>
       </c>
       <c r="F827" t="n">
         <v>2509053</v>
@@ -16972,16 +16972,16 @@
         <v>45524</v>
       </c>
       <c r="B828" t="n">
-        <v>12.41032028198242</v>
+        <v>12.41031932830811</v>
       </c>
       <c r="C828" t="n">
-        <v>12.47304349472877</v>
+        <v>12.47304253623447</v>
       </c>
       <c r="D828" t="n">
-        <v>12.19526773068562</v>
+        <v>12.19526679353708</v>
       </c>
       <c r="E828" t="n">
-        <v>12.35655714415822</v>
+        <v>12.35655619461535</v>
       </c>
       <c r="F828" t="n">
         <v>514247</v>
@@ -16992,16 +16992,16 @@
         <v>45525</v>
       </c>
       <c r="B829" t="n">
-        <v>12.08774185180664</v>
+        <v>12.08774089813232</v>
       </c>
       <c r="C829" t="n">
-        <v>12.49992592198841</v>
+        <v>12.49992493579443</v>
       </c>
       <c r="D829" t="n">
-        <v>12.08774185180664</v>
+        <v>12.08774089813232</v>
       </c>
       <c r="E829" t="n">
-        <v>12.49992592198841</v>
+        <v>12.49992493579443</v>
       </c>
       <c r="F829" t="n">
         <v>645535</v>
@@ -17112,16 +17112,16 @@
         <v>45533</v>
       </c>
       <c r="B835" t="n">
-        <v>11.42466449737549</v>
+        <v>11.42466354370117</v>
       </c>
       <c r="C835" t="n">
-        <v>12.12358444475269</v>
+        <v>12.123583432736</v>
       </c>
       <c r="D835" t="n">
-        <v>11.29921627039831</v>
+        <v>11.29921532719579</v>
       </c>
       <c r="E835" t="n">
-        <v>11.93541389648125</v>
+        <v>11.93541290017211</v>
       </c>
       <c r="F835" t="n">
         <v>1428127</v>
@@ -17152,16 +17152,16 @@
         <v>45537</v>
       </c>
       <c r="B837" t="n">
-        <v>11.6845178604126</v>
+        <v>11.68451881408691</v>
       </c>
       <c r="C837" t="n">
-        <v>11.6845178604126</v>
+        <v>11.68451881408691</v>
       </c>
       <c r="D837" t="n">
-        <v>11.42466315363044</v>
+        <v>11.42466408609577</v>
       </c>
       <c r="E837" t="n">
-        <v>11.56803061881927</v>
+        <v>11.56803156298606</v>
       </c>
       <c r="F837" t="n">
         <v>1157790</v>
@@ -17192,16 +17192,16 @@
         <v>45539</v>
       </c>
       <c r="B839" t="n">
-        <v>11.64867687225342</v>
+        <v>11.6486759185791</v>
       </c>
       <c r="C839" t="n">
-        <v>11.85476846305313</v>
+        <v>11.85476749250614</v>
       </c>
       <c r="D839" t="n">
-        <v>11.50530849740244</v>
+        <v>11.50530755546566</v>
       </c>
       <c r="E839" t="n">
-        <v>11.50530849740244</v>
+        <v>11.50530755546566</v>
       </c>
       <c r="F839" t="n">
         <v>552941</v>
@@ -17252,16 +17252,16 @@
         <v>45544</v>
       </c>
       <c r="B842" t="n">
-        <v>11.23649120330811</v>
+        <v>11.23649215698242</v>
       </c>
       <c r="C842" t="n">
-        <v>11.41570075039603</v>
+        <v>11.41570171928039</v>
       </c>
       <c r="D842" t="n">
-        <v>11.20960918878185</v>
+        <v>11.20961014017461</v>
       </c>
       <c r="E842" t="n">
-        <v>11.35297754332981</v>
+        <v>11.35297850689067</v>
       </c>
       <c r="F842" t="n">
         <v>579052</v>
@@ -17312,16 +17312,16 @@
         <v>45547</v>
       </c>
       <c r="B845" t="n">
-        <v>11.34401798248291</v>
+        <v>11.34401893615723</v>
       </c>
       <c r="C845" t="n">
-        <v>11.47842537290442</v>
+        <v>11.47842633787816</v>
       </c>
       <c r="D845" t="n">
-        <v>11.2902548470949</v>
+        <v>11.29025579624943</v>
       </c>
       <c r="E845" t="n">
-        <v>11.39778111787093</v>
+        <v>11.39778207606503</v>
       </c>
       <c r="F845" t="n">
         <v>413998</v>
@@ -17352,16 +17352,16 @@
         <v>45551</v>
       </c>
       <c r="B847" t="n">
-        <v>11.46946620941162</v>
+        <v>11.4694652557373</v>
       </c>
       <c r="C847" t="n">
-        <v>11.62179465706196</v>
+        <v>11.62179369072169</v>
       </c>
       <c r="D847" t="n">
-        <v>11.46946620941162</v>
+        <v>11.4694652557373</v>
       </c>
       <c r="E847" t="n">
-        <v>11.59491353528131</v>
+        <v>11.59491257117618</v>
       </c>
       <c r="F847" t="n">
         <v>377086</v>
@@ -17392,16 +17392,16 @@
         <v>45553</v>
       </c>
       <c r="B849" t="n">
-        <v>11.42466449737549</v>
+        <v>11.42466354370117</v>
       </c>
       <c r="C849" t="n">
-        <v>11.7114003575755</v>
+        <v>11.71139937996589</v>
       </c>
       <c r="D849" t="n">
-        <v>11.39778247842404</v>
+        <v>11.39778152699371</v>
       </c>
       <c r="E849" t="n">
-        <v>11.6307560929155</v>
+        <v>11.63075512203768</v>
       </c>
       <c r="F849" t="n">
         <v>662418</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276733398438</v>
+        <v>10.49276828765869</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029359905444</v>
+        <v>10.60029456250169</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212308323033</v>
+        <v>10.41212402957499</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900509754635</v>
+        <v>10.43900604633429</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -26652,19 +26652,39 @@
         <v>46233</v>
       </c>
       <c r="B1312" t="n">
-        <v>5.51</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="C1312" t="n">
-        <v>5.55</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="D1312" t="n">
-        <v>5.33</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="E1312" t="n">
-        <v>5.38</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="F1312" t="n">
         <v>812600</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1313" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>528100</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1313"/>
+  <dimension ref="A1:F1314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44316</v>
       </c>
       <c r="B2" t="n">
-        <v>13.41818809509277</v>
+        <v>13.41818904876709</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80970374344109</v>
+        <v>14.80970479601495</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42424798962781</v>
+        <v>12.42424887265957</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50707647044507</v>
+        <v>12.50707735936371</v>
       </c>
       <c r="F2" t="n">
         <v>8063577</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970443725586</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606625476003</v>
+        <v>13.76606824847914</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404556981654</v>
+        <v>13.00404745317332</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647056839647</v>
+        <v>13.42647251293245</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -512,16 +512,16 @@
         <v>44321</v>
       </c>
       <c r="B5" t="n">
-        <v>12.93778419494629</v>
+        <v>12.93778324127197</v>
       </c>
       <c r="C5" t="n">
-        <v>13.33535974162644</v>
+        <v>13.3353587586459</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92949993209467</v>
+        <v>12.92949897903101</v>
       </c>
       <c r="E5" t="n">
-        <v>13.32707631094588</v>
+        <v>13.32707532857593</v>
       </c>
       <c r="F5" t="n">
         <v>876510</v>
@@ -532,16 +532,16 @@
         <v>44322</v>
       </c>
       <c r="B6" t="n">
-        <v>12.64788436889648</v>
+        <v>12.64788341522217</v>
       </c>
       <c r="C6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="D6" t="n">
-        <v>12.59818794458523</v>
+        <v>12.59818699465811</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12828923982652</v>
+        <v>13.12828824992877</v>
       </c>
       <c r="F6" t="n">
         <v>671078</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="C9" t="n">
-        <v>12.54849100757134</v>
+        <v>12.54848908114925</v>
       </c>
       <c r="D9" t="n">
-        <v>12.2171770654824</v>
+        <v>12.21717518992304</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566200256348</v>
+        <v>12.46566390991211</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75556044155362</v>
+        <v>12.7555623932591</v>
       </c>
       <c r="D10" t="n">
-        <v>12.30000503842248</v>
+        <v>12.30000692042424</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141969554326</v>
+        <v>12.3414215838818</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98142051696777</v>
+        <v>13.98142147064209</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778424385328</v>
+        <v>14.57778523820564</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495522297252</v>
+        <v>13.67495615574281</v>
       </c>
       <c r="E13" t="n">
-        <v>13.98970394752027</v>
+        <v>13.9897049017596</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889507293701</v>
+        <v>13.8488941192627</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24647062182232</v>
+        <v>14.24646964076982</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323894097274</v>
+        <v>13.68323799870598</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222914697741</v>
+        <v>14.12222817448053</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="D16" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253096774176</v>
+        <v>13.25253000199559</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21940040588379</v>
+        <v>13.21939849853516</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48445105518772</v>
+        <v>13.4844491095965</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687466514628</v>
+        <v>13.086872776919</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687466514628</v>
+        <v>13.086872776919</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -772,16 +772,16 @@
         <v>44340</v>
       </c>
       <c r="B18" t="n">
-        <v>13.42647075653076</v>
+        <v>13.42646884918213</v>
       </c>
       <c r="C18" t="n">
-        <v>14.02283448973993</v>
+        <v>14.02283249767257</v>
       </c>
       <c r="D18" t="n">
-        <v>13.3270762462152</v>
+        <v>13.32707435298643</v>
       </c>
       <c r="E18" t="n">
-        <v>13.40162212895187</v>
+        <v>13.40162022513321</v>
       </c>
       <c r="F18" t="n">
         <v>1040223</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970252990723</v>
+        <v>13.16970443725586</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131836345614</v>
+        <v>13.45132031159078</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313733320078</v>
+        <v>13.1531392381503</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707605947365</v>
+        <v>13.32707798961446</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889442443848</v>
+        <v>13.02889537811279</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879284288401</v>
+        <v>13.31879381777798</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263114417541</v>
+        <v>12.96263209299946</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111657277715</v>
+        <v>13.21111753978956</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980270385742</v>
+        <v>12.87980365753174</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111660958277</v>
+        <v>13.21111758778895</v>
       </c>
       <c r="D23" t="n">
-        <v>12.61475207857974</v>
+        <v>12.6147530126286</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374225471193</v>
+        <v>13.05374322126546</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253200531006</v>
+        <v>13.25253009796143</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707706042999</v>
+        <v>13.32707514235259</v>
       </c>
       <c r="D24" t="n">
-        <v>12.84667383729587</v>
+        <v>12.8466719883597</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061257663275</v>
+        <v>13.02061070266274</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95434761047363</v>
+        <v>12.95434951782227</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879188082604</v>
+        <v>13.31879384183405</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808433499697</v>
+        <v>12.88808623258925</v>
       </c>
       <c r="E25" t="n">
-        <v>13.25252943752032</v>
+        <v>13.2525313887721</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -932,16 +932,16 @@
         <v>44351</v>
       </c>
       <c r="B26" t="n">
-        <v>12.97919750213623</v>
+        <v>12.97919654846191</v>
       </c>
       <c r="C26" t="n">
-        <v>13.23596470306119</v>
+        <v>13.23596373052036</v>
       </c>
       <c r="D26" t="n">
-        <v>12.85495520076337</v>
+        <v>12.85495425621803</v>
       </c>
       <c r="E26" t="n">
-        <v>12.98748010031548</v>
+        <v>12.98747914603258</v>
       </c>
       <c r="F26" t="n">
         <v>460799</v>
@@ -972,16 +972,16 @@
         <v>44355</v>
       </c>
       <c r="B28" t="n">
-        <v>12.44909763336182</v>
+        <v>12.4490966796875</v>
       </c>
       <c r="C28" t="n">
-        <v>12.73899609163126</v>
+        <v>12.73899511574901</v>
       </c>
       <c r="D28" t="n">
-        <v>12.42424900387104</v>
+        <v>12.42424805210027</v>
       </c>
       <c r="E28" t="n">
-        <v>12.69758226392737</v>
+        <v>12.69758129121766</v>
       </c>
       <c r="F28" t="n">
         <v>727440</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95434761047363</v>
+        <v>12.95434951782227</v>
       </c>
       <c r="C30" t="n">
-        <v>13.00404402686745</v>
+        <v>13.0040459415332</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72242822673267</v>
+        <v>12.72243009993438</v>
       </c>
       <c r="E30" t="n">
-        <v>12.82182189169125</v>
+        <v>12.8218237795273</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1072,16 +1072,16 @@
         <v>44362</v>
       </c>
       <c r="B33" t="n">
-        <v>12.74727725982666</v>
+        <v>12.74727821350098</v>
       </c>
       <c r="C33" t="n">
-        <v>12.93778367526155</v>
+        <v>12.9377846431884</v>
       </c>
       <c r="D33" t="n">
-        <v>12.70586343677157</v>
+        <v>12.70586438734755</v>
       </c>
       <c r="E33" t="n">
-        <v>12.82182313993105</v>
+        <v>12.82182409918244</v>
       </c>
       <c r="F33" t="n">
         <v>320579</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414661407471</v>
+        <v>12.71414756774902</v>
       </c>
       <c r="C35" t="n">
-        <v>12.86323753914516</v>
+        <v>12.86323850400263</v>
       </c>
       <c r="D35" t="n">
-        <v>12.58990431521116</v>
+        <v>12.5899052595662</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384386648853</v>
+        <v>12.76384482389058</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1172,16 +1172,16 @@
         <v>44369</v>
       </c>
       <c r="B38" t="n">
-        <v>12.3993968963623</v>
+        <v>12.39939785003662</v>
       </c>
       <c r="C38" t="n">
-        <v>12.66444750075422</v>
+        <v>12.66444847481437</v>
       </c>
       <c r="D38" t="n">
-        <v>12.22545819138502</v>
+        <v>12.22545913168119</v>
       </c>
       <c r="E38" t="n">
-        <v>12.51535741996539</v>
+        <v>12.51535838255857</v>
       </c>
       <c r="F38" t="n">
         <v>779904</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="C39" t="n">
-        <v>12.4905092885157</v>
+        <v>12.49051027219619</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424684284646</v>
+        <v>12.42424782130851</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657218933105</v>
+        <v>12.31656932830811</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424846959927</v>
+        <v>12.42424558356415</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293453353099</v>
+        <v>12.09293172445695</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596587084889</v>
+        <v>12.41596298673773</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1352,16 +1352,16 @@
         <v>44382</v>
       </c>
       <c r="B47" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="C47" t="n">
-        <v>12.64788281412843</v>
+        <v>12.64788378432207</v>
       </c>
       <c r="D47" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="E47" t="n">
-        <v>12.5567717432249</v>
+        <v>12.55677270642959</v>
       </c>
       <c r="F47" t="n">
         <v>186679</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C48" t="n">
-        <v>12.4987937073347</v>
+        <v>12.49879274279404</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25859086647818</v>
+        <v>12.25858992047414</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394424802878</v>
+        <v>12.47394328540577</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54848903140645</v>
+        <v>12.54849097075757</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768154358154</v>
+        <v>12.40768346117107</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C50" t="n">
-        <v>12.65616529667426</v>
+        <v>12.6561672526666</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576132133995</v>
+        <v>12.17576320308654</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25858979381817</v>
+        <v>12.25859168836578</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.21717548370361</v>
+        <v>12.21717643737793</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020678506824</v>
+        <v>12.54020776395842</v>
       </c>
       <c r="D51" t="n">
-        <v>12.21717548370361</v>
+        <v>12.21717643737793</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424708678483</v>
+        <v>12.42424805662318</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1452,16 +1452,16 @@
         <v>44390</v>
       </c>
       <c r="B52" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C52" t="n">
-        <v>12.3082870318438</v>
+        <v>12.30828800250133</v>
       </c>
       <c r="D52" t="n">
-        <v>12.05151983187154</v>
+        <v>12.05152078227987</v>
       </c>
       <c r="E52" t="n">
-        <v>12.21717595569702</v>
+        <v>12.21717691916935</v>
       </c>
       <c r="F52" t="n">
         <v>433935</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121822357178</v>
+        <v>12.10121726989746</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030916512651</v>
+        <v>12.25030819970261</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172210889838</v>
+        <v>12.29172113487724</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010627604678</v>
+        <v>12.01010532434145</v>
       </c>
       <c r="E54" t="n">
-        <v>12.10121735421974</v>
+        <v>12.10121639529459</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10949897766113</v>
+        <v>12.10949993133545</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16747882566446</v>
+        <v>12.16747978390493</v>
       </c>
       <c r="D55" t="n">
-        <v>11.89414561315063</v>
+        <v>11.89414654986496</v>
       </c>
       <c r="E55" t="n">
-        <v>12.0680851571606</v>
+        <v>12.06808610757341</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1532,16 +1532,16 @@
         <v>44396</v>
       </c>
       <c r="B56" t="n">
-        <v>11.63737773895264</v>
+        <v>11.63737869262695</v>
       </c>
       <c r="C56" t="n">
-        <v>12.02667065225621</v>
+        <v>12.02667163783278</v>
       </c>
       <c r="D56" t="n">
-        <v>11.53798406922757</v>
+        <v>11.53798501475665</v>
       </c>
       <c r="E56" t="n">
-        <v>12.01010545672085</v>
+        <v>12.01010644093992</v>
       </c>
       <c r="F56" t="n">
         <v>557721</v>
@@ -1552,16 +1552,16 @@
         <v>44397</v>
       </c>
       <c r="B57" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="C57" t="n">
-        <v>11.86929859769704</v>
+        <v>11.8692995808735</v>
       </c>
       <c r="D57" t="n">
-        <v>11.37232852343671</v>
+        <v>11.37232946544736</v>
       </c>
       <c r="E57" t="n">
-        <v>11.67879300034788</v>
+        <v>11.67879396774409</v>
       </c>
       <c r="F57" t="n">
         <v>1030110</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303604125977</v>
+        <v>10.98303508758545</v>
       </c>
       <c r="C58" t="n">
-        <v>11.67051091068954</v>
+        <v>11.6705098973207</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303604125977</v>
+        <v>10.98303508758545</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970339644604</v>
+        <v>11.52970239530374</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C59" t="n">
-        <v>11.34747966894678</v>
+        <v>11.3474776588947</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172224457312</v>
+        <v>10.65172035776503</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414642480609</v>
+        <v>11.07414446317129</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697479248047</v>
+        <v>11.15697383880615</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697479248047</v>
+        <v>11.15697383880615</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707552191041</v>
+        <v>10.86707459301606</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707552191041</v>
+        <v>10.86707459301606</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.2977819442749</v>
+        <v>11.29778099060059</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47172150119681</v>
+        <v>11.47172053283982</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05758076893598</v>
+        <v>11.05757983553765</v>
       </c>
       <c r="E62" t="n">
-        <v>11.18182307183133</v>
+        <v>11.1818221279454</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747982025146</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C63" t="n">
-        <v>11.5131367879722</v>
+        <v>11.51313582037561</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495407964066</v>
+        <v>11.21495313710418</v>
       </c>
       <c r="E63" t="n">
-        <v>11.36404584989197</v>
+        <v>11.3640448948254</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1692,16 +1692,16 @@
         <v>44406</v>
       </c>
       <c r="B64" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C64" t="n">
-        <v>11.45515649173092</v>
+        <v>11.45515552548068</v>
       </c>
       <c r="D64" t="n">
-        <v>11.01616629311581</v>
+        <v>11.01616536389469</v>
       </c>
       <c r="E64" t="n">
-        <v>11.33919678522236</v>
+        <v>11.3391958287534</v>
       </c>
       <c r="F64" t="n">
         <v>449738</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273265838623</v>
+        <v>11.85273170471191</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556114342346</v>
+        <v>11.93556018308474</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030846651876</v>
+        <v>11.43030754683281</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727854457107</v>
+        <v>11.92727758489877</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515727996826</v>
+        <v>11.45515632629395</v>
       </c>
       <c r="C68" t="n">
-        <v>11.8527328495186</v>
+        <v>11.85273186274499</v>
       </c>
       <c r="D68" t="n">
-        <v>11.4468746809823</v>
+        <v>11.44687372799754</v>
       </c>
       <c r="E68" t="n">
-        <v>11.8527328495186</v>
+        <v>11.85273186274499</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283187866211</v>
+        <v>11.56283283233643</v>
       </c>
       <c r="C70" t="n">
-        <v>11.595963934121</v>
+        <v>11.59596489052797</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495278588257</v>
+        <v>11.21495371086467</v>
       </c>
       <c r="E70" t="n">
-        <v>11.28121606462938</v>
+        <v>11.2812169950767</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1872,16 +1872,16 @@
         <v>44419</v>
       </c>
       <c r="B73" t="n">
-        <v>11.88586235046387</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C73" t="n">
-        <v>12.0183872343875</v>
+        <v>12.01838916300267</v>
       </c>
       <c r="D73" t="n">
-        <v>11.71192281618591</v>
+        <v>11.71192469562211</v>
       </c>
       <c r="E73" t="n">
-        <v>12.0183872343875</v>
+        <v>12.01838916300267</v>
       </c>
       <c r="F73" t="n">
         <v>262426</v>
@@ -1892,16 +1892,16 @@
         <v>44420</v>
       </c>
       <c r="B74" t="n">
-        <v>12.07636737823486</v>
+        <v>12.07636833190918</v>
       </c>
       <c r="C74" t="n">
-        <v>12.24202431941305</v>
+        <v>12.24202528616934</v>
       </c>
       <c r="D74" t="n">
-        <v>11.81131677165233</v>
+        <v>11.81131770439553</v>
       </c>
       <c r="E74" t="n">
-        <v>11.95212425626575</v>
+        <v>11.95212520012855</v>
       </c>
       <c r="F74" t="n">
         <v>242515</v>
@@ -1912,16 +1912,16 @@
         <v>44421</v>
       </c>
       <c r="B75" t="n">
-        <v>12.50707530975342</v>
+        <v>12.50707626342773</v>
       </c>
       <c r="C75" t="n">
-        <v>12.61475157586925</v>
+        <v>12.61475253775396</v>
       </c>
       <c r="D75" t="n">
-        <v>11.87758041186906</v>
+        <v>11.87758131754389</v>
       </c>
       <c r="E75" t="n">
-        <v>12.00182187330842</v>
+        <v>12.00182278845676</v>
       </c>
       <c r="F75" t="n">
         <v>464803</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C78" t="n">
-        <v>12.33313676490402</v>
+        <v>12.3331357876011</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313622917634</v>
+        <v>11.51313531685193</v>
       </c>
       <c r="E78" t="n">
-        <v>11.57939868018012</v>
+        <v>11.57939776260494</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -1992,16 +1992,16 @@
         <v>44427</v>
       </c>
       <c r="B79" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C79" t="n">
-        <v>12.19232816125147</v>
+        <v>12.19232912276424</v>
       </c>
       <c r="D79" t="n">
-        <v>11.54626719790453</v>
+        <v>11.54626810846757</v>
       </c>
       <c r="E79" t="n">
-        <v>11.59596445113769</v>
+        <v>11.59596536561996</v>
       </c>
       <c r="F79" t="n">
         <v>301405</v>
@@ -2012,16 +2012,16 @@
         <v>44428</v>
       </c>
       <c r="B80" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C80" t="n">
-        <v>12.12606487955025</v>
+        <v>12.12606583583737</v>
       </c>
       <c r="D80" t="n">
-        <v>11.87758110989754</v>
+        <v>11.8775820465887</v>
       </c>
       <c r="E80" t="n">
-        <v>12.05980326219108</v>
+        <v>12.05980421325266</v>
       </c>
       <c r="F80" t="n">
         <v>324055</v>
@@ -2032,16 +2032,16 @@
         <v>44431</v>
       </c>
       <c r="B81" t="n">
-        <v>11.99353981018066</v>
+        <v>11.99353885650635</v>
       </c>
       <c r="C81" t="n">
-        <v>12.39111533388724</v>
+        <v>12.39111434859944</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95212515568412</v>
+        <v>11.95212420530292</v>
       </c>
       <c r="E81" t="n">
-        <v>12.21717578221218</v>
+        <v>12.21717481075529</v>
       </c>
       <c r="F81" t="n">
         <v>344599</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010696614738</v>
+        <v>12.01010599913494</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071245175947</v>
+        <v>11.91071149274992</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.57939720153809</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C86" t="n">
-        <v>11.96869092385892</v>
+        <v>11.9686919095953</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55454857754198</v>
+        <v>11.55454952916977</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101299842849</v>
+        <v>11.86101397529656</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C89" t="n">
-        <v>11.6290964280881</v>
+        <v>11.62909547100532</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010621525682</v>
+        <v>11.19010529430325</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55455054341664</v>
+        <v>11.55454959246905</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465225219727</v>
+        <v>11.26465129852295</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596535792752</v>
+        <v>11.59596437620398</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838896531435</v>
+        <v>11.19838801724993</v>
       </c>
       <c r="E90" t="n">
-        <v>11.35576333546881</v>
+        <v>11.35576237408096</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566040039062</v>
+        <v>11.64566230773926</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67050902600049</v>
+        <v>11.67051093741888</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010503811302</v>
+        <v>11.19010687084992</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313550669932</v>
+        <v>11.51313739234277</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889312744141</v>
+        <v>11.38889408111572</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111611650414</v>
+        <v>11.57111708543731</v>
       </c>
       <c r="D93" t="n">
-        <v>11.18182317547715</v>
+        <v>11.181824111812</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141886201694</v>
+        <v>11.52141982678859</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909470007334</v>
+        <v>11.62909565647244</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38060928692969</v>
+        <v>11.38061022289286</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485240958699</v>
+        <v>11.50485335576816</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.57939720153809</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444780387837</v>
+        <v>11.84444877938214</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545766573625</v>
+        <v>11.40545860508498</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596322825914</v>
+        <v>11.59596418329782</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444805906109</v>
+        <v>11.84444903317125</v>
       </c>
       <c r="D97" t="n">
-        <v>11.58768004846393</v>
+        <v>11.587681001457</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364057366772</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192317112123</v>
+        <v>11.71192413433229</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313500704049</v>
+        <v>11.51313595390284</v>
       </c>
       <c r="E98" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889312744141</v>
+        <v>11.38889408111572</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424734210526</v>
+        <v>11.60424831381274</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606547952412</v>
+        <v>11.30606642626268</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596474374774</v>
+        <v>11.59596571476166</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2432,16 +2432,16 @@
         <v>44460</v>
       </c>
       <c r="B101" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="C101" t="n">
-        <v>11.67879300034788</v>
+        <v>11.67879396774409</v>
       </c>
       <c r="D101" t="n">
-        <v>11.33919729610883</v>
+        <v>11.33919823537511</v>
       </c>
       <c r="E101" t="n">
-        <v>11.48000480420954</v>
+        <v>11.48000575513941</v>
       </c>
       <c r="F101" t="n">
         <v>218811</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34141826629639</v>
+        <v>12.34142017364502</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677116615927</v>
+        <v>11.73677298006055</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76161979111983</v>
+        <v>11.76162160886144</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2512,16 +2512,16 @@
         <v>44466</v>
       </c>
       <c r="B105" t="n">
-        <v>11.88586235046387</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C105" t="n">
-        <v>12.16747814488704</v>
+        <v>12.16748009742714</v>
       </c>
       <c r="D105" t="n">
-        <v>11.88586235046387</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="E105" t="n">
-        <v>12.0515184553684</v>
+        <v>12.05152038930021</v>
       </c>
       <c r="F105" t="n">
         <v>207539</v>
@@ -2572,16 +2572,16 @@
         <v>44469</v>
       </c>
       <c r="B108" t="n">
-        <v>11.63737773895264</v>
+        <v>11.63737869262695</v>
       </c>
       <c r="C108" t="n">
-        <v>11.94384217806649</v>
+        <v>11.94384315685534</v>
       </c>
       <c r="D108" t="n">
-        <v>11.51313544375356</v>
+        <v>11.51313638724631</v>
       </c>
       <c r="E108" t="n">
-        <v>11.94384217806649</v>
+        <v>11.94384315685534</v>
       </c>
       <c r="F108" t="n">
         <v>264322</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C109" t="n">
-        <v>11.7616195880132</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889188438319</v>
+        <v>11.38889282102754</v>
       </c>
       <c r="E109" t="n">
-        <v>11.7616195880132</v>
+        <v>11.76162055531139</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545977752449</v>
+        <v>11.40545885919616</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596444165342</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2672,16 +2672,16 @@
         <v>44476</v>
       </c>
       <c r="B113" t="n">
-        <v>11.33091449737549</v>
+        <v>11.33091259002686</v>
       </c>
       <c r="C113" t="n">
-        <v>11.52970269000604</v>
+        <v>11.52970074919511</v>
       </c>
       <c r="D113" t="n">
-        <v>11.28121724117508</v>
+        <v>11.28121534219206</v>
       </c>
       <c r="E113" t="n">
-        <v>11.45515680570543</v>
+        <v>11.45515487744292</v>
       </c>
       <c r="F113" t="n">
         <v>136744</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.4054594039917</v>
+        <v>11.40545845031738</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939896630289</v>
+        <v>11.57939799808451</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38061077620852</v>
+        <v>11.38060982461194</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43859146248331</v>
+        <v>11.43859050603864</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677096348174</v>
+        <v>11.73677192873634</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687256307056</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687256307056</v>
+        <v>11.44687350448336</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667140960693</v>
+        <v>12.02667045593262</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495400789619</v>
+        <v>12.03495305356509</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768121771099</v>
+        <v>11.58768029884711</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768121771099</v>
+        <v>11.58768029884711</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2772,16 +2772,16 @@
         <v>44484</v>
       </c>
       <c r="B118" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="C118" t="n">
-        <v>12.09293365478516</v>
+        <v>12.09293460845947</v>
       </c>
       <c r="D118" t="n">
-        <v>11.84444905296142</v>
+        <v>11.84444998703971</v>
       </c>
       <c r="E118" t="n">
-        <v>11.92727753095967</v>
+        <v>11.92727847157</v>
       </c>
       <c r="F118" t="n">
         <v>256632</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16747856140137</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22545840814544</v>
+        <v>12.22545936636416</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727657693906</v>
+        <v>11.92727751178659</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465009002827</v>
+        <v>12.08465103721058</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2812,16 +2812,16 @@
         <v>44488</v>
       </c>
       <c r="B120" t="n">
-        <v>12.07636737823486</v>
+        <v>12.07636833190918</v>
       </c>
       <c r="C120" t="n">
-        <v>12.29172073602975</v>
+        <v>12.29172170671058</v>
       </c>
       <c r="D120" t="n">
-        <v>11.9355590614505</v>
+        <v>11.93556000400514</v>
       </c>
       <c r="E120" t="n">
-        <v>12.10949860003631</v>
+        <v>12.10949955632701</v>
       </c>
       <c r="F120" t="n">
         <v>251785</v>
@@ -2832,16 +2832,16 @@
         <v>44489</v>
       </c>
       <c r="B121" t="n">
-        <v>11.80303478240967</v>
+        <v>11.8030366897583</v>
       </c>
       <c r="C121" t="n">
-        <v>12.20061029668353</v>
+        <v>12.20061226827963</v>
       </c>
       <c r="D121" t="n">
-        <v>11.72848890538714</v>
+        <v>11.7284908006893</v>
       </c>
       <c r="E121" t="n">
-        <v>12.01838815130088</v>
+        <v>12.01839009345022</v>
       </c>
       <c r="F121" t="n">
         <v>129580</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D122" t="n">
-        <v>11.41374237633313</v>
+        <v>11.4137414573379</v>
       </c>
       <c r="E122" t="n">
-        <v>11.6787930277491</v>
+        <v>11.67879208741291</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030834197998</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81960130202524</v>
+        <v>11.81960031587073</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212646483165</v>
+        <v>11.13212553603579</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76162144634801</v>
+        <v>11.76162046503097</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="C124" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172236012447</v>
+        <v>11.47172059900599</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141961787203</v>
+        <v>11.52141784912412</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C125" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D125" t="n">
-        <v>11.84444821601161</v>
+        <v>11.8444491374672</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030714700461</v>
+        <v>12.25030810003457</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980225021978</v>
+        <v>12.05980324204109</v>
       </c>
       <c r="D127" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010500115686</v>
+        <v>12.01010598889097</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030834197998</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72849021912831</v>
+        <v>11.72848924057554</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030834197998</v>
+        <v>11.43030738830566</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596531024953</v>
+        <v>11.59596434275382</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -2992,16 +2992,16 @@
         <v>44501</v>
       </c>
       <c r="B129" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="C129" t="n">
-        <v>11.65394437180921</v>
+        <v>11.65394533714711</v>
       </c>
       <c r="D129" t="n">
-        <v>11.36404592464751</v>
+        <v>11.36404686597209</v>
       </c>
       <c r="E129" t="n">
-        <v>11.5048542649193</v>
+        <v>11.50485521790754</v>
       </c>
       <c r="F129" t="n">
         <v>1267357</v>
@@ -3032,16 +3032,16 @@
         <v>44504</v>
       </c>
       <c r="B131" t="n">
-        <v>11.77818584442139</v>
+        <v>11.7781867980957</v>
       </c>
       <c r="C131" t="n">
-        <v>12.08465027787762</v>
+        <v>12.08465125636622</v>
       </c>
       <c r="D131" t="n">
-        <v>11.73677119200559</v>
+        <v>11.73677214232659</v>
       </c>
       <c r="E131" t="n">
-        <v>12.01010523500273</v>
+        <v>12.01010620745546</v>
       </c>
       <c r="F131" t="n">
         <v>218179</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020588356491</v>
+        <v>11.72020683994276</v>
       </c>
       <c r="D133" t="n">
-        <v>11.38060939858799</v>
+        <v>11.3806103272545</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859007784422</v>
+        <v>11.43859101124201</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374366760254</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374366760254</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929758022087</v>
+        <v>11.86929850548507</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05151973098904</v>
+        <v>12.05152067045827</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232940673828</v>
+        <v>12.19232845306396</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374406605356</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465229112388</v>
+        <v>12.08465134587198</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374406605356</v>
+        <v>12.23374310913982</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3152,16 +3152,16 @@
         <v>44512</v>
       </c>
       <c r="B137" t="n">
-        <v>11.88586235046387</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="C137" t="n">
-        <v>12.23374141901978</v>
+        <v>12.23374338219328</v>
       </c>
       <c r="D137" t="n">
-        <v>11.88586235046387</v>
+        <v>11.8858642578125</v>
       </c>
       <c r="E137" t="n">
-        <v>12.14263035327955</v>
+        <v>12.14263230183227</v>
       </c>
       <c r="F137" t="n">
         <v>236720</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16747856140137</v>
+        <v>12.16747951507568</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576115888739</v>
+        <v>12.17576211321089</v>
       </c>
       <c r="D138" t="n">
-        <v>11.68707459247675</v>
+        <v>11.6870755084975</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242795231003</v>
+        <v>11.90242888520996</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49051027684238</v>
+        <v>12.49050931294096</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293390702631</v>
+        <v>12.09293297380614</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485414956155</v>
+        <v>12.32485319844393</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.98748016357422</v>
+        <v>12.9874792098999</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374261367302</v>
+        <v>13.05374165513303</v>
       </c>
       <c r="D142" t="n">
-        <v>12.35798439112253</v>
+        <v>12.35798348367227</v>
       </c>
       <c r="E142" t="n">
-        <v>12.35798439112253</v>
+        <v>12.35798348367227</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.4408130645752</v>
+        <v>12.44081211090088</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89636928852036</v>
+        <v>12.89636829992451</v>
       </c>
       <c r="D144" t="n">
-        <v>12.4408130645752</v>
+        <v>12.44081211090088</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010600521327</v>
+        <v>12.83010502169696</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010673522949</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010673522949</v>
+        <v>12.83010482788086</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283391635538</v>
+        <v>12.38283207549919</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131937051061</v>
+        <v>12.63131749271409</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3392,16 +3392,16 @@
         <v>44531</v>
       </c>
       <c r="B149" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="C149" t="n">
-        <v>12.58990549663439</v>
+        <v>12.58990653950131</v>
       </c>
       <c r="D149" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="E149" t="n">
-        <v>12.37455127074656</v>
+        <v>12.37455229577492</v>
       </c>
       <c r="F149" t="n">
         <v>554877</v>
@@ -3412,16 +3412,16 @@
         <v>44532</v>
       </c>
       <c r="B150" t="n">
-        <v>11.24808597564697</v>
+        <v>11.24808502197266</v>
       </c>
       <c r="C150" t="n">
-        <v>11.8196010912967</v>
+        <v>11.8196000891662</v>
       </c>
       <c r="D150" t="n">
-        <v>11.18182352238896</v>
+        <v>11.18182257433274</v>
       </c>
       <c r="E150" t="n">
-        <v>11.75333863803869</v>
+        <v>11.75333764152628</v>
       </c>
       <c r="F150" t="n">
         <v>650429</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67051025368041</v>
+        <v>11.67050929318926</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2480860703887</v>
+        <v>11.24808514466335</v>
       </c>
       <c r="E151" t="n">
-        <v>11.33919715242866</v>
+        <v>11.3391962192048</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.7699031829834</v>
+        <v>11.76990413665771</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212533542978</v>
+        <v>11.95212630386892</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485338464032</v>
+        <v>11.50485431683857</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970201127774</v>
+        <v>11.52970294548939</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374271392822</v>
+        <v>12.23374366760254</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626761187925</v>
+        <v>12.36626857588447</v>
       </c>
       <c r="D154" t="n">
-        <v>11.89414620662944</v>
+        <v>11.8941471338307</v>
       </c>
       <c r="E154" t="n">
-        <v>12.0101059084221</v>
+        <v>12.01010684466293</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C155" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99353913300503</v>
+        <v>11.99354006605936</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22545852214389</v>
+        <v>12.22545947324071</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000591278076</v>
+        <v>12.30000400543213</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626920245019</v>
+        <v>12.36626728482618</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778373857486</v>
+        <v>12.11778185948322</v>
       </c>
       <c r="E156" t="n">
-        <v>12.26687468403161</v>
+        <v>12.2668727818206</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485389709473</v>
+        <v>12.32485485076904</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303492009218</v>
+        <v>12.62303589683919</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374282091386</v>
+        <v>12.23374376753817</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000443829783</v>
+        <v>12.30000539004934</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.25858974456787</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192295369397</v>
+        <v>12.53192392863263</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606402270097</v>
+        <v>12.12606496606526</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909531371949</v>
+        <v>12.44909628221446</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3612,16 +3612,16 @@
         <v>44546</v>
       </c>
       <c r="B160" t="n">
-        <v>12.43252944946289</v>
+        <v>12.43253040313721</v>
       </c>
       <c r="C160" t="n">
-        <v>12.56505434089677</v>
+        <v>12.56505530473681</v>
       </c>
       <c r="D160" t="n">
-        <v>12.31657058554373</v>
+        <v>12.31657153032308</v>
       </c>
       <c r="E160" t="n">
-        <v>12.54848914555302</v>
+        <v>12.54849010812237</v>
       </c>
       <c r="F160" t="n">
         <v>252523</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606590270996</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606494903564</v>
+        <v>12.94606590270996</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25858939858541</v>
+        <v>12.25859030161671</v>
       </c>
       <c r="E161" t="n">
-        <v>12.42424633820085</v>
+        <v>12.4242472534353</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3692,16 +3692,16 @@
         <v>44552</v>
       </c>
       <c r="B164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.82182312011719</v>
       </c>
       <c r="C164" t="n">
-        <v>12.82182216644287</v>
+        <v>12.82182312011719</v>
       </c>
       <c r="D164" t="n">
-        <v>12.43252926346614</v>
+        <v>12.43253018818525</v>
       </c>
       <c r="E164" t="n">
-        <v>12.72242849935444</v>
+        <v>12.72242944563595</v>
       </c>
       <c r="F164" t="n">
         <v>107667</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.83838748931885</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495434892158</v>
+        <v>12.85495625873149</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020648508576</v>
+        <v>12.54020834813482</v>
       </c>
       <c r="E165" t="n">
-        <v>12.81353969642765</v>
+        <v>12.81354160008474</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828866415499</v>
+        <v>13.12828770746268</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384435172153</v>
+        <v>12.76384342158722</v>
       </c>
       <c r="E166" t="n">
-        <v>12.83838856883414</v>
+        <v>12.8383876332676</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="D167" t="n">
-        <v>12.92121704861566</v>
+        <v>12.9212161070132</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C168" t="n">
-        <v>13.37677327132853</v>
+        <v>13.3767722965285</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04546018437347</v>
+        <v>13.04545923371708</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970248796023</v>
+        <v>13.16970152824999</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3792,16 +3792,16 @@
         <v>44560</v>
       </c>
       <c r="B169" t="n">
-        <v>13.13657188415527</v>
+        <v>13.13656997680664</v>
       </c>
       <c r="C169" t="n">
-        <v>13.33536007860415</v>
+        <v>13.33535814239271</v>
       </c>
       <c r="D169" t="n">
-        <v>13.1034398249379</v>
+        <v>13.10343792239983</v>
       </c>
       <c r="E169" t="n">
-        <v>13.21111776913776</v>
+        <v>13.21111585096552</v>
       </c>
       <c r="F169" t="n">
         <v>310044</v>
@@ -3812,16 +3812,16 @@
         <v>44564</v>
       </c>
       <c r="B170" t="n">
-        <v>12.92949962615967</v>
+        <v>12.92949867248535</v>
       </c>
       <c r="C170" t="n">
-        <v>13.60041006166028</v>
+        <v>13.6004090584999</v>
       </c>
       <c r="D170" t="n">
-        <v>12.78869212614555</v>
+        <v>12.78869118285713</v>
       </c>
       <c r="E170" t="n">
-        <v>13.1697024667913</v>
+        <v>13.16970149539972</v>
       </c>
       <c r="F170" t="n">
         <v>289922</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970188140869</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98748125957582</v>
+        <v>12.98748025665069</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970283508301</v>
+        <v>12.34970188140869</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92950057063265</v>
+        <v>12.92949957218493</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616633728321</v>
+        <v>11.83616441649305</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47172120414394</v>
+        <v>11.47171934249647</v>
       </c>
       <c r="E173" t="n">
-        <v>11.63737815849552</v>
+        <v>11.637376269965</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.6953592300415</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78647031479358</v>
+        <v>11.78646935368979</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657103050467</v>
+        <v>11.49657009304013</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333908689929</v>
+        <v>11.75333812849712</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586465533357</v>
+        <v>11.88586369832469</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202580731284</v>
+        <v>11.42202488765067</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55455071693529</v>
+        <v>11.55454978660266</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727741252527</v>
+        <v>11.92727547694948</v>
       </c>
       <c r="D176" t="n">
-        <v>11.61253036429669</v>
+        <v>11.6125284797985</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444893534948</v>
+        <v>11.84444701321522</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838848776734</v>
+        <v>12.01838653740591</v>
       </c>
       <c r="D177" t="n">
-        <v>11.6456607565618</v>
+        <v>11.64565886668716</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818648647726</v>
+        <v>11.77818457509616</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131771091337</v>
+        <v>11.81131579415569</v>
       </c>
       <c r="D179" t="n">
-        <v>11.5297018871209</v>
+        <v>11.52970001606424</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67050938293163</v>
+        <v>11.67050748902453</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.57939720153809</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818536133603</v>
+        <v>11.77818633138246</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798338299186</v>
+        <v>11.53798433325535</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333673733992</v>
+        <v>11.75333770533982</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010511899131</v>
+        <v>12.01010609902517</v>
       </c>
       <c r="D182" t="n">
-        <v>11.5628315373786</v>
+        <v>11.56283248091458</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596359185958</v>
+        <v>11.59596453809916</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434741069664</v>
+        <v>12.13434840086876</v>
       </c>
       <c r="D184" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84444817527024</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111549377441</v>
+        <v>11.57111644744873</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101391022536</v>
+        <v>11.86101488779268</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828701814372</v>
+        <v>11.48828796499143</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707519322319</v>
+        <v>11.68707615645473</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616542816162</v>
+        <v>11.83616733551025</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444802559172</v>
+        <v>11.84444993427506</v>
       </c>
       <c r="D186" t="n">
-        <v>11.46343772558484</v>
+        <v>11.46343957286996</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172032301494</v>
+        <v>11.47172217163477</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747982025146</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374227447133</v>
+        <v>11.41374131522813</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242917120093</v>
+        <v>11.08242823980222</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818236847018</v>
+        <v>11.1818227449497</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4212,16 +4212,16 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>11.67879295349121</v>
+        <v>11.67879199981689</v>
       </c>
       <c r="C190" t="n">
-        <v>11.78647006600311</v>
+        <v>11.78646910353603</v>
       </c>
       <c r="D190" t="n">
-        <v>11.45515696188252</v>
+        <v>11.45515602647001</v>
       </c>
       <c r="E190" t="n">
-        <v>11.55455064346737</v>
+        <v>11.55454969993852</v>
       </c>
       <c r="F190" t="n">
         <v>318367</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586282728598</v>
+        <v>11.88586379718157</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626634230906</v>
+        <v>11.54626728449331</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788214802975</v>
+        <v>11.82788311319406</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.48828792572021</v>
+        <v>11.4882869720459</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84444965011515</v>
+        <v>11.84444866687487</v>
       </c>
       <c r="D193" t="n">
-        <v>11.48828792572021</v>
+        <v>11.4882869720459</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67051008720073</v>
+        <v>11.67050911839965</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4292,16 +4292,16 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>11.30606555938721</v>
+        <v>11.30606460571289</v>
       </c>
       <c r="C194" t="n">
-        <v>11.62909605149376</v>
+        <v>11.6290950705716</v>
       </c>
       <c r="D194" t="n">
-        <v>11.19838845129467</v>
+        <v>11.19838750670299</v>
       </c>
       <c r="E194" t="n">
-        <v>11.48828771756607</v>
+        <v>11.48828674852119</v>
       </c>
       <c r="F194" t="n">
         <v>381155</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.59596347808838</v>
+        <v>11.5959644317627</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697377917189</v>
+        <v>11.97697476418123</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970103411845</v>
+        <v>11.52970198234322</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364057366772</v>
+        <v>11.70364153619761</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444999694824</v>
+        <v>11.84444904327393</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313689072104</v>
+        <v>11.51313596372292</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596537532062</v>
+        <v>11.59596444165342</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788276672363</v>
+        <v>11.82788372039795</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84444974984068</v>
       </c>
       <c r="D198" t="n">
-        <v>11.6290954224653</v>
+        <v>11.62909636011153</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84444879483066</v>
+        <v>11.84444974984068</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.68707466125488</v>
+        <v>11.6870756149292</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84444817527024</v>
+        <v>11.84444914178635</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081221663484</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081221663484</v>
+        <v>11.62081316490208</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.6953592300415</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960154268786</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394457104532</v>
+        <v>11.65394362074808</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960154268786</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899398228799</v>
+        <v>11.91899204805644</v>
       </c>
       <c r="D207" t="n">
-        <v>11.54626708325345</v>
+        <v>11.54626520950857</v>
       </c>
       <c r="E207" t="n">
-        <v>11.54626708325345</v>
+        <v>11.54626520950857</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.14263248443604</v>
+        <v>12.14263153076172</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576287906074</v>
+        <v>12.17576192278439</v>
       </c>
       <c r="D208" t="n">
-        <v>11.4220255970719</v>
+        <v>11.42202469999357</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596516187804</v>
+        <v>11.59596425113861</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4592,16 +4592,16 @@
         <v>44617</v>
       </c>
       <c r="B209" t="n">
-        <v>11.99353981018066</v>
+        <v>11.99353885650635</v>
       </c>
       <c r="C209" t="n">
-        <v>12.31657111943808</v>
+        <v>12.31657014007771</v>
       </c>
       <c r="D209" t="n">
-        <v>11.8196002585056</v>
+        <v>11.8195993186622</v>
       </c>
       <c r="E209" t="n">
-        <v>12.09293348306456</v>
+        <v>12.09293252148689</v>
       </c>
       <c r="F209" t="n">
         <v>373254</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687400817871</v>
+        <v>13.08687305450439</v>
       </c>
       <c r="D210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="E210" t="n">
-        <v>12.010106267532</v>
+        <v>12.01010539232453</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4632,16 +4632,16 @@
         <v>44623</v>
       </c>
       <c r="B211" t="n">
-        <v>12.7058629989624</v>
+        <v>12.70586204528809</v>
       </c>
       <c r="C211" t="n">
-        <v>13.12828797398962</v>
+        <v>13.12828698860901</v>
       </c>
       <c r="D211" t="n">
-        <v>12.59818672986099</v>
+        <v>12.59818578426862</v>
       </c>
       <c r="E211" t="n">
-        <v>13.12828797398962</v>
+        <v>13.12828698860901</v>
       </c>
       <c r="F211" t="n">
         <v>452688</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.83838748931885</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="C212" t="n">
-        <v>12.83838748931885</v>
+        <v>12.83838939666748</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000366426548</v>
+        <v>12.30000549162855</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586259854859</v>
+        <v>12.70586448620852</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4672,16 +4672,16 @@
         <v>44627</v>
       </c>
       <c r="B213" t="n">
-        <v>12.73899555206299</v>
+        <v>12.73899459838867</v>
       </c>
       <c r="C213" t="n">
-        <v>13.06202605741871</v>
+        <v>13.06202507956149</v>
       </c>
       <c r="D213" t="n">
-        <v>12.1095005710341</v>
+        <v>12.10949966448541</v>
       </c>
       <c r="E213" t="n">
-        <v>12.846673496743</v>
+        <v>12.84667253500764</v>
       </c>
       <c r="F213" t="n">
         <v>394008</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.1591968536377</v>
+        <v>12.15919780731201</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="D214" t="n">
-        <v>12.14263165745353</v>
+        <v>12.1426326098286</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081389317532</v>
+        <v>12.44081198328363</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293475328459</v>
+        <v>12.09293289679869</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576323880683</v>
+        <v>12.17576136960524</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="C216" t="n">
-        <v>12.42424869537354</v>
+        <v>12.4242467880249</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919804100504</v>
+        <v>12.15919617434651</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111663542777</v>
+        <v>12.39111473316551</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.79475116729736</v>
+        <v>11.794753074646</v>
       </c>
       <c r="C220" t="n">
-        <v>11.8030337644174</v>
+        <v>11.80303567310543</v>
       </c>
       <c r="D220" t="n">
-        <v>11.46343729644494</v>
+        <v>11.46343915021626</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596301122009</v>
+        <v>11.59596488642237</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4832,16 +4832,16 @@
         <v>44637</v>
       </c>
       <c r="B221" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="C221" t="n">
-        <v>11.80303614304128</v>
+        <v>11.80303712072899</v>
       </c>
       <c r="D221" t="n">
-        <v>11.5131368637085</v>
+        <v>11.51313781738281</v>
       </c>
       <c r="E221" t="n">
-        <v>11.80303614304128</v>
+        <v>11.80303712072899</v>
       </c>
       <c r="F221" t="n">
         <v>333116</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222667694092</v>
+        <v>11.66222763061523</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444882573873</v>
+        <v>11.84444979431419</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404482760432</v>
+        <v>11.36404575689492</v>
       </c>
       <c r="E222" t="n">
-        <v>11.5379843784125</v>
+        <v>11.53798532192695</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4872,16 +4872,16 @@
         <v>44641</v>
       </c>
       <c r="B223" t="n">
-        <v>11.67879295349121</v>
+        <v>11.67879199981689</v>
       </c>
       <c r="C223" t="n">
-        <v>11.75333883880816</v>
+        <v>11.75333787904653</v>
       </c>
       <c r="D223" t="n">
-        <v>11.55455064346737</v>
+        <v>11.55454969993852</v>
       </c>
       <c r="E223" t="n">
-        <v>11.69535898317423</v>
+        <v>11.69535802814715</v>
       </c>
       <c r="F223" t="n">
         <v>273488</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333786010742</v>
+        <v>11.75333595275879</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475251478082</v>
+        <v>11.79475060071136</v>
       </c>
       <c r="D224" t="n">
-        <v>11.57939830768957</v>
+        <v>11.5793964285681</v>
       </c>
       <c r="E224" t="n">
-        <v>11.67879198099791</v>
+        <v>11.67879008574669</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.96869373321533</v>
+        <v>11.96869277954102</v>
       </c>
       <c r="C225" t="n">
-        <v>12.2088949357699</v>
+        <v>12.20889396295617</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798609125025</v>
+        <v>11.53798517189504</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677346553771</v>
+        <v>11.73677253034297</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374206542969</v>
+        <v>11.41374015808105</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283300077933</v>
+        <v>11.56283106851614</v>
       </c>
       <c r="D231" t="n">
-        <v>11.2315199035769</v>
+        <v>11.23151802667939</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283300077933</v>
+        <v>11.56283106851614</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374206542969</v>
+        <v>11.41374015808105</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909628595667</v>
+        <v>11.62909434262023</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636853149702</v>
+        <v>11.25636665044706</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313657711016</v>
+        <v>11.51313465315173</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444744110107</v>
+        <v>11.02444839477539</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495217263222</v>
+        <v>11.21495314278623</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192255519609</v>
+        <v>10.89192349740629</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495217263222</v>
+        <v>11.21495314278623</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364028930664</v>
+        <v>10.88364124298096</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394303949338</v>
+        <v>10.833943988813</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192485809326</v>
+        <v>10.89192390441895</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303594445944</v>
+        <v>10.98303498280762</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313665503474</v>
+        <v>10.69313571876591</v>
       </c>
       <c r="E237" t="n">
-        <v>10.93333868565203</v>
+        <v>10.9333377283516</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5172,16 +5172,16 @@
         <v>44662</v>
       </c>
       <c r="B238" t="n">
-        <v>10.84222507476807</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="C238" t="n">
-        <v>11.07414445230742</v>
+        <v>11.07414640045497</v>
       </c>
       <c r="D238" t="n">
-        <v>10.80909385400115</v>
+        <v>10.80909575552138</v>
       </c>
       <c r="E238" t="n">
-        <v>10.84222507476807</v>
+        <v>10.8422269821167</v>
       </c>
       <c r="F238" t="n">
         <v>406860</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798324584961</v>
+        <v>10.71798515319824</v>
       </c>
       <c r="C239" t="n">
-        <v>11.0078824801347</v>
+        <v>11.00788443907316</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798324584961</v>
+        <v>10.71798515319824</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333660610241</v>
+        <v>10.93333855177485</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5212,16 +5212,16 @@
         <v>44664</v>
       </c>
       <c r="B240" t="n">
-        <v>10.80909442901611</v>
+        <v>10.80909633636475</v>
       </c>
       <c r="C240" t="n">
-        <v>10.89192290142512</v>
+        <v>10.89192482338948</v>
       </c>
       <c r="D240" t="n">
-        <v>10.65172091395867</v>
+        <v>10.65172279353752</v>
       </c>
       <c r="E240" t="n">
-        <v>10.81737702660573</v>
+        <v>10.81737893541589</v>
       </c>
       <c r="F240" t="n">
         <v>281389</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C242" t="n">
-        <v>11.03273176734258</v>
+        <v>11.03272981304382</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172224457312</v>
+        <v>10.65172035776503</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000484319739</v>
+        <v>10.66000295492215</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76768112182617</v>
+        <v>10.76767921447754</v>
       </c>
       <c r="C243" t="n">
-        <v>10.9250554887138</v>
+        <v>10.92505355348844</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000484319739</v>
+        <v>10.66000295492215</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081318066541</v>
+        <v>10.80081126744788</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434661865234</v>
+        <v>10.49434757232666</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919607588605</v>
+        <v>10.51919703181856</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707386403591</v>
+        <v>10.04707477706429</v>
       </c>
       <c r="E246" t="n">
-        <v>10.1547501297465</v>
+        <v>10.15475105255997</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525775909424</v>
+        <v>10.34525680541992</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061114821748</v>
+        <v>10.56061017469088</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32869089752705</v>
+        <v>10.32868994537994</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151938016555</v>
+        <v>10.41151842038292</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838935852051</v>
+        <v>10.37838745117188</v>
       </c>
       <c r="C249" t="n">
-        <v>10.55232894260518</v>
+        <v>10.55232700328979</v>
       </c>
       <c r="D249" t="n">
-        <v>10.2375810049037</v>
+        <v>10.23757912343294</v>
       </c>
       <c r="E249" t="n">
-        <v>10.3452589602238</v>
+        <v>10.3452570589639</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434448242188</v>
+        <v>10.73434543609619</v>
       </c>
       <c r="C251" t="n">
-        <v>10.92543536845984</v>
+        <v>10.9254363391113</v>
       </c>
       <c r="D251" t="n">
-        <v>10.4103192818045</v>
+        <v>10.41032020669135</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389329081236</v>
+        <v>10.88389425777308</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5452,16 +5452,16 @@
         <v>44684</v>
       </c>
       <c r="B252" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C252" t="n">
-        <v>10.72603654719261</v>
+        <v>10.72603559055428</v>
       </c>
       <c r="D252" t="n">
-        <v>10.51002056175287</v>
+        <v>10.51001962438067</v>
       </c>
       <c r="E252" t="n">
-        <v>10.71772763006424</v>
+        <v>10.71772667416696</v>
       </c>
       <c r="F252" t="n">
         <v>311097</v>
@@ -5472,16 +5472,16 @@
         <v>44685</v>
       </c>
       <c r="B253" t="n">
-        <v>10.90050983428955</v>
+        <v>10.90051174163818</v>
       </c>
       <c r="C253" t="n">
-        <v>10.90050983428955</v>
+        <v>10.90051174163818</v>
       </c>
       <c r="D253" t="n">
-        <v>10.48509408352501</v>
+        <v>10.48509591818506</v>
       </c>
       <c r="E253" t="n">
-        <v>10.69280195890728</v>
+        <v>10.69280382991162</v>
       </c>
       <c r="F253" t="n">
         <v>328902</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.850661277771</v>
+        <v>10.85066032409668</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344493624595</v>
+        <v>11.03344396650661</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633637198398</v>
+        <v>10.62633543802578</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772778385571</v>
+        <v>10.71772684186504</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5532,16 +5532,16 @@
         <v>44690</v>
       </c>
       <c r="B256" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036047311521</v>
       </c>
       <c r="D256" t="n">
-        <v>10.618028137107</v>
+        <v>10.61802719010177</v>
       </c>
       <c r="E256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036047311521</v>
       </c>
       <c r="F256" t="n">
         <v>340595</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389316500986</v>
+        <v>10.88389415417323</v>
       </c>
       <c r="D257" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727700192804</v>
+        <v>10.86727798958128</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5572,16 +5572,16 @@
         <v>44692</v>
       </c>
       <c r="B258" t="n">
-        <v>10.62633609771729</v>
+        <v>10.6263370513916</v>
       </c>
       <c r="C258" t="n">
-        <v>10.80081083444142</v>
+        <v>10.8008118037742</v>
       </c>
       <c r="D258" t="n">
-        <v>10.46847919505945</v>
+        <v>10.46848013456669</v>
       </c>
       <c r="E258" t="n">
-        <v>10.51002044129933</v>
+        <v>10.51002138453475</v>
       </c>
       <c r="F258" t="n">
         <v>211647</v>
@@ -5592,16 +5592,16 @@
         <v>44693</v>
       </c>
       <c r="B259" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C259" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="D259" t="n">
-        <v>10.36046825648242</v>
+        <v>10.36046917836759</v>
       </c>
       <c r="E259" t="n">
-        <v>10.53494296466207</v>
+        <v>10.53494390207218</v>
       </c>
       <c r="F259" t="n">
         <v>307094</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340261960133</v>
+        <v>10.49340354046572</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802718328567</v>
+        <v>10.61802811508668</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.10822010040283</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085310445568</v>
+        <v>11.34085115716256</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95867043133051</v>
+        <v>10.95866854966046</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806943360591</v>
+        <v>11.15806751769784</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.10822010040283</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423610356696</v>
+        <v>11.32423415912707</v>
       </c>
       <c r="D265" t="n">
-        <v>11.10822010040283</v>
+        <v>11.1082181930542</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100293652106</v>
+        <v>11.29100099778751</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190139770508</v>
+        <v>10.99190330505371</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19960927620575</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="D268" t="n">
-        <v>10.89220108179667</v>
+        <v>10.892202971845</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19960927620575</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.19130229949951</v>
+        <v>11.1913013458252</v>
       </c>
       <c r="C269" t="n">
-        <v>11.19130229949951</v>
+        <v>11.1913013458252</v>
       </c>
       <c r="D269" t="n">
-        <v>10.86727791027506</v>
+        <v>10.8672769842127</v>
       </c>
       <c r="E269" t="n">
-        <v>11.01682756416854</v>
+        <v>11.0168266253622</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5812,16 +5812,16 @@
         <v>44708</v>
       </c>
       <c r="B270" t="n">
-        <v>11.08329486846924</v>
+        <v>11.08329391479492</v>
       </c>
       <c r="C270" t="n">
-        <v>11.25776961917957</v>
+        <v>11.25776865049238</v>
       </c>
       <c r="D270" t="n">
-        <v>11.06667786780236</v>
+        <v>11.06667691555787</v>
       </c>
       <c r="E270" t="n">
-        <v>11.19961136894279</v>
+        <v>11.1996104052599</v>
       </c>
       <c r="F270" t="n">
         <v>219970</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776863098145</v>
+        <v>11.25776767730713</v>
       </c>
       <c r="C271" t="n">
-        <v>11.2743856301897</v>
+        <v>11.27438467510771</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160187295824</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160187295824</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34915924072266</v>
+        <v>11.34916019439697</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19960959730377</v>
+        <v>11.19961053841137</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39900940010609</v>
+        <v>11.39901035796933</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="C274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.349159222931</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622753143311</v>
+        <v>11.21622657775879</v>
       </c>
       <c r="E274" t="n">
-        <v>11.34916018790809</v>
+        <v>11.349159222931</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712760925293</v>
+        <v>10.91712856292725</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24945923185963</v>
+        <v>11.24946021456504</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051061075688</v>
+        <v>10.90051156297961</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622690433039</v>
+        <v>11.21622788413276</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250335693359</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344429480254</v>
+        <v>11.03344526976758</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250335693359</v>
       </c>
       <c r="E276" t="n">
-        <v>11.00851921397176</v>
+        <v>11.0085201867343</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D277" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250303440952</v>
+        <v>10.79250209732709</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5972,16 +5972,16 @@
         <v>44720</v>
       </c>
       <c r="B278" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588748931885</v>
       </c>
       <c r="C278" t="n">
-        <v>10.9752855183135</v>
+        <v>10.97528648963478</v>
       </c>
       <c r="D278" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588748931885</v>
       </c>
       <c r="E278" t="n">
-        <v>10.95866935379015</v>
+        <v>10.95867032364089</v>
       </c>
       <c r="F278" t="n">
         <v>141800</v>
@@ -5992,16 +5992,16 @@
         <v>44721</v>
       </c>
       <c r="B279" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C279" t="n">
-        <v>10.82573687488132</v>
+        <v>10.82573590935088</v>
       </c>
       <c r="D279" t="n">
-        <v>10.6263362195039</v>
+        <v>10.62633527175769</v>
       </c>
       <c r="E279" t="n">
-        <v>10.79250287583077</v>
+        <v>10.79250191326441</v>
       </c>
       <c r="F279" t="n">
         <v>205537</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768859863281</v>
+        <v>10.1776876449585</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216336049145</v>
+        <v>10.35216239046842</v>
       </c>
       <c r="D284" t="n">
-        <v>10.0779890924557</v>
+        <v>10.07798814812347</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599668213134</v>
+        <v>10.18599572767854</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496406309403417</v>
+        <v>9.496405321144287</v>
       </c>
       <c r="D291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488098226848217</v>
+        <v>9.488097239453682</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072681427001953</v>
+        <v>9.072680473327637</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974876940689</v>
+        <v>8.93974782970578</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6272,16 +6272,16 @@
         <v>44742</v>
       </c>
       <c r="B293" t="n">
-        <v>8.732038497924805</v>
+        <v>8.732039451599121</v>
       </c>
       <c r="C293" t="n">
-        <v>9.056063672064838</v>
+        <v>9.05606466112774</v>
       </c>
       <c r="D293" t="n">
-        <v>8.698806174092596</v>
+        <v>8.698807124137426</v>
       </c>
       <c r="E293" t="n">
-        <v>9.056063672064838</v>
+        <v>9.05606466112774</v>
       </c>
       <c r="F293" t="n">
         <v>345757</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.89820671081543</v>
+        <v>8.898205757141113</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039448285923172</v>
+        <v>9.039447317111145</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657265642254186</v>
+        <v>8.657264714402972</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823431464676691</v>
+        <v>8.823430519016487</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6332,16 +6332,16 @@
         <v>44747</v>
       </c>
       <c r="B296" t="n">
-        <v>9.031140327453613</v>
+        <v>9.031139373779297</v>
       </c>
       <c r="C296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213922179017237</v>
       </c>
       <c r="D296" t="n">
-        <v>9.022831410169822</v>
+        <v>9.022830457372914</v>
       </c>
       <c r="E296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213922179017237</v>
       </c>
       <c r="F296" t="n">
         <v>222182</v>
@@ -6392,16 +6392,16 @@
         <v>44750</v>
       </c>
       <c r="B299" t="n">
-        <v>8.914822578430176</v>
+        <v>8.914824485778809</v>
       </c>
       <c r="C299" t="n">
-        <v>9.13083853751573</v>
+        <v>9.130840491081521</v>
       </c>
       <c r="D299" t="n">
-        <v>8.89820558093219</v>
+        <v>8.898207484725576</v>
       </c>
       <c r="E299" t="n">
-        <v>8.981288898959365</v>
+        <v>8.981290820528635</v>
       </c>
       <c r="F299" t="n">
         <v>122521</v>
@@ -6412,16 +6412,16 @@
         <v>44753</v>
       </c>
       <c r="B300" t="n">
-        <v>8.840048789978027</v>
+        <v>8.840047836303711</v>
       </c>
       <c r="C300" t="n">
-        <v>8.964674204800824</v>
+        <v>8.964673237681779</v>
       </c>
       <c r="D300" t="n">
-        <v>8.798507541524769</v>
+        <v>8.79850659233197</v>
       </c>
       <c r="E300" t="n">
-        <v>8.889898955907146</v>
+        <v>8.889897996854938</v>
       </c>
       <c r="F300" t="n">
         <v>130423</v>
@@ -6472,16 +6472,16 @@
         <v>44756</v>
       </c>
       <c r="B303" t="n">
-        <v>8.499406814575195</v>
+        <v>8.499407768249512</v>
       </c>
       <c r="C303" t="n">
-        <v>8.565873135038302</v>
+        <v>8.565874096170459</v>
       </c>
       <c r="D303" t="n">
-        <v>8.34985717616752</v>
+        <v>8.349858113061646</v>
       </c>
       <c r="E303" t="n">
-        <v>8.358165257542563</v>
+        <v>8.358166195368899</v>
       </c>
       <c r="F303" t="n">
         <v>213754</v>
@@ -6492,16 +6492,16 @@
         <v>44757</v>
       </c>
       <c r="B304" t="n">
-        <v>8.499406814575195</v>
+        <v>8.499407768249512</v>
       </c>
       <c r="C304" t="n">
-        <v>8.582490132519766</v>
+        <v>8.58249109551643</v>
       </c>
       <c r="D304" t="n">
-        <v>8.42463157800567</v>
+        <v>8.424632523289844</v>
       </c>
       <c r="E304" t="n">
-        <v>8.540948056181794</v>
+        <v>8.540949014517237</v>
       </c>
       <c r="F304" t="n">
         <v>109458</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557564735412598</v>
+        <v>8.557565689086914</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673882055340277</v>
+        <v>8.673883021977259</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482790329061535</v>
+        <v>8.482791274402823</v>
       </c>
       <c r="E306" t="n">
-        <v>8.499407327545896</v>
+        <v>8.49940827473902</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864973068237305</v>
+        <v>8.864974021911621</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873281984958936</v>
+        <v>8.873282939527108</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615723930679971</v>
+        <v>8.615724857540613</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632340094660361</v>
+        <v>8.632341023308532</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6572,16 +6572,16 @@
         <v>44763</v>
       </c>
       <c r="B308" t="n">
-        <v>8.823430061340332</v>
+        <v>8.823431968688965</v>
       </c>
       <c r="C308" t="n">
-        <v>8.881589133352559</v>
+        <v>8.881591053273359</v>
       </c>
       <c r="D308" t="n">
-        <v>8.756964577673919</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="E308" t="n">
-        <v>8.756964577673919</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="F308" t="n">
         <v>93866</v>
@@ -6592,16 +6592,16 @@
         <v>44764</v>
       </c>
       <c r="B309" t="n">
-        <v>8.848356246948242</v>
+        <v>8.848357200622559</v>
       </c>
       <c r="C309" t="n">
-        <v>8.956363808991638</v>
+        <v>8.956364774306991</v>
       </c>
       <c r="D309" t="n">
-        <v>8.806814170620388</v>
+        <v>8.806815119817307</v>
       </c>
       <c r="E309" t="n">
-        <v>8.82343033336643</v>
+        <v>8.823431284354236</v>
       </c>
       <c r="F309" t="n">
         <v>116832</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039448738098145</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039448738098145</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815123823192138</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815123823192138</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756964683532715</v>
+        <v>8.756966590881348</v>
       </c>
       <c r="C311" t="n">
-        <v>9.1225302738709</v>
+        <v>9.122532260843132</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756964683532715</v>
+        <v>8.756966590881348</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039446957503669</v>
+        <v>9.039448926379578</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6692,16 +6692,16 @@
         <v>44771</v>
       </c>
       <c r="B314" t="n">
-        <v>8.914822578430176</v>
+        <v>8.914824485778809</v>
       </c>
       <c r="C314" t="n">
-        <v>9.114221540017745</v>
+        <v>9.114223490028287</v>
       </c>
       <c r="D314" t="n">
-        <v>8.906513662315495</v>
+        <v>8.906515567886416</v>
       </c>
       <c r="E314" t="n">
-        <v>9.097605377251137</v>
+        <v>9.097607323706608</v>
       </c>
       <c r="F314" t="n">
         <v>141168</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.939748764038086</v>
+        <v>8.939746856689453</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172380914689739</v>
+        <v>9.172378957707652</v>
       </c>
       <c r="D317" t="n">
-        <v>8.939748764038086</v>
+        <v>8.939746856689453</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114222668343956</v>
+        <v>9.114220723770277</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513022422790527</v>
+        <v>9.513023376464844</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596105752085279</v>
+        <v>9.596106714088645</v>
       </c>
       <c r="D322" t="n">
-        <v>9.205615022604585</v>
+        <v>9.20561594546151</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288697517167847</v>
+        <v>9.288698448353738</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6872,16 +6872,16 @@
         <v>44784</v>
       </c>
       <c r="B323" t="n">
-        <v>9.762272834777832</v>
+        <v>9.762271881103516</v>
       </c>
       <c r="C323" t="n">
-        <v>9.77058091764879</v>
+        <v>9.770579963162858</v>
       </c>
       <c r="D323" t="n">
-        <v>9.446556503634687</v>
+        <v>9.446555580802631</v>
       </c>
       <c r="E323" t="n">
-        <v>9.446556503634687</v>
+        <v>9.446555580802631</v>
       </c>
       <c r="F323" t="n">
         <v>1309919</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.770580291748047</v>
+        <v>9.77057933807373</v>
       </c>
       <c r="C324" t="n">
-        <v>9.86197170166864</v>
+        <v>9.861970739073907</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262965348279</v>
+        <v>9.654262023027314</v>
       </c>
       <c r="E324" t="n">
-        <v>9.82042962051198</v>
+        <v>9.820428661972032</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494453430176</v>
+        <v>10.53494644165039</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.7592713789844</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216171794617</v>
+        <v>10.35216359220203</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.7592713789844</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.4934024810791</v>
+        <v>10.49340343475342</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494372351503</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092019610571</v>
+        <v>10.21092112410713</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494372351503</v>
+        <v>10.53494468096475</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7032,16 +7032,16 @@
         <v>44796</v>
       </c>
       <c r="B331" t="n">
-        <v>10.48509502410889</v>
+        <v>10.4850959777832</v>
       </c>
       <c r="C331" t="n">
-        <v>10.48509502410889</v>
+        <v>10.4850959777832</v>
       </c>
       <c r="D331" t="n">
-        <v>10.29400412889686</v>
+        <v>10.29400506519045</v>
       </c>
       <c r="E331" t="n">
-        <v>10.38539553548497</v>
+        <v>10.3853964800911</v>
       </c>
       <c r="F331" t="n">
         <v>120309</v>
@@ -7052,16 +7052,16 @@
         <v>44797</v>
       </c>
       <c r="B332" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588748931885</v>
       </c>
       <c r="C332" t="n">
-        <v>10.8257366986775</v>
+        <v>10.8257376567636</v>
       </c>
       <c r="D332" t="n">
-        <v>10.3853958178368</v>
+        <v>10.38539673695239</v>
       </c>
       <c r="E332" t="n">
-        <v>10.3853958178368</v>
+        <v>10.38539673695239</v>
       </c>
       <c r="F332" t="n">
         <v>196055</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250240325928</v>
+        <v>10.79250335693359</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389380981785</v>
+        <v>10.88389477156793</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633575420836</v>
+        <v>10.62633669319944</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573640085461</v>
+        <v>10.82573735746564</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096035003662</v>
+        <v>10.75096130371094</v>
       </c>
       <c r="C334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="D334" t="n">
-        <v>10.3272365119659</v>
+        <v>10.32723742805339</v>
       </c>
       <c r="E334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7112,16 +7112,16 @@
         <v>44802</v>
       </c>
       <c r="B335" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787910461426</v>
       </c>
       <c r="C335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75927052205955</v>
       </c>
       <c r="D335" t="n">
-        <v>10.56817865938468</v>
+        <v>10.56817960414618</v>
       </c>
       <c r="E335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75927052205955</v>
       </c>
       <c r="F335" t="n">
         <v>128948</v>
@@ -7172,16 +7172,16 @@
         <v>44805</v>
       </c>
       <c r="B338" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="C338" t="n">
-        <v>10.71772749611192</v>
+        <v>10.71772651584117</v>
       </c>
       <c r="D338" t="n">
-        <v>10.31892869453579</v>
+        <v>10.3189277507402</v>
       </c>
       <c r="E338" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="F338" t="n">
         <v>1368072</v>
@@ -7232,16 +7232,16 @@
         <v>44810</v>
       </c>
       <c r="B341" t="n">
-        <v>10.5764856338501</v>
+        <v>10.57648754119873</v>
       </c>
       <c r="C341" t="n">
-        <v>10.63464387318185</v>
+        <v>10.63464579101866</v>
       </c>
       <c r="D341" t="n">
-        <v>10.50171123169863</v>
+        <v>10.50171312556255</v>
       </c>
       <c r="E341" t="n">
-        <v>10.63464387318185</v>
+        <v>10.63464579101866</v>
       </c>
       <c r="F341" t="n">
         <v>83753</v>
@@ -7252,16 +7252,16 @@
         <v>44812</v>
       </c>
       <c r="B342" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C342" t="n">
-        <v>10.90881937119658</v>
+        <v>10.90881840426656</v>
       </c>
       <c r="D342" t="n">
-        <v>10.57648689318649</v>
+        <v>10.57648595571358</v>
       </c>
       <c r="E342" t="n">
-        <v>10.57648689318649</v>
+        <v>10.57648595571358</v>
       </c>
       <c r="F342" t="n">
         <v>294768</v>
@@ -7272,16 +7272,16 @@
         <v>44813</v>
       </c>
       <c r="B343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.0500602722168</v>
       </c>
       <c r="C343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.0500602722168</v>
       </c>
       <c r="D343" t="n">
-        <v>10.68449557428166</v>
+        <v>10.68449465215745</v>
       </c>
       <c r="E343" t="n">
-        <v>10.76757890457422</v>
+        <v>10.76757797527951</v>
       </c>
       <c r="F343" t="n">
         <v>298877</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314342498779</v>
+        <v>11.13314437866211</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913016668102</v>
+        <v>11.1913026254664</v>
       </c>
       <c r="D344" t="n">
-        <v>10.94205170125786</v>
+        <v>10.9420526385631</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006010313701</v>
+        <v>11.05006104969434</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314342498779</v>
+        <v>11.13314437866211</v>
       </c>
       <c r="C346" t="n">
-        <v>11.1497595885191</v>
+        <v>11.14976054361677</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389345943545</v>
+        <v>10.88389439175881</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145150675345</v>
+        <v>11.14145246113944</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7372,16 +7372,16 @@
         <v>44820</v>
       </c>
       <c r="B348" t="n">
-        <v>11.3823938369751</v>
+        <v>11.38239288330078</v>
       </c>
       <c r="C348" t="n">
-        <v>11.3823938369751</v>
+        <v>11.38239288330078</v>
       </c>
       <c r="D348" t="n">
-        <v>11.07498642973096</v>
+        <v>11.07498550181278</v>
       </c>
       <c r="E348" t="n">
-        <v>11.28269434037115</v>
+        <v>11.28269339505016</v>
       </c>
       <c r="F348" t="n">
         <v>238301</v>
@@ -7412,16 +7412,16 @@
         <v>44824</v>
       </c>
       <c r="B350" t="n">
-        <v>11.15806770324707</v>
+        <v>11.15806865692139</v>
       </c>
       <c r="C350" t="n">
-        <v>11.30761818385911</v>
+        <v>11.30761915031543</v>
       </c>
       <c r="D350" t="n">
-        <v>11.15806770324707</v>
+        <v>11.15806865692139</v>
       </c>
       <c r="E350" t="n">
-        <v>11.17468470155888</v>
+        <v>11.17468565665344</v>
       </c>
       <c r="F350" t="n">
         <v>127157</v>
@@ -7432,16 +7432,16 @@
         <v>44825</v>
       </c>
       <c r="B351" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C351" t="n">
-        <v>11.16637743815185</v>
+        <v>11.16637644839254</v>
       </c>
       <c r="D351" t="n">
-        <v>10.67618638617008</v>
+        <v>10.67618543986006</v>
       </c>
       <c r="E351" t="n">
-        <v>11.12483619142489</v>
+        <v>11.12483520534769</v>
       </c>
       <c r="F351" t="n">
         <v>359874</v>
@@ -7492,16 +7492,16 @@
         <v>44830</v>
       </c>
       <c r="B354" t="n">
-        <v>10.42693710327148</v>
+        <v>10.42693614959717</v>
       </c>
       <c r="C354" t="n">
-        <v>10.60971992210769</v>
+        <v>10.60971895171559</v>
       </c>
       <c r="D354" t="n">
-        <v>10.34385377614644</v>
+        <v>10.34385283007114</v>
       </c>
       <c r="E354" t="n">
-        <v>10.60971992210769</v>
+        <v>10.60971895171559</v>
       </c>
       <c r="F354" t="n">
         <v>121152</v>
@@ -7512,16 +7512,16 @@
         <v>44831</v>
       </c>
       <c r="B355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569507598877</v>
       </c>
       <c r="C355" t="n">
-        <v>10.58479547644101</v>
+        <v>10.58479351362845</v>
       </c>
       <c r="D355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569507598877</v>
       </c>
       <c r="E355" t="n">
-        <v>10.42693772973123</v>
+        <v>10.42693579619133</v>
       </c>
       <c r="F355" t="n">
         <v>115674</v>
@@ -7552,16 +7552,16 @@
         <v>44833</v>
       </c>
       <c r="B357" t="n">
-        <v>10.12783718109131</v>
+        <v>10.12783813476562</v>
       </c>
       <c r="C357" t="n">
-        <v>10.20261242140248</v>
+        <v>10.2026133821179</v>
       </c>
       <c r="D357" t="n">
-        <v>9.978287535200392</v>
+        <v>9.978288474792565</v>
       </c>
       <c r="E357" t="n">
-        <v>10.17768650656734</v>
+        <v>10.17768746493565</v>
       </c>
       <c r="F357" t="n">
         <v>97132</v>
@@ -7572,16 +7572,16 @@
         <v>44834</v>
       </c>
       <c r="B358" t="n">
-        <v>10.18599510192871</v>
+        <v>10.18599414825439</v>
       </c>
       <c r="C358" t="n">
-        <v>10.26907842821965</v>
+        <v>10.26907746676657</v>
       </c>
       <c r="D358" t="n">
-        <v>9.920128958636587</v>
+        <v>9.920128029854263</v>
       </c>
       <c r="E358" t="n">
-        <v>10.17768701971906</v>
+        <v>10.17768606682259</v>
       </c>
       <c r="F358" t="n">
         <v>188154</v>
@@ -7592,16 +7592,16 @@
         <v>44837</v>
       </c>
       <c r="B359" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569507598877</v>
       </c>
       <c r="C359" t="n">
-        <v>10.60972055954919</v>
+        <v>10.6097185921146</v>
       </c>
       <c r="D359" t="n">
-        <v>10.13614648468832</v>
+        <v>10.13614460507188</v>
       </c>
       <c r="E359" t="n">
-        <v>10.36047056319891</v>
+        <v>10.36046864198449</v>
       </c>
       <c r="F359" t="n">
         <v>398643</v>
@@ -7612,16 +7612,16 @@
         <v>44838</v>
       </c>
       <c r="B360" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C360" t="n">
-        <v>10.75926782795914</v>
+        <v>10.75926878532992</v>
       </c>
       <c r="D360" t="n">
-        <v>10.32723593271258</v>
+        <v>10.32723685164071</v>
       </c>
       <c r="E360" t="n">
-        <v>10.38539416877246</v>
+        <v>10.38539509287557</v>
       </c>
       <c r="F360" t="n">
         <v>266324</v>
@@ -7632,16 +7632,16 @@
         <v>44839</v>
       </c>
       <c r="B361" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787910461426</v>
       </c>
       <c r="C361" t="n">
-        <v>10.90051113263368</v>
+        <v>10.90051210710464</v>
       </c>
       <c r="D361" t="n">
-        <v>10.55987057710461</v>
+        <v>10.55987152112339</v>
       </c>
       <c r="E361" t="n">
-        <v>10.80081080634695</v>
+        <v>10.80081177190503</v>
       </c>
       <c r="F361" t="n">
         <v>399697</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156279823885</v>
+        <v>10.55156188207657</v>
       </c>
       <c r="E364" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="F364" t="n">
         <v>167927</v>
@@ -7712,16 +7712,16 @@
         <v>44845</v>
       </c>
       <c r="B365" t="n">
-        <v>11.06667709350586</v>
+        <v>11.06667613983154</v>
       </c>
       <c r="C365" t="n">
-        <v>11.17468550345477</v>
+        <v>11.1746845404728</v>
       </c>
       <c r="D365" t="n">
-        <v>10.80081094455824</v>
+        <v>10.80081001379502</v>
       </c>
       <c r="E365" t="n">
-        <v>10.81742794406249</v>
+        <v>10.8174270118673</v>
       </c>
       <c r="F365" t="n">
         <v>221655</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558460235596</v>
+        <v>10.87558555603027</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160139071456</v>
+        <v>11.09160236333128</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85065952410448</v>
+        <v>10.85066047559313</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344315303822</v>
+        <v>11.03344412055507</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7772,16 +7772,16 @@
         <v>44851</v>
       </c>
       <c r="B368" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="D368" t="n">
-        <v>10.79250300417271</v>
+        <v>10.79250206495899</v>
       </c>
       <c r="E368" t="n">
-        <v>11.02513599190414</v>
+        <v>11.02513503244562</v>
       </c>
       <c r="F368" t="n">
         <v>132003</v>
@@ -7792,16 +7792,16 @@
         <v>44852</v>
       </c>
       <c r="B369" t="n">
-        <v>10.75926971435547</v>
+        <v>10.75926876068115</v>
       </c>
       <c r="C369" t="n">
-        <v>11.09160302709703</v>
+        <v>11.09160204396554</v>
       </c>
       <c r="D369" t="n">
-        <v>10.75096163195637</v>
+        <v>10.75096067901846</v>
       </c>
       <c r="E369" t="n">
-        <v>10.95866953505411</v>
+        <v>10.9586685637055</v>
       </c>
       <c r="F369" t="n">
         <v>172246</v>
@@ -7812,16 +7812,16 @@
         <v>44853</v>
       </c>
       <c r="B370" t="n">
-        <v>10.80911827087402</v>
+        <v>10.80911922454834</v>
       </c>
       <c r="C370" t="n">
-        <v>10.91712750799944</v>
+        <v>10.91712847120327</v>
       </c>
       <c r="D370" t="n">
-        <v>10.71772686682196</v>
+        <v>10.71772781243293</v>
       </c>
       <c r="E370" t="n">
-        <v>10.75926894531107</v>
+        <v>10.75926989458725</v>
       </c>
       <c r="F370" t="n">
         <v>116727</v>
@@ -7832,16 +7832,16 @@
         <v>44854</v>
       </c>
       <c r="B371" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C371" t="n">
-        <v>11.0417509273161</v>
+        <v>11.04175190982251</v>
       </c>
       <c r="D371" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="E371" t="n">
-        <v>10.95866761369751</v>
+        <v>10.95866858881108</v>
       </c>
       <c r="F371" t="n">
         <v>119045</v>
@@ -7872,16 +7872,16 @@
         <v>44858</v>
       </c>
       <c r="B373" t="n">
-        <v>10.84235191345215</v>
+        <v>10.84235286712646</v>
       </c>
       <c r="C373" t="n">
-        <v>10.95866839385256</v>
+        <v>10.95866935775788</v>
       </c>
       <c r="D373" t="n">
-        <v>10.67618527438544</v>
+        <v>10.67618621344403</v>
       </c>
       <c r="E373" t="n">
-        <v>10.67618527438544</v>
+        <v>10.67618621344403</v>
       </c>
       <c r="F373" t="n">
         <v>186469</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.65126037597656</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866870237426</v>
+        <v>10.95866772117583</v>
       </c>
       <c r="D374" t="n">
-        <v>10.65126132965088</v>
+        <v>10.65126037597656</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772681852483</v>
+        <v>10.71772585889944</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -7912,16 +7912,16 @@
         <v>44860</v>
       </c>
       <c r="B375" t="n">
-        <v>10.71772575378418</v>
+        <v>10.7177267074585</v>
       </c>
       <c r="C375" t="n">
-        <v>10.96697569463996</v>
+        <v>10.9669766704928</v>
       </c>
       <c r="D375" t="n">
-        <v>10.65126027151317</v>
+        <v>10.65126121927332</v>
       </c>
       <c r="E375" t="n">
-        <v>10.65126027151317</v>
+        <v>10.65126121927332</v>
       </c>
       <c r="F375" t="n">
         <v>230294</v>
@@ -7952,16 +7952,16 @@
         <v>44862</v>
       </c>
       <c r="B377" t="n">
-        <v>10.95866966247559</v>
+        <v>10.95866870880127</v>
       </c>
       <c r="C377" t="n">
-        <v>10.99190282718986</v>
+        <v>10.99190187062344</v>
       </c>
       <c r="D377" t="n">
-        <v>10.68449542753418</v>
+        <v>10.68449449771977</v>
       </c>
       <c r="E377" t="n">
-        <v>10.89220249831554</v>
+        <v>10.89220155042551</v>
       </c>
       <c r="F377" t="n">
         <v>271802</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19960975646973</v>
+        <v>11.19961071014404</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577640028841</v>
+        <v>11.36577736811222</v>
       </c>
       <c r="D381" t="n">
-        <v>10.8838934671068</v>
+        <v>10.8838943938971</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344394738246</v>
+        <v>11.03344488690735</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8052,16 +8052,16 @@
         <v>44872</v>
       </c>
       <c r="B382" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="C382" t="n">
-        <v>11.24115083643875</v>
+        <v>11.24115182292292</v>
       </c>
       <c r="D382" t="n">
-        <v>10.72603558366884</v>
+        <v>10.72603652494829</v>
       </c>
       <c r="E382" t="n">
-        <v>11.11652627275442</v>
+        <v>11.11652724830197</v>
       </c>
       <c r="F382" t="n">
         <v>110617</v>
@@ -8072,16 +8072,16 @@
         <v>44873</v>
       </c>
       <c r="B383" t="n">
-        <v>10.77588653564453</v>
+        <v>10.77588748931885</v>
       </c>
       <c r="C383" t="n">
-        <v>10.91712810775032</v>
+        <v>10.91712907392462</v>
       </c>
       <c r="D383" t="n">
-        <v>10.62633604654561</v>
+        <v>10.62633698698459</v>
       </c>
       <c r="E383" t="n">
-        <v>10.9005111084955</v>
+        <v>10.90051207319919</v>
       </c>
       <c r="F383" t="n">
         <v>103348</v>
@@ -8092,16 +8092,16 @@
         <v>44874</v>
       </c>
       <c r="B384" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280242919922</v>
       </c>
       <c r="C384" t="n">
-        <v>10.84235303967512</v>
+        <v>10.84235207266271</v>
       </c>
       <c r="D384" t="n">
-        <v>10.49340356222759</v>
+        <v>10.49340262633743</v>
       </c>
       <c r="E384" t="n">
-        <v>10.79250287583077</v>
+        <v>10.79250191326441</v>
       </c>
       <c r="F384" t="n">
         <v>162870</v>
@@ -8112,16 +8112,16 @@
         <v>44875</v>
       </c>
       <c r="B385" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787910461426</v>
       </c>
       <c r="C385" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787910461426</v>
       </c>
       <c r="D385" t="n">
-        <v>10.23584535140422</v>
+        <v>10.23584626645618</v>
       </c>
       <c r="E385" t="n">
-        <v>10.58479482394483</v>
+        <v>10.58479577019176</v>
       </c>
       <c r="F385" t="n">
         <v>289395</v>
@@ -8152,16 +8152,16 @@
         <v>44879</v>
       </c>
       <c r="B387" t="n">
-        <v>10.08629703521729</v>
+        <v>10.08629608154297</v>
       </c>
       <c r="C387" t="n">
-        <v>10.50171372532113</v>
+        <v>10.50171273236855</v>
       </c>
       <c r="D387" t="n">
-        <v>9.953364362169316</v>
+        <v>9.95336342106398</v>
       </c>
       <c r="E387" t="n">
-        <v>10.25246371125882</v>
+        <v>10.2524627418732</v>
       </c>
       <c r="F387" t="n">
         <v>430564</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.707115173339844</v>
+        <v>8.70711612701416</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629515547199</v>
+        <v>10.08629626020535</v>
       </c>
       <c r="D388" t="n">
-        <v>8.707115173339844</v>
+        <v>8.70711612701416</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629515547199</v>
+        <v>10.08629626020535</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765275001525879</v>
+        <v>8.765273094177246</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873283423838657</v>
+        <v>8.873281492987086</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225234559425131</v>
+        <v>8.225232769590827</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707116748700779</v>
+        <v>8.707114854007546</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8212,16 +8212,16 @@
         <v>44883</v>
       </c>
       <c r="B390" t="n">
-        <v>8.557564735412598</v>
+        <v>8.557565689086914</v>
       </c>
       <c r="C390" t="n">
-        <v>8.914823107609253</v>
+        <v>8.914824101097249</v>
       </c>
       <c r="D390" t="n">
-        <v>8.39139892422611</v>
+        <v>8.391399859382533</v>
       </c>
       <c r="E390" t="n">
-        <v>8.848356783134658</v>
+        <v>8.848357769215497</v>
       </c>
       <c r="F390" t="n">
         <v>571733</v>
@@ -8252,16 +8252,16 @@
         <v>44887</v>
       </c>
       <c r="B392" t="n">
-        <v>8.562845230102539</v>
+        <v>8.562846183776855</v>
       </c>
       <c r="C392" t="n">
-        <v>9.039488002680034</v>
+        <v>9.039489009439741</v>
       </c>
       <c r="D392" t="n">
-        <v>8.52939671765821</v>
+        <v>8.529397667607249</v>
       </c>
       <c r="E392" t="n">
-        <v>8.947504383423015</v>
+        <v>8.94750537993818</v>
       </c>
       <c r="F392" t="n">
         <v>321211</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.780261039733887</v>
+        <v>8.78026008605957</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880606577737419</v>
+        <v>8.880605613163999</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462499749319136</v>
+        <v>8.462498830158687</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537758692786666</v>
+        <v>8.537757765451913</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081298828125</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081298828125</v>
+        <v>9.081299781799316</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621380711839127</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621380711839127</v>
+        <v>8.621381617215055</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.822073936462402</v>
+        <v>8.82207202911377</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098024846931471</v>
+        <v>9.098022879921743</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746814138985041</v>
+        <v>8.746812247907716</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081300167445182</v>
+        <v>9.081298204051361</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8392,16 +8392,16 @@
         <v>44896</v>
       </c>
       <c r="B399" t="n">
-        <v>8.955867767333984</v>
+        <v>8.955866813659668</v>
       </c>
       <c r="C399" t="n">
-        <v>8.955867767333984</v>
+        <v>8.955866813659668</v>
       </c>
       <c r="D399" t="n">
-        <v>8.596295149529491</v>
+        <v>8.596294234144615</v>
       </c>
       <c r="E399" t="n">
-        <v>8.721727301760714</v>
+        <v>8.721726373019072</v>
       </c>
       <c r="F399" t="n">
         <v>469965</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947505950927734</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198370118006814</v>
+        <v>9.198371098419715</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822072856946983</v>
+        <v>8.822073797252052</v>
       </c>
       <c r="E400" t="n">
-        <v>9.139834167037881</v>
+        <v>9.1398351412117</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8432,16 +8432,16 @@
         <v>44900</v>
       </c>
       <c r="B401" t="n">
-        <v>8.746813774108887</v>
+        <v>8.74681282043457</v>
       </c>
       <c r="C401" t="n">
-        <v>9.089662548080438</v>
+        <v>9.089661557024961</v>
       </c>
       <c r="D401" t="n">
-        <v>8.663192900587594</v>
+        <v>8.66319195603055</v>
       </c>
       <c r="E401" t="n">
-        <v>8.947505718869293</v>
+        <v>8.947504743313322</v>
       </c>
       <c r="F401" t="n">
         <v>131055</v>
@@ -8452,16 +8452,16 @@
         <v>44901</v>
       </c>
       <c r="B402" t="n">
-        <v>8.746813774108887</v>
+        <v>8.74681282043457</v>
       </c>
       <c r="C402" t="n">
-        <v>8.863884005207408</v>
+        <v>8.863883038768801</v>
       </c>
       <c r="D402" t="n">
-        <v>8.688278658559627</v>
+        <v>8.688277711267455</v>
       </c>
       <c r="E402" t="n">
-        <v>8.771900372221511</v>
+        <v>8.771899415811978</v>
       </c>
       <c r="F402" t="n">
         <v>122416</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905695681933357</v>
+        <v>8.905693728734814</v>
       </c>
       <c r="D403" t="n">
-        <v>8.679917128923909</v>
+        <v>8.679915225243152</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437412261962891</v>
+        <v>8.437413215637207</v>
       </c>
       <c r="C404" t="n">
-        <v>8.73845055437487</v>
+        <v>8.738451542075317</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412326507723987</v>
+        <v>8.412327458562881</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705002041915865</v>
+        <v>8.705003025835651</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952408313751221</v>
+        <v>7.952408790588379</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027667255826291</v>
+        <v>8.027667737176076</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818614265555337</v>
+        <v>7.818614734370023</v>
       </c>
       <c r="E406" t="n">
-        <v>7.935683637656506</v>
+        <v>7.93568411349083</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8552,16 +8552,16 @@
         <v>44908</v>
       </c>
       <c r="B407" t="n">
-        <v>8.027668952941895</v>
+        <v>8.027666091918945</v>
       </c>
       <c r="C407" t="n">
-        <v>8.24508474729393</v>
+        <v>8.245081808785029</v>
       </c>
       <c r="D407" t="n">
-        <v>7.893874036320201</v>
+        <v>7.893871222981123</v>
       </c>
       <c r="E407" t="n">
-        <v>7.893874036320201</v>
+        <v>7.893871222981123</v>
       </c>
       <c r="F407" t="n">
         <v>284655</v>
@@ -8612,16 +8612,16 @@
         <v>44911</v>
       </c>
       <c r="B410" t="n">
-        <v>8.027668952941895</v>
+        <v>8.027666091918945</v>
       </c>
       <c r="C410" t="n">
-        <v>8.295257946044645</v>
+        <v>8.295254989654255</v>
       </c>
       <c r="D410" t="n">
-        <v>8.027668952941895</v>
+        <v>8.027666091918945</v>
       </c>
       <c r="E410" t="n">
-        <v>8.253446667038839</v>
+        <v>8.253443725549788</v>
       </c>
       <c r="F410" t="n">
         <v>177935</v>
@@ -8672,16 +8672,16 @@
         <v>44916</v>
       </c>
       <c r="B413" t="n">
-        <v>8.454137802124023</v>
+        <v>8.454140663146973</v>
       </c>
       <c r="C413" t="n">
-        <v>8.613017606644735</v>
+        <v>8.613020521435294</v>
       </c>
       <c r="D413" t="n">
-        <v>8.370516100671649</v>
+        <v>8.370518933395603</v>
       </c>
       <c r="E413" t="n">
-        <v>8.429050367533794</v>
+        <v>8.429053220066731</v>
       </c>
       <c r="F413" t="n">
         <v>125998</v>
@@ -8712,16 +8712,16 @@
         <v>44918</v>
       </c>
       <c r="B415" t="n">
-        <v>8.688277244567871</v>
+        <v>8.688278198242188</v>
       </c>
       <c r="C415" t="n">
-        <v>8.763537026657437</v>
+        <v>8.763537988592692</v>
       </c>
       <c r="D415" t="n">
-        <v>8.50431000853621</v>
+        <v>8.504310942017245</v>
       </c>
       <c r="E415" t="n">
-        <v>8.529396602566065</v>
+        <v>8.529397538800746</v>
       </c>
       <c r="F415" t="n">
         <v>92391</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780262685738871</v>
+        <v>8.780260760050309</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613019250906639</v>
+        <v>8.613017361897933</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730090327401705</v>
+        <v>8.730088412716954</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8772,16 +8772,16 @@
         <v>44923</v>
       </c>
       <c r="B418" t="n">
-        <v>8.746813774108887</v>
+        <v>8.74681282043457</v>
       </c>
       <c r="C418" t="n">
-        <v>8.930781880221272</v>
+        <v>8.930780906488719</v>
       </c>
       <c r="D418" t="n">
-        <v>8.679916739235615</v>
+        <v>8.679915792855153</v>
       </c>
       <c r="E418" t="n">
-        <v>8.688278658559627</v>
+        <v>8.688277711267455</v>
       </c>
       <c r="F418" t="n">
         <v>114515</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914057601632781</v>
+        <v>8.914055646600298</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696640968322754</v>
+        <v>8.696639060974121</v>
       </c>
       <c r="E419" t="n">
-        <v>8.830435884216666</v>
+        <v>8.83043394752411</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8812,16 +8812,16 @@
         <v>44928</v>
       </c>
       <c r="B420" t="n">
-        <v>8.529396057128906</v>
+        <v>8.529397964477539</v>
       </c>
       <c r="C420" t="n">
-        <v>8.771898383675891</v>
+        <v>8.771900345253039</v>
       </c>
       <c r="D420" t="n">
-        <v>8.529396057128906</v>
+        <v>8.529397964477539</v>
       </c>
       <c r="E420" t="n">
-        <v>8.70500136396784</v>
+        <v>8.705003310585438</v>
       </c>
       <c r="F420" t="n">
         <v>132530</v>
@@ -8872,16 +8872,16 @@
         <v>44931</v>
       </c>
       <c r="B423" t="n">
-        <v>8.395603179931641</v>
+        <v>8.395604133605957</v>
       </c>
       <c r="C423" t="n">
-        <v>8.454138290314409</v>
+        <v>8.454139250637853</v>
       </c>
       <c r="D423" t="n">
-        <v>8.270171040580143</v>
+        <v>8.270171980006358</v>
       </c>
       <c r="E423" t="n">
-        <v>8.362154665447276</v>
+        <v>8.362155615322106</v>
       </c>
       <c r="F423" t="n">
         <v>69636</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947505950927734</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947504997253418</v>
+        <v>8.947505950927734</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387240485058745</v>
+        <v>8.387241379016988</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395603243848893</v>
+        <v>8.395604138698484</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8912,16 +8912,16 @@
         <v>44935</v>
       </c>
       <c r="B425" t="n">
-        <v>8.81371021270752</v>
+        <v>8.813712120056152</v>
       </c>
       <c r="C425" t="n">
-        <v>8.947504260648964</v>
+        <v>8.947506196951567</v>
       </c>
       <c r="D425" t="n">
-        <v>8.69663916054807</v>
+        <v>8.696641042561707</v>
       </c>
       <c r="E425" t="n">
-        <v>8.905693830702377</v>
+        <v>8.905695757956909</v>
       </c>
       <c r="F425" t="n">
         <v>148121</v>
@@ -8932,16 +8932,16 @@
         <v>44936</v>
       </c>
       <c r="B426" t="n">
-        <v>8.930781364440918</v>
+        <v>8.930782318115234</v>
       </c>
       <c r="C426" t="n">
-        <v>8.972591798786882</v>
+        <v>8.972592756925931</v>
       </c>
       <c r="D426" t="n">
-        <v>8.75517602793489</v>
+        <v>8.755176962857174</v>
       </c>
       <c r="E426" t="n">
-        <v>8.830434977785734</v>
+        <v>8.830435920744552</v>
       </c>
       <c r="F426" t="n">
         <v>133478</v>
@@ -8952,16 +8952,16 @@
         <v>44937</v>
       </c>
       <c r="B427" t="n">
-        <v>8.964229583740234</v>
+        <v>8.964228630065918</v>
       </c>
       <c r="C427" t="n">
-        <v>9.072937895832748</v>
+        <v>9.072936930593318</v>
       </c>
       <c r="D427" t="n">
-        <v>8.847160192439846</v>
+        <v>8.847159251220148</v>
       </c>
       <c r="E427" t="n">
-        <v>8.922419146857282</v>
+        <v>8.922418197631035</v>
       </c>
       <c r="F427" t="n">
         <v>136954</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139833970240518</v>
+        <v>9.139834941690628</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006039914165292</v>
+        <v>9.006040871394767</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847159262540833</v>
+        <v>8.847160202883281</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972591400146484</v>
+        <v>8.972592353820801</v>
       </c>
       <c r="C431" t="n">
-        <v>9.06457502373333</v>
+        <v>9.064575987184355</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905694372108872</v>
+        <v>8.905695318672869</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964228641536403</v>
+        <v>8.964229594321862</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566304206848145</v>
+        <v>9.566306114196777</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616476556718098</v>
+        <v>9.616478474070194</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407422718528574</v>
+        <v>9.407424594199101</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424147395245551</v>
+        <v>9.424149274250677</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C438" t="n">
-        <v>9.959326039139317</v>
+        <v>9.95932505997885</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741910266268745</v>
+        <v>9.741909308483715</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="D439" t="n">
-        <v>9.649926637741174</v>
+        <v>9.6499256889996</v>
       </c>
       <c r="E439" t="n">
-        <v>9.800444538840333</v>
+        <v>9.80044357530045</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9232,16 +9232,16 @@
         <v>44957</v>
       </c>
       <c r="B441" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="C441" t="n">
-        <v>9.68337541974836</v>
+        <v>9.683374442443164</v>
       </c>
       <c r="D441" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="E441" t="n">
-        <v>9.616477546137954</v>
+        <v>9.616476575584498</v>
       </c>
       <c r="F441" t="n">
         <v>134742</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.666650772094727</v>
+        <v>9.66664981842041</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725185886602381</v>
+        <v>9.725184927153217</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457596911730329</v>
+        <v>9.457595978680457</v>
       </c>
       <c r="E443" t="n">
-        <v>9.70009928893616</v>
+        <v>9.700098331961943</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9292,16 +9292,16 @@
         <v>44960</v>
       </c>
       <c r="B444" t="n">
-        <v>9.67501163482666</v>
+        <v>9.675012588500977</v>
       </c>
       <c r="C444" t="n">
-        <v>9.867341635839546</v>
+        <v>9.867342608471997</v>
       </c>
       <c r="D444" t="n">
-        <v>9.382336934386988</v>
+        <v>9.382337859212104</v>
       </c>
       <c r="E444" t="n">
-        <v>9.474320555692112</v>
+        <v>9.474321489584133</v>
       </c>
       <c r="F444" t="n">
         <v>1290218</v>
@@ -9352,16 +9352,16 @@
         <v>44965</v>
       </c>
       <c r="B447" t="n">
-        <v>10.09312057495117</v>
+        <v>10.09312152862549</v>
       </c>
       <c r="C447" t="n">
-        <v>10.16001676400513</v>
+        <v>10.1600177240003</v>
       </c>
       <c r="D447" t="n">
-        <v>9.649926286291848</v>
+        <v>9.649927198089818</v>
       </c>
       <c r="E447" t="n">
-        <v>9.741909911469383</v>
+        <v>9.741910831958663</v>
       </c>
       <c r="F447" t="n">
         <v>233139</v>
@@ -9372,16 +9372,16 @@
         <v>44966</v>
       </c>
       <c r="B448" t="n">
-        <v>10.00949859619141</v>
+        <v>10.00950050354004</v>
       </c>
       <c r="C448" t="n">
-        <v>10.14329265094199</v>
+        <v>10.1432945837856</v>
       </c>
       <c r="D448" t="n">
-        <v>9.88406561968711</v>
+        <v>9.884067503134004</v>
       </c>
       <c r="E448" t="n">
-        <v>10.09312030048077</v>
+        <v>10.09312222376384</v>
       </c>
       <c r="F448" t="n">
         <v>166136</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363994598389</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088338319906</v>
+        <v>10.41088144470998</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458606953524</v>
+        <v>10.03458420111209</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820778814282</v>
+        <v>10.11820590414945</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363994598389</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C455" t="n">
-        <v>10.61993809978836</v>
+        <v>10.61993612237364</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992776470442406</v>
+        <v>9.992774609804133</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889974477291</v>
+        <v>10.31889782341103</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458404541016</v>
+        <v>10.03458499908447</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889766329754</v>
+        <v>10.31889864399266</v>
       </c>
       <c r="D459" t="n">
-        <v>9.909152753011098</v>
+        <v>9.90915369476458</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950963183810783</v>
+        <v>9.950964129537878</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363994598389</v>
+        <v>10.24363803863525</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053782495434</v>
+        <v>10.31053590514944</v>
       </c>
       <c r="D460" t="n">
-        <v>9.850618792682926</v>
+        <v>9.850616958514175</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458606953524</v>
+        <v>10.03458420111209</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9632,16 +9632,16 @@
         <v>44987</v>
       </c>
       <c r="B461" t="n">
-        <v>10.47778034210205</v>
+        <v>10.47777843475342</v>
       </c>
       <c r="C461" t="n">
-        <v>10.55304014031698</v>
+        <v>10.55303821926824</v>
       </c>
       <c r="D461" t="n">
-        <v>10.1182077109589</v>
+        <v>10.11820586906596</v>
       </c>
       <c r="E461" t="n">
-        <v>10.2018294289286</v>
+        <v>10.20182757181338</v>
       </c>
       <c r="F461" t="n">
         <v>220181</v>
@@ -9672,16 +9672,16 @@
         <v>44991</v>
       </c>
       <c r="B463" t="n">
-        <v>10.6366605758667</v>
+        <v>10.63665962219238</v>
       </c>
       <c r="C463" t="n">
-        <v>10.6366605758667</v>
+        <v>10.63665962219238</v>
       </c>
       <c r="D463" t="n">
-        <v>10.20182819893464</v>
+        <v>10.20182728424704</v>
       </c>
       <c r="E463" t="n">
-        <v>10.32726034069602</v>
+        <v>10.32725941476227</v>
       </c>
       <c r="F463" t="n">
         <v>82488</v>
@@ -9692,16 +9692,16 @@
         <v>44992</v>
       </c>
       <c r="B464" t="n">
-        <v>10.66174697875977</v>
+        <v>10.66174793243408</v>
       </c>
       <c r="C464" t="n">
-        <v>10.73700592639459</v>
+        <v>10.73700688680069</v>
       </c>
       <c r="D464" t="n">
-        <v>10.37743334512914</v>
+        <v>10.3774342733721</v>
       </c>
       <c r="E464" t="n">
-        <v>10.66174697875977</v>
+        <v>10.66174793243408</v>
       </c>
       <c r="F464" t="n">
         <v>103874</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.74536895751953</v>
       </c>
       <c r="C465" t="n">
-        <v>10.74536800384521</v>
+        <v>10.74536895751953</v>
       </c>
       <c r="D465" t="n">
-        <v>10.50286563988488</v>
+        <v>10.5028665720366</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502245880179</v>
+        <v>10.64502340357023</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9752,16 +9752,16 @@
         <v>44995</v>
       </c>
       <c r="B467" t="n">
-        <v>10.82062721252441</v>
+        <v>10.82062816619873</v>
       </c>
       <c r="C467" t="n">
-        <v>10.82062721252441</v>
+        <v>10.82062816619873</v>
       </c>
       <c r="D467" t="n">
-        <v>10.23527613080669</v>
+        <v>10.23527703289118</v>
       </c>
       <c r="E467" t="n">
-        <v>10.8122652942543</v>
+        <v>10.81226624719164</v>
       </c>
       <c r="F467" t="n">
         <v>153705</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758634567260742</v>
+        <v>9.758633613586426</v>
       </c>
       <c r="C470" t="n">
-        <v>9.9676884311345</v>
+        <v>9.967687457030143</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675012853683121</v>
+        <v>9.675011908180837</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892428636872463</v>
+        <v>9.892427670122959</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165615081787</v>
+        <v>10.15165519714355</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837999019679</v>
+        <v>10.16837903495139</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683376046098697</v>
+        <v>9.683375136415892</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833894801212116</v>
+        <v>9.833893877389167</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9852,16 +9852,16 @@
         <v>45002</v>
       </c>
       <c r="B472" t="n">
-        <v>9.942600250244141</v>
+        <v>9.942602157592773</v>
       </c>
       <c r="C472" t="n">
-        <v>10.18510343305635</v>
+        <v>10.18510538692582</v>
       </c>
       <c r="D472" t="n">
-        <v>9.750271095759805</v>
+        <v>9.750272966212783</v>
       </c>
       <c r="E472" t="n">
-        <v>10.18510343305635</v>
+        <v>10.18510538692582</v>
       </c>
       <c r="F472" t="n">
         <v>69952</v>
@@ -9872,16 +9872,16 @@
         <v>45005</v>
       </c>
       <c r="B473" t="n">
-        <v>9.532855033874512</v>
+        <v>9.532855987548828</v>
       </c>
       <c r="C473" t="n">
-        <v>9.909153125935795</v>
+        <v>9.909154117255268</v>
       </c>
       <c r="D473" t="n">
-        <v>9.340525868761105</v>
+        <v>9.340526803194662</v>
       </c>
       <c r="E473" t="n">
-        <v>9.909153125935795</v>
+        <v>9.909154117255268</v>
       </c>
       <c r="F473" t="n">
         <v>182676</v>
@@ -9892,16 +9892,16 @@
         <v>45006</v>
       </c>
       <c r="B474" t="n">
-        <v>9.440873146057129</v>
+        <v>9.440871238708496</v>
       </c>
       <c r="C474" t="n">
-        <v>9.583029986483497</v>
+        <v>9.583028050414784</v>
       </c>
       <c r="D474" t="n">
-        <v>9.415787386105999</v>
+        <v>9.415785483825466</v>
       </c>
       <c r="E474" t="n">
-        <v>9.532856786299918</v>
+        <v>9.532854860367744</v>
       </c>
       <c r="F474" t="n">
         <v>47196</v>
@@ -9912,16 +9912,16 @@
         <v>45007</v>
       </c>
       <c r="B475" t="n">
-        <v>9.449234962463379</v>
+        <v>9.449234008789062</v>
       </c>
       <c r="C475" t="n">
-        <v>9.507770076784624</v>
+        <v>9.507769117202587</v>
       </c>
       <c r="D475" t="n">
-        <v>9.206732586029814</v>
+        <v>9.206731656830312</v>
       </c>
       <c r="E475" t="n">
-        <v>9.482683479198295</v>
+        <v>9.482682522148149</v>
       </c>
       <c r="F475" t="n">
         <v>116622</v>
@@ -9932,16 +9932,16 @@
         <v>45008</v>
       </c>
       <c r="B476" t="n">
-        <v>9.33216381072998</v>
+        <v>9.332164764404297</v>
       </c>
       <c r="C476" t="n">
-        <v>9.407422755904157</v>
+        <v>9.407423717269351</v>
       </c>
       <c r="D476" t="n">
-        <v>9.131471890031355</v>
+        <v>9.131472823196523</v>
       </c>
       <c r="E476" t="n">
-        <v>9.399060837582692</v>
+        <v>9.399061798093364</v>
       </c>
       <c r="F476" t="n">
         <v>179094</v>
@@ -10052,16 +10052,16 @@
         <v>45016</v>
       </c>
       <c r="B482" t="n">
-        <v>9.984411239624023</v>
+        <v>9.984410285949707</v>
       </c>
       <c r="C482" t="n">
-        <v>11.00459469578863</v>
+        <v>11.00459364467013</v>
       </c>
       <c r="D482" t="n">
-        <v>9.984411239624023</v>
+        <v>9.984410285949707</v>
       </c>
       <c r="E482" t="n">
-        <v>11.00459469578863</v>
+        <v>11.00459364467013</v>
       </c>
       <c r="F482" t="n">
         <v>804556</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820669929775</v>
+        <v>10.11820570451678</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201959763182</v>
+        <v>9.633201012665911</v>
       </c>
       <c r="E483" t="n">
-        <v>10.0345849896889</v>
+        <v>10.03458400312928</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10092,16 +10092,16 @@
         <v>45020</v>
       </c>
       <c r="B484" t="n">
-        <v>9.599753379821777</v>
+        <v>9.599754333496094</v>
       </c>
       <c r="C484" t="n">
-        <v>9.758634038918892</v>
+        <v>9.758635008376988</v>
       </c>
       <c r="D484" t="n">
-        <v>9.53285550849724</v>
+        <v>9.532856455525678</v>
       </c>
       <c r="E484" t="n">
-        <v>9.700098926597763</v>
+        <v>9.70009989024077</v>
       </c>
       <c r="F484" t="n">
         <v>529909</v>
@@ -10132,16 +10132,16 @@
         <v>45022</v>
       </c>
       <c r="B486" t="n">
-        <v>9.541218757629395</v>
+        <v>9.541217803955078</v>
       </c>
       <c r="C486" t="n">
-        <v>9.633202390267682</v>
+        <v>9.633201427399317</v>
       </c>
       <c r="D486" t="n">
-        <v>9.390700009663053</v>
+        <v>9.39069907103355</v>
       </c>
       <c r="E486" t="n">
-        <v>9.524494078903984</v>
+        <v>9.52449312690135</v>
       </c>
       <c r="F486" t="n">
         <v>123364</v>
@@ -10152,16 +10152,16 @@
         <v>45026</v>
       </c>
       <c r="B487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="C487" t="n">
-        <v>9.700098570263346</v>
+        <v>9.700099553607547</v>
       </c>
       <c r="D487" t="n">
-        <v>9.40742301940918</v>
+        <v>9.407423973083496</v>
       </c>
       <c r="E487" t="n">
-        <v>9.574666431365994</v>
+        <v>9.574667401994555</v>
       </c>
       <c r="F487" t="n">
         <v>160237</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758634104106184</v>
+        <v>9.758633144676933</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474321299604751</v>
+        <v>9.474320368127982</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10192,16 +10192,16 @@
         <v>45028</v>
       </c>
       <c r="B489" t="n">
-        <v>9.574666976928711</v>
+        <v>9.574666023254395</v>
       </c>
       <c r="C489" t="n">
-        <v>9.78372083371632</v>
+        <v>9.783719859219421</v>
       </c>
       <c r="D489" t="n">
-        <v>9.574666976928711</v>
+        <v>9.574666023254395</v>
       </c>
       <c r="E489" t="n">
-        <v>9.700099122973164</v>
+        <v>9.700098156805314</v>
       </c>
       <c r="F489" t="n">
         <v>241777</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683374404907227</v>
+        <v>9.683375358581543</v>
       </c>
       <c r="C490" t="n">
-        <v>9.77535802632328</v>
+        <v>9.775358989056672</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566304188533978</v>
+        <v>9.566305130678549</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608114620035645</v>
+        <v>9.608115566297945</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098991394043</v>
+        <v>9.700098037719727</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766996023024904</v>
+        <v>9.766995062773542</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549581090294884</v>
+        <v>9.549580151418876</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691737072475323</v>
+        <v>9.691736119623117</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10292,16 +10292,16 @@
         <v>45035</v>
       </c>
       <c r="B494" t="n">
-        <v>9.658287048339844</v>
+        <v>9.658288955688477</v>
       </c>
       <c r="C494" t="n">
-        <v>9.716821311770225</v>
+        <v>9.716823230678386</v>
       </c>
       <c r="D494" t="n">
-        <v>9.599751944769041</v>
+        <v>9.59975384055798</v>
       </c>
       <c r="E494" t="n">
-        <v>9.616475779994744</v>
+        <v>9.616477679086358</v>
       </c>
       <c r="F494" t="n">
         <v>232823</v>
@@ -10312,16 +10312,16 @@
         <v>45036</v>
       </c>
       <c r="B495" t="n">
-        <v>9.599753379821777</v>
+        <v>9.599754333496094</v>
       </c>
       <c r="C495" t="n">
-        <v>9.775358716785163</v>
+        <v>9.77535968790475</v>
       </c>
       <c r="D495" t="n">
-        <v>9.549581026504057</v>
+        <v>9.549581975194069</v>
       </c>
       <c r="E495" t="n">
-        <v>9.658288492142907</v>
+        <v>9.658289451632312</v>
       </c>
       <c r="F495" t="n">
         <v>169823</v>
@@ -10332,16 +10332,16 @@
         <v>45040</v>
       </c>
       <c r="B496" t="n">
-        <v>9.516130447387695</v>
+        <v>9.516131401062012</v>
       </c>
       <c r="C496" t="n">
-        <v>9.700097679563306</v>
+        <v>9.700098651674196</v>
       </c>
       <c r="D496" t="n">
-        <v>9.516130447387695</v>
+        <v>9.516131401062012</v>
       </c>
       <c r="E496" t="n">
-        <v>9.633200656979527</v>
+        <v>9.633201622386224</v>
       </c>
       <c r="F496" t="n">
         <v>136322</v>
@@ -10352,16 +10352,16 @@
         <v>45041</v>
       </c>
       <c r="B497" t="n">
-        <v>9.248541831970215</v>
+        <v>9.248542785644531</v>
       </c>
       <c r="C497" t="n">
-        <v>9.633200985141286</v>
+        <v>9.633201978480185</v>
       </c>
       <c r="D497" t="n">
-        <v>9.248541831970215</v>
+        <v>9.248542785644531</v>
       </c>
       <c r="E497" t="n">
-        <v>9.633200985141286</v>
+        <v>9.633201978480185</v>
       </c>
       <c r="F497" t="n">
         <v>58153</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.28199291229248</v>
+        <v>9.281991958618164</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382338468264816</v>
+        <v>9.382337504280539</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215095034836967</v>
+        <v>9.215094088036043</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248543553494413</v>
+        <v>9.248542603256835</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10392,16 +10392,16 @@
         <v>45043</v>
       </c>
       <c r="B499" t="n">
-        <v>9.31544017791748</v>
+        <v>9.315439224243164</v>
       </c>
       <c r="C499" t="n">
-        <v>9.365613373750113</v>
+        <v>9.365612414939283</v>
       </c>
       <c r="D499" t="n">
-        <v>9.139834832643849</v>
+        <v>9.139833896947247</v>
       </c>
       <c r="E499" t="n">
-        <v>9.365613373750113</v>
+        <v>9.365612414939283</v>
       </c>
       <c r="F499" t="n">
         <v>124734</v>
@@ -10412,16 +10412,16 @@
         <v>45044</v>
       </c>
       <c r="B500" t="n">
-        <v>9.1761474609375</v>
+        <v>9.176148414611816</v>
       </c>
       <c r="C500" t="n">
-        <v>9.393830394462805</v>
+        <v>9.393831370760845</v>
       </c>
       <c r="D500" t="n">
-        <v>9.1761474609375</v>
+        <v>9.176148414611816</v>
       </c>
       <c r="E500" t="n">
-        <v>9.326850577363659</v>
+        <v>9.326851546700507</v>
       </c>
       <c r="F500" t="n">
         <v>147595</v>
@@ -10432,16 +10432,16 @@
         <v>45048</v>
       </c>
       <c r="B501" t="n">
-        <v>9.109169006347656</v>
+        <v>9.10916805267334</v>
       </c>
       <c r="C501" t="n">
-        <v>9.201265313813998</v>
+        <v>9.201264350497761</v>
       </c>
       <c r="D501" t="n">
-        <v>9.017072698881314</v>
+        <v>9.017071754848917</v>
       </c>
       <c r="E501" t="n">
-        <v>9.176147986110502</v>
+        <v>9.176147025423896</v>
       </c>
       <c r="F501" t="n">
         <v>926867</v>
@@ -10452,16 +10452,16 @@
         <v>45049</v>
       </c>
       <c r="B502" t="n">
-        <v>9.151030540466309</v>
+        <v>9.151029586791992</v>
       </c>
       <c r="C502" t="n">
-        <v>9.259872012055444</v>
+        <v>9.259871047038219</v>
       </c>
       <c r="D502" t="n">
-        <v>8.941721441697471</v>
+        <v>8.941720509836294</v>
       </c>
       <c r="E502" t="n">
-        <v>9.100796726876458</v>
+        <v>9.100795778437256</v>
       </c>
       <c r="F502" t="n">
         <v>158340</v>
@@ -10472,16 +10472,16 @@
         <v>45050</v>
       </c>
       <c r="B503" t="n">
-        <v>9.209638595581055</v>
+        <v>9.209637641906738</v>
       </c>
       <c r="C503" t="n">
-        <v>9.469182360300858</v>
+        <v>9.469181379750328</v>
       </c>
       <c r="D503" t="n">
-        <v>9.067306787235129</v>
+        <v>9.067305848299521</v>
       </c>
       <c r="E503" t="n">
-        <v>9.159403938655403</v>
+        <v>9.159402990182974</v>
       </c>
       <c r="F503" t="n">
         <v>221234</v>
@@ -10552,16 +10552,16 @@
         <v>45056</v>
       </c>
       <c r="B507" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="C507" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="D507" t="n">
-        <v>9.418946980877298</v>
+        <v>9.418947917893513</v>
       </c>
       <c r="E507" t="n">
-        <v>9.452436469202278</v>
+        <v>9.452437409550097</v>
       </c>
       <c r="F507" t="n">
         <v>185415</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845939636230469</v>
+        <v>9.845940589904785</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293249575018</v>
+        <v>10.27293349078287</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745471173433298</v>
+        <v>9.745472117376274</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548421658523</v>
+        <v>10.10548519539895</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10652,16 +10652,16 @@
         <v>45063</v>
       </c>
       <c r="B512" t="n">
-        <v>9.787332534790039</v>
+        <v>9.787333488464355</v>
       </c>
       <c r="C512" t="n">
-        <v>9.904545317354632</v>
+        <v>9.904546282450122</v>
       </c>
       <c r="D512" t="n">
-        <v>9.594766935296825</v>
+        <v>9.594767870207617</v>
       </c>
       <c r="E512" t="n">
-        <v>9.812449018873401</v>
+        <v>9.81244997499506</v>
       </c>
       <c r="F512" t="n">
         <v>227976</v>
@@ -10672,16 +10672,16 @@
         <v>45064</v>
       </c>
       <c r="B513" t="n">
-        <v>9.871055603027344</v>
+        <v>9.871057510375977</v>
       </c>
       <c r="C513" t="n">
-        <v>10.10548282511095</v>
+        <v>10.10548477775711</v>
       </c>
       <c r="D513" t="n">
-        <v>9.670117863931463</v>
+        <v>9.670119732453616</v>
       </c>
       <c r="E513" t="n">
-        <v>9.728723828282821</v>
+        <v>9.728725708129195</v>
       </c>
       <c r="F513" t="n">
         <v>659595</v>
@@ -10692,16 +10692,16 @@
         <v>45065</v>
       </c>
       <c r="B514" t="n">
-        <v>9.795705795288086</v>
+        <v>9.79570484161377</v>
       </c>
       <c r="C514" t="n">
-        <v>10.05525039713199</v>
+        <v>10.05524941818936</v>
       </c>
       <c r="D514" t="n">
-        <v>9.703609486473098</v>
+        <v>9.703608541764943</v>
       </c>
       <c r="E514" t="n">
-        <v>9.938036760245696</v>
+        <v>9.938035792714553</v>
       </c>
       <c r="F514" t="n">
         <v>287815</v>
@@ -10732,16 +10732,16 @@
         <v>45069</v>
       </c>
       <c r="B516" t="n">
-        <v>9.603139877319336</v>
+        <v>9.60313892364502</v>
       </c>
       <c r="C516" t="n">
-        <v>9.996642428485981</v>
+        <v>9.99664143573348</v>
       </c>
       <c r="D516" t="n">
-        <v>9.594767715277623</v>
+        <v>9.594766762434734</v>
       </c>
       <c r="E516" t="n">
-        <v>9.862684471139762</v>
+        <v>9.862683491690436</v>
       </c>
       <c r="F516" t="n">
         <v>117359</v>
@@ -10792,16 +10792,16 @@
         <v>45072</v>
       </c>
       <c r="B519" t="n">
-        <v>9.37708568572998</v>
+        <v>9.377084732055664</v>
       </c>
       <c r="C519" t="n">
-        <v>9.45243682702116</v>
+        <v>9.452435865683434</v>
       </c>
       <c r="D519" t="n">
-        <v>9.301734544438801</v>
+        <v>9.301733598427894</v>
       </c>
       <c r="E519" t="n">
-        <v>9.326851030756055</v>
+        <v>9.326850082190736</v>
       </c>
       <c r="F519" t="n">
         <v>104401</v>
@@ -10812,16 +10812,16 @@
         <v>45075</v>
       </c>
       <c r="B520" t="n">
-        <v>9.43569278717041</v>
+        <v>9.435691833496094</v>
       </c>
       <c r="C520" t="n">
-        <v>9.502671768374364</v>
+        <v>9.50267080793042</v>
       </c>
       <c r="D520" t="n">
-        <v>9.368713805966456</v>
+        <v>9.368712859061768</v>
       </c>
       <c r="E520" t="n">
-        <v>9.460810115414327</v>
+        <v>9.460809159201379</v>
       </c>
       <c r="F520" t="n">
         <v>106087</v>
@@ -10832,16 +10832,16 @@
         <v>45076</v>
       </c>
       <c r="B521" t="n">
-        <v>9.209638595581055</v>
+        <v>9.209637641906738</v>
       </c>
       <c r="C521" t="n">
-        <v>9.544533504519595</v>
+        <v>9.544532516166321</v>
       </c>
       <c r="D521" t="n">
-        <v>9.151030935054633</v>
+        <v>9.151029987449244</v>
       </c>
       <c r="E521" t="n">
-        <v>9.544533504519595</v>
+        <v>9.544532516166321</v>
       </c>
       <c r="F521" t="n">
         <v>214913</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.16777515411377</v>
+        <v>9.167776107788086</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226381967416739</v>
+        <v>9.226382927187608</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109168340810799</v>
+        <v>9.109169288388564</v>
       </c>
       <c r="E528" t="n">
-        <v>9.209637644284264</v>
+        <v>9.20963860231331</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -11052,16 +11052,16 @@
         <v>45092</v>
       </c>
       <c r="B532" t="n">
-        <v>9.201265335083008</v>
+        <v>9.201264381408691</v>
       </c>
       <c r="C532" t="n">
-        <v>9.251499990606119</v>
+        <v>9.251499031725182</v>
       </c>
       <c r="D532" t="n">
-        <v>9.092423861839507</v>
+        <v>9.092422919446173</v>
       </c>
       <c r="E532" t="n">
-        <v>9.125914192968059</v>
+        <v>9.125913247103586</v>
       </c>
       <c r="F532" t="n">
         <v>477550</v>
@@ -11072,16 +11072,16 @@
         <v>45093</v>
       </c>
       <c r="B533" t="n">
-        <v>9.159403800964355</v>
+        <v>9.159402847290039</v>
       </c>
       <c r="C533" t="n">
-        <v>9.234754944050357</v>
+        <v>9.234753982530503</v>
       </c>
       <c r="D533" t="n">
-        <v>9.075679654403453</v>
+        <v>9.075678709446471</v>
       </c>
       <c r="E533" t="n">
-        <v>9.218010619440014</v>
+        <v>9.218009659663574</v>
       </c>
       <c r="F533" t="n">
         <v>202060</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.991955757141113</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="C535" t="n">
-        <v>8.991955757141113</v>
+        <v>8.991954803466797</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899859445721704</v>
+        <v>8.899858501814995</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983583594603827</v>
+        <v>8.983582641817451</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11132,16 +11132,16 @@
         <v>45098</v>
       </c>
       <c r="B536" t="n">
-        <v>9.000327110290527</v>
+        <v>9.000328063964844</v>
       </c>
       <c r="C536" t="n">
-        <v>9.042189601551824</v>
+        <v>9.042190559661888</v>
       </c>
       <c r="D536" t="n">
-        <v>8.857996995277212</v>
+        <v>8.857997933870235</v>
       </c>
       <c r="E536" t="n">
-        <v>9.033817439767434</v>
+        <v>9.033818396990386</v>
       </c>
       <c r="F536" t="n">
         <v>259897</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950093269348145</v>
+        <v>8.950094223022461</v>
       </c>
       <c r="C537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.000328040087979</v>
       </c>
       <c r="D537" t="n">
-        <v>8.83287964006866</v>
+        <v>8.832880581253315</v>
       </c>
       <c r="E537" t="n">
-        <v>9.000327081061014</v>
+        <v>9.000328040087979</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11172,16 +11172,16 @@
         <v>45100</v>
       </c>
       <c r="B538" t="n">
-        <v>8.983582496643066</v>
+        <v>8.983583450317383</v>
       </c>
       <c r="C538" t="n">
-        <v>9.008699822354874</v>
+        <v>9.008700778695582</v>
       </c>
       <c r="D538" t="n">
-        <v>8.874741032281783</v>
+        <v>8.874741974401767</v>
       </c>
       <c r="E538" t="n">
-        <v>8.89985835799359</v>
+        <v>8.899859302779966</v>
       </c>
       <c r="F538" t="n">
         <v>372938</v>
@@ -11252,16 +11252,16 @@
         <v>45106</v>
       </c>
       <c r="B542" t="n">
-        <v>8.782644271850586</v>
+        <v>8.782646179199219</v>
       </c>
       <c r="C542" t="n">
-        <v>8.849624083961778</v>
+        <v>8.849626005856582</v>
       </c>
       <c r="D542" t="n">
-        <v>8.615196003327013</v>
+        <v>8.615197874310489</v>
       </c>
       <c r="E542" t="n">
-        <v>8.665430652118006</v>
+        <v>8.665432534011066</v>
       </c>
       <c r="F542" t="n">
         <v>269063</v>
@@ -11312,16 +11312,16 @@
         <v>45111</v>
       </c>
       <c r="B545" t="n">
-        <v>9.586395263671875</v>
+        <v>9.586396217346191</v>
       </c>
       <c r="C545" t="n">
-        <v>9.5947674254607</v>
+        <v>9.594768379967897</v>
       </c>
       <c r="D545" t="n">
-        <v>9.318478515902356</v>
+        <v>9.318479442923763</v>
       </c>
       <c r="E545" t="n">
-        <v>9.335222839480007</v>
+        <v>9.335223768167175</v>
       </c>
       <c r="F545" t="n">
         <v>135795</v>
@@ -11332,16 +11332,16 @@
         <v>45112</v>
       </c>
       <c r="B546" t="n">
-        <v>9.695236206054688</v>
+        <v>9.695237159729004</v>
       </c>
       <c r="C546" t="n">
-        <v>9.753843017738918</v>
+        <v>9.753843977178107</v>
       </c>
       <c r="D546" t="n">
-        <v>9.511042768497374</v>
+        <v>9.511043704053456</v>
       </c>
       <c r="E546" t="n">
-        <v>9.611512069195841</v>
+        <v>9.611513014634612</v>
       </c>
       <c r="F546" t="n">
         <v>192684</v>
@@ -11372,16 +11372,16 @@
         <v>45114</v>
       </c>
       <c r="B548" t="n">
-        <v>9.628256797790527</v>
+        <v>9.628255844116211</v>
       </c>
       <c r="C548" t="n">
-        <v>9.695236614803234</v>
+        <v>9.695235654494597</v>
       </c>
       <c r="D548" t="n">
-        <v>9.444064193637333</v>
+        <v>9.444063258207208</v>
       </c>
       <c r="E548" t="n">
-        <v>9.444064193637333</v>
+        <v>9.444063258207208</v>
       </c>
       <c r="F548" t="n">
         <v>257790</v>
@@ -11412,16 +11412,16 @@
         <v>45118</v>
       </c>
       <c r="B550" t="n">
-        <v>9.703607559204102</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="C550" t="n">
-        <v>9.703607559204102</v>
+        <v>9.703609466552734</v>
       </c>
       <c r="D550" t="n">
-        <v>9.38545704327581</v>
+        <v>9.385458888088531</v>
       </c>
       <c r="E550" t="n">
-        <v>9.619883429318397</v>
+        <v>9.61988532021015</v>
       </c>
       <c r="F550" t="n">
         <v>205116</v>
@@ -11452,16 +11452,16 @@
         <v>45120</v>
       </c>
       <c r="B552" t="n">
-        <v>9.636629104614258</v>
+        <v>9.636630058288574</v>
       </c>
       <c r="C552" t="n">
-        <v>9.879429367748973</v>
+        <v>9.879430345451647</v>
       </c>
       <c r="D552" t="n">
-        <v>9.611512619172093</v>
+        <v>9.611513570360794</v>
       </c>
       <c r="E552" t="n">
-        <v>9.879429367748973</v>
+        <v>9.879430345451647</v>
       </c>
       <c r="F552" t="n">
         <v>274014</v>
@@ -11472,16 +11472,16 @@
         <v>45121</v>
       </c>
       <c r="B553" t="n">
-        <v>9.460809707641602</v>
+        <v>9.460808753967285</v>
       </c>
       <c r="C553" t="n">
-        <v>9.720353458912697</v>
+        <v>9.720352479075693</v>
       </c>
       <c r="D553" t="n">
-        <v>9.444064542477484</v>
+        <v>9.444063590491124</v>
       </c>
       <c r="E553" t="n">
-        <v>9.686863969754159</v>
+        <v>9.686862993292984</v>
       </c>
       <c r="F553" t="n">
         <v>130739</v>
@@ -11492,16 +11492,16 @@
         <v>45124</v>
       </c>
       <c r="B554" t="n">
-        <v>9.37708568572998</v>
+        <v>9.377084732055664</v>
       </c>
       <c r="C554" t="n">
-        <v>9.578023464455972</v>
+        <v>9.578022490345754</v>
       </c>
       <c r="D554" t="n">
-        <v>9.259872051570627</v>
+        <v>9.259871109817247</v>
       </c>
       <c r="E554" t="n">
-        <v>9.469181992402371</v>
+        <v>9.469181029361618</v>
       </c>
       <c r="F554" t="n">
         <v>232190</v>
@@ -11512,16 +11512,16 @@
         <v>45125</v>
       </c>
       <c r="B555" t="n">
-        <v>9.795705795288086</v>
+        <v>9.79570484161377</v>
       </c>
       <c r="C555" t="n">
-        <v>9.83756828913018</v>
+        <v>9.837567331380283</v>
       </c>
       <c r="D555" t="n">
-        <v>9.310106923141838</v>
+        <v>9.310106016743662</v>
       </c>
       <c r="E555" t="n">
-        <v>9.469182212700503</v>
+        <v>9.469181290815333</v>
       </c>
       <c r="F555" t="n">
         <v>306673</v>
@@ -11532,16 +11532,16 @@
         <v>45126</v>
       </c>
       <c r="B556" t="n">
-        <v>9.594767570495605</v>
+        <v>9.594766616821289</v>
       </c>
       <c r="C556" t="n">
-        <v>9.854312160399585</v>
+        <v>9.85431118092777</v>
       </c>
       <c r="D556" t="n">
-        <v>9.469181777086149</v>
+        <v>9.469180835894464</v>
       </c>
       <c r="E556" t="n">
-        <v>9.854312160399585</v>
+        <v>9.85431118092777</v>
       </c>
       <c r="F556" t="n">
         <v>152546</v>
@@ -11552,16 +11552,16 @@
         <v>45127</v>
       </c>
       <c r="B557" t="n">
-        <v>9.519415855407715</v>
+        <v>9.519416809082031</v>
       </c>
       <c r="C557" t="n">
-        <v>9.628256477236604</v>
+        <v>9.628257441814794</v>
       </c>
       <c r="D557" t="n">
-        <v>9.49429853001039</v>
+        <v>9.494299481168403</v>
       </c>
       <c r="E557" t="n">
-        <v>9.628256477236604</v>
+        <v>9.628257441814794</v>
       </c>
       <c r="F557" t="n">
         <v>109247</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921292304992676</v>
+        <v>9.921291351318359</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711981520878043</v>
+        <v>9.711980587323517</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753844014168855</v>
+        <v>9.753843076590339</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11612,16 +11612,16 @@
         <v>45132</v>
       </c>
       <c r="B560" t="n">
-        <v>9.770587921142578</v>
+        <v>9.770586967468262</v>
       </c>
       <c r="C560" t="n">
-        <v>10.04687683214587</v>
+        <v>10.04687585150392</v>
       </c>
       <c r="D560" t="n">
-        <v>9.661747293809594</v>
+        <v>9.661746350758847</v>
       </c>
       <c r="E560" t="n">
-        <v>9.92129188114766</v>
+        <v>9.921290912763636</v>
       </c>
       <c r="F560" t="n">
         <v>194370</v>
@@ -11632,16 +11632,16 @@
         <v>45133</v>
       </c>
       <c r="B561" t="n">
-        <v>9.54453182220459</v>
+        <v>9.544532775878906</v>
       </c>
       <c r="C561" t="n">
-        <v>9.820821545427227</v>
+        <v>9.820822526707969</v>
       </c>
       <c r="D561" t="n">
-        <v>9.460808530311857</v>
+        <v>9.460809475620675</v>
       </c>
       <c r="E561" t="n">
-        <v>9.820821545427227</v>
+        <v>9.820822526707969</v>
       </c>
       <c r="F561" t="n">
         <v>168665</v>
@@ -11672,16 +11672,16 @@
         <v>45135</v>
       </c>
       <c r="B563" t="n">
-        <v>9.527787208557129</v>
+        <v>9.527789115905762</v>
       </c>
       <c r="C563" t="n">
-        <v>9.795703921451324</v>
+        <v>9.795705882433666</v>
       </c>
       <c r="D563" t="n">
-        <v>9.511042045989557</v>
+        <v>9.511043949986009</v>
       </c>
       <c r="E563" t="n">
-        <v>9.795703921451324</v>
+        <v>9.795705882433666</v>
       </c>
       <c r="F563" t="n">
         <v>123785</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728725433349609</v>
+        <v>9.728724479675293</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795705251545078</v>
+        <v>9.795704291304954</v>
       </c>
       <c r="D564" t="n">
-        <v>9.544532825943854</v>
+        <v>9.54453189032532</v>
       </c>
       <c r="E564" t="n">
-        <v>9.544532825943854</v>
+        <v>9.54453189032532</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11732,16 +11732,16 @@
         <v>45140</v>
       </c>
       <c r="B566" t="n">
-        <v>9.795705795288086</v>
+        <v>9.79570484161377</v>
       </c>
       <c r="C566" t="n">
-        <v>9.887802104103073</v>
+        <v>9.887801141462594</v>
       </c>
       <c r="D566" t="n">
-        <v>9.69523732417257</v>
+        <v>9.6952363802795</v>
       </c>
       <c r="E566" t="n">
-        <v>9.770588467216776</v>
+        <v>9.77058751598779</v>
       </c>
       <c r="F566" t="n">
         <v>111986</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578022003173828</v>
+        <v>9.578023910522461</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695235619450347</v>
+        <v>9.695237550140671</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469180547725751</v>
+        <v>9.469182433399908</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686862617452325</v>
+        <v>9.686864546475267</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11892,16 +11892,16 @@
         <v>45152</v>
       </c>
       <c r="B574" t="n">
-        <v>10.74178600311279</v>
+        <v>10.74178695678711</v>
       </c>
       <c r="C574" t="n">
-        <v>10.88411611299378</v>
+        <v>10.88411707930441</v>
       </c>
       <c r="D574" t="n">
-        <v>10.23106985279666</v>
+        <v>10.23107076112871</v>
       </c>
       <c r="E574" t="n">
-        <v>10.45712494218117</v>
+        <v>10.45712587058279</v>
       </c>
       <c r="F574" t="n">
         <v>441415</v>
@@ -11912,16 +11912,16 @@
         <v>45153</v>
       </c>
       <c r="B575" t="n">
-        <v>11.10179996490479</v>
+        <v>11.10179901123047</v>
       </c>
       <c r="C575" t="n">
-        <v>11.10179996490479</v>
+        <v>11.10179901123047</v>
       </c>
       <c r="D575" t="n">
-        <v>10.54084995783585</v>
+        <v>10.54084905234865</v>
       </c>
       <c r="E575" t="n">
-        <v>10.72504257279906</v>
+        <v>10.72504165148921</v>
       </c>
       <c r="F575" t="n">
         <v>301089</v>
@@ -11932,16 +11932,16 @@
         <v>45154</v>
       </c>
       <c r="B576" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="C576" t="n">
-        <v>11.26087395777899</v>
+        <v>11.2608749384303</v>
       </c>
       <c r="D576" t="n">
-        <v>10.78364730969746</v>
+        <v>10.78364824878957</v>
       </c>
       <c r="E576" t="n">
-        <v>11.05993620038423</v>
+        <v>11.05993716353692</v>
       </c>
       <c r="F576" t="n">
         <v>525379</v>
@@ -11972,16 +11972,16 @@
         <v>45156</v>
       </c>
       <c r="B578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="C578" t="n">
-        <v>11.38646221160889</v>
+        <v>11.38646125793457</v>
       </c>
       <c r="D578" t="n">
-        <v>10.77527669072958</v>
+        <v>10.77527578824517</v>
       </c>
       <c r="E578" t="n">
-        <v>11.09342811537701</v>
+        <v>11.0934271862458</v>
       </c>
       <c r="F578" t="n">
         <v>450370</v>
@@ -12012,16 +12012,16 @@
         <v>45160</v>
       </c>
       <c r="B580" t="n">
-        <v>11.53716468811035</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="C580" t="n">
-        <v>11.53716468811035</v>
+        <v>11.53716373443604</v>
       </c>
       <c r="D580" t="n">
-        <v>11.10180045903246</v>
+        <v>11.10179954134582</v>
       </c>
       <c r="E580" t="n">
-        <v>11.16877944178756</v>
+        <v>11.16877851856436</v>
       </c>
       <c r="F580" t="n">
         <v>225343</v>
@@ -12032,16 +12032,16 @@
         <v>45161</v>
       </c>
       <c r="B581" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="C581" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="D581" t="n">
-        <v>11.31948165818213</v>
+        <v>11.3194807332412</v>
       </c>
       <c r="E581" t="n">
-        <v>11.47018477777884</v>
+        <v>11.47018384052361</v>
       </c>
       <c r="F581" t="n">
         <v>383262</v>
@@ -12052,16 +12052,16 @@
         <v>45162</v>
       </c>
       <c r="B582" t="n">
-        <v>11.75484561920166</v>
+        <v>11.75484657287598</v>
       </c>
       <c r="C582" t="n">
-        <v>11.75484561920166</v>
+        <v>11.75484657287598</v>
       </c>
       <c r="D582" t="n">
-        <v>11.51204537648651</v>
+        <v>11.51204631046236</v>
       </c>
       <c r="E582" t="n">
-        <v>11.62088683559435</v>
+        <v>11.62088777840055</v>
       </c>
       <c r="F582" t="n">
         <v>205326</v>
@@ -12072,16 +12072,16 @@
         <v>45163</v>
       </c>
       <c r="B583" t="n">
-        <v>11.67112255096436</v>
+        <v>11.67112159729004</v>
       </c>
       <c r="C583" t="n">
-        <v>11.74647453134756</v>
+        <v>11.74647357151606</v>
       </c>
       <c r="D583" t="n">
-        <v>11.55390892003695</v>
+        <v>11.55390797594043</v>
       </c>
       <c r="E583" t="n">
-        <v>11.74647453134756</v>
+        <v>11.74647357151606</v>
       </c>
       <c r="F583" t="n">
         <v>173405</v>
@@ -12152,16 +12152,16 @@
         <v>45169</v>
       </c>
       <c r="B587" t="n">
-        <v>12.26556301116943</v>
+        <v>12.26556205749512</v>
       </c>
       <c r="C587" t="n">
-        <v>12.39114880544301</v>
+        <v>12.39114784200412</v>
       </c>
       <c r="D587" t="n">
-        <v>12.08136955957587</v>
+        <v>12.081368620223</v>
       </c>
       <c r="E587" t="n">
-        <v>12.37440448149703</v>
+        <v>12.37440351936005</v>
       </c>
       <c r="F587" t="n">
         <v>308253</v>
@@ -12172,16 +12172,16 @@
         <v>45170</v>
       </c>
       <c r="B588" t="n">
-        <v>12.12323188781738</v>
+        <v>12.1232328414917</v>
       </c>
       <c r="C588" t="n">
-        <v>12.26556284528164</v>
+        <v>12.26556381015243</v>
       </c>
       <c r="D588" t="n">
-        <v>12.10648756409787</v>
+        <v>12.10648851645499</v>
       </c>
       <c r="E588" t="n">
-        <v>12.15672137642609</v>
+        <v>12.15672233273486</v>
       </c>
       <c r="F588" t="n">
         <v>195423</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625227825024</v>
+        <v>12.05625325429223</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66274975627503</v>
+        <v>11.66275070046011</v>
       </c>
       <c r="E589" t="n">
-        <v>11.9976454659665</v>
+        <v>11.99764643726385</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461082458496</v>
+        <v>11.70461273193359</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80507928016331</v>
+        <v>11.80508120388398</v>
       </c>
       <c r="D590" t="n">
-        <v>11.59576936683122</v>
+        <v>11.59577125644338</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996195597632</v>
+        <v>11.77996387560395</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996253967285</v>
+        <v>11.77996349334717</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879096769665</v>
+        <v>11.52879190103679</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903865368277</v>
+        <v>11.93903962023547</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12292,16 +12292,16 @@
         <v>45181</v>
       </c>
       <c r="B594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="C594" t="n">
-        <v>12.27393627166748</v>
+        <v>12.27393531799316</v>
       </c>
       <c r="D594" t="n">
-        <v>11.71298458432168</v>
+        <v>11.71298367423283</v>
       </c>
       <c r="E594" t="n">
-        <v>11.72135758763992</v>
+        <v>11.72135667690049</v>
       </c>
       <c r="F594" t="n">
         <v>228714</v>
@@ -12332,16 +12332,16 @@
         <v>45183</v>
       </c>
       <c r="B596" t="n">
-        <v>12.34091472625732</v>
+        <v>12.34091377258301</v>
       </c>
       <c r="C596" t="n">
-        <v>12.51673518290008</v>
+        <v>12.51673421563881</v>
       </c>
       <c r="D596" t="n">
-        <v>12.26556358265027</v>
+        <v>12.2655626347989</v>
       </c>
       <c r="E596" t="n">
-        <v>12.47487352991503</v>
+        <v>12.47487256588872</v>
       </c>
       <c r="F596" t="n">
         <v>207012</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461082458496</v>
+        <v>11.70461273193359</v>
       </c>
       <c r="C599" t="n">
-        <v>11.86368608954307</v>
+        <v>11.86368802281414</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414152783702</v>
+        <v>11.60414341881347</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786566140377</v>
+        <v>11.68786756602366</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12472,16 +12472,16 @@
         <v>45194</v>
       </c>
       <c r="B603" t="n">
-        <v>11.11854457855225</v>
+        <v>11.11854553222656</v>
       </c>
       <c r="C603" t="n">
-        <v>11.54553660487908</v>
+        <v>11.54553759517791</v>
       </c>
       <c r="D603" t="n">
-        <v>11.10179941385507</v>
+        <v>11.10180036609309</v>
       </c>
       <c r="E603" t="n">
-        <v>11.54553660487908</v>
+        <v>11.54553759517791</v>
       </c>
       <c r="F603" t="n">
         <v>266745</v>
@@ -12512,16 +12512,16 @@
         <v>45196</v>
       </c>
       <c r="B605" t="n">
-        <v>10.7669038772583</v>
+        <v>10.76690483093262</v>
       </c>
       <c r="C605" t="n">
-        <v>11.12691693338246</v>
+        <v>11.12691791894479</v>
       </c>
       <c r="D605" t="n">
-        <v>10.63294592203521</v>
+        <v>10.63294686384426</v>
       </c>
       <c r="E605" t="n">
-        <v>11.09342744457668</v>
+        <v>11.0934284271727</v>
       </c>
       <c r="F605" t="n">
         <v>269906</v>
@@ -12532,16 +12532,16 @@
         <v>45197</v>
       </c>
       <c r="B606" t="n">
-        <v>11.10179996490479</v>
+        <v>11.10179901123047</v>
       </c>
       <c r="C606" t="n">
-        <v>11.18552411020707</v>
+        <v>11.18552314934063</v>
       </c>
       <c r="D606" t="n">
-        <v>10.66643491403472</v>
+        <v>10.66643399775942</v>
       </c>
       <c r="E606" t="n">
-        <v>10.66643491403472</v>
+        <v>10.66643399775942</v>
       </c>
       <c r="F606" t="n">
         <v>215545</v>
@@ -12552,16 +12552,16 @@
         <v>45198</v>
       </c>
       <c r="B607" t="n">
-        <v>11.11854457855225</v>
+        <v>11.11854553222656</v>
       </c>
       <c r="C607" t="n">
-        <v>11.41994997257442</v>
+        <v>11.41995095210127</v>
       </c>
       <c r="D607" t="n">
-        <v>11.06830908446071</v>
+        <v>11.06831003382616</v>
       </c>
       <c r="E607" t="n">
-        <v>11.126916740316</v>
+        <v>11.12691769470842</v>
       </c>
       <c r="F607" t="n">
         <v>376204</v>
@@ -12672,16 +12672,16 @@
         <v>45208</v>
       </c>
       <c r="B613" t="n">
-        <v>10.18920803070068</v>
+        <v>10.189208984375</v>
       </c>
       <c r="C613" t="n">
-        <v>10.41526227506603</v>
+        <v>10.41526324989824</v>
       </c>
       <c r="D613" t="n">
-        <v>10.18920803070068</v>
+        <v>10.189208984375</v>
       </c>
       <c r="E613" t="n">
-        <v>10.39851711121656</v>
+        <v>10.39851808448147</v>
       </c>
       <c r="F613" t="n">
         <v>296138</v>
@@ -12692,16 +12692,16 @@
         <v>45209</v>
       </c>
       <c r="B614" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="C614" t="n">
-        <v>10.95109558105469</v>
+        <v>10.951096534729</v>
       </c>
       <c r="D614" t="n">
-        <v>10.15571755386226</v>
+        <v>10.15571843827122</v>
       </c>
       <c r="E614" t="n">
-        <v>10.15571755386226</v>
+        <v>10.15571843827122</v>
       </c>
       <c r="F614" t="n">
         <v>338699</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203380584717</v>
+        <v>11.15203189849854</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203380584717</v>
+        <v>11.15203189849854</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457244623281</v>
+        <v>10.62457062909666</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411704494031</v>
+        <v>10.88411518341387</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691593170166</v>
+        <v>11.12691688537598</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226706443887</v>
+        <v>11.20226802457144</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690290798703</v>
+        <v>10.76690383080508</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970231084856</v>
+        <v>11.00970325447664</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12752,16 +12752,16 @@
         <v>45215</v>
       </c>
       <c r="B617" t="n">
-        <v>11.02644824981689</v>
+        <v>11.02644729614258</v>
       </c>
       <c r="C617" t="n">
-        <v>11.27762069182936</v>
+        <v>11.27761971643121</v>
       </c>
       <c r="D617" t="n">
-        <v>10.95109710603197</v>
+        <v>10.95109615887475</v>
       </c>
       <c r="E617" t="n">
-        <v>11.12691756308977</v>
+        <v>11.1269166007259</v>
       </c>
       <c r="F617" t="n">
         <v>160026</v>
@@ -12792,16 +12792,16 @@
         <v>45217</v>
       </c>
       <c r="B619" t="n">
-        <v>10.24781513214111</v>
+        <v>10.2478141784668</v>
       </c>
       <c r="C619" t="n">
-        <v>10.60782820352242</v>
+        <v>10.60782721634484</v>
       </c>
       <c r="D619" t="n">
-        <v>10.23107080761346</v>
+        <v>10.23106985549739</v>
       </c>
       <c r="E619" t="n">
-        <v>10.57433871329738</v>
+        <v>10.57433772923638</v>
       </c>
       <c r="F619" t="n">
         <v>234192</v>
@@ -12812,16 +12812,16 @@
         <v>45218</v>
       </c>
       <c r="B620" t="n">
-        <v>10.34828281402588</v>
+        <v>10.3482837677002</v>
       </c>
       <c r="C620" t="n">
-        <v>10.4906137675105</v>
+        <v>10.49061473430172</v>
       </c>
       <c r="D620" t="n">
-        <v>10.28130467985089</v>
+        <v>10.28130562735265</v>
       </c>
       <c r="E620" t="n">
-        <v>10.30642116472789</v>
+        <v>10.30642211454433</v>
       </c>
       <c r="F620" t="n">
         <v>130844</v>
@@ -12832,16 +12832,16 @@
         <v>45219</v>
       </c>
       <c r="B621" t="n">
-        <v>10.8757438659668</v>
+        <v>10.87574481964111</v>
       </c>
       <c r="C621" t="n">
-        <v>11.00970265448127</v>
+        <v>11.00970361990219</v>
       </c>
       <c r="D621" t="n">
-        <v>10.27293226174542</v>
+        <v>10.27293316256027</v>
       </c>
       <c r="E621" t="n">
-        <v>10.34828255566484</v>
+        <v>10.34828346308703</v>
       </c>
       <c r="F621" t="n">
         <v>2108154</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295806884766</v>
+        <v>10.99295902252197</v>
       </c>
       <c r="C622" t="n">
-        <v>11.13528902626719</v>
+        <v>11.13528999228917</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039245794601</v>
+        <v>10.80039339491465</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82551062585675</v>
+        <v>10.82551156500447</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12912,16 +12912,16 @@
         <v>45225</v>
       </c>
       <c r="B625" t="n">
-        <v>11.32785320281982</v>
+        <v>11.32785224914551</v>
       </c>
       <c r="C625" t="n">
-        <v>11.63763242817845</v>
+        <v>11.6376314484243</v>
       </c>
       <c r="D625" t="n">
-        <v>11.25250206771208</v>
+        <v>11.25250112038145</v>
       </c>
       <c r="E625" t="n">
-        <v>11.2608742291308</v>
+        <v>11.26087328109533</v>
       </c>
       <c r="F625" t="n">
         <v>344599</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.43200778961182</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668279217249</v>
+        <v>11.07668177956321</v>
       </c>
       <c r="D627" t="n">
-        <v>10.43200778961182</v>
+        <v>10.4320068359375</v>
       </c>
       <c r="E627" t="n">
-        <v>10.9929586456988</v>
+        <v>10.99295764074342</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -12972,16 +12972,16 @@
         <v>45230</v>
       </c>
       <c r="B628" t="n">
-        <v>10.68783950805664</v>
+        <v>10.68783855438232</v>
       </c>
       <c r="C628" t="n">
-        <v>10.70476440977975</v>
+        <v>10.70476345459523</v>
       </c>
       <c r="D628" t="n">
-        <v>10.06163174747778</v>
+        <v>10.06163084967988</v>
       </c>
       <c r="E628" t="n">
-        <v>10.57783062255122</v>
+        <v>10.57782967869298</v>
       </c>
       <c r="F628" t="n">
         <v>335223</v>
@@ -13012,16 +13012,16 @@
         <v>45233</v>
       </c>
       <c r="B630" t="n">
-        <v>11.21250057220459</v>
+        <v>11.21249961853027</v>
       </c>
       <c r="C630" t="n">
-        <v>11.21250057220459</v>
+        <v>11.21249961853027</v>
       </c>
       <c r="D630" t="n">
-        <v>10.68783966372706</v>
+        <v>10.68783875467755</v>
       </c>
       <c r="E630" t="n">
-        <v>10.78938737514776</v>
+        <v>10.78938645746115</v>
       </c>
       <c r="F630" t="n">
         <v>226607</v>
@@ -13032,16 +13032,16 @@
         <v>45236</v>
       </c>
       <c r="B631" t="n">
-        <v>11.18711280822754</v>
+        <v>11.18711185455322</v>
       </c>
       <c r="C631" t="n">
-        <v>11.21250058631318</v>
+        <v>11.21249963047462</v>
       </c>
       <c r="D631" t="n">
-        <v>10.96709503373525</v>
+        <v>10.96709409881691</v>
       </c>
       <c r="E631" t="n">
-        <v>11.19557568432226</v>
+        <v>11.1955747299265</v>
       </c>
       <c r="F631" t="n">
         <v>130949</v>
@@ -13052,16 +13052,16 @@
         <v>45237</v>
       </c>
       <c r="B632" t="n">
-        <v>11.22096252441406</v>
+        <v>11.22096157073975</v>
       </c>
       <c r="C632" t="n">
-        <v>11.50021702859036</v>
+        <v>11.50021605118209</v>
       </c>
       <c r="D632" t="n">
-        <v>10.97555697375624</v>
+        <v>10.97555604093904</v>
       </c>
       <c r="E632" t="n">
-        <v>11.24634945210255</v>
+        <v>11.24634849627058</v>
       </c>
       <c r="F632" t="n">
         <v>179726</v>
@@ -13072,16 +13072,16 @@
         <v>45238</v>
       </c>
       <c r="B633" t="n">
-        <v>11.40713119506836</v>
+        <v>11.40713214874268</v>
       </c>
       <c r="C633" t="n">
-        <v>11.40713119506836</v>
+        <v>11.40713214874268</v>
       </c>
       <c r="D633" t="n">
-        <v>11.0178669883917</v>
+        <v>11.01786790952223</v>
       </c>
       <c r="E633" t="n">
-        <v>11.22096154191832</v>
+        <v>11.22096248002823</v>
       </c>
       <c r="F633" t="n">
         <v>171088</v>
@@ -13132,16 +13132,16 @@
         <v>45243</v>
       </c>
       <c r="B636" t="n">
-        <v>12.36336803436279</v>
+        <v>12.36336708068848</v>
       </c>
       <c r="C636" t="n">
-        <v>12.51568874678828</v>
+        <v>12.51568778136439</v>
       </c>
       <c r="D636" t="n">
-        <v>12.04180170804298</v>
+        <v>12.04180077917336</v>
       </c>
       <c r="E636" t="n">
-        <v>12.1348873908238</v>
+        <v>12.13488645477382</v>
       </c>
       <c r="F636" t="n">
         <v>539496</v>
@@ -13192,16 +13192,16 @@
         <v>45247</v>
       </c>
       <c r="B639" t="n">
-        <v>12.85418033599854</v>
+        <v>12.85417938232422</v>
       </c>
       <c r="C639" t="n">
-        <v>12.85418033599854</v>
+        <v>12.85417938232422</v>
       </c>
       <c r="D639" t="n">
-        <v>12.4818392948031</v>
+        <v>12.48183836875342</v>
       </c>
       <c r="E639" t="n">
-        <v>12.70185876909171</v>
+        <v>12.7018578267184</v>
       </c>
       <c r="F639" t="n">
         <v>197425</v>
@@ -13232,16 +13232,16 @@
         <v>45251</v>
       </c>
       <c r="B641" t="n">
-        <v>12.57492256164551</v>
+        <v>12.57492351531982</v>
       </c>
       <c r="C641" t="n">
-        <v>13.10804542873219</v>
+        <v>13.10804642283821</v>
       </c>
       <c r="D641" t="n">
-        <v>12.41414068931551</v>
+        <v>12.41414163079623</v>
       </c>
       <c r="E641" t="n">
-        <v>12.99803655550682</v>
+        <v>12.99803754126984</v>
       </c>
       <c r="F641" t="n">
         <v>206064</v>
@@ -13352,16 +13352,16 @@
         <v>45259</v>
       </c>
       <c r="B647" t="n">
-        <v>12.93033885955811</v>
+        <v>12.93033790588379</v>
       </c>
       <c r="C647" t="n">
-        <v>13.23498112999133</v>
+        <v>13.23498015384819</v>
       </c>
       <c r="D647" t="n">
-        <v>12.90495278303728</v>
+        <v>12.90495183123531</v>
       </c>
       <c r="E647" t="n">
-        <v>13.20959335307354</v>
+        <v>13.20959237880287</v>
       </c>
       <c r="F647" t="n">
         <v>170772</v>
@@ -13392,16 +13392,16 @@
         <v>45261</v>
       </c>
       <c r="B649" t="n">
-        <v>13.22651958465576</v>
+        <v>13.22651863098145</v>
       </c>
       <c r="C649" t="n">
-        <v>13.35345337266199</v>
+        <v>13.35345240983534</v>
       </c>
       <c r="D649" t="n">
-        <v>12.9895760602716</v>
+        <v>12.98957512368167</v>
       </c>
       <c r="E649" t="n">
-        <v>12.9895760602716</v>
+        <v>12.98957512368167</v>
       </c>
       <c r="F649" t="n">
         <v>156128</v>
@@ -13432,16 +13432,16 @@
         <v>45265</v>
       </c>
       <c r="B651" t="n">
-        <v>12.83725357055664</v>
+        <v>12.83725452423096</v>
       </c>
       <c r="C651" t="n">
-        <v>12.94726414921587</v>
+        <v>12.94726511106283</v>
       </c>
       <c r="D651" t="n">
-        <v>12.73570671749947</v>
+        <v>12.73570766362991</v>
       </c>
       <c r="E651" t="n">
-        <v>12.76109364331337</v>
+        <v>12.7610945913298</v>
       </c>
       <c r="F651" t="n">
         <v>155706</v>
@@ -13472,16 +13472,16 @@
         <v>45267</v>
       </c>
       <c r="B653" t="n">
-        <v>12.51568794250488</v>
+        <v>12.5156888961792</v>
       </c>
       <c r="C653" t="n">
-        <v>12.51568794250488</v>
+        <v>12.5156888961792</v>
       </c>
       <c r="D653" t="n">
-        <v>12.16873471137699</v>
+        <v>12.16873563861405</v>
       </c>
       <c r="E653" t="n">
-        <v>12.16873471137699</v>
+        <v>12.16873563861405</v>
       </c>
       <c r="F653" t="n">
         <v>114831</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495204925537</v>
+        <v>12.90495300292969</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413126845579</v>
+        <v>12.30413217772953</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568784548951</v>
+        <v>12.51568877039725</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960296630859</v>
+        <v>13.31960391998291</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109316972536</v>
+        <v>12.76109408341076</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033791853966</v>
+        <v>12.93033884434287</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13612,16 +13612,16 @@
         <v>45278</v>
       </c>
       <c r="B660" t="n">
-        <v>13.1672830581665</v>
+        <v>13.16728210449219</v>
       </c>
       <c r="C660" t="n">
-        <v>13.66655704234154</v>
+        <v>13.66655605250602</v>
       </c>
       <c r="D660" t="n">
-        <v>13.15882103222074</v>
+        <v>13.15882007915931</v>
       </c>
       <c r="E660" t="n">
-        <v>13.26883077030978</v>
+        <v>13.26882980928061</v>
       </c>
       <c r="F660" t="n">
         <v>541076</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45500087738037</v>
+        <v>13.45499897003174</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040643933103</v>
+        <v>13.70040449719429</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806708329535</v>
+        <v>13.32806519394055</v>
       </c>
       <c r="E662" t="n">
-        <v>13.38730211702961</v>
+        <v>13.38730021927779</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13692,16 +13692,16 @@
         <v>45282</v>
       </c>
       <c r="B664" t="n">
-        <v>13.88704776763916</v>
+        <v>13.88704872131348</v>
       </c>
       <c r="C664" t="n">
-        <v>14.31516532026503</v>
+        <v>14.31516630333975</v>
       </c>
       <c r="D664" t="n">
-        <v>13.74434251416193</v>
+        <v>13.74434345803615</v>
       </c>
       <c r="E664" t="n">
-        <v>13.89596662195722</v>
+        <v>13.89596757624402</v>
       </c>
       <c r="F664" t="n">
         <v>242936</v>
@@ -13712,16 +13712,16 @@
         <v>45286</v>
       </c>
       <c r="B665" t="n">
-        <v>14.1813793182373</v>
+        <v>14.18137836456299</v>
       </c>
       <c r="C665" t="n">
-        <v>14.1813793182373</v>
+        <v>14.18137836456299</v>
       </c>
       <c r="D665" t="n">
-        <v>13.77110033293046</v>
+        <v>13.77109940684673</v>
       </c>
       <c r="E665" t="n">
-        <v>13.88704903402712</v>
+        <v>13.88704810014603</v>
       </c>
       <c r="F665" t="n">
         <v>187522</v>
@@ -13732,16 +13732,16 @@
         <v>45287</v>
       </c>
       <c r="B666" t="n">
-        <v>14.54706192016602</v>
+        <v>14.54706287384033</v>
       </c>
       <c r="C666" t="n">
-        <v>14.54706192016602</v>
+        <v>14.54706287384033</v>
       </c>
       <c r="D666" t="n">
-        <v>13.89596673176415</v>
+        <v>13.89596764275405</v>
       </c>
       <c r="E666" t="n">
-        <v>14.18137813707104</v>
+        <v>14.18137906677191</v>
       </c>
       <c r="F666" t="n">
         <v>258949</v>
@@ -13772,16 +13772,16 @@
         <v>45293</v>
       </c>
       <c r="B668" t="n">
-        <v>14.08326721191406</v>
+        <v>14.0832691192627</v>
       </c>
       <c r="C668" t="n">
-        <v>14.57381761552982</v>
+        <v>14.5738195893155</v>
       </c>
       <c r="D668" t="n">
-        <v>13.94056196580658</v>
+        <v>13.94056385382812</v>
       </c>
       <c r="E668" t="n">
-        <v>14.27056851950291</v>
+        <v>14.27057045221845</v>
       </c>
       <c r="F668" t="n">
         <v>272434</v>
@@ -13792,16 +13792,16 @@
         <v>45294</v>
       </c>
       <c r="B669" t="n">
-        <v>14.23489284515381</v>
+        <v>14.23489379882812</v>
       </c>
       <c r="C669" t="n">
-        <v>14.35976038913565</v>
+        <v>14.35976135117554</v>
       </c>
       <c r="D669" t="n">
-        <v>13.64623233446546</v>
+        <v>13.64623324870215</v>
       </c>
       <c r="E669" t="n">
-        <v>13.92272308910211</v>
+        <v>13.92272402186245</v>
       </c>
       <c r="F669" t="n">
         <v>120520</v>
@@ -13812,16 +13812,16 @@
         <v>45295</v>
       </c>
       <c r="B670" t="n">
-        <v>13.98515796661377</v>
+        <v>13.98515892028809</v>
       </c>
       <c r="C670" t="n">
-        <v>14.35084085368154</v>
+        <v>14.35084183229246</v>
       </c>
       <c r="D670" t="n">
-        <v>13.83353385759136</v>
+        <v>13.83353480092614</v>
       </c>
       <c r="E670" t="n">
-        <v>14.26165051758498</v>
+        <v>14.26165149011384</v>
       </c>
       <c r="F670" t="n">
         <v>190472</v>
@@ -13832,16 +13832,16 @@
         <v>45296</v>
       </c>
       <c r="B671" t="n">
-        <v>13.96731948852539</v>
+        <v>13.96731853485107</v>
       </c>
       <c r="C671" t="n">
-        <v>14.27056950151718</v>
+        <v>14.27056852713726</v>
       </c>
       <c r="D671" t="n">
-        <v>13.8692094010509</v>
+        <v>13.86920845407544</v>
       </c>
       <c r="E671" t="n">
-        <v>13.97623923909369</v>
+        <v>13.97623828481034</v>
       </c>
       <c r="F671" t="n">
         <v>90074</v>
@@ -13872,16 +13872,16 @@
         <v>45300</v>
       </c>
       <c r="B673" t="n">
-        <v>14.1813793182373</v>
+        <v>14.18137836456299</v>
       </c>
       <c r="C673" t="n">
-        <v>14.1813793182373</v>
+        <v>14.18137836456299</v>
       </c>
       <c r="D673" t="n">
-        <v>13.61055646007971</v>
+        <v>13.61055554479229</v>
       </c>
       <c r="E673" t="n">
-        <v>13.78001918806184</v>
+        <v>13.78001826137833</v>
       </c>
       <c r="F673" t="n">
         <v>115358</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623920440674</v>
+        <v>13.97623825073242</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461330219005</v>
+        <v>13.82461235886199</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597429775732</v>
+        <v>14.22597332704223</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13972,16 +13972,16 @@
         <v>45307</v>
       </c>
       <c r="B678" t="n">
-        <v>14.31516647338867</v>
+        <v>14.31516551971436</v>
       </c>
       <c r="C678" t="n">
-        <v>14.44003313219104</v>
+        <v>14.44003217019812</v>
       </c>
       <c r="D678" t="n">
-        <v>14.13678399607587</v>
+        <v>14.13678305428537</v>
       </c>
       <c r="E678" t="n">
-        <v>14.34192303849815</v>
+        <v>14.34192208304131</v>
       </c>
       <c r="F678" t="n">
         <v>181728</v>
@@ -13992,16 +13992,16 @@
         <v>45308</v>
       </c>
       <c r="B679" t="n">
-        <v>14.37759876251221</v>
+        <v>14.37759780883789</v>
       </c>
       <c r="C679" t="n">
-        <v>14.52922377237277</v>
+        <v>14.52922280864108</v>
       </c>
       <c r="D679" t="n">
-        <v>14.243812358087</v>
+        <v>14.24381141328681</v>
       </c>
       <c r="E679" t="n">
-        <v>14.3240847384004</v>
+        <v>14.3240837882757</v>
       </c>
       <c r="F679" t="n">
         <v>153283</v>
@@ -14052,16 +14052,16 @@
         <v>45313</v>
       </c>
       <c r="B682" t="n">
-        <v>14.52922439575195</v>
+        <v>14.52922344207764</v>
       </c>
       <c r="C682" t="n">
-        <v>14.7967981121798</v>
+        <v>14.79679714094238</v>
       </c>
       <c r="D682" t="n">
-        <v>14.27948928552483</v>
+        <v>14.27948834824271</v>
       </c>
       <c r="E682" t="n">
-        <v>14.60949677950945</v>
+        <v>14.60949582056619</v>
       </c>
       <c r="F682" t="n">
         <v>189524</v>
@@ -14112,16 +14112,16 @@
         <v>45316</v>
       </c>
       <c r="B685" t="n">
-        <v>14.57381916046143</v>
+        <v>14.57381820678711</v>
       </c>
       <c r="C685" t="n">
-        <v>14.77003934270851</v>
+        <v>14.77003837619403</v>
       </c>
       <c r="D685" t="n">
-        <v>14.46679021453496</v>
+        <v>14.46678926786436</v>
       </c>
       <c r="E685" t="n">
-        <v>14.60949637186738</v>
+        <v>14.60949541585844</v>
       </c>
       <c r="F685" t="n">
         <v>152967</v>
@@ -14232,16 +14232,16 @@
         <v>45324</v>
       </c>
       <c r="B691" t="n">
-        <v>13.76218128204346</v>
+        <v>13.76218032836914</v>
       </c>
       <c r="C691" t="n">
-        <v>13.76218128204346</v>
+        <v>13.76218032836914</v>
       </c>
       <c r="D691" t="n">
-        <v>13.28946852534654</v>
+        <v>13.28946760442967</v>
       </c>
       <c r="E691" t="n">
-        <v>13.70866635982202</v>
+        <v>13.70866540985612</v>
       </c>
       <c r="F691" t="n">
         <v>554139</v>
@@ -14272,16 +14272,16 @@
         <v>45328</v>
       </c>
       <c r="B693" t="n">
-        <v>13.41433620452881</v>
+        <v>13.41433429718018</v>
       </c>
       <c r="C693" t="n">
-        <v>13.47676998233529</v>
+        <v>13.47676806610936</v>
       </c>
       <c r="D693" t="n">
-        <v>13.0843296053215</v>
+        <v>13.08432774489562</v>
       </c>
       <c r="E693" t="n">
-        <v>13.20027740974985</v>
+        <v>13.20027553283766</v>
       </c>
       <c r="F693" t="n">
         <v>1178021</v>
@@ -14292,16 +14292,16 @@
         <v>45329</v>
       </c>
       <c r="B694" t="n">
-        <v>14.1813793182373</v>
+        <v>14.18137836456299</v>
       </c>
       <c r="C694" t="n">
-        <v>14.25273195148271</v>
+        <v>14.25273099301005</v>
       </c>
       <c r="D694" t="n">
-        <v>13.51244636534298</v>
+        <v>13.5124454566533</v>
       </c>
       <c r="E694" t="n">
-        <v>13.60163760494833</v>
+        <v>13.60163669026068</v>
       </c>
       <c r="F694" t="n">
         <v>562778</v>
@@ -14332,16 +14332,16 @@
         <v>45331</v>
       </c>
       <c r="B696" t="n">
-        <v>13.86920833587646</v>
+        <v>13.86920928955078</v>
       </c>
       <c r="C696" t="n">
-        <v>13.86920833587646</v>
+        <v>13.86920928955078</v>
       </c>
       <c r="D696" t="n">
-        <v>13.49460572369088</v>
+        <v>13.49460665160678</v>
       </c>
       <c r="E696" t="n">
-        <v>13.74434169457831</v>
+        <v>13.74434263966654</v>
       </c>
       <c r="F696" t="n">
         <v>146541</v>
@@ -14392,16 +14392,16 @@
         <v>45338</v>
       </c>
       <c r="B699" t="n">
-        <v>13.88704776763916</v>
+        <v>13.88704872131348</v>
       </c>
       <c r="C699" t="n">
-        <v>14.12786400300335</v>
+        <v>14.1278649732154</v>
       </c>
       <c r="D699" t="n">
-        <v>13.29838635680286</v>
+        <v>13.29838727005164</v>
       </c>
       <c r="E699" t="n">
-        <v>13.51244513311579</v>
+        <v>13.51244606106478</v>
       </c>
       <c r="F699" t="n">
         <v>253260</v>
@@ -14692,16 +14692,16 @@
         <v>45359</v>
       </c>
       <c r="B714" t="n">
-        <v>13.41433620452881</v>
+        <v>13.41433429718018</v>
       </c>
       <c r="C714" t="n">
-        <v>13.42325505961626</v>
+        <v>13.42325315099948</v>
       </c>
       <c r="D714" t="n">
-        <v>12.96838090479599</v>
+        <v>12.96837906085655</v>
       </c>
       <c r="E714" t="n">
-        <v>13.15568134211827</v>
+        <v>13.15567947154708</v>
       </c>
       <c r="F714" t="n">
         <v>200691</v>
@@ -14712,16 +14712,16 @@
         <v>45362</v>
       </c>
       <c r="B715" t="n">
-        <v>13.7354211807251</v>
+        <v>13.73542213439941</v>
       </c>
       <c r="C715" t="n">
-        <v>13.8692084692905</v>
+        <v>13.86920943225391</v>
       </c>
       <c r="D715" t="n">
-        <v>13.25378963018077</v>
+        <v>13.25379055041456</v>
       </c>
       <c r="E715" t="n">
-        <v>13.42325323033127</v>
+        <v>13.42325416233122</v>
       </c>
       <c r="F715" t="n">
         <v>388635</v>
@@ -14732,16 +14732,16 @@
         <v>45363</v>
       </c>
       <c r="B716" t="n">
-        <v>15.42113399505615</v>
+        <v>15.42113304138184</v>
       </c>
       <c r="C716" t="n">
-        <v>15.98303706065691</v>
+        <v>15.98303607223336</v>
       </c>
       <c r="D716" t="n">
-        <v>13.85137169862826</v>
+        <v>13.85137084203124</v>
       </c>
       <c r="E716" t="n">
-        <v>14.09218704214369</v>
+        <v>14.09218617065416</v>
       </c>
       <c r="F716" t="n">
         <v>1351743</v>
@@ -14752,16 +14752,16 @@
         <v>45364</v>
       </c>
       <c r="B717" t="n">
-        <v>15.79573535919189</v>
+        <v>15.79573631286621</v>
       </c>
       <c r="C717" t="n">
-        <v>15.99195551836995</v>
+        <v>15.99195648389114</v>
       </c>
       <c r="D717" t="n">
-        <v>15.33194241860686</v>
+        <v>15.33194334427948</v>
       </c>
       <c r="E717" t="n">
-        <v>15.33194241860686</v>
+        <v>15.33194334427948</v>
       </c>
       <c r="F717" t="n">
         <v>474916</v>
@@ -14792,16 +14792,16 @@
         <v>45366</v>
       </c>
       <c r="B719" t="n">
-        <v>15.77789974212646</v>
+        <v>15.77789878845215</v>
       </c>
       <c r="C719" t="n">
-        <v>15.8670900836811</v>
+        <v>15.86708912461579</v>
       </c>
       <c r="D719" t="n">
-        <v>15.37653962074202</v>
+        <v>15.37653869132738</v>
       </c>
       <c r="E719" t="n">
-        <v>15.67978964953865</v>
+        <v>15.67978870179447</v>
       </c>
       <c r="F719" t="n">
         <v>999032</v>
@@ -14832,16 +14832,16 @@
         <v>45370</v>
       </c>
       <c r="B721" t="n">
-        <v>16.15250205993652</v>
+        <v>16.15250015258789</v>
       </c>
       <c r="C721" t="n">
-        <v>16.15250205993652</v>
+        <v>16.15250015258789</v>
       </c>
       <c r="D721" t="n">
-        <v>15.61735464537877</v>
+        <v>15.61735280122237</v>
       </c>
       <c r="E721" t="n">
-        <v>15.83141432807958</v>
+        <v>15.8314124586462</v>
       </c>
       <c r="F721" t="n">
         <v>227239</v>
@@ -14852,16 +14852,16 @@
         <v>45371</v>
       </c>
       <c r="B722" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="C722" t="n">
-        <v>16.29520886762698</v>
+        <v>16.2952069476677</v>
       </c>
       <c r="D722" t="n">
-        <v>16.08114916459959</v>
+        <v>16.08114726986159</v>
       </c>
       <c r="E722" t="n">
-        <v>16.15250359373834</v>
+        <v>16.15250169059311</v>
       </c>
       <c r="F722" t="n">
         <v>449422</v>
@@ -14872,16 +14872,16 @@
         <v>45372</v>
       </c>
       <c r="B723" t="n">
-        <v>16.58061981201172</v>
+        <v>16.58061790466309</v>
       </c>
       <c r="C723" t="n">
-        <v>16.58061981201172</v>
+        <v>16.58061790466309</v>
       </c>
       <c r="D723" t="n">
-        <v>16.1168250226195</v>
+        <v>16.11682316862342</v>
       </c>
       <c r="E723" t="n">
-        <v>16.25061232575078</v>
+        <v>16.25061045636449</v>
       </c>
       <c r="F723" t="n">
         <v>298350</v>
@@ -14892,16 +14892,16 @@
         <v>45373</v>
       </c>
       <c r="B724" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="C724" t="n">
-        <v>16.65197205234856</v>
+        <v>16.65197009035419</v>
       </c>
       <c r="D724" t="n">
-        <v>16.18817901611328</v>
+        <v>16.18817710876465</v>
       </c>
       <c r="E724" t="n">
-        <v>16.42007643032814</v>
+        <v>16.42007449565653</v>
       </c>
       <c r="F724" t="n">
         <v>404437</v>
@@ -14952,16 +14952,16 @@
         <v>45378</v>
       </c>
       <c r="B727" t="n">
-        <v>15.4300537109375</v>
+        <v>15.43005466461182</v>
       </c>
       <c r="C727" t="n">
-        <v>15.75114143230092</v>
+        <v>15.75114240582048</v>
       </c>
       <c r="D727" t="n">
-        <v>14.90382606442144</v>
+        <v>14.90382698557158</v>
       </c>
       <c r="E727" t="n">
-        <v>15.23383353633731</v>
+        <v>15.23383447788399</v>
       </c>
       <c r="F727" t="n">
         <v>340806</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196617126465</v>
+        <v>16.32196235656738</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55386179102265</v>
+        <v>16.55385792212777</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26059279475697</v>
+        <v>15.26058922811916</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005552987071</v>
+        <v>15.43005192362683</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -14992,16 +14992,16 @@
         <v>45383</v>
       </c>
       <c r="B729" t="n">
-        <v>16.41115570068359</v>
+        <v>16.41115379333496</v>
       </c>
       <c r="C729" t="n">
-        <v>16.52710350478439</v>
+        <v>16.52710158395999</v>
       </c>
       <c r="D729" t="n">
-        <v>16.06331049618689</v>
+        <v>16.06330862926576</v>
       </c>
       <c r="E729" t="n">
-        <v>16.25061272517437</v>
+        <v>16.25061083648447</v>
       </c>
       <c r="F729" t="n">
         <v>424348</v>
@@ -15052,16 +15052,16 @@
         <v>45386</v>
       </c>
       <c r="B732" t="n">
-        <v>15.83141231536865</v>
+        <v>15.83141326904297</v>
       </c>
       <c r="C732" t="n">
-        <v>16.42007278356858</v>
+        <v>16.42007377270343</v>
       </c>
       <c r="D732" t="n">
-        <v>15.83141231536865</v>
+        <v>15.83141326904297</v>
       </c>
       <c r="E732" t="n">
-        <v>16.10790484224275</v>
+        <v>16.1079058125728</v>
       </c>
       <c r="F732" t="n">
         <v>700260</v>
@@ -15092,16 +15092,16 @@
         <v>45390</v>
       </c>
       <c r="B734" t="n">
-        <v>15.22491264343262</v>
+        <v>15.22491455078125</v>
       </c>
       <c r="C734" t="n">
-        <v>15.84033058052042</v>
+        <v>15.84033256496746</v>
       </c>
       <c r="D734" t="n">
-        <v>15.20707493586032</v>
+        <v>15.20707684097428</v>
       </c>
       <c r="E734" t="n">
-        <v>15.7422205005817</v>
+        <v>15.7422224727377</v>
       </c>
       <c r="F734" t="n">
         <v>693201</v>
@@ -15112,16 +15112,16 @@
         <v>45391</v>
       </c>
       <c r="B735" t="n">
-        <v>15.51924419403076</v>
+        <v>15.51924228668213</v>
       </c>
       <c r="C735" t="n">
-        <v>15.59059682254057</v>
+        <v>15.59059490642255</v>
       </c>
       <c r="D735" t="n">
-        <v>15.2159941787184</v>
+        <v>15.21599230863985</v>
       </c>
       <c r="E735" t="n">
-        <v>15.26950909814931</v>
+        <v>15.26950722149366</v>
       </c>
       <c r="F735" t="n">
         <v>380734</v>
@@ -15132,16 +15132,16 @@
         <v>45392</v>
       </c>
       <c r="B736" t="n">
-        <v>15.14327907562256</v>
+        <v>15.14328002929688</v>
       </c>
       <c r="C736" t="n">
-        <v>15.53754207945022</v>
+        <v>15.53754305795394</v>
       </c>
       <c r="D736" t="n">
-        <v>15.05367295138282</v>
+        <v>15.05367389941404</v>
       </c>
       <c r="E736" t="n">
-        <v>15.53754207945022</v>
+        <v>15.53754305795394</v>
       </c>
       <c r="F736" t="n">
         <v>317419</v>
@@ -15172,16 +15172,16 @@
         <v>45394</v>
       </c>
       <c r="B738" t="n">
-        <v>14.96406841278076</v>
+        <v>14.96406936645508</v>
       </c>
       <c r="C738" t="n">
-        <v>15.14327886659233</v>
+        <v>15.1432798316879</v>
       </c>
       <c r="D738" t="n">
-        <v>14.76693691358803</v>
+        <v>14.76693785469897</v>
       </c>
       <c r="E738" t="n">
-        <v>14.96406841278076</v>
+        <v>14.96406936645508</v>
       </c>
       <c r="F738" t="n">
         <v>376247</v>
@@ -15232,16 +15232,16 @@
         <v>45399</v>
       </c>
       <c r="B741" t="n">
-        <v>14.89238548278809</v>
+        <v>14.89238452911377</v>
       </c>
       <c r="C741" t="n">
-        <v>15.08951610245028</v>
+        <v>15.08951513615217</v>
       </c>
       <c r="D741" t="n">
-        <v>14.74901621159323</v>
+        <v>14.74901526709996</v>
       </c>
       <c r="E741" t="n">
-        <v>14.9103065296753</v>
+        <v>14.91030557485336</v>
       </c>
       <c r="F741" t="n">
         <v>190430</v>
@@ -15252,16 +15252,16 @@
         <v>45400</v>
       </c>
       <c r="B742" t="n">
-        <v>14.88342380523682</v>
+        <v>14.8834228515625</v>
       </c>
       <c r="C742" t="n">
-        <v>15.29560696799188</v>
+        <v>15.29560598790641</v>
       </c>
       <c r="D742" t="n">
-        <v>14.83862163819274</v>
+        <v>14.83862068738918</v>
       </c>
       <c r="E742" t="n">
-        <v>14.87446373026684</v>
+        <v>14.87446277716666</v>
       </c>
       <c r="F742" t="n">
         <v>502607</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051544189453</v>
+        <v>15.77051448822021</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804172020233</v>
+        <v>15.87804076002569</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847665051934</v>
+        <v>15.09847573748455</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808098634539</v>
+        <v>15.18808006789204</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15372,16 +15372,16 @@
         <v>45408</v>
       </c>
       <c r="B748" t="n">
-        <v>16.41567230224609</v>
+        <v>16.41567420959473</v>
       </c>
       <c r="C748" t="n">
-        <v>16.74721209206137</v>
+        <v>16.74721403793184</v>
       </c>
       <c r="D748" t="n">
-        <v>16.14685751582961</v>
+        <v>16.14685939194446</v>
       </c>
       <c r="E748" t="n">
-        <v>16.48735648424971</v>
+        <v>16.48735839992738</v>
       </c>
       <c r="F748" t="n">
         <v>618795</v>
@@ -15392,16 +15392,16 @@
         <v>45411</v>
       </c>
       <c r="B749" t="n">
-        <v>16.50527763366699</v>
+        <v>16.50527954101562</v>
       </c>
       <c r="C749" t="n">
-        <v>16.50527763366699</v>
+        <v>16.50527954101562</v>
       </c>
       <c r="D749" t="n">
-        <v>16.23646106795836</v>
+        <v>16.23646294424257</v>
       </c>
       <c r="E749" t="n">
-        <v>16.40671054399719</v>
+        <v>16.40671243995541</v>
       </c>
       <c r="F749" t="n">
         <v>222938</v>
@@ -15452,16 +15452,16 @@
         <v>45415</v>
       </c>
       <c r="B752" t="n">
-        <v>16.26334190368652</v>
+        <v>16.26334381103516</v>
       </c>
       <c r="C752" t="n">
-        <v>16.45151331718664</v>
+        <v>16.45151524660383</v>
       </c>
       <c r="D752" t="n">
-        <v>16.17373757813992</v>
+        <v>16.17373947497985</v>
       </c>
       <c r="E752" t="n">
-        <v>16.23646078524195</v>
+        <v>16.23646268943799</v>
       </c>
       <c r="F752" t="n">
         <v>303682</v>
@@ -15492,16 +15492,16 @@
         <v>45419</v>
       </c>
       <c r="B754" t="n">
-        <v>16.57696342468262</v>
+        <v>16.57696151733398</v>
       </c>
       <c r="C754" t="n">
-        <v>16.66656776050532</v>
+        <v>16.6665658428468</v>
       </c>
       <c r="D754" t="n">
-        <v>16.29022668253917</v>
+        <v>16.29022480818252</v>
       </c>
       <c r="E754" t="n">
-        <v>16.4156731111298</v>
+        <v>16.41567122233926</v>
       </c>
       <c r="F754" t="n">
         <v>374150</v>
@@ -15512,16 +15512,16 @@
         <v>45420</v>
       </c>
       <c r="B755" t="n">
-        <v>16.97122573852539</v>
+        <v>16.97122383117676</v>
       </c>
       <c r="C755" t="n">
-        <v>16.97122573852539</v>
+        <v>16.97122383117676</v>
       </c>
       <c r="D755" t="n">
-        <v>16.45151451893167</v>
+        <v>16.45151266999193</v>
       </c>
       <c r="E755" t="n">
-        <v>16.57696273449346</v>
+        <v>16.57696087145495</v>
       </c>
       <c r="F755" t="n">
         <v>667766</v>
@@ -15572,16 +15572,16 @@
         <v>45425</v>
       </c>
       <c r="B758" t="n">
-        <v>15.76155376434326</v>
+        <v>15.76155471801758</v>
       </c>
       <c r="C758" t="n">
-        <v>15.94076422015877</v>
+        <v>15.94076518467647</v>
       </c>
       <c r="D758" t="n">
-        <v>15.68091040337191</v>
+        <v>15.68091135216679</v>
       </c>
       <c r="E758" t="n">
-        <v>15.90492212899567</v>
+        <v>15.90492309134469</v>
       </c>
       <c r="F758" t="n">
         <v>299278</v>
@@ -15592,16 +15592,16 @@
         <v>45426</v>
       </c>
       <c r="B759" t="n">
-        <v>15.61818695068359</v>
+        <v>15.61818790435791</v>
       </c>
       <c r="C759" t="n">
-        <v>15.74363337172002</v>
+        <v>15.74363433305432</v>
       </c>
       <c r="D759" t="n">
-        <v>15.38521246562432</v>
+        <v>15.38521340507279</v>
       </c>
       <c r="E759" t="n">
-        <v>15.67194919050088</v>
+        <v>15.67195014745801</v>
       </c>
       <c r="F759" t="n">
         <v>391243</v>
@@ -15612,16 +15612,16 @@
         <v>45427</v>
       </c>
       <c r="B760" t="n">
-        <v>15.76155376434326</v>
+        <v>15.76155471801758</v>
       </c>
       <c r="C760" t="n">
-        <v>15.8870019795112</v>
+        <v>15.88700294077594</v>
       </c>
       <c r="D760" t="n">
-        <v>15.09847597392295</v>
+        <v>15.09847688747684</v>
       </c>
       <c r="E760" t="n">
-        <v>15.59130427936707</v>
+        <v>15.59130522274021</v>
       </c>
       <c r="F760" t="n">
         <v>279879</v>
@@ -15632,16 +15632,16 @@
         <v>45428</v>
       </c>
       <c r="B761" t="n">
-        <v>15.81531715393066</v>
+        <v>15.81531810760498</v>
       </c>
       <c r="C761" t="n">
-        <v>16.12893499080353</v>
+        <v>16.12893596338921</v>
       </c>
       <c r="D761" t="n">
-        <v>15.63610670540415</v>
+        <v>15.63610764827196</v>
       </c>
       <c r="E761" t="n">
-        <v>15.80635618345582</v>
+        <v>15.80635713658978</v>
       </c>
       <c r="F761" t="n">
         <v>286904</v>
@@ -15692,16 +15692,16 @@
         <v>45433</v>
       </c>
       <c r="B764" t="n">
-        <v>15.17016124725342</v>
+        <v>15.1701602935791</v>
       </c>
       <c r="C764" t="n">
-        <v>15.34937171595735</v>
+        <v>15.34937075101694</v>
       </c>
       <c r="D764" t="n">
-        <v>14.97302973167909</v>
+        <v>14.97302879039748</v>
       </c>
       <c r="E764" t="n">
-        <v>15.2060033409942</v>
+        <v>15.20600238506667</v>
       </c>
       <c r="F764" t="n">
         <v>342062</v>
@@ -15852,16 +15852,16 @@
         <v>45446</v>
       </c>
       <c r="B772" t="n">
-        <v>14.33683204650879</v>
+        <v>14.33683109283447</v>
       </c>
       <c r="C772" t="n">
-        <v>15.36729261993504</v>
+        <v>15.36729159771533</v>
       </c>
       <c r="D772" t="n">
-        <v>14.33683204650879</v>
+        <v>14.33683109283447</v>
       </c>
       <c r="E772" t="n">
-        <v>14.69525295968364</v>
+        <v>14.69525198216746</v>
       </c>
       <c r="F772" t="n">
         <v>2218059</v>
@@ -15872,16 +15872,16 @@
         <v>45447</v>
       </c>
       <c r="B773" t="n">
-        <v>14.18450355529785</v>
+        <v>14.18450450897217</v>
       </c>
       <c r="C773" t="n">
-        <v>14.39059513158153</v>
+        <v>14.39059609911211</v>
       </c>
       <c r="D773" t="n">
-        <v>14.0142531741053</v>
+        <v>14.01425411633309</v>
       </c>
       <c r="E773" t="n">
-        <v>14.39059513158153</v>
+        <v>14.39059609911211</v>
       </c>
       <c r="F773" t="n">
         <v>553151</v>
@@ -15912,16 +15912,16 @@
         <v>45449</v>
       </c>
       <c r="B775" t="n">
-        <v>13.97841167449951</v>
+        <v>13.9784107208252</v>
       </c>
       <c r="C775" t="n">
-        <v>14.10385899896733</v>
+        <v>14.10385803673439</v>
       </c>
       <c r="D775" t="n">
-        <v>13.79920121097406</v>
+        <v>13.79920026952634</v>
       </c>
       <c r="E775" t="n">
-        <v>13.97841167449951</v>
+        <v>13.9784107208252</v>
       </c>
       <c r="F775" t="n">
         <v>568356</v>
@@ -16052,16 +16052,16 @@
         <v>45460</v>
       </c>
       <c r="B782" t="n">
-        <v>13.16300487518311</v>
+        <v>13.16300392150879</v>
       </c>
       <c r="C782" t="n">
-        <v>13.45870170007631</v>
+        <v>13.45870072497843</v>
       </c>
       <c r="D782" t="n">
-        <v>12.93899134157258</v>
+        <v>12.93899040412829</v>
       </c>
       <c r="E782" t="n">
-        <v>13.04651762264232</v>
+        <v>13.04651667740763</v>
       </c>
       <c r="F782" t="n">
         <v>743268</v>
@@ -16132,16 +16132,16 @@
         <v>45464</v>
       </c>
       <c r="B786" t="n">
-        <v>12.89418792724609</v>
+        <v>12.89418888092041</v>
       </c>
       <c r="C786" t="n">
-        <v>13.06443740778267</v>
+        <v>13.06443837404891</v>
       </c>
       <c r="D786" t="n">
-        <v>12.75978053693796</v>
+        <v>12.75978148067129</v>
       </c>
       <c r="E786" t="n">
-        <v>13.02859621365129</v>
+        <v>13.02859717726665</v>
       </c>
       <c r="F786" t="n">
         <v>315427</v>
@@ -16172,16 +16172,16 @@
         <v>45468</v>
       </c>
       <c r="B788" t="n">
-        <v>12.72393894195557</v>
+        <v>12.72393989562988</v>
       </c>
       <c r="C788" t="n">
-        <v>13.24364837439928</v>
+        <v>13.24364936702643</v>
       </c>
       <c r="D788" t="n">
-        <v>12.71497797100114</v>
+        <v>12.71497892400382</v>
       </c>
       <c r="E788" t="n">
-        <v>13.20780628277578</v>
+        <v>13.20780727271652</v>
       </c>
       <c r="F788" t="n">
         <v>394179</v>
@@ -16192,16 +16192,16 @@
         <v>45469</v>
       </c>
       <c r="B789" t="n">
-        <v>12.84042453765869</v>
+        <v>12.84042549133301</v>
       </c>
       <c r="C789" t="n">
-        <v>12.89418767193683</v>
+        <v>12.8941886296042</v>
       </c>
       <c r="D789" t="n">
-        <v>12.67017416439606</v>
+        <v>12.67017510542567</v>
       </c>
       <c r="E789" t="n">
-        <v>12.78666140338055</v>
+        <v>12.78666235306181</v>
       </c>
       <c r="F789" t="n">
         <v>397115</v>
@@ -16212,16 +16212,16 @@
         <v>45470</v>
       </c>
       <c r="B790" t="n">
-        <v>13.18092441558838</v>
+        <v>13.1809253692627</v>
       </c>
       <c r="C790" t="n">
-        <v>13.26156956522237</v>
+        <v>13.26157052473157</v>
       </c>
       <c r="D790" t="n">
-        <v>12.83146359400282</v>
+        <v>12.83146452239273</v>
       </c>
       <c r="E790" t="n">
-        <v>12.90314777318991</v>
+        <v>12.90314870676636</v>
       </c>
       <c r="F790" t="n">
         <v>447659</v>
@@ -16272,16 +16272,16 @@
         <v>45475</v>
       </c>
       <c r="B793" t="n">
-        <v>13.29741191864014</v>
+        <v>13.29741287231445</v>
       </c>
       <c r="C793" t="n">
-        <v>13.54830565467569</v>
+        <v>13.5483066263438</v>
       </c>
       <c r="D793" t="n">
-        <v>13.27052990286311</v>
+        <v>13.27053085460948</v>
       </c>
       <c r="E793" t="n">
-        <v>13.36013512862476</v>
+        <v>13.36013608679751</v>
       </c>
       <c r="F793" t="n">
         <v>528404</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61103057861328</v>
+        <v>13.61102962493896</v>
       </c>
       <c r="C795" t="n">
-        <v>13.7006358097591</v>
+        <v>13.70063484980648</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766220877997</v>
+        <v>13.46766126515094</v>
       </c>
       <c r="E795" t="n">
-        <v>13.593108636287</v>
+        <v>13.59310768386841</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16332,16 +16332,16 @@
         <v>45478</v>
       </c>
       <c r="B796" t="n">
-        <v>13.54830646514893</v>
+        <v>13.54830551147461</v>
       </c>
       <c r="C796" t="n">
-        <v>13.88880634341223</v>
+        <v>13.8888053657699</v>
       </c>
       <c r="D796" t="n">
-        <v>13.27949077178316</v>
+        <v>13.27948983703096</v>
       </c>
       <c r="E796" t="n">
-        <v>13.87088619328496</v>
+        <v>13.87088521690404</v>
       </c>
       <c r="F796" t="n">
         <v>907063</v>
@@ -16412,16 +16412,16 @@
         <v>45484</v>
       </c>
       <c r="B800" t="n">
-        <v>14.01425266265869</v>
+        <v>14.01425361633301</v>
       </c>
       <c r="C800" t="n">
-        <v>14.05905482696037</v>
+        <v>14.05905578368349</v>
       </c>
       <c r="D800" t="n">
-        <v>13.64687168943554</v>
+        <v>13.64687261810947</v>
       </c>
       <c r="E800" t="n">
-        <v>13.64687168943554</v>
+        <v>13.64687261810947</v>
       </c>
       <c r="F800" t="n">
         <v>415676</v>
@@ -16552,16 +16552,16 @@
         <v>45495</v>
       </c>
       <c r="B807" t="n">
-        <v>13.98737239837646</v>
+        <v>13.98737335205078</v>
       </c>
       <c r="C807" t="n">
-        <v>14.11281972062591</v>
+        <v>14.11282068285336</v>
       </c>
       <c r="D807" t="n">
-        <v>13.79023999588737</v>
+        <v>13.79024093612098</v>
       </c>
       <c r="E807" t="n">
-        <v>13.79920096695374</v>
+        <v>13.79920190779832</v>
       </c>
       <c r="F807" t="n">
         <v>314378</v>
@@ -16692,16 +16692,16 @@
         <v>45504</v>
       </c>
       <c r="B814" t="n">
-        <v>13.43181991577148</v>
+        <v>13.43181896209717</v>
       </c>
       <c r="C814" t="n">
-        <v>13.61103037538734</v>
+        <v>13.61102940898888</v>
       </c>
       <c r="D814" t="n">
-        <v>13.40493789878055</v>
+        <v>13.40493694701489</v>
       </c>
       <c r="E814" t="n">
-        <v>13.46766200769466</v>
+        <v>13.46766105147551</v>
       </c>
       <c r="F814" t="n">
         <v>351395</v>
@@ -16752,16 +16752,16 @@
         <v>45509</v>
       </c>
       <c r="B817" t="n">
-        <v>12.77770233154297</v>
+        <v>12.77770137786865</v>
       </c>
       <c r="C817" t="n">
-        <v>13.23468948885766</v>
+        <v>13.23468850107574</v>
       </c>
       <c r="D817" t="n">
-        <v>12.77770233154297</v>
+        <v>12.77770137786865</v>
       </c>
       <c r="E817" t="n">
-        <v>13.04651804287597</v>
+        <v>13.04651706913838</v>
       </c>
       <c r="F817" t="n">
         <v>596040</v>
@@ -16952,16 +16952,16 @@
         <v>45523</v>
       </c>
       <c r="B827" t="n">
-        <v>12.33863544464111</v>
+        <v>12.33863639831543</v>
       </c>
       <c r="C827" t="n">
-        <v>12.44616171459386</v>
+        <v>12.44616267657907</v>
       </c>
       <c r="D827" t="n">
-        <v>12.03397857587205</v>
+        <v>12.03397950599891</v>
       </c>
       <c r="E827" t="n">
-        <v>12.28487230966474</v>
+        <v>12.28487325918361</v>
       </c>
       <c r="F827" t="n">
         <v>2509053</v>
@@ -16972,16 +16972,16 @@
         <v>45524</v>
       </c>
       <c r="B828" t="n">
-        <v>12.41031932830811</v>
+        <v>12.41032028198242</v>
       </c>
       <c r="C828" t="n">
-        <v>12.47304253623447</v>
+        <v>12.47304349472877</v>
       </c>
       <c r="D828" t="n">
-        <v>12.19526679353708</v>
+        <v>12.19526773068562</v>
       </c>
       <c r="E828" t="n">
-        <v>12.35655619461535</v>
+        <v>12.35655714415822</v>
       </c>
       <c r="F828" t="n">
         <v>514247</v>
@@ -16992,16 +16992,16 @@
         <v>45525</v>
       </c>
       <c r="B829" t="n">
-        <v>12.08774089813232</v>
+        <v>12.08774185180664</v>
       </c>
       <c r="C829" t="n">
-        <v>12.49992493579443</v>
+        <v>12.49992592198841</v>
       </c>
       <c r="D829" t="n">
-        <v>12.08774089813232</v>
+        <v>12.08774185180664</v>
       </c>
       <c r="E829" t="n">
-        <v>12.49992493579443</v>
+        <v>12.49992592198841</v>
       </c>
       <c r="F829" t="n">
         <v>645535</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37986087799072</v>
+        <v>11.37985992431641</v>
       </c>
       <c r="C844" t="n">
-        <v>11.5232292491703</v>
+        <v>11.52322828348119</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089990674344</v>
+        <v>11.37089895382008</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882184923801</v>
+        <v>11.38882089481273</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17352,16 +17352,16 @@
         <v>45551</v>
       </c>
       <c r="B847" t="n">
-        <v>11.4694652557373</v>
+        <v>11.46946620941162</v>
       </c>
       <c r="C847" t="n">
-        <v>11.62179369072169</v>
+        <v>11.62179465706196</v>
       </c>
       <c r="D847" t="n">
-        <v>11.4694652557373</v>
+        <v>11.46946620941162</v>
       </c>
       <c r="E847" t="n">
-        <v>11.59491257117618</v>
+        <v>11.59491353528131</v>
       </c>
       <c r="F847" t="n">
         <v>377086</v>
@@ -17372,16 +17372,16 @@
         <v>45552</v>
       </c>
       <c r="B848" t="n">
-        <v>11.53219032287598</v>
+        <v>11.53218936920166</v>
       </c>
       <c r="C848" t="n">
-        <v>11.63075563088909</v>
+        <v>11.63075466906374</v>
       </c>
       <c r="D848" t="n">
-        <v>11.3977820256524</v>
+        <v>11.39778108309321</v>
       </c>
       <c r="E848" t="n">
-        <v>11.52322935154908</v>
+        <v>11.5232283986158</v>
       </c>
       <c r="F848" t="n">
         <v>1190193</v>
@@ -26672,19 +26672,39 @@
         <v>46234</v>
       </c>
       <c r="B1313" t="n">
-        <v>5.51</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="C1313" t="n">
-        <v>5.58</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="D1313" t="n">
-        <v>5.46</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="E1313" t="n">
-        <v>5.51</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="F1313" t="n">
-        <v>528100</v>
+        <v>535600</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1314" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>739000</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2856616973877</v>
+        <v>13.28566265106201</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83010549167658</v>
+        <v>12.83010641265006</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970443725586</v>
+        <v>13.16970252990723</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606824847914</v>
+        <v>13.76606625476003</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404745317332</v>
+        <v>13.00404556981654</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647251293245</v>
+        <v>13.42647056839647</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -552,16 +552,16 @@
         <v>44323</v>
       </c>
       <c r="B7" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="C7" t="n">
-        <v>12.85495449619264</v>
+        <v>12.85495643096718</v>
       </c>
       <c r="D7" t="n">
-        <v>12.26687258210669</v>
+        <v>12.26687442837015</v>
       </c>
       <c r="E7" t="n">
-        <v>12.71414617400787</v>
+        <v>12.71414808758961</v>
       </c>
       <c r="F7" t="n">
         <v>847960</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C9" t="n">
-        <v>12.54848908114925</v>
+        <v>12.5484900443603</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717518992304</v>
+        <v>12.21717612770272</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566390991211</v>
+        <v>12.46566009521484</v>
       </c>
       <c r="C10" t="n">
-        <v>12.7555623932591</v>
+        <v>12.75555848984815</v>
       </c>
       <c r="D10" t="n">
-        <v>12.30000692042424</v>
+        <v>12.30000315642073</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3414215838818</v>
+        <v>12.34141780720472</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162181854248</v>
+        <v>13.40162086486816</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172308737706</v>
+        <v>13.93172209598015</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566158371901</v>
+        <v>12.46566069664867</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273319802321</v>
+        <v>12.67273229621742</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83232975006104</v>
+        <v>13.83232879638672</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677323706887</v>
+        <v>14.19677225826788</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101582480272</v>
+        <v>13.50101489397095</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56727910915701</v>
+        <v>13.5672781737567</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98142147064209</v>
+        <v>13.98141956329346</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778523820564</v>
+        <v>14.57778324950092</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495615574281</v>
+        <v>13.67495429020224</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9897049017596</v>
+        <v>13.98970299328094</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -732,16 +732,16 @@
         <v>44336</v>
       </c>
       <c r="B16" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253193348793</v>
       </c>
       <c r="D16" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838950440068</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25253000199559</v>
+        <v>13.25253193348793</v>
       </c>
       <c r="F16" t="n">
         <v>1118709</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21939849853516</v>
+        <v>13.21940040588379</v>
       </c>
       <c r="C17" t="n">
-        <v>13.4844491095965</v>
+        <v>13.48445105518772</v>
       </c>
       <c r="D17" t="n">
-        <v>13.086872776919</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="E17" t="n">
-        <v>13.086872776919</v>
+        <v>13.08687466514628</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -772,16 +772,16 @@
         <v>44340</v>
       </c>
       <c r="B18" t="n">
-        <v>13.42646884918213</v>
+        <v>13.42647171020508</v>
       </c>
       <c r="C18" t="n">
-        <v>14.02283249767257</v>
+        <v>14.02283548577361</v>
       </c>
       <c r="D18" t="n">
-        <v>13.32707435298643</v>
+        <v>13.32707719282958</v>
       </c>
       <c r="E18" t="n">
-        <v>13.40162022513321</v>
+        <v>13.4016230808612</v>
       </c>
       <c r="F18" t="n">
         <v>1040223</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.2690954208374</v>
+        <v>13.26909637451172</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182314288226</v>
+        <v>13.64182412334521</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25253022511198</v>
+        <v>13.25253117759573</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162114749573</v>
+        <v>13.40162211069491</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970443725586</v>
+        <v>13.16970252990723</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45132031159078</v>
+        <v>13.45131836345614</v>
       </c>
       <c r="D21" t="n">
-        <v>13.1531392381503</v>
+        <v>13.15313733320078</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707798961446</v>
+        <v>13.32707605947365</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889537811279</v>
+        <v>13.02889442443848</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879381777798</v>
+        <v>13.31879284288401</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263209299946</v>
+        <v>12.96263114417541</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111753978956</v>
+        <v>13.21111657277715</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980365753174</v>
+        <v>12.87980270385742</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111758778895</v>
+        <v>13.21111660958277</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6147530126286</v>
+        <v>12.61475207857974</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374322126546</v>
+        <v>13.05374225471193</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -912,16 +912,16 @@
         <v>44349</v>
       </c>
       <c r="B25" t="n">
-        <v>12.95434951782227</v>
+        <v>12.95434856414795</v>
       </c>
       <c r="C25" t="n">
-        <v>13.31879384183405</v>
+        <v>13.31879286133005</v>
       </c>
       <c r="D25" t="n">
-        <v>12.88808623258925</v>
+        <v>12.88808528379311</v>
       </c>
       <c r="E25" t="n">
-        <v>13.2525313887721</v>
+        <v>13.25253041314621</v>
       </c>
       <c r="F25" t="n">
         <v>598492</v>
@@ -932,16 +932,16 @@
         <v>44351</v>
       </c>
       <c r="B26" t="n">
-        <v>12.97919654846191</v>
+        <v>12.97919845581055</v>
       </c>
       <c r="C26" t="n">
-        <v>13.23596373052036</v>
+        <v>13.23596567560203</v>
       </c>
       <c r="D26" t="n">
-        <v>12.85495425621803</v>
+        <v>12.85495614530872</v>
       </c>
       <c r="E26" t="n">
-        <v>12.98747914603258</v>
+        <v>12.98748105459838</v>
       </c>
       <c r="F26" t="n">
         <v>460799</v>
@@ -952,16 +952,16 @@
         <v>44354</v>
       </c>
       <c r="B27" t="n">
-        <v>12.76384353637695</v>
+        <v>12.76384449005127</v>
       </c>
       <c r="C27" t="n">
-        <v>13.07859057440149</v>
+        <v>13.07859155159272</v>
       </c>
       <c r="D27" t="n">
-        <v>12.69758025748196</v>
+        <v>12.69758120620529</v>
       </c>
       <c r="E27" t="n">
-        <v>12.86323720646297</v>
+        <v>12.86323816756367</v>
       </c>
       <c r="F27" t="n">
         <v>662018</v>
@@ -992,16 +992,16 @@
         <v>44356</v>
       </c>
       <c r="B29" t="n">
-        <v>12.73071193695068</v>
+        <v>12.73071098327637</v>
       </c>
       <c r="C29" t="n">
-        <v>12.73899453504518</v>
+        <v>12.7389935807504</v>
       </c>
       <c r="D29" t="n">
-        <v>12.53192375748563</v>
+        <v>12.5319228187028</v>
       </c>
       <c r="E29" t="n">
-        <v>12.53192375748563</v>
+        <v>12.5319228187028</v>
       </c>
       <c r="F29" t="n">
         <v>453530</v>
@@ -1012,16 +1012,16 @@
         <v>44357</v>
       </c>
       <c r="B30" t="n">
-        <v>12.95434951782227</v>
+        <v>12.95434856414795</v>
       </c>
       <c r="C30" t="n">
-        <v>13.0040459415332</v>
+        <v>13.00404498420033</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72243009993438</v>
+        <v>12.72242916333352</v>
       </c>
       <c r="E30" t="n">
-        <v>12.8218237795273</v>
+        <v>12.82182283560928</v>
       </c>
       <c r="F30" t="n">
         <v>493879</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667110443115</v>
+        <v>12.84667301177979</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555837422966</v>
+        <v>12.75556026805076</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576118295518</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1052,16 +1052,16 @@
         <v>44361</v>
       </c>
       <c r="B32" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="C32" t="n">
-        <v>13.00404458393173</v>
+        <v>13.00404654114553</v>
       </c>
       <c r="D32" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="E32" t="n">
-        <v>12.93778296995845</v>
+        <v>12.93778491719934</v>
       </c>
       <c r="F32" t="n">
         <v>396641</v>
@@ -1132,16 +1132,16 @@
         <v>44365</v>
       </c>
       <c r="B36" t="n">
-        <v>12.65616607666016</v>
+        <v>12.65616512298584</v>
       </c>
       <c r="C36" t="n">
-        <v>12.74727715234998</v>
+        <v>12.74727619181022</v>
       </c>
       <c r="D36" t="n">
-        <v>12.54848980475637</v>
+        <v>12.54848885919573</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6396008804462</v>
+        <v>12.63959992802011</v>
       </c>
       <c r="F36" t="n">
         <v>365879</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.33313751220703</v>
+        <v>12.3331356048584</v>
       </c>
       <c r="C40" t="n">
-        <v>12.51535967959436</v>
+        <v>12.51535774406464</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717696766745</v>
+        <v>12.21717507825239</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717696766745</v>
+        <v>12.21717507825239</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31656932830811</v>
+        <v>12.31657218933105</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424558356415</v>
+        <v>12.42424846959927</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293172445695</v>
+        <v>12.09293453353099</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596298673773</v>
+        <v>12.41596587084889</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1272,16 +1272,16 @@
         <v>44376</v>
       </c>
       <c r="B43" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="C43" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="D43" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152102990341</v>
       </c>
       <c r="E43" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152102990341</v>
       </c>
       <c r="F43" t="n">
         <v>538653</v>
@@ -1352,16 +1352,16 @@
         <v>44382</v>
       </c>
       <c r="B47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252849578857</v>
       </c>
       <c r="C47" t="n">
-        <v>12.64788378432207</v>
+        <v>12.64788184393479</v>
       </c>
       <c r="D47" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252849578857</v>
       </c>
       <c r="E47" t="n">
-        <v>12.55677270642959</v>
+        <v>12.5567707800202</v>
       </c>
       <c r="F47" t="n">
         <v>186679</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798454284668</v>
       </c>
       <c r="C48" t="n">
-        <v>12.49879274279404</v>
+        <v>12.4987937073347</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25858992047414</v>
+        <v>12.25859086647818</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394328540577</v>
+        <v>12.47394424802878</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1392,16 +1392,16 @@
         <v>44384</v>
       </c>
       <c r="B49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.3414192199707</v>
       </c>
       <c r="C49" t="n">
-        <v>12.54849097075757</v>
+        <v>12.54849000108201</v>
       </c>
       <c r="D49" t="n">
-        <v>12.34142017364502</v>
+        <v>12.3414192199707</v>
       </c>
       <c r="E49" t="n">
-        <v>12.40768346117107</v>
+        <v>12.4076825023763</v>
       </c>
       <c r="F49" t="n">
         <v>205326</v>
@@ -1412,16 +1412,16 @@
         <v>44385</v>
       </c>
       <c r="B50" t="n">
-        <v>12.34142017364502</v>
+        <v>12.3414192199707</v>
       </c>
       <c r="C50" t="n">
-        <v>12.6561672526666</v>
+        <v>12.65616627467043</v>
       </c>
       <c r="D50" t="n">
-        <v>12.17576320308654</v>
+        <v>12.17576226221325</v>
       </c>
       <c r="E50" t="n">
-        <v>12.25859168836578</v>
+        <v>12.25859074109198</v>
       </c>
       <c r="F50" t="n">
         <v>421609</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717739105225</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020776395842</v>
+        <v>12.5402087428486</v>
       </c>
       <c r="D51" t="n">
-        <v>12.21717643737793</v>
+        <v>12.21717739105225</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424805662318</v>
+        <v>12.42424902646154</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121726989746</v>
+        <v>12.10121822357178</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030819970261</v>
+        <v>12.25030916512651</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293383945143</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293383945143</v>
+        <v>12.09293479247294</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1532,16 +1532,16 @@
         <v>44396</v>
       </c>
       <c r="B56" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C56" t="n">
-        <v>12.02667163783278</v>
+        <v>12.02667065225621</v>
       </c>
       <c r="D56" t="n">
-        <v>11.53798501475665</v>
+        <v>11.53798406922757</v>
       </c>
       <c r="E56" t="n">
-        <v>12.01010644093992</v>
+        <v>12.01010545672085</v>
       </c>
       <c r="F56" t="n">
         <v>557721</v>
@@ -1552,16 +1552,16 @@
         <v>44397</v>
       </c>
       <c r="B57" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C57" t="n">
-        <v>11.8692995808735</v>
+        <v>11.86929859769704</v>
       </c>
       <c r="D57" t="n">
-        <v>11.37232946544736</v>
+        <v>11.37232852343671</v>
       </c>
       <c r="E57" t="n">
-        <v>11.67879396774409</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="F57" t="n">
         <v>1030110</v>
@@ -1572,16 +1572,16 @@
         <v>44398</v>
       </c>
       <c r="B58" t="n">
-        <v>10.98303508758545</v>
+        <v>10.98303413391113</v>
       </c>
       <c r="C58" t="n">
-        <v>11.6705098973207</v>
+        <v>11.67050888395185</v>
       </c>
       <c r="D58" t="n">
-        <v>10.98303508758545</v>
+        <v>10.98303413391113</v>
       </c>
       <c r="E58" t="n">
-        <v>11.52970239530374</v>
+        <v>11.52970139416144</v>
       </c>
       <c r="F58" t="n">
         <v>1221952</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C59" t="n">
-        <v>11.3474776588947</v>
+        <v>11.34747966894678</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172035776503</v>
+        <v>10.65172224457312</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414446317129</v>
+        <v>11.07414642480609</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879230499268</v>
+        <v>10.85879039764404</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525761084529</v>
+        <v>11.16525564966597</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798479837585</v>
+        <v>10.71798291576008</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76768122275841</v>
+        <v>10.76767933141345</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.29778099060059</v>
+        <v>11.29778289794922</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47172053283982</v>
+        <v>11.4717224695538</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05757983553765</v>
+        <v>11.05758170233431</v>
       </c>
       <c r="E62" t="n">
-        <v>11.1818221279454</v>
+        <v>11.18182401571727</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C63" t="n">
-        <v>11.51313582037561</v>
+        <v>11.5131367879722</v>
       </c>
       <c r="D63" t="n">
-        <v>11.21495313710418</v>
+        <v>11.21495407964066</v>
       </c>
       <c r="E63" t="n">
-        <v>11.3640448948254</v>
+        <v>11.36404584989197</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="C69" t="n">
-        <v>11.66222697699479</v>
+        <v>11.6622279694364</v>
       </c>
       <c r="D69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768109665717</v>
+        <v>11.58768208275502</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283283233643</v>
+        <v>11.56283187866211</v>
       </c>
       <c r="C70" t="n">
-        <v>11.59596489052797</v>
+        <v>11.595963934121</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495371086467</v>
+        <v>11.21495278588257</v>
       </c>
       <c r="E70" t="n">
-        <v>11.2812169950767</v>
+        <v>11.28121606462938</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1852,16 +1852,16 @@
         <v>44418</v>
       </c>
       <c r="B72" t="n">
-        <v>11.92727661132812</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2503070680949</v>
+        <v>12.2503080475979</v>
       </c>
       <c r="D72" t="n">
-        <v>11.92727661132812</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="E72" t="n">
-        <v>12.05151890266051</v>
+        <v>12.05151986626892</v>
       </c>
       <c r="F72" t="n">
         <v>351025</v>
@@ -1872,16 +1872,16 @@
         <v>44419</v>
       </c>
       <c r="B73" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.01838819869508</v>
       </c>
       <c r="D73" t="n">
-        <v>11.71192469562211</v>
+        <v>11.71192375590401</v>
       </c>
       <c r="E73" t="n">
-        <v>12.01838916300267</v>
+        <v>12.01838819869508</v>
       </c>
       <c r="F73" t="n">
         <v>262426</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859100341797</v>
+        <v>11.43859004974365</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727761224746</v>
+        <v>11.92727661782967</v>
       </c>
       <c r="D77" t="n">
-        <v>11.3226304676933</v>
+        <v>11.32262952368701</v>
       </c>
       <c r="E77" t="n">
-        <v>11.84444913368471</v>
+        <v>11.84444814617262</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -2032,16 +2032,16 @@
         <v>44431</v>
       </c>
       <c r="B81" t="n">
-        <v>11.99353885650635</v>
+        <v>11.99353981018066</v>
       </c>
       <c r="C81" t="n">
-        <v>12.39111434859944</v>
+        <v>12.39111533388724</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95212420530292</v>
+        <v>11.95212515568412</v>
       </c>
       <c r="E81" t="n">
-        <v>12.21717481075529</v>
+        <v>12.21717578221218</v>
       </c>
       <c r="F81" t="n">
         <v>344599</v>
@@ -2072,16 +2072,16 @@
         <v>44433</v>
       </c>
       <c r="B83" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C83" t="n">
-        <v>12.01010599913494</v>
+        <v>12.01010696614738</v>
       </c>
       <c r="D83" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="E83" t="n">
-        <v>11.91071149274992</v>
+        <v>11.91071245175947</v>
       </c>
       <c r="F83" t="n">
         <v>140958</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848987579346</v>
+        <v>11.72848796844482</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697532092373</v>
+        <v>11.97697337316509</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081359852429</v>
+        <v>11.62081170868654</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444958375337</v>
+        <v>11.84444765754676</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2152,16 +2152,16 @@
         <v>44439</v>
       </c>
       <c r="B87" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="D87" t="n">
-        <v>11.388893311891</v>
+        <v>11.38889235890981</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68707601147242</v>
+        <v>11.68707503354038</v>
       </c>
       <c r="F87" t="n">
         <v>336803</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141952514648</v>
+        <v>11.52141857147217</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737923751014</v>
+        <v>11.63737827423737</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576338760633</v>
+        <v>11.35576244764404</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313692631225</v>
+        <v>11.51313597332352</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C89" t="n">
-        <v>11.62909547100532</v>
+        <v>11.6290964280881</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010529430325</v>
+        <v>11.19010621525682</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55454959246905</v>
+        <v>11.55455054341664</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2212,16 +2212,16 @@
         <v>44442</v>
       </c>
       <c r="B90" t="n">
-        <v>11.26465129852295</v>
+        <v>11.26465225219727</v>
       </c>
       <c r="C90" t="n">
-        <v>11.59596437620398</v>
+        <v>11.59596535792752</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19838801724993</v>
+        <v>11.19838896531435</v>
       </c>
       <c r="E90" t="n">
-        <v>11.35576237408096</v>
+        <v>11.35576333546881</v>
       </c>
       <c r="F90" t="n">
         <v>466804</v>
@@ -2232,16 +2232,16 @@
         <v>44445</v>
       </c>
       <c r="B91" t="n">
-        <v>11.61252975463867</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="C91" t="n">
-        <v>11.72848861799172</v>
+        <v>11.72848958118911</v>
       </c>
       <c r="D91" t="n">
-        <v>11.26465066806662</v>
+        <v>11.26465159317151</v>
       </c>
       <c r="E91" t="n">
-        <v>11.34747830872295</v>
+        <v>11.34747924063002</v>
       </c>
       <c r="F91" t="n">
         <v>145382</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566230773926</v>
+        <v>11.64566135406494</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67051093741888</v>
+        <v>11.67050998170969</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010687084992</v>
+        <v>11.19010595448147</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313739234277</v>
+        <v>11.51313644952104</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111708543731</v>
+        <v>11.57111611650414</v>
       </c>
       <c r="D93" t="n">
-        <v>11.181824111812</v>
+        <v>11.18182317547715</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141982678859</v>
+        <v>11.52141886201694</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2292,16 +2292,16 @@
         <v>44449</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C94" t="n">
-        <v>11.62909565647244</v>
+        <v>11.62909470007334</v>
       </c>
       <c r="D94" t="n">
-        <v>11.38061022289286</v>
+        <v>11.38060928692969</v>
       </c>
       <c r="E94" t="n">
-        <v>11.50485335576816</v>
+        <v>11.50485240958699</v>
       </c>
       <c r="F94" t="n">
         <v>217652</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364093780518</v>
+        <v>11.70364284515381</v>
       </c>
       <c r="C96" t="n">
-        <v>11.8361658298683</v>
+        <v>11.83616775881459</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172071235275</v>
+        <v>11.47172258190522</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313536525071</v>
+        <v>11.51313724155255</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2352,16 +2352,16 @@
         <v>44454</v>
       </c>
       <c r="B97" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C97" t="n">
-        <v>11.84444903317125</v>
+        <v>11.84444805906109</v>
       </c>
       <c r="D97" t="n">
-        <v>11.587681001457</v>
+        <v>11.58768004846393</v>
       </c>
       <c r="E97" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F97" t="n">
         <v>300984</v>
@@ -2372,16 +2372,16 @@
         <v>44455</v>
       </c>
       <c r="B98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C98" t="n">
-        <v>11.71192413433229</v>
+        <v>11.71192317112123</v>
       </c>
       <c r="D98" t="n">
-        <v>11.51313595390284</v>
+        <v>11.51313500704049</v>
       </c>
       <c r="E98" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="F98" t="n">
         <v>205642</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424831381274</v>
+        <v>11.60424734210526</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606642626268</v>
+        <v>11.30606547952412</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596571476166</v>
+        <v>11.59596474374774</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C100" t="n">
-        <v>11.6456602402011</v>
+        <v>11.64566120833546</v>
       </c>
       <c r="D100" t="n">
-        <v>11.0575799923214</v>
+        <v>11.05758091156711</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26465075999399</v>
+        <v>11.26465169645404</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2432,16 +2432,16 @@
         <v>44460</v>
       </c>
       <c r="B101" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C101" t="n">
-        <v>11.67879396774409</v>
+        <v>11.67879300034788</v>
       </c>
       <c r="D101" t="n">
-        <v>11.33919823537511</v>
+        <v>11.33919729610883</v>
       </c>
       <c r="E101" t="n">
-        <v>11.48000575513941</v>
+        <v>11.48000480420954</v>
       </c>
       <c r="F101" t="n">
         <v>218811</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81960105895996</v>
+        <v>11.81959915161133</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05152047689957</v>
+        <v>12.05151853212572</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58768164102035</v>
+        <v>11.58767977109694</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535875139833</v>
+        <v>11.69535686409888</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2472,16 +2472,16 @@
         <v>44462</v>
       </c>
       <c r="B103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.3414192199707</v>
       </c>
       <c r="C103" t="n">
-        <v>12.34142017364502</v>
+        <v>12.3414192199707</v>
       </c>
       <c r="D103" t="n">
-        <v>11.73677298006055</v>
+        <v>11.73677207310991</v>
       </c>
       <c r="E103" t="n">
-        <v>11.76162160886144</v>
+        <v>11.76162069999063</v>
       </c>
       <c r="F103" t="n">
         <v>381998</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.05152034759521</v>
+        <v>12.05151844024658</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424809845207</v>
+        <v>12.42424613211322</v>
       </c>
       <c r="D104" t="n">
-        <v>11.99354049373239</v>
+        <v>11.99353859556001</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34141961690932</v>
+        <v>12.34141766367942</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2512,16 +2512,16 @@
         <v>44466</v>
       </c>
       <c r="B105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C105" t="n">
-        <v>12.16748009742714</v>
+        <v>12.16747912115709</v>
       </c>
       <c r="D105" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="E105" t="n">
-        <v>12.05152038930021</v>
+        <v>12.05151942233431</v>
       </c>
       <c r="F105" t="n">
         <v>207539</v>
@@ -2572,16 +2572,16 @@
         <v>44469</v>
       </c>
       <c r="B108" t="n">
-        <v>11.63737869262695</v>
+        <v>11.63737773895264</v>
       </c>
       <c r="C108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="D108" t="n">
-        <v>11.51313638724631</v>
+        <v>11.51313544375356</v>
       </c>
       <c r="E108" t="n">
-        <v>11.94384315685534</v>
+        <v>11.94384217806649</v>
       </c>
       <c r="F108" t="n">
         <v>264322</v>
@@ -2592,16 +2592,16 @@
         <v>44470</v>
       </c>
       <c r="B109" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="D109" t="n">
-        <v>11.38889282102754</v>
+        <v>11.38889188438319</v>
       </c>
       <c r="E109" t="n">
-        <v>11.76162055531139</v>
+        <v>11.7616195880132</v>
       </c>
       <c r="F109" t="n">
         <v>232823</v>
@@ -2612,16 +2612,16 @@
         <v>44473</v>
       </c>
       <c r="B110" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C110" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D110" t="n">
-        <v>11.40545885919616</v>
+        <v>11.40545977752449</v>
       </c>
       <c r="E110" t="n">
-        <v>11.59596444165342</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F110" t="n">
         <v>214702</v>
@@ -2632,16 +2632,16 @@
         <v>44474</v>
       </c>
       <c r="B111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="C111" t="n">
-        <v>12.01010650652883</v>
+        <v>12.01010550156678</v>
       </c>
       <c r="D111" t="n">
-        <v>11.39717674255371</v>
+        <v>11.39717578887939</v>
       </c>
       <c r="E111" t="n">
-        <v>11.84444954366927</v>
+        <v>11.84444855256879</v>
       </c>
       <c r="F111" t="n">
         <v>205642</v>
@@ -2672,16 +2672,16 @@
         <v>44476</v>
       </c>
       <c r="B113" t="n">
-        <v>11.33091259002686</v>
+        <v>11.33091354370117</v>
       </c>
       <c r="C113" t="n">
-        <v>11.52970074919511</v>
+        <v>11.52970171960058</v>
       </c>
       <c r="D113" t="n">
-        <v>11.28121534219206</v>
+        <v>11.28121629168357</v>
       </c>
       <c r="E113" t="n">
-        <v>11.45515487744292</v>
+        <v>11.45515584157418</v>
       </c>
       <c r="F113" t="n">
         <v>136744</v>
@@ -2692,16 +2692,16 @@
         <v>44477</v>
       </c>
       <c r="B114" t="n">
-        <v>11.40545845031738</v>
+        <v>11.4054594039917</v>
       </c>
       <c r="C114" t="n">
-        <v>11.57939799808451</v>
+        <v>11.57939896630289</v>
       </c>
       <c r="D114" t="n">
-        <v>11.38060982461194</v>
+        <v>11.38061077620852</v>
       </c>
       <c r="E114" t="n">
-        <v>11.43859050603864</v>
+        <v>11.43859146248331</v>
       </c>
       <c r="F114" t="n">
         <v>102610</v>
@@ -2712,16 +2712,16 @@
         <v>44480</v>
       </c>
       <c r="B115" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C115" t="n">
-        <v>11.73677192873634</v>
+        <v>11.73677096348174</v>
       </c>
       <c r="D115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="E115" t="n">
-        <v>11.44687350448336</v>
+        <v>11.44687256307056</v>
       </c>
       <c r="F115" t="n">
         <v>154548</v>
@@ -2732,16 +2732,16 @@
         <v>44482</v>
       </c>
       <c r="B116" t="n">
-        <v>12.02667045593262</v>
+        <v>12.02667140960693</v>
       </c>
       <c r="C116" t="n">
-        <v>12.03495305356509</v>
+        <v>12.03495400789619</v>
       </c>
       <c r="D116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768121771099</v>
       </c>
       <c r="E116" t="n">
-        <v>11.58768029884711</v>
+        <v>11.58768121771099</v>
       </c>
       <c r="F116" t="n">
         <v>174564</v>
@@ -2752,16 +2752,16 @@
         <v>44483</v>
       </c>
       <c r="B117" t="n">
-        <v>11.93556118011475</v>
+        <v>11.93556022644043</v>
       </c>
       <c r="C117" t="n">
-        <v>12.02667226428446</v>
+        <v>12.0266713033302</v>
       </c>
       <c r="D117" t="n">
-        <v>11.81960146714036</v>
+        <v>11.81960052273145</v>
       </c>
       <c r="E117" t="n">
-        <v>12.0183896654066</v>
+        <v>12.01838870511413</v>
       </c>
       <c r="F117" t="n">
         <v>96605</v>
@@ -2792,16 +2792,16 @@
         <v>44487</v>
       </c>
       <c r="B119" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C119" t="n">
-        <v>12.22545936636416</v>
+        <v>12.22546032458287</v>
       </c>
       <c r="D119" t="n">
-        <v>11.92727751178659</v>
+        <v>11.92727844663413</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08465103721058</v>
+        <v>12.08465198439289</v>
       </c>
       <c r="F119" t="n">
         <v>266429</v>
@@ -2832,16 +2832,16 @@
         <v>44489</v>
       </c>
       <c r="B121" t="n">
-        <v>11.8030366897583</v>
+        <v>11.80303573608398</v>
       </c>
       <c r="C121" t="n">
-        <v>12.20061226827963</v>
+        <v>12.20061128248158</v>
       </c>
       <c r="D121" t="n">
-        <v>11.7284908006893</v>
+        <v>11.72848985303822</v>
       </c>
       <c r="E121" t="n">
-        <v>12.01839009345022</v>
+        <v>12.01838912237555</v>
       </c>
       <c r="F121" t="n">
         <v>129580</v>
@@ -2852,16 +2852,16 @@
         <v>44490</v>
       </c>
       <c r="B122" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C122" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D122" t="n">
-        <v>11.4137414573379</v>
+        <v>11.41374237633313</v>
       </c>
       <c r="E122" t="n">
-        <v>11.67879208741291</v>
+        <v>11.6787930277491</v>
       </c>
       <c r="F122" t="n">
         <v>198689</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C124" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172059900599</v>
+        <v>11.47172147956523</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141784912412</v>
+        <v>11.52141873349808</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.05152034759521</v>
+        <v>12.05151844024658</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030853686361</v>
+        <v>12.25030659805352</v>
       </c>
       <c r="D126" t="n">
-        <v>11.84444955982386</v>
+        <v>11.84444768524754</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717647850966</v>
+        <v>12.21717454494326</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -2952,16 +2952,16 @@
         <v>44497</v>
       </c>
       <c r="B127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C127" t="n">
-        <v>12.05980324204109</v>
+        <v>12.05980225021978</v>
       </c>
       <c r="D127" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="E127" t="n">
-        <v>12.01010598889097</v>
+        <v>12.01010500115686</v>
       </c>
       <c r="F127" t="n">
         <v>345020</v>
@@ -2992,16 +2992,16 @@
         <v>44501</v>
       </c>
       <c r="B129" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C129" t="n">
-        <v>11.65394533714711</v>
+        <v>11.65394437180921</v>
       </c>
       <c r="D129" t="n">
-        <v>11.36404686597209</v>
+        <v>11.36404592464751</v>
       </c>
       <c r="E129" t="n">
-        <v>11.50485521790754</v>
+        <v>11.5048542649193</v>
       </c>
       <c r="F129" t="n">
         <v>1267357</v>
@@ -3032,16 +3032,16 @@
         <v>44504</v>
       </c>
       <c r="B131" t="n">
-        <v>11.7781867980957</v>
+        <v>11.77818775177002</v>
       </c>
       <c r="C131" t="n">
-        <v>12.08465125636622</v>
+        <v>12.08465223485482</v>
       </c>
       <c r="D131" t="n">
-        <v>11.73677214232659</v>
+        <v>11.73677309264758</v>
       </c>
       <c r="E131" t="n">
-        <v>12.01010620745546</v>
+        <v>12.01010717990818</v>
       </c>
       <c r="F131" t="n">
         <v>218179</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727688367788</v>
+        <v>11.92727787522379</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899381298753</v>
+        <v>11.09899473567608</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81959978490659</v>
+        <v>11.81960076750101</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.05152034759521</v>
+        <v>12.05151844024658</v>
       </c>
       <c r="C134" t="n">
-        <v>12.05152034759521</v>
+        <v>12.05151844024658</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283288901272</v>
+        <v>11.56283105900681</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707602741238</v>
+        <v>11.68707417774297</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3112,16 +3112,16 @@
         <v>44510</v>
       </c>
       <c r="B135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C135" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="D135" t="n">
-        <v>11.86929850548507</v>
+        <v>11.86929758022087</v>
       </c>
       <c r="E135" t="n">
-        <v>12.05152067045827</v>
+        <v>12.05151973098904</v>
       </c>
       <c r="F135" t="n">
         <v>295400</v>
@@ -3152,16 +3152,16 @@
         <v>44512</v>
       </c>
       <c r="B137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="C137" t="n">
-        <v>12.23374338219328</v>
+        <v>12.23374240060653</v>
       </c>
       <c r="D137" t="n">
-        <v>11.8858642578125</v>
+        <v>11.88586330413818</v>
       </c>
       <c r="E137" t="n">
-        <v>12.14263230183227</v>
+        <v>12.14263132755591</v>
       </c>
       <c r="F137" t="n">
         <v>236720</v>
@@ -3172,16 +3172,16 @@
         <v>44516</v>
       </c>
       <c r="B138" t="n">
-        <v>12.16747951507568</v>
+        <v>12.16748046875</v>
       </c>
       <c r="C138" t="n">
-        <v>12.17576211321089</v>
+        <v>12.17576306753439</v>
       </c>
       <c r="D138" t="n">
-        <v>11.6870755084975</v>
+        <v>11.68707642451825</v>
       </c>
       <c r="E138" t="n">
-        <v>11.90242888520996</v>
+        <v>11.90242981810988</v>
       </c>
       <c r="F138" t="n">
         <v>286867</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.05152034759521</v>
+        <v>12.05151844024658</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364177700074</v>
+        <v>12.52363979493123</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131833364097</v>
+        <v>11.81131646430821</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424809845207</v>
+        <v>12.42424613211322</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.33313751220703</v>
+        <v>12.3331356048584</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566242224469</v>
+        <v>12.46566049440077</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010700377637</v>
+        <v>12.01010514638517</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05152083012037</v>
+        <v>12.05151896632442</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798358917236</v>
+        <v>12.35798454284668</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49050931294096</v>
+        <v>12.49051027684238</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293297380614</v>
+        <v>12.09293390702631</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485319844393</v>
+        <v>12.32485414956155</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3292,16 +3292,16 @@
         <v>44524</v>
       </c>
       <c r="B144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="C144" t="n">
-        <v>12.89636829992451</v>
+        <v>12.89636928852036</v>
       </c>
       <c r="D144" t="n">
-        <v>12.44081211090088</v>
+        <v>12.4408130645752</v>
       </c>
       <c r="E144" t="n">
-        <v>12.83010502169696</v>
+        <v>12.83010600521327</v>
       </c>
       <c r="F144" t="n">
         <v>166874</v>
@@ -3312,16 +3312,16 @@
         <v>44525</v>
       </c>
       <c r="B145" t="n">
-        <v>12.83010482788086</v>
+        <v>12.83010578155518</v>
       </c>
       <c r="C145" t="n">
-        <v>12.83010482788086</v>
+        <v>12.83010578155518</v>
       </c>
       <c r="D145" t="n">
-        <v>12.38283207549919</v>
+        <v>12.38283299592728</v>
       </c>
       <c r="E145" t="n">
-        <v>12.63131749271409</v>
+        <v>12.63131843161235</v>
       </c>
       <c r="F145" t="n">
         <v>155812</v>
@@ -3332,16 +3332,16 @@
         <v>44526</v>
       </c>
       <c r="B146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="C146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="D146" t="n">
-        <v>12.05151921605237</v>
+        <v>12.05152102990341</v>
       </c>
       <c r="E146" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="F146" t="n">
         <v>386739</v>
@@ -3352,16 +3352,16 @@
         <v>44529</v>
       </c>
       <c r="B147" t="n">
-        <v>12.67273235321045</v>
+        <v>12.67273426055908</v>
       </c>
       <c r="C147" t="n">
-        <v>12.98747938848116</v>
+        <v>12.98748134320176</v>
       </c>
       <c r="D147" t="n">
-        <v>12.35798365359779</v>
+        <v>12.3579855135742</v>
       </c>
       <c r="E147" t="n">
-        <v>12.75555916263431</v>
+        <v>12.75556108244904</v>
       </c>
       <c r="F147" t="n">
         <v>340279</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455081939697</v>
+        <v>12.37454986572266</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90242939089549</v>
+        <v>11.90242847360634</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3392,16 +3392,16 @@
         <v>44531</v>
       </c>
       <c r="B149" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C149" t="n">
-        <v>12.58990653950131</v>
+        <v>12.58990549663439</v>
       </c>
       <c r="D149" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E149" t="n">
-        <v>12.37455229577492</v>
+        <v>12.37455127074656</v>
       </c>
       <c r="F149" t="n">
         <v>554877</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768081665039</v>
+        <v>11.58768177032471</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67050929318926</v>
+        <v>11.67051025368041</v>
       </c>
       <c r="D151" t="n">
-        <v>11.24808514466335</v>
+        <v>11.2480860703887</v>
       </c>
       <c r="E151" t="n">
-        <v>11.3391962192048</v>
+        <v>11.33919715242866</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3492,16 +3492,16 @@
         <v>44538</v>
       </c>
       <c r="B154" t="n">
-        <v>12.23374366760254</v>
+        <v>12.23374271392822</v>
       </c>
       <c r="C154" t="n">
-        <v>12.36626857588447</v>
+        <v>12.36626761187925</v>
       </c>
       <c r="D154" t="n">
-        <v>11.8941471338307</v>
+        <v>11.89414620662944</v>
       </c>
       <c r="E154" t="n">
-        <v>12.01010684466293</v>
+        <v>12.0101059084221</v>
       </c>
       <c r="F154" t="n">
         <v>204483</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000400543213</v>
+        <v>12.30000495910645</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626728482618</v>
+        <v>12.36626824363818</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778185948322</v>
+        <v>12.11778279902904</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668727818206</v>
+        <v>12.2668737329261</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485485076904</v>
+        <v>12.32485294342041</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303589683919</v>
+        <v>12.62303394334516</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374376753817</v>
+        <v>12.23374187428955</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000539004934</v>
+        <v>12.30000348654632</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3612,16 +3612,16 @@
         <v>44546</v>
       </c>
       <c r="B160" t="n">
-        <v>12.43253040313721</v>
+        <v>12.43252849578857</v>
       </c>
       <c r="C160" t="n">
-        <v>12.56505530473681</v>
+        <v>12.56505337705674</v>
       </c>
       <c r="D160" t="n">
-        <v>12.31657153032308</v>
+        <v>12.31656964076438</v>
       </c>
       <c r="E160" t="n">
-        <v>12.54849010812237</v>
+        <v>12.54848818298367</v>
       </c>
       <c r="F160" t="n">
         <v>252523</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202602386475</v>
+        <v>13.06202507019043</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16142053736261</v>
+        <v>13.16141957643138</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273389729204</v>
+        <v>12.67273297204042</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273389729204</v>
+        <v>12.67273297204042</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.7224292755127</v>
+        <v>12.72242832183838</v>
       </c>
       <c r="C163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.06202397044703</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737864826929</v>
+        <v>12.45737771446318</v>
       </c>
       <c r="E163" t="n">
-        <v>13.06202494957747</v>
+        <v>13.06202397044703</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3712,16 +3712,16 @@
         <v>44553</v>
       </c>
       <c r="B165" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838844299316</v>
       </c>
       <c r="C165" t="n">
-        <v>12.85495625873149</v>
+        <v>12.85495530382653</v>
       </c>
       <c r="D165" t="n">
-        <v>12.54020834813482</v>
+        <v>12.54020741661029</v>
       </c>
       <c r="E165" t="n">
-        <v>12.81354160008474</v>
+        <v>12.8135406482562</v>
       </c>
       <c r="F165" t="n">
         <v>1292325</v>
@@ -3732,16 +3732,16 @@
         <v>44557</v>
       </c>
       <c r="B166" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="C166" t="n">
-        <v>13.12828770746268</v>
+        <v>13.1282896208473</v>
       </c>
       <c r="D166" t="n">
-        <v>12.76384342158722</v>
+        <v>12.76384528185584</v>
       </c>
       <c r="E166" t="n">
-        <v>12.8383876332676</v>
+        <v>12.83838950440068</v>
       </c>
       <c r="F166" t="n">
         <v>193738</v>
@@ -3752,16 +3752,16 @@
         <v>44558</v>
       </c>
       <c r="B167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="C167" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970344767048</v>
       </c>
       <c r="D167" t="n">
-        <v>12.9212161070132</v>
+        <v>12.92121799021813</v>
       </c>
       <c r="E167" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="F167" t="n">
         <v>213754</v>
@@ -3772,16 +3772,16 @@
         <v>44559</v>
       </c>
       <c r="B168" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="C168" t="n">
-        <v>13.3767722965285</v>
+        <v>13.37677424612855</v>
       </c>
       <c r="D168" t="n">
-        <v>13.04545923371708</v>
+        <v>13.04546113502985</v>
       </c>
       <c r="E168" t="n">
-        <v>13.16970152824999</v>
+        <v>13.16970344767048</v>
       </c>
       <c r="F168" t="n">
         <v>271486</v>
@@ -3792,16 +3792,16 @@
         <v>44560</v>
       </c>
       <c r="B169" t="n">
-        <v>13.13656997680664</v>
+        <v>13.13657093048096</v>
       </c>
       <c r="C169" t="n">
-        <v>13.33535814239271</v>
+        <v>13.33535911049843</v>
       </c>
       <c r="D169" t="n">
-        <v>13.10343792239983</v>
+        <v>13.10343887366887</v>
       </c>
       <c r="E169" t="n">
-        <v>13.21111585096552</v>
+        <v>13.21111681005164</v>
       </c>
       <c r="F169" t="n">
         <v>310044</v>
@@ -3852,16 +3852,16 @@
         <v>44566</v>
       </c>
       <c r="B172" t="n">
-        <v>11.61252975463867</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="C172" t="n">
-        <v>12.39939733389957</v>
+        <v>12.39939835219506</v>
       </c>
       <c r="D172" t="n">
-        <v>11.61252975463867</v>
+        <v>11.61253070831299</v>
       </c>
       <c r="E172" t="n">
-        <v>12.3579835135714</v>
+        <v>12.35798452846581</v>
       </c>
       <c r="F172" t="n">
         <v>223973</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616441649305</v>
+        <v>11.83616633728321</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47171934249647</v>
+        <v>11.47172120414394</v>
       </c>
       <c r="E173" t="n">
-        <v>11.637376269965</v>
+        <v>11.63737815849552</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.69535827636719</v>
+        <v>11.6953592300415</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78646935368979</v>
+        <v>11.78647031479358</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657009304013</v>
+        <v>11.49657103050467</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333812849712</v>
+        <v>11.75333908689929</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3912,16 +3912,16 @@
         <v>44571</v>
       </c>
       <c r="B175" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C175" t="n">
-        <v>11.88586369832469</v>
+        <v>11.88586465533357</v>
       </c>
       <c r="D175" t="n">
-        <v>11.42202488765067</v>
+        <v>11.42202580731284</v>
       </c>
       <c r="E175" t="n">
-        <v>11.55454978660266</v>
+        <v>11.55455071693529</v>
       </c>
       <c r="F175" t="n">
         <v>157076</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727547694948</v>
+        <v>11.92727741252527</v>
       </c>
       <c r="D176" t="n">
-        <v>11.6125284797985</v>
+        <v>11.61253036429669</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444701321522</v>
+        <v>11.84444893534948</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838653740591</v>
+        <v>12.01838848776734</v>
       </c>
       <c r="D177" t="n">
-        <v>11.64565886668716</v>
+        <v>11.6456607565618</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818457509616</v>
+        <v>11.77818648647726</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3972,16 +3972,16 @@
         <v>44574</v>
       </c>
       <c r="B178" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C178" t="n">
-        <v>11.91071108497109</v>
+        <v>11.91071205965744</v>
       </c>
       <c r="D178" t="n">
-        <v>11.59596404465037</v>
+        <v>11.5959649935801</v>
       </c>
       <c r="E178" t="n">
-        <v>11.85273123562185</v>
+        <v>11.85273220556355</v>
       </c>
       <c r="F178" t="n">
         <v>225659</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131579415569</v>
+        <v>11.81131771091337</v>
       </c>
       <c r="D179" t="n">
-        <v>11.52970001606424</v>
+        <v>11.5297018871209</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67050748902453</v>
+        <v>11.67050938293163</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4032,16 +4032,16 @@
         <v>44579</v>
       </c>
       <c r="B181" t="n">
-        <v>11.49657154083252</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="C181" t="n">
-        <v>11.72020837925999</v>
+        <v>11.72020643480869</v>
       </c>
       <c r="D181" t="n">
-        <v>11.46344031146755</v>
+        <v>11.46343840961558</v>
       </c>
       <c r="E181" t="n">
-        <v>11.57940003033051</v>
+        <v>11.57939810924015</v>
       </c>
       <c r="F181" t="n">
         <v>311203</v>
@@ -4112,16 +4112,16 @@
         <v>44585</v>
       </c>
       <c r="B185" t="n">
-        <v>11.57111644744873</v>
+        <v>11.5711145401001</v>
       </c>
       <c r="C185" t="n">
-        <v>11.86101488779268</v>
+        <v>11.86101293265804</v>
       </c>
       <c r="D185" t="n">
-        <v>11.48828796499143</v>
+        <v>11.488286071296</v>
       </c>
       <c r="E185" t="n">
-        <v>11.68707615645473</v>
+        <v>11.68707422999165</v>
       </c>
       <c r="F185" t="n">
         <v>280651</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616733551025</v>
+        <v>11.83616638183594</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444993427506</v>
+        <v>11.84444897993339</v>
       </c>
       <c r="D186" t="n">
-        <v>11.46343957286996</v>
+        <v>11.4634386492274</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172217163477</v>
+        <v>11.47172124732486</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4152,16 +4152,16 @@
         <v>44587</v>
       </c>
       <c r="B187" t="n">
-        <v>11.01616668701172</v>
+        <v>11.01616477966309</v>
       </c>
       <c r="C187" t="n">
-        <v>12.08465187904177</v>
+        <v>12.08464978669469</v>
       </c>
       <c r="D187" t="n">
-        <v>10.90020697635688</v>
+        <v>10.90020508908562</v>
       </c>
       <c r="E187" t="n">
-        <v>11.88586451692297</v>
+        <v>11.88586245899411</v>
       </c>
       <c r="F187" t="n">
         <v>1763028</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747886657715</v>
+        <v>11.34747982025146</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374131522813</v>
+        <v>11.41374227447133</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242823980222</v>
+        <v>11.08242917120093</v>
       </c>
       <c r="E188" t="n">
-        <v>11.1818227449497</v>
+        <v>11.1818236847018</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4212,16 +4212,16 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C190" t="n">
-        <v>11.78646910353603</v>
+        <v>11.78647006600311</v>
       </c>
       <c r="D190" t="n">
-        <v>11.45515602647001</v>
+        <v>11.45515696188252</v>
       </c>
       <c r="E190" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="F190" t="n">
         <v>318367</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.4882869720459</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84444866687487</v>
+        <v>11.84444965011515</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4882869720459</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67050911839965</v>
+        <v>11.67051008720073</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4332,16 +4332,16 @@
         <v>44600</v>
       </c>
       <c r="B196" t="n">
-        <v>11.5959644317627</v>
+        <v>11.59596347808838</v>
       </c>
       <c r="C196" t="n">
-        <v>11.97697476418123</v>
+        <v>11.97697377917189</v>
       </c>
       <c r="D196" t="n">
-        <v>11.52970198234322</v>
+        <v>11.52970103411845</v>
       </c>
       <c r="E196" t="n">
-        <v>11.70364153619761</v>
+        <v>11.70364057366772</v>
       </c>
       <c r="F196" t="n">
         <v>170034</v>
@@ -4352,16 +4352,16 @@
         <v>44601</v>
       </c>
       <c r="B197" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="C197" t="n">
-        <v>11.84444904327393</v>
+        <v>11.84444999694824</v>
       </c>
       <c r="D197" t="n">
-        <v>11.51313596372292</v>
+        <v>11.51313689072104</v>
       </c>
       <c r="E197" t="n">
-        <v>11.59596444165342</v>
+        <v>11.59596537532062</v>
       </c>
       <c r="F197" t="n">
         <v>125366</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788372039795</v>
+        <v>11.82788181304932</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84444974984068</v>
+        <v>11.84444783982064</v>
       </c>
       <c r="D198" t="n">
-        <v>11.62909636011153</v>
+        <v>11.62909448481908</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84444974984068</v>
+        <v>11.84444783982064</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444909778491</v>
+        <v>11.8444500711998</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313601670912</v>
+        <v>11.51313696289563</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253052355157</v>
+        <v>11.61253147790664</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.69535827636719</v>
+        <v>11.6953592300415</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81960154268786</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394362074808</v>
+        <v>11.65394457104532</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960057888246</v>
+        <v>11.81960154268786</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4492,16 +4492,16 @@
         <v>44610</v>
       </c>
       <c r="B204" t="n">
-        <v>11.92727661132812</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="C204" t="n">
-        <v>11.92727661132812</v>
+        <v>11.92727756500244</v>
       </c>
       <c r="D204" t="n">
-        <v>11.48000303105801</v>
+        <v>11.48000394896948</v>
       </c>
       <c r="E204" t="n">
-        <v>11.76161966810431</v>
+        <v>11.76162060853312</v>
       </c>
       <c r="F204" t="n">
         <v>336065</v>
@@ -4512,16 +4512,16 @@
         <v>44613</v>
       </c>
       <c r="B205" t="n">
-        <v>11.49657154083252</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="C205" t="n">
-        <v>11.92727918691941</v>
+        <v>11.92727720811385</v>
       </c>
       <c r="D205" t="n">
-        <v>11.49657154083252</v>
+        <v>11.49656963348389</v>
       </c>
       <c r="E205" t="n">
-        <v>11.92727918691941</v>
+        <v>11.92727720811385</v>
       </c>
       <c r="F205" t="n">
         <v>449843</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899204805644</v>
+        <v>11.91899398228799</v>
       </c>
       <c r="D207" t="n">
-        <v>11.54626520950857</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="E207" t="n">
-        <v>11.54626520950857</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4592,16 +4592,16 @@
         <v>44617</v>
       </c>
       <c r="B209" t="n">
-        <v>11.99353885650635</v>
+        <v>11.99353981018066</v>
       </c>
       <c r="C209" t="n">
-        <v>12.31657014007771</v>
+        <v>12.31657111943808</v>
       </c>
       <c r="D209" t="n">
-        <v>11.8195993186622</v>
+        <v>11.8196002585056</v>
       </c>
       <c r="E209" t="n">
-        <v>12.09293252148689</v>
+        <v>12.09293348306456</v>
       </c>
       <c r="F209" t="n">
         <v>373254</v>
@@ -4612,16 +4612,16 @@
         <v>44622</v>
       </c>
       <c r="B210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="C210" t="n">
-        <v>13.08687305450439</v>
+        <v>13.08687496185303</v>
       </c>
       <c r="D210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.01010714273947</v>
       </c>
       <c r="E210" t="n">
-        <v>12.01010539232453</v>
+        <v>12.01010714273947</v>
       </c>
       <c r="F210" t="n">
         <v>455216</v>
@@ -4632,16 +4632,16 @@
         <v>44623</v>
       </c>
       <c r="B211" t="n">
-        <v>12.70586204528809</v>
+        <v>12.70586395263672</v>
       </c>
       <c r="C211" t="n">
-        <v>13.12828698860901</v>
+        <v>13.12828895937023</v>
       </c>
       <c r="D211" t="n">
-        <v>12.59818578426862</v>
+        <v>12.59818767545336</v>
       </c>
       <c r="E211" t="n">
-        <v>13.12828698860901</v>
+        <v>13.12828895937023</v>
       </c>
       <c r="F211" t="n">
         <v>452688</v>
@@ -4652,16 +4652,16 @@
         <v>44624</v>
       </c>
       <c r="B212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838844299316</v>
       </c>
       <c r="C212" t="n">
-        <v>12.83838939666748</v>
+        <v>12.83838844299316</v>
       </c>
       <c r="D212" t="n">
-        <v>12.30000549162855</v>
+        <v>12.30000457794701</v>
       </c>
       <c r="E212" t="n">
-        <v>12.70586448620852</v>
+        <v>12.70586354237855</v>
       </c>
       <c r="F212" t="n">
         <v>696467</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081198328363</v>
+        <v>12.44081293822948</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293289679869</v>
+        <v>12.09293382504164</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576136960524</v>
+        <v>12.17576230420604</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="C216" t="n">
-        <v>12.4242467880249</v>
+        <v>12.42424774169922</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919617434651</v>
+        <v>12.15919710767578</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111473316551</v>
+        <v>12.39111568429664</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242825840982</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242825840982</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141952514648</v>
+        <v>11.52141857147217</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303620722139</v>
+        <v>11.80303523023652</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515707013042</v>
+        <v>11.45515612194091</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626815382028</v>
+        <v>11.54626719808914</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4812,16 +4812,16 @@
         <v>44636</v>
       </c>
       <c r="B220" t="n">
-        <v>11.794753074646</v>
+        <v>11.79475212097168</v>
       </c>
       <c r="C220" t="n">
-        <v>11.80303567310543</v>
+        <v>11.80303471876141</v>
       </c>
       <c r="D220" t="n">
-        <v>11.46343915021626</v>
+        <v>11.4634382233306</v>
       </c>
       <c r="E220" t="n">
-        <v>11.59596488642237</v>
+        <v>11.59596394882123</v>
       </c>
       <c r="F220" t="n">
         <v>237669</v>
@@ -4832,16 +4832,16 @@
         <v>44637</v>
       </c>
       <c r="B221" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="C221" t="n">
-        <v>11.80303712072899</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="D221" t="n">
-        <v>11.51313781738281</v>
+        <v>11.5131368637085</v>
       </c>
       <c r="E221" t="n">
-        <v>11.80303712072899</v>
+        <v>11.80303614304128</v>
       </c>
       <c r="F221" t="n">
         <v>333116</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222763061523</v>
+        <v>11.6622257232666</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444979431419</v>
+        <v>11.84444785716326</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404575689492</v>
+        <v>11.36404389831371</v>
       </c>
       <c r="E222" t="n">
-        <v>11.53798532192695</v>
+        <v>11.53798343489805</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4872,16 +4872,16 @@
         <v>44641</v>
       </c>
       <c r="B223" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C223" t="n">
-        <v>11.75333787904653</v>
+        <v>11.75333883880816</v>
       </c>
       <c r="D223" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="E223" t="n">
-        <v>11.69535802814715</v>
+        <v>11.69535898317423</v>
       </c>
       <c r="F223" t="n">
         <v>273488</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475060071136</v>
+        <v>11.79475251478082</v>
       </c>
       <c r="D224" t="n">
-        <v>11.5793964285681</v>
+        <v>11.57939830768957</v>
       </c>
       <c r="E224" t="n">
-        <v>11.67879008574669</v>
+        <v>11.67879198099791</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4912,16 +4912,16 @@
         <v>44643</v>
       </c>
       <c r="B225" t="n">
-        <v>11.96869277954102</v>
+        <v>11.9686918258667</v>
       </c>
       <c r="C225" t="n">
-        <v>12.20889396295617</v>
+        <v>12.20889299014245</v>
       </c>
       <c r="D225" t="n">
-        <v>11.53798517189504</v>
+        <v>11.53798425253982</v>
       </c>
       <c r="E225" t="n">
-        <v>11.73677253034297</v>
+        <v>11.73677159514823</v>
       </c>
       <c r="F225" t="n">
         <v>470070</v>
@@ -4932,16 +4932,16 @@
         <v>44644</v>
       </c>
       <c r="B226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="C226" t="n">
-        <v>12.10949925876433</v>
+        <v>12.10950024971806</v>
       </c>
       <c r="D226" t="n">
-        <v>11.65394306182861</v>
+        <v>11.65394401550293</v>
       </c>
       <c r="E226" t="n">
-        <v>12.03495338152774</v>
+        <v>12.03495436638118</v>
       </c>
       <c r="F226" t="n">
         <v>350498</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78646924618382</v>
+        <v>11.78647021483374</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030753839741</v>
+        <v>11.43030847777682</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535816969225</v>
+        <v>11.69535913085437</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C230" t="n">
-        <v>11.89414566071079</v>
+        <v>11.8941466495024</v>
       </c>
       <c r="D230" t="n">
-        <v>11.35576183119625</v>
+        <v>11.3557627752306</v>
       </c>
       <c r="E230" t="n">
-        <v>11.84444841017465</v>
+        <v>11.84444939483481</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.41374015808105</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283106851614</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23151802667939</v>
+        <v>11.2315199035769</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283106851614</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.41374015808105</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909434262023</v>
+        <v>11.62909628595667</v>
       </c>
       <c r="D232" t="n">
-        <v>11.25636665044706</v>
+        <v>11.25636853149702</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313465315173</v>
+        <v>11.51313657711016</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47172069549561</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283176669787</v>
+        <v>11.56283272794649</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919580362721</v>
+        <v>11.33919674628439</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41374084726044</v>
+        <v>11.41374179611474</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5092,16 +5092,16 @@
         <v>44656</v>
       </c>
       <c r="B234" t="n">
-        <v>11.19010543823242</v>
+        <v>11.19010639190674</v>
       </c>
       <c r="C234" t="n">
-        <v>11.57939836758414</v>
+        <v>11.57939935443586</v>
       </c>
       <c r="D234" t="n">
-        <v>11.19010543823242</v>
+        <v>11.19010639190674</v>
       </c>
       <c r="E234" t="n">
-        <v>11.52141851647829</v>
+        <v>11.52141949838869</v>
       </c>
       <c r="F234" t="n">
         <v>602179</v>
@@ -5112,16 +5112,16 @@
         <v>44657</v>
       </c>
       <c r="B235" t="n">
-        <v>11.02444839477539</v>
+        <v>11.02444934844971</v>
       </c>
       <c r="C235" t="n">
-        <v>11.21495314278623</v>
+        <v>11.21495411294023</v>
       </c>
       <c r="D235" t="n">
-        <v>10.89192349740629</v>
+        <v>10.89192443961648</v>
       </c>
       <c r="E235" t="n">
-        <v>11.21495314278623</v>
+        <v>11.21495411294023</v>
       </c>
       <c r="F235" t="n">
         <v>603022</v>
@@ -5192,16 +5192,16 @@
         <v>44663</v>
       </c>
       <c r="B239" t="n">
-        <v>10.71798515319824</v>
+        <v>10.71798229217529</v>
       </c>
       <c r="C239" t="n">
-        <v>11.00788443907316</v>
+        <v>11.00788150066547</v>
       </c>
       <c r="D239" t="n">
-        <v>10.71798515319824</v>
+        <v>10.71798229217529</v>
       </c>
       <c r="E239" t="n">
-        <v>10.93333855177485</v>
+        <v>10.93333563326619</v>
       </c>
       <c r="F239" t="n">
         <v>330692</v>
@@ -5212,16 +5212,16 @@
         <v>44664</v>
       </c>
       <c r="B240" t="n">
-        <v>10.80909633636475</v>
+        <v>10.80909729003906</v>
       </c>
       <c r="C240" t="n">
-        <v>10.89192482338948</v>
+        <v>10.89192578437166</v>
       </c>
       <c r="D240" t="n">
-        <v>10.65172279353752</v>
+        <v>10.65172373332695</v>
       </c>
       <c r="E240" t="n">
-        <v>10.81737893541589</v>
+        <v>10.81737988982097</v>
       </c>
       <c r="F240" t="n">
         <v>281389</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000270843506</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82565964077266</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000270843506</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82565964077266</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C242" t="n">
-        <v>11.03272981304382</v>
+        <v>11.03273176734258</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172035776503</v>
+        <v>10.65172224457312</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000295492215</v>
+        <v>10.66000484319739</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76767921447754</v>
+        <v>10.76768112182617</v>
       </c>
       <c r="C243" t="n">
-        <v>10.92505355348844</v>
+        <v>10.9250554887138</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000295492215</v>
+        <v>10.66000484319739</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081126744788</v>
+        <v>10.80081318066541</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5312,16 +5312,16 @@
         <v>44673</v>
       </c>
       <c r="B245" t="n">
-        <v>10.23757934570312</v>
+        <v>10.23757839202881</v>
       </c>
       <c r="C245" t="n">
-        <v>10.64343830945661</v>
+        <v>10.6434373179748</v>
       </c>
       <c r="D245" t="n">
-        <v>10.23757934570312</v>
+        <v>10.23757839202881</v>
       </c>
       <c r="E245" t="n">
-        <v>10.64343830945661</v>
+        <v>10.6434373179748</v>
       </c>
       <c r="F245" t="n">
         <v>624092</v>
@@ -5332,16 +5332,16 @@
         <v>44676</v>
       </c>
       <c r="B246" t="n">
-        <v>10.49434757232666</v>
+        <v>10.49434661865234</v>
       </c>
       <c r="C246" t="n">
-        <v>10.51919703181856</v>
+        <v>10.51919607588605</v>
       </c>
       <c r="D246" t="n">
-        <v>10.04707477706429</v>
+        <v>10.04707386403591</v>
       </c>
       <c r="E246" t="n">
-        <v>10.15475105255997</v>
+        <v>10.1547501297465</v>
       </c>
       <c r="F246" t="n">
         <v>524115</v>
@@ -5352,16 +5352,16 @@
         <v>44677</v>
       </c>
       <c r="B247" t="n">
-        <v>10.35353946685791</v>
+        <v>10.35354137420654</v>
       </c>
       <c r="C247" t="n">
-        <v>10.66828650876296</v>
+        <v>10.66828847409488</v>
       </c>
       <c r="D247" t="n">
-        <v>10.35353946685791</v>
+        <v>10.35354137420654</v>
       </c>
       <c r="E247" t="n">
-        <v>10.48606436193982</v>
+        <v>10.48606629370245</v>
       </c>
       <c r="F247" t="n">
         <v>670551</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525680541992</v>
+        <v>10.34525775909424</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061017469088</v>
+        <v>10.56061114821748</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32868994537994</v>
+        <v>10.32869089752705</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151842038292</v>
+        <v>10.41151938016555</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394336700439</v>
+        <v>10.83394527435303</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525643404281</v>
+        <v>11.16525839972011</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576152345272</v>
+        <v>10.53576337830554</v>
       </c>
       <c r="E250" t="n">
-        <v>10.56889274693946</v>
+        <v>10.56889460762513</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5432,16 +5432,16 @@
         <v>44683</v>
       </c>
       <c r="B251" t="n">
-        <v>10.73434543609619</v>
+        <v>10.73434638977051</v>
       </c>
       <c r="C251" t="n">
-        <v>10.9254363391113</v>
+        <v>10.92543730976276</v>
       </c>
       <c r="D251" t="n">
-        <v>10.41032020669135</v>
+        <v>10.41032113157821</v>
       </c>
       <c r="E251" t="n">
-        <v>10.88389425777308</v>
+        <v>10.8838952247338</v>
       </c>
       <c r="F251" t="n">
         <v>324898</v>
@@ -5452,16 +5452,16 @@
         <v>44684</v>
       </c>
       <c r="B252" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C252" t="n">
-        <v>10.72603559055428</v>
+        <v>10.72603654719261</v>
       </c>
       <c r="D252" t="n">
-        <v>10.51001962438067</v>
+        <v>10.51002056175287</v>
       </c>
       <c r="E252" t="n">
-        <v>10.71772667416696</v>
+        <v>10.71772763006424</v>
       </c>
       <c r="F252" t="n">
         <v>311097</v>
@@ -5472,16 +5472,16 @@
         <v>44685</v>
       </c>
       <c r="B253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90051078796387</v>
       </c>
       <c r="C253" t="n">
-        <v>10.90051174163818</v>
+        <v>10.90051078796387</v>
       </c>
       <c r="D253" t="n">
-        <v>10.48509591818506</v>
+        <v>10.48509500085503</v>
       </c>
       <c r="E253" t="n">
-        <v>10.69280382991162</v>
+        <v>10.69280289440945</v>
       </c>
       <c r="F253" t="n">
         <v>328902</v>
@@ -5512,16 +5512,16 @@
         <v>44687</v>
       </c>
       <c r="B255" t="n">
-        <v>10.85066032409668</v>
+        <v>10.850661277771</v>
       </c>
       <c r="C255" t="n">
-        <v>11.03344396650661</v>
+        <v>11.03344493624595</v>
       </c>
       <c r="D255" t="n">
-        <v>10.62633543802578</v>
+        <v>10.62633637198398</v>
       </c>
       <c r="E255" t="n">
-        <v>10.71772684186504</v>
+        <v>10.71772778385571</v>
       </c>
       <c r="F255" t="n">
         <v>382946</v>
@@ -5532,16 +5532,16 @@
         <v>44690</v>
       </c>
       <c r="B256" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C256" t="n">
-        <v>10.95036047311521</v>
+        <v>10.95036144976073</v>
       </c>
       <c r="D256" t="n">
-        <v>10.61802719010177</v>
+        <v>10.618028137107</v>
       </c>
       <c r="E256" t="n">
-        <v>10.95036047311521</v>
+        <v>10.95036144976073</v>
       </c>
       <c r="F256" t="n">
         <v>340595</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389415417323</v>
+        <v>10.88389316500986</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727798958128</v>
+        <v>10.86727700192804</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5572,16 +5572,16 @@
         <v>44692</v>
       </c>
       <c r="B258" t="n">
-        <v>10.6263370513916</v>
+        <v>10.62633609771729</v>
       </c>
       <c r="C258" t="n">
-        <v>10.8008118037742</v>
+        <v>10.80081083444142</v>
       </c>
       <c r="D258" t="n">
-        <v>10.46848013456669</v>
+        <v>10.46847919505945</v>
       </c>
       <c r="E258" t="n">
-        <v>10.51002138453475</v>
+        <v>10.51002044129933</v>
       </c>
       <c r="F258" t="n">
         <v>211647</v>
@@ -5592,16 +5592,16 @@
         <v>44693</v>
       </c>
       <c r="B259" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="C259" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="D259" t="n">
-        <v>10.36046917836759</v>
+        <v>10.36047010025277</v>
       </c>
       <c r="E259" t="n">
-        <v>10.53494390207218</v>
+        <v>10.5349448394823</v>
       </c>
       <c r="F259" t="n">
         <v>307094</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.16637706756592</v>
+        <v>11.1663761138916</v>
       </c>
       <c r="C261" t="n">
-        <v>11.16637706756592</v>
+        <v>11.1663761138916</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75926935728049</v>
+        <v>10.75926843837557</v>
       </c>
       <c r="E261" t="n">
-        <v>10.87558584593347</v>
+        <v>10.87558491709443</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5652,16 +5652,16 @@
         <v>44698</v>
       </c>
       <c r="B262" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C262" t="n">
-        <v>11.34085115716256</v>
+        <v>11.34085213080912</v>
       </c>
       <c r="D262" t="n">
-        <v>10.95866854966046</v>
+        <v>10.95866949049548</v>
       </c>
       <c r="E262" t="n">
-        <v>11.15806751769784</v>
+        <v>11.15806847565188</v>
       </c>
       <c r="F262" t="n">
         <v>414340</v>
@@ -5712,16 +5712,16 @@
         <v>44701</v>
       </c>
       <c r="B265" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="C265" t="n">
-        <v>11.32423415912707</v>
+        <v>11.32423513134702</v>
       </c>
       <c r="D265" t="n">
-        <v>11.1082181930542</v>
+        <v>11.10821914672852</v>
       </c>
       <c r="E265" t="n">
-        <v>11.29100099778751</v>
+        <v>11.29100196715428</v>
       </c>
       <c r="F265" t="n">
         <v>265902</v>
@@ -5732,16 +5732,16 @@
         <v>44704</v>
       </c>
       <c r="B266" t="n">
-        <v>10.9669771194458</v>
+        <v>10.96697616577148</v>
       </c>
       <c r="C266" t="n">
-        <v>11.19961009390851</v>
+        <v>11.19960912000472</v>
       </c>
       <c r="D266" t="n">
-        <v>10.72603606296127</v>
+        <v>10.72603513023888</v>
       </c>
       <c r="E266" t="n">
-        <v>11.14975993231466</v>
+        <v>11.14975896274578</v>
       </c>
       <c r="F266" t="n">
         <v>653906</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.16637706756592</v>
+        <v>11.1663761138916</v>
       </c>
       <c r="C267" t="n">
-        <v>11.16637706756592</v>
+        <v>11.1663761138916</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772727720074</v>
+        <v>10.71772636184375</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05006057891294</v>
+        <v>11.05005963517273</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190330505371</v>
+        <v>10.99190235137939</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="D268" t="n">
-        <v>10.892202971845</v>
+        <v>10.89220202682084</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961121959649</v>
+        <v>11.19961024790112</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5792,16 +5792,16 @@
         <v>44707</v>
       </c>
       <c r="B269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="C269" t="n">
-        <v>11.1913013458252</v>
+        <v>11.19130229949951</v>
       </c>
       <c r="D269" t="n">
-        <v>10.8672769842127</v>
+        <v>10.86727791027506</v>
       </c>
       <c r="E269" t="n">
-        <v>11.0168266253622</v>
+        <v>11.01682756416854</v>
       </c>
       <c r="F269" t="n">
         <v>244832</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085178375244</v>
+        <v>11.34085273742676</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085178375244</v>
+        <v>11.34085273742676</v>
       </c>
       <c r="D272" t="n">
-        <v>11.1331438878556</v>
+        <v>11.13314482406336</v>
       </c>
       <c r="E272" t="n">
-        <v>11.2494595416049</v>
+        <v>11.24946048759386</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5872,16 +5872,16 @@
         <v>44713</v>
       </c>
       <c r="B273" t="n">
-        <v>11.34916019439697</v>
+        <v>11.34916114807129</v>
       </c>
       <c r="C273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39901131583258</v>
       </c>
       <c r="D273" t="n">
-        <v>11.19961053841137</v>
+        <v>11.19961147951897</v>
       </c>
       <c r="E273" t="n">
-        <v>11.39901035796933</v>
+        <v>11.39901131583258</v>
       </c>
       <c r="F273" t="n">
         <v>181096</v>
@@ -5892,16 +5892,16 @@
         <v>44714</v>
       </c>
       <c r="B274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622848510742</v>
       </c>
       <c r="C274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916115288518</v>
       </c>
       <c r="D274" t="n">
-        <v>11.21622657775879</v>
+        <v>11.21622848510742</v>
       </c>
       <c r="E274" t="n">
-        <v>11.349159222931</v>
+        <v>11.34916115288518</v>
       </c>
       <c r="F274" t="n">
         <v>186890</v>
@@ -5912,16 +5912,16 @@
         <v>44715</v>
       </c>
       <c r="B275" t="n">
-        <v>10.91712856292725</v>
+        <v>10.91712760925293</v>
       </c>
       <c r="C275" t="n">
-        <v>11.24946021456504</v>
+        <v>11.24945923185963</v>
       </c>
       <c r="D275" t="n">
-        <v>10.90051156297961</v>
+        <v>10.90051061075688</v>
       </c>
       <c r="E275" t="n">
-        <v>11.21622788413276</v>
+        <v>11.21622690433039</v>
       </c>
       <c r="F275" t="n">
         <v>120309</v>
@@ -5932,16 +5932,16 @@
         <v>44718</v>
       </c>
       <c r="B276" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C276" t="n">
-        <v>11.03344526976758</v>
+        <v>11.03344429480254</v>
       </c>
       <c r="D276" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="E276" t="n">
-        <v>11.0085201867343</v>
+        <v>11.00851921397176</v>
       </c>
       <c r="F276" t="n">
         <v>166979</v>
@@ -5992,16 +5992,16 @@
         <v>44721</v>
       </c>
       <c r="B279" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C279" t="n">
-        <v>10.82573590935088</v>
+        <v>10.82573687488132</v>
       </c>
       <c r="D279" t="n">
-        <v>10.62633527175769</v>
+        <v>10.6263362195039</v>
       </c>
       <c r="E279" t="n">
-        <v>10.79250191326441</v>
+        <v>10.79250287583077</v>
       </c>
       <c r="F279" t="n">
         <v>205537</v>
@@ -6052,16 +6052,16 @@
         <v>44726</v>
       </c>
       <c r="B282" t="n">
-        <v>10.21092224121094</v>
+        <v>10.21092128753662</v>
       </c>
       <c r="C282" t="n">
-        <v>10.46848033314689</v>
+        <v>10.4684793554173</v>
       </c>
       <c r="D282" t="n">
-        <v>10.10291298588943</v>
+        <v>10.10291204230291</v>
       </c>
       <c r="E282" t="n">
-        <v>10.46017224994199</v>
+        <v>10.46017127298836</v>
       </c>
       <c r="F282" t="n">
         <v>156655</v>
@@ -6072,16 +6072,16 @@
         <v>44727</v>
       </c>
       <c r="B283" t="n">
-        <v>10.29400444030762</v>
+        <v>10.2940034866333</v>
       </c>
       <c r="C283" t="n">
-        <v>10.36877885035474</v>
+        <v>10.36877788975305</v>
       </c>
       <c r="D283" t="n">
-        <v>10.16107095005616</v>
+        <v>10.16107000869729</v>
       </c>
       <c r="E283" t="n">
-        <v>10.29400444030762</v>
+        <v>10.2940034866333</v>
       </c>
       <c r="F283" t="n">
         <v>138113</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911820411682129</v>
+        <v>9.911822319030762</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21922862107171</v>
+        <v>10.21923058757544</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787195845454841</v>
+        <v>9.787197728821756</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783721685627</v>
+        <v>10.12783916577339</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6152,16 +6152,16 @@
         <v>44734</v>
       </c>
       <c r="B287" t="n">
-        <v>9.83704662322998</v>
+        <v>9.837047576904297</v>
       </c>
       <c r="C287" t="n">
-        <v>10.13614593484008</v>
+        <v>10.13614691751124</v>
       </c>
       <c r="D287" t="n">
-        <v>9.820429623815432</v>
+        <v>9.820430575878776</v>
       </c>
       <c r="E287" t="n">
-        <v>9.920129116108306</v>
+        <v>9.920130077837239</v>
       </c>
       <c r="F287" t="n">
         <v>227344</v>
@@ -6192,16 +6192,16 @@
         <v>44736</v>
       </c>
       <c r="B289" t="n">
-        <v>9.388398170471191</v>
+        <v>9.388397216796875</v>
       </c>
       <c r="C289" t="n">
-        <v>9.795505913764142</v>
+        <v>9.795504918735785</v>
       </c>
       <c r="D289" t="n">
-        <v>9.388398170471191</v>
+        <v>9.388397216796875</v>
       </c>
       <c r="E289" t="n">
-        <v>9.695805581274389</v>
+        <v>9.6958045963736</v>
       </c>
       <c r="F289" t="n">
         <v>325741</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.164071083068848</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496405321144287</v>
+        <v>9.496404332885158</v>
       </c>
       <c r="D291" t="n">
-        <v>9.164072036743164</v>
+        <v>9.164071083068848</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488097239453682</v>
+        <v>9.488096252059146</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.898205757141113</v>
+        <v>8.898207664489746</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039447317111145</v>
+        <v>9.039449254735196</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657264714402972</v>
+        <v>8.657266570105399</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823430519016487</v>
+        <v>8.823432410336896</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6352,16 +6352,16 @@
         <v>44748</v>
       </c>
       <c r="B297" t="n">
-        <v>9.080988883972168</v>
+        <v>9.080989837646484</v>
       </c>
       <c r="C297" t="n">
-        <v>9.24715552925287</v>
+        <v>9.247156500377804</v>
       </c>
       <c r="D297" t="n">
-        <v>8.923131155267498</v>
+        <v>8.923132092363788</v>
       </c>
       <c r="E297" t="n">
-        <v>9.031139558173097</v>
+        <v>9.031140506612298</v>
       </c>
       <c r="F297" t="n">
         <v>199743</v>
@@ -6372,16 +6372,16 @@
         <v>44749</v>
       </c>
       <c r="B298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="C298" t="n">
-        <v>9.355164883523981</v>
+        <v>9.355163898352176</v>
       </c>
       <c r="D298" t="n">
-        <v>9.056065559387207</v>
+        <v>9.056064605712891</v>
       </c>
       <c r="E298" t="n">
-        <v>9.230540304255577</v>
+        <v>9.230539332207711</v>
       </c>
       <c r="F298" t="n">
         <v>150966</v>
@@ -6512,16 +6512,16 @@
         <v>44760</v>
       </c>
       <c r="B305" t="n">
-        <v>8.57418155670166</v>
+        <v>8.574182510375977</v>
       </c>
       <c r="C305" t="n">
-        <v>8.723731201044597</v>
+        <v>8.723732171352765</v>
       </c>
       <c r="D305" t="n">
-        <v>8.482790153754944</v>
+        <v>8.482791097264135</v>
       </c>
       <c r="E305" t="n">
-        <v>8.58249047313784</v>
+        <v>8.582491427736327</v>
       </c>
       <c r="F305" t="n">
         <v>154548</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039446830749512</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039447784423828</v>
+        <v>9.039446830749512</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815121963176683</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815122893184411</v>
+        <v>8.815121963176683</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6632,16 +6632,16 @@
         <v>44768</v>
       </c>
       <c r="B311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="C311" t="n">
-        <v>9.122532260843132</v>
+        <v>9.122531267357015</v>
       </c>
       <c r="D311" t="n">
-        <v>8.756966590881348</v>
+        <v>8.756965637207031</v>
       </c>
       <c r="E311" t="n">
-        <v>9.039448926379578</v>
+        <v>9.039447941941624</v>
       </c>
       <c r="F311" t="n">
         <v>167716</v>
@@ -6712,16 +6712,16 @@
         <v>44774</v>
       </c>
       <c r="B315" t="n">
-        <v>8.923131942749023</v>
+        <v>8.92313289642334</v>
       </c>
       <c r="C315" t="n">
-        <v>9.122531767736954</v>
+        <v>9.122532742722452</v>
       </c>
       <c r="D315" t="n">
-        <v>8.864973695241357</v>
+        <v>8.864974642699915</v>
       </c>
       <c r="E315" t="n">
-        <v>9.122531767736954</v>
+        <v>9.122532742722452</v>
       </c>
       <c r="F315" t="n">
         <v>159078</v>
@@ -6752,16 +6752,16 @@
         <v>44776</v>
       </c>
       <c r="B317" t="n">
-        <v>8.939746856689453</v>
+        <v>8.93974781036377</v>
       </c>
       <c r="C317" t="n">
-        <v>9.172378957707652</v>
+        <v>9.172379936198697</v>
       </c>
       <c r="D317" t="n">
-        <v>8.939746856689453</v>
+        <v>8.93974781036377</v>
       </c>
       <c r="E317" t="n">
-        <v>9.114220723770277</v>
+        <v>9.114221696057117</v>
       </c>
       <c r="F317" t="n">
         <v>188470</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.38008975982666</v>
+        <v>9.380088806152344</v>
       </c>
       <c r="C319" t="n">
-        <v>9.52963943191118</v>
+        <v>9.529638463032139</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197306920026865</v>
+        <v>9.197305984936092</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305315341150182</v>
+        <v>9.305314395078184</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513023376464844</v>
+        <v>9.513022422790527</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596106714088645</v>
+        <v>9.596105752085279</v>
       </c>
       <c r="D322" t="n">
-        <v>9.20561594546151</v>
+        <v>9.205615022604585</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288698448353738</v>
+        <v>9.288697517167847</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.77057933807373</v>
+        <v>9.770580291748047</v>
       </c>
       <c r="C324" t="n">
-        <v>9.861970739073907</v>
+        <v>9.86197170166864</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262023027314</v>
+        <v>9.654262965348279</v>
       </c>
       <c r="E324" t="n">
-        <v>9.820428661972032</v>
+        <v>9.82042962051198</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953362464904785</v>
+        <v>9.953363418579102</v>
       </c>
       <c r="C325" t="n">
-        <v>10.1195291092724</v>
+        <v>10.11953007886785</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704112498353368</v>
+        <v>9.704113428145977</v>
       </c>
       <c r="E325" t="n">
-        <v>9.72903757848165</v>
+        <v>9.72903851066244</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6952,16 +6952,16 @@
         <v>44790</v>
       </c>
       <c r="B327" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C327" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D327" t="n">
-        <v>10.30231205007301</v>
+        <v>10.30231297394502</v>
       </c>
       <c r="E327" t="n">
-        <v>10.46847869658313</v>
+        <v>10.46847963535633</v>
       </c>
       <c r="F327" t="n">
         <v>150439</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494644165039</v>
+        <v>10.53494548797607</v>
       </c>
       <c r="C328" t="n">
-        <v>10.7592713789844</v>
+        <v>10.75927040500311</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216359220203</v>
+        <v>10.3521626550741</v>
       </c>
       <c r="E328" t="n">
-        <v>10.7592713789844</v>
+        <v>10.75927040500311</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092112410713</v>
+        <v>10.21092019610571</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7032,16 +7032,16 @@
         <v>44796</v>
       </c>
       <c r="B331" t="n">
-        <v>10.4850959777832</v>
+        <v>10.48509502410889</v>
       </c>
       <c r="C331" t="n">
-        <v>10.4850959777832</v>
+        <v>10.48509502410889</v>
       </c>
       <c r="D331" t="n">
-        <v>10.29400506519045</v>
+        <v>10.29400412889686</v>
       </c>
       <c r="E331" t="n">
-        <v>10.3853964800911</v>
+        <v>10.38539553548497</v>
       </c>
       <c r="F331" t="n">
         <v>120309</v>
@@ -7072,16 +7072,16 @@
         <v>44798</v>
       </c>
       <c r="B333" t="n">
-        <v>10.79250335693359</v>
+        <v>10.79250240325928</v>
       </c>
       <c r="C333" t="n">
-        <v>10.88389477156793</v>
+        <v>10.88389380981785</v>
       </c>
       <c r="D333" t="n">
-        <v>10.62633669319944</v>
+        <v>10.62633575420836</v>
       </c>
       <c r="E333" t="n">
-        <v>10.82573735746564</v>
+        <v>10.82573640085461</v>
       </c>
       <c r="F333" t="n">
         <v>93339</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539505004883</v>
+        <v>10.38539600372314</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648593632885</v>
+        <v>10.57648690755074</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907773332736</v>
+        <v>10.26907867632044</v>
       </c>
       <c r="E337" t="n">
-        <v>10.40201121334375</v>
+        <v>10.4020121685439</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7172,16 +7172,16 @@
         <v>44805</v>
       </c>
       <c r="B338" t="n">
-        <v>10.42693614959717</v>
+        <v>10.42693710327148</v>
       </c>
       <c r="C338" t="n">
-        <v>10.71772651584117</v>
+        <v>10.71772749611192</v>
       </c>
       <c r="D338" t="n">
-        <v>10.3189277507402</v>
+        <v>10.31892869453579</v>
       </c>
       <c r="E338" t="n">
-        <v>10.42693614959717</v>
+        <v>10.42693710327148</v>
       </c>
       <c r="F338" t="n">
         <v>1368072</v>
@@ -7192,16 +7192,16 @@
         <v>44806</v>
       </c>
       <c r="B339" t="n">
-        <v>10.22753715515137</v>
+        <v>10.22753620147705</v>
       </c>
       <c r="C339" t="n">
-        <v>10.39370380728989</v>
+        <v>10.39370283812124</v>
       </c>
       <c r="D339" t="n">
-        <v>10.16937891037603</v>
+        <v>10.16937796212472</v>
       </c>
       <c r="E339" t="n">
-        <v>10.34385364470204</v>
+        <v>10.3438526801817</v>
       </c>
       <c r="F339" t="n">
         <v>1420115</v>
@@ -7212,16 +7212,16 @@
         <v>44809</v>
       </c>
       <c r="B340" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C340" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="D340" t="n">
-        <v>10.2524617502037</v>
+        <v>10.25246083437947</v>
       </c>
       <c r="E340" t="n">
-        <v>10.35216123591951</v>
+        <v>10.3521603111894</v>
       </c>
       <c r="F340" t="n">
         <v>138429</v>
@@ -7272,16 +7272,16 @@
         <v>44813</v>
       </c>
       <c r="B343" t="n">
-        <v>11.0500602722168</v>
+        <v>11.05005931854248</v>
       </c>
       <c r="C343" t="n">
-        <v>11.0500602722168</v>
+        <v>11.05005931854248</v>
       </c>
       <c r="D343" t="n">
-        <v>10.68449465215745</v>
+        <v>10.68449373003323</v>
       </c>
       <c r="E343" t="n">
-        <v>10.76757797527951</v>
+        <v>10.7675770459848</v>
       </c>
       <c r="F343" t="n">
         <v>298877</v>
@@ -7412,16 +7412,16 @@
         <v>44824</v>
       </c>
       <c r="B350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.15806770324707</v>
       </c>
       <c r="C350" t="n">
-        <v>11.30761915031543</v>
+        <v>11.30761818385911</v>
       </c>
       <c r="D350" t="n">
-        <v>11.15806865692139</v>
+        <v>11.15806770324707</v>
       </c>
       <c r="E350" t="n">
-        <v>11.17468565665344</v>
+        <v>11.17468470155888</v>
       </c>
       <c r="F350" t="n">
         <v>127157</v>
@@ -7452,16 +7452,16 @@
         <v>44826</v>
       </c>
       <c r="B352" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C352" t="n">
-        <v>10.85066048103983</v>
+        <v>10.85066145408563</v>
       </c>
       <c r="D352" t="n">
-        <v>10.5931032641</v>
+        <v>10.59310421404906</v>
       </c>
       <c r="E352" t="n">
-        <v>10.68449466926114</v>
+        <v>10.68449562740583</v>
       </c>
       <c r="F352" t="n">
         <v>130423</v>
@@ -7472,16 +7472,16 @@
         <v>44827</v>
       </c>
       <c r="B353" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C353" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="D353" t="n">
-        <v>10.34385329433483</v>
+        <v>10.3438542219321</v>
       </c>
       <c r="E353" t="n">
-        <v>10.55156201983819</v>
+        <v>10.55156296606198</v>
       </c>
       <c r="F353" t="n">
         <v>170666</v>
@@ -7492,16 +7492,16 @@
         <v>44830</v>
       </c>
       <c r="B354" t="n">
-        <v>10.42693614959717</v>
+        <v>10.42693710327148</v>
       </c>
       <c r="C354" t="n">
-        <v>10.60971895171559</v>
+        <v>10.60971992210769</v>
       </c>
       <c r="D354" t="n">
-        <v>10.34385283007114</v>
+        <v>10.34385377614644</v>
       </c>
       <c r="E354" t="n">
-        <v>10.60971895171559</v>
+        <v>10.60971992210769</v>
       </c>
       <c r="F354" t="n">
         <v>121152</v>
@@ -7512,16 +7512,16 @@
         <v>44831</v>
       </c>
       <c r="B355" t="n">
-        <v>10.28569507598877</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="C355" t="n">
-        <v>10.58479351362845</v>
+        <v>10.58479547644101</v>
       </c>
       <c r="D355" t="n">
-        <v>10.28569507598877</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="E355" t="n">
-        <v>10.42693579619133</v>
+        <v>10.42693772973123</v>
       </c>
       <c r="F355" t="n">
         <v>115674</v>
@@ -7532,16 +7532,16 @@
         <v>44832</v>
       </c>
       <c r="B356" t="n">
-        <v>10.21092224121094</v>
+        <v>10.21092128753662</v>
       </c>
       <c r="C356" t="n">
-        <v>10.44355441406907</v>
+        <v>10.4435534386675</v>
       </c>
       <c r="D356" t="n">
-        <v>10.19430607480114</v>
+        <v>10.19430512267873</v>
       </c>
       <c r="E356" t="n">
-        <v>10.40201316331301</v>
+        <v>10.40201219179128</v>
       </c>
       <c r="F356" t="n">
         <v>104928</v>
@@ -7552,16 +7552,16 @@
         <v>44833</v>
       </c>
       <c r="B357" t="n">
-        <v>10.12783813476562</v>
+        <v>10.12783718109131</v>
       </c>
       <c r="C357" t="n">
-        <v>10.2026133821179</v>
+        <v>10.20261242140248</v>
       </c>
       <c r="D357" t="n">
-        <v>9.978288474792565</v>
+        <v>9.978287535200392</v>
       </c>
       <c r="E357" t="n">
-        <v>10.17768746493565</v>
+        <v>10.17768650656734</v>
       </c>
       <c r="F357" t="n">
         <v>97132</v>
@@ -7592,16 +7592,16 @@
         <v>44837</v>
       </c>
       <c r="B359" t="n">
-        <v>10.28569507598877</v>
+        <v>10.2856969833374</v>
       </c>
       <c r="C359" t="n">
-        <v>10.6097185921146</v>
+        <v>10.60972055954919</v>
       </c>
       <c r="D359" t="n">
-        <v>10.13614460507188</v>
+        <v>10.13614648468832</v>
       </c>
       <c r="E359" t="n">
-        <v>10.36046864198449</v>
+        <v>10.36047056319891</v>
       </c>
       <c r="F359" t="n">
         <v>398643</v>
@@ -7612,16 +7612,16 @@
         <v>44838</v>
       </c>
       <c r="B360" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="C360" t="n">
-        <v>10.75926878532992</v>
+        <v>10.75926974270069</v>
       </c>
       <c r="D360" t="n">
-        <v>10.32723685164071</v>
+        <v>10.32723777056884</v>
       </c>
       <c r="E360" t="n">
-        <v>10.38539509287557</v>
+        <v>10.38539601697868</v>
       </c>
       <c r="F360" t="n">
         <v>266324</v>
@@ -7672,16 +7672,16 @@
         <v>44841</v>
       </c>
       <c r="B363" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="C363" t="n">
-        <v>10.88389364339556</v>
+        <v>10.88389461942159</v>
       </c>
       <c r="D363" t="n">
-        <v>10.63464450836182</v>
+        <v>10.63464546203613</v>
       </c>
       <c r="E363" t="n">
-        <v>10.82573623532159</v>
+        <v>10.82573720613229</v>
       </c>
       <c r="F363" t="n">
         <v>365774</v>
@@ -7732,16 +7732,16 @@
         <v>44847</v>
       </c>
       <c r="B366" t="n">
-        <v>10.9669771194458</v>
+        <v>10.96697616577148</v>
       </c>
       <c r="C366" t="n">
-        <v>11.15806801433649</v>
+        <v>11.15806704404515</v>
       </c>
       <c r="D366" t="n">
-        <v>10.85896954896772</v>
+        <v>10.8589686046856</v>
       </c>
       <c r="E366" t="n">
-        <v>10.85896954896772</v>
+        <v>10.8589686046856</v>
       </c>
       <c r="F366" t="n">
         <v>180569</v>
@@ -7752,16 +7752,16 @@
         <v>44848</v>
       </c>
       <c r="B367" t="n">
-        <v>10.87558555603027</v>
+        <v>10.87558650970459</v>
       </c>
       <c r="C367" t="n">
-        <v>11.09160236333128</v>
+        <v>11.09160333594799</v>
       </c>
       <c r="D367" t="n">
-        <v>10.85066047559313</v>
+        <v>10.85066142708177</v>
       </c>
       <c r="E367" t="n">
-        <v>11.03344412055507</v>
+        <v>11.03344508807192</v>
       </c>
       <c r="F367" t="n">
         <v>169191</v>
@@ -7812,16 +7812,16 @@
         <v>44853</v>
       </c>
       <c r="B370" t="n">
-        <v>10.80911922454834</v>
+        <v>10.80911827087402</v>
       </c>
       <c r="C370" t="n">
-        <v>10.91712847120327</v>
+        <v>10.91712750799944</v>
       </c>
       <c r="D370" t="n">
-        <v>10.71772781243293</v>
+        <v>10.71772686682196</v>
       </c>
       <c r="E370" t="n">
-        <v>10.75926989458725</v>
+        <v>10.75926894531107</v>
       </c>
       <c r="F370" t="n">
         <v>116727</v>
@@ -7832,16 +7832,16 @@
         <v>44854</v>
       </c>
       <c r="B371" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="C371" t="n">
-        <v>11.04175190982251</v>
+        <v>11.04175289232892</v>
       </c>
       <c r="D371" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="E371" t="n">
-        <v>10.95866858881108</v>
+        <v>10.95866956392465</v>
       </c>
       <c r="F371" t="n">
         <v>119045</v>
@@ -7872,16 +7872,16 @@
         <v>44858</v>
       </c>
       <c r="B373" t="n">
-        <v>10.84235286712646</v>
+        <v>10.84235382080078</v>
       </c>
       <c r="C373" t="n">
-        <v>10.95866935775788</v>
+        <v>10.95867032166319</v>
       </c>
       <c r="D373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618715250262</v>
       </c>
       <c r="E373" t="n">
-        <v>10.67618621344403</v>
+        <v>10.67618715250262</v>
       </c>
       <c r="F373" t="n">
         <v>186469</v>
@@ -7892,16 +7892,16 @@
         <v>44859</v>
       </c>
       <c r="B374" t="n">
-        <v>10.65126037597656</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="C374" t="n">
-        <v>10.95866772117583</v>
+        <v>10.95866870237426</v>
       </c>
       <c r="D374" t="n">
-        <v>10.65126037597656</v>
+        <v>10.65126132965088</v>
       </c>
       <c r="E374" t="n">
-        <v>10.71772585889944</v>
+        <v>10.71772681852483</v>
       </c>
       <c r="F374" t="n">
         <v>99344</v>
@@ -7912,16 +7912,16 @@
         <v>44860</v>
       </c>
       <c r="B375" t="n">
-        <v>10.7177267074585</v>
+        <v>10.71772766113281</v>
       </c>
       <c r="C375" t="n">
-        <v>10.9669766704928</v>
+        <v>10.96697764634563</v>
       </c>
       <c r="D375" t="n">
-        <v>10.65126121927332</v>
+        <v>10.65126216703347</v>
       </c>
       <c r="E375" t="n">
-        <v>10.65126121927332</v>
+        <v>10.65126216703347</v>
       </c>
       <c r="F375" t="n">
         <v>230294</v>
@@ -7972,16 +7972,16 @@
         <v>44865</v>
       </c>
       <c r="B378" t="n">
-        <v>10.59310340881348</v>
+        <v>10.59310436248779</v>
       </c>
       <c r="C378" t="n">
-        <v>10.90051079085215</v>
+        <v>10.90051177220169</v>
       </c>
       <c r="D378" t="n">
-        <v>10.48509500363324</v>
+        <v>10.4850959475838</v>
       </c>
       <c r="E378" t="n">
-        <v>10.6180276548722</v>
+        <v>10.61802861079039</v>
       </c>
       <c r="F378" t="n">
         <v>218495</v>
@@ -8032,16 +8032,16 @@
         <v>44869</v>
       </c>
       <c r="B381" t="n">
-        <v>11.19961071014404</v>
+        <v>11.19960975646973</v>
       </c>
       <c r="C381" t="n">
-        <v>11.36577736811222</v>
+        <v>11.36577640028841</v>
       </c>
       <c r="D381" t="n">
-        <v>10.8838943938971</v>
+        <v>10.8838934671068</v>
       </c>
       <c r="E381" t="n">
-        <v>11.03344488690735</v>
+        <v>11.03344394738246</v>
       </c>
       <c r="F381" t="n">
         <v>304250</v>
@@ -8092,16 +8092,16 @@
         <v>44874</v>
       </c>
       <c r="B384" t="n">
-        <v>10.69280242919922</v>
+        <v>10.69280338287354</v>
       </c>
       <c r="C384" t="n">
-        <v>10.84235207266271</v>
+        <v>10.84235303967512</v>
       </c>
       <c r="D384" t="n">
-        <v>10.49340262633743</v>
+        <v>10.49340356222759</v>
       </c>
       <c r="E384" t="n">
-        <v>10.79250191326441</v>
+        <v>10.79250287583077</v>
       </c>
       <c r="F384" t="n">
         <v>162870</v>
@@ -8132,16 +8132,16 @@
         <v>44876</v>
       </c>
       <c r="B386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="C386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="D386" t="n">
-        <v>10.21922874450684</v>
+        <v>10.21922969818115</v>
       </c>
       <c r="E386" t="n">
-        <v>10.65126152534211</v>
+        <v>10.6512625193344</v>
       </c>
       <c r="F386" t="n">
         <v>372832</v>
@@ -8172,16 +8172,16 @@
         <v>44881</v>
       </c>
       <c r="B388" t="n">
-        <v>8.70711612701416</v>
+        <v>8.707117080688477</v>
       </c>
       <c r="C388" t="n">
-        <v>10.08629626020535</v>
+        <v>10.08629736493872</v>
       </c>
       <c r="D388" t="n">
-        <v>8.70711612701416</v>
+        <v>8.707117080688477</v>
       </c>
       <c r="E388" t="n">
-        <v>10.08629626020535</v>
+        <v>10.08629736493872</v>
       </c>
       <c r="F388" t="n">
         <v>1262722</v>
@@ -8192,16 +8192,16 @@
         <v>44882</v>
       </c>
       <c r="B389" t="n">
-        <v>8.765273094177246</v>
+        <v>8.765274047851562</v>
       </c>
       <c r="C389" t="n">
-        <v>8.873281492987086</v>
+        <v>8.873282458412872</v>
       </c>
       <c r="D389" t="n">
-        <v>8.225232769590827</v>
+        <v>8.225233664507979</v>
       </c>
       <c r="E389" t="n">
-        <v>8.707114854007546</v>
+        <v>8.707115801354162</v>
       </c>
       <c r="F389" t="n">
         <v>1047598</v>
@@ -8232,16 +8232,16 @@
         <v>44886</v>
       </c>
       <c r="B391" t="n">
-        <v>8.923131942749023</v>
+        <v>8.92313289642334</v>
       </c>
       <c r="C391" t="n">
-        <v>8.923131942749023</v>
+        <v>8.92313289642334</v>
       </c>
       <c r="D391" t="n">
-        <v>8.516025044926849</v>
+        <v>8.516025955090951</v>
       </c>
       <c r="E391" t="n">
-        <v>8.723732117761093</v>
+        <v>8.723733050124228</v>
       </c>
       <c r="F391" t="n">
         <v>232085</v>
@@ -8272,16 +8272,16 @@
         <v>44888</v>
       </c>
       <c r="B393" t="n">
-        <v>8.78026008605957</v>
+        <v>8.780261039733887</v>
       </c>
       <c r="C393" t="n">
-        <v>8.880605613163999</v>
+        <v>8.880606577737419</v>
       </c>
       <c r="D393" t="n">
-        <v>8.462498830158687</v>
+        <v>8.462499749319136</v>
       </c>
       <c r="E393" t="n">
-        <v>8.537757765451913</v>
+        <v>8.537758692786666</v>
       </c>
       <c r="F393" t="n">
         <v>214913</v>
@@ -8292,16 +8292,16 @@
         <v>44889</v>
       </c>
       <c r="B394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="C394" t="n">
-        <v>9.081299781799316</v>
+        <v>9.081298828125</v>
       </c>
       <c r="D394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="E394" t="n">
-        <v>8.621381617215055</v>
+        <v>8.621380711839127</v>
       </c>
       <c r="F394" t="n">
         <v>113672</v>
@@ -8312,16 +8312,16 @@
         <v>44890</v>
       </c>
       <c r="B395" t="n">
-        <v>8.82207202911377</v>
+        <v>8.822072982788086</v>
       </c>
       <c r="C395" t="n">
-        <v>9.098022879921743</v>
+        <v>9.098023863426608</v>
       </c>
       <c r="D395" t="n">
-        <v>8.746812247907716</v>
+        <v>8.746813193446378</v>
       </c>
       <c r="E395" t="n">
-        <v>9.081298204051361</v>
+        <v>9.081299185748271</v>
       </c>
       <c r="F395" t="n">
         <v>162344</v>
@@ -8332,16 +8332,16 @@
         <v>44893</v>
       </c>
       <c r="B396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="C396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="D396" t="n">
-        <v>8.537759780883789</v>
+        <v>8.537760734558105</v>
       </c>
       <c r="E396" t="n">
-        <v>8.888970468867001</v>
+        <v>8.888971461771821</v>
       </c>
       <c r="F396" t="n">
         <v>122943</v>
@@ -8392,16 +8392,16 @@
         <v>44896</v>
       </c>
       <c r="B399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955867767333984</v>
       </c>
       <c r="C399" t="n">
-        <v>8.955866813659668</v>
+        <v>8.955867767333984</v>
       </c>
       <c r="D399" t="n">
-        <v>8.596294234144615</v>
+        <v>8.596295149529491</v>
       </c>
       <c r="E399" t="n">
-        <v>8.721726373019072</v>
+        <v>8.721727301760714</v>
       </c>
       <c r="F399" t="n">
         <v>469965</v>
@@ -8412,16 +8412,16 @@
         <v>44897</v>
       </c>
       <c r="B400" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C400" t="n">
-        <v>9.198371098419715</v>
+        <v>9.198370118006814</v>
       </c>
       <c r="D400" t="n">
-        <v>8.822073797252052</v>
+        <v>8.822072856946983</v>
       </c>
       <c r="E400" t="n">
-        <v>9.1398351412117</v>
+        <v>9.139834167037881</v>
       </c>
       <c r="F400" t="n">
         <v>155601</v>
@@ -8432,16 +8432,16 @@
         <v>44900</v>
       </c>
       <c r="B401" t="n">
-        <v>8.74681282043457</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C401" t="n">
-        <v>9.089661557024961</v>
+        <v>9.089662548080438</v>
       </c>
       <c r="D401" t="n">
-        <v>8.66319195603055</v>
+        <v>8.663192900587594</v>
       </c>
       <c r="E401" t="n">
-        <v>8.947504743313322</v>
+        <v>8.947505718869293</v>
       </c>
       <c r="F401" t="n">
         <v>131055</v>
@@ -8452,16 +8452,16 @@
         <v>44901</v>
       </c>
       <c r="B402" t="n">
-        <v>8.74681282043457</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C402" t="n">
-        <v>8.863883038768801</v>
+        <v>8.863884005207408</v>
       </c>
       <c r="D402" t="n">
-        <v>8.688277711267455</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="E402" t="n">
-        <v>8.771899415811978</v>
+        <v>8.771900372221511</v>
       </c>
       <c r="F402" t="n">
         <v>122416</v>
@@ -8472,16 +8472,16 @@
         <v>44902</v>
       </c>
       <c r="B403" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C403" t="n">
-        <v>8.905693728734814</v>
+        <v>8.905694705334085</v>
       </c>
       <c r="D403" t="n">
-        <v>8.679915225243152</v>
+        <v>8.67991617708353</v>
       </c>
       <c r="E403" t="n">
-        <v>8.780260760050309</v>
+        <v>8.780261722894588</v>
       </c>
       <c r="F403" t="n">
         <v>128948</v>
@@ -8492,16 +8492,16 @@
         <v>44903</v>
       </c>
       <c r="B404" t="n">
-        <v>8.437413215637207</v>
+        <v>8.437412261962891</v>
       </c>
       <c r="C404" t="n">
-        <v>8.738451542075317</v>
+        <v>8.73845055437487</v>
       </c>
       <c r="D404" t="n">
-        <v>8.412327458562881</v>
+        <v>8.412326507723987</v>
       </c>
       <c r="E404" t="n">
-        <v>8.705003025835651</v>
+        <v>8.705002041915865</v>
       </c>
       <c r="F404" t="n">
         <v>134531</v>
@@ -8512,16 +8512,16 @@
         <v>44904</v>
       </c>
       <c r="B405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="C405" t="n">
-        <v>8.479224033940735</v>
+        <v>8.479225052935186</v>
       </c>
       <c r="D405" t="n">
-        <v>7.935684204101562</v>
+        <v>7.935685157775879</v>
       </c>
       <c r="E405" t="n">
-        <v>8.462500196792739</v>
+        <v>8.462501213777397</v>
       </c>
       <c r="F405" t="n">
         <v>686564</v>
@@ -8532,16 +8532,16 @@
         <v>44907</v>
       </c>
       <c r="B406" t="n">
-        <v>7.952408790588379</v>
+        <v>7.952409267425537</v>
       </c>
       <c r="C406" t="n">
-        <v>8.027667737176076</v>
+        <v>8.027668218525863</v>
       </c>
       <c r="D406" t="n">
-        <v>7.818614734370023</v>
+        <v>7.818615203184709</v>
       </c>
       <c r="E406" t="n">
-        <v>7.93568411349083</v>
+        <v>7.935684589325154</v>
       </c>
       <c r="F406" t="n">
         <v>212911</v>
@@ -8552,16 +8552,16 @@
         <v>44908</v>
       </c>
       <c r="B407" t="n">
-        <v>8.027666091918945</v>
+        <v>8.027667999267578</v>
       </c>
       <c r="C407" t="n">
-        <v>8.245081808785029</v>
+        <v>8.245083767790964</v>
       </c>
       <c r="D407" t="n">
-        <v>7.893871222981123</v>
+        <v>7.893873098540508</v>
       </c>
       <c r="E407" t="n">
-        <v>7.893871222981123</v>
+        <v>7.893873098540508</v>
       </c>
       <c r="F407" t="n">
         <v>284655</v>
@@ -8572,16 +8572,16 @@
         <v>44909</v>
       </c>
       <c r="B408" t="n">
-        <v>8.136377334594727</v>
+        <v>8.13637638092041</v>
       </c>
       <c r="C408" t="n">
-        <v>8.161463094028024</v>
+        <v>8.161462137413377</v>
       </c>
       <c r="D408" t="n">
-        <v>7.634647023397222</v>
+        <v>7.634646128531304</v>
       </c>
       <c r="E408" t="n">
-        <v>8.002583257054573</v>
+        <v>8.002582319062418</v>
       </c>
       <c r="F408" t="n">
         <v>518426</v>
@@ -8592,16 +8592,16 @@
         <v>44910</v>
       </c>
       <c r="B409" t="n">
-        <v>8.253446578979492</v>
+        <v>8.253445625305176</v>
       </c>
       <c r="C409" t="n">
-        <v>8.253446578979492</v>
+        <v>8.253445625305176</v>
       </c>
       <c r="D409" t="n">
-        <v>8.027668867291462</v>
+        <v>8.027667939705447</v>
       </c>
       <c r="E409" t="n">
-        <v>8.111290584270247</v>
+        <v>8.111289647021858</v>
       </c>
       <c r="F409" t="n">
         <v>145488</v>
@@ -8612,16 +8612,16 @@
         <v>44911</v>
       </c>
       <c r="B410" t="n">
-        <v>8.027666091918945</v>
+        <v>8.027667999267578</v>
       </c>
       <c r="C410" t="n">
-        <v>8.295254989654255</v>
+        <v>8.295256960581183</v>
       </c>
       <c r="D410" t="n">
-        <v>8.027666091918945</v>
+        <v>8.027667999267578</v>
       </c>
       <c r="E410" t="n">
-        <v>8.253443725549788</v>
+        <v>8.253445686542488</v>
       </c>
       <c r="F410" t="n">
         <v>177935</v>
@@ -8632,16 +8632,16 @@
         <v>44914</v>
       </c>
       <c r="B411" t="n">
-        <v>8.16146183013916</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="C411" t="n">
-        <v>8.16146183013916</v>
+        <v>8.161462783813477</v>
       </c>
       <c r="D411" t="n">
-        <v>7.952408826391903</v>
+        <v>7.952409755638184</v>
       </c>
       <c r="E411" t="n">
-        <v>8.128014156074491</v>
+        <v>8.128015105840415</v>
       </c>
       <c r="F411" t="n">
         <v>108510</v>
@@ -8672,16 +8672,16 @@
         <v>44916</v>
       </c>
       <c r="B413" t="n">
-        <v>8.454140663146973</v>
+        <v>8.45413875579834</v>
       </c>
       <c r="C413" t="n">
-        <v>8.613020521435294</v>
+        <v>8.613018578241588</v>
       </c>
       <c r="D413" t="n">
-        <v>8.370518933395603</v>
+        <v>8.370517044912967</v>
       </c>
       <c r="E413" t="n">
-        <v>8.429053220066731</v>
+        <v>8.429051318378106</v>
       </c>
       <c r="F413" t="n">
         <v>125998</v>
@@ -8712,16 +8712,16 @@
         <v>44918</v>
       </c>
       <c r="B415" t="n">
-        <v>8.688278198242188</v>
+        <v>8.688277244567871</v>
       </c>
       <c r="C415" t="n">
-        <v>8.763537988592692</v>
+        <v>8.763537026657437</v>
       </c>
       <c r="D415" t="n">
-        <v>8.504310942017245</v>
+        <v>8.50431000853621</v>
       </c>
       <c r="E415" t="n">
-        <v>8.529397538800746</v>
+        <v>8.529396602566065</v>
       </c>
       <c r="F415" t="n">
         <v>92391</v>
@@ -8732,16 +8732,16 @@
         <v>44921</v>
       </c>
       <c r="B416" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C416" t="n">
-        <v>8.780260760050309</v>
+        <v>8.780261722894588</v>
       </c>
       <c r="D416" t="n">
-        <v>8.613017361897933</v>
+        <v>8.613018306402285</v>
       </c>
       <c r="E416" t="n">
-        <v>8.730088412716954</v>
+        <v>8.730089370059329</v>
       </c>
       <c r="F416" t="n">
         <v>50778</v>
@@ -8752,16 +8752,16 @@
         <v>44922</v>
       </c>
       <c r="B417" t="n">
-        <v>8.738451957702637</v>
+        <v>8.73845100402832</v>
       </c>
       <c r="C417" t="n">
-        <v>8.788624314378202</v>
+        <v>8.788623355228307</v>
       </c>
       <c r="D417" t="n">
-        <v>8.56284660898665</v>
+        <v>8.56284567447709</v>
       </c>
       <c r="E417" t="n">
-        <v>8.713365359294553</v>
+        <v>8.713364408358071</v>
       </c>
       <c r="F417" t="n">
         <v>181939</v>
@@ -8772,16 +8772,16 @@
         <v>44923</v>
       </c>
       <c r="B418" t="n">
-        <v>8.74681282043457</v>
+        <v>8.746813774108887</v>
       </c>
       <c r="C418" t="n">
-        <v>8.930780906488719</v>
+        <v>8.930781880221272</v>
       </c>
       <c r="D418" t="n">
-        <v>8.679915792855153</v>
+        <v>8.679916739235615</v>
       </c>
       <c r="E418" t="n">
-        <v>8.688277711267455</v>
+        <v>8.688278658559627</v>
       </c>
       <c r="F418" t="n">
         <v>114515</v>
@@ -8792,16 +8792,16 @@
         <v>44924</v>
       </c>
       <c r="B419" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="C419" t="n">
-        <v>8.914055646600298</v>
+        <v>8.914056624116538</v>
       </c>
       <c r="D419" t="n">
-        <v>8.696639060974121</v>
+        <v>8.696640014648438</v>
       </c>
       <c r="E419" t="n">
-        <v>8.83043394752411</v>
+        <v>8.830434915870388</v>
       </c>
       <c r="F419" t="n">
         <v>78169</v>
@@ -8892,16 +8892,16 @@
         <v>44932</v>
       </c>
       <c r="B424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="C424" t="n">
-        <v>8.947505950927734</v>
+        <v>8.947504997253418</v>
       </c>
       <c r="D424" t="n">
-        <v>8.387241379016988</v>
+        <v>8.387240485058745</v>
       </c>
       <c r="E424" t="n">
-        <v>8.395604138698484</v>
+        <v>8.395603243848893</v>
       </c>
       <c r="F424" t="n">
         <v>169613</v>
@@ -8932,16 +8932,16 @@
         <v>44936</v>
       </c>
       <c r="B426" t="n">
-        <v>8.930782318115234</v>
+        <v>8.930781364440918</v>
       </c>
       <c r="C426" t="n">
-        <v>8.972592756925931</v>
+        <v>8.972591798786882</v>
       </c>
       <c r="D426" t="n">
-        <v>8.755176962857174</v>
+        <v>8.75517602793489</v>
       </c>
       <c r="E426" t="n">
-        <v>8.830435920744552</v>
+        <v>8.830434977785734</v>
       </c>
       <c r="F426" t="n">
         <v>133478</v>
@@ -8992,16 +8992,16 @@
         <v>44939</v>
       </c>
       <c r="B429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C429" t="n">
-        <v>9.139834941690628</v>
+        <v>9.139833970240518</v>
       </c>
       <c r="D429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="E429" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F429" t="n">
         <v>64052</v>
@@ -9012,16 +9012,16 @@
         <v>44942</v>
       </c>
       <c r="B430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C430" t="n">
-        <v>9.006040871394767</v>
+        <v>9.006039914165292</v>
       </c>
       <c r="D430" t="n">
-        <v>8.847160202883281</v>
+        <v>8.847159262540833</v>
       </c>
       <c r="E430" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="F430" t="n">
         <v>64474</v>
@@ -9032,16 +9032,16 @@
         <v>44943</v>
       </c>
       <c r="B431" t="n">
-        <v>8.972592353820801</v>
+        <v>8.972591400146484</v>
       </c>
       <c r="C431" t="n">
-        <v>9.064575987184355</v>
+        <v>9.06457502373333</v>
       </c>
       <c r="D431" t="n">
-        <v>8.905695318672869</v>
+        <v>8.905694372108872</v>
       </c>
       <c r="E431" t="n">
-        <v>8.964229594321862</v>
+        <v>8.964228641536403</v>
       </c>
       <c r="F431" t="n">
         <v>59206</v>
@@ -9112,16 +9112,16 @@
         <v>44949</v>
       </c>
       <c r="B435" t="n">
-        <v>9.566306114196777</v>
+        <v>9.566305160522461</v>
       </c>
       <c r="C435" t="n">
-        <v>9.616478474070194</v>
+        <v>9.616477515394145</v>
       </c>
       <c r="D435" t="n">
-        <v>9.407424594199101</v>
+        <v>9.407423656363838</v>
       </c>
       <c r="E435" t="n">
-        <v>9.424149274250677</v>
+        <v>9.424148334748114</v>
       </c>
       <c r="F435" t="n">
         <v>228503</v>
@@ -9152,16 +9152,16 @@
         <v>44951</v>
       </c>
       <c r="B437" t="n">
-        <v>9.783720970153809</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="C437" t="n">
-        <v>9.842256084476254</v>
+        <v>9.842255125096191</v>
       </c>
       <c r="D437" t="n">
-        <v>9.415786445921619</v>
+        <v>9.41578552811195</v>
       </c>
       <c r="E437" t="n">
-        <v>9.541218593715268</v>
+        <v>9.541217663679022</v>
       </c>
       <c r="F437" t="n">
         <v>142538</v>
@@ -9172,16 +9172,16 @@
         <v>44952</v>
       </c>
       <c r="B438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C438" t="n">
-        <v>9.95932505997885</v>
+        <v>9.959326039139317</v>
       </c>
       <c r="D438" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="E438" t="n">
-        <v>9.741909308483715</v>
+        <v>9.741910266268745</v>
       </c>
       <c r="F438" t="n">
         <v>182255</v>
@@ -9192,16 +9192,16 @@
         <v>44953</v>
       </c>
       <c r="B439" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="D439" t="n">
-        <v>9.6499256889996</v>
+        <v>9.649926637741174</v>
       </c>
       <c r="E439" t="n">
-        <v>9.80044357530045</v>
+        <v>9.800444538840333</v>
       </c>
       <c r="F439" t="n">
         <v>86070</v>
@@ -9232,16 +9232,16 @@
         <v>44957</v>
       </c>
       <c r="B441" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="C441" t="n">
-        <v>9.683374442443164</v>
+        <v>9.68337541974836</v>
       </c>
       <c r="D441" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="E441" t="n">
-        <v>9.616476575584498</v>
+        <v>9.616477546137954</v>
       </c>
       <c r="F441" t="n">
         <v>134742</v>
@@ -9252,16 +9252,16 @@
         <v>44958</v>
       </c>
       <c r="B442" t="n">
-        <v>9.783720970153809</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="C442" t="n">
-        <v>9.783720970153809</v>
+        <v>9.783720016479492</v>
       </c>
       <c r="D442" t="n">
-        <v>9.323801974722995</v>
+        <v>9.323801065879572</v>
       </c>
       <c r="E442" t="n">
-        <v>9.44923496265722</v>
+        <v>9.449234041587136</v>
       </c>
       <c r="F442" t="n">
         <v>177092</v>
@@ -9272,16 +9272,16 @@
         <v>44959</v>
       </c>
       <c r="B443" t="n">
-        <v>9.66664981842041</v>
+        <v>9.666648864746094</v>
       </c>
       <c r="C443" t="n">
-        <v>9.725184927153217</v>
+        <v>9.725183967704053</v>
       </c>
       <c r="D443" t="n">
-        <v>9.457595978680457</v>
+        <v>9.457595045630583</v>
       </c>
       <c r="E443" t="n">
-        <v>9.700098331961943</v>
+        <v>9.700097374987726</v>
       </c>
       <c r="F443" t="n">
         <v>116411</v>
@@ -9312,16 +9312,16 @@
         <v>44963</v>
       </c>
       <c r="B445" t="n">
-        <v>9.608115196228027</v>
+        <v>9.608114242553711</v>
       </c>
       <c r="C445" t="n">
-        <v>9.842255643015774</v>
+        <v>9.842254666101338</v>
       </c>
       <c r="D445" t="n">
-        <v>9.599753277454333</v>
+        <v>9.599752324609996</v>
       </c>
       <c r="E445" t="n">
-        <v>9.666650307924964</v>
+        <v>9.666649348440618</v>
       </c>
       <c r="F445" t="n">
         <v>107772</v>
@@ -9372,16 +9372,16 @@
         <v>44966</v>
       </c>
       <c r="B448" t="n">
-        <v>10.00950050354004</v>
+        <v>10.00949859619141</v>
       </c>
       <c r="C448" t="n">
-        <v>10.1432945837856</v>
+        <v>10.14329265094199</v>
       </c>
       <c r="D448" t="n">
-        <v>9.884067503134004</v>
+        <v>9.88406561968711</v>
       </c>
       <c r="E448" t="n">
-        <v>10.09312222376384</v>
+        <v>10.09312030048077</v>
       </c>
       <c r="F448" t="n">
         <v>166136</v>
@@ -9412,16 +9412,16 @@
         <v>44970</v>
       </c>
       <c r="B450" t="n">
-        <v>9.583028793334961</v>
+        <v>9.583027839660645</v>
       </c>
       <c r="C450" t="n">
-        <v>9.817170084992688</v>
+        <v>9.81716910801733</v>
       </c>
       <c r="D450" t="n">
-        <v>9.390699616811887</v>
+        <v>9.390698682277593</v>
       </c>
       <c r="E450" t="n">
-        <v>9.390699616811887</v>
+        <v>9.390698682277593</v>
       </c>
       <c r="F450" t="n">
         <v>216072</v>
@@ -9452,16 +9452,16 @@
         <v>44972</v>
       </c>
       <c r="B452" t="n">
-        <v>10.22691535949707</v>
+        <v>10.22691440582275</v>
       </c>
       <c r="C452" t="n">
-        <v>10.3439847488296</v>
+        <v>10.34398378423839</v>
       </c>
       <c r="D452" t="n">
-        <v>9.917515947398474</v>
+        <v>9.91751502257609</v>
       </c>
       <c r="E452" t="n">
-        <v>9.917515947398474</v>
+        <v>9.91751502257609</v>
       </c>
       <c r="F452" t="n">
         <v>361455</v>
@@ -9472,16 +9472,16 @@
         <v>44973</v>
       </c>
       <c r="B453" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363708496094</v>
       </c>
       <c r="C453" t="n">
-        <v>10.41088144470998</v>
+        <v>10.41088047546544</v>
       </c>
       <c r="D453" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458326690051</v>
       </c>
       <c r="E453" t="n">
-        <v>10.11820590414945</v>
+        <v>10.11820496215276</v>
       </c>
       <c r="F453" t="n">
         <v>189102</v>
@@ -9512,16 +9512,16 @@
         <v>44979</v>
       </c>
       <c r="B455" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363708496094</v>
       </c>
       <c r="C455" t="n">
-        <v>10.61993612237364</v>
+        <v>10.61993513366628</v>
       </c>
       <c r="D455" t="n">
-        <v>9.992774609804133</v>
+        <v>9.992773679484996</v>
       </c>
       <c r="E455" t="n">
-        <v>10.31889782341103</v>
+        <v>10.31889686273009</v>
       </c>
       <c r="F455" t="n">
         <v>261056</v>
@@ -9572,16 +9572,16 @@
         <v>44984</v>
       </c>
       <c r="B458" t="n">
-        <v>9.95096492767334</v>
+        <v>9.950963973999023</v>
       </c>
       <c r="C458" t="n">
-        <v>10.04294856366475</v>
+        <v>10.04294760117497</v>
       </c>
       <c r="D458" t="n">
-        <v>9.817170853555146</v>
+        <v>9.817169912703301</v>
       </c>
       <c r="E458" t="n">
-        <v>10.00113812553797</v>
+        <v>10.00113716705519</v>
       </c>
       <c r="F458" t="n">
         <v>122627</v>
@@ -9592,16 +9592,16 @@
         <v>44985</v>
       </c>
       <c r="B459" t="n">
-        <v>10.03458499908447</v>
+        <v>10.03458404541016</v>
       </c>
       <c r="C459" t="n">
-        <v>10.31889864399266</v>
+        <v>10.31889766329754</v>
       </c>
       <c r="D459" t="n">
-        <v>9.90915369476458</v>
+        <v>9.909152753011098</v>
       </c>
       <c r="E459" t="n">
-        <v>9.950964129537878</v>
+        <v>9.950963183810783</v>
       </c>
       <c r="F459" t="n">
         <v>302669</v>
@@ -9612,16 +9612,16 @@
         <v>44986</v>
       </c>
       <c r="B460" t="n">
-        <v>10.24363803863525</v>
+        <v>10.24363708496094</v>
       </c>
       <c r="C460" t="n">
-        <v>10.31053590514944</v>
+        <v>10.31053494524699</v>
       </c>
       <c r="D460" t="n">
-        <v>9.850616958514175</v>
+        <v>9.850616041429799</v>
       </c>
       <c r="E460" t="n">
-        <v>10.03458420111209</v>
+        <v>10.03458326690051</v>
       </c>
       <c r="F460" t="n">
         <v>355766</v>
@@ -9632,16 +9632,16 @@
         <v>44987</v>
       </c>
       <c r="B461" t="n">
-        <v>10.47777843475342</v>
+        <v>10.47777938842773</v>
       </c>
       <c r="C461" t="n">
-        <v>10.55303821926824</v>
+        <v>10.55303917979261</v>
       </c>
       <c r="D461" t="n">
-        <v>10.11820586906596</v>
+        <v>10.11820679001243</v>
       </c>
       <c r="E461" t="n">
-        <v>10.20182757181338</v>
+        <v>10.20182850037099</v>
       </c>
       <c r="F461" t="n">
         <v>220181</v>
@@ -9672,16 +9672,16 @@
         <v>44991</v>
       </c>
       <c r="B463" t="n">
-        <v>10.63665962219238</v>
+        <v>10.63666152954102</v>
       </c>
       <c r="C463" t="n">
-        <v>10.63665962219238</v>
+        <v>10.63666152954102</v>
       </c>
       <c r="D463" t="n">
-        <v>10.20182728424704</v>
+        <v>10.20182911362224</v>
       </c>
       <c r="E463" t="n">
-        <v>10.32725941476227</v>
+        <v>10.32726126662976</v>
       </c>
       <c r="F463" t="n">
         <v>82488</v>
@@ -9712,16 +9712,16 @@
         <v>44993</v>
       </c>
       <c r="B465" t="n">
-        <v>10.74536895751953</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="C465" t="n">
-        <v>10.74536895751953</v>
+        <v>10.74536800384521</v>
       </c>
       <c r="D465" t="n">
-        <v>10.5028665720366</v>
+        <v>10.50286563988488</v>
       </c>
       <c r="E465" t="n">
-        <v>10.64502340357023</v>
+        <v>10.64502245880179</v>
       </c>
       <c r="F465" t="n">
         <v>92707</v>
@@ -9812,16 +9812,16 @@
         <v>45000</v>
       </c>
       <c r="B470" t="n">
-        <v>9.758633613586426</v>
+        <v>9.758632659912109</v>
       </c>
       <c r="C470" t="n">
-        <v>9.967687457030143</v>
+        <v>9.967686482925785</v>
       </c>
       <c r="D470" t="n">
-        <v>9.675011908180837</v>
+        <v>9.675010962678554</v>
       </c>
       <c r="E470" t="n">
-        <v>9.892427670122959</v>
+        <v>9.892426703373456</v>
       </c>
       <c r="F470" t="n">
         <v>133688</v>
@@ -9832,16 +9832,16 @@
         <v>45001</v>
       </c>
       <c r="B471" t="n">
-        <v>10.15165519714355</v>
+        <v>10.15165615081787</v>
       </c>
       <c r="C471" t="n">
-        <v>10.16837903495139</v>
+        <v>10.16837999019679</v>
       </c>
       <c r="D471" t="n">
-        <v>9.683375136415892</v>
+        <v>9.683376046098697</v>
       </c>
       <c r="E471" t="n">
-        <v>9.833893877389167</v>
+        <v>9.833894801212116</v>
       </c>
       <c r="F471" t="n">
         <v>137902</v>
@@ -9852,16 +9852,16 @@
         <v>45002</v>
       </c>
       <c r="B472" t="n">
-        <v>9.942602157592773</v>
+        <v>9.942601203918457</v>
       </c>
       <c r="C472" t="n">
-        <v>10.18510538692582</v>
+        <v>10.18510440999109</v>
       </c>
       <c r="D472" t="n">
-        <v>9.750272966212783</v>
+        <v>9.750272030986295</v>
       </c>
       <c r="E472" t="n">
-        <v>10.18510538692582</v>
+        <v>10.18510440999109</v>
       </c>
       <c r="F472" t="n">
         <v>69952</v>
@@ -9872,16 +9872,16 @@
         <v>45005</v>
       </c>
       <c r="B473" t="n">
-        <v>9.532855987548828</v>
+        <v>9.532854080200195</v>
       </c>
       <c r="C473" t="n">
-        <v>9.909154117255268</v>
+        <v>9.909152134616322</v>
       </c>
       <c r="D473" t="n">
-        <v>9.340526803194662</v>
+        <v>9.340524934327551</v>
       </c>
       <c r="E473" t="n">
-        <v>9.909154117255268</v>
+        <v>9.909152134616322</v>
       </c>
       <c r="F473" t="n">
         <v>182676</v>
@@ -9912,16 +9912,16 @@
         <v>45007</v>
       </c>
       <c r="B475" t="n">
-        <v>9.449234008789062</v>
+        <v>9.449234962463379</v>
       </c>
       <c r="C475" t="n">
-        <v>9.507769117202587</v>
+        <v>9.507770076784624</v>
       </c>
       <c r="D475" t="n">
-        <v>9.206731656830312</v>
+        <v>9.206732586029814</v>
       </c>
       <c r="E475" t="n">
-        <v>9.482682522148149</v>
+        <v>9.482683479198295</v>
       </c>
       <c r="F475" t="n">
         <v>116622</v>
@@ -9972,16 +9972,16 @@
         <v>45012</v>
       </c>
       <c r="B478" t="n">
-        <v>10.46941757202148</v>
+        <v>10.46941661834717</v>
       </c>
       <c r="C478" t="n">
-        <v>10.54467736412381</v>
+        <v>10.54467640359397</v>
       </c>
       <c r="D478" t="n">
-        <v>9.87570451484077</v>
+        <v>9.875703615248632</v>
       </c>
       <c r="E478" t="n">
-        <v>10.3188988279574</v>
+        <v>10.31889788799405</v>
       </c>
       <c r="F478" t="n">
         <v>649270</v>
@@ -10012,16 +10012,16 @@
         <v>45014</v>
       </c>
       <c r="B480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028255462646</v>
       </c>
       <c r="C480" t="n">
-        <v>10.72028160095215</v>
+        <v>10.72028255462646</v>
       </c>
       <c r="D480" t="n">
-        <v>10.45269265683905</v>
+        <v>10.4526935867087</v>
       </c>
       <c r="E480" t="n">
-        <v>10.70355692438362</v>
+        <v>10.70355787657011</v>
       </c>
       <c r="F480" t="n">
         <v>215756</v>
@@ -10052,16 +10052,16 @@
         <v>45016</v>
       </c>
       <c r="B482" t="n">
-        <v>9.984410285949707</v>
+        <v>9.984411239624023</v>
       </c>
       <c r="C482" t="n">
-        <v>11.00459364467013</v>
+        <v>11.00459469578863</v>
       </c>
       <c r="D482" t="n">
-        <v>9.984410285949707</v>
+        <v>9.984411239624023</v>
       </c>
       <c r="E482" t="n">
-        <v>11.00459364467013</v>
+        <v>11.00459469578863</v>
       </c>
       <c r="F482" t="n">
         <v>804556</v>
@@ -10072,16 +10072,16 @@
         <v>45019</v>
       </c>
       <c r="B483" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C483" t="n">
-        <v>10.11820570451678</v>
+        <v>10.11820669929775</v>
       </c>
       <c r="D483" t="n">
-        <v>9.633201012665911</v>
+        <v>9.633201959763182</v>
       </c>
       <c r="E483" t="n">
-        <v>10.03458400312928</v>
+        <v>10.0345849896889</v>
       </c>
       <c r="F483" t="n">
         <v>894103</v>
@@ -10092,16 +10092,16 @@
         <v>45020</v>
       </c>
       <c r="B484" t="n">
-        <v>9.599754333496094</v>
+        <v>9.599753379821777</v>
       </c>
       <c r="C484" t="n">
-        <v>9.758635008376988</v>
+        <v>9.758634038918892</v>
       </c>
       <c r="D484" t="n">
-        <v>9.532856455525678</v>
+        <v>9.53285550849724</v>
       </c>
       <c r="E484" t="n">
-        <v>9.70009989024077</v>
+        <v>9.700098926597763</v>
       </c>
       <c r="F484" t="n">
         <v>529909</v>
@@ -10152,16 +10152,16 @@
         <v>45026</v>
       </c>
       <c r="B487" t="n">
-        <v>9.407423973083496</v>
+        <v>9.40742301940918</v>
       </c>
       <c r="C487" t="n">
-        <v>9.700099553607547</v>
+        <v>9.700098570263346</v>
       </c>
       <c r="D487" t="n">
-        <v>9.407423973083496</v>
+        <v>9.40742301940918</v>
       </c>
       <c r="E487" t="n">
-        <v>9.574667401994555</v>
+        <v>9.574666431365994</v>
       </c>
       <c r="F487" t="n">
         <v>160237</v>
@@ -10172,16 +10172,16 @@
         <v>45027</v>
       </c>
       <c r="B488" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C488" t="n">
-        <v>9.758633144676933</v>
+        <v>9.758634104106184</v>
       </c>
       <c r="D488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="E488" t="n">
-        <v>9.474320368127982</v>
+        <v>9.474321299604751</v>
       </c>
       <c r="F488" t="n">
         <v>244200</v>
@@ -10212,16 +10212,16 @@
         <v>45029</v>
       </c>
       <c r="B490" t="n">
-        <v>9.683375358581543</v>
+        <v>9.683376312255859</v>
       </c>
       <c r="C490" t="n">
-        <v>9.775358989056672</v>
+        <v>9.775359951790064</v>
       </c>
       <c r="D490" t="n">
-        <v>9.566305130678549</v>
+        <v>9.566306072823117</v>
       </c>
       <c r="E490" t="n">
-        <v>9.608115566297945</v>
+        <v>9.608116512560244</v>
       </c>
       <c r="F490" t="n">
         <v>171614</v>
@@ -10232,16 +10232,16 @@
         <v>45030</v>
       </c>
       <c r="B491" t="n">
-        <v>9.583028793334961</v>
+        <v>9.583027839660645</v>
       </c>
       <c r="C491" t="n">
-        <v>9.750272213030243</v>
+        <v>9.750271242712362</v>
       </c>
       <c r="D491" t="n">
-        <v>9.532855599398266</v>
+        <v>9.532854650717034</v>
       </c>
       <c r="E491" t="n">
-        <v>9.700099019093548</v>
+        <v>9.700098053768752</v>
       </c>
       <c r="F491" t="n">
         <v>94288</v>
@@ -10272,16 +10272,16 @@
         <v>45034</v>
       </c>
       <c r="B493" t="n">
-        <v>9.700098037719727</v>
+        <v>9.700098991394043</v>
       </c>
       <c r="C493" t="n">
-        <v>9.766995062773542</v>
+        <v>9.766996023024904</v>
       </c>
       <c r="D493" t="n">
-        <v>9.549580151418876</v>
+        <v>9.549581090294884</v>
       </c>
       <c r="E493" t="n">
-        <v>9.691736119623117</v>
+        <v>9.691737072475323</v>
       </c>
       <c r="F493" t="n">
         <v>308358</v>
@@ -10312,16 +10312,16 @@
         <v>45036</v>
       </c>
       <c r="B495" t="n">
-        <v>9.599754333496094</v>
+        <v>9.599753379821777</v>
       </c>
       <c r="C495" t="n">
-        <v>9.77535968790475</v>
+        <v>9.775358716785163</v>
       </c>
       <c r="D495" t="n">
-        <v>9.549581975194069</v>
+        <v>9.549581026504057</v>
       </c>
       <c r="E495" t="n">
-        <v>9.658289451632312</v>
+        <v>9.658288492142907</v>
       </c>
       <c r="F495" t="n">
         <v>169823</v>
@@ -10332,16 +10332,16 @@
         <v>45040</v>
       </c>
       <c r="B496" t="n">
-        <v>9.516131401062012</v>
+        <v>9.516133308410645</v>
       </c>
       <c r="C496" t="n">
-        <v>9.700098651674196</v>
+        <v>9.700100595895972</v>
       </c>
       <c r="D496" t="n">
-        <v>9.516131401062012</v>
+        <v>9.516133308410645</v>
       </c>
       <c r="E496" t="n">
-        <v>9.633201622386224</v>
+        <v>9.633203553199616</v>
       </c>
       <c r="F496" t="n">
         <v>136322</v>
@@ -10372,16 +10372,16 @@
         <v>45042</v>
       </c>
       <c r="B498" t="n">
-        <v>9.281991958618164</v>
+        <v>9.28199291229248</v>
       </c>
       <c r="C498" t="n">
-        <v>9.382337504280539</v>
+        <v>9.382338468264816</v>
       </c>
       <c r="D498" t="n">
-        <v>9.215094088036043</v>
+        <v>9.215095034836967</v>
       </c>
       <c r="E498" t="n">
-        <v>9.248542603256835</v>
+        <v>9.248543553494413</v>
       </c>
       <c r="F498" t="n">
         <v>262531</v>
@@ -10412,16 +10412,16 @@
         <v>45044</v>
       </c>
       <c r="B500" t="n">
-        <v>9.176148414611816</v>
+        <v>9.1761474609375</v>
       </c>
       <c r="C500" t="n">
-        <v>9.393831370760845</v>
+        <v>9.393830394462805</v>
       </c>
       <c r="D500" t="n">
-        <v>9.176148414611816</v>
+        <v>9.1761474609375</v>
       </c>
       <c r="E500" t="n">
-        <v>9.326851546700507</v>
+        <v>9.326850577363659</v>
       </c>
       <c r="F500" t="n">
         <v>147595</v>
@@ -10432,16 +10432,16 @@
         <v>45048</v>
       </c>
       <c r="B501" t="n">
-        <v>9.10916805267334</v>
+        <v>9.109167098999023</v>
       </c>
       <c r="C501" t="n">
-        <v>9.201264350497761</v>
+        <v>9.201263387181525</v>
       </c>
       <c r="D501" t="n">
-        <v>9.017071754848917</v>
+        <v>9.017070810816522</v>
       </c>
       <c r="E501" t="n">
-        <v>9.176147025423896</v>
+        <v>9.17614606473729</v>
       </c>
       <c r="F501" t="n">
         <v>926867</v>
@@ -10452,16 +10452,16 @@
         <v>45049</v>
       </c>
       <c r="B502" t="n">
-        <v>9.151029586791992</v>
+        <v>9.151030540466309</v>
       </c>
       <c r="C502" t="n">
-        <v>9.259871047038219</v>
+        <v>9.259872012055444</v>
       </c>
       <c r="D502" t="n">
-        <v>8.941720509836294</v>
+        <v>8.941721441697471</v>
       </c>
       <c r="E502" t="n">
-        <v>9.100795778437256</v>
+        <v>9.100796726876458</v>
       </c>
       <c r="F502" t="n">
         <v>158340</v>
@@ -10512,16 +10512,16 @@
         <v>45054</v>
       </c>
       <c r="B505" t="n">
-        <v>9.385457992553711</v>
+        <v>9.385458946228027</v>
       </c>
       <c r="C505" t="n">
-        <v>9.519415940984162</v>
+        <v>9.519416908270202</v>
       </c>
       <c r="D505" t="n">
-        <v>9.326850338653331</v>
+        <v>9.326851286372412</v>
       </c>
       <c r="E505" t="n">
-        <v>9.418946638491677</v>
+        <v>9.41894759556884</v>
       </c>
       <c r="F505" t="n">
         <v>225237</v>
@@ -10532,16 +10532,16 @@
         <v>45055</v>
       </c>
       <c r="B506" t="n">
-        <v>9.502670288085938</v>
+        <v>9.502671241760254</v>
       </c>
       <c r="C506" t="n">
-        <v>9.594766583187411</v>
+        <v>9.594767546104379</v>
       </c>
       <c r="D506" t="n">
-        <v>9.343595022214229</v>
+        <v>9.343595959923981</v>
       </c>
       <c r="E506" t="n">
-        <v>9.385457509822828</v>
+        <v>9.385458451733838</v>
       </c>
       <c r="F506" t="n">
         <v>112092</v>
@@ -10552,16 +10552,16 @@
         <v>45056</v>
       </c>
       <c r="B507" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="C507" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="D507" t="n">
-        <v>9.418947917893513</v>
+        <v>9.418946980877298</v>
       </c>
       <c r="E507" t="n">
-        <v>9.452437409550097</v>
+        <v>9.452436469202278</v>
       </c>
       <c r="F507" t="n">
         <v>185415</v>
@@ -10572,16 +10572,16 @@
         <v>45057</v>
       </c>
       <c r="B508" t="n">
-        <v>9.862683296203613</v>
+        <v>9.86268424987793</v>
       </c>
       <c r="C508" t="n">
-        <v>9.929663108067157</v>
+        <v>9.929664068218099</v>
       </c>
       <c r="D508" t="n">
-        <v>9.477553794128655</v>
+        <v>9.477554710562789</v>
       </c>
       <c r="E508" t="n">
-        <v>9.477553794128655</v>
+        <v>9.477554710562789</v>
       </c>
       <c r="F508" t="n">
         <v>216809</v>
@@ -10592,16 +10592,16 @@
         <v>45058</v>
       </c>
       <c r="B509" t="n">
-        <v>10.08036708831787</v>
+        <v>10.08036613464355</v>
       </c>
       <c r="C509" t="n">
-        <v>10.29805004190088</v>
+        <v>10.29804906763221</v>
       </c>
       <c r="D509" t="n">
-        <v>9.762216502753041</v>
+        <v>9.762215579178029</v>
       </c>
       <c r="E509" t="n">
-        <v>9.795705993803564</v>
+        <v>9.795705067060208</v>
       </c>
       <c r="F509" t="n">
         <v>501359</v>
@@ -10612,16 +10612,16 @@
         <v>45061</v>
       </c>
       <c r="B510" t="n">
-        <v>10.18083477020264</v>
+        <v>10.18083381652832</v>
       </c>
       <c r="C510" t="n">
-        <v>10.32316656815221</v>
+        <v>10.32316560114518</v>
       </c>
       <c r="D510" t="n">
-        <v>10.00501600731443</v>
+        <v>10.00501507010967</v>
       </c>
       <c r="E510" t="n">
-        <v>10.0719941430401</v>
+        <v>10.07199319956127</v>
       </c>
       <c r="F510" t="n">
         <v>215124</v>
@@ -10632,16 +10632,16 @@
         <v>45062</v>
       </c>
       <c r="B511" t="n">
-        <v>9.845940589904785</v>
+        <v>9.845939636230469</v>
       </c>
       <c r="C511" t="n">
-        <v>10.27293349078287</v>
+        <v>10.27293249575018</v>
       </c>
       <c r="D511" t="n">
-        <v>9.745472117376274</v>
+        <v>9.745471173433298</v>
       </c>
       <c r="E511" t="n">
-        <v>10.10548519539895</v>
+        <v>10.10548421658523</v>
       </c>
       <c r="F511" t="n">
         <v>132003</v>
@@ -10652,16 +10652,16 @@
         <v>45063</v>
       </c>
       <c r="B512" t="n">
-        <v>9.787333488464355</v>
+        <v>9.787332534790039</v>
       </c>
       <c r="C512" t="n">
-        <v>9.904546282450122</v>
+        <v>9.904545317354632</v>
       </c>
       <c r="D512" t="n">
-        <v>9.594767870207617</v>
+        <v>9.594766935296825</v>
       </c>
       <c r="E512" t="n">
-        <v>9.81244997499506</v>
+        <v>9.812449018873401</v>
       </c>
       <c r="F512" t="n">
         <v>227976</v>
@@ -10672,16 +10672,16 @@
         <v>45064</v>
       </c>
       <c r="B513" t="n">
-        <v>9.871057510375977</v>
+        <v>9.87105655670166</v>
       </c>
       <c r="C513" t="n">
-        <v>10.10548477775711</v>
+        <v>10.10548380143403</v>
       </c>
       <c r="D513" t="n">
-        <v>9.670119732453616</v>
+        <v>9.670118798192538</v>
       </c>
       <c r="E513" t="n">
-        <v>9.728725708129195</v>
+        <v>9.728724768206007</v>
       </c>
       <c r="F513" t="n">
         <v>659595</v>
@@ -10712,16 +10712,16 @@
         <v>45068</v>
       </c>
       <c r="B515" t="n">
-        <v>9.904545783996582</v>
+        <v>9.904546737670898</v>
       </c>
       <c r="C515" t="n">
-        <v>9.904545783996582</v>
+        <v>9.904546737670898</v>
       </c>
       <c r="D515" t="n">
-        <v>9.670119366653017</v>
+        <v>9.670120297755227</v>
       </c>
       <c r="E515" t="n">
-        <v>9.737098343036893</v>
+        <v>9.737099280588277</v>
       </c>
       <c r="F515" t="n">
         <v>159710</v>
@@ -10752,16 +10752,16 @@
         <v>45070</v>
       </c>
       <c r="B517" t="n">
-        <v>9.351968765258789</v>
+        <v>9.351967811584473</v>
       </c>
       <c r="C517" t="n">
-        <v>9.678492354460824</v>
+        <v>9.678491367489009</v>
       </c>
       <c r="D517" t="n">
-        <v>9.293362786798175</v>
+        <v>9.29336183910025</v>
       </c>
       <c r="E517" t="n">
-        <v>9.619885534830464</v>
+        <v>9.619884553835126</v>
       </c>
       <c r="F517" t="n">
         <v>244411</v>
@@ -10772,16 +10772,16 @@
         <v>45071</v>
       </c>
       <c r="B518" t="n">
-        <v>9.301734924316406</v>
+        <v>9.301735877990723</v>
       </c>
       <c r="C518" t="n">
-        <v>9.56127953072173</v>
+        <v>9.561280511006245</v>
       </c>
       <c r="D518" t="n">
-        <v>9.293362761868741</v>
+        <v>9.293363714684688</v>
       </c>
       <c r="E518" t="n">
-        <v>9.43569288815803</v>
+        <v>9.435693855566587</v>
       </c>
       <c r="F518" t="n">
         <v>216177</v>
@@ -10812,16 +10812,16 @@
         <v>45075</v>
       </c>
       <c r="B520" t="n">
-        <v>9.435691833496094</v>
+        <v>9.43569278717041</v>
       </c>
       <c r="C520" t="n">
-        <v>9.50267080793042</v>
+        <v>9.502671768374364</v>
       </c>
       <c r="D520" t="n">
-        <v>9.368712859061768</v>
+        <v>9.368713805966456</v>
       </c>
       <c r="E520" t="n">
-        <v>9.460809159201379</v>
+        <v>9.460810115414327</v>
       </c>
       <c r="F520" t="n">
         <v>106087</v>
@@ -10912,16 +10912,16 @@
         <v>45082</v>
       </c>
       <c r="B525" t="n">
-        <v>8.874741554260254</v>
+        <v>8.874740600585938</v>
       </c>
       <c r="C525" t="n">
-        <v>9.142658308994628</v>
+        <v>9.142657326530141</v>
       </c>
       <c r="D525" t="n">
-        <v>8.849625068240838</v>
+        <v>8.849624117265524</v>
       </c>
       <c r="E525" t="n">
-        <v>8.933348370644952</v>
+        <v>8.933347410672782</v>
       </c>
       <c r="F525" t="n">
         <v>464803</v>
@@ -10932,16 +10932,16 @@
         <v>45083</v>
       </c>
       <c r="B526" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958464622497559</v>
       </c>
       <c r="C526" t="n">
-        <v>9.058934042394197</v>
+        <v>9.0589330780245</v>
       </c>
       <c r="D526" t="n">
-        <v>8.83287978310155</v>
+        <v>8.832878842796482</v>
       </c>
       <c r="E526" t="n">
-        <v>8.933348249323872</v>
+        <v>8.933347298323424</v>
       </c>
       <c r="F526" t="n">
         <v>546554</v>
@@ -10952,16 +10952,16 @@
         <v>45084</v>
       </c>
       <c r="B527" t="n">
-        <v>9.117542266845703</v>
+        <v>9.117541313171387</v>
       </c>
       <c r="C527" t="n">
-        <v>9.192893410911674</v>
+        <v>9.192892449355798</v>
       </c>
       <c r="D527" t="n">
-        <v>8.966838296374284</v>
+        <v>8.966837358463263</v>
       </c>
       <c r="E527" t="n">
-        <v>9.092424097264061</v>
+        <v>9.092423146217049</v>
       </c>
       <c r="F527" t="n">
         <v>438781</v>
@@ -10972,16 +10972,16 @@
         <v>45086</v>
       </c>
       <c r="B528" t="n">
-        <v>9.167776107788086</v>
+        <v>9.16777515411377</v>
       </c>
       <c r="C528" t="n">
-        <v>9.226382927187608</v>
+        <v>9.226381967416739</v>
       </c>
       <c r="D528" t="n">
-        <v>9.109169288388564</v>
+        <v>9.109168340810799</v>
       </c>
       <c r="E528" t="n">
-        <v>9.20963860231331</v>
+        <v>9.209637644284264</v>
       </c>
       <c r="F528" t="n">
         <v>317102</v>
@@ -11032,16 +11032,16 @@
         <v>45091</v>
       </c>
       <c r="B531" t="n">
-        <v>9.100796699523926</v>
+        <v>9.100795745849609</v>
       </c>
       <c r="C531" t="n">
-        <v>9.218010332830801</v>
+        <v>9.218009366873643</v>
       </c>
       <c r="D531" t="n">
-        <v>9.04218988287049</v>
+        <v>9.042188935337592</v>
       </c>
       <c r="E531" t="n">
-        <v>9.142658350917937</v>
+        <v>9.142657392856929</v>
       </c>
       <c r="F531" t="n">
         <v>269590</v>
@@ -11052,16 +11052,16 @@
         <v>45092</v>
       </c>
       <c r="B532" t="n">
-        <v>9.201264381408691</v>
+        <v>9.201265335083008</v>
       </c>
       <c r="C532" t="n">
-        <v>9.251499031725182</v>
+        <v>9.251499990606119</v>
       </c>
       <c r="D532" t="n">
-        <v>9.092422919446173</v>
+        <v>9.092423861839507</v>
       </c>
       <c r="E532" t="n">
-        <v>9.125913247103586</v>
+        <v>9.125914192968059</v>
       </c>
       <c r="F532" t="n">
         <v>477550</v>
@@ -11112,16 +11112,16 @@
         <v>45097</v>
       </c>
       <c r="B535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.991955757141113</v>
       </c>
       <c r="C535" t="n">
-        <v>8.991954803466797</v>
+        <v>8.991955757141113</v>
       </c>
       <c r="D535" t="n">
-        <v>8.899858501814995</v>
+        <v>8.899859445721704</v>
       </c>
       <c r="E535" t="n">
-        <v>8.983582641817451</v>
+        <v>8.983583594603827</v>
       </c>
       <c r="F535" t="n">
         <v>272118</v>
@@ -11132,16 +11132,16 @@
         <v>45098</v>
       </c>
       <c r="B536" t="n">
-        <v>9.000328063964844</v>
+        <v>9.000327110290527</v>
       </c>
       <c r="C536" t="n">
-        <v>9.042190559661888</v>
+        <v>9.042189601551824</v>
       </c>
       <c r="D536" t="n">
-        <v>8.857997933870235</v>
+        <v>8.857996995277212</v>
       </c>
       <c r="E536" t="n">
-        <v>9.033818396990386</v>
+        <v>9.033817439767434</v>
       </c>
       <c r="F536" t="n">
         <v>259897</v>
@@ -11152,16 +11152,16 @@
         <v>45099</v>
       </c>
       <c r="B537" t="n">
-        <v>8.950094223022461</v>
+        <v>8.950092315673828</v>
       </c>
       <c r="C537" t="n">
-        <v>9.000328040087979</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="D537" t="n">
-        <v>8.832880581253315</v>
+        <v>8.832878698884004</v>
       </c>
       <c r="E537" t="n">
-        <v>9.000328040087979</v>
+        <v>9.00032612203405</v>
       </c>
       <c r="F537" t="n">
         <v>192684</v>
@@ -11192,16 +11192,16 @@
         <v>45103</v>
       </c>
       <c r="B539" t="n">
-        <v>8.958465576171875</v>
+        <v>8.958464622497559</v>
       </c>
       <c r="C539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000326268674719</v>
       </c>
       <c r="D539" t="n">
-        <v>8.841251944994323</v>
+        <v>8.841251003797995</v>
       </c>
       <c r="E539" t="n">
-        <v>9.000327226805421</v>
+        <v>9.000326268674719</v>
       </c>
       <c r="F539" t="n">
         <v>181728</v>
@@ -11252,16 +11252,16 @@
         <v>45106</v>
       </c>
       <c r="B542" t="n">
-        <v>8.782646179199219</v>
+        <v>8.782645225524902</v>
       </c>
       <c r="C542" t="n">
-        <v>8.849626005856582</v>
+        <v>8.84962504490918</v>
       </c>
       <c r="D542" t="n">
-        <v>8.615197874310489</v>
+        <v>8.615196938818752</v>
       </c>
       <c r="E542" t="n">
-        <v>8.665432534011066</v>
+        <v>8.665431593064536</v>
       </c>
       <c r="F542" t="n">
         <v>269063</v>
@@ -11272,16 +11272,16 @@
         <v>45107</v>
       </c>
       <c r="B543" t="n">
-        <v>9.050561904907227</v>
+        <v>9.05056095123291</v>
       </c>
       <c r="C543" t="n">
-        <v>9.176147698316207</v>
+        <v>9.176146731408684</v>
       </c>
       <c r="D543" t="n">
-        <v>8.765900829258186</v>
+        <v>8.765899905579127</v>
       </c>
       <c r="E543" t="n">
-        <v>8.782645153088882</v>
+        <v>8.782644227645445</v>
       </c>
       <c r="F543" t="n">
         <v>473547</v>
@@ -11312,16 +11312,16 @@
         <v>45111</v>
       </c>
       <c r="B545" t="n">
-        <v>9.586396217346191</v>
+        <v>9.586395263671875</v>
       </c>
       <c r="C545" t="n">
-        <v>9.594768379967897</v>
+        <v>9.5947674254607</v>
       </c>
       <c r="D545" t="n">
-        <v>9.318479442923763</v>
+        <v>9.318478515902356</v>
       </c>
       <c r="E545" t="n">
-        <v>9.335223768167175</v>
+        <v>9.335222839480007</v>
       </c>
       <c r="F545" t="n">
         <v>135795</v>
@@ -11372,16 +11372,16 @@
         <v>45114</v>
       </c>
       <c r="B548" t="n">
-        <v>9.628255844116211</v>
+        <v>9.628256797790527</v>
       </c>
       <c r="C548" t="n">
-        <v>9.695235654494597</v>
+        <v>9.695236614803234</v>
       </c>
       <c r="D548" t="n">
-        <v>9.444063258207208</v>
+        <v>9.444064193637333</v>
       </c>
       <c r="E548" t="n">
-        <v>9.444063258207208</v>
+        <v>9.444064193637333</v>
       </c>
       <c r="F548" t="n">
         <v>257790</v>
@@ -11432,16 +11432,16 @@
         <v>45119</v>
       </c>
       <c r="B551" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C551" t="n">
-        <v>9.912918058384282</v>
+        <v>9.912919025122674</v>
       </c>
       <c r="D551" t="n">
-        <v>9.594766682188503</v>
+        <v>9.594767617899787</v>
       </c>
       <c r="E551" t="n">
-        <v>9.753842790871198</v>
+        <v>9.753843742096077</v>
       </c>
       <c r="F551" t="n">
         <v>281073</v>
@@ -11452,16 +11452,16 @@
         <v>45120</v>
       </c>
       <c r="B552" t="n">
-        <v>9.636630058288574</v>
+        <v>9.636629104614258</v>
       </c>
       <c r="C552" t="n">
-        <v>9.879430345451647</v>
+        <v>9.879429367748973</v>
       </c>
       <c r="D552" t="n">
-        <v>9.611513570360794</v>
+        <v>9.611512619172093</v>
       </c>
       <c r="E552" t="n">
-        <v>9.879430345451647</v>
+        <v>9.879429367748973</v>
       </c>
       <c r="F552" t="n">
         <v>274014</v>
@@ -11472,16 +11472,16 @@
         <v>45121</v>
       </c>
       <c r="B553" t="n">
-        <v>9.460808753967285</v>
+        <v>9.460809707641602</v>
       </c>
       <c r="C553" t="n">
-        <v>9.720352479075693</v>
+        <v>9.720353458912697</v>
       </c>
       <c r="D553" t="n">
-        <v>9.444063590491124</v>
+        <v>9.444064542477484</v>
       </c>
       <c r="E553" t="n">
-        <v>9.686862993292984</v>
+        <v>9.686863969754159</v>
       </c>
       <c r="F553" t="n">
         <v>130739</v>
@@ -11532,16 +11532,16 @@
         <v>45126</v>
       </c>
       <c r="B556" t="n">
-        <v>9.594766616821289</v>
+        <v>9.594767570495605</v>
       </c>
       <c r="C556" t="n">
-        <v>9.85431118092777</v>
+        <v>9.854312160399585</v>
       </c>
       <c r="D556" t="n">
-        <v>9.469180835894464</v>
+        <v>9.469181777086149</v>
       </c>
       <c r="E556" t="n">
-        <v>9.85431118092777</v>
+        <v>9.854312160399585</v>
       </c>
       <c r="F556" t="n">
         <v>152546</v>
@@ -11592,16 +11592,16 @@
         <v>45131</v>
       </c>
       <c r="B559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="C559" t="n">
-        <v>9.921291351318359</v>
+        <v>9.921292304992676</v>
       </c>
       <c r="D559" t="n">
-        <v>9.711980587323517</v>
+        <v>9.711981520878043</v>
       </c>
       <c r="E559" t="n">
-        <v>9.753843076590339</v>
+        <v>9.753844014168855</v>
       </c>
       <c r="F559" t="n">
         <v>210067</v>
@@ -11632,16 +11632,16 @@
         <v>45133</v>
       </c>
       <c r="B561" t="n">
-        <v>9.544532775878906</v>
+        <v>9.54453182220459</v>
       </c>
       <c r="C561" t="n">
-        <v>9.820822526707969</v>
+        <v>9.820821545427227</v>
       </c>
       <c r="D561" t="n">
-        <v>9.460809475620675</v>
+        <v>9.460808530311857</v>
       </c>
       <c r="E561" t="n">
-        <v>9.820822526707969</v>
+        <v>9.820821545427227</v>
       </c>
       <c r="F561" t="n">
         <v>168665</v>
@@ -11692,16 +11692,16 @@
         <v>45138</v>
       </c>
       <c r="B564" t="n">
-        <v>9.728724479675293</v>
+        <v>9.728725433349609</v>
       </c>
       <c r="C564" t="n">
-        <v>9.795704291304954</v>
+        <v>9.795705251545078</v>
       </c>
       <c r="D564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="E564" t="n">
-        <v>9.54453189032532</v>
+        <v>9.544532825943854</v>
       </c>
       <c r="F564" t="n">
         <v>242515</v>
@@ -11752,16 +11752,16 @@
         <v>45141</v>
       </c>
       <c r="B567" t="n">
-        <v>9.862683296203613</v>
+        <v>9.86268424987793</v>
       </c>
       <c r="C567" t="n">
-        <v>9.8794284594619</v>
+        <v>9.879429414755393</v>
       </c>
       <c r="D567" t="n">
-        <v>9.686862867254819</v>
+        <v>9.686863803928139</v>
       </c>
       <c r="E567" t="n">
-        <v>9.837566813070588</v>
+        <v>9.837567764316258</v>
       </c>
       <c r="F567" t="n">
         <v>144645</v>
@@ -11772,16 +11772,16 @@
         <v>45142</v>
       </c>
       <c r="B568" t="n">
-        <v>9.996641159057617</v>
+        <v>9.996640205383301</v>
       </c>
       <c r="C568" t="n">
-        <v>10.01338716335395</v>
+        <v>10.01338620808207</v>
       </c>
       <c r="D568" t="n">
-        <v>9.770586924449054</v>
+        <v>9.770585992340195</v>
       </c>
       <c r="E568" t="n">
-        <v>9.862683218722113</v>
+        <v>9.862682277827314</v>
       </c>
       <c r="F568" t="n">
         <v>196582</v>
@@ -11832,16 +11832,16 @@
         <v>45147</v>
       </c>
       <c r="B571" t="n">
-        <v>9.578023910522461</v>
+        <v>9.578022003173828</v>
       </c>
       <c r="C571" t="n">
-        <v>9.695237550140671</v>
+        <v>9.695235619450347</v>
       </c>
       <c r="D571" t="n">
-        <v>9.469182433399908</v>
+        <v>9.469180547725751</v>
       </c>
       <c r="E571" t="n">
-        <v>9.686864546475267</v>
+        <v>9.686862617452325</v>
       </c>
       <c r="F571" t="n">
         <v>142432</v>
@@ -11852,16 +11852,16 @@
         <v>45148</v>
       </c>
       <c r="B572" t="n">
-        <v>9.778959274291992</v>
+        <v>9.778960227966309</v>
       </c>
       <c r="C572" t="n">
-        <v>9.837566925782678</v>
+        <v>9.837567885172595</v>
       </c>
       <c r="D572" t="n">
-        <v>9.544532033007691</v>
+        <v>9.54453296381994</v>
       </c>
       <c r="E572" t="n">
-        <v>9.578022359907973</v>
+        <v>9.5780232939863</v>
       </c>
       <c r="F572" t="n">
         <v>202060</v>
@@ -11872,16 +11872,16 @@
         <v>45149</v>
       </c>
       <c r="B573" t="n">
-        <v>10.45712566375732</v>
+        <v>10.45712471008301</v>
       </c>
       <c r="C573" t="n">
-        <v>10.45712566375732</v>
+        <v>10.45712471008301</v>
       </c>
       <c r="D573" t="n">
-        <v>9.845940168798856</v>
+        <v>9.845939270863749</v>
       </c>
       <c r="E573" t="n">
-        <v>9.845940168798856</v>
+        <v>9.845939270863749</v>
       </c>
       <c r="F573" t="n">
         <v>774110</v>
@@ -11932,16 +11932,16 @@
         <v>45154</v>
       </c>
       <c r="B576" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C576" t="n">
-        <v>11.2608749384303</v>
+        <v>11.26087395777899</v>
       </c>
       <c r="D576" t="n">
-        <v>10.78364824878957</v>
+        <v>10.78364730969746</v>
       </c>
       <c r="E576" t="n">
-        <v>11.05993716353692</v>
+        <v>11.05993620038423</v>
       </c>
       <c r="F576" t="n">
         <v>525379</v>
@@ -11952,16 +11952,16 @@
         <v>45155</v>
       </c>
       <c r="B577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C577" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="D577" t="n">
-        <v>10.63294521258928</v>
+        <v>10.63294612667715</v>
       </c>
       <c r="E577" t="n">
-        <v>10.95109575560148</v>
+        <v>10.95109669703995</v>
       </c>
       <c r="F577" t="n">
         <v>481132</v>
@@ -11992,16 +11992,16 @@
         <v>45159</v>
       </c>
       <c r="B579" t="n">
-        <v>11.16877937316895</v>
+        <v>11.16877841949463</v>
       </c>
       <c r="C579" t="n">
-        <v>11.43669614371307</v>
+        <v>11.436695167162</v>
       </c>
       <c r="D579" t="n">
-        <v>11.04319357098227</v>
+        <v>11.04319262803141</v>
       </c>
       <c r="E579" t="n">
-        <v>11.37808932386998</v>
+        <v>11.37808835232321</v>
       </c>
       <c r="F579" t="n">
         <v>524641</v>
@@ -12032,16 +12032,16 @@
         <v>45161</v>
       </c>
       <c r="B581" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="C581" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="D581" t="n">
-        <v>11.3194807332412</v>
+        <v>11.31948165818213</v>
       </c>
       <c r="E581" t="n">
-        <v>11.47018384052361</v>
+        <v>11.47018477777884</v>
       </c>
       <c r="F581" t="n">
         <v>383262</v>
@@ -12072,16 +12072,16 @@
         <v>45163</v>
       </c>
       <c r="B583" t="n">
-        <v>11.67112159729004</v>
+        <v>11.67112255096436</v>
       </c>
       <c r="C583" t="n">
-        <v>11.74647357151606</v>
+        <v>11.74647453134756</v>
       </c>
       <c r="D583" t="n">
-        <v>11.55390797594043</v>
+        <v>11.55390892003695</v>
       </c>
       <c r="E583" t="n">
-        <v>11.74647357151606</v>
+        <v>11.74647453134756</v>
       </c>
       <c r="F583" t="n">
         <v>173405</v>
@@ -12132,16 +12132,16 @@
         <v>45168</v>
       </c>
       <c r="B586" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="C586" t="n">
-        <v>12.57534186904209</v>
+        <v>12.57534090704158</v>
       </c>
       <c r="D586" t="n">
-        <v>12.30742510572441</v>
+        <v>12.30742416421925</v>
       </c>
       <c r="E586" t="n">
-        <v>12.51673505077979</v>
+        <v>12.51673409326264</v>
       </c>
       <c r="F586" t="n">
         <v>381576</v>
@@ -12152,16 +12152,16 @@
         <v>45169</v>
       </c>
       <c r="B587" t="n">
-        <v>12.26556205749512</v>
+        <v>12.26556301116943</v>
       </c>
       <c r="C587" t="n">
-        <v>12.39114784200412</v>
+        <v>12.39114880544301</v>
       </c>
       <c r="D587" t="n">
-        <v>12.081368620223</v>
+        <v>12.08136955957587</v>
       </c>
       <c r="E587" t="n">
-        <v>12.37440351936005</v>
+        <v>12.37440448149703</v>
       </c>
       <c r="F587" t="n">
         <v>308253</v>
@@ -12192,16 +12192,16 @@
         <v>45173</v>
       </c>
       <c r="B589" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996444702148</v>
       </c>
       <c r="C589" t="n">
-        <v>12.05625325429223</v>
+        <v>12.05625423033423</v>
       </c>
       <c r="D589" t="n">
-        <v>11.66275070046011</v>
+        <v>11.66275164464519</v>
       </c>
       <c r="E589" t="n">
-        <v>11.99764643726385</v>
+        <v>11.99764740856119</v>
       </c>
       <c r="F589" t="n">
         <v>283706</v>
@@ -12212,16 +12212,16 @@
         <v>45174</v>
       </c>
       <c r="B590" t="n">
-        <v>11.70461273193359</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C590" t="n">
-        <v>11.80508120388398</v>
+        <v>11.80507928016331</v>
       </c>
       <c r="D590" t="n">
-        <v>11.59577125644338</v>
+        <v>11.59576936683122</v>
       </c>
       <c r="E590" t="n">
-        <v>11.77996387560395</v>
+        <v>11.77996195597632</v>
       </c>
       <c r="F590" t="n">
         <v>218284</v>
@@ -12252,16 +12252,16 @@
         <v>45177</v>
       </c>
       <c r="B592" t="n">
-        <v>11.77159023284912</v>
+        <v>11.77159118652344</v>
       </c>
       <c r="C592" t="n">
-        <v>11.82182488309172</v>
+        <v>11.82182584083579</v>
       </c>
       <c r="D592" t="n">
-        <v>11.59576979816967</v>
+        <v>11.59577073759991</v>
       </c>
       <c r="E592" t="n">
-        <v>11.74647374889745</v>
+        <v>11.74647470053696</v>
       </c>
       <c r="F592" t="n">
         <v>200375</v>
@@ -12272,16 +12272,16 @@
         <v>45180</v>
       </c>
       <c r="B593" t="n">
-        <v>11.77996349334717</v>
+        <v>11.77996444702148</v>
       </c>
       <c r="C593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93904058678816</v>
       </c>
       <c r="D593" t="n">
-        <v>11.52879190103679</v>
+        <v>11.52879283437693</v>
       </c>
       <c r="E593" t="n">
-        <v>11.93903962023547</v>
+        <v>11.93904058678816</v>
       </c>
       <c r="F593" t="n">
         <v>200269</v>
@@ -12312,16 +12312,16 @@
         <v>45182</v>
       </c>
       <c r="B595" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="C595" t="n">
-        <v>12.46650123596191</v>
+        <v>12.4665002822876</v>
       </c>
       <c r="D595" t="n">
-        <v>12.14834981665663</v>
+        <v>12.14834888732056</v>
       </c>
       <c r="E595" t="n">
-        <v>12.30742510572441</v>
+        <v>12.30742416421925</v>
       </c>
       <c r="F595" t="n">
         <v>353764</v>
@@ -12332,16 +12332,16 @@
         <v>45183</v>
       </c>
       <c r="B596" t="n">
-        <v>12.34091377258301</v>
+        <v>12.34091281890869</v>
       </c>
       <c r="C596" t="n">
-        <v>12.51673421563881</v>
+        <v>12.51673324837754</v>
       </c>
       <c r="D596" t="n">
-        <v>12.2655626347989</v>
+        <v>12.26556168694753</v>
       </c>
       <c r="E596" t="n">
-        <v>12.47487256588872</v>
+        <v>12.47487160186241</v>
       </c>
       <c r="F596" t="n">
         <v>207012</v>
@@ -12352,16 +12352,16 @@
         <v>45184</v>
       </c>
       <c r="B597" t="n">
-        <v>12.03950691223145</v>
+        <v>12.03950786590576</v>
       </c>
       <c r="C597" t="n">
-        <v>12.33254096873336</v>
+        <v>12.33254194561951</v>
       </c>
       <c r="D597" t="n">
-        <v>11.87205948078009</v>
+        <v>11.87206042119054</v>
       </c>
       <c r="E597" t="n">
-        <v>12.29067932116292</v>
+        <v>12.29068029473313</v>
       </c>
       <c r="F597" t="n">
         <v>162660</v>
@@ -12392,16 +12392,16 @@
         <v>45188</v>
       </c>
       <c r="B599" t="n">
-        <v>11.70461273193359</v>
+        <v>11.70461082458496</v>
       </c>
       <c r="C599" t="n">
-        <v>11.86368802281414</v>
+        <v>11.86368608954307</v>
       </c>
       <c r="D599" t="n">
-        <v>11.60414341881347</v>
+        <v>11.60414152783702</v>
       </c>
       <c r="E599" t="n">
-        <v>11.68786756602366</v>
+        <v>11.68786566140377</v>
       </c>
       <c r="F599" t="n">
         <v>151703</v>
@@ -12472,16 +12472,16 @@
         <v>45194</v>
       </c>
       <c r="B603" t="n">
-        <v>11.11854553222656</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C603" t="n">
-        <v>11.54553759517791</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="D603" t="n">
-        <v>11.10180036609309</v>
+        <v>11.10179941385507</v>
       </c>
       <c r="E603" t="n">
-        <v>11.54553759517791</v>
+        <v>11.54553660487908</v>
       </c>
       <c r="F603" t="n">
         <v>266745</v>
@@ -12492,16 +12492,16 @@
         <v>45195</v>
       </c>
       <c r="B604" t="n">
-        <v>11.09342670440674</v>
+        <v>11.09342765808105</v>
       </c>
       <c r="C604" t="n">
-        <v>11.27761930113372</v>
+        <v>11.27762027064262</v>
       </c>
       <c r="D604" t="n">
-        <v>10.91760626903017</v>
+        <v>10.91760720758964</v>
       </c>
       <c r="E604" t="n">
-        <v>11.21901248934153</v>
+        <v>11.21901345381215</v>
       </c>
       <c r="F604" t="n">
         <v>357451</v>
@@ -12512,16 +12512,16 @@
         <v>45196</v>
       </c>
       <c r="B605" t="n">
-        <v>10.76690483093262</v>
+        <v>10.7669038772583</v>
       </c>
       <c r="C605" t="n">
-        <v>11.12691791894479</v>
+        <v>11.12691693338246</v>
       </c>
       <c r="D605" t="n">
-        <v>10.63294686384426</v>
+        <v>10.63294592203521</v>
       </c>
       <c r="E605" t="n">
-        <v>11.0934284271727</v>
+        <v>11.09342744457668</v>
       </c>
       <c r="F605" t="n">
         <v>269906</v>
@@ -12552,16 +12552,16 @@
         <v>45198</v>
       </c>
       <c r="B607" t="n">
-        <v>11.11854553222656</v>
+        <v>11.11854457855225</v>
       </c>
       <c r="C607" t="n">
-        <v>11.41995095210127</v>
+        <v>11.41994997257442</v>
       </c>
       <c r="D607" t="n">
-        <v>11.06831003382616</v>
+        <v>11.06830908446071</v>
       </c>
       <c r="E607" t="n">
-        <v>11.12691769470842</v>
+        <v>11.126916740316</v>
       </c>
       <c r="F607" t="n">
         <v>376204</v>
@@ -12612,16 +12612,16 @@
         <v>45203</v>
       </c>
       <c r="B610" t="n">
-        <v>10.50735950469971</v>
+        <v>10.50735855102539</v>
       </c>
       <c r="C610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="D610" t="n">
-        <v>10.44037968453425</v>
+        <v>10.44037873693919</v>
       </c>
       <c r="E610" t="n">
-        <v>10.75015893443658</v>
+        <v>10.75015795872518</v>
       </c>
       <c r="F610" t="n">
         <v>180674</v>
@@ -12692,16 +12692,16 @@
         <v>45209</v>
       </c>
       <c r="B614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="C614" t="n">
-        <v>10.951096534729</v>
+        <v>10.95109558105469</v>
       </c>
       <c r="D614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="E614" t="n">
-        <v>10.15571843827122</v>
+        <v>10.15571755386226</v>
       </c>
       <c r="F614" t="n">
         <v>338699</v>
@@ -12712,16 +12712,16 @@
         <v>45210</v>
       </c>
       <c r="B615" t="n">
-        <v>11.15203189849854</v>
+        <v>11.15203285217285</v>
       </c>
       <c r="C615" t="n">
-        <v>11.15203189849854</v>
+        <v>11.15203285217285</v>
       </c>
       <c r="D615" t="n">
-        <v>10.62457062909666</v>
+        <v>10.62457153766474</v>
       </c>
       <c r="E615" t="n">
-        <v>10.88411518341387</v>
+        <v>10.88411611417709</v>
       </c>
       <c r="F615" t="n">
         <v>253682</v>
@@ -12732,16 +12732,16 @@
         <v>45212</v>
       </c>
       <c r="B616" t="n">
-        <v>11.12691688537598</v>
+        <v>11.12691497802734</v>
       </c>
       <c r="C616" t="n">
-        <v>11.20226802457144</v>
+        <v>11.2022661043063</v>
       </c>
       <c r="D616" t="n">
-        <v>10.76690383080508</v>
+        <v>10.76690198516899</v>
       </c>
       <c r="E616" t="n">
-        <v>11.00970325447664</v>
+        <v>11.00970136722048</v>
       </c>
       <c r="F616" t="n">
         <v>274225</v>
@@ -12792,16 +12792,16 @@
         <v>45217</v>
       </c>
       <c r="B619" t="n">
-        <v>10.2478141784668</v>
+        <v>10.24781513214111</v>
       </c>
       <c r="C619" t="n">
-        <v>10.60782721634484</v>
+        <v>10.60782820352242</v>
       </c>
       <c r="D619" t="n">
-        <v>10.23106985549739</v>
+        <v>10.23107080761346</v>
       </c>
       <c r="E619" t="n">
-        <v>10.57433772923638</v>
+        <v>10.57433871329738</v>
       </c>
       <c r="F619" t="n">
         <v>234192</v>
@@ -12812,16 +12812,16 @@
         <v>45218</v>
       </c>
       <c r="B620" t="n">
-        <v>10.3482837677002</v>
+        <v>10.34828281402588</v>
       </c>
       <c r="C620" t="n">
-        <v>10.49061473430172</v>
+        <v>10.4906137675105</v>
       </c>
       <c r="D620" t="n">
-        <v>10.28130562735265</v>
+        <v>10.28130467985089</v>
       </c>
       <c r="E620" t="n">
-        <v>10.30642211454433</v>
+        <v>10.30642116472789</v>
       </c>
       <c r="F620" t="n">
         <v>130844</v>
@@ -12852,16 +12852,16 @@
         <v>45222</v>
       </c>
       <c r="B622" t="n">
-        <v>10.99295902252197</v>
+        <v>10.99295806884766</v>
       </c>
       <c r="C622" t="n">
-        <v>11.13528999228917</v>
+        <v>11.13528902626719</v>
       </c>
       <c r="D622" t="n">
-        <v>10.80039339491465</v>
+        <v>10.80039245794601</v>
       </c>
       <c r="E622" t="n">
-        <v>10.82551156500447</v>
+        <v>10.82551062585675</v>
       </c>
       <c r="F622" t="n">
         <v>1034956</v>
@@ -12912,16 +12912,16 @@
         <v>45225</v>
       </c>
       <c r="B625" t="n">
-        <v>11.32785224914551</v>
+        <v>11.32785415649414</v>
       </c>
       <c r="C625" t="n">
-        <v>11.6376314484243</v>
+        <v>11.6376334079326</v>
       </c>
       <c r="D625" t="n">
-        <v>11.25250112038145</v>
+        <v>11.2525030150427</v>
       </c>
       <c r="E625" t="n">
-        <v>11.26087328109533</v>
+        <v>11.26087517716626</v>
       </c>
       <c r="F625" t="n">
         <v>344599</v>
@@ -12952,16 +12952,16 @@
         <v>45229</v>
       </c>
       <c r="B627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="C627" t="n">
-        <v>11.07668177956321</v>
+        <v>11.07668279217249</v>
       </c>
       <c r="D627" t="n">
-        <v>10.4320068359375</v>
+        <v>10.43200778961182</v>
       </c>
       <c r="E627" t="n">
-        <v>10.99295764074342</v>
+        <v>10.9929586456988</v>
       </c>
       <c r="F627" t="n">
         <v>312572</v>
@@ -12972,16 +12972,16 @@
         <v>45230</v>
       </c>
       <c r="B628" t="n">
-        <v>10.68783855438232</v>
+        <v>10.68783950805664</v>
       </c>
       <c r="C628" t="n">
-        <v>10.70476345459523</v>
+        <v>10.70476440977975</v>
       </c>
       <c r="D628" t="n">
-        <v>10.06163084967988</v>
+        <v>10.06163174747778</v>
       </c>
       <c r="E628" t="n">
-        <v>10.57782967869298</v>
+        <v>10.57783062255122</v>
       </c>
       <c r="F628" t="n">
         <v>335223</v>
@@ -12992,16 +12992,16 @@
         <v>45231</v>
       </c>
       <c r="B629" t="n">
-        <v>10.78092384338379</v>
+        <v>10.78092288970947</v>
       </c>
       <c r="C629" t="n">
-        <v>10.78092384338379</v>
+        <v>10.78092288970947</v>
       </c>
       <c r="D629" t="n">
-        <v>10.45935752710632</v>
+        <v>10.45935660187757</v>
       </c>
       <c r="E629" t="n">
-        <v>10.54398033141075</v>
+        <v>10.54397939869632</v>
       </c>
       <c r="F629" t="n">
         <v>233349</v>
@@ -13012,16 +13012,16 @@
         <v>45233</v>
       </c>
       <c r="B630" t="n">
-        <v>11.21249961853027</v>
+        <v>11.21250057220459</v>
       </c>
       <c r="C630" t="n">
-        <v>11.21249961853027</v>
+        <v>11.21250057220459</v>
       </c>
       <c r="D630" t="n">
-        <v>10.68783875467755</v>
+        <v>10.68783966372706</v>
       </c>
       <c r="E630" t="n">
-        <v>10.78938645746115</v>
+        <v>10.78938737514776</v>
       </c>
       <c r="F630" t="n">
         <v>226607</v>
@@ -13032,16 +13032,16 @@
         <v>45236</v>
       </c>
       <c r="B631" t="n">
-        <v>11.18711185455322</v>
+        <v>11.18711280822754</v>
       </c>
       <c r="C631" t="n">
-        <v>11.21249963047462</v>
+        <v>11.21250058631318</v>
       </c>
       <c r="D631" t="n">
-        <v>10.96709409881691</v>
+        <v>10.96709503373525</v>
       </c>
       <c r="E631" t="n">
-        <v>11.1955747299265</v>
+        <v>11.19557568432226</v>
       </c>
       <c r="F631" t="n">
         <v>130949</v>
@@ -13052,16 +13052,16 @@
         <v>45237</v>
       </c>
       <c r="B632" t="n">
-        <v>11.22096157073975</v>
+        <v>11.22096252441406</v>
       </c>
       <c r="C632" t="n">
-        <v>11.50021605118209</v>
+        <v>11.50021702859036</v>
       </c>
       <c r="D632" t="n">
-        <v>10.97555604093904</v>
+        <v>10.97555697375624</v>
       </c>
       <c r="E632" t="n">
-        <v>11.24634849627058</v>
+        <v>11.24634945210255</v>
       </c>
       <c r="F632" t="n">
         <v>179726</v>
@@ -13092,16 +13092,16 @@
         <v>45239</v>
       </c>
       <c r="B634" t="n">
-        <v>11.33097171783447</v>
+        <v>11.33097076416016</v>
       </c>
       <c r="C634" t="n">
-        <v>11.63561228489743</v>
+        <v>11.63561130558296</v>
       </c>
       <c r="D634" t="n">
-        <v>11.25481093841988</v>
+        <v>11.25480999115565</v>
       </c>
       <c r="E634" t="n">
-        <v>11.33943374325882</v>
+        <v>11.3394327888723</v>
       </c>
       <c r="F634" t="n">
         <v>143591</v>
@@ -13212,16 +13212,16 @@
         <v>45250</v>
       </c>
       <c r="B640" t="n">
-        <v>12.99803733825684</v>
+        <v>12.99803829193115</v>
       </c>
       <c r="C640" t="n">
-        <v>13.12497196915852</v>
+        <v>13.12497293214611</v>
       </c>
       <c r="D640" t="n">
-        <v>12.59184906996684</v>
+        <v>12.59184999383886</v>
       </c>
       <c r="E640" t="n">
-        <v>12.73570690132464</v>
+        <v>12.7357078357516</v>
       </c>
       <c r="F640" t="n">
         <v>416026</v>
@@ -13392,16 +13392,16 @@
         <v>45261</v>
       </c>
       <c r="B649" t="n">
-        <v>13.22651863098145</v>
+        <v>13.22651958465576</v>
       </c>
       <c r="C649" t="n">
-        <v>13.35345240983534</v>
+        <v>13.35345337266199</v>
       </c>
       <c r="D649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="E649" t="n">
-        <v>12.98957512368167</v>
+        <v>12.9895760602716</v>
       </c>
       <c r="F649" t="n">
         <v>156128</v>
@@ -13432,16 +13432,16 @@
         <v>45265</v>
       </c>
       <c r="B651" t="n">
-        <v>12.83725452423096</v>
+        <v>12.83725357055664</v>
       </c>
       <c r="C651" t="n">
-        <v>12.94726511106283</v>
+        <v>12.94726414921587</v>
       </c>
       <c r="D651" t="n">
-        <v>12.73570766362991</v>
+        <v>12.73570671749947</v>
       </c>
       <c r="E651" t="n">
-        <v>12.7610945913298</v>
+        <v>12.76109364331337</v>
       </c>
       <c r="F651" t="n">
         <v>155706</v>
@@ -13472,16 +13472,16 @@
         <v>45267</v>
       </c>
       <c r="B653" t="n">
-        <v>12.5156888961792</v>
+        <v>12.51568794250488</v>
       </c>
       <c r="C653" t="n">
-        <v>12.5156888961792</v>
+        <v>12.51568794250488</v>
       </c>
       <c r="D653" t="n">
-        <v>12.16873563861405</v>
+        <v>12.16873471137699</v>
       </c>
       <c r="E653" t="n">
-        <v>12.16873563861405</v>
+        <v>12.16873471137699</v>
       </c>
       <c r="F653" t="n">
         <v>114831</v>
@@ -13492,16 +13492,16 @@
         <v>45268</v>
       </c>
       <c r="B654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="C654" t="n">
-        <v>12.90495300292969</v>
+        <v>12.90495204925537</v>
       </c>
       <c r="D654" t="n">
-        <v>12.30413217772953</v>
+        <v>12.30413126845579</v>
       </c>
       <c r="E654" t="n">
-        <v>12.51568877039725</v>
+        <v>12.51568784548951</v>
       </c>
       <c r="F654" t="n">
         <v>119361</v>
@@ -13532,16 +13532,16 @@
         <v>45272</v>
       </c>
       <c r="B656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="C656" t="n">
-        <v>13.31960391998291</v>
+        <v>13.31960296630859</v>
       </c>
       <c r="D656" t="n">
-        <v>12.76109408341076</v>
+        <v>12.76109316972536</v>
       </c>
       <c r="E656" t="n">
-        <v>12.93033884434287</v>
+        <v>12.93033791853966</v>
       </c>
       <c r="F656" t="n">
         <v>175196</v>
@@ -13632,16 +13632,16 @@
         <v>45279</v>
       </c>
       <c r="B661" t="n">
-        <v>13.3957633972168</v>
+        <v>13.39576435089111</v>
       </c>
       <c r="C661" t="n">
-        <v>13.4549992740911</v>
+        <v>13.45500023198255</v>
       </c>
       <c r="D661" t="n">
-        <v>13.17574479034014</v>
+        <v>13.17574572835084</v>
       </c>
       <c r="E661" t="n">
-        <v>13.20959289118437</v>
+        <v>13.20959383160479</v>
       </c>
       <c r="F661" t="n">
         <v>220918</v>
@@ -13652,16 +13652,16 @@
         <v>45280</v>
       </c>
       <c r="B662" t="n">
-        <v>13.45499897003174</v>
+        <v>13.45499992370605</v>
       </c>
       <c r="C662" t="n">
-        <v>13.70040449719429</v>
+        <v>13.70040546826266</v>
       </c>
       <c r="D662" t="n">
-        <v>13.32806519394055</v>
+        <v>13.32806613861795</v>
       </c>
       <c r="E662" t="n">
-        <v>13.38730021927779</v>
+        <v>13.3873011681537</v>
       </c>
       <c r="F662" t="n">
         <v>1178969</v>
@@ -13692,16 +13692,16 @@
         <v>45282</v>
       </c>
       <c r="B664" t="n">
-        <v>13.88704872131348</v>
+        <v>13.88704776763916</v>
       </c>
       <c r="C664" t="n">
-        <v>14.31516630333975</v>
+        <v>14.31516532026503</v>
       </c>
       <c r="D664" t="n">
-        <v>13.74434345803615</v>
+        <v>13.74434251416193</v>
       </c>
       <c r="E664" t="n">
-        <v>13.89596757624402</v>
+        <v>13.89596662195722</v>
       </c>
       <c r="F664" t="n">
         <v>242936</v>
@@ -13732,16 +13732,16 @@
         <v>45287</v>
       </c>
       <c r="B666" t="n">
-        <v>14.54706287384033</v>
+        <v>14.54706192016602</v>
       </c>
       <c r="C666" t="n">
-        <v>14.54706287384033</v>
+        <v>14.54706192016602</v>
       </c>
       <c r="D666" t="n">
-        <v>13.89596764275405</v>
+        <v>13.89596673176415</v>
       </c>
       <c r="E666" t="n">
-        <v>14.18137906677191</v>
+        <v>14.18137813707104</v>
       </c>
       <c r="F666" t="n">
         <v>258949</v>
@@ -13772,16 +13772,16 @@
         <v>45293</v>
       </c>
       <c r="B668" t="n">
-        <v>14.0832691192627</v>
+        <v>14.08326816558838</v>
       </c>
       <c r="C668" t="n">
-        <v>14.5738195893155</v>
+        <v>14.57381860242266</v>
       </c>
       <c r="D668" t="n">
-        <v>13.94056385382812</v>
+        <v>13.94056290981735</v>
       </c>
       <c r="E668" t="n">
-        <v>14.27057045221845</v>
+        <v>14.27056948586068</v>
       </c>
       <c r="F668" t="n">
         <v>272434</v>
@@ -13792,16 +13792,16 @@
         <v>45294</v>
       </c>
       <c r="B669" t="n">
-        <v>14.23489379882812</v>
+        <v>14.23489284515381</v>
       </c>
       <c r="C669" t="n">
-        <v>14.35976135117554</v>
+        <v>14.35976038913565</v>
       </c>
       <c r="D669" t="n">
-        <v>13.64623324870215</v>
+        <v>13.64623233446546</v>
       </c>
       <c r="E669" t="n">
-        <v>13.92272402186245</v>
+        <v>13.92272308910211</v>
       </c>
       <c r="F669" t="n">
         <v>120520</v>
@@ -13832,16 +13832,16 @@
         <v>45296</v>
       </c>
       <c r="B671" t="n">
-        <v>13.96731853485107</v>
+        <v>13.96731948852539</v>
       </c>
       <c r="C671" t="n">
-        <v>14.27056852713726</v>
+        <v>14.27056950151718</v>
       </c>
       <c r="D671" t="n">
-        <v>13.86920845407544</v>
+        <v>13.8692094010509</v>
       </c>
       <c r="E671" t="n">
-        <v>13.97623828481034</v>
+        <v>13.97623923909369</v>
       </c>
       <c r="F671" t="n">
         <v>90074</v>
@@ -13852,16 +13852,16 @@
         <v>45299</v>
       </c>
       <c r="B672" t="n">
-        <v>13.7978572845459</v>
+        <v>13.79785633087158</v>
       </c>
       <c r="C672" t="n">
-        <v>13.97623975716477</v>
+        <v>13.97623879116109</v>
       </c>
       <c r="D672" t="n">
-        <v>13.66407087813031</v>
+        <v>13.66406993370299</v>
       </c>
       <c r="E672" t="n">
-        <v>13.96732000626583</v>
+        <v>13.96731904087866</v>
       </c>
       <c r="F672" t="n">
         <v>138218</v>
@@ -13892,16 +13892,16 @@
         <v>45301</v>
       </c>
       <c r="B674" t="n">
-        <v>13.97623825073242</v>
+        <v>13.97623920440674</v>
       </c>
       <c r="C674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="D674" t="n">
-        <v>13.82461235886199</v>
+        <v>13.82461330219005</v>
       </c>
       <c r="E674" t="n">
-        <v>14.22597332704223</v>
+        <v>14.22597429775732</v>
       </c>
       <c r="F674" t="n">
         <v>252102</v>
@@ -13912,16 +13912,16 @@
         <v>45302</v>
       </c>
       <c r="B675" t="n">
-        <v>14.20813465118408</v>
+        <v>14.2081356048584</v>
       </c>
       <c r="C675" t="n">
-        <v>14.20813465118408</v>
+        <v>14.2081356048584</v>
       </c>
       <c r="D675" t="n">
-        <v>13.64623248909294</v>
+        <v>13.64623340505142</v>
       </c>
       <c r="E675" t="n">
-        <v>14.13678292022506</v>
+        <v>14.13678386911013</v>
       </c>
       <c r="F675" t="n">
         <v>191209</v>
@@ -13992,16 +13992,16 @@
         <v>45308</v>
       </c>
       <c r="B679" t="n">
-        <v>14.37759780883789</v>
+        <v>14.37759876251221</v>
       </c>
       <c r="C679" t="n">
-        <v>14.52922280864108</v>
+        <v>14.52922377237277</v>
       </c>
       <c r="D679" t="n">
-        <v>14.24381141328681</v>
+        <v>14.243812358087</v>
       </c>
       <c r="E679" t="n">
-        <v>14.3240837882757</v>
+        <v>14.3240847384004</v>
       </c>
       <c r="F679" t="n">
         <v>153283</v>
@@ -14112,16 +14112,16 @@
         <v>45316</v>
       </c>
       <c r="B685" t="n">
-        <v>14.57381820678711</v>
+        <v>14.57381916046143</v>
       </c>
       <c r="C685" t="n">
-        <v>14.77003837619403</v>
+        <v>14.77003934270851</v>
       </c>
       <c r="D685" t="n">
-        <v>14.46678926786436</v>
+        <v>14.46679021453496</v>
       </c>
       <c r="E685" t="n">
-        <v>14.60949541585844</v>
+        <v>14.60949637186738</v>
       </c>
       <c r="F685" t="n">
         <v>152967</v>
@@ -14252,16 +14252,16 @@
         <v>45327</v>
       </c>
       <c r="B692" t="n">
-        <v>13.21811485290527</v>
+        <v>13.21811580657959</v>
       </c>
       <c r="C692" t="n">
-        <v>13.76218019901698</v>
+        <v>13.76218119194509</v>
       </c>
       <c r="D692" t="n">
-        <v>13.21811485290527</v>
+        <v>13.21811580657959</v>
       </c>
       <c r="E692" t="n">
-        <v>13.76218019901698</v>
+        <v>13.76218119194509</v>
       </c>
       <c r="F692" t="n">
         <v>142538</v>
@@ -14272,16 +14272,16 @@
         <v>45328</v>
       </c>
       <c r="B693" t="n">
-        <v>13.41433429718018</v>
+        <v>13.41433525085449</v>
       </c>
       <c r="C693" t="n">
-        <v>13.47676806610936</v>
+        <v>13.47676902422233</v>
       </c>
       <c r="D693" t="n">
-        <v>13.08432774489562</v>
+        <v>13.08432867510856</v>
       </c>
       <c r="E693" t="n">
-        <v>13.20027553283766</v>
+        <v>13.20027647129375</v>
       </c>
       <c r="F693" t="n">
         <v>1178021</v>
@@ -14352,16 +14352,16 @@
         <v>45336</v>
       </c>
       <c r="B697" t="n">
-        <v>13.5392017364502</v>
+        <v>13.53920078277588</v>
       </c>
       <c r="C697" t="n">
-        <v>13.86920920427044</v>
+        <v>13.86920822735105</v>
       </c>
       <c r="D697" t="n">
-        <v>13.43217279602306</v>
+        <v>13.43217184988765</v>
       </c>
       <c r="E697" t="n">
-        <v>13.86920920427044</v>
+        <v>13.86920822735105</v>
       </c>
       <c r="F697" t="n">
         <v>116200</v>
@@ -14372,16 +14372,16 @@
         <v>45337</v>
       </c>
       <c r="B698" t="n">
-        <v>13.5124454498291</v>
+        <v>13.51244449615479</v>
       </c>
       <c r="C698" t="n">
-        <v>13.65515160274826</v>
+        <v>13.6551506390021</v>
       </c>
       <c r="D698" t="n">
-        <v>13.33406298270443</v>
+        <v>13.3340620416199</v>
       </c>
       <c r="E698" t="n">
-        <v>13.5124454498291</v>
+        <v>13.51244449615479</v>
       </c>
       <c r="F698" t="n">
         <v>118097</v>
@@ -14392,16 +14392,16 @@
         <v>45338</v>
       </c>
       <c r="B699" t="n">
-        <v>13.88704872131348</v>
+        <v>13.88704776763916</v>
       </c>
       <c r="C699" t="n">
-        <v>14.1278649732154</v>
+        <v>14.12786400300335</v>
       </c>
       <c r="D699" t="n">
-        <v>13.29838727005164</v>
+        <v>13.29838635680286</v>
       </c>
       <c r="E699" t="n">
-        <v>13.51244606106478</v>
+        <v>13.51244513311579</v>
       </c>
       <c r="F699" t="n">
         <v>253260</v>
@@ -14452,16 +14452,16 @@
         <v>45343</v>
       </c>
       <c r="B702" t="n">
-        <v>13.75326156616211</v>
+        <v>13.75326061248779</v>
       </c>
       <c r="C702" t="n">
-        <v>14.09218699609062</v>
+        <v>14.09218601891464</v>
       </c>
       <c r="D702" t="n">
-        <v>13.5213641817828</v>
+        <v>13.52136324418864</v>
       </c>
       <c r="E702" t="n">
-        <v>13.85137165336216</v>
+        <v>13.85137069288472</v>
       </c>
       <c r="F702" t="n">
         <v>146120</v>
@@ -14472,16 +14472,16 @@
         <v>45344</v>
       </c>
       <c r="B703" t="n">
-        <v>13.71758460998535</v>
+        <v>13.71758556365967</v>
       </c>
       <c r="C703" t="n">
-        <v>13.8335342004174</v>
+        <v>13.83353516215277</v>
       </c>
       <c r="D703" t="n">
-        <v>13.37865917378605</v>
+        <v>13.37866010389759</v>
       </c>
       <c r="E703" t="n">
-        <v>13.77109952984718</v>
+        <v>13.77110048724197</v>
       </c>
       <c r="F703" t="n">
         <v>122205</v>
@@ -14512,16 +14512,16 @@
         <v>45348</v>
       </c>
       <c r="B705" t="n">
-        <v>13.5392017364502</v>
+        <v>13.53920078277588</v>
       </c>
       <c r="C705" t="n">
-        <v>13.73542190861516</v>
+        <v>13.73542094111948</v>
       </c>
       <c r="D705" t="n">
-        <v>13.30730525080952</v>
+        <v>13.30730431346953</v>
       </c>
       <c r="E705" t="n">
-        <v>13.52136402776089</v>
+        <v>13.52136307534302</v>
       </c>
       <c r="F705" t="n">
         <v>310571</v>
@@ -14692,16 +14692,16 @@
         <v>45359</v>
       </c>
       <c r="B714" t="n">
-        <v>13.41433429718018</v>
+        <v>13.41433525085449</v>
       </c>
       <c r="C714" t="n">
-        <v>13.42325315099948</v>
+        <v>13.42325410530787</v>
       </c>
       <c r="D714" t="n">
-        <v>12.96837906085655</v>
+        <v>12.96837998282627</v>
       </c>
       <c r="E714" t="n">
-        <v>13.15567947154708</v>
+        <v>13.15568040683267</v>
       </c>
       <c r="F714" t="n">
         <v>200691</v>
@@ -14732,16 +14732,16 @@
         <v>45363</v>
       </c>
       <c r="B716" t="n">
-        <v>15.42113304138184</v>
+        <v>15.42113399505615</v>
       </c>
       <c r="C716" t="n">
-        <v>15.98303607223336</v>
+        <v>15.98303706065691</v>
       </c>
       <c r="D716" t="n">
-        <v>13.85137084203124</v>
+        <v>13.85137169862826</v>
       </c>
       <c r="E716" t="n">
-        <v>14.09218617065416</v>
+        <v>14.09218704214369</v>
       </c>
       <c r="F716" t="n">
         <v>1351743</v>
@@ -14752,16 +14752,16 @@
         <v>45364</v>
       </c>
       <c r="B717" t="n">
-        <v>15.79573631286621</v>
+        <v>15.79573535919189</v>
       </c>
       <c r="C717" t="n">
-        <v>15.99195648389114</v>
+        <v>15.99195551836995</v>
       </c>
       <c r="D717" t="n">
-        <v>15.33194334427948</v>
+        <v>15.33194241860686</v>
       </c>
       <c r="E717" t="n">
-        <v>15.33194334427948</v>
+        <v>15.33194241860686</v>
       </c>
       <c r="F717" t="n">
         <v>474916</v>
@@ -14792,16 +14792,16 @@
         <v>45366</v>
       </c>
       <c r="B719" t="n">
-        <v>15.77789878845215</v>
+        <v>15.77789974212646</v>
       </c>
       <c r="C719" t="n">
-        <v>15.86708912461579</v>
+        <v>15.8670900836811</v>
       </c>
       <c r="D719" t="n">
-        <v>15.37653869132738</v>
+        <v>15.37653962074202</v>
       </c>
       <c r="E719" t="n">
-        <v>15.67978870179447</v>
+        <v>15.67978964953865</v>
       </c>
       <c r="F719" t="n">
         <v>999032</v>
@@ -14832,16 +14832,16 @@
         <v>45370</v>
       </c>
       <c r="B721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="C721" t="n">
-        <v>16.15250015258789</v>
+        <v>16.15250205993652</v>
       </c>
       <c r="D721" t="n">
-        <v>15.61735280122237</v>
+        <v>15.61735464537877</v>
       </c>
       <c r="E721" t="n">
-        <v>15.8314124586462</v>
+        <v>15.83141432807958</v>
       </c>
       <c r="F721" t="n">
         <v>227239</v>
@@ -14852,16 +14852,16 @@
         <v>45371</v>
       </c>
       <c r="B722" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="C722" t="n">
-        <v>16.2952069476677</v>
+        <v>16.29520886762698</v>
       </c>
       <c r="D722" t="n">
-        <v>16.08114726986159</v>
+        <v>16.08114916459959</v>
       </c>
       <c r="E722" t="n">
-        <v>16.15250169059311</v>
+        <v>16.15250359373834</v>
       </c>
       <c r="F722" t="n">
         <v>449422</v>
@@ -14872,16 +14872,16 @@
         <v>45372</v>
       </c>
       <c r="B723" t="n">
-        <v>16.58061790466309</v>
+        <v>16.58061981201172</v>
       </c>
       <c r="C723" t="n">
-        <v>16.58061790466309</v>
+        <v>16.58061981201172</v>
       </c>
       <c r="D723" t="n">
-        <v>16.11682316862342</v>
+        <v>16.1168250226195</v>
       </c>
       <c r="E723" t="n">
-        <v>16.25061045636449</v>
+        <v>16.25061232575078</v>
       </c>
       <c r="F723" t="n">
         <v>298350</v>
@@ -14892,16 +14892,16 @@
         <v>45373</v>
       </c>
       <c r="B724" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="C724" t="n">
-        <v>16.65197009035419</v>
+        <v>16.65197205234856</v>
       </c>
       <c r="D724" t="n">
-        <v>16.18817710876465</v>
+        <v>16.18817901611328</v>
       </c>
       <c r="E724" t="n">
-        <v>16.42007449565653</v>
+        <v>16.42007643032814</v>
       </c>
       <c r="F724" t="n">
         <v>404437</v>
@@ -14952,16 +14952,16 @@
         <v>45378</v>
       </c>
       <c r="B727" t="n">
-        <v>15.43005466461182</v>
+        <v>15.4300537109375</v>
       </c>
       <c r="C727" t="n">
-        <v>15.75114240582048</v>
+        <v>15.75114143230092</v>
       </c>
       <c r="D727" t="n">
-        <v>14.90382698557158</v>
+        <v>14.90382606442144</v>
       </c>
       <c r="E727" t="n">
-        <v>15.23383447788399</v>
+        <v>15.23383353633731</v>
       </c>
       <c r="F727" t="n">
         <v>340806</v>
@@ -14972,16 +14972,16 @@
         <v>45379</v>
       </c>
       <c r="B728" t="n">
-        <v>16.32196235656738</v>
+        <v>16.32196426391602</v>
       </c>
       <c r="C728" t="n">
-        <v>16.55385792212777</v>
+        <v>16.55385985657521</v>
       </c>
       <c r="D728" t="n">
-        <v>15.26058922811916</v>
+        <v>15.26059101143806</v>
       </c>
       <c r="E728" t="n">
-        <v>15.43005192362683</v>
+        <v>15.43005372674877</v>
       </c>
       <c r="F728" t="n">
         <v>647795</v>
@@ -14992,16 +14992,16 @@
         <v>45383</v>
       </c>
       <c r="B729" t="n">
-        <v>16.41115379333496</v>
+        <v>16.41115570068359</v>
       </c>
       <c r="C729" t="n">
-        <v>16.52710158395999</v>
+        <v>16.52710350478439</v>
       </c>
       <c r="D729" t="n">
-        <v>16.06330862926576</v>
+        <v>16.06331049618689</v>
       </c>
       <c r="E729" t="n">
-        <v>16.25061083648447</v>
+        <v>16.25061272517437</v>
       </c>
       <c r="F729" t="n">
         <v>424348</v>
@@ -15052,16 +15052,16 @@
         <v>45386</v>
       </c>
       <c r="B732" t="n">
-        <v>15.83141326904297</v>
+        <v>15.83141231536865</v>
       </c>
       <c r="C732" t="n">
-        <v>16.42007377270343</v>
+        <v>16.42007278356858</v>
       </c>
       <c r="D732" t="n">
-        <v>15.83141326904297</v>
+        <v>15.83141231536865</v>
       </c>
       <c r="E732" t="n">
-        <v>16.1079058125728</v>
+        <v>16.10790484224275</v>
       </c>
       <c r="F732" t="n">
         <v>700260</v>
@@ -15092,16 +15092,16 @@
         <v>45390</v>
       </c>
       <c r="B734" t="n">
-        <v>15.22491455078125</v>
+        <v>15.22491359710693</v>
       </c>
       <c r="C734" t="n">
-        <v>15.84033256496746</v>
+        <v>15.84033157274394</v>
       </c>
       <c r="D734" t="n">
-        <v>15.20707684097428</v>
+        <v>15.2070758884173</v>
       </c>
       <c r="E734" t="n">
-        <v>15.7422224727377</v>
+        <v>15.7422214866597</v>
       </c>
       <c r="F734" t="n">
         <v>693201</v>
@@ -15112,16 +15112,16 @@
         <v>45391</v>
       </c>
       <c r="B735" t="n">
-        <v>15.51924228668213</v>
+        <v>15.51924419403076</v>
       </c>
       <c r="C735" t="n">
-        <v>15.59059490642255</v>
+        <v>15.59059682254057</v>
       </c>
       <c r="D735" t="n">
-        <v>15.21599230863985</v>
+        <v>15.2159941787184</v>
       </c>
       <c r="E735" t="n">
-        <v>15.26950722149366</v>
+        <v>15.26950909814931</v>
       </c>
       <c r="F735" t="n">
         <v>380734</v>
@@ -15132,16 +15132,16 @@
         <v>45392</v>
       </c>
       <c r="B736" t="n">
-        <v>15.14328002929688</v>
+        <v>15.14327907562256</v>
       </c>
       <c r="C736" t="n">
-        <v>15.53754305795394</v>
+        <v>15.53754207945022</v>
       </c>
       <c r="D736" t="n">
-        <v>15.05367389941404</v>
+        <v>15.05367295138282</v>
       </c>
       <c r="E736" t="n">
-        <v>15.53754305795394</v>
+        <v>15.53754207945022</v>
       </c>
       <c r="F736" t="n">
         <v>317419</v>
@@ -15152,16 +15152,16 @@
         <v>45393</v>
       </c>
       <c r="B737" t="n">
-        <v>14.95510768890381</v>
+        <v>14.95510864257812</v>
       </c>
       <c r="C737" t="n">
-        <v>15.2060023283815</v>
+        <v>15.20600329805515</v>
       </c>
       <c r="D737" t="n">
-        <v>14.75797708255414</v>
+        <v>14.75797802365761</v>
       </c>
       <c r="E737" t="n">
-        <v>15.02679276770881</v>
+        <v>15.02679372595442</v>
       </c>
       <c r="F737" t="n">
         <v>214129</v>
@@ -15172,16 +15172,16 @@
         <v>45394</v>
       </c>
       <c r="B738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="C738" t="n">
-        <v>15.1432798316879</v>
+        <v>15.14327886659233</v>
       </c>
       <c r="D738" t="n">
-        <v>14.76693785469897</v>
+        <v>14.76693691358803</v>
       </c>
       <c r="E738" t="n">
-        <v>14.96406936645508</v>
+        <v>14.96406841278076</v>
       </c>
       <c r="F738" t="n">
         <v>376247</v>
@@ -15252,16 +15252,16 @@
         <v>45400</v>
       </c>
       <c r="B742" t="n">
-        <v>14.8834228515625</v>
+        <v>14.88342380523682</v>
       </c>
       <c r="C742" t="n">
-        <v>15.29560598790641</v>
+        <v>15.29560696799188</v>
       </c>
       <c r="D742" t="n">
-        <v>14.83862068738918</v>
+        <v>14.83862163819274</v>
       </c>
       <c r="E742" t="n">
-        <v>14.87446277716666</v>
+        <v>14.87446373026684</v>
       </c>
       <c r="F742" t="n">
         <v>502607</v>
@@ -15292,16 +15292,16 @@
         <v>45404</v>
       </c>
       <c r="B744" t="n">
-        <v>15.77051448822021</v>
+        <v>15.77051544189453</v>
       </c>
       <c r="C744" t="n">
-        <v>15.87804076002569</v>
+        <v>15.87804172020233</v>
       </c>
       <c r="D744" t="n">
-        <v>15.09847573748455</v>
+        <v>15.09847665051934</v>
       </c>
       <c r="E744" t="n">
-        <v>15.18808006789204</v>
+        <v>15.18808098634539</v>
       </c>
       <c r="F744" t="n">
         <v>1943528</v>
@@ -15372,16 +15372,16 @@
         <v>45408</v>
       </c>
       <c r="B748" t="n">
-        <v>16.41567420959473</v>
+        <v>16.41567230224609</v>
       </c>
       <c r="C748" t="n">
-        <v>16.74721403793184</v>
+        <v>16.74721209206137</v>
       </c>
       <c r="D748" t="n">
-        <v>16.14685939194446</v>
+        <v>16.14685751582961</v>
       </c>
       <c r="E748" t="n">
-        <v>16.48735839992738</v>
+        <v>16.48735648424971</v>
       </c>
       <c r="F748" t="n">
         <v>618795</v>
@@ -15392,16 +15392,16 @@
         <v>45411</v>
       </c>
       <c r="B749" t="n">
-        <v>16.50527954101562</v>
+        <v>16.50527763366699</v>
       </c>
       <c r="C749" t="n">
-        <v>16.50527954101562</v>
+        <v>16.50527763366699</v>
       </c>
       <c r="D749" t="n">
-        <v>16.23646294424257</v>
+        <v>16.23646106795836</v>
       </c>
       <c r="E749" t="n">
-        <v>16.40671243995541</v>
+        <v>16.40671054399719</v>
       </c>
       <c r="F749" t="n">
         <v>222938</v>
@@ -15492,16 +15492,16 @@
         <v>45419</v>
       </c>
       <c r="B754" t="n">
-        <v>16.57696151733398</v>
+        <v>16.57696342468262</v>
       </c>
       <c r="C754" t="n">
-        <v>16.6665658428468</v>
+        <v>16.66656776050532</v>
       </c>
       <c r="D754" t="n">
-        <v>16.29022480818252</v>
+        <v>16.29022668253917</v>
       </c>
       <c r="E754" t="n">
-        <v>16.41567122233926</v>
+        <v>16.4156731111298</v>
       </c>
       <c r="F754" t="n">
         <v>374150</v>
@@ -15552,16 +15552,16 @@
         <v>45422</v>
       </c>
       <c r="B757" t="n">
-        <v>16.10205459594727</v>
+        <v>16.1020565032959</v>
       </c>
       <c r="C757" t="n">
-        <v>16.83681657186323</v>
+        <v>16.83681856624717</v>
       </c>
       <c r="D757" t="n">
-        <v>16.07517168331335</v>
+        <v>16.0751735874776</v>
       </c>
       <c r="E757" t="n">
-        <v>16.82785739317944</v>
+        <v>16.82785938650213</v>
       </c>
       <c r="F757" t="n">
         <v>188543</v>
@@ -15572,16 +15572,16 @@
         <v>45425</v>
       </c>
       <c r="B758" t="n">
-        <v>15.76155471801758</v>
+        <v>15.76155376434326</v>
       </c>
       <c r="C758" t="n">
-        <v>15.94076518467647</v>
+        <v>15.94076422015877</v>
       </c>
       <c r="D758" t="n">
-        <v>15.68091135216679</v>
+        <v>15.68091040337191</v>
       </c>
       <c r="E758" t="n">
-        <v>15.90492309134469</v>
+        <v>15.90492212899567</v>
       </c>
       <c r="F758" t="n">
         <v>299278</v>
@@ -15592,16 +15592,16 @@
         <v>45426</v>
       </c>
       <c r="B759" t="n">
-        <v>15.61818790435791</v>
+        <v>15.61818695068359</v>
       </c>
       <c r="C759" t="n">
-        <v>15.74363433305432</v>
+        <v>15.74363337172002</v>
       </c>
       <c r="D759" t="n">
-        <v>15.38521340507279</v>
+        <v>15.38521246562432</v>
       </c>
       <c r="E759" t="n">
-        <v>15.67195014745801</v>
+        <v>15.67194919050088</v>
       </c>
       <c r="F759" t="n">
         <v>391243</v>
@@ -15612,16 +15612,16 @@
         <v>45427</v>
       </c>
       <c r="B760" t="n">
-        <v>15.76155471801758</v>
+        <v>15.76155376434326</v>
       </c>
       <c r="C760" t="n">
-        <v>15.88700294077594</v>
+        <v>15.8870019795112</v>
       </c>
       <c r="D760" t="n">
-        <v>15.09847688747684</v>
+        <v>15.09847597392295</v>
       </c>
       <c r="E760" t="n">
-        <v>15.59130522274021</v>
+        <v>15.59130427936707</v>
       </c>
       <c r="F760" t="n">
         <v>279879</v>
@@ -15632,16 +15632,16 @@
         <v>45428</v>
       </c>
       <c r="B761" t="n">
-        <v>15.81531810760498</v>
+        <v>15.8153190612793</v>
       </c>
       <c r="C761" t="n">
-        <v>16.12893596338921</v>
+        <v>16.1289369359749</v>
       </c>
       <c r="D761" t="n">
-        <v>15.63610764827196</v>
+        <v>15.63610859113976</v>
       </c>
       <c r="E761" t="n">
-        <v>15.80635713658978</v>
+        <v>15.80635808972374</v>
       </c>
       <c r="F761" t="n">
         <v>286904</v>
@@ -15652,16 +15652,16 @@
         <v>45429</v>
       </c>
       <c r="B762" t="n">
-        <v>15.41209411621094</v>
+        <v>15.41209316253662</v>
       </c>
       <c r="C762" t="n">
-        <v>15.87804131017911</v>
+        <v>15.87804032767277</v>
       </c>
       <c r="D762" t="n">
-        <v>15.27768671984559</v>
+        <v>15.27768577448818</v>
       </c>
       <c r="E762" t="n">
-        <v>15.83323824732593</v>
+        <v>15.83323726759193</v>
       </c>
       <c r="F762" t="n">
         <v>361357</v>
@@ -15712,16 +15712,16 @@
         <v>45434</v>
       </c>
       <c r="B765" t="n">
-        <v>14.92822647094727</v>
+        <v>14.92822742462158</v>
       </c>
       <c r="C765" t="n">
-        <v>15.1074369265467</v>
+        <v>15.10743789166969</v>
       </c>
       <c r="D765" t="n">
-        <v>14.82966027231904</v>
+        <v>14.82966121969655</v>
       </c>
       <c r="E765" t="n">
-        <v>15.0626338645983</v>
+        <v>15.06263482685909</v>
       </c>
       <c r="F765" t="n">
         <v>235522</v>
@@ -15732,16 +15732,16 @@
         <v>45435</v>
       </c>
       <c r="B766" t="n">
-        <v>14.87446403503418</v>
+        <v>14.87446308135986</v>
       </c>
       <c r="C766" t="n">
-        <v>14.94614822065114</v>
+        <v>14.9461472623808</v>
       </c>
       <c r="D766" t="n">
-        <v>14.73109566380025</v>
+        <v>14.73109471931798</v>
       </c>
       <c r="E766" t="n">
-        <v>14.93718724940046</v>
+        <v>14.93718629170465</v>
       </c>
       <c r="F766" t="n">
         <v>226398</v>
@@ -15852,16 +15852,16 @@
         <v>45446</v>
       </c>
       <c r="B772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="C772" t="n">
-        <v>15.36729159771533</v>
+        <v>15.36729261993504</v>
       </c>
       <c r="D772" t="n">
-        <v>14.33683109283447</v>
+        <v>14.33683204650879</v>
       </c>
       <c r="E772" t="n">
-        <v>14.69525198216746</v>
+        <v>14.69525295968364</v>
       </c>
       <c r="F772" t="n">
         <v>2218059</v>
@@ -15872,16 +15872,16 @@
         <v>45447</v>
       </c>
       <c r="B773" t="n">
-        <v>14.18450450897217</v>
+        <v>14.18450355529785</v>
       </c>
       <c r="C773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="D773" t="n">
-        <v>14.01425411633309</v>
+        <v>14.0142531741053</v>
       </c>
       <c r="E773" t="n">
-        <v>14.39059609911211</v>
+        <v>14.39059513158153</v>
       </c>
       <c r="F773" t="n">
         <v>553151</v>
@@ -15952,16 +15952,16 @@
         <v>45453</v>
       </c>
       <c r="B777" t="n">
-        <v>13.27949047088623</v>
+        <v>13.27949142456055</v>
       </c>
       <c r="C777" t="n">
-        <v>13.53038600843974</v>
+        <v>13.53038698013227</v>
       </c>
       <c r="D777" t="n">
-        <v>13.27949047088623</v>
+        <v>13.27949142456055</v>
       </c>
       <c r="E777" t="n">
-        <v>13.43181980839046</v>
+        <v>13.43182077300439</v>
       </c>
       <c r="F777" t="n">
         <v>375304</v>
@@ -16052,16 +16052,16 @@
         <v>45460</v>
       </c>
       <c r="B782" t="n">
-        <v>13.16300392150879</v>
+        <v>13.16300487518311</v>
       </c>
       <c r="C782" t="n">
-        <v>13.45870072497843</v>
+        <v>13.45870170007631</v>
       </c>
       <c r="D782" t="n">
-        <v>12.93899040412829</v>
+        <v>12.93899134157258</v>
       </c>
       <c r="E782" t="n">
-        <v>13.04651667740763</v>
+        <v>13.04651762264232</v>
       </c>
       <c r="F782" t="n">
         <v>743268</v>
@@ -16072,16 +16072,16 @@
         <v>45461</v>
       </c>
       <c r="B783" t="n">
-        <v>13.47662162780762</v>
+        <v>13.47662258148193</v>
       </c>
       <c r="C783" t="n">
-        <v>13.55726588386456</v>
+        <v>13.55726684324567</v>
       </c>
       <c r="D783" t="n">
-        <v>13.06443758460185</v>
+        <v>13.06443850910792</v>
       </c>
       <c r="E783" t="n">
-        <v>13.08235862995862</v>
+        <v>13.08235955573288</v>
       </c>
       <c r="F783" t="n">
         <v>385685</v>
@@ -16172,16 +16172,16 @@
         <v>45468</v>
       </c>
       <c r="B788" t="n">
-        <v>12.72393989562988</v>
+        <v>12.72393894195557</v>
       </c>
       <c r="C788" t="n">
-        <v>13.24364936702643</v>
+        <v>13.24364837439928</v>
       </c>
       <c r="D788" t="n">
-        <v>12.71497892400382</v>
+        <v>12.71497797100114</v>
       </c>
       <c r="E788" t="n">
-        <v>13.20780727271652</v>
+        <v>13.20780628277578</v>
       </c>
       <c r="F788" t="n">
         <v>394179</v>
@@ -16192,16 +16192,16 @@
         <v>45469</v>
       </c>
       <c r="B789" t="n">
-        <v>12.84042549133301</v>
+        <v>12.84042453765869</v>
       </c>
       <c r="C789" t="n">
-        <v>12.8941886296042</v>
+        <v>12.89418767193683</v>
       </c>
       <c r="D789" t="n">
-        <v>12.67017510542567</v>
+        <v>12.67017416439606</v>
       </c>
       <c r="E789" t="n">
-        <v>12.78666235306181</v>
+        <v>12.78666140338055</v>
       </c>
       <c r="F789" t="n">
         <v>397115</v>
@@ -16212,16 +16212,16 @@
         <v>45470</v>
       </c>
       <c r="B790" t="n">
-        <v>13.1809253692627</v>
+        <v>13.18092441558838</v>
       </c>
       <c r="C790" t="n">
-        <v>13.26157052473157</v>
+        <v>13.26156956522237</v>
       </c>
       <c r="D790" t="n">
-        <v>12.83146452239273</v>
+        <v>12.83146359400282</v>
       </c>
       <c r="E790" t="n">
-        <v>12.90314870676636</v>
+        <v>12.90314777318991</v>
       </c>
       <c r="F790" t="n">
         <v>447659</v>
@@ -16312,16 +16312,16 @@
         <v>45477</v>
       </c>
       <c r="B795" t="n">
-        <v>13.61102962493896</v>
+        <v>13.61103057861328</v>
       </c>
       <c r="C795" t="n">
-        <v>13.70063484980648</v>
+        <v>13.7006358097591</v>
       </c>
       <c r="D795" t="n">
-        <v>13.46766126515094</v>
+        <v>13.46766220877997</v>
       </c>
       <c r="E795" t="n">
-        <v>13.59310768386841</v>
+        <v>13.593108636287</v>
       </c>
       <c r="F795" t="n">
         <v>390823</v>
@@ -16332,16 +16332,16 @@
         <v>45478</v>
       </c>
       <c r="B796" t="n">
-        <v>13.54830551147461</v>
+        <v>13.54830646514893</v>
       </c>
       <c r="C796" t="n">
-        <v>13.8888053657699</v>
+        <v>13.88880634341223</v>
       </c>
       <c r="D796" t="n">
-        <v>13.27948983703096</v>
+        <v>13.27949077178316</v>
       </c>
       <c r="E796" t="n">
-        <v>13.87088521690404</v>
+        <v>13.87088619328496</v>
       </c>
       <c r="F796" t="n">
         <v>907063</v>
@@ -16532,16 +16532,16 @@
         <v>45492</v>
       </c>
       <c r="B806" t="n">
-        <v>13.79024028778076</v>
+        <v>13.79023933410645</v>
       </c>
       <c r="C806" t="n">
-        <v>13.89776656627055</v>
+        <v>13.89776560516017</v>
       </c>
       <c r="D806" t="n">
-        <v>13.65583288771709</v>
+        <v>13.65583194333782</v>
       </c>
       <c r="E806" t="n">
-        <v>13.89776656627055</v>
+        <v>13.89776560516017</v>
       </c>
       <c r="F806" t="n">
         <v>491387</v>
@@ -16552,16 +16552,16 @@
         <v>45495</v>
       </c>
       <c r="B807" t="n">
-        <v>13.98737335205078</v>
+        <v>13.98737239837646</v>
       </c>
       <c r="C807" t="n">
-        <v>14.11282068285336</v>
+        <v>14.11281972062591</v>
       </c>
       <c r="D807" t="n">
-        <v>13.79024093612098</v>
+        <v>13.79023999588737</v>
       </c>
       <c r="E807" t="n">
-        <v>13.79920190779832</v>
+        <v>13.79920096695374</v>
       </c>
       <c r="F807" t="n">
         <v>314378</v>
@@ -16592,16 +16592,16 @@
         <v>45497</v>
       </c>
       <c r="B809" t="n">
-        <v>13.58414840698242</v>
+        <v>13.58414745330811</v>
       </c>
       <c r="C809" t="n">
-        <v>13.77231983830065</v>
+        <v>13.77231887141577</v>
       </c>
       <c r="D809" t="n">
-        <v>13.52142429784398</v>
+        <v>13.5214233485732</v>
       </c>
       <c r="E809" t="n">
-        <v>13.72751677518789</v>
+        <v>13.7275158114484</v>
       </c>
       <c r="F809" t="n">
         <v>613342</v>
@@ -16692,16 +16692,16 @@
         <v>45504</v>
       </c>
       <c r="B814" t="n">
-        <v>13.43181896209717</v>
+        <v>13.43181991577148</v>
       </c>
       <c r="C814" t="n">
-        <v>13.61102940898888</v>
+        <v>13.61103037538734</v>
       </c>
       <c r="D814" t="n">
-        <v>13.40493694701489</v>
+        <v>13.40493789878055</v>
       </c>
       <c r="E814" t="n">
-        <v>13.46766105147551</v>
+        <v>13.46766200769466</v>
       </c>
       <c r="F814" t="n">
         <v>351395</v>
@@ -16712,16 +16712,16 @@
         <v>45505</v>
       </c>
       <c r="B815" t="n">
-        <v>13.36013603210449</v>
+        <v>13.36013507843018</v>
       </c>
       <c r="C815" t="n">
-        <v>13.64687277393235</v>
+        <v>13.64687179979016</v>
       </c>
       <c r="D815" t="n">
-        <v>13.29741281787821</v>
+        <v>13.29741186868121</v>
       </c>
       <c r="E815" t="n">
-        <v>13.44078029269502</v>
+        <v>13.44077933326414</v>
       </c>
       <c r="F815" t="n">
         <v>623514</v>
@@ -16792,16 +16792,16 @@
         <v>45511</v>
       </c>
       <c r="B819" t="n">
-        <v>12.93899059295654</v>
+        <v>12.93899154663086</v>
       </c>
       <c r="C819" t="n">
-        <v>13.00171470133341</v>
+        <v>13.00171565963084</v>
       </c>
       <c r="D819" t="n">
-        <v>12.75082006002013</v>
+        <v>12.75082099982525</v>
       </c>
       <c r="E819" t="n">
-        <v>13.00171470133341</v>
+        <v>13.00171565963084</v>
       </c>
       <c r="F819" t="n">
         <v>296971</v>
@@ -16812,16 +16812,16 @@
         <v>45512</v>
       </c>
       <c r="B820" t="n">
-        <v>12.8045825958252</v>
+        <v>12.80458354949951</v>
       </c>
       <c r="C820" t="n">
-        <v>13.10027938971694</v>
+        <v>13.1002803654145</v>
       </c>
       <c r="D820" t="n">
-        <v>12.8045825958252</v>
+        <v>12.80458354949951</v>
       </c>
       <c r="E820" t="n">
-        <v>13.00171409045204</v>
+        <v>13.00171505880854</v>
       </c>
       <c r="F820" t="n">
         <v>258486</v>
@@ -17112,16 +17112,16 @@
         <v>45533</v>
       </c>
       <c r="B835" t="n">
-        <v>11.42466354370117</v>
+        <v>11.42466449737549</v>
       </c>
       <c r="C835" t="n">
-        <v>12.123583432736</v>
+        <v>12.12358444475269</v>
       </c>
       <c r="D835" t="n">
-        <v>11.29921532719579</v>
+        <v>11.29921627039831</v>
       </c>
       <c r="E835" t="n">
-        <v>11.93541290017211</v>
+        <v>11.93541389648125</v>
       </c>
       <c r="F835" t="n">
         <v>1428127</v>
@@ -17152,16 +17152,16 @@
         <v>45537</v>
       </c>
       <c r="B837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="C837" t="n">
-        <v>11.68451881408691</v>
+        <v>11.6845178604126</v>
       </c>
       <c r="D837" t="n">
-        <v>11.42466408609577</v>
+        <v>11.42466315363044</v>
       </c>
       <c r="E837" t="n">
-        <v>11.56803156298606</v>
+        <v>11.56803061881927</v>
       </c>
       <c r="F837" t="n">
         <v>1157790</v>
@@ -17192,16 +17192,16 @@
         <v>45539</v>
       </c>
       <c r="B839" t="n">
-        <v>11.6486759185791</v>
+        <v>11.64867687225342</v>
       </c>
       <c r="C839" t="n">
-        <v>11.85476749250614</v>
+        <v>11.85476846305313</v>
       </c>
       <c r="D839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="E839" t="n">
-        <v>11.50530755546566</v>
+        <v>11.50530849740244</v>
       </c>
       <c r="F839" t="n">
         <v>552941</v>
@@ -17252,16 +17252,16 @@
         <v>45544</v>
       </c>
       <c r="B842" t="n">
-        <v>11.23649215698242</v>
+        <v>11.23649120330811</v>
       </c>
       <c r="C842" t="n">
-        <v>11.41570171928039</v>
+        <v>11.41570075039603</v>
       </c>
       <c r="D842" t="n">
-        <v>11.20961014017461</v>
+        <v>11.20960918878185</v>
       </c>
       <c r="E842" t="n">
-        <v>11.35297850689067</v>
+        <v>11.35297754332981</v>
       </c>
       <c r="F842" t="n">
         <v>579052</v>
@@ -17292,16 +17292,16 @@
         <v>45546</v>
       </c>
       <c r="B844" t="n">
-        <v>11.37985992431641</v>
+        <v>11.37986087799072</v>
       </c>
       <c r="C844" t="n">
-        <v>11.52322828348119</v>
+        <v>11.5232292491703</v>
       </c>
       <c r="D844" t="n">
-        <v>11.37089895382008</v>
+        <v>11.37089990674344</v>
       </c>
       <c r="E844" t="n">
-        <v>11.38882089481273</v>
+        <v>11.38882184923801</v>
       </c>
       <c r="F844" t="n">
         <v>345418</v>
@@ -17312,16 +17312,16 @@
         <v>45547</v>
       </c>
       <c r="B845" t="n">
-        <v>11.34401893615723</v>
+        <v>11.34401798248291</v>
       </c>
       <c r="C845" t="n">
-        <v>11.47842633787816</v>
+        <v>11.47842537290442</v>
       </c>
       <c r="D845" t="n">
-        <v>11.29025579624943</v>
+        <v>11.2902548470949</v>
       </c>
       <c r="E845" t="n">
-        <v>11.39778207606503</v>
+        <v>11.39778111787093</v>
       </c>
       <c r="F845" t="n">
         <v>413998</v>
@@ -17372,16 +17372,16 @@
         <v>45552</v>
       </c>
       <c r="B848" t="n">
-        <v>11.53218936920166</v>
+        <v>11.53219032287598</v>
       </c>
       <c r="C848" t="n">
-        <v>11.63075466906374</v>
+        <v>11.63075563088909</v>
       </c>
       <c r="D848" t="n">
-        <v>11.39778108309321</v>
+        <v>11.3977820256524</v>
       </c>
       <c r="E848" t="n">
-        <v>11.5232283986158</v>
+        <v>11.52322935154908</v>
       </c>
       <c r="F848" t="n">
         <v>1190193</v>
@@ -17392,16 +17392,16 @@
         <v>45553</v>
       </c>
       <c r="B849" t="n">
-        <v>11.42466354370117</v>
+        <v>11.42466449737549</v>
       </c>
       <c r="C849" t="n">
-        <v>11.71139937996589</v>
+        <v>11.7114003575755</v>
       </c>
       <c r="D849" t="n">
-        <v>11.39778152699371</v>
+        <v>11.39778247842404</v>
       </c>
       <c r="E849" t="n">
-        <v>11.63075512203768</v>
+        <v>11.6307560929155</v>
       </c>
       <c r="F849" t="n">
         <v>662418</v>
@@ -17512,16 +17512,16 @@
         <v>45561</v>
       </c>
       <c r="B855" t="n">
-        <v>10.49276828765869</v>
+        <v>10.49276733398438</v>
       </c>
       <c r="C855" t="n">
-        <v>10.60029456250169</v>
+        <v>10.60029359905444</v>
       </c>
       <c r="D855" t="n">
-        <v>10.41212402957499</v>
+        <v>10.41212308323033</v>
       </c>
       <c r="E855" t="n">
-        <v>10.43900604633429</v>
+        <v>10.43900509754635</v>
       </c>
       <c r="F855" t="n">
         <v>526306</v>
@@ -26669,42 +26669,42 @@
     </row>
     <row r="1313">
       <c r="A1313" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1313" t="n">
-        <v>5.510000228881836</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="C1313" t="n">
-        <v>5.579999923706055</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="D1313" t="n">
-        <v>5.460000038146973</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="E1313" t="n">
-        <v>5.510000228881836</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="F1313" t="n">
-        <v>535600</v>
+        <v>739000</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1314" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D1314" t="n">
         <v>5.53</v>
       </c>
-      <c r="C1314" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="D1314" t="n">
-        <v>5.43</v>
-      </c>
       <c r="E1314" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="F1314" t="n">
-        <v>739000</v>
+        <v>572400</v>
       </c>
     </row>
   </sheetData>

--- a/database/SOJA3.xlsx
+++ b/database/SOJA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1316"/>
+  <dimension ref="A1:F1317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44316</v>
       </c>
       <c r="B2" t="n">
-        <v>13.41818904876709</v>
+        <v>13.41818809509277</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80970479601495</v>
+        <v>14.80970374344109</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42424887265957</v>
+        <v>12.42424798962781</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50707735936371</v>
+        <v>12.50707647044507</v>
       </c>
       <c r="F2" t="n">
         <v>8063577</v>
@@ -472,16 +472,16 @@
         <v>44319</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2856616973877</v>
+        <v>13.28566265106201</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83010549167658</v>
+        <v>12.83010641265006</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24646969691628</v>
+        <v>14.24647071955953</v>
       </c>
       <c r="F3" t="n">
         <v>3253201</v>
@@ -492,16 +492,16 @@
         <v>44320</v>
       </c>
       <c r="B4" t="n">
-        <v>13.16970348358154</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C4" t="n">
-        <v>13.76606725161959</v>
+        <v>13.76606525790047</v>
       </c>
       <c r="D4" t="n">
-        <v>13.00404651149493</v>
+        <v>13.00404462813815</v>
       </c>
       <c r="E4" t="n">
-        <v>13.42647154066446</v>
+        <v>13.42646959612849</v>
       </c>
       <c r="F4" t="n">
         <v>1304335</v>
@@ -512,16 +512,16 @@
         <v>44321</v>
       </c>
       <c r="B5" t="n">
-        <v>12.93778324127197</v>
+        <v>12.93778419494629</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3353587586459</v>
+        <v>13.33535974162644</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92949897903101</v>
+        <v>12.92949993209467</v>
       </c>
       <c r="E5" t="n">
-        <v>13.32707532857593</v>
+        <v>13.32707631094588</v>
       </c>
       <c r="F5" t="n">
         <v>876510</v>
@@ -592,16 +592,16 @@
         <v>44327</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C9" t="n">
-        <v>12.5484900443603</v>
+        <v>12.54849100757134</v>
       </c>
       <c r="D9" t="n">
-        <v>12.21717612770272</v>
+        <v>12.2171770654824</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="F9" t="n">
         <v>404121</v>
@@ -612,16 +612,16 @@
         <v>44328</v>
       </c>
       <c r="B10" t="n">
-        <v>12.46566200256348</v>
+        <v>12.46566104888916</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75556044155362</v>
+        <v>12.75555946570089</v>
       </c>
       <c r="D10" t="n">
-        <v>12.30000503842248</v>
+        <v>12.3000040974216</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34141969554326</v>
+        <v>12.34141875137399</v>
       </c>
       <c r="F10" t="n">
         <v>559828</v>
@@ -632,16 +632,16 @@
         <v>44329</v>
       </c>
       <c r="B11" t="n">
-        <v>13.40162181854248</v>
+        <v>13.40162086486816</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93172308737706</v>
+        <v>13.93172209598015</v>
       </c>
       <c r="D11" t="n">
-        <v>12.46566158371901</v>
+        <v>12.46566069664867</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67273319802321</v>
+        <v>12.67273229621742</v>
       </c>
       <c r="F11" t="n">
         <v>3216644</v>
@@ -652,16 +652,16 @@
         <v>44330</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83232975006104</v>
+        <v>13.83232879638672</v>
       </c>
       <c r="C12" t="n">
-        <v>14.19677323706887</v>
+        <v>14.19677225826788</v>
       </c>
       <c r="D12" t="n">
-        <v>13.50101582480272</v>
+        <v>13.50101489397095</v>
       </c>
       <c r="E12" t="n">
-        <v>13.56727910915701</v>
+        <v>13.5672781737567</v>
       </c>
       <c r="F12" t="n">
         <v>2182426</v>
@@ -672,16 +672,16 @@
         <v>44333</v>
       </c>
       <c r="B13" t="n">
-        <v>13.98141956329346</v>
+        <v>13.98142051696777</v>
       </c>
       <c r="C13" t="n">
-        <v>14.57778324950092</v>
+        <v>14.57778424385328</v>
       </c>
       <c r="D13" t="n">
-        <v>13.67495429020224</v>
+        <v>13.67495522297252</v>
       </c>
       <c r="E13" t="n">
-        <v>13.98970299328094</v>
+        <v>13.98970394752027</v>
       </c>
       <c r="F13" t="n">
         <v>2009125</v>
@@ -692,16 +692,16 @@
         <v>44334</v>
       </c>
       <c r="B14" t="n">
-        <v>13.84889507293701</v>
+        <v>13.84889602661133</v>
       </c>
       <c r="C14" t="n">
-        <v>14.24647062182232</v>
+        <v>14.24647160287482</v>
       </c>
       <c r="D14" t="n">
-        <v>13.68323894097274</v>
+        <v>13.68323988323951</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12222914697741</v>
+        <v>14.12223011947429</v>
       </c>
       <c r="F14" t="n">
         <v>888836</v>
@@ -712,16 +712,16 @@
         <v>44335</v>
       </c>
       <c r="B15" t="n">
-        <v>13.48444938659668</v>
+        <v>13.484450340271</v>
       </c>
       <c r="C15" t="n">
-        <v>13.94828817352505</v>
+        <v>13.9482891600039</v>
       </c>
       <c r="D15" t="n">
-        <v>13.36020625997589</v>
+        <v>13.36020720486323</v>
       </c>
       <c r="E15" t="n">
-        <v>13.77434862842691</v>
+        <v>13.77434960260406</v>
       </c>
       <c r="F15" t="n">
         <v>804661</v>
@@ -752,16 +752,16 @@
         <v>44337</v>
       </c>
       <c r="B17" t="n">
-        <v>13.21939945220947</v>
+        <v>13.21939849853516</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48445008239211</v>
+        <v>13.4844491095965</v>
       </c>
       <c r="D17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.086872776919</v>
       </c>
       <c r="E17" t="n">
-        <v>13.08687372103264</v>
+        <v>13.086872776919</v>
       </c>
       <c r="F17" t="n">
         <v>536441</v>
@@ -792,16 +792,16 @@
         <v>44341</v>
       </c>
       <c r="B19" t="n">
-        <v>13.26909446716309</v>
+        <v>13.26909637451172</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64182216241932</v>
+        <v>13.64182412334521</v>
       </c>
       <c r="D19" t="n">
-        <v>13.25252927262824</v>
+        <v>13.25253117759573</v>
       </c>
       <c r="E19" t="n">
-        <v>13.40162018429654</v>
+        <v>13.40162211069491</v>
       </c>
       <c r="F19" t="n">
         <v>544026</v>
@@ -832,16 +832,16 @@
         <v>44343</v>
       </c>
       <c r="B21" t="n">
-        <v>13.16970348358154</v>
+        <v>13.16970157623291</v>
       </c>
       <c r="C21" t="n">
-        <v>13.45131933752346</v>
+        <v>13.45131738938882</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15313828567554</v>
+        <v>13.15313638072602</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32707702454405</v>
+        <v>13.32707509440325</v>
       </c>
       <c r="F21" t="n">
         <v>469333</v>
@@ -852,16 +852,16 @@
         <v>44344</v>
       </c>
       <c r="B22" t="n">
-        <v>13.02889633178711</v>
+        <v>13.02889442443848</v>
       </c>
       <c r="C22" t="n">
-        <v>13.31879479267196</v>
+        <v>13.31879284288401</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96263304182351</v>
+        <v>12.96263114417541</v>
       </c>
       <c r="E22" t="n">
-        <v>13.21111850680197</v>
+        <v>13.21111657277715</v>
       </c>
       <c r="F22" t="n">
         <v>784961</v>
@@ -872,16 +872,16 @@
         <v>44347</v>
       </c>
       <c r="B23" t="n">
-        <v>12.87980365753174</v>
+        <v>12.87980270385742</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21111758778895</v>
+        <v>13.21111660958277</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6147530126286</v>
+        <v>12.61475207857974</v>
       </c>
       <c r="E23" t="n">
-        <v>13.05374322126546</v>
+        <v>13.05374225471193</v>
       </c>
       <c r="F23" t="n">
         <v>718590</v>
@@ -892,16 +892,16 @@
         <v>44348</v>
       </c>
       <c r="B24" t="n">
-        <v>13.25253009796143</v>
+        <v>13.25253200531006</v>
       </c>
       <c r="C24" t="n">
-        <v>13.32707514235259</v>
+        <v>13.32707706042999</v>
       </c>
       <c r="D24" t="n">
-        <v>12.8466719883597</v>
+        <v>12.84667383729587</v>
       </c>
       <c r="E24" t="n">
-        <v>13.02061070266274</v>
+        <v>13.02061257663275</v>
       </c>
       <c r="F24" t="n">
         <v>626093</v>
@@ -932,16 +932,16 @@
         <v>44351</v>
       </c>
       <c r="B26" t="n">
-        <v>12.97919750213623</v>
+        <v>12.97919845581055</v>
       </c>
       <c r="C26" t="n">
-        <v>13.23596470306119</v>
+        <v>13.23596567560203</v>
       </c>
       <c r="D26" t="n">
-        <v>12.85495520076337</v>
+        <v>12.85495614530872</v>
       </c>
       <c r="E26" t="n">
-        <v>12.98748010031548</v>
+        <v>12.98748105459838</v>
       </c>
       <c r="F26" t="n">
         <v>460799</v>
@@ -972,16 +972,16 @@
         <v>44355</v>
       </c>
       <c r="B28" t="n">
-        <v>12.4490966796875</v>
+        <v>12.44909763336182</v>
       </c>
       <c r="C28" t="n">
-        <v>12.73899511574901</v>
+        <v>12.73899609163126</v>
       </c>
       <c r="D28" t="n">
-        <v>12.42424805210027</v>
+        <v>12.42424900387104</v>
       </c>
       <c r="E28" t="n">
-        <v>12.69758129121766</v>
+        <v>12.69758226392737</v>
       </c>
       <c r="F28" t="n">
         <v>727440</v>
@@ -1032,16 +1032,16 @@
         <v>44358</v>
       </c>
       <c r="B31" t="n">
-        <v>12.84667205810547</v>
+        <v>12.84667301177979</v>
       </c>
       <c r="C31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="D31" t="n">
-        <v>12.75555932114021</v>
+        <v>12.75556026805076</v>
       </c>
       <c r="E31" t="n">
-        <v>12.99576214769721</v>
+        <v>12.99576311243925</v>
       </c>
       <c r="F31" t="n">
         <v>298034</v>
@@ -1112,16 +1112,16 @@
         <v>44364</v>
       </c>
       <c r="B35" t="n">
-        <v>12.71414756774902</v>
+        <v>12.71414661407471</v>
       </c>
       <c r="C35" t="n">
-        <v>12.86323850400263</v>
+        <v>12.86323753914516</v>
       </c>
       <c r="D35" t="n">
-        <v>12.5899052595662</v>
+        <v>12.58990431521116</v>
       </c>
       <c r="E35" t="n">
-        <v>12.76384482389058</v>
+        <v>12.76384386648853</v>
       </c>
       <c r="F35" t="n">
         <v>314153</v>
@@ -1132,16 +1132,16 @@
         <v>44365</v>
       </c>
       <c r="B36" t="n">
-        <v>12.65616512298584</v>
+        <v>12.65616703033447</v>
       </c>
       <c r="C36" t="n">
-        <v>12.74727619181022</v>
+        <v>12.74727811288975</v>
       </c>
       <c r="D36" t="n">
-        <v>12.54848885919573</v>
+        <v>12.548490750317</v>
       </c>
       <c r="E36" t="n">
-        <v>12.63959992802011</v>
+        <v>12.63960183287228</v>
       </c>
       <c r="F36" t="n">
         <v>365879</v>
@@ -1172,16 +1172,16 @@
         <v>44369</v>
       </c>
       <c r="B38" t="n">
-        <v>12.39939880371094</v>
+        <v>12.39939785003662</v>
       </c>
       <c r="C38" t="n">
-        <v>12.66444944887451</v>
+        <v>12.66444847481437</v>
       </c>
       <c r="D38" t="n">
-        <v>12.22546007197737</v>
+        <v>12.22545913168119</v>
       </c>
       <c r="E38" t="n">
-        <v>12.51535934515176</v>
+        <v>12.51535838255857</v>
       </c>
       <c r="F38" t="n">
         <v>779904</v>
@@ -1192,16 +1192,16 @@
         <v>44370</v>
       </c>
       <c r="B39" t="n">
-        <v>12.10950088500977</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C39" t="n">
-        <v>12.49051125587668</v>
+        <v>12.4905092885157</v>
       </c>
       <c r="D39" t="n">
-        <v>12.10950088500977</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="E39" t="n">
-        <v>12.42424879977055</v>
+        <v>12.42424684284646</v>
       </c>
       <c r="F39" t="n">
         <v>912539</v>
@@ -1212,16 +1212,16 @@
         <v>44371</v>
       </c>
       <c r="B40" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313655853271</v>
       </c>
       <c r="C40" t="n">
-        <v>12.51535774406464</v>
+        <v>12.5153587118295</v>
       </c>
       <c r="D40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717602295992</v>
       </c>
       <c r="E40" t="n">
-        <v>12.21717507825239</v>
+        <v>12.21717602295992</v>
       </c>
       <c r="F40" t="n">
         <v>335223</v>
@@ -1232,16 +1232,16 @@
         <v>44372</v>
       </c>
       <c r="B41" t="n">
-        <v>12.31657218933105</v>
+        <v>12.31657123565674</v>
       </c>
       <c r="C41" t="n">
-        <v>12.42424846959927</v>
+        <v>12.42424750758757</v>
       </c>
       <c r="D41" t="n">
-        <v>12.09293453353099</v>
+        <v>12.09293359717298</v>
       </c>
       <c r="E41" t="n">
-        <v>12.41596587084889</v>
+        <v>12.41596490947851</v>
       </c>
       <c r="F41" t="n">
         <v>346284</v>
@@ -1292,16 +1292,16 @@
         <v>44377</v>
       </c>
       <c r="B44" t="n">
-        <v>12.80525875091553</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="C44" t="n">
-        <v>12.80525875091553</v>
+        <v>12.80525779724121</v>
       </c>
       <c r="D44" t="n">
-        <v>12.43253099123612</v>
+        <v>12.43253006532078</v>
       </c>
       <c r="E44" t="n">
-        <v>12.58990535954375</v>
+        <v>12.58990442190792</v>
       </c>
       <c r="F44" t="n">
         <v>541392</v>
@@ -1332,16 +1332,16 @@
         <v>44379</v>
       </c>
       <c r="B46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="C46" t="n">
-        <v>12.74727718624468</v>
+        <v>12.7472762129657</v>
       </c>
       <c r="D46" t="n">
-        <v>12.49050998687744</v>
+        <v>12.49050903320312</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51535861343547</v>
+        <v>12.51535765786391</v>
       </c>
       <c r="F46" t="n">
         <v>443206</v>
@@ -1372,16 +1372,16 @@
         <v>44383</v>
       </c>
       <c r="B48" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C48" t="n">
-        <v>12.4987937073347</v>
+        <v>12.49879274279404</v>
       </c>
       <c r="D48" t="n">
-        <v>12.25859086647818</v>
+        <v>12.25858992047414</v>
       </c>
       <c r="E48" t="n">
-        <v>12.47394424802878</v>
+        <v>12.47394328540577</v>
       </c>
       <c r="F48" t="n">
         <v>280862</v>
@@ -1432,16 +1432,16 @@
         <v>44389</v>
       </c>
       <c r="B51" t="n">
-        <v>12.2171745300293</v>
+        <v>12.21717548370361</v>
       </c>
       <c r="C51" t="n">
-        <v>12.54020580617806</v>
+        <v>12.54020678506824</v>
       </c>
       <c r="D51" t="n">
-        <v>12.2171745300293</v>
+        <v>12.21717548370361</v>
       </c>
       <c r="E51" t="n">
-        <v>12.42424611694648</v>
+        <v>12.42424708678483</v>
       </c>
       <c r="F51" t="n">
         <v>300457</v>
@@ -1472,16 +1472,16 @@
         <v>44391</v>
       </c>
       <c r="B53" t="n">
-        <v>12.10121822357178</v>
+        <v>12.10121726989746</v>
       </c>
       <c r="C53" t="n">
-        <v>12.25030916512651</v>
+        <v>12.25030819970261</v>
       </c>
       <c r="D53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="E53" t="n">
-        <v>12.09293479247294</v>
+        <v>12.09293383945143</v>
       </c>
       <c r="F53" t="n">
         <v>237563</v>
@@ -1492,16 +1492,16 @@
         <v>44392</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C54" t="n">
-        <v>12.29172210889838</v>
+        <v>12.29172113487724</v>
       </c>
       <c r="D54" t="n">
-        <v>12.01010627604678</v>
+        <v>12.01010532434145</v>
       </c>
       <c r="E54" t="n">
-        <v>12.10121735421974</v>
+        <v>12.10121639529459</v>
       </c>
       <c r="F54" t="n">
         <v>321948</v>
@@ -1512,16 +1512,16 @@
         <v>44393</v>
       </c>
       <c r="B55" t="n">
-        <v>12.10950088500977</v>
+        <v>12.10949897766113</v>
       </c>
       <c r="C55" t="n">
-        <v>12.16748074214541</v>
+        <v>12.16747882566446</v>
       </c>
       <c r="D55" t="n">
-        <v>11.89414748657928</v>
+        <v>11.89414561315063</v>
       </c>
       <c r="E55" t="n">
-        <v>12.06808705798621</v>
+        <v>12.0680851571606</v>
       </c>
       <c r="F55" t="n">
         <v>331430</v>
@@ -1592,16 +1592,16 @@
         <v>44399</v>
       </c>
       <c r="B59" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76768207550049</v>
       </c>
       <c r="C59" t="n">
-        <v>11.34747866392074</v>
+        <v>11.34748067397282</v>
       </c>
       <c r="D59" t="n">
-        <v>10.65172130116907</v>
+        <v>10.65172318797716</v>
       </c>
       <c r="E59" t="n">
-        <v>11.07414544398869</v>
+        <v>11.07414740562349</v>
       </c>
       <c r="F59" t="n">
         <v>1532944</v>
@@ -1612,16 +1612,16 @@
         <v>44400</v>
       </c>
       <c r="B60" t="n">
-        <v>10.85879135131836</v>
+        <v>10.85879230499268</v>
       </c>
       <c r="C60" t="n">
-        <v>11.16525663025563</v>
+        <v>11.16525761084529</v>
       </c>
       <c r="D60" t="n">
-        <v>10.71798385706797</v>
+        <v>10.71798479837585</v>
       </c>
       <c r="E60" t="n">
-        <v>10.76768027708593</v>
+        <v>10.76768122275841</v>
       </c>
       <c r="F60" t="n">
         <v>702683</v>
@@ -1632,16 +1632,16 @@
         <v>44403</v>
       </c>
       <c r="B61" t="n">
-        <v>11.15697574615479</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="C61" t="n">
-        <v>11.15697574615479</v>
+        <v>11.15697479248047</v>
       </c>
       <c r="D61" t="n">
-        <v>10.86707645080476</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="E61" t="n">
-        <v>10.86707645080476</v>
+        <v>10.86707552191041</v>
       </c>
       <c r="F61" t="n">
         <v>518004</v>
@@ -1652,16 +1652,16 @@
         <v>44404</v>
       </c>
       <c r="B62" t="n">
-        <v>11.29778003692627</v>
+        <v>11.29778289794922</v>
       </c>
       <c r="C62" t="n">
-        <v>11.47171956448282</v>
+        <v>11.4717224695538</v>
       </c>
       <c r="D62" t="n">
-        <v>11.05757890213932</v>
+        <v>11.05758170233431</v>
       </c>
       <c r="E62" t="n">
-        <v>11.18182118405946</v>
+        <v>11.18182401571727</v>
       </c>
       <c r="F62" t="n">
         <v>593646</v>
@@ -1672,16 +1672,16 @@
         <v>44405</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34747791290283</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C63" t="n">
-        <v>11.51313485277901</v>
+        <v>11.51313582037561</v>
       </c>
       <c r="D63" t="n">
-        <v>11.2149521945677</v>
+        <v>11.21495313710418</v>
       </c>
       <c r="E63" t="n">
-        <v>11.36404393975882</v>
+        <v>11.3640448948254</v>
       </c>
       <c r="F63" t="n">
         <v>861023</v>
@@ -1712,16 +1712,16 @@
         <v>44407</v>
       </c>
       <c r="B65" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C65" t="n">
-        <v>11.9272788379407</v>
+        <v>11.92727785279649</v>
       </c>
       <c r="D65" t="n">
-        <v>11.09899563153766</v>
+        <v>11.09899471480624</v>
       </c>
       <c r="E65" t="n">
-        <v>11.20667191578054</v>
+        <v>11.2066709901555</v>
       </c>
       <c r="F65" t="n">
         <v>977013</v>
@@ -1752,16 +1752,16 @@
         <v>44411</v>
       </c>
       <c r="B67" t="n">
-        <v>11.85273265838623</v>
+        <v>11.85273170471191</v>
       </c>
       <c r="C67" t="n">
-        <v>11.93556114342346</v>
+        <v>11.93556018308474</v>
       </c>
       <c r="D67" t="n">
-        <v>11.43030846651876</v>
+        <v>11.43030754683281</v>
       </c>
       <c r="E67" t="n">
-        <v>11.92727854457107</v>
+        <v>11.92727758489877</v>
       </c>
       <c r="F67" t="n">
         <v>233981</v>
@@ -1772,16 +1772,16 @@
         <v>44412</v>
       </c>
       <c r="B68" t="n">
-        <v>11.45515632629395</v>
+        <v>11.45515727996826</v>
       </c>
       <c r="C68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="D68" t="n">
-        <v>11.44687372799754</v>
+        <v>11.4468746809823</v>
       </c>
       <c r="E68" t="n">
-        <v>11.85273186274499</v>
+        <v>11.8527328495186</v>
       </c>
       <c r="F68" t="n">
         <v>326795</v>
@@ -1792,16 +1792,16 @@
         <v>44413</v>
       </c>
       <c r="B69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="C69" t="n">
-        <v>11.66222697699479</v>
+        <v>11.6622279694364</v>
       </c>
       <c r="D69" t="n">
-        <v>11.2066707611084</v>
+        <v>11.20667171478271</v>
       </c>
       <c r="E69" t="n">
-        <v>11.58768109665717</v>
+        <v>11.58768208275502</v>
       </c>
       <c r="F69" t="n">
         <v>215651</v>
@@ -1812,16 +1812,16 @@
         <v>44414</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56283283233643</v>
+        <v>11.56283092498779</v>
       </c>
       <c r="C70" t="n">
-        <v>11.59596489052797</v>
+        <v>11.59596297771403</v>
       </c>
       <c r="D70" t="n">
-        <v>11.21495371086467</v>
+        <v>11.21495186090048</v>
       </c>
       <c r="E70" t="n">
-        <v>11.2812169950767</v>
+        <v>11.28121513418205</v>
       </c>
       <c r="F70" t="n">
         <v>198162</v>
@@ -1832,16 +1832,16 @@
         <v>44417</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C71" t="n">
-        <v>12.03495292569004</v>
+        <v>12.03495388133742</v>
       </c>
       <c r="D71" t="n">
-        <v>11.59596360543989</v>
+        <v>11.59596452622889</v>
       </c>
       <c r="E71" t="n">
-        <v>11.62909482778872</v>
+        <v>11.62909575120853</v>
       </c>
       <c r="F71" t="n">
         <v>438360</v>
@@ -1892,16 +1892,16 @@
         <v>44420</v>
       </c>
       <c r="B74" t="n">
-        <v>12.0763692855835</v>
+        <v>12.07636737823486</v>
       </c>
       <c r="C74" t="n">
-        <v>12.24202625292564</v>
+        <v>12.24202431941305</v>
       </c>
       <c r="D74" t="n">
-        <v>11.81131863713872</v>
+        <v>11.81131677165233</v>
       </c>
       <c r="E74" t="n">
-        <v>11.95212614399135</v>
+        <v>11.95212425626575</v>
       </c>
       <c r="F74" t="n">
         <v>242515</v>
@@ -1912,16 +1912,16 @@
         <v>44421</v>
       </c>
       <c r="B75" t="n">
-        <v>12.50707530975342</v>
+        <v>12.50707626342773</v>
       </c>
       <c r="C75" t="n">
-        <v>12.61475157586925</v>
+        <v>12.61475253775396</v>
       </c>
       <c r="D75" t="n">
-        <v>11.87758041186906</v>
+        <v>11.87758131754389</v>
       </c>
       <c r="E75" t="n">
-        <v>12.00182187330842</v>
+        <v>12.00182278845676</v>
       </c>
       <c r="F75" t="n">
         <v>464803</v>
@@ -1952,16 +1952,16 @@
         <v>44425</v>
       </c>
       <c r="B77" t="n">
-        <v>11.43859195709229</v>
+        <v>11.43859004974365</v>
       </c>
       <c r="C77" t="n">
-        <v>11.92727860666524</v>
+        <v>11.92727661782967</v>
       </c>
       <c r="D77" t="n">
-        <v>11.32263141169959</v>
+        <v>11.32262952368701</v>
       </c>
       <c r="E77" t="n">
-        <v>11.8444501211968</v>
+        <v>11.84444814617262</v>
       </c>
       <c r="F77" t="n">
         <v>449000</v>
@@ -1972,16 +1972,16 @@
         <v>44426</v>
       </c>
       <c r="B78" t="n">
-        <v>12.03495407104492</v>
+        <v>12.03495311737061</v>
       </c>
       <c r="C78" t="n">
-        <v>12.33313676490402</v>
+        <v>12.3331357876011</v>
       </c>
       <c r="D78" t="n">
-        <v>11.51313622917634</v>
+        <v>11.51313531685193</v>
       </c>
       <c r="E78" t="n">
-        <v>11.57939868018012</v>
+        <v>11.57939776260494</v>
       </c>
       <c r="F78" t="n">
         <v>474811</v>
@@ -2032,16 +2032,16 @@
         <v>44431</v>
       </c>
       <c r="B81" t="n">
-        <v>11.99353981018066</v>
+        <v>11.99354076385498</v>
       </c>
       <c r="C81" t="n">
-        <v>12.39111533388724</v>
+        <v>12.39111631917504</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95212515568412</v>
+        <v>11.95212610606532</v>
       </c>
       <c r="E81" t="n">
-        <v>12.21717578221218</v>
+        <v>12.21717675366905</v>
       </c>
       <c r="F81" t="n">
         <v>344599</v>
@@ -2092,16 +2092,16 @@
         <v>44434</v>
       </c>
       <c r="B84" t="n">
-        <v>11.72848796844482</v>
+        <v>11.72848987579346</v>
       </c>
       <c r="C84" t="n">
-        <v>11.97697337316509</v>
+        <v>11.97697532092373</v>
       </c>
       <c r="D84" t="n">
-        <v>11.62081170868654</v>
+        <v>11.62081359852429</v>
       </c>
       <c r="E84" t="n">
-        <v>11.84444765754676</v>
+        <v>11.84444958375337</v>
       </c>
       <c r="F84" t="n">
         <v>190788</v>
@@ -2112,16 +2112,16 @@
         <v>44435</v>
       </c>
       <c r="B85" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C85" t="n">
-        <v>11.89414528775495</v>
+        <v>11.8941472165949</v>
       </c>
       <c r="D85" t="n">
-        <v>11.35576147512211</v>
+        <v>11.35576331665388</v>
       </c>
       <c r="E85" t="n">
-        <v>11.87758009287631</v>
+        <v>11.87758201902993</v>
       </c>
       <c r="F85" t="n">
         <v>370831</v>
@@ -2132,16 +2132,16 @@
         <v>44438</v>
       </c>
       <c r="B86" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C86" t="n">
-        <v>11.9686919095953</v>
+        <v>11.96869289533168</v>
       </c>
       <c r="D86" t="n">
-        <v>11.55454952916977</v>
+        <v>11.55455048079756</v>
       </c>
       <c r="E86" t="n">
-        <v>11.86101397529656</v>
+        <v>11.86101495216464</v>
       </c>
       <c r="F86" t="n">
         <v>185626</v>
@@ -2172,16 +2172,16 @@
         <v>44440</v>
       </c>
       <c r="B88" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C88" t="n">
-        <v>11.63737827423737</v>
+        <v>11.63737923751014</v>
       </c>
       <c r="D88" t="n">
-        <v>11.35576244764404</v>
+        <v>11.35576338760633</v>
       </c>
       <c r="E88" t="n">
-        <v>11.51313597332352</v>
+        <v>11.51313692631225</v>
       </c>
       <c r="F88" t="n">
         <v>328691</v>
@@ -2192,16 +2192,16 @@
         <v>44441</v>
       </c>
       <c r="B89" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C89" t="n">
-        <v>11.6290964280881</v>
+        <v>11.62909547100532</v>
       </c>
       <c r="D89" t="n">
-        <v>11.19010621525682</v>
+        <v>11.19010529430325</v>
       </c>
       <c r="E89" t="n">
-        <v>11.55455054341664</v>
+        <v>11.55454959246905</v>
       </c>
       <c r="F89" t="n">
         <v>342913</v>
@@ -2252,16 +2252,16 @@
         <v>44447</v>
       </c>
       <c r="B92" t="n">
-        <v>11.64566135406494</v>
+        <v>11.64566040039062</v>
       </c>
       <c r="C92" t="n">
-        <v>11.67050998170969</v>
+        <v>11.67050902600049</v>
       </c>
       <c r="D92" t="n">
-        <v>11.19010595448147</v>
+        <v>11.19010503811302</v>
       </c>
       <c r="E92" t="n">
-        <v>11.51313644952104</v>
+        <v>11.51313550669932</v>
       </c>
       <c r="F92" t="n">
         <v>325004</v>
@@ -2272,16 +2272,16 @@
         <v>44448</v>
       </c>
       <c r="B93" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C93" t="n">
-        <v>11.57111708543731</v>
+        <v>11.57111611650414</v>
       </c>
       <c r="D93" t="n">
-        <v>11.181824111812</v>
+        <v>11.18182317547715</v>
       </c>
       <c r="E93" t="n">
-        <v>11.52141982678859</v>
+        <v>11.52141886201694</v>
       </c>
       <c r="F93" t="n">
         <v>457007</v>
@@ -2312,16 +2312,16 @@
         <v>44452</v>
       </c>
       <c r="B95" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C95" t="n">
-        <v>11.84444877938214</v>
+        <v>11.84444975488591</v>
       </c>
       <c r="D95" t="n">
-        <v>11.40545860508498</v>
+        <v>11.40545954443371</v>
       </c>
       <c r="E95" t="n">
-        <v>11.59596418329782</v>
+        <v>11.59596513833651</v>
       </c>
       <c r="F95" t="n">
         <v>436780</v>
@@ -2332,16 +2332,16 @@
         <v>44453</v>
       </c>
       <c r="B96" t="n">
-        <v>11.70364093780518</v>
+        <v>11.70364189147949</v>
       </c>
       <c r="C96" t="n">
-        <v>11.8361658298683</v>
+        <v>11.83616679434145</v>
       </c>
       <c r="D96" t="n">
-        <v>11.47172071235275</v>
+        <v>11.47172164712899</v>
       </c>
       <c r="E96" t="n">
-        <v>11.51313536525071</v>
+        <v>11.51313630340163</v>
       </c>
       <c r="F96" t="n">
         <v>291186</v>
@@ -2392,16 +2392,16 @@
         <v>44456</v>
       </c>
       <c r="B99" t="n">
-        <v>11.38889408111572</v>
+        <v>11.38889312744141</v>
       </c>
       <c r="C99" t="n">
-        <v>11.60424831381274</v>
+        <v>11.60424734210526</v>
       </c>
       <c r="D99" t="n">
-        <v>11.30606642626268</v>
+        <v>11.30606547952412</v>
       </c>
       <c r="E99" t="n">
-        <v>11.59596571476166</v>
+        <v>11.59596474374774</v>
       </c>
       <c r="F99" t="n">
         <v>163397</v>
@@ -2412,16 +2412,16 @@
         <v>44459</v>
       </c>
       <c r="B100" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C100" t="n">
-        <v>11.64565927206673</v>
+        <v>11.64566120833546</v>
       </c>
       <c r="D100" t="n">
-        <v>11.05757907307569</v>
+        <v>11.05758091156711</v>
       </c>
       <c r="E100" t="n">
-        <v>11.26464982353394</v>
+        <v>11.26465169645404</v>
       </c>
       <c r="F100" t="n">
         <v>536125</v>
@@ -2452,16 +2452,16 @@
         <v>44461</v>
       </c>
       <c r="B102" t="n">
-        <v>11.81960105895996</v>
+        <v>11.81960201263428</v>
       </c>
       <c r="C102" t="n">
-        <v>12.05152047689957</v>
+        <v>12.0515214492865</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58768164102035</v>
+        <v>11.58768257598205</v>
       </c>
       <c r="E102" t="n">
-        <v>11.69535875139833</v>
+        <v>11.69535969504805</v>
       </c>
       <c r="F102" t="n">
         <v>399802</v>
@@ -2492,16 +2492,16 @@
         <v>44463</v>
       </c>
       <c r="B104" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C104" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="D104" t="n">
-        <v>11.9935395446462</v>
+        <v>11.99354049373239</v>
       </c>
       <c r="E104" t="n">
-        <v>12.34141864029437</v>
+        <v>12.34141961690932</v>
       </c>
       <c r="F104" t="n">
         <v>376520</v>
@@ -2652,16 +2652,16 @@
         <v>44475</v>
       </c>
       <c r="B112" t="n">
-        <v>11.38061141967773</v>
+        <v>11.3806095123291</v>
       </c>
       <c r="C112" t="n">
-        <v>11.62909687938803</v>
+        <v>11.62909493039415</v>
       </c>
       <c r="D112" t="n">
-        <v>11.18182405051482</v>
+        <v>11.18182217648222</v>
       </c>
       <c r="E112" t="n">
-        <v>11.40546004886587</v>
+        <v>11.4054581373527</v>
       </c>
       <c r="F112" t="n">
         <v>433409</v>
@@ -2812,16 +2812,16 @@
         <v>44488</v>
       </c>
       <c r="B120" t="n">
-        <v>12.0763692855835</v>
+        <v>12.07636737823486</v>
       </c>
       <c r="C120" t="n">
-        <v>12.29172267739142</v>
+        <v>12.29172073602975</v>
       </c>
       <c r="D120" t="n">
-        <v>11.93556094655978</v>
+        <v>11.9355590614505</v>
       </c>
       <c r="E120" t="n">
-        <v>12.10950051261771</v>
+        <v>12.10949860003631</v>
       </c>
       <c r="F120" t="n">
         <v>251785</v>
@@ -2872,16 +2872,16 @@
         <v>44491</v>
       </c>
       <c r="B123" t="n">
-        <v>11.43030738830566</v>
+        <v>11.4303092956543</v>
       </c>
       <c r="C123" t="n">
-        <v>11.81960031587073</v>
+        <v>11.81960228817976</v>
       </c>
       <c r="D123" t="n">
-        <v>11.13212553603579</v>
+        <v>11.13212739362751</v>
       </c>
       <c r="E123" t="n">
-        <v>11.76162046503097</v>
+        <v>11.76162242766504</v>
       </c>
       <c r="F123" t="n">
         <v>786330</v>
@@ -2892,16 +2892,16 @@
         <v>44494</v>
       </c>
       <c r="B124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C124" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D124" t="n">
-        <v>11.47172147956523</v>
+        <v>11.47172236012447</v>
       </c>
       <c r="E124" t="n">
-        <v>11.52141873349808</v>
+        <v>11.52141961787203</v>
       </c>
       <c r="F124" t="n">
         <v>322791</v>
@@ -2912,16 +2912,16 @@
         <v>44495</v>
       </c>
       <c r="B125" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C125" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D125" t="n">
-        <v>11.84445005892279</v>
+        <v>11.8444491374672</v>
       </c>
       <c r="E125" t="n">
-        <v>12.25030905306453</v>
+        <v>12.25030810003457</v>
       </c>
       <c r="F125" t="n">
         <v>315733</v>
@@ -2932,16 +2932,16 @@
         <v>44496</v>
       </c>
       <c r="B126" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C126" t="n">
-        <v>12.25030756745856</v>
+        <v>12.25030853686361</v>
       </c>
       <c r="D126" t="n">
-        <v>11.8444486225357</v>
+        <v>11.84444955982386</v>
       </c>
       <c r="E126" t="n">
-        <v>12.21717551172646</v>
+        <v>12.21717647850966</v>
       </c>
       <c r="F126" t="n">
         <v>211226</v>
@@ -2972,16 +2972,16 @@
         <v>44498</v>
       </c>
       <c r="B128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.4303092956543</v>
       </c>
       <c r="C128" t="n">
-        <v>11.72848924057554</v>
+        <v>11.72849119768108</v>
       </c>
       <c r="D128" t="n">
-        <v>11.43030738830566</v>
+        <v>11.4303092956543</v>
       </c>
       <c r="E128" t="n">
-        <v>11.59596434275382</v>
+        <v>11.59596627774524</v>
       </c>
       <c r="F128" t="n">
         <v>513053</v>
@@ -3012,16 +3012,16 @@
         <v>44503</v>
       </c>
       <c r="B130" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C130" t="n">
-        <v>12.01838773060111</v>
+        <v>12.01838868493311</v>
       </c>
       <c r="D130" t="n">
-        <v>11.43859009124023</v>
+        <v>11.43859099953283</v>
       </c>
       <c r="E130" t="n">
-        <v>11.50485253593789</v>
+        <v>11.50485344949212</v>
       </c>
       <c r="F130" t="n">
         <v>128737</v>
@@ -3032,16 +3032,16 @@
         <v>44504</v>
       </c>
       <c r="B131" t="n">
-        <v>11.77818584442139</v>
+        <v>11.7781867980957</v>
       </c>
       <c r="C131" t="n">
-        <v>12.08465027787762</v>
+        <v>12.08465125636622</v>
       </c>
       <c r="D131" t="n">
-        <v>11.73677119200559</v>
+        <v>11.73677214232659</v>
       </c>
       <c r="E131" t="n">
-        <v>12.01010523500273</v>
+        <v>12.01010620745546</v>
       </c>
       <c r="F131" t="n">
         <v>218179</v>
@@ -3052,16 +3052,16 @@
         <v>44505</v>
       </c>
       <c r="B132" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C132" t="n">
-        <v>11.92727589213198</v>
+        <v>11.92727787522379</v>
       </c>
       <c r="D132" t="n">
-        <v>11.09899289029898</v>
+        <v>11.09899473567608</v>
       </c>
       <c r="E132" t="n">
-        <v>11.81959880231217</v>
+        <v>11.81960076750101</v>
       </c>
       <c r="F132" t="n">
         <v>552243</v>
@@ -3072,16 +3072,16 @@
         <v>44508</v>
       </c>
       <c r="B133" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C133" t="n">
-        <v>11.72020779632061</v>
+        <v>11.72020588356491</v>
       </c>
       <c r="D133" t="n">
-        <v>11.38061125592101</v>
+        <v>11.38060939858799</v>
       </c>
       <c r="E133" t="n">
-        <v>11.43859194463979</v>
+        <v>11.43859007784422</v>
       </c>
       <c r="F133" t="n">
         <v>342913</v>
@@ -3092,16 +3092,16 @@
         <v>44509</v>
       </c>
       <c r="B134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C134" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="D134" t="n">
-        <v>11.56283197400976</v>
+        <v>11.56283288901272</v>
       </c>
       <c r="E134" t="n">
-        <v>11.68707510257767</v>
+        <v>11.68707602741238</v>
       </c>
       <c r="F134" t="n">
         <v>196688</v>
@@ -3132,16 +3132,16 @@
         <v>44511</v>
       </c>
       <c r="B136" t="n">
-        <v>12.19232749938965</v>
+        <v>12.19232654571533</v>
       </c>
       <c r="C136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374119531235</v>
       </c>
       <c r="D136" t="n">
-        <v>12.08465040062008</v>
+        <v>12.08464945536818</v>
       </c>
       <c r="E136" t="n">
-        <v>12.23374215222609</v>
+        <v>12.23374119531235</v>
       </c>
       <c r="F136" t="n">
         <v>424243</v>
@@ -3192,16 +3192,16 @@
         <v>44517</v>
       </c>
       <c r="B139" t="n">
-        <v>12.0515193939209</v>
+        <v>12.05152034759521</v>
       </c>
       <c r="C139" t="n">
-        <v>12.52364078596598</v>
+        <v>12.52364177700074</v>
       </c>
       <c r="D139" t="n">
-        <v>11.81131739897459</v>
+        <v>11.81131833364097</v>
       </c>
       <c r="E139" t="n">
-        <v>12.42424711528264</v>
+        <v>12.42424809845207</v>
       </c>
       <c r="F139" t="n">
         <v>529593</v>
@@ -3212,16 +3212,16 @@
         <v>44518</v>
       </c>
       <c r="B140" t="n">
-        <v>12.3331356048584</v>
+        <v>12.33313655853271</v>
       </c>
       <c r="C140" t="n">
-        <v>12.46566049440077</v>
+        <v>12.46566145832273</v>
       </c>
       <c r="D140" t="n">
-        <v>12.01010514638517</v>
+        <v>12.01010607508077</v>
       </c>
       <c r="E140" t="n">
-        <v>12.05151896632442</v>
+        <v>12.05151989822239</v>
       </c>
       <c r="F140" t="n">
         <v>393060</v>
@@ -3232,16 +3232,16 @@
         <v>44519</v>
       </c>
       <c r="B141" t="n">
-        <v>12.35798454284668</v>
+        <v>12.35798358917236</v>
       </c>
       <c r="C141" t="n">
-        <v>12.49051027684238</v>
+        <v>12.49050931294096</v>
       </c>
       <c r="D141" t="n">
-        <v>12.09293390702631</v>
+        <v>12.09293297380614</v>
       </c>
       <c r="E141" t="n">
-        <v>12.32485414956155</v>
+        <v>12.32485319844393</v>
       </c>
       <c r="F141" t="n">
         <v>201850</v>
@@ -3252,16 +3252,16 @@
         <v>44522</v>
       </c>
       <c r="B142" t="n">
-        <v>12.9874792098999</v>
+        <v>12.98748111724854</v>
       </c>
       <c r="C142" t="n">
-        <v>13.05374165513303</v>
+        <v>13.05374357221301</v>
       </c>
       <c r="D142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="E142" t="n">
-        <v>12.35798348367227</v>
+        <v>12.3579852985728</v>
       </c>
       <c r="F142" t="n">
         <v>777270</v>
@@ -3272,16 +3272,16 @@
         <v>44523</v>
       </c>
       <c r="B143" t="n">
-        <v>12.79697322845459</v>
+        <v>12.79697513580322</v>
       </c>
       <c r="C143" t="n">
-        <v>13.33535786714481</v>
+        <v>13.33535985473798</v>
       </c>
       <c r="D143" t="n">
-        <v>12.65616491273035</v>
+        <v>12.65616679909195</v>
       </c>
       <c r="E143" t="n">
-        <v>13.03717604100579</v>
+        <v>13.0371779841559</v>
       </c>
       <c r="F143" t="n">
         <v>747456</v>
@@ -3372,16 +3372,16 @@
         <v>44530</v>
       </c>
       <c r="B148" t="n">
-        <v>12.37455081939697</v>
+        <v>12.37454986572266</v>
       </c>
       <c r="C148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="D148" t="n">
-        <v>11.90242939089549</v>
+        <v>11.90242847360634</v>
       </c>
       <c r="E148" t="n">
-        <v>12.59818763591707</v>
+        <v>12.59818666500764</v>
       </c>
       <c r="F148" t="n">
         <v>373781</v>
@@ -3432,16 +3432,16 @@
         <v>44533</v>
       </c>
       <c r="B151" t="n">
-        <v>11.58768177032471</v>
+        <v>11.58768081665039</v>
       </c>
       <c r="C151" t="n">
-        <v>11.67051025368041</v>
+        <v>11.67050929318926</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2480860703887</v>
+        <v>11.24808514466335</v>
       </c>
       <c r="E151" t="n">
-        <v>11.33919715242866</v>
+        <v>11.3391962192048</v>
       </c>
       <c r="F151" t="n">
         <v>269590</v>
@@ -3452,16 +3452,16 @@
         <v>44536</v>
       </c>
       <c r="B152" t="n">
-        <v>11.76990222930908</v>
+        <v>11.76990413665771</v>
       </c>
       <c r="C152" t="n">
-        <v>11.95212436699063</v>
+        <v>11.95212630386892</v>
       </c>
       <c r="D152" t="n">
-        <v>11.50485245244207</v>
+        <v>11.50485431683857</v>
       </c>
       <c r="E152" t="n">
-        <v>11.52970107706609</v>
+        <v>11.52970294548939</v>
       </c>
       <c r="F152" t="n">
         <v>302669</v>
@@ -3472,16 +3472,16 @@
         <v>44537</v>
       </c>
       <c r="B153" t="n">
-        <v>12.01010513305664</v>
+        <v>12.01010608673096</v>
       </c>
       <c r="C153" t="n">
-        <v>12.09293277284322</v>
+        <v>12.09293373309455</v>
       </c>
       <c r="D153" t="n">
-        <v>11.78646834198837</v>
+        <v>11.78646927790459</v>
       </c>
       <c r="E153" t="n">
-        <v>11.89414543875028</v>
+        <v>11.8941463832167</v>
       </c>
       <c r="F153" t="n">
         <v>308042</v>
@@ -3512,16 +3512,16 @@
         <v>44539</v>
       </c>
       <c r="B155" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C155" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="D155" t="n">
-        <v>11.99354099911369</v>
+        <v>11.99354006605936</v>
       </c>
       <c r="E155" t="n">
-        <v>12.22546042433754</v>
+        <v>12.22545947324071</v>
       </c>
       <c r="F155" t="n">
         <v>208487</v>
@@ -3532,16 +3532,16 @@
         <v>44540</v>
       </c>
       <c r="B156" t="n">
-        <v>12.30000495910645</v>
+        <v>12.30000400543213</v>
       </c>
       <c r="C156" t="n">
-        <v>12.36626824363818</v>
+        <v>12.36626728482618</v>
       </c>
       <c r="D156" t="n">
-        <v>12.11778279902904</v>
+        <v>12.11778185948322</v>
       </c>
       <c r="E156" t="n">
-        <v>12.2668737329261</v>
+        <v>12.2668727818206</v>
       </c>
       <c r="F156" t="n">
         <v>171404</v>
@@ -3552,16 +3552,16 @@
         <v>44543</v>
       </c>
       <c r="B157" t="n">
-        <v>12.32485389709473</v>
+        <v>12.32485485076904</v>
       </c>
       <c r="C157" t="n">
-        <v>12.62303492009218</v>
+        <v>12.62303589683919</v>
       </c>
       <c r="D157" t="n">
-        <v>12.23374282091386</v>
+        <v>12.23374376753817</v>
       </c>
       <c r="E157" t="n">
-        <v>12.30000443829783</v>
+        <v>12.30000539004934</v>
       </c>
       <c r="F157" t="n">
         <v>257896</v>
@@ -3572,16 +3572,16 @@
         <v>44544</v>
       </c>
       <c r="B158" t="n">
-        <v>12.2585916519165</v>
+        <v>12.25859069824219</v>
       </c>
       <c r="C158" t="n">
-        <v>12.53192490357129</v>
+        <v>12.53192392863263</v>
       </c>
       <c r="D158" t="n">
-        <v>12.12606590942955</v>
+        <v>12.12606496606526</v>
       </c>
       <c r="E158" t="n">
-        <v>12.44909725070942</v>
+        <v>12.44909628221446</v>
       </c>
       <c r="F158" t="n">
         <v>253682</v>
@@ -3632,16 +3632,16 @@
         <v>44547</v>
       </c>
       <c r="B161" t="n">
-        <v>12.94606781005859</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="C161" t="n">
-        <v>12.94606781005859</v>
+        <v>12.94606494903564</v>
       </c>
       <c r="D161" t="n">
-        <v>12.25859210767931</v>
+        <v>12.25858939858541</v>
       </c>
       <c r="E161" t="n">
-        <v>12.4242490839042</v>
+        <v>12.42424633820085</v>
       </c>
       <c r="F161" t="n">
         <v>496302</v>
@@ -3652,16 +3652,16 @@
         <v>44550</v>
       </c>
       <c r="B162" t="n">
-        <v>13.06202507019043</v>
+        <v>13.06202602386475</v>
       </c>
       <c r="C162" t="n">
-        <v>13.16141957643138</v>
+        <v>13.16142053736261</v>
       </c>
       <c r="D162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273389729204</v>
       </c>
       <c r="E162" t="n">
-        <v>12.67273297204042</v>
+        <v>12.67273389729204</v>
       </c>
       <c r="F162" t="n">
         <v>355766</v>
@@ -3672,16 +3672,16 @@
         <v>44551</v>
       </c>
       <c r="B163" t="n">
-        <v>12.72243022918701</v>
+        <v>12.7224292755127</v>
       </c>
       <c r="C163" t="n">
-        <v>13.0620259287079</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="D163" t="n">
-        <v>12.45737958207539</v>
+        <v>12.45737864826929</v>
       </c>
       <c r="E163" t="n">
-        <v>13.0620259287079</v>
+        <v>13.06202494957747</v>
       </c>
       <c r="F163" t="n">
         <v>229241</v>
@@ -3792,16 +3792,16 @@
         <v>44560</v>
       </c>
       <c r="B169" t="n">
-        <v>13.13657283782959</v>
+        <v>13.13657093048096</v>
       </c>
       <c r="C169" t="n">
-        <v>13.33536104670987</v>
+        <v>13.33535911049843</v>
       </c>
       <c r="D169" t="n">
-        <v>13.10344077620693</v>
+        <v>13.10343887366887</v>
       </c>
       <c r="E169" t="n">
-        <v>13.21111872822387</v>
+        <v>13.21111681005164</v>
       </c>
       <c r="F169" t="n">
         <v>310044</v>
@@ -3832,16 +3832,16 @@
         <v>44565</v>
       </c>
       <c r="B171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970188140869</v>
       </c>
       <c r="C171" t="n">
-        <v>12.98747925372556</v>
+        <v>12.98748025665069</v>
       </c>
       <c r="D171" t="n">
-        <v>12.34970092773438</v>
+        <v>12.34970188140869</v>
       </c>
       <c r="E171" t="n">
-        <v>12.92949857373721</v>
+        <v>12.92949957218493</v>
       </c>
       <c r="F171" t="n">
         <v>168243</v>
@@ -3872,16 +3872,16 @@
         <v>44567</v>
       </c>
       <c r="B173" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C173" t="n">
-        <v>11.83616441649305</v>
+        <v>11.83616633728321</v>
       </c>
       <c r="D173" t="n">
-        <v>11.47171934249647</v>
+        <v>11.47172120414394</v>
       </c>
       <c r="E173" t="n">
-        <v>11.637376269965</v>
+        <v>11.63737815849552</v>
       </c>
       <c r="F173" t="n">
         <v>385474</v>
@@ -3892,16 +3892,16 @@
         <v>44568</v>
       </c>
       <c r="B174" t="n">
-        <v>11.6953592300415</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C174" t="n">
-        <v>11.78647031479358</v>
+        <v>11.78646935368979</v>
       </c>
       <c r="D174" t="n">
-        <v>11.49657103050467</v>
+        <v>11.49657009304013</v>
       </c>
       <c r="E174" t="n">
-        <v>11.75333908689929</v>
+        <v>11.75333812849712</v>
       </c>
       <c r="F174" t="n">
         <v>183519</v>
@@ -3932,16 +3932,16 @@
         <v>44572</v>
       </c>
       <c r="B176" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C176" t="n">
-        <v>11.92727547694948</v>
+        <v>11.92727741252527</v>
       </c>
       <c r="D176" t="n">
-        <v>11.6125284797985</v>
+        <v>11.61253036429669</v>
       </c>
       <c r="E176" t="n">
-        <v>11.84444701321522</v>
+        <v>11.84444893534948</v>
       </c>
       <c r="F176" t="n">
         <v>150860</v>
@@ -3952,16 +3952,16 @@
         <v>44573</v>
       </c>
       <c r="B177" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C177" t="n">
-        <v>12.01838653740591</v>
+        <v>12.01838848776734</v>
       </c>
       <c r="D177" t="n">
-        <v>11.64565886668716</v>
+        <v>11.6456607565618</v>
       </c>
       <c r="E177" t="n">
-        <v>11.77818457509616</v>
+        <v>11.77818648647726</v>
       </c>
       <c r="F177" t="n">
         <v>185520</v>
@@ -3992,16 +3992,16 @@
         <v>44575</v>
       </c>
       <c r="B179" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C179" t="n">
-        <v>11.81131579415569</v>
+        <v>11.81131771091337</v>
       </c>
       <c r="D179" t="n">
-        <v>11.52970001606424</v>
+        <v>11.5297018871209</v>
       </c>
       <c r="E179" t="n">
-        <v>11.67050748902453</v>
+        <v>11.67050938293163</v>
       </c>
       <c r="F179" t="n">
         <v>278228</v>
@@ -4012,16 +4012,16 @@
         <v>44578</v>
       </c>
       <c r="B180" t="n">
-        <v>11.5793981552124</v>
+        <v>11.57939910888672</v>
       </c>
       <c r="C180" t="n">
-        <v>11.77818633138246</v>
+        <v>11.77818730142888</v>
       </c>
       <c r="D180" t="n">
-        <v>11.53798433325535</v>
+        <v>11.53798528351884</v>
       </c>
       <c r="E180" t="n">
-        <v>11.75333770533982</v>
+        <v>11.75333867333973</v>
       </c>
       <c r="F180" t="n">
         <v>199216</v>
@@ -4052,16 +4052,16 @@
         <v>44580</v>
       </c>
       <c r="B182" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C182" t="n">
-        <v>12.01010707905902</v>
+        <v>12.01010511899131</v>
       </c>
       <c r="D182" t="n">
-        <v>11.56283342445056</v>
+        <v>11.5628315373786</v>
       </c>
       <c r="E182" t="n">
-        <v>11.59596548433874</v>
+        <v>11.59596359185958</v>
       </c>
       <c r="F182" t="n">
         <v>354502</v>
@@ -4072,16 +4072,16 @@
         <v>44581</v>
       </c>
       <c r="B183" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C183" t="n">
-        <v>12.21717490959789</v>
+        <v>12.21717689082265</v>
       </c>
       <c r="D183" t="n">
-        <v>11.67050849952573</v>
+        <v>11.67051039209914</v>
       </c>
       <c r="E183" t="n">
-        <v>11.67050849952573</v>
+        <v>11.67051039209914</v>
       </c>
       <c r="F183" t="n">
         <v>1415690</v>
@@ -4092,16 +4092,16 @@
         <v>44582</v>
       </c>
       <c r="B184" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C184" t="n">
-        <v>12.13434939104088</v>
+        <v>12.13434741069664</v>
       </c>
       <c r="D184" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="E184" t="n">
-        <v>11.84445010830247</v>
+        <v>11.84444817527024</v>
       </c>
       <c r="F184" t="n">
         <v>338172</v>
@@ -4132,16 +4132,16 @@
         <v>44586</v>
       </c>
       <c r="B186" t="n">
-        <v>11.83616638183594</v>
+        <v>11.83616542816162</v>
       </c>
       <c r="C186" t="n">
-        <v>11.84444897993339</v>
+        <v>11.84444802559172</v>
       </c>
       <c r="D186" t="n">
-        <v>11.4634386492274</v>
+        <v>11.46343772558484</v>
       </c>
       <c r="E186" t="n">
-        <v>11.47172124732486</v>
+        <v>11.47172032301494</v>
       </c>
       <c r="F186" t="n">
         <v>476075</v>
@@ -4152,16 +4152,16 @@
         <v>44587</v>
       </c>
       <c r="B187" t="n">
-        <v>11.0161657333374</v>
+        <v>11.01616764068604</v>
       </c>
       <c r="C187" t="n">
-        <v>12.08465083286823</v>
+        <v>12.08465292521531</v>
       </c>
       <c r="D187" t="n">
-        <v>10.90020603272125</v>
+        <v>10.90020791999252</v>
       </c>
       <c r="E187" t="n">
-        <v>11.88586348795854</v>
+        <v>11.88586554588741</v>
       </c>
       <c r="F187" t="n">
         <v>1763028</v>
@@ -4172,16 +4172,16 @@
         <v>44588</v>
       </c>
       <c r="B188" t="n">
-        <v>11.34747791290283</v>
+        <v>11.34747886657715</v>
       </c>
       <c r="C188" t="n">
-        <v>11.41374035598493</v>
+        <v>11.41374131522813</v>
       </c>
       <c r="D188" t="n">
-        <v>11.08242730840351</v>
+        <v>11.08242823980222</v>
       </c>
       <c r="E188" t="n">
-        <v>11.18182180519759</v>
+        <v>11.1818227449497</v>
       </c>
       <c r="F188" t="n">
         <v>573734</v>
@@ -4192,16 +4192,16 @@
         <v>44589</v>
       </c>
       <c r="B189" t="n">
-        <v>11.53798389434814</v>
+        <v>11.53798484802246</v>
       </c>
       <c r="C189" t="n">
-        <v>11.57939771472981</v>
+        <v>11.57939867182719</v>
       </c>
       <c r="D189" t="n">
-        <v>11.14040755713192</v>
+        <v>11.14040847794448</v>
       </c>
       <c r="E189" t="n">
-        <v>11.36404435083742</v>
+        <v>11.36404529013473</v>
       </c>
       <c r="F189" t="n">
         <v>538653</v>
@@ -4212,16 +4212,16 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C190" t="n">
-        <v>11.78646910353603</v>
+        <v>11.78647006600311</v>
       </c>
       <c r="D190" t="n">
-        <v>11.45515602647001</v>
+        <v>11.45515696188252</v>
       </c>
       <c r="E190" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="F190" t="n">
         <v>318367</v>
@@ -4232,16 +4232,16 @@
         <v>44593</v>
       </c>
       <c r="B191" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C191" t="n">
-        <v>11.81959941428823</v>
+        <v>11.81960133103929</v>
       </c>
       <c r="D191" t="n">
-        <v>11.61252948527955</v>
+        <v>11.61253136845066</v>
       </c>
       <c r="E191" t="n">
-        <v>11.68707452657532</v>
+        <v>11.6870764218352</v>
       </c>
       <c r="F191" t="n">
         <v>160869</v>
@@ -4252,16 +4252,16 @@
         <v>44594</v>
       </c>
       <c r="B192" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C192" t="n">
-        <v>11.88586476707715</v>
+        <v>11.88586282728598</v>
       </c>
       <c r="D192" t="n">
-        <v>11.54626822667756</v>
+        <v>11.54626634230906</v>
       </c>
       <c r="E192" t="n">
-        <v>11.82788407835838</v>
+        <v>11.82788214802975</v>
       </c>
       <c r="F192" t="n">
         <v>227239</v>
@@ -4272,16 +4272,16 @@
         <v>44595</v>
       </c>
       <c r="B193" t="n">
-        <v>11.48828601837158</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="C193" t="n">
-        <v>11.84444768363459</v>
+        <v>11.84444965011515</v>
       </c>
       <c r="D193" t="n">
-        <v>11.48828601837158</v>
+        <v>11.48828792572021</v>
       </c>
       <c r="E193" t="n">
-        <v>11.67050814959857</v>
+        <v>11.67051008720073</v>
       </c>
       <c r="F193" t="n">
         <v>232928</v>
@@ -4312,16 +4312,16 @@
         <v>44599</v>
       </c>
       <c r="B195" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C195" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="D195" t="n">
-        <v>11.1569733113818</v>
+        <v>11.15697512067666</v>
       </c>
       <c r="E195" t="n">
-        <v>11.43858994602815</v>
+        <v>11.43859180099198</v>
       </c>
       <c r="F195" t="n">
         <v>474179</v>
@@ -4372,16 +4372,16 @@
         <v>44602</v>
       </c>
       <c r="B198" t="n">
-        <v>11.82788467407227</v>
+        <v>11.82788181304932</v>
       </c>
       <c r="C198" t="n">
-        <v>11.84445070485071</v>
+        <v>11.84444783982064</v>
       </c>
       <c r="D198" t="n">
-        <v>11.62909729775775</v>
+        <v>11.62909448481908</v>
       </c>
       <c r="E198" t="n">
-        <v>11.84445070485071</v>
+        <v>11.84444783982064</v>
       </c>
       <c r="F198" t="n">
         <v>136533</v>
@@ -4392,16 +4392,16 @@
         <v>44603</v>
       </c>
       <c r="B199" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C199" t="n">
-        <v>11.8196017215267</v>
+        <v>11.81960074527618</v>
       </c>
       <c r="D199" t="n">
-        <v>11.5214198337953</v>
+        <v>11.52141888217337</v>
       </c>
       <c r="E199" t="n">
-        <v>11.71192543728382</v>
+        <v>11.71192446992692</v>
       </c>
       <c r="F199" t="n">
         <v>419186</v>
@@ -4412,16 +4412,16 @@
         <v>44606</v>
       </c>
       <c r="B200" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C200" t="n">
-        <v>11.84444909778491</v>
+        <v>11.8444500711998</v>
       </c>
       <c r="D200" t="n">
-        <v>11.51313601670912</v>
+        <v>11.51313696289563</v>
       </c>
       <c r="E200" t="n">
-        <v>11.61253052355157</v>
+        <v>11.61253147790664</v>
       </c>
       <c r="F200" t="n">
         <v>316470</v>
@@ -4432,16 +4432,16 @@
         <v>44607</v>
       </c>
       <c r="B201" t="n">
-        <v>11.68707656860352</v>
+        <v>11.68707466125488</v>
       </c>
       <c r="C201" t="n">
-        <v>11.84445010830247</v>
+        <v>11.84444817527024</v>
       </c>
       <c r="D201" t="n">
-        <v>11.62081411316933</v>
+        <v>11.62081221663484</v>
       </c>
       <c r="E201" t="n">
-        <v>11.62081411316933</v>
+        <v>11.62081221663484</v>
       </c>
       <c r="F201" t="n">
         <v>128526</v>
@@ -4452,16 +4452,16 @@
         <v>44608</v>
       </c>
       <c r="B202" t="n">
-        <v>11.6953592300415</v>
+        <v>11.69535827636719</v>
       </c>
       <c r="C202" t="n">
-        <v>11.81960154268786</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="D202" t="n">
-        <v>11.65394457104532</v>
+        <v>11.65394362074808</v>
       </c>
       <c r="E202" t="n">
-        <v>11.81960154268786</v>
+        <v>11.81960057888246</v>
       </c>
       <c r="F202" t="n">
         <v>113251</v>
@@ -4472,16 +4472,16 @@
         <v>44609</v>
       </c>
       <c r="B203" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C203" t="n">
-        <v>11.98525635610031</v>
+        <v>11.98525829971548</v>
       </c>
       <c r="D203" t="n">
-        <v>11.68707452657532</v>
+        <v>11.6870764218352</v>
       </c>
       <c r="E203" t="n">
-        <v>11.69535712401464</v>
+        <v>11.69535902061768</v>
       </c>
       <c r="F203" t="n">
         <v>1539476</v>
@@ -4532,16 +4532,16 @@
         <v>44614</v>
       </c>
       <c r="B206" t="n">
-        <v>11.54626846313477</v>
+        <v>11.54626750946045</v>
       </c>
       <c r="C206" t="n">
-        <v>11.72849063539606</v>
+        <v>11.72848966667094</v>
       </c>
       <c r="D206" t="n">
-        <v>11.51313723473918</v>
+        <v>11.51313628380136</v>
       </c>
       <c r="E206" t="n">
-        <v>11.51313723473918</v>
+        <v>11.51313628380136</v>
       </c>
       <c r="F206" t="n">
         <v>213649</v>
@@ -4552,16 +4552,16 @@
         <v>44615</v>
       </c>
       <c r="B207" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C207" t="n">
-        <v>11.91899204805644</v>
+        <v>11.91899398228799</v>
       </c>
       <c r="D207" t="n">
-        <v>11.54626520950857</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="E207" t="n">
-        <v>11.54626520950857</v>
+        <v>11.54626708325345</v>
       </c>
       <c r="F207" t="n">
         <v>360401</v>
@@ -4572,16 +4572,16 @@
         <v>44616</v>
       </c>
       <c r="B208" t="n">
-        <v>12.14263153076172</v>
+        <v>12.14263248443604</v>
       </c>
       <c r="C208" t="n">
-        <v>12.17576192278439</v>
+        <v>12.17576287906074</v>
       </c>
       <c r="D208" t="n">
-        <v>11.42202469999357</v>
+        <v>11.4220255970719</v>
       </c>
       <c r="E208" t="n">
-        <v>11.59596425113861</v>
+        <v>11.59596516187804</v>
       </c>
       <c r="F208" t="n">
         <v>512210</v>
@@ -4592,16 +4592,16 @@
         <v>44617</v>
       </c>
       <c r="B209" t="n">
-        <v>11.99353981018066</v>
+        <v>11.99354076385498</v>
       </c>
       <c r="C209" t="n">
-        <v>12.31657111943808</v>
+        <v>12.31657209879845</v>
       </c>
       <c r="D209" t="n">
-        <v>11.8196002585056</v>
+        <v>11.81960119834899</v>
       </c>
       <c r="E209" t="n">
-        <v>12.09293348306456</v>
+        <v>12.09293444464223</v>
       </c>
       <c r="F209" t="n">
         <v>373254</v>
@@ -4692,16 +4692,16 @@
         <v>44628</v>
       </c>
       <c r="B214" t="n">
-        <v>12.1591968536377</v>
+        <v>12.15919780731201</v>
       </c>
       <c r="C214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="D214" t="n">
-        <v>12.14263165745353</v>
+        <v>12.1426326098286</v>
       </c>
       <c r="E214" t="n">
-        <v>12.79697438231949</v>
+        <v>12.79697538601619</v>
       </c>
       <c r="F214" t="n">
         <v>363878</v>
@@ -4712,16 +4712,16 @@
         <v>44629</v>
       </c>
       <c r="B215" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C215" t="n">
-        <v>12.44081293822948</v>
+        <v>12.44081389317532</v>
       </c>
       <c r="D215" t="n">
-        <v>12.09293382504164</v>
+        <v>12.09293475328459</v>
       </c>
       <c r="E215" t="n">
-        <v>12.17576230420604</v>
+        <v>12.17576323880683</v>
       </c>
       <c r="F215" t="n">
         <v>243990</v>
@@ -4732,16 +4732,16 @@
         <v>44630</v>
       </c>
       <c r="B216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="C216" t="n">
-        <v>12.42424774169922</v>
+        <v>12.42424869537354</v>
       </c>
       <c r="D216" t="n">
-        <v>12.15919710767578</v>
+        <v>12.15919804100504</v>
       </c>
       <c r="E216" t="n">
-        <v>12.39111568429664</v>
+        <v>12.39111663542777</v>
       </c>
       <c r="F216" t="n">
         <v>181517</v>
@@ -4772,16 +4772,16 @@
         <v>44634</v>
       </c>
       <c r="B218" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C218" t="n">
-        <v>11.90242726892965</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="D218" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="E218" t="n">
-        <v>11.90242726892965</v>
+        <v>11.90242924788999</v>
       </c>
       <c r="F218" t="n">
         <v>493247</v>
@@ -4792,16 +4792,16 @@
         <v>44635</v>
       </c>
       <c r="B219" t="n">
-        <v>11.52141857147217</v>
+        <v>11.52141952514648</v>
       </c>
       <c r="C219" t="n">
-        <v>11.80303523023652</v>
+        <v>11.80303620722139</v>
       </c>
       <c r="D219" t="n">
-        <v>11.45515612194091</v>
+        <v>11.45515707013042</v>
       </c>
       <c r="E219" t="n">
-        <v>11.54626719808914</v>
+        <v>11.54626815382028</v>
       </c>
       <c r="F219" t="n">
         <v>195002</v>
@@ -4852,16 +4852,16 @@
         <v>44638</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66222763061523</v>
+        <v>11.6622257232666</v>
       </c>
       <c r="C222" t="n">
-        <v>11.84444979431419</v>
+        <v>11.84444785716326</v>
       </c>
       <c r="D222" t="n">
-        <v>11.36404575689492</v>
+        <v>11.36404389831371</v>
       </c>
       <c r="E222" t="n">
-        <v>11.53798532192695</v>
+        <v>11.53798343489805</v>
       </c>
       <c r="F222" t="n">
         <v>581846</v>
@@ -4872,16 +4872,16 @@
         <v>44641</v>
       </c>
       <c r="B223" t="n">
-        <v>11.67879199981689</v>
+        <v>11.67879295349121</v>
       </c>
       <c r="C223" t="n">
-        <v>11.75333787904653</v>
+        <v>11.75333883880816</v>
       </c>
       <c r="D223" t="n">
-        <v>11.55454969993852</v>
+        <v>11.55455064346737</v>
       </c>
       <c r="E223" t="n">
-        <v>11.69535802814715</v>
+        <v>11.69535898317423</v>
       </c>
       <c r="F223" t="n">
         <v>273488</v>
@@ -4892,16 +4892,16 @@
         <v>44642</v>
       </c>
       <c r="B224" t="n">
-        <v>11.75333595275879</v>
+        <v>11.75333786010742</v>
       </c>
       <c r="C224" t="n">
-        <v>11.79475060071136</v>
+        <v>11.79475251478082</v>
       </c>
       <c r="D224" t="n">
-        <v>11.5793964285681</v>
+        <v>11.57939830768957</v>
       </c>
       <c r="E224" t="n">
-        <v>11.67879008574669</v>
+        <v>11.67879198099791</v>
       </c>
       <c r="F224" t="n">
         <v>792441</v>
@@ -4952,16 +4952,16 @@
         <v>44645</v>
       </c>
       <c r="B227" t="n">
-        <v>11.60424709320068</v>
+        <v>11.604248046875</v>
       </c>
       <c r="C227" t="n">
-        <v>11.78646924618382</v>
+        <v>11.78647021483374</v>
       </c>
       <c r="D227" t="n">
-        <v>11.43030753839741</v>
+        <v>11.43030847777682</v>
       </c>
       <c r="E227" t="n">
-        <v>11.69535816969225</v>
+        <v>11.69535913085437</v>
       </c>
       <c r="F227" t="n">
         <v>679506</v>
@@ -4972,16 +4972,16 @@
         <v>44648</v>
       </c>
       <c r="B228" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C228" t="n">
-        <v>11.76990216531041</v>
+        <v>11.76990407400221</v>
       </c>
       <c r="D228" t="n">
-        <v>11.52970101437351</v>
+        <v>11.52970288411256</v>
       </c>
       <c r="E228" t="n">
-        <v>11.65394247247615</v>
+        <v>11.65394436236309</v>
       </c>
       <c r="F228" t="n">
         <v>221866</v>
@@ -4992,16 +4992,16 @@
         <v>44649</v>
       </c>
       <c r="B229" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="C229" t="n">
-        <v>12.17576109023034</v>
+        <v>12.17576306473914</v>
       </c>
       <c r="D229" t="n">
-        <v>11.76161956787109</v>
+        <v>11.76162147521973</v>
       </c>
       <c r="E229" t="n">
-        <v>11.83616544133781</v>
+        <v>11.83616736077534</v>
       </c>
       <c r="F229" t="n">
         <v>841955</v>
@@ -5012,16 +5012,16 @@
         <v>44650</v>
       </c>
       <c r="B230" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C230" t="n">
-        <v>11.89414467191917</v>
+        <v>11.8941466495024</v>
       </c>
       <c r="D230" t="n">
-        <v>11.3557608871619</v>
+        <v>11.3557627752306</v>
       </c>
       <c r="E230" t="n">
-        <v>11.8444474255145</v>
+        <v>11.84444939483481</v>
       </c>
       <c r="F230" t="n">
         <v>1241441</v>
@@ -5032,16 +5032,16 @@
         <v>44651</v>
       </c>
       <c r="B231" t="n">
-        <v>11.413743019104</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C231" t="n">
-        <v>11.56283396691093</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="D231" t="n">
-        <v>11.23152084202566</v>
+        <v>11.2315199035769</v>
       </c>
       <c r="E231" t="n">
-        <v>11.56283396691093</v>
+        <v>11.56283300077933</v>
       </c>
       <c r="F231" t="n">
         <v>710268</v>
@@ -5052,16 +5052,16 @@
         <v>44652</v>
       </c>
       <c r="B232" t="n">
-        <v>11.413743019104</v>
+        <v>11.41374206542969</v>
       </c>
       <c r="C232" t="n">
-        <v>11.62909725762489</v>
+        <v>11.62909628595667</v>
       </c>
       <c r="D232" t="n">
-        <v>11.256369472022</v>
+        <v>11.25636853149702</v>
       </c>
       <c r="E232" t="n">
-        <v>11.51313753908938</v>
+        <v>11.51313657711016</v>
       </c>
       <c r="F232" t="n">
         <v>713955</v>
@@ -5072,16 +5072,16 @@
         <v>44655</v>
       </c>
       <c r="B233" t="n">
-        <v>11.47171974182129</v>
+        <v>11.47172164916992</v>
       </c>
       <c r="C233" t="n">
-        <v>11.56283080544925</v>
+        <v>11.56283272794649</v>
       </c>
       <c r="D233" t="n">
-        <v>11.33919486097004</v>
+        <v>11.33919674628439</v>
       </c>
       <c r="E233" t="n">
-        <v>11.41373989840614</v>
+        <v>11.41374179611474</v>
       </c>
       <c r="F233" t="n">
         <v>616506</v>
@@ -5132,16 +5132,16 @@
         <v>44658</v>
       </c>
       <c r="B236" t="n">
-        <v>10.88364028930664</v>
+        <v>10.88364124298096</v>
       </c>
       <c r="C236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="D236" t="n">
-        <v>10.83394303949338</v>
+        <v>10.833943988813</v>
       </c>
       <c r="E236" t="n">
-        <v>11.07414502663918</v>
+        <v>11.0741459970064</v>
       </c>
       <c r="F236" t="n">
         <v>432987</v>
@@ -5152,16 +5152,16 @@
         <v>44659</v>
       </c>
       <c r="B237" t="n">
-        <v>10.89192295074463</v>
+        <v>10.89192390441895</v>
       </c>
       <c r="C237" t="n">
-        <v>10.98303402115581</v>
+        <v>10.98303498280762</v>
       </c>
       <c r="D237" t="n">
-        <v>10.69313478249707</v>
+        <v>10.69313571876591</v>
       </c>
       <c r="E237" t="n">
-        <v>10.93333677105118</v>
+        <v>10.9333377283516</v>
       </c>
       <c r="F237" t="n">
         <v>611134</v>
@@ -5232,16 +5232,16 @@
         <v>44665</v>
       </c>
       <c r="B241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000556945801</v>
       </c>
       <c r="C241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82566254625604</v>
       </c>
       <c r="D241" t="n">
-        <v>10.66000461578369</v>
+        <v>10.66000556945801</v>
       </c>
       <c r="E241" t="n">
-        <v>10.82566157776158</v>
+        <v>10.82566254625604</v>
       </c>
       <c r="F241" t="n">
         <v>278755</v>
@@ -5252,16 +5252,16 @@
         <v>44669</v>
       </c>
       <c r="B242" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76768207550049</v>
       </c>
       <c r="C242" t="n">
-        <v>11.0327307901932</v>
+        <v>11.03273274449196</v>
       </c>
       <c r="D242" t="n">
-        <v>10.65172130116907</v>
+        <v>10.65172318797716</v>
       </c>
       <c r="E242" t="n">
-        <v>10.66000389905977</v>
+        <v>10.66000578733501</v>
       </c>
       <c r="F242" t="n">
         <v>1174439</v>
@@ -5272,16 +5272,16 @@
         <v>44670</v>
       </c>
       <c r="B243" t="n">
-        <v>10.76768016815186</v>
+        <v>10.76768207550049</v>
       </c>
       <c r="C243" t="n">
-        <v>10.92505452110112</v>
+        <v>10.92505645632649</v>
       </c>
       <c r="D243" t="n">
-        <v>10.66000389905977</v>
+        <v>10.66000578733501</v>
       </c>
       <c r="E243" t="n">
-        <v>10.80081222405664</v>
+        <v>10.80081413727417</v>
       </c>
       <c r="F243" t="n">
         <v>540022</v>
@@ -5372,16 +5372,16 @@
         <v>44678</v>
       </c>
       <c r="B248" t="n">
-        <v>10.34525775909424</v>
+        <v>10.34525585174561</v>
       </c>
       <c r="C248" t="n">
-        <v>10.56061114821748</v>
+        <v>10.56060920116428</v>
       </c>
       <c r="D248" t="n">
-        <v>10.32869089752705</v>
+        <v>10.32868899323284</v>
       </c>
       <c r="E248" t="n">
-        <v>10.41151938016555</v>
+        <v>10.4115174606003</v>
       </c>
       <c r="F248" t="n">
         <v>267483</v>
@@ -5392,16 +5392,16 @@
         <v>44679</v>
       </c>
       <c r="B249" t="n">
-        <v>10.37838745117188</v>
+        <v>10.37838935852051</v>
       </c>
       <c r="C249" t="n">
-        <v>10.55232700328979</v>
+        <v>10.55232894260518</v>
       </c>
       <c r="D249" t="n">
-        <v>10.23757912343294</v>
+        <v>10.2375810049037</v>
       </c>
       <c r="E249" t="n">
-        <v>10.3452570589639</v>
+        <v>10.3452589602238</v>
       </c>
       <c r="F249" t="n">
         <v>289711</v>
@@ -5412,16 +5412,16 @@
         <v>44680</v>
       </c>
       <c r="B250" t="n">
-        <v>10.83394336700439</v>
+        <v>10.83394432067871</v>
       </c>
       <c r="C250" t="n">
-        <v>11.16525643404281</v>
+        <v>11.16525741688146</v>
       </c>
       <c r="D250" t="n">
-        <v>10.53576152345272</v>
+        <v>10.53576245087913</v>
       </c>
       <c r="E250" t="n">
-        <v>10.56889274693946</v>
+        <v>10.5688936772823</v>
       </c>
       <c r="F250" t="n">
         <v>1735216</v>
@@ -5452,16 +5452,16 @@
         <v>44684</v>
       </c>
       <c r="B252" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280433654785</v>
       </c>
       <c r="C252" t="n">
-        <v>10.72603654719261</v>
+        <v>10.72603750383094</v>
       </c>
       <c r="D252" t="n">
-        <v>10.51002056175287</v>
+        <v>10.51002149912508</v>
       </c>
       <c r="E252" t="n">
-        <v>10.71772763006424</v>
+        <v>10.71772858596151</v>
       </c>
       <c r="F252" t="n">
         <v>311097</v>
@@ -5532,16 +5532,16 @@
         <v>44690</v>
       </c>
       <c r="B256" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280433654785</v>
       </c>
       <c r="C256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036242640624</v>
       </c>
       <c r="D256" t="n">
-        <v>10.618028137107</v>
+        <v>10.61802908411223</v>
       </c>
       <c r="E256" t="n">
-        <v>10.95036144976073</v>
+        <v>10.95036242640624</v>
       </c>
       <c r="F256" t="n">
         <v>340595</v>
@@ -5552,16 +5552,16 @@
         <v>44691</v>
       </c>
       <c r="B257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C257" t="n">
-        <v>10.88389415417323</v>
+        <v>10.88389316500986</v>
       </c>
       <c r="D257" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="E257" t="n">
-        <v>10.86727798958128</v>
+        <v>10.86727700192804</v>
       </c>
       <c r="F257" t="n">
         <v>236720</v>
@@ -5572,16 +5572,16 @@
         <v>44692</v>
       </c>
       <c r="B258" t="n">
-        <v>10.62633514404297</v>
+        <v>10.62633609771729</v>
       </c>
       <c r="C258" t="n">
-        <v>10.80080986510865</v>
+        <v>10.80081083444142</v>
       </c>
       <c r="D258" t="n">
-        <v>10.4684782555522</v>
+        <v>10.46847919505945</v>
       </c>
       <c r="E258" t="n">
-        <v>10.51001949806391</v>
+        <v>10.51002044129933</v>
       </c>
       <c r="F258" t="n">
         <v>211647</v>
@@ -5612,16 +5612,16 @@
         <v>44694</v>
       </c>
       <c r="B260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86727714538574</v>
+        <v>10.86727809906006</v>
       </c>
       <c r="D260" t="n">
-        <v>10.49340261960133</v>
+        <v>10.49340354046572</v>
       </c>
       <c r="E260" t="n">
-        <v>10.61802718328567</v>
+        <v>10.61802811508668</v>
       </c>
       <c r="F260" t="n">
         <v>280967</v>
@@ -5632,16 +5632,16 @@
         <v>44697</v>
       </c>
       <c r="B261" t="n">
-        <v>11.1663761138916</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="C261" t="n">
-        <v>11.1663761138916</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="D261" t="n">
-        <v>10.75926843837557</v>
+        <v>10.75927027618541</v>
       </c>
       <c r="E261" t="n">
-        <v>10.87558491709443</v>
+        <v>10.8755867747725</v>
       </c>
       <c r="F261" t="n">
         <v>1349214</v>
@@ -5672,16 +5672,16 @@
         <v>44699</v>
       </c>
       <c r="B263" t="n">
-        <v>11.11652755737305</v>
+        <v>11.11652660369873</v>
       </c>
       <c r="C263" t="n">
-        <v>11.24946021806958</v>
+        <v>11.24945925299112</v>
       </c>
       <c r="D263" t="n">
-        <v>10.8091193187322</v>
+        <v>10.80911839143009</v>
       </c>
       <c r="E263" t="n">
-        <v>11.01682806185065</v>
+        <v>11.01682711672944</v>
       </c>
       <c r="F263" t="n">
         <v>416658</v>
@@ -5732,16 +5732,16 @@
         <v>44704</v>
       </c>
       <c r="B266" t="n">
-        <v>10.96697616577148</v>
+        <v>10.96697807312012</v>
       </c>
       <c r="C266" t="n">
-        <v>11.19960912000472</v>
+        <v>11.19961106781229</v>
       </c>
       <c r="D266" t="n">
-        <v>10.72603513023888</v>
+        <v>10.72603699568366</v>
       </c>
       <c r="E266" t="n">
-        <v>11.14975896274578</v>
+        <v>11.14976090188353</v>
       </c>
       <c r="F266" t="n">
         <v>653906</v>
@@ -5752,16 +5752,16 @@
         <v>44705</v>
       </c>
       <c r="B267" t="n">
-        <v>11.1663761138916</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="C267" t="n">
-        <v>11.1663761138916</v>
+        <v>11.16637802124023</v>
       </c>
       <c r="D267" t="n">
-        <v>10.71772636184375</v>
+        <v>10.71772819255772</v>
       </c>
       <c r="E267" t="n">
-        <v>11.05005963517273</v>
+        <v>11.05006152265314</v>
       </c>
       <c r="F267" t="n">
         <v>359032</v>
@@ -5772,16 +5772,16 @@
         <v>44706</v>
       </c>
       <c r="B268" t="n">
-        <v>10.99190235137939</v>
+        <v>10.99190330505371</v>
       </c>
       <c r="C268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="D268" t="n">
-        <v>10.89220202682084</v>
+        <v>10.892202971845</v>
       </c>
       <c r="E268" t="n">
-        <v>11.19961024790112</v>
+        <v>11.19961121959649</v>
       </c>
       <c r="F268" t="n">
         <v>140009</v>
@@ -5832,16 +5832,16 @@
         <v>44711</v>
       </c>
       <c r="B271" t="n">
-        <v>11.25776863098145</v>
+        <v>11.25776958465576</v>
       </c>
       <c r="C271" t="n">
-        <v>11.2743856301897</v>
+        <v>11.27438658527168</v>
       </c>
       <c r="D271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="E271" t="n">
-        <v>11.09160281255622</v>
+        <v>11.09160375215421</v>
       </c>
       <c r="F271" t="n">
         <v>182571</v>
@@ -5852,16 +5852,16 @@
         <v>44712</v>
       </c>
       <c r="B272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085178375244</v>
       </c>
       <c r="C272" t="n">
-        <v>11.34085083007812</v>
+        <v>11.34085178375244</v>
       </c>
       <c r="D272" t="n">
-        <v>11.13314295164785</v>
+        <v>11.1331438878556</v>
       </c>
       <c r="E272" t="n">
-        <v>11.24945859561594</v>
+        <v>11.2494595416049</v>
       </c>
       <c r="F272" t="n">
         <v>190683</v>
@@ -5952,16 +5952,16 @@
         <v>44719</v>
       </c>
       <c r="B277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C277" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D277" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79250303440952</v>
+        <v>10.79250209732709</v>
       </c>
       <c r="F277" t="n">
         <v>265270</v>
@@ -5992,16 +5992,16 @@
         <v>44721</v>
       </c>
       <c r="B279" t="n">
-        <v>10.69280338287354</v>
+        <v>10.69280433654785</v>
       </c>
       <c r="C279" t="n">
-        <v>10.82573687488132</v>
+        <v>10.82573784041177</v>
       </c>
       <c r="D279" t="n">
-        <v>10.6263362195039</v>
+        <v>10.62633716725012</v>
       </c>
       <c r="E279" t="n">
-        <v>10.79250287583077</v>
+        <v>10.79250383839712</v>
       </c>
       <c r="F279" t="n">
         <v>205537</v>
@@ -6032,16 +6032,16 @@
         <v>44725</v>
       </c>
       <c r="B281" t="n">
-        <v>10.25246143341064</v>
+        <v>10.25246238708496</v>
       </c>
       <c r="C281" t="n">
-        <v>10.47678631275402</v>
+        <v>10.47678728729483</v>
       </c>
       <c r="D281" t="n">
-        <v>10.18599427692247</v>
+        <v>10.18599522441408</v>
       </c>
       <c r="E281" t="n">
-        <v>10.3853949116556</v>
+        <v>10.38539587769526</v>
       </c>
       <c r="F281" t="n">
         <v>299930</v>
@@ -6092,16 +6092,16 @@
         <v>44729</v>
       </c>
       <c r="B284" t="n">
-        <v>10.17768669128418</v>
+        <v>10.17768573760986</v>
       </c>
       <c r="C284" t="n">
-        <v>10.35216142044539</v>
+        <v>10.35216045042237</v>
       </c>
       <c r="D284" t="n">
-        <v>10.07798720379124</v>
+        <v>10.07798625945901</v>
       </c>
       <c r="E284" t="n">
-        <v>10.18599477322573</v>
+        <v>10.18599381877293</v>
       </c>
       <c r="F284" t="n">
         <v>237458</v>
@@ -6132,16 +6132,16 @@
         <v>44733</v>
       </c>
       <c r="B286" t="n">
-        <v>9.911820411682129</v>
+        <v>9.911821365356445</v>
       </c>
       <c r="C286" t="n">
-        <v>10.21922862107171</v>
+        <v>10.21922960432357</v>
       </c>
       <c r="D286" t="n">
-        <v>9.787195845454841</v>
+        <v>9.787196787138297</v>
       </c>
       <c r="E286" t="n">
-        <v>10.12783721685627</v>
+        <v>10.12783819131483</v>
       </c>
       <c r="F286" t="n">
         <v>295716</v>
@@ -6152,16 +6152,16 @@
         <v>44734</v>
       </c>
       <c r="B287" t="n">
-        <v>9.837047576904297</v>
+        <v>9.83704662322998</v>
       </c>
       <c r="C287" t="n">
-        <v>10.13614691751124</v>
+        <v>10.13614593484008</v>
       </c>
       <c r="D287" t="n">
-        <v>9.820430575878776</v>
+        <v>9.820429623815432</v>
       </c>
       <c r="E287" t="n">
-        <v>9.920130077837239</v>
+        <v>9.920129116108306</v>
       </c>
       <c r="F287" t="n">
         <v>227344</v>
@@ -6192,16 +6192,16 @@
         <v>44736</v>
       </c>
       <c r="B289" t="n">
-        <v>9.388397216796875</v>
+        <v>9.388398170471191</v>
       </c>
       <c r="C289" t="n">
-        <v>9.795504918735785</v>
+        <v>9.795505913764142</v>
       </c>
       <c r="D289" t="n">
-        <v>9.388397216796875</v>
+        <v>9.388398170471191</v>
       </c>
       <c r="E289" t="n">
-        <v>9.6958045963736</v>
+        <v>9.695805581274389</v>
       </c>
       <c r="F289" t="n">
         <v>325741</v>
@@ -6232,16 +6232,16 @@
         <v>44740</v>
       </c>
       <c r="B291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="C291" t="n">
-        <v>9.496406309403417</v>
+        <v>9.496405321144287</v>
       </c>
       <c r="D291" t="n">
-        <v>9.16407299041748</v>
+        <v>9.164072036743164</v>
       </c>
       <c r="E291" t="n">
-        <v>9.488098226848217</v>
+        <v>9.488097239453682</v>
       </c>
       <c r="F291" t="n">
         <v>210278</v>
@@ -6252,16 +6252,16 @@
         <v>44741</v>
       </c>
       <c r="B292" t="n">
-        <v>9.072681427001953</v>
+        <v>9.072680473327637</v>
       </c>
       <c r="C292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="D292" t="n">
-        <v>8.93974876940689</v>
+        <v>8.93974782970578</v>
       </c>
       <c r="E292" t="n">
-        <v>9.255464248560907</v>
+        <v>9.255463275673385</v>
       </c>
       <c r="F292" t="n">
         <v>344177</v>
@@ -6272,16 +6272,16 @@
         <v>44742</v>
       </c>
       <c r="B293" t="n">
-        <v>8.732039451599121</v>
+        <v>8.732040405273438</v>
       </c>
       <c r="C293" t="n">
-        <v>9.05606466112774</v>
+        <v>9.056065650190641</v>
       </c>
       <c r="D293" t="n">
-        <v>8.698807124137426</v>
+        <v>8.698808074182256</v>
       </c>
       <c r="E293" t="n">
-        <v>9.05606466112774</v>
+        <v>9.056065650190641</v>
       </c>
       <c r="F293" t="n">
         <v>345757</v>
@@ -6292,16 +6292,16 @@
         <v>44743</v>
       </c>
       <c r="B294" t="n">
-        <v>8.89820671081543</v>
+        <v>8.898205757141113</v>
       </c>
       <c r="C294" t="n">
-        <v>9.039448285923172</v>
+        <v>9.039447317111145</v>
       </c>
       <c r="D294" t="n">
-        <v>8.657265642254186</v>
+        <v>8.657264714402972</v>
       </c>
       <c r="E294" t="n">
-        <v>8.823431464676691</v>
+        <v>8.823430519016487</v>
       </c>
       <c r="F294" t="n">
         <v>217547</v>
@@ -6312,16 +6312,16 @@
         <v>44746</v>
       </c>
       <c r="B295" t="n">
-        <v>9.222230911254883</v>
+        <v>9.222232818603516</v>
       </c>
       <c r="C295" t="n">
-        <v>9.297005314299241</v>
+        <v>9.297007237112771</v>
       </c>
       <c r="D295" t="n">
-        <v>8.87328147109751</v>
+        <v>8.873283306276161</v>
       </c>
       <c r="E295" t="n">
-        <v>8.97298095340045</v>
+        <v>8.972982809199021</v>
       </c>
       <c r="F295" t="n">
         <v>166874</v>
@@ -6332,16 +6332,16 @@
         <v>44747</v>
       </c>
       <c r="B296" t="n">
-        <v>9.031140327453613</v>
+        <v>9.03114128112793</v>
       </c>
       <c r="C296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213924124969031</v>
       </c>
       <c r="D296" t="n">
-        <v>9.022831410169822</v>
+        <v>9.02283236296673</v>
       </c>
       <c r="E296" t="n">
-        <v>9.213923151993134</v>
+        <v>9.213924124969031</v>
       </c>
       <c r="F296" t="n">
         <v>222182</v>
@@ -6372,16 +6372,16 @@
         <v>44749</v>
       </c>
       <c r="B298" t="n">
-        <v>9.056064605712891</v>
+        <v>9.056065559387207</v>
       </c>
       <c r="C298" t="n">
-        <v>9.355163898352176</v>
+        <v>9.355164883523981</v>
       </c>
       <c r="D298" t="n">
-        <v>9.056064605712891</v>
+        <v>9.056065559387207</v>
       </c>
       <c r="E298" t="n">
-        <v>9.230539332207711</v>
+        <v>9.230540304255577</v>
       </c>
       <c r="F298" t="n">
         <v>150966</v>
@@ -6432,16 +6432,16 @@
         <v>44754</v>
       </c>
       <c r="B301" t="n">
-        <v>8.690499305725098</v>
+        <v>8.690498352050781</v>
       </c>
       <c r="C301" t="n">
-        <v>8.864974055335237</v>
+        <v>8.864973082514485</v>
       </c>
       <c r="D301" t="n">
-        <v>8.574182805985005</v>
+        <v>8.57418186507498</v>
       </c>
       <c r="E301" t="n">
-        <v>8.864974055335237</v>
+        <v>8.864973082514485</v>
       </c>
       <c r="F301" t="n">
         <v>237774</v>
@@ -6452,16 +6452,16 @@
         <v>44755</v>
       </c>
       <c r="B302" t="n">
-        <v>8.59910774230957</v>
+        <v>8.599105834960938</v>
       </c>
       <c r="C302" t="n">
-        <v>8.823431820304181</v>
+        <v>8.823429863198731</v>
       </c>
       <c r="D302" t="n">
-        <v>8.549257576207872</v>
+        <v>8.549255679916392</v>
       </c>
       <c r="E302" t="n">
-        <v>8.56587457648561</v>
+        <v>8.56587267650835</v>
       </c>
       <c r="F302" t="n">
         <v>184467</v>
@@ -6472,16 +6472,16 @@
         <v>44756</v>
       </c>
       <c r="B303" t="n">
-        <v>8.499407768249512</v>
+        <v>8.499406814575195</v>
       </c>
       <c r="C303" t="n">
-        <v>8.565874096170459</v>
+        <v>8.565873135038302</v>
       </c>
       <c r="D303" t="n">
-        <v>8.349858113061646</v>
+        <v>8.34985717616752</v>
       </c>
       <c r="E303" t="n">
-        <v>8.358166195368899</v>
+        <v>8.358165257542563</v>
       </c>
       <c r="F303" t="n">
         <v>213754</v>
@@ -6492,16 +6492,16 @@
         <v>44757</v>
       </c>
       <c r="B304" t="n">
-        <v>8.499407768249512</v>
+        <v>8.499406814575195</v>
       </c>
       <c r="C304" t="n">
-        <v>8.58249109551643</v>
+        <v>8.582490132519766</v>
       </c>
       <c r="D304" t="n">
-        <v>8.424632523289844</v>
+        <v>8.42463157800567</v>
       </c>
       <c r="E304" t="n">
-        <v>8.540949014517237</v>
+        <v>8.540948056181794</v>
       </c>
       <c r="F304" t="n">
         <v>109458</v>
@@ -6512,16 +6512,16 @@
         <v>44760</v>
       </c>
       <c r="B305" t="n">
-        <v>8.574182510375977</v>
+        <v>8.574180603027344</v>
       </c>
       <c r="C305" t="n">
-        <v>8.723732171352765</v>
+        <v>8.723730230736431</v>
       </c>
       <c r="D305" t="n">
-        <v>8.482791097264135</v>
+        <v>8.482789210245754</v>
       </c>
       <c r="E305" t="n">
-        <v>8.582491427736327</v>
+        <v>8.582489518539354</v>
       </c>
       <c r="F305" t="n">
         <v>154548</v>
@@ -6532,16 +6532,16 @@
         <v>44761</v>
       </c>
       <c r="B306" t="n">
-        <v>8.557564735412598</v>
+        <v>8.557565689086914</v>
       </c>
       <c r="C306" t="n">
-        <v>8.673882055340277</v>
+        <v>8.673883021977259</v>
       </c>
       <c r="D306" t="n">
-        <v>8.482790329061535</v>
+        <v>8.482791274402823</v>
       </c>
       <c r="E306" t="n">
-        <v>8.499407327545896</v>
+        <v>8.49940827473902</v>
       </c>
       <c r="F306" t="n">
         <v>159183</v>
@@ -6552,16 +6552,16 @@
         <v>44762</v>
       </c>
       <c r="B307" t="n">
-        <v>8.864974021911621</v>
+        <v>8.864973068237305</v>
       </c>
       <c r="C307" t="n">
-        <v>8.873282939527108</v>
+        <v>8.873281984958936</v>
       </c>
       <c r="D307" t="n">
-        <v>8.615724857540613</v>
+        <v>8.615723930679971</v>
       </c>
       <c r="E307" t="n">
-        <v>8.632341023308532</v>
+        <v>8.632340094660361</v>
       </c>
       <c r="F307" t="n">
         <v>307199</v>
@@ -6572,16 +6572,16 @@
         <v>44763</v>
       </c>
       <c r="B308" t="n">
-        <v>8.823431015014648</v>
+        <v>8.823431968688965</v>
       </c>
       <c r="C308" t="n">
-        <v>8.881590093312958</v>
+        <v>8.881591053273359</v>
       </c>
       <c r="D308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="E308" t="n">
-        <v>8.756965524164361</v>
+        <v>8.756966470654801</v>
       </c>
       <c r="F308" t="n">
         <v>93866</v>
@@ -6612,16 +6612,16 @@
         <v>44767</v>
       </c>
       <c r="B310" t="n">
-        <v>9.039446830749512</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="C310" t="n">
-        <v>9.039446830749512</v>
+        <v>9.039447784423828</v>
       </c>
       <c r="D310" t="n">
-        <v>8.815121963176683</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="E310" t="n">
-        <v>8.815121963176683</v>
+        <v>8.815122893184411</v>
       </c>
       <c r="F310" t="n">
         <v>69004</v>
@@ -6652,16 +6652,16 @@
         <v>44769</v>
       </c>
       <c r="B312" t="n">
-        <v>9.047757148742676</v>
+        <v>9.047756195068359</v>
       </c>
       <c r="C312" t="n">
-        <v>9.072681395907718</v>
+        <v>9.072680439606275</v>
       </c>
       <c r="D312" t="n">
-        <v>8.756965917835734</v>
+        <v>8.756964994812122</v>
       </c>
       <c r="E312" t="n">
-        <v>8.765274000224082</v>
+        <v>8.76527307632476</v>
       </c>
       <c r="F312" t="n">
         <v>161185</v>
@@ -6672,16 +6672,16 @@
         <v>44770</v>
       </c>
       <c r="B313" t="n">
-        <v>9.047757148742676</v>
+        <v>9.047756195068359</v>
       </c>
       <c r="C313" t="n">
-        <v>9.172380888762323</v>
+        <v>9.172379921952103</v>
       </c>
       <c r="D313" t="n">
-        <v>8.914823656871727</v>
+        <v>8.914822717209198</v>
       </c>
       <c r="E313" t="n">
-        <v>8.914823656871727</v>
+        <v>8.914822717209198</v>
       </c>
       <c r="F313" t="n">
         <v>129685</v>
@@ -6792,16 +6792,16 @@
         <v>44778</v>
       </c>
       <c r="B319" t="n">
-        <v>9.38008975982666</v>
+        <v>9.380088806152344</v>
       </c>
       <c r="C319" t="n">
-        <v>9.52963943191118</v>
+        <v>9.529638463032139</v>
       </c>
       <c r="D319" t="n">
-        <v>9.197306920026865</v>
+        <v>9.197305984936092</v>
       </c>
       <c r="E319" t="n">
-        <v>9.305315341150182</v>
+        <v>9.305314395078184</v>
       </c>
       <c r="F319" t="n">
         <v>223236</v>
@@ -6852,16 +6852,16 @@
         <v>44783</v>
       </c>
       <c r="B322" t="n">
-        <v>9.513022422790527</v>
+        <v>9.513021469116211</v>
       </c>
       <c r="C322" t="n">
-        <v>9.596105752085279</v>
+        <v>9.596104790081913</v>
       </c>
       <c r="D322" t="n">
-        <v>9.205615022604585</v>
+        <v>9.205614099747661</v>
       </c>
       <c r="E322" t="n">
-        <v>9.288697517167847</v>
+        <v>9.288696585981958</v>
       </c>
       <c r="F322" t="n">
         <v>209856</v>
@@ -6892,16 +6892,16 @@
         <v>44785</v>
       </c>
       <c r="B324" t="n">
-        <v>9.770580291748047</v>
+        <v>9.770581245422363</v>
       </c>
       <c r="C324" t="n">
-        <v>9.86197170166864</v>
+        <v>9.861972664263373</v>
       </c>
       <c r="D324" t="n">
-        <v>9.654262965348279</v>
+        <v>9.654263907669241</v>
       </c>
       <c r="E324" t="n">
-        <v>9.82042962051198</v>
+        <v>9.820430579051925</v>
       </c>
       <c r="F324" t="n">
         <v>170455</v>
@@ -6912,16 +6912,16 @@
         <v>44788</v>
       </c>
       <c r="B325" t="n">
-        <v>9.953362464904785</v>
+        <v>9.953363418579102</v>
       </c>
       <c r="C325" t="n">
-        <v>10.1195291092724</v>
+        <v>10.11953007886785</v>
       </c>
       <c r="D325" t="n">
-        <v>9.704112498353368</v>
+        <v>9.704113428145977</v>
       </c>
       <c r="E325" t="n">
-        <v>9.72903757848165</v>
+        <v>9.72903851066244</v>
       </c>
       <c r="F325" t="n">
         <v>231032</v>
@@ -6972,16 +6972,16 @@
         <v>44791</v>
       </c>
       <c r="B328" t="n">
-        <v>10.53494453430176</v>
+        <v>10.53494358062744</v>
       </c>
       <c r="C328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.75926845704052</v>
       </c>
       <c r="D328" t="n">
-        <v>10.35216171794617</v>
+        <v>10.35216078081824</v>
       </c>
       <c r="E328" t="n">
-        <v>10.75926943102181</v>
+        <v>10.75926845704052</v>
       </c>
       <c r="F328" t="n">
         <v>456796</v>
@@ -6992,16 +6992,16 @@
         <v>44792</v>
       </c>
       <c r="B329" t="n">
-        <v>10.49340343475342</v>
+        <v>10.4934024810791</v>
       </c>
       <c r="C329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="D329" t="n">
-        <v>10.21092112410713</v>
+        <v>10.21092019610571</v>
       </c>
       <c r="E329" t="n">
-        <v>10.53494468096475</v>
+        <v>10.53494372351503</v>
       </c>
       <c r="F329" t="n">
         <v>166663</v>
@@ -7092,16 +7092,16 @@
         <v>44799</v>
       </c>
       <c r="B334" t="n">
-        <v>10.75096035003662</v>
+        <v>10.75096130371094</v>
       </c>
       <c r="C334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="D334" t="n">
-        <v>10.3272365119659</v>
+        <v>10.32723742805339</v>
       </c>
       <c r="E334" t="n">
-        <v>10.77588542899338</v>
+        <v>10.7758863848787</v>
       </c>
       <c r="F334" t="n">
         <v>180990</v>
@@ -7112,16 +7112,16 @@
         <v>44802</v>
       </c>
       <c r="B335" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="C335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75926859837071</v>
       </c>
       <c r="D335" t="n">
-        <v>10.56817865938468</v>
+        <v>10.56817771462318</v>
       </c>
       <c r="E335" t="n">
-        <v>10.75926956021513</v>
+        <v>10.75926859837071</v>
       </c>
       <c r="F335" t="n">
         <v>128948</v>
@@ -7152,16 +7152,16 @@
         <v>44804</v>
       </c>
       <c r="B337" t="n">
-        <v>10.38539409637451</v>
+        <v>10.38539600372314</v>
       </c>
       <c r="C337" t="n">
-        <v>10.57648496510696</v>
+        <v>10.57648690755074</v>
       </c>
       <c r="D337" t="n">
-        <v>10.26907679033428</v>
+        <v>10.26907867632044</v>
       </c>
       <c r="E337" t="n">
-        <v>10.4020102581436</v>
+        <v>10.4020121685439</v>
       </c>
       <c r="F337" t="n">
         <v>170350</v>
@@ -7232,16 +7232,16 @@
         <v>44810</v>
       </c>
       <c r="B341" t="n">
-        <v>10.5764856338501</v>
+        <v>10.57648754119873</v>
       </c>
       <c r="C341" t="n">
-        <v>10.63464387318185</v>
+        <v>10.63464579101866</v>
       </c>
       <c r="D341" t="n">
-        <v>10.50171123169863</v>
+        <v>10.50171312556255</v>
       </c>
       <c r="E341" t="n">
-        <v>10.63464387318185</v>
+        <v>10.63464579101866</v>
       </c>
       <c r="F341" t="n">
         <v>83753</v>
@@ -7272,16 +7272,16 @@
         <v>44813</v>
       </c>
       <c r="B343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.05006217956543</v>
       </c>
       <c r="C343" t="n">
-        <v>11.05006122589111</v>
+        <v>11.05006217956543</v>
       </c>
       <c r="D343" t="n">
-        <v>10.68449557428166</v>
+        <v>10.68449649640587</v>
       </c>
       <c r="E343" t="n">
-        <v>10.76757890457422</v>
+        <v>10.76757983386893</v>
       </c>
       <c r="F343" t="n">
         <v>298877</v>
@@ -7292,16 +7292,16 @@
         <v>44816</v>
       </c>
       <c r="B344" t="n">
-        <v>11.13314437866211</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C344" t="n">
-        <v>11.1913026254664</v>
+        <v>11.1913016668102</v>
       </c>
       <c r="D344" t="n">
-        <v>10.9420526385631</v>
+        <v>10.94205170125786</v>
       </c>
       <c r="E344" t="n">
-        <v>11.05006104969434</v>
+        <v>11.05006010313701</v>
       </c>
       <c r="F344" t="n">
         <v>234297</v>
@@ -7332,16 +7332,16 @@
         <v>44818</v>
       </c>
       <c r="B346" t="n">
-        <v>11.13314437866211</v>
+        <v>11.13314342498779</v>
       </c>
       <c r="C346" t="n">
-        <v>11.14976054361677</v>
+        <v>11.1497595885191</v>
       </c>
       <c r="D346" t="n">
-        <v>10.88389439175881</v>
+        <v>10.88389345943545</v>
       </c>
       <c r="E346" t="n">
-        <v>11.14145246113944</v>
+        <v>11.14145150675345</v>
       </c>
       <c r="F346" t="n">
         <v>330903</v>
@@ -7512,16 +7512,16 @@
         <v>44831</v>
       </c>
       <c r="B355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="C355" t="n">
-        <v>10.58479547644101</v>
+        <v>10.58479449503473</v>
       </c>
       <c r="D355" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="E355" t="n">
-        <v>10.42693772973123</v>
+        <v>10.42693676296128</v>
       </c>
       <c r="F355" t="n">
         <v>115674</v>
@@ -7552,16 +7552,16 @@
         <v>44833</v>
       </c>
       <c r="B357" t="n">
-        <v>10.12783718109131</v>
+        <v>10.12783813476562</v>
       </c>
       <c r="C357" t="n">
-        <v>10.20261242140248</v>
+        <v>10.2026133821179</v>
       </c>
       <c r="D357" t="n">
-        <v>9.978287535200392</v>
+        <v>9.978288474792565</v>
       </c>
       <c r="E357" t="n">
-        <v>10.17768650656734</v>
+        <v>10.17768746493565</v>
       </c>
       <c r="F357" t="n">
         <v>97132</v>
@@ -7572,16 +7572,16 @@
         <v>44834</v>
       </c>
       <c r="B358" t="n">
-        <v>10.18599510192871</v>
+        <v>10.18599414825439</v>
       </c>
       <c r="C358" t="n">
-        <v>10.26907842821965</v>
+        <v>10.26907746676657</v>
       </c>
       <c r="D358" t="n">
-        <v>9.920128958636587</v>
+        <v>9.920128029854263</v>
       </c>
       <c r="E358" t="n">
-        <v>10.17768701971906</v>
+        <v>10.17768606682259</v>
       </c>
       <c r="F358" t="n">
         <v>188154</v>
@@ -7592,16 +7592,16 @@
         <v>44837</v>
       </c>
       <c r="B359" t="n">
-        <v>10.2856969833374</v>
+        <v>10.28569602966309</v>
       </c>
       <c r="C359" t="n">
-        <v>10.60972055954919</v>
+        <v>10.60971957583189</v>
       </c>
       <c r="D359" t="n">
-        <v>10.13614648468832</v>
+        <v>10.1361455448801</v>
       </c>
       <c r="E359" t="n">
-        <v>10.36047056319891</v>
+        <v>10.3604696025917</v>
       </c>
       <c r="F359" t="n">
         <v>398643</v>
@@ -7632,16 +7632,16 @@
         <v>44839</v>
       </c>
       <c r="B361" t="n">
-        <v>10.66787815093994</v>
+        <v>10.66787719726562</v>
       </c>
       <c r="C361" t="n">
-        <v>10.90051113263368</v>
+        <v>10.90051015816272</v>
       </c>
       <c r="D361" t="n">
-        <v>10.55987057710461</v>
+        <v>10.55986963308583</v>
       </c>
       <c r="E361" t="n">
-        <v>10.80081080634695</v>
+        <v>10.80080984078888</v>
       </c>
       <c r="F361" t="n">
         <v>399697</v>
@@ -7652,16 +7652,16 @@
         <v>44840</v>
       </c>
       <c r="B362" t="n">
-        <v>10.88389301300049</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="C362" t="n">
-        <v>10.88389301300049</v>
+        <v>10.8838939666748</v>
       </c>
       <c r="D362" t="n">
-        <v>10.5183274135295</v>
+        <v>10.51832833517203</v>
       </c>
       <c r="E362" t="n">
-        <v>10.53494357637925</v>
+        <v>10.53494449947773</v>
       </c>
       <c r="F362" t="n">
         <v>536757</v>
@@ -7692,16 +7692,16 @@
         <v>44844</v>
       </c>
       <c r="B364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="C364" t="n">
-        <v>10.98359394073486</v>
+        <v>10.98359298706055</v>
       </c>
       <c r="D364" t="n">
-        <v>10.55156279823885</v>
+        <v>10.55156188207657</v>
       </c>
       <c r="E364" t="n">
-        <v>10.64295421014203</v>
+        <v>10.6429532860445</v>
       </c>
       <c r="F364" 